--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music</v>
       </c>
       <c r="B2" t="str">
-        <v>8 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=KdsHxyl4bE8</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>8 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>4:58</v>
@@ -477,7 +477,7 @@
         <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield CA (2026)</v>
       </c>
       <c r="B3" t="str">
-        <v>8 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=Mwkl_Cz_SG8</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>8 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>5:08</v>
@@ -515,7 +515,7 @@
         <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered)</v>
       </c>
       <c r="B4" t="str">
-        <v>10 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=I7a-pDZFE7U</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>10 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>4:38</v>
@@ -553,7 +553,7 @@
         <v>Jessie Ware - I Could Get Used To This (Live on The Graham Norton Show)</v>
       </c>
       <c r="B5" t="str">
-        <v>17 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=kGeamxRf8Gw</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>17 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>3:50</v>
@@ -2260,7 +2260,7 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
       </c>
       <c r="B50" t="str">
         <v>8 days ago</v>
@@ -2293,7 +2293,7 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992 - OfficiallyExtreme</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
       </c>
     </row>
     <row r="51">
@@ -3099,7 +3099,7 @@
         <v>Lauren Sanderson - SPELL IT OUT (Official Music Video)</v>
       </c>
       <c r="B72" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C72" t="str">
         <v>https://www.youtube.com/watch?v=kfF0bVZMCw0</v>
@@ -3111,7 +3111,7 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G72" t="str">
         <v>2:34</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music</v>
       </c>
       <c r="B2" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=KdsHxyl4bE8</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>4:58</v>
@@ -477,7 +477,7 @@
         <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield CA (2026)</v>
       </c>
       <c r="B3" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=Mwkl_Cz_SG8</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>5:08</v>
@@ -515,7 +515,7 @@
         <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered)</v>
       </c>
       <c r="B4" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=I7a-pDZFE7U</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>4:38</v>
@@ -553,7 +553,7 @@
         <v>Jessie Ware - I Could Get Used To This (Live on The Graham Norton Show)</v>
       </c>
       <c r="B5" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=kGeamxRf8Gw</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>3:50</v>
@@ -1009,7 +1009,7 @@
         <v>Ella Langley - Dandelion (Official Visualizer)</v>
       </c>
       <c r="B17" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=sf6eRmInk1s</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G17" t="str">
         <v>4:01</v>
@@ -1047,7 +1047,7 @@
         <v>Dogpark - Dandelion (Official Music Video)</v>
       </c>
       <c r="B18" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=fv9prIYHHzk</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G18" t="str">
         <v>3:16</v>
@@ -1085,7 +1085,7 @@
         <v>Lauren Spencer Smith - Natural Disaster (Visualizer)</v>
       </c>
       <c r="B19" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=T9YvLA2cdZs</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G19" t="str">
         <v>3:03</v>
@@ -1123,7 +1123,7 @@
         <v>ERNEST - Lorelei (Official Music Video)</v>
       </c>
       <c r="B20" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=dPWc_6IdDJk</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G20" t="str">
         <v>2:41</v>
@@ -1161,7 +1161,7 @@
         <v>Labrinth - I Keep My Promises (Official Audio)</v>
       </c>
       <c r="B21" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=CV5rR9JZK-0</v>
@@ -1173,7 +1173,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G21" t="str">
         <v>3:05</v>
@@ -1199,7 +1199,7 @@
         <v>Grace VanderWaal - Prettier (Official Lyric Video)</v>
       </c>
       <c r="B22" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=9HwTj3NZ16E</v>
@@ -1211,7 +1211,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G22" t="str">
         <v>2:46</v>
@@ -1237,7 +1237,7 @@
         <v>VOILÀ - Frozen Lake (Official Lyric Video)</v>
       </c>
       <c r="B23" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=Lmus-UbL1H0</v>
@@ -1249,7 +1249,7 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G23" t="str">
         <v>3:32</v>
@@ -1275,7 +1275,7 @@
         <v>Cannons - Starlight (Official Video)</v>
       </c>
       <c r="B24" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=bu6WSMDDPGY</v>
@@ -1287,7 +1287,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G24" t="str">
         <v>3:42</v>
@@ -1313,7 +1313,7 @@
         <v>Kylie Morgan - Like My Own (Official Video)</v>
       </c>
       <c r="B25" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=zcYeoGBglC0</v>
@@ -1325,7 +1325,7 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G25" t="str">
         <v>2:38</v>
@@ -1351,7 +1351,7 @@
         <v>Lizzy McAlpine - House of the Rising Sun (Audio)</v>
       </c>
       <c r="B26" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=3igYRj82EiU</v>
@@ -1363,7 +1363,7 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G26" t="str">
         <v>3:10</v>
@@ -1389,7 +1389,7 @@
         <v>Willie Nelson - Heart Of America (From The Gray House Original Soundtrack)</v>
       </c>
       <c r="B27" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C27" t="str">
         <v>https://www.youtube.com/watch?v=0bhcO4Yphuo</v>
@@ -1401,7 +1401,7 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G27" t="str">
         <v>3:57</v>
@@ -1427,7 +1427,7 @@
         <v>Jeremy Camp - No Survivors (Live) ft. Skillet</v>
       </c>
       <c r="B28" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=Jjz1wFe5dMo</v>
@@ -1439,7 +1439,7 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G28" t="str">
         <v>2:19</v>
@@ -2415,7 +2415,7 @@
         <v>Bella White - Dream Song (Official Audio)</v>
       </c>
       <c r="B54" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C54" t="str">
         <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
@@ -2427,7 +2427,7 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G54" t="str">
         <v>4:37</v>
@@ -2453,7 +2453,7 @@
         <v>Ryan Wright - Film School Kids (Official Video)</v>
       </c>
       <c r="B55" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C55" t="str">
         <v>https://www.youtube.com/watch?v=pnAz9RwGSek</v>
@@ -2465,7 +2465,7 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G55" t="str">
         <v>4:06</v>
@@ -2491,7 +2491,7 @@
         <v>Dove Cameron - Do I Wanna Know? (Official Visualizer)</v>
       </c>
       <c r="B56" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C56" t="str">
         <v>https://www.youtube.com/watch?v=u7aPv2saz_I</v>
@@ -2503,7 +2503,7 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G56" t="str">
         <v>3:54</v>
@@ -2529,7 +2529,7 @@
         <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video)</v>
       </c>
       <c r="B57" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C57" t="str">
         <v>https://www.youtube.com/watch?v=WGb8KVdqs6k</v>
@@ -2541,7 +2541,7 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G57" t="str">
         <v>4:10</v>
@@ -2567,7 +2567,7 @@
         <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video)</v>
       </c>
       <c r="B58" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C58" t="str">
         <v>https://www.youtube.com/watch?v=X1ZeY4Y3l1M</v>
@@ -2579,7 +2579,7 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G58" t="str">
         <v>3:26</v>
@@ -2643,7 +2643,7 @@
         <v>Mitchell Tenpenny - You Phase (Official Music Video)</v>
       </c>
       <c r="B60" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C60" t="str">
         <v>https://www.youtube.com/watch?v=UPuK6wV5Zco</v>
@@ -2655,7 +2655,7 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G60" t="str">
         <v>2:56</v>
@@ -2681,7 +2681,7 @@
         <v>Tauren Wells - Breathe On It (Official Lyric Video)</v>
       </c>
       <c r="B61" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C61" t="str">
         <v>https://www.youtube.com/watch?v=9hW9sNMn2A0</v>
@@ -2693,7 +2693,7 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G61" t="str">
         <v>4:01</v>
@@ -2719,7 +2719,7 @@
         <v>Maiah Manser - Feeling it All (Official Music Video)</v>
       </c>
       <c r="B62" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C62" t="str">
         <v>https://www.youtube.com/watch?v=JMYvXleIwfU</v>
@@ -2731,7 +2731,7 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G62" t="str">
         <v>3:05</v>
@@ -2757,7 +2757,7 @@
         <v>Taylor Austin Dye - Man For That (Official Music Video)</v>
       </c>
       <c r="B63" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C63" t="str">
         <v>https://www.youtube.com/watch?v=vOzX-o11seI</v>
@@ -2769,7 +2769,7 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G63" t="str">
         <v>2:27</v>
@@ -2795,7 +2795,7 @@
         <v>Chelsea Cutler - BAD (Official Video)</v>
       </c>
       <c r="B64" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C64" t="str">
         <v>https://www.youtube.com/watch?v=86k4E6ydHVU</v>
@@ -2807,7 +2807,7 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G64" t="str">
         <v>2:34</v>
@@ -2833,7 +2833,7 @@
         <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video)</v>
       </c>
       <c r="B65" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C65" t="str">
         <v>https://www.youtube.com/watch?v=-UWIFAiOOPE</v>
@@ -2845,7 +2845,7 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G65" t="str">
         <v>3:13</v>
@@ -2871,7 +2871,7 @@
         <v>Louis Tomlinson - Dark To Light (Visualiser)</v>
       </c>
       <c r="B66" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C66" t="str">
         <v>https://www.youtube.com/watch?v=02QyA29poAM</v>
@@ -2883,7 +2883,7 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G66" t="str">
         <v>3:13</v>
@@ -2909,7 +2909,7 @@
         <v>CAIN - So Long Sad Songs (Lyric Video)</v>
       </c>
       <c r="B67" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C67" t="str">
         <v>https://www.youtube.com/watch?v=feOv8nufa_I</v>
@@ -2921,7 +2921,7 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G67" t="str">
         <v>3:08</v>
@@ -3213,7 +3213,7 @@
         <v>The Avett Brothers - Matrimony (Official Video)</v>
       </c>
       <c r="B75" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C75" t="str">
         <v>https://www.youtube.com/watch?v=7sD9-MtV9CY</v>
@@ -3225,7 +3225,7 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G75" t="str">
         <v>3:06</v>
@@ -3251,7 +3251,7 @@
         <v>Jordana Bryant - Love Like That (Official Video)</v>
       </c>
       <c r="B76" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C76" t="str">
         <v>https://www.youtube.com/watch?v=3ATlH-Rtzmk</v>
@@ -3263,7 +3263,7 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G76" t="str">
         <v>3:21</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music</v>
       </c>
       <c r="B2" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=KdsHxyl4bE8</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>4:58</v>
@@ -477,7 +477,7 @@
         <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield CA (2026)</v>
       </c>
       <c r="B3" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=Mwkl_Cz_SG8</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>5:08</v>
@@ -515,7 +515,7 @@
         <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered)</v>
       </c>
       <c r="B4" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=I7a-pDZFE7U</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>4:38</v>
@@ -553,7 +553,7 @@
         <v>Jessie Ware - I Could Get Used To This (Live on The Graham Norton Show)</v>
       </c>
       <c r="B5" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=kGeamxRf8Gw</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>3:50</v>
@@ -971,7 +971,7 @@
         <v>SANTOS BRAVOS “KAWASAKI” Performance Video</v>
       </c>
       <c r="B16" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=Cmy8CsYIUL0</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G16" t="str">
         <v>2:41</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music</v>
       </c>
       <c r="B2" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=KdsHxyl4bE8</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>4:58</v>
@@ -477,7 +477,7 @@
         <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield CA (2026)</v>
       </c>
       <c r="B3" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=Mwkl_Cz_SG8</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>5:08</v>
@@ -515,7 +515,7 @@
         <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered)</v>
       </c>
       <c r="B4" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=I7a-pDZFE7U</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>4:38</v>
@@ -553,7 +553,7 @@
         <v>Jessie Ware - I Could Get Used To This (Live on The Graham Norton Show)</v>
       </c>
       <c r="B5" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=kGeamxRf8Gw</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>3:50</v>
@@ -895,7 +895,7 @@
         <v>Katelyn Tarver - So Am I (Official Music Video)</v>
       </c>
       <c r="B14" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=MjUiVPzMQHw</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G14" t="str">
         <v>2:52</v>
@@ -933,7 +933,7 @@
         <v>David Guetta, TeddySwims, Tones And I - Gone Gone Gone (Unplugged) [Visualizer]</v>
       </c>
       <c r="B15" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=eWglDE7O5r8</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G15" t="str">
         <v>3:33</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music</v>
       </c>
       <c r="B2" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=KdsHxyl4bE8</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>4:58</v>
@@ -477,7 +477,7 @@
         <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield CA (2026)</v>
       </c>
       <c r="B3" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=Mwkl_Cz_SG8</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>5:08</v>
@@ -515,7 +515,7 @@
         <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered)</v>
       </c>
       <c r="B4" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=I7a-pDZFE7U</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>4:38</v>
@@ -553,7 +553,7 @@
         <v>Jessie Ware - I Could Get Used To This (Live on The Graham Norton Show)</v>
       </c>
       <c r="B5" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=kGeamxRf8Gw</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G5" t="str">
         <v>3:50</v>
@@ -819,7 +819,7 @@
         <v>Zara Larsson - Lush Life (Official UGC Compilation Video)</v>
       </c>
       <c r="B12" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=FgAyfRnbbRs</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G12" t="str">
         <v>3:22</v>
@@ -857,7 +857,7 @@
         <v>Only The Poets - Monumental</v>
       </c>
       <c r="B13" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=nwXiAjjl6NE</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G13" t="str">
         <v>2:48</v>
@@ -1959,7 +1959,7 @@
         <v>We Three - Drunk Driving (Official Music Video)</v>
       </c>
       <c r="B42" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C42" t="str">
         <v>https://www.youtube.com/watch?v=BTqRGxSX6AQ</v>
@@ -1971,7 +1971,7 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G42" t="str">
         <v>4:27</v>
@@ -2377,7 +2377,7 @@
         <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
       </c>
       <c r="B53" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C53" t="str">
         <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
@@ -2389,7 +2389,7 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G53" t="str">
         <v>3:46</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music</v>
       </c>
       <c r="B2" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=KdsHxyl4bE8</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>4:58</v>
@@ -477,7 +477,7 @@
         <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield CA (2026)</v>
       </c>
       <c r="B3" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=Mwkl_Cz_SG8</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>5:08</v>
@@ -515,7 +515,7 @@
         <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered)</v>
       </c>
       <c r="B4" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=I7a-pDZFE7U</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>4:38</v>
@@ -781,7 +781,7 @@
         <v>Paris Paloma - Good Girl [Official Music Video]</v>
       </c>
       <c r="B11" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=qhO6VMC-nx0</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G11" t="str">
         <v>4:47</v>
@@ -2339,7 +2339,7 @@
         <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
       </c>
       <c r="B52" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C52" t="str">
         <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
@@ -2351,7 +2351,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G52" t="str">
         <v>2:56</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music</v>
       </c>
       <c r="B2" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=KdsHxyl4bE8</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>4:58</v>
@@ -477,7 +477,7 @@
         <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield CA (2026)</v>
       </c>
       <c r="B3" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=Mwkl_Cz_SG8</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>5:08</v>
@@ -515,7 +515,7 @@
         <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered)</v>
       </c>
       <c r="B4" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=I7a-pDZFE7U</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>4:38</v>
@@ -2301,7 +2301,7 @@
         <v>Holly Humberstone - To Love Somebody (Official Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C51" t="str">
         <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
@@ -2313,7 +2313,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G51" t="str">
         <v>3:59</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music</v>
       </c>
       <c r="B2" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=KdsHxyl4bE8</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>4:58</v>
@@ -477,7 +477,7 @@
         <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield CA (2026)</v>
       </c>
       <c r="B3" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=Mwkl_Cz_SG8</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>5:08</v>
@@ -515,7 +515,7 @@
         <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered)</v>
       </c>
       <c r="B4" t="str">
-        <v>19 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=I7a-pDZFE7U</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>19 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>4:38</v>
@@ -743,7 +743,7 @@
         <v>The Kiffness &amp; Matisyahu - ONE DAY (ft. Andel and Nalyn) [OFFICIAL VIDEO]</v>
       </c>
       <c r="B10" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=buS21tVq5r0</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G10" t="str">
         <v>3:07</v>
@@ -3023,7 +3023,7 @@
         <v>DEF LEPPARD - Rejoice (Official Lyric Video)</v>
       </c>
       <c r="B70" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C70" t="str">
         <v>https://www.youtube.com/watch?v=zy2TLLeNgp0</v>
@@ -3035,7 +3035,7 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G70" t="str">
         <v>4:21</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music</v>
       </c>
       <c r="B2" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=KdsHxyl4bE8</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>4:58</v>
@@ -477,7 +477,7 @@
         <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield CA (2026)</v>
       </c>
       <c r="B3" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=Mwkl_Cz_SG8</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>5:08</v>
@@ -515,7 +515,7 @@
         <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered)</v>
       </c>
       <c r="B4" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=I7a-pDZFE7U</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>4:38</v>
@@ -705,7 +705,7 @@
         <v>The Cure - Boys Don't Cry (86 Mix) (Official Lyric Video)</v>
       </c>
       <c r="B9" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=isNztTjXQsQ</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G9" t="str">
         <v>2:39</v>
@@ -1997,7 +1997,7 @@
         <v>Timebelle - Top of the World (Mood Video)</v>
       </c>
       <c r="B43" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C43" t="str">
         <v>https://www.youtube.com/watch?v=r9KyYK_E34s</v>
@@ -2009,7 +2009,7 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G43" t="str">
         <v>3:01</v>
@@ -3175,7 +3175,7 @@
         <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel)</v>
       </c>
       <c r="B74" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C74" t="str">
         <v>https://www.youtube.com/watch?v=fo_j8Fqag8I</v>
@@ -3187,7 +3187,7 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G74" t="str">
         <v>3:21</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music</v>
       </c>
       <c r="B2" t="str">
-        <v>19 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=KdsHxyl4bE8</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>19 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>4:58</v>
@@ -477,7 +477,7 @@
         <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield CA (2026)</v>
       </c>
       <c r="B3" t="str">
-        <v>19 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=Mwkl_Cz_SG8</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>19 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>5:08</v>
@@ -515,7 +515,7 @@
         <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered)</v>
       </c>
       <c r="B4" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=I7a-pDZFE7U</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>4:38</v>
@@ -629,7 +629,7 @@
         <v>Dean Lewis - I Am Getting Well (Lyric Video)</v>
       </c>
       <c r="B7" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=6ecgOSOMWzc</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G7" t="str">
         <v>2:44</v>
@@ -667,7 +667,7 @@
         <v>Take That - Take That and Party (Official HD Video)</v>
       </c>
       <c r="B8" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=DAerJcerikU</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G8" t="str">
         <v>2:57</v>
@@ -1883,7 +1883,7 @@
         <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video)</v>
       </c>
       <c r="B40" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=yUAvfo8fpuU</v>
@@ -1895,7 +1895,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G40" t="str">
         <v>3:50</v>
@@ -1921,7 +1921,7 @@
         <v>I Explained "HOW MUSIC WORKS" Live To 1500 People</v>
       </c>
       <c r="B41" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=KnsBdAM3HqY</v>
@@ -1933,7 +1933,7 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G41" t="str">
         <v>5:32</v>
@@ -3137,7 +3137,7 @@
         <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show]</v>
       </c>
       <c r="B73" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C73" t="str">
         <v>https://www.youtube.com/watch?v=dLzpNstMHZY</v>
@@ -3149,7 +3149,7 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G73" t="str">
         <v>3:10</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music</v>
       </c>
       <c r="B2" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=KdsHxyl4bE8</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>4:58</v>
@@ -477,7 +477,7 @@
         <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield CA (2026)</v>
       </c>
       <c r="B3" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=Mwkl_Cz_SG8</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>5:08</v>
@@ -515,7 +515,7 @@
         <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered)</v>
       </c>
       <c r="B4" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=I7a-pDZFE7U</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>4:38</v>
@@ -591,7 +591,7 @@
         <v>JOSEPH - Water in the Room (Official Music Video)</v>
       </c>
       <c r="B6" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=tNmT47k6MjM</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G6" t="str">
         <v>3:10</v>
@@ -1918,7 +1918,7 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>I Explained "HOW MUSIC WORKS" Live To 1500 People</v>
+        <v>I Explained "How Music Works" LIVE At My Concert</v>
       </c>
       <c r="B41" t="str">
         <v>4 days ago</v>
@@ -1951,7 +1951,7 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>I Explained "HOW MUSIC WORKS" Live To 1500 People - Marcin</v>
+        <v>I Explained "How Music Works" LIVE At My Concert - Marcin</v>
       </c>
     </row>
     <row r="42">

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music</v>
       </c>
       <c r="B2" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=KdsHxyl4bE8</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>4:58</v>
@@ -477,7 +477,7 @@
         <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield CA (2026)</v>
       </c>
       <c r="B3" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=Mwkl_Cz_SG8</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>5:08</v>
@@ -515,7 +515,7 @@
         <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered)</v>
       </c>
       <c r="B4" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=I7a-pDZFE7U</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G4" t="str">
         <v>4:38</v>
@@ -1693,7 +1693,7 @@
         <v>Beck - Love (Audio)</v>
       </c>
       <c r="B35" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=ByABj3Xof1I</v>
@@ -1705,7 +1705,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G35" t="str">
         <v>3:14</v>
@@ -1845,7 +1845,7 @@
         <v>Lights - COME GET YOUR GIRL</v>
       </c>
       <c r="B39" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=EhzX2y5MpSM</v>
@@ -1857,7 +1857,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G39" t="str">
         <v>3:52</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music</v>
       </c>
       <c r="B2" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=KdsHxyl4bE8</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>4:58</v>
@@ -477,7 +477,7 @@
         <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield CA (2026)</v>
       </c>
       <c r="B3" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=Mwkl_Cz_SG8</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>5:08</v>
@@ -1655,7 +1655,7 @@
         <v>Teddy Swims - Need You More (Live - Green Room Sessions)</v>
       </c>
       <c r="B34" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=1ugf5aaY4pY</v>
@@ -1667,7 +1667,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G34" t="str">
         <v>3:16</v>
@@ -1769,7 +1769,7 @@
         <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show</v>
       </c>
       <c r="B37" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C37" t="str">
         <v>https://www.youtube.com/watch?v=ylifHFJWJ_c</v>
@@ -1781,7 +1781,7 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G37" t="str">
         <v>4:10</v>
@@ -1807,7 +1807,7 @@
         <v>Jason Derulo - Sexy For Me [Official Music Video]</v>
       </c>
       <c r="B38" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=9ST-eBNL0NU</v>
@@ -1819,7 +1819,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G38" t="str">
         <v>2:10</v>
@@ -2225,7 +2225,7 @@
         <v>Neal Francis - Back It Up (Live At The Salt Shed)</v>
       </c>
       <c r="B49" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C49" t="str">
         <v>https://www.youtube.com/watch?v=46iZEdsxjC0</v>
@@ -2237,7 +2237,7 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G49" t="str">
         <v>5:01</v>
@@ -2263,7 +2263,7 @@
         <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
       </c>
       <c r="B50" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C50" t="str">
         <v>https://www.youtube.com/watch?v=K2nG1Uukz7E</v>
@@ -2275,7 +2275,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G50" t="str">
         <v>4:12</v>
@@ -3365,7 +3365,7 @@
         <v>Just A Mess (Live acoustic studio session)</v>
       </c>
       <c r="B79" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C79" t="str">
         <v>https://www.youtube.com/watch?v=ShW-I63KD8w</v>
@@ -3377,7 +3377,7 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G79" t="str">
         <v>3:45</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music</v>
       </c>
       <c r="B2" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=KdsHxyl4bE8</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G2" t="str">
         <v>4:58</v>
@@ -477,7 +477,7 @@
         <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield CA (2026)</v>
       </c>
       <c r="B3" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=Mwkl_Cz_SG8</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G3" t="str">
         <v>5:08</v>
@@ -1617,7 +1617,7 @@
         <v>Demi Lovato - Ghost (Live)</v>
       </c>
       <c r="B33" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C33" t="str">
         <v>https://www.youtube.com/watch?v=E-ECwdRndVA</v>
@@ -1629,7 +1629,7 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G33" t="str">
         <v>4:05</v>
@@ -1731,7 +1731,7 @@
         <v>The Offspring - Looking Out For #1 | Live in Spokane WA (2026)</v>
       </c>
       <c r="B36" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=2HSbo51EFNg</v>
@@ -1743,7 +1743,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G36" t="str">
         <v>2:57</v>
@@ -2149,7 +2149,7 @@
         <v>Amazon Music presents: Sienna Spiro - You Stole The Show</v>
       </c>
       <c r="B47" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C47" t="str">
         <v>https://www.youtube.com/watch?v=stYIRyCLN4Y</v>
@@ -2161,7 +2161,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G47" t="str">
         <v>3:24</v>
@@ -2187,7 +2187,7 @@
         <v>Harry Styles - Aperture (Official Video)</v>
       </c>
       <c r="B48" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C48" t="str">
         <v>https://www.youtube.com/watch?v=7sxVHYZ_PnA</v>
@@ -2199,7 +2199,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G48" t="str">
         <v>5:52</v>
@@ -2605,7 +2605,7 @@
         <v>Louis Tomlinson - Imposter (Official Video)</v>
       </c>
       <c r="B59" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C59" t="str">
         <v>https://www.youtube.com/watch?v=rzuD5szQhso</v>
@@ -2617,7 +2617,7 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G59" t="str">
         <v>2:56</v>
@@ -2985,7 +2985,7 @@
         <v>Lana Lubany - BAD IDEA (Official Video)</v>
       </c>
       <c r="B69" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C69" t="str">
         <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
@@ -2997,7 +2997,7 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G69" t="str">
         <v>2:59</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
@@ -2111,7 +2111,7 @@
         <v>SIENNA SPIRO - Die On This Hill (Official Music Video)</v>
       </c>
       <c r="B46" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=5RNy_1odv20</v>
@@ -2123,7 +2123,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G46" t="str">
         <v>4:01</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L203"/>
+  <dimension ref="A1:L202"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3061,7 +3061,7 @@
         <v>Dermot Kennedy - Funeral (Official Music Video)</v>
       </c>
       <c r="B71" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C71" t="str">
         <v>https://www.youtube.com/watch?v=JzOUJZPky6o</v>
@@ -3073,7 +3073,7 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G71" t="str">
         <v>4:09</v>
@@ -3327,7 +3327,7 @@
         <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session)</v>
       </c>
       <c r="B78" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C78" t="str">
         <v>https://www.youtube.com/watch?v=oJ-l2ptQwbQ</v>
@@ -3339,7 +3339,7 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G78" t="str">
         <v>3:17</v>
@@ -6098,13 +6098,13 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Too Late</v>
+        <v>Mono (feat. skaiwater)</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/too-late/1866685876</v>
+        <v>https://music.apple.com/us/song/mono-feat-skaiwater/1869130804</v>
       </c>
       <c r="D151" t="str">
         <v>2026-02-01</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>Too Late - EP</v>
+        <v>Mono (feat. skaiwater) - Single</v>
       </c>
       <c r="G151" t="str">
-        <v>2:56</v>
+        <v>2:50</v>
       </c>
       <c r="H151" t="str">
-        <v>Hunter Hayes</v>
+        <v>i-dle</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/hunter-hayes/429231434</v>
+        <v>https://music.apple.com/us/artist/i-dle/1378887586</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/too-late/1866685875</v>
+        <v>https://music.apple.com/us/album/mono-feat-skaiwater/1869130801</v>
       </c>
       <c r="L151" t="str">
-        <v>Too Late - Hunter Hayes</v>
+        <v>Mono (feat. skaiwater) - i-dle</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Mono (feat. skaiwater)</v>
+        <v>Thank You Is Enough</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/mono-feat-skaiwater/1869130804</v>
+        <v>https://music.apple.com/us/song/thank-you-is-enough/1870679042</v>
       </c>
       <c r="D152" t="str">
         <v>2026-02-01</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>Mono (feat. skaiwater) - Single</v>
+        <v>Yo Gabba GabbaLand! (Season 2) [Apple TV+ Original Series Soundtrack]</v>
       </c>
       <c r="G152" t="str">
-        <v>2:50</v>
+        <v>1:55</v>
       </c>
       <c r="H152" t="str">
-        <v>i-dle</v>
+        <v>Yo Gabba Gabba</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/i-dle/1378887586</v>
+        <v>https://music.apple.com/us/artist/yo-gabba-gabba/433108373</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/mono-feat-skaiwater/1869130801</v>
+        <v>https://music.apple.com/us/album/thank-you-is-enough/1870678950</v>
       </c>
       <c r="L152" t="str">
-        <v>Mono (feat. skaiwater) - i-dle</v>
+        <v>Thank You Is Enough - Yo Gabba Gabba</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Thank You Is Enough</v>
+        <v>RIDIN</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/thank-you-is-enough/1870679042</v>
+        <v>https://music.apple.com/us/song/ridin/1869786726</v>
       </c>
       <c r="D153" t="str">
         <v>2026-02-01</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Yo Gabba GabbaLand! (Season 2) [Apple TV+ Original Series Soundtrack]</v>
+        <v>RIDIN - Single</v>
       </c>
       <c r="G153" t="str">
-        <v>1:55</v>
+        <v>2:00</v>
       </c>
       <c r="H153" t="str">
-        <v>Yo Gabba Gabba</v>
+        <v>Tokischa</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/yo-gabba-gabba/433108373</v>
+        <v>https://music.apple.com/us/artist/tokischa/1414103446</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/thank-you-is-enough/1870678950</v>
+        <v>https://music.apple.com/us/album/ridin/1869786725</v>
       </c>
       <c r="L153" t="str">
-        <v>Thank You Is Enough - Yo Gabba Gabba</v>
+        <v>RIDIN - Tokischa</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>RIDIN</v>
+        <v>POSSESSION</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/ridin/1869786726</v>
+        <v>https://music.apple.com/us/song/possession/1872536200</v>
       </c>
       <c r="D154" t="str">
         <v>2026-02-01</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>RIDIN - Single</v>
+        <v>POSSESSION - Single</v>
       </c>
       <c r="G154" t="str">
-        <v>2:00</v>
+        <v>3:07</v>
       </c>
       <c r="H154" t="str">
-        <v>Tokischa</v>
+        <v>Melanie Martinez</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/tokischa/1414103446</v>
+        <v>https://music.apple.com/us/artist/melanie-martinez/993014053</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/ridin/1869786725</v>
+        <v>https://music.apple.com/us/album/possession/1872536199</v>
       </c>
       <c r="L154" t="str">
-        <v>RIDIN - Tokischa</v>
+        <v>POSSESSION - Melanie Martinez</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>POSSESSION</v>
+        <v>Poema</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/possession/1872536200</v>
+        <v>https://music.apple.com/us/song/poema/1872723644</v>
       </c>
       <c r="D155" t="str">
         <v>2026-02-01</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>POSSESSION - Single</v>
+        <v>Poema - Single</v>
       </c>
       <c r="G155" t="str">
-        <v>3:07</v>
+        <v>3:14</v>
       </c>
       <c r="H155" t="str">
-        <v>Melanie Martinez</v>
+        <v>Óscar Maydon</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/melanie-martinez/993014053</v>
+        <v>https://music.apple.com/us/artist/%C3%B3scar-maydon/1524147696</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/possession/1872536199</v>
+        <v>https://music.apple.com/us/album/poema/1872723468</v>
       </c>
       <c r="L155" t="str">
-        <v>POSSESSION - Melanie Martinez</v>
+        <v>Poema - Óscar Maydon</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Poema</v>
+        <v>Live Without</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/poema/1872723644</v>
+        <v>https://music.apple.com/us/song/live-without/1862777625</v>
       </c>
       <c r="D156" t="str">
         <v>2026-02-01</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>Poema - Single</v>
+        <v>WORRIED SICK (Deluxe Edition)</v>
       </c>
       <c r="G156" t="str">
-        <v>3:14</v>
+        <v>2:55</v>
       </c>
       <c r="H156" t="str">
-        <v>Óscar Maydon</v>
+        <v>Meet Me @ The Altar</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/%C3%B3scar-maydon/1524147696</v>
+        <v>https://music.apple.com/us/artist/meet-me-the-altar/1109900880</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/poema/1872723468</v>
+        <v>https://music.apple.com/us/album/live-without/1862777608</v>
       </c>
       <c r="L156" t="str">
-        <v>Poema - Óscar Maydon</v>
+        <v>Live Without - Meet Me @ The Altar</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Live Without</v>
+        <v>FANÁTICO</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/live-without/1862777625</v>
+        <v>https://music.apple.com/us/song/fan%C3%A1tico/1871611852</v>
       </c>
       <c r="D157" t="str">
         <v>2026-02-01</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>WORRIED SICK (Deluxe Edition)</v>
+        <v>FANÁTICO - Single</v>
       </c>
       <c r="G157" t="str">
-        <v>2:55</v>
+        <v>3:55</v>
       </c>
       <c r="H157" t="str">
-        <v>Meet Me @ The Altar</v>
+        <v>Blessd</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/meet-me-the-altar/1109900880</v>
+        <v>https://music.apple.com/us/artist/blessd/1481245915</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/live-without/1862777608</v>
+        <v>https://music.apple.com/us/album/fan%C3%A1tico/1871611851</v>
       </c>
       <c r="L157" t="str">
-        <v>Live Without - Meet Me @ The Altar</v>
+        <v>FANÁTICO - Blessd</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>FANÁTICO</v>
+        <v>Frozen Lake</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/fan%C3%A1tico/1871611852</v>
+        <v>https://music.apple.com/us/song/frozen-lake/1867287070</v>
       </c>
       <c r="D158" t="str">
         <v>2026-02-01</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>FANÁTICO - Single</v>
+        <v>Frozen Lake - Single</v>
       </c>
       <c r="G158" t="str">
-        <v>3:55</v>
+        <v>3:29</v>
       </c>
       <c r="H158" t="str">
-        <v>Blessd</v>
+        <v>VOILÀ</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/blessd/1481245915</v>
+        <v>https://music.apple.com/us/artist/voil%C3%A0/1333272109</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/fan%C3%A1tico/1871611851</v>
+        <v>https://music.apple.com/us/album/frozen-lake/1867287069</v>
       </c>
       <c r="L158" t="str">
-        <v>FANÁTICO - Blessd</v>
+        <v>Frozen Lake - VOILÀ</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Frozen Lake</v>
+        <v>Fine Shyt (EB Remix) [feat. Eric Bellinger]</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/frozen-lake/1867287070</v>
+        <v>https://music.apple.com/us/song/fine-shyt-eb-remix-feat-eric-bellinger/1870964385</v>
       </c>
       <c r="D159" t="str">
         <v>2026-02-01</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>Frozen Lake - Single</v>
+        <v>Fine Shyt (EB Remix) [feat. Eric Bellinger] - Single</v>
       </c>
       <c r="G159" t="str">
-        <v>3:29</v>
+        <v>2:45</v>
       </c>
       <c r="H159" t="str">
-        <v>VOILÀ</v>
+        <v>VEDO</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/voil%C3%A0/1333272109</v>
+        <v>https://music.apple.com/us/artist/vedo/267769510</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/frozen-lake/1867287069</v>
+        <v>https://music.apple.com/us/album/fine-shyt-eb-remix-feat-eric-bellinger/1870964384</v>
       </c>
       <c r="L159" t="str">
-        <v>Frozen Lake - VOILÀ</v>
+        <v>Fine Shyt (EB Remix) [feat. Eric Bellinger] - VEDO</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Fine Shyt (EB Remix) [feat. Eric Bellinger]</v>
+        <v>Hell Yeah (Feat. Waxmaster)</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/fine-shyt-eb-remix-feat-eric-bellinger/1870964385</v>
+        <v>https://music.apple.com/us/song/hell-yeah-feat-waxmaster/1866602820</v>
       </c>
       <c r="D160" t="str">
         <v>2026-02-01</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>Fine Shyt (EB Remix) [feat. Eric Bellinger] - Single</v>
+        <v>Hell Yeah (Feat. Waxmaster) - Single</v>
       </c>
       <c r="G160" t="str">
-        <v>2:45</v>
+        <v>3:32</v>
       </c>
       <c r="H160" t="str">
-        <v>VEDO</v>
+        <v>Chris Lorenzo</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/vedo/267769510</v>
+        <v>https://music.apple.com/us/artist/chris-lorenzo/621431022</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/fine-shyt-eb-remix-feat-eric-bellinger/1870964384</v>
+        <v>https://music.apple.com/us/album/hell-yeah-feat-waxmaster/1866602819</v>
       </c>
       <c r="L160" t="str">
-        <v>Fine Shyt (EB Remix) [feat. Eric Bellinger] - VEDO</v>
+        <v>Hell Yeah (Feat. Waxmaster) - Chris Lorenzo</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Hell Yeah (Feat. Waxmaster)</v>
+        <v>It’s Like That</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/hell-yeah-feat-waxmaster/1866602820</v>
+        <v>https://music.apple.com/us/song/its-like-that/1858689757</v>
       </c>
       <c r="D161" t="str">
         <v>2026-02-01</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>Hell Yeah (Feat. Waxmaster) - Single</v>
+        <v>A Pound of Feathers</v>
       </c>
       <c r="G161" t="str">
-        <v>3:32</v>
+        <v>3:20</v>
       </c>
       <c r="H161" t="str">
-        <v>Chris Lorenzo</v>
+        <v>The Black Crowes</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/chris-lorenzo/621431022</v>
+        <v>https://music.apple.com/us/artist/the-black-crowes/2969371</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/hell-yeah-feat-waxmaster/1866602819</v>
+        <v>https://music.apple.com/us/album/its-like-that/1858689485</v>
       </c>
       <c r="L161" t="str">
-        <v>Hell Yeah (Feat. Waxmaster) - Chris Lorenzo</v>
+        <v>It’s Like That - The Black Crowes</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>It’s Like That</v>
+        <v>A.S.A.P.</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/its-like-that/1858689757</v>
+        <v>https://music.apple.com/us/song/a-s-a-p/1833414737</v>
       </c>
       <c r="D162" t="str">
         <v>2026-02-01</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>A Pound of Feathers</v>
+        <v>A.S.A.P. - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>3:20</v>
+        <v>2:48</v>
       </c>
       <c r="H162" t="str">
-        <v>The Black Crowes</v>
+        <v>Mýa</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/the-black-crowes/2969371</v>
+        <v>https://music.apple.com/us/artist/m%C3%BDa/108751</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/its-like-that/1858689485</v>
+        <v>https://music.apple.com/us/album/a-s-a-p/1833414736</v>
       </c>
       <c r="L162" t="str">
-        <v>It’s Like That - The Black Crowes</v>
+        <v>A.S.A.P. - Mýa</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>A.S.A.P.</v>
+        <v>Once I Say</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/a-s-a-p/1833414737</v>
+        <v>https://music.apple.com/us/song/once-i-say/1867855025</v>
       </c>
       <c r="D163" t="str">
         <v>2026-02-01</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>A.S.A.P. - Single</v>
+        <v>PASSION</v>
       </c>
       <c r="G163" t="str">
-        <v>2:48</v>
+        <v>3:21</v>
       </c>
       <c r="H163" t="str">
-        <v>Mýa</v>
+        <v>Terrace Martin</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/m%C3%BDa/108751</v>
+        <v>https://music.apple.com/us/artist/terrace-martin/27522754</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/a-s-a-p/1833414736</v>
+        <v>https://music.apple.com/us/album/once-i-say/1867854756</v>
       </c>
       <c r="L163" t="str">
-        <v>A.S.A.P. - Mýa</v>
+        <v>Once I Say - Terrace Martin</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Once I Say</v>
+        <v>believer</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/once-i-say/1867855025</v>
+        <v>https://music.apple.com/us/song/believer/1862797080</v>
       </c>
       <c r="D164" t="str">
         <v>2026-02-01</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>PASSION</v>
+        <v>believer - Single</v>
       </c>
       <c r="G164" t="str">
-        <v>3:21</v>
+        <v>2:57</v>
       </c>
       <c r="H164" t="str">
-        <v>Terrace Martin</v>
+        <v>Yuna</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/terrace-martin/27522754</v>
+        <v>https://music.apple.com/us/artist/yuna/423966062</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/once-i-say/1867854756</v>
+        <v>https://music.apple.com/us/album/believer/1862796978</v>
       </c>
       <c r="L164" t="str">
-        <v>Once I Say - Terrace Martin</v>
+        <v>believer - Yuna</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>believer</v>
+        <v>I Envy The Wind</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/believer/1862797080</v>
+        <v>https://music.apple.com/us/song/i-envy-the-wind/1863202477</v>
       </c>
       <c r="D165" t="str">
         <v>2026-02-01</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>believer - Single</v>
+        <v>I Envy The Wind - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>2:57</v>
+        <v>3:51</v>
       </c>
       <c r="H165" t="str">
-        <v>Yuna</v>
+        <v>Molly Parden</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/yuna/423966062</v>
+        <v>https://music.apple.com/us/artist/molly-parden/374789677</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/believer/1862796978</v>
+        <v>https://music.apple.com/us/album/i-envy-the-wind/1863202476</v>
       </c>
       <c r="L165" t="str">
-        <v>believer - Yuna</v>
+        <v>I Envy The Wind - Molly Parden</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>I Envy The Wind</v>
+        <v>The Alchemist</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/i-envy-the-wind/1863202477</v>
+        <v>https://music.apple.com/us/song/the-alchemist/1831827347</v>
       </c>
       <c r="D166" t="str">
         <v>2026-02-01</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>I Envy The Wind - Single</v>
+        <v>The Alchemist</v>
       </c>
       <c r="G166" t="str">
-        <v>3:51</v>
+        <v>3:13</v>
       </c>
       <c r="H166" t="str">
-        <v>Molly Parden</v>
+        <v>Bre Kennedy</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/molly-parden/374789677</v>
+        <v>https://music.apple.com/us/artist/bre-kennedy/1242283415</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/i-envy-the-wind/1863202476</v>
+        <v>https://music.apple.com/us/album/the-alchemist/1831827332</v>
       </c>
       <c r="L166" t="str">
-        <v>I Envy The Wind - Molly Parden</v>
+        <v>The Alchemist - Bre Kennedy</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>The Alchemist</v>
+        <v>Daysa</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/the-alchemist/1831827347</v>
+        <v>https://music.apple.com/us/song/daysa/1861575845</v>
       </c>
       <c r="D167" t="str">
         <v>2026-02-01</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>The Alchemist</v>
+        <v>Daysa - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>3:13</v>
+        <v>4:36</v>
       </c>
       <c r="H167" t="str">
-        <v>Bre Kennedy</v>
+        <v>⌭ IceMorph ⌬</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/bre-kennedy/1242283415</v>
+        <v>https://music.apple.com/us/artist/icemorph/1733236411</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/the-alchemist/1831827332</v>
+        <v>https://music.apple.com/us/album/daysa/1861575844</v>
       </c>
       <c r="L167" t="str">
-        <v>The Alchemist - Bre Kennedy</v>
+        <v>Daysa - ⌭ IceMorph ⌬</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Daysa</v>
+        <v>Fabulous</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/daysa/1861575845</v>
+        <v>https://music.apple.com/us/song/fabulous/1862804005</v>
       </c>
       <c r="D168" t="str">
         <v>2026-02-01</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Daysa - Single</v>
+        <v>Fabulous - Single</v>
       </c>
       <c r="G168" t="str">
-        <v>4:36</v>
+        <v>2:33</v>
       </c>
       <c r="H168" t="str">
-        <v>⌭ IceMorph ⌬</v>
+        <v>MEEK</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/icemorph/1733236411</v>
+        <v>https://music.apple.com/us/artist/meek/1784432868</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/daysa/1861575844</v>
+        <v>https://music.apple.com/us/album/fabulous/1862804004</v>
       </c>
       <c r="L168" t="str">
-        <v>Daysa - ⌭ IceMorph ⌬</v>
+        <v>Fabulous - MEEK</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Fabulous</v>
+        <v>Me Asusta Amar Tanto la Soledad</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/fabulous/1862804005</v>
+        <v>https://music.apple.com/us/song/me-asusta-amar-tanto-la-soledad/1866982109</v>
       </c>
       <c r="D169" t="str">
         <v>2026-02-01</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Fabulous - Single</v>
+        <v>Me Asusta Amar Tanto la Soledad - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>2:33</v>
+        <v>3:22</v>
       </c>
       <c r="H169" t="str">
-        <v>MEEK</v>
+        <v>RUBIO</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/meek/1784432868</v>
+        <v>https://music.apple.com/us/artist/rubio/34747724</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/fabulous/1862804004</v>
+        <v>https://music.apple.com/us/album/me-asusta-amar-tanto-la-soledad/1866981907</v>
       </c>
       <c r="L169" t="str">
-        <v>Fabulous - MEEK</v>
+        <v>Me Asusta Amar Tanto la Soledad - RUBIO</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Me Asusta Amar Tanto la Soledad</v>
+        <v>brainchem</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/me-asusta-amar-tanto-la-soledad/1866982109</v>
+        <v>https://music.apple.com/us/song/brainchem/1870656942</v>
       </c>
       <c r="D170" t="str">
         <v>2026-02-01</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Me Asusta Amar Tanto la Soledad - Single</v>
+        <v>brainchem - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>3:22</v>
+        <v>2:28</v>
       </c>
       <c r="H170" t="str">
-        <v>RUBIO</v>
+        <v>EMJAY</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/rubio/34747724</v>
+        <v>https://music.apple.com/us/artist/emjay/1517993423</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/me-asusta-amar-tanto-la-soledad/1866981907</v>
+        <v>https://music.apple.com/us/album/brainchem/1870656608</v>
       </c>
       <c r="L170" t="str">
-        <v>Me Asusta Amar Tanto la Soledad - RUBIO</v>
+        <v>brainchem - EMJAY</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>brainchem</v>
+        <v>Boyfriend In Yo Brain (Notice Me)</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/brainchem/1870656942</v>
+        <v>https://music.apple.com/us/song/boyfriend-in-yo-brain-notice-me/1871675026</v>
       </c>
       <c r="D171" t="str">
         <v>2026-02-01</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>brainchem - Single</v>
+        <v>With No Due Respect</v>
       </c>
       <c r="G171" t="str">
-        <v>2:28</v>
+        <v>2:48</v>
       </c>
       <c r="H171" t="str">
-        <v>EMJAY</v>
+        <v>Foggieraw</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/emjay/1517993423</v>
+        <v>https://music.apple.com/us/artist/foggieraw/1152021457</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/brainchem/1870656608</v>
+        <v>https://music.apple.com/us/album/boyfriend-in-yo-brain-notice-me/1871675010</v>
       </c>
       <c r="L171" t="str">
-        <v>brainchem - EMJAY</v>
+        <v>Boyfriend In Yo Brain (Notice Me) - Foggieraw</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Boyfriend In Yo Brain (Notice Me)</v>
+        <v>Giants</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/boyfriend-in-yo-brain-notice-me/1871675026</v>
+        <v>https://music.apple.com/us/song/giants/1869154957</v>
       </c>
       <c r="D172" t="str">
         <v>2026-02-01</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>With No Due Respect</v>
+        <v>Giants - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>2:48</v>
+        <v>3:12</v>
       </c>
       <c r="H172" t="str">
-        <v>Foggieraw</v>
+        <v>Picture This</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/foggieraw/1152021457</v>
+        <v>https://music.apple.com/us/artist/picture-this/1194282721</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/boyfriend-in-yo-brain-notice-me/1871675010</v>
+        <v>https://music.apple.com/us/album/giants/1869154821</v>
       </c>
       <c r="L172" t="str">
-        <v>Boyfriend In Yo Brain (Notice Me) - Foggieraw</v>
+        <v>Giants - Picture This</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Giants</v>
+        <v>Scooby</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/giants/1869154957</v>
+        <v>https://music.apple.com/us/song/scooby/1872510752</v>
       </c>
       <c r="D173" t="str">
         <v>2026-02-01</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Giants - Single</v>
+        <v>Scooby - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>3:12</v>
+        <v>3:41</v>
       </c>
       <c r="H173" t="str">
-        <v>Picture This</v>
+        <v>corook</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/picture-this/1194282721</v>
+        <v>https://music.apple.com/us/artist/corook/1514463762</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/giants/1869154821</v>
+        <v>https://music.apple.com/us/album/scooby/1872510751</v>
       </c>
       <c r="L173" t="str">
-        <v>Giants - Picture This</v>
+        <v>Scooby - corook</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Scooby</v>
+        <v>La Racha</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/scooby/1872510752</v>
+        <v>https://music.apple.com/us/song/la-racha/1868757762</v>
       </c>
       <c r="D174" t="str">
         <v>2026-02-01</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>Scooby - Single</v>
+        <v>La Racha - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>3:41</v>
+        <v>2:48</v>
       </c>
       <c r="H174" t="str">
-        <v>corook</v>
+        <v>Hermanos Espinoza</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/corook/1514463762</v>
+        <v>https://music.apple.com/us/artist/hermanos-espinoza/1613044599</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/scooby/1872510751</v>
+        <v>https://music.apple.com/us/album/la-racha/1868757747</v>
       </c>
       <c r="L174" t="str">
-        <v>Scooby - corook</v>
+        <v>La Racha - Hermanos Espinoza</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>La Racha</v>
+        <v>So Am I</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/la-racha/1868757762</v>
+        <v>https://music.apple.com/us/song/so-am-i/1867012209</v>
       </c>
       <c r="D175" t="str">
         <v>2026-02-01</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>La Racha - Single</v>
+        <v>Tell Me How You Really Feel</v>
       </c>
       <c r="G175" t="str">
-        <v>2:48</v>
+        <v>2:50</v>
       </c>
       <c r="H175" t="str">
-        <v>Hermanos Espinoza</v>
+        <v>Katelyn Tarver</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/hermanos-espinoza/1613044599</v>
+        <v>https://music.apple.com/us/artist/katelyn-tarver/2356378</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/la-racha/1868757747</v>
+        <v>https://music.apple.com/us/album/so-am-i/1867012005</v>
       </c>
       <c r="L175" t="str">
-        <v>La Racha - Hermanos Espinoza</v>
+        <v>So Am I - Katelyn Tarver</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>So Am I</v>
+        <v>best thing</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/so-am-i/1867012209</v>
+        <v>https://music.apple.com/us/song/best-thing/1860673616</v>
       </c>
       <c r="D176" t="str">
         <v>2026-02-01</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Tell Me How You Really Feel</v>
+        <v>best thing - Single</v>
       </c>
       <c r="G176" t="str">
-        <v>2:50</v>
+        <v>4:27</v>
       </c>
       <c r="H176" t="str">
-        <v>Katelyn Tarver</v>
+        <v>WRABEL</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/katelyn-tarver/2356378</v>
+        <v>https://music.apple.com/us/artist/wrabel/435072161</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/so-am-i/1867012005</v>
+        <v>https://music.apple.com/us/album/best-thing/1860673615</v>
       </c>
       <c r="L176" t="str">
-        <v>So Am I - Katelyn Tarver</v>
+        <v>best thing - WRABEL</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>best thing</v>
+        <v>Count It Back</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/best-thing/1860673616</v>
+        <v>https://music.apple.com/us/song/count-it-back/1855219865</v>
       </c>
       <c r="D177" t="str">
         <v>2026-02-01</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>best thing - Single</v>
+        <v>Magic Boy</v>
       </c>
       <c r="G177" t="str">
-        <v>4:27</v>
+        <v>2:52</v>
       </c>
       <c r="H177" t="str">
-        <v>WRABEL</v>
+        <v>Bartees Strange</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/wrabel/435072161</v>
+        <v>https://music.apple.com/us/artist/bartees-strange/1450776625</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/best-thing/1860673615</v>
+        <v>https://music.apple.com/us/album/count-it-back/1855219618</v>
       </c>
       <c r="L177" t="str">
-        <v>best thing - WRABEL</v>
+        <v>Count It Back - Bartees Strange</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Count It Back</v>
+        <v>Good Girl</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/count-it-back/1855219865</v>
+        <v>https://music.apple.com/us/song/good-girl/1862640697</v>
       </c>
       <c r="D178" t="str">
         <v>2026-02-01</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Magic Boy</v>
+        <v>Good Girl - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>2:52</v>
+        <v>4:23</v>
       </c>
       <c r="H178" t="str">
-        <v>Bartees Strange</v>
+        <v>Paris Paloma</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/bartees-strange/1450776625</v>
+        <v>https://music.apple.com/us/artist/paris-paloma/1530898376</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/count-it-back/1855219618</v>
+        <v>https://music.apple.com/us/album/good-girl/1862640694</v>
       </c>
       <c r="L178" t="str">
-        <v>Count It Back - Bartees Strange</v>
+        <v>Good Girl - Paris Paloma</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Good Girl</v>
+        <v>MY REVIVAL</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/good-girl/1862640697</v>
+        <v>https://music.apple.com/us/song/my-revival/1869465104</v>
       </c>
       <c r="D179" t="str">
         <v>2026-02-01</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Good Girl - Single</v>
+        <v>HEARTLAND (Deluxe Version)</v>
       </c>
       <c r="G179" t="str">
-        <v>4:23</v>
+        <v>3:34</v>
       </c>
       <c r="H179" t="str">
-        <v>Paris Paloma</v>
+        <v>MORGXN</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/paris-paloma/1530898376</v>
+        <v>https://music.apple.com/us/artist/morgxn/1116360149</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/good-girl/1862640694</v>
+        <v>https://music.apple.com/us/album/my-revival/1869464853</v>
       </c>
       <c r="L179" t="str">
-        <v>Good Girl - Paris Paloma</v>
+        <v>MY REVIVAL - MORGXN</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>MY REVIVAL</v>
+        <v>Run My Way</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/my-revival/1869465104</v>
+        <v>https://music.apple.com/us/song/run-my-way/1860964996</v>
       </c>
       <c r="D180" t="str">
         <v>2026-02-01</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>HEARTLAND (Deluxe Version)</v>
+        <v>Run My Way - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>3:34</v>
+        <v>2:44</v>
       </c>
       <c r="H180" t="str">
-        <v>MORGXN</v>
+        <v>December 10</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/morgxn/1116360149</v>
+        <v>https://music.apple.com/us/artist/december-10/1414032285</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/my-revival/1869464853</v>
+        <v>https://music.apple.com/us/album/run-my-way/1860964992</v>
       </c>
       <c r="L180" t="str">
-        <v>MY REVIVAL - MORGXN</v>
+        <v>Run My Way - December 10</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Run My Way</v>
+        <v>Cold Night</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/run-my-way/1860964996</v>
+        <v>https://music.apple.com/us/song/cold-night/1867687787</v>
       </c>
       <c r="D181" t="str">
         <v>2026-02-01</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Run My Way - Single</v>
+        <v>Cold Night - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>2:44</v>
+        <v>3:12</v>
       </c>
       <c r="H181" t="str">
-        <v>December 10</v>
+        <v>HANA</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/december-10/1414032285</v>
+        <v>https://music.apple.com/us/artist/hana/1792783458</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/run-my-way/1860964992</v>
+        <v>https://music.apple.com/us/album/cold-night/1867687784</v>
       </c>
       <c r="L181" t="str">
-        <v>Run My Way - December 10</v>
+        <v>Cold Night - HANA</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Cold Night</v>
+        <v>Away With The Fairies</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/cold-night/1867687787</v>
+        <v>https://music.apple.com/us/song/away-with-the-fairies/1870603474</v>
       </c>
       <c r="D182" t="str">
         <v>2026-02-01</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Cold Night - Single</v>
+        <v>Away With The Fairies - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>3:12</v>
+        <v>2:28</v>
       </c>
       <c r="H182" t="str">
-        <v>HANA</v>
+        <v>LUNA</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/hana/1792783458</v>
+        <v>https://music.apple.com/us/artist/luna/1439101807</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/cold-night/1867687784</v>
+        <v>https://music.apple.com/us/album/away-with-the-fairies/1870603470</v>
       </c>
       <c r="L182" t="str">
-        <v>Cold Night - HANA</v>
+        <v>Away With The Fairies - LUNA</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Away With The Fairies</v>
+        <v>Fragile</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/away-with-the-fairies/1870603474</v>
+        <v>https://music.apple.com/us/song/fragile/1866957569</v>
       </c>
       <c r="D183" t="str">
         <v>2026-02-01</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Away With The Fairies - Single</v>
+        <v>Fragile - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>2:28</v>
+        <v>3:10</v>
       </c>
       <c r="H183" t="str">
-        <v>LUNA</v>
+        <v>Anajah</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/luna/1439101807</v>
+        <v>https://music.apple.com/us/artist/anajah/1355166756</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/away-with-the-fairies/1870603470</v>
+        <v>https://music.apple.com/us/album/fragile/1866957565</v>
       </c>
       <c r="L183" t="str">
-        <v>Away With The Fairies - LUNA</v>
+        <v>Fragile - Anajah</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Fragile</v>
+        <v>Slow Dancin'</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/fragile/1866957569</v>
+        <v>https://music.apple.com/us/song/slow-dancin/1871537173</v>
       </c>
       <c r="D184" t="str">
         <v>2026-02-01</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>Fragile - Single</v>
+        <v>Slow Dancin' - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>3:10</v>
+        <v>2:04</v>
       </c>
       <c r="H184" t="str">
-        <v>Anajah</v>
+        <v>STELLA LEFTY</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/anajah/1355166756</v>
+        <v>https://music.apple.com/us/artist/stella-lefty/1641742186</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/fragile/1866957565</v>
+        <v>https://music.apple.com/us/album/slow-dancin/1871537170</v>
       </c>
       <c r="L184" t="str">
-        <v>Fragile - Anajah</v>
+        <v>Slow Dancin' - STELLA LEFTY</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Slow Dancin'</v>
+        <v>Never Kissed a Cowboy</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/slow-dancin/1871537173</v>
+        <v>https://music.apple.com/us/song/never-kissed-a-cowboy/1866744530</v>
       </c>
       <c r="D185" t="str">
         <v>2026-02-01</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>Slow Dancin' - Single</v>
+        <v>Never Kissed a Cowboy - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>2:04</v>
+        <v>3:04</v>
       </c>
       <c r="H185" t="str">
-        <v>STELLA LEFTY</v>
+        <v>Lily Meola</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/stella-lefty/1641742186</v>
+        <v>https://music.apple.com/us/artist/lily-meola/678241726</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/slow-dancin/1871537170</v>
+        <v>https://music.apple.com/us/album/never-kissed-a-cowboy/1866744528</v>
       </c>
       <c r="L185" t="str">
-        <v>Slow Dancin' - STELLA LEFTY</v>
+        <v>Never Kissed a Cowboy - Lily Meola</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Never Kissed a Cowboy</v>
+        <v>More Of What Matters</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/never-kissed-a-cowboy/1866744530</v>
+        <v>https://music.apple.com/us/song/more-of-what-matters/1871592720</v>
       </c>
       <c r="D186" t="str">
         <v>2026-02-01</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Never Kissed a Cowboy - Single</v>
+        <v>More Of What Matters - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>3:04</v>
+        <v>3:41</v>
       </c>
       <c r="H186" t="str">
-        <v>Lily Meola</v>
+        <v>Jamey Johnson</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/lily-meola/678241726</v>
+        <v>https://music.apple.com/us/artist/jamey-johnson/81030634</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/never-kissed-a-cowboy/1866744528</v>
+        <v>https://music.apple.com/us/album/more-of-what-matters/1871592717</v>
       </c>
       <c r="L186" t="str">
-        <v>Never Kissed a Cowboy - Lily Meola</v>
+        <v>More Of What Matters - Jamey Johnson</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>More Of What Matters</v>
+        <v>Is This The Real You</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/more-of-what-matters/1871592720</v>
+        <v>https://music.apple.com/us/song/is-this-the-real-you/1869323368</v>
       </c>
       <c r="D187" t="str">
         <v>2026-02-01</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>More Of What Matters - Single</v>
+        <v>ONE</v>
       </c>
       <c r="G187" t="str">
-        <v>3:41</v>
+        <v>3:46</v>
       </c>
       <c r="H187" t="str">
-        <v>Jamey Johnson</v>
+        <v>Sevendust</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/jamey-johnson/81030634</v>
+        <v>https://music.apple.com/us/artist/sevendust/13125174</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/more-of-what-matters/1871592717</v>
+        <v>https://music.apple.com/us/album/is-this-the-real-you/1869323199</v>
       </c>
       <c r="L187" t="str">
-        <v>More Of What Matters - Jamey Johnson</v>
+        <v>Is This The Real You - Sevendust</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Is This The Real You</v>
+        <v>Hud</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/is-this-the-real-you/1869323368</v>
+        <v>https://music.apple.com/us/song/hud/1842015019</v>
       </c>
       <c r="D188" t="str">
         <v>2026-02-01</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>ONE</v>
+        <v>DREAMCRUSH</v>
       </c>
       <c r="G188" t="str">
-        <v>3:46</v>
+        <v>4:46</v>
       </c>
       <c r="H188" t="str">
-        <v>Sevendust</v>
+        <v>MØL</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/sevendust/13125174</v>
+        <v>https://music.apple.com/us/artist/m%C3%B8l/975294671</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/is-this-the-real-you/1869323199</v>
+        <v>https://music.apple.com/us/album/hud/1842014730</v>
       </c>
       <c r="L188" t="str">
-        <v>Is This The Real You - Sevendust</v>
+        <v>Hud - MØL</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Hud</v>
+        <v>Ego Death</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/hud/1842015019</v>
+        <v>https://music.apple.com/us/song/ego-death/1867855427</v>
       </c>
       <c r="D189" t="str">
         <v>2026-02-01</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>DREAMCRUSH</v>
+        <v>Ego Death - Single</v>
       </c>
       <c r="G189" t="str">
-        <v>4:46</v>
+        <v>2:12</v>
       </c>
       <c r="H189" t="str">
-        <v>MØL</v>
+        <v>Atreyu</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/m%C3%B8l/975294671</v>
+        <v>https://music.apple.com/us/artist/atreyu/6095061</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/hud/1842014730</v>
+        <v>https://music.apple.com/us/album/ego-death/1867855173</v>
       </c>
       <c r="L189" t="str">
-        <v>Hud - MØL</v>
+        <v>Ego Death - Atreyu</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Ego Death</v>
+        <v>Gas Station Love (remix)</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/ego-death/1867855427</v>
+        <v>https://music.apple.com/us/song/gas-station-love-remix/1872150728</v>
       </c>
       <c r="D190" t="str">
         <v>2026-02-01</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Ego Death - Single</v>
+        <v>Gas Station Love (remix) - Single</v>
       </c>
       <c r="G190" t="str">
-        <v>2:12</v>
+        <v>4:05</v>
       </c>
       <c r="H190" t="str">
-        <v>Atreyu</v>
+        <v>EJ Jones</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/atreyu/6095061</v>
+        <v>https://music.apple.com/us/artist/ej-jones/1781306141</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/ego-death/1867855173</v>
+        <v>https://music.apple.com/us/album/gas-station-love-remix/1872150723</v>
       </c>
       <c r="L190" t="str">
-        <v>Ego Death - Atreyu</v>
+        <v>Gas Station Love (remix) - EJ Jones</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Gas Station Love (remix)</v>
+        <v>Disappear</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/gas-station-love-remix/1872150728</v>
+        <v>https://music.apple.com/us/song/disappear/1861907311</v>
       </c>
       <c r="D191" t="str">
         <v>2026-02-01</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Gas Station Love (remix) - Single</v>
+        <v>Disappear</v>
       </c>
       <c r="G191" t="str">
-        <v>4:05</v>
+        <v>5:50</v>
       </c>
       <c r="H191" t="str">
-        <v>EJ Jones</v>
+        <v>Lane 8</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/ej-jones/1781306141</v>
+        <v>https://music.apple.com/us/artist/lane-8/634763116</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/gas-station-love-remix/1872150723</v>
+        <v>https://music.apple.com/us/album/disappear/1861907305</v>
       </c>
       <c r="L191" t="str">
-        <v>Gas Station Love (remix) - EJ Jones</v>
+        <v>Disappear - Lane 8</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Disappear</v>
+        <v>Misbehave</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/disappear/1861907311</v>
+        <v>https://music.apple.com/us/song/misbehave/1859630128</v>
       </c>
       <c r="D192" t="str">
         <v>2026-02-01</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>Disappear</v>
+        <v>Misbehave - Single</v>
       </c>
       <c r="G192" t="str">
-        <v>5:50</v>
+        <v>3:43</v>
       </c>
       <c r="H192" t="str">
-        <v>Lane 8</v>
+        <v>Aluna</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/lane-8/634763116</v>
+        <v>https://music.apple.com/us/artist/aluna/1508017201</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/disappear/1861907305</v>
+        <v>https://music.apple.com/us/album/misbehave/1859630126</v>
       </c>
       <c r="L192" t="str">
-        <v>Disappear - Lane 8</v>
+        <v>Misbehave - Aluna</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Misbehave</v>
+        <v>Club Bizarre</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/misbehave/1859630128</v>
+        <v>https://music.apple.com/us/song/club-bizarre/1870355078</v>
       </c>
       <c r="D193" t="str">
         <v>2026-02-01</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>Misbehave - Single</v>
+        <v>Club Bizarre - Single</v>
       </c>
       <c r="G193" t="str">
-        <v>3:43</v>
+        <v>2:47</v>
       </c>
       <c r="H193" t="str">
-        <v>Aluna</v>
+        <v>Alok</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/aluna/1508017201</v>
+        <v>https://music.apple.com/us/artist/alok/324709167</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/misbehave/1859630126</v>
+        <v>https://music.apple.com/us/album/club-bizarre/1870355077</v>
       </c>
       <c r="L193" t="str">
-        <v>Misbehave - Aluna</v>
+        <v>Club Bizarre - Alok</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Club Bizarre</v>
+        <v>Fly</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/club-bizarre/1870355078</v>
+        <v>https://music.apple.com/us/song/fly/1867903625</v>
       </c>
       <c r="D194" t="str">
         <v>2026-02-01</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Club Bizarre - Single</v>
+        <v>Fly - Single</v>
       </c>
       <c r="G194" t="str">
-        <v>2:47</v>
+        <v>3:04</v>
       </c>
       <c r="H194" t="str">
-        <v>Alok</v>
+        <v>Stephen Stanley</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/alok/324709167</v>
+        <v>https://music.apple.com/us/artist/stephen-stanley/28074609</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/club-bizarre/1870355077</v>
+        <v>https://music.apple.com/us/album/fly/1867903548</v>
       </c>
       <c r="L194" t="str">
-        <v>Club Bizarre - Alok</v>
+        <v>Fly - Stephen Stanley</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Fly</v>
+        <v>ily anyway</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/fly/1867903625</v>
+        <v>https://music.apple.com/us/song/ily-anyway/1870369432</v>
       </c>
       <c r="D195" t="str">
         <v>2026-02-01</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Fly - Single</v>
+        <v>ily anyway - Single</v>
       </c>
       <c r="G195" t="str">
-        <v>3:04</v>
+        <v>3:05</v>
       </c>
       <c r="H195" t="str">
-        <v>Stephen Stanley</v>
+        <v>Strings &amp; Heart</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/stephen-stanley/28074609</v>
+        <v>https://music.apple.com/us/artist/strings-heart/1435173742</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/fly/1867903548</v>
+        <v>https://music.apple.com/us/album/ily-anyway/1870369426</v>
       </c>
       <c r="L195" t="str">
-        <v>Fly - Stephen Stanley</v>
+        <v>ily anyway - Strings &amp; Heart</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>ily anyway</v>
+        <v>George Jones (feat. Angela Autumn)</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/ily-anyway/1870369432</v>
+        <v>https://music.apple.com/us/song/george-jones-feat-angela-autumn/1867306007</v>
       </c>
       <c r="D196" t="str">
         <v>2026-02-01</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>ily anyway - Single</v>
+        <v>Nellene - EP</v>
       </c>
       <c r="G196" t="str">
-        <v>3:05</v>
+        <v>3:35</v>
       </c>
       <c r="H196" t="str">
-        <v>Strings &amp; Heart</v>
+        <v>Deloyd Elze</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/strings-heart/1435173742</v>
+        <v>https://music.apple.com/us/artist/deloyd-elze/1699032462</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/ily-anyway/1870369426</v>
+        <v>https://music.apple.com/us/album/george-jones-feat-angela-autumn/1867306004</v>
       </c>
       <c r="L196" t="str">
-        <v>ily anyway - Strings &amp; Heart</v>
+        <v>George Jones (feat. Angela Autumn) - Deloyd Elze</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>George Jones (feat. Angela Autumn)</v>
+        <v>Kiss Big</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/george-jones-feat-angela-autumn/1867306007</v>
+        <v>https://music.apple.com/us/song/kiss-big/1837292261</v>
       </c>
       <c r="D197" t="str">
         <v>2026-02-01</v>
@@ -7861,36 +7861,36 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>Nellene - EP</v>
+        <v>Kiss Big</v>
       </c>
       <c r="G197" t="str">
-        <v>3:35</v>
+        <v>3:41</v>
       </c>
       <c r="H197" t="str">
-        <v>Deloyd Elze</v>
+        <v>Ailbhe Reddy</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/deloyd-elze/1699032462</v>
+        <v>https://music.apple.com/us/artist/ailbhe-reddy/947186338</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/george-jones-feat-angela-autumn/1867306004</v>
+        <v>https://music.apple.com/us/album/kiss-big/1837292249</v>
       </c>
       <c r="L197" t="str">
-        <v>George Jones (feat. Angela Autumn) - Deloyd Elze</v>
+        <v>Kiss Big - Ailbhe Reddy</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Kiss Big</v>
+        <v>praxis</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/kiss-big/1837292261</v>
+        <v>https://music.apple.com/us/song/praxis/1845253734</v>
       </c>
       <c r="D198" t="str">
         <v>2026-02-01</v>
@@ -7899,36 +7899,36 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>Kiss Big</v>
+        <v>Whole World As Vigil</v>
       </c>
       <c r="G198" t="str">
-        <v>3:41</v>
+        <v>3:28</v>
       </c>
       <c r="H198" t="str">
-        <v>Ailbhe Reddy</v>
+        <v>Lauren Auder</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/ailbhe-reddy/947186338</v>
+        <v>https://music.apple.com/us/artist/lauren-auder/1096049552</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/kiss-big/1837292249</v>
+        <v>https://music.apple.com/us/album/praxis/1845253730</v>
       </c>
       <c r="L198" t="str">
-        <v>Kiss Big - Ailbhe Reddy</v>
+        <v>praxis - Lauren Auder</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>praxis</v>
+        <v>House</v>
       </c>
       <c r="B199" t="str">
         <v/>
       </c>
       <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/praxis/1845253734</v>
+        <v>https://music.apple.com/us/song/house/1866696487</v>
       </c>
       <c r="D199" t="str">
         <v>2026-02-01</v>
@@ -7937,36 +7937,36 @@
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>Whole World As Vigil</v>
+        <v>House - Single</v>
       </c>
       <c r="G199" t="str">
-        <v>3:28</v>
+        <v>2:30</v>
       </c>
       <c r="H199" t="str">
-        <v>Lauren Auder</v>
+        <v>Connie Converse</v>
       </c>
       <c r="I199" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/lauren-auder/1096049552</v>
+        <v>https://music.apple.com/us/artist/connie-converse/308326962</v>
       </c>
       <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/praxis/1845253730</v>
+        <v>https://music.apple.com/us/album/house/1866696486</v>
       </c>
       <c r="L199" t="str">
-        <v>praxis - Lauren Auder</v>
+        <v>House - Connie Converse</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>House</v>
+        <v>Cowboy Without a Clue</v>
       </c>
       <c r="B200" t="str">
         <v/>
       </c>
       <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/house/1866696487</v>
+        <v>https://music.apple.com/us/song/cowboy-without-a-clue/1834024322</v>
       </c>
       <c r="D200" t="str">
         <v>2026-02-01</v>
@@ -7975,36 +7975,36 @@
         <v/>
       </c>
       <c r="F200" t="str">
-        <v>House - Single</v>
+        <v>No Love Lost to Kindness</v>
       </c>
       <c r="G200" t="str">
-        <v>2:30</v>
+        <v>3:57</v>
       </c>
       <c r="H200" t="str">
-        <v>Connie Converse</v>
+        <v>Yumi Zouma</v>
       </c>
       <c r="I200" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J200" t="str">
-        <v>https://music.apple.com/us/artist/connie-converse/308326962</v>
+        <v>https://music.apple.com/us/artist/yumi-zouma/795031200</v>
       </c>
       <c r="K200" t="str">
-        <v>https://music.apple.com/us/album/house/1866696486</v>
+        <v>https://music.apple.com/us/album/cowboy-without-a-clue/1834024311</v>
       </c>
       <c r="L200" t="str">
-        <v>House - Connie Converse</v>
+        <v>Cowboy Without a Clue - Yumi Zouma</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Cowboy Without a Clue</v>
+        <v>Brincar</v>
       </c>
       <c r="B201" t="str">
         <v/>
       </c>
       <c r="C201" t="str">
-        <v>https://music.apple.com/us/song/cowboy-without-a-clue/1834024322</v>
+        <v>https://music.apple.com/us/song/brincar/1871554907</v>
       </c>
       <c r="D201" t="str">
         <v>2026-02-01</v>
@@ -8013,36 +8013,36 @@
         <v/>
       </c>
       <c r="F201" t="str">
-        <v>No Love Lost to Kindness</v>
+        <v>JET LAG - EP</v>
       </c>
       <c r="G201" t="str">
-        <v>3:57</v>
+        <v>3:06</v>
       </c>
       <c r="H201" t="str">
-        <v>Yumi Zouma</v>
+        <v>J Castle</v>
       </c>
       <c r="I201" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J201" t="str">
-        <v>https://music.apple.com/us/artist/yumi-zouma/795031200</v>
+        <v>https://music.apple.com/us/artist/j-castle/309829058</v>
       </c>
       <c r="K201" t="str">
-        <v>https://music.apple.com/us/album/cowboy-without-a-clue/1834024311</v>
+        <v>https://music.apple.com/us/album/brincar/1871554901</v>
       </c>
       <c r="L201" t="str">
-        <v>Cowboy Without a Clue - Yumi Zouma</v>
+        <v>Brincar - J Castle</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>Brincar</v>
+        <v>Quién</v>
       </c>
       <c r="B202" t="str">
         <v/>
       </c>
       <c r="C202" t="str">
-        <v>https://music.apple.com/us/song/brincar/1871554907</v>
+        <v>https://music.apple.com/us/song/qui%C3%A9n/1870329662</v>
       </c>
       <c r="D202" t="str">
         <v>2026-02-01</v>
@@ -8051,68 +8051,30 @@
         <v/>
       </c>
       <c r="F202" t="str">
-        <v>JET LAG - EP</v>
+        <v>Quién - Single</v>
       </c>
       <c r="G202" t="str">
-        <v>3:06</v>
+        <v>4:19</v>
       </c>
       <c r="H202" t="str">
-        <v>J Castle</v>
+        <v>Daniela Darcourt</v>
       </c>
       <c r="I202" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J202" t="str">
-        <v>https://music.apple.com/us/artist/j-castle/309829058</v>
+        <v>https://music.apple.com/us/artist/daniela-darcourt/1396749684</v>
       </c>
       <c r="K202" t="str">
-        <v>https://music.apple.com/us/album/brincar/1871554901</v>
+        <v>https://music.apple.com/us/album/qui%C3%A9n/1870329660</v>
       </c>
       <c r="L202" t="str">
-        <v>Brincar - J Castle</v>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="str">
-        <v>Quién</v>
-      </c>
-      <c r="B203" t="str">
-        <v/>
-      </c>
-      <c r="C203" t="str">
-        <v>https://music.apple.com/us/song/qui%C3%A9n/1870329662</v>
-      </c>
-      <c r="D203" t="str">
-        <v>2026-02-01</v>
-      </c>
-      <c r="E203" t="str">
-        <v/>
-      </c>
-      <c r="F203" t="str">
-        <v>Quién - Single</v>
-      </c>
-      <c r="G203" t="str">
-        <v>4:19</v>
-      </c>
-      <c r="H203" t="str">
-        <v>Daniela Darcourt</v>
-      </c>
-      <c r="I203" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J203" t="str">
-        <v>https://music.apple.com/us/artist/daniela-darcourt/1396749684</v>
-      </c>
-      <c r="K203" t="str">
-        <v>https://music.apple.com/us/album/qui%C3%A9n/1870329660</v>
-      </c>
-      <c r="L203" t="str">
         <v>Quién - Daniela Darcourt</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L203"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L202"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
@@ -1541,7 +1541,7 @@
         <v>TINI - FUTTTURA LIVE - el cielo + fresa</v>
       </c>
       <c r="B31" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=q_rrgJZAdNg</v>
@@ -1553,7 +1553,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G31" t="str">
         <v>5:58</v>
@@ -1579,7 +1579,7 @@
         <v>Charley - Serial Idealist (Official Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=uVIuKbPJz0U</v>
@@ -1591,7 +1591,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G32" t="str">
         <v>3:26</v>
@@ -1918,7 +1918,7 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>I Explained "How Music Works" LIVE At My Concert</v>
+        <v>I Explained How Music Works LIVE At My Concert</v>
       </c>
       <c r="B41" t="str">
         <v>4 days ago</v>
@@ -1951,7 +1951,7 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>I Explained "How Music Works" LIVE At My Concert - Marcin</v>
+        <v>I Explained How Music Works LIVE At My Concert - Marcin</v>
       </c>
     </row>
     <row r="42">
@@ -2035,7 +2035,7 @@
         <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop)</v>
       </c>
       <c r="B44" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C44" t="str">
         <v>https://www.youtube.com/watch?v=57a_OheOlDw</v>
@@ -2047,7 +2047,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G44" t="str">
         <v>3:20</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
@@ -1465,7 +1465,7 @@
         <v>India Martinez, Coro ArteSí de Olvidados - Niño Sin Miedo</v>
       </c>
       <c r="B29" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=Vug_FPbXe9E</v>
@@ -1477,7 +1477,7 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G29" t="str">
         <v>4:04</v>
@@ -1503,7 +1503,7 @@
         <v>Chelsea Cutler - BAD (Official Lyric Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=ZIW2vA3Zs1U</v>
@@ -1515,7 +1515,7 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G30" t="str">
         <v>2:16</v>
@@ -3289,7 +3289,7 @@
         <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards</v>
       </c>
       <c r="B77" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C77" t="str">
         <v>https://www.youtube.com/watch?v=kIRmKmEb2g0</v>
@@ -3301,7 +3301,7 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G77" t="str">
         <v>7:21</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L202"/>
+  <dimension ref="A1:L203"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -445,7 +445,7 @@
         <v>https://www.youtube.com/watch?v=KdsHxyl4bE8</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -483,7 +483,7 @@
         <v>https://www.youtube.com/watch?v=Mwkl_Cz_SG8</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -521,7 +521,7 @@
         <v>https://www.youtube.com/watch?v=I7a-pDZFE7U</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -559,7 +559,7 @@
         <v>https://www.youtube.com/watch?v=kGeamxRf8Gw</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -597,7 +597,7 @@
         <v>https://www.youtube.com/watch?v=tNmT47k6MjM</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -635,7 +635,7 @@
         <v>https://www.youtube.com/watch?v=6ecgOSOMWzc</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -673,7 +673,7 @@
         <v>https://www.youtube.com/watch?v=DAerJcerikU</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -711,7 +711,7 @@
         <v>https://www.youtube.com/watch?v=isNztTjXQsQ</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -749,7 +749,7 @@
         <v>https://www.youtube.com/watch?v=buS21tVq5r0</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -787,7 +787,7 @@
         <v>https://www.youtube.com/watch?v=qhO6VMC-nx0</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://www.youtube.com/watch?v=FgAyfRnbbRs</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -863,7 +863,7 @@
         <v>https://www.youtube.com/watch?v=nwXiAjjl6NE</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -901,7 +901,7 @@
         <v>https://www.youtube.com/watch?v=MjUiVPzMQHw</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -939,7 +939,7 @@
         <v>https://www.youtube.com/watch?v=eWglDE7O5r8</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -977,7 +977,7 @@
         <v>https://www.youtube.com/watch?v=Cmy8CsYIUL0</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1015,7 +1015,7 @@
         <v>https://www.youtube.com/watch?v=sf6eRmInk1s</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1053,7 +1053,7 @@
         <v>https://www.youtube.com/watch?v=fv9prIYHHzk</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1091,7 +1091,7 @@
         <v>https://www.youtube.com/watch?v=T9YvLA2cdZs</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1129,7 +1129,7 @@
         <v>https://www.youtube.com/watch?v=dPWc_6IdDJk</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1167,7 +1167,7 @@
         <v>https://www.youtube.com/watch?v=CV5rR9JZK-0</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1205,7 +1205,7 @@
         <v>https://www.youtube.com/watch?v=9HwTj3NZ16E</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1243,7 +1243,7 @@
         <v>https://www.youtube.com/watch?v=Lmus-UbL1H0</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1281,7 +1281,7 @@
         <v>https://www.youtube.com/watch?v=bu6WSMDDPGY</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1319,7 +1319,7 @@
         <v>https://www.youtube.com/watch?v=zcYeoGBglC0</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1357,7 +1357,7 @@
         <v>https://www.youtube.com/watch?v=3igYRj82EiU</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1395,7 +1395,7 @@
         <v>https://www.youtube.com/watch?v=0bhcO4Yphuo</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1433,7 +1433,7 @@
         <v>https://www.youtube.com/watch?v=Jjz1wFe5dMo</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1471,7 +1471,7 @@
         <v>https://www.youtube.com/watch?v=Vug_FPbXe9E</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1509,7 +1509,7 @@
         <v>https://www.youtube.com/watch?v=ZIW2vA3Zs1U</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1547,7 +1547,7 @@
         <v>https://www.youtube.com/watch?v=q_rrgJZAdNg</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1585,7 +1585,7 @@
         <v>https://www.youtube.com/watch?v=uVIuKbPJz0U</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1623,7 +1623,7 @@
         <v>https://www.youtube.com/watch?v=E-ECwdRndVA</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1661,7 +1661,7 @@
         <v>https://www.youtube.com/watch?v=1ugf5aaY4pY</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1699,7 +1699,7 @@
         <v>https://www.youtube.com/watch?v=ByABj3Xof1I</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1737,7 +1737,7 @@
         <v>https://www.youtube.com/watch?v=2HSbo51EFNg</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1775,7 +1775,7 @@
         <v>https://www.youtube.com/watch?v=ylifHFJWJ_c</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1813,7 +1813,7 @@
         <v>https://www.youtube.com/watch?v=9ST-eBNL0NU</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1851,7 +1851,7 @@
         <v>https://www.youtube.com/watch?v=EhzX2y5MpSM</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1889,7 +1889,7 @@
         <v>https://www.youtube.com/watch?v=yUAvfo8fpuU</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1918,7 +1918,7 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>I Explained How Music Works LIVE At My Concert</v>
+        <v>I Had To Explain How Music Works LIVE In Concert</v>
       </c>
       <c r="B41" t="str">
         <v>4 days ago</v>
@@ -1927,7 +1927,7 @@
         <v>https://www.youtube.com/watch?v=KnsBdAM3HqY</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1951,7 +1951,7 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>I Explained How Music Works LIVE At My Concert - Marcin</v>
+        <v>I Had To Explain How Music Works LIVE In Concert - Marcin</v>
       </c>
     </row>
     <row r="42">
@@ -1965,7 +1965,7 @@
         <v>https://www.youtube.com/watch?v=BTqRGxSX6AQ</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -2003,7 +2003,7 @@
         <v>https://www.youtube.com/watch?v=r9KyYK_E34s</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -2041,7 +2041,7 @@
         <v>https://www.youtube.com/watch?v=57a_OheOlDw</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2079,7 +2079,7 @@
         <v>https://www.youtube.com/watch?v=-5Aa8NTiRqE</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -2117,7 +2117,7 @@
         <v>https://www.youtube.com/watch?v=5RNy_1odv20</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -2155,7 +2155,7 @@
         <v>https://www.youtube.com/watch?v=stYIRyCLN4Y</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2193,7 +2193,7 @@
         <v>https://www.youtube.com/watch?v=7sxVHYZ_PnA</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2231,7 +2231,7 @@
         <v>https://www.youtube.com/watch?v=46iZEdsxjC0</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -2269,7 +2269,7 @@
         <v>https://www.youtube.com/watch?v=K2nG1Uukz7E</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2307,7 +2307,7 @@
         <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2345,7 +2345,7 @@
         <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2383,7 +2383,7 @@
         <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2421,7 +2421,7 @@
         <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2459,7 +2459,7 @@
         <v>https://www.youtube.com/watch?v=pnAz9RwGSek</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2497,7 +2497,7 @@
         <v>https://www.youtube.com/watch?v=u7aPv2saz_I</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2535,7 +2535,7 @@
         <v>https://www.youtube.com/watch?v=WGb8KVdqs6k</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2573,7 +2573,7 @@
         <v>https://www.youtube.com/watch?v=X1ZeY4Y3l1M</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2611,7 +2611,7 @@
         <v>https://www.youtube.com/watch?v=rzuD5szQhso</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2649,7 +2649,7 @@
         <v>https://www.youtube.com/watch?v=UPuK6wV5Zco</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -2687,7 +2687,7 @@
         <v>https://www.youtube.com/watch?v=9hW9sNMn2A0</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -2725,7 +2725,7 @@
         <v>https://www.youtube.com/watch?v=JMYvXleIwfU</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -2763,7 +2763,7 @@
         <v>https://www.youtube.com/watch?v=vOzX-o11seI</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -2801,7 +2801,7 @@
         <v>https://www.youtube.com/watch?v=86k4E6ydHVU</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -2839,7 +2839,7 @@
         <v>https://www.youtube.com/watch?v=-UWIFAiOOPE</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -2877,7 +2877,7 @@
         <v>https://www.youtube.com/watch?v=02QyA29poAM</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -2915,7 +2915,7 @@
         <v>https://www.youtube.com/watch?v=feOv8nufa_I</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -2947,19 +2947,19 @@
         <v>Harry Styles - Aperture (Official Audio)</v>
       </c>
       <c r="B68" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C68" t="str">
         <v>https://www.youtube.com/watch?v=rA_eCxPay7E</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E68" t="str">
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G68" t="str">
         <v>5:14</v>
@@ -2991,7 +2991,7 @@
         <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -3029,7 +3029,7 @@
         <v>https://www.youtube.com/watch?v=zy2TLLeNgp0</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -3067,7 +3067,7 @@
         <v>https://www.youtube.com/watch?v=JzOUJZPky6o</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -3105,7 +3105,7 @@
         <v>https://www.youtube.com/watch?v=kfF0bVZMCw0</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -3143,7 +3143,7 @@
         <v>https://www.youtube.com/watch?v=dLzpNstMHZY</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -3181,7 +3181,7 @@
         <v>https://www.youtube.com/watch?v=fo_j8Fqag8I</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -3219,7 +3219,7 @@
         <v>https://www.youtube.com/watch?v=7sD9-MtV9CY</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -3257,7 +3257,7 @@
         <v>https://www.youtube.com/watch?v=3ATlH-Rtzmk</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -3295,7 +3295,7 @@
         <v>https://www.youtube.com/watch?v=kIRmKmEb2g0</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -3333,7 +3333,7 @@
         <v>https://www.youtube.com/watch?v=oJ-l2ptQwbQ</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -3371,7 +3371,7 @@
         <v>https://www.youtube.com/watch?v=ShW-I63KD8w</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -3409,7 +3409,7 @@
         <v>https://www.youtube.com/watch?v=66PDbaI-BVA</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -3447,7 +3447,7 @@
         <v>https://www.youtube.com/watch?v=4tmW_JSXHII</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -3485,7 +3485,7 @@
         <v>https://www.youtube.com/watch?v=6kZVtF8iaWw</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -3523,7 +3523,7 @@
         <v>https://www.youtube.com/watch?v=guUvgEKkk1U</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -3561,7 +3561,7 @@
         <v>https://www.youtube.com/watch?v=4okJouEbZ_s</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -3599,7 +3599,7 @@
         <v>https://www.youtube.com/watch?v=yL_TxDF8WtI</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E85" t="str">
         <v/>
@@ -3637,7 +3637,7 @@
         <v>https://www.youtube.com/watch?v=0m45tTheoCs</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3675,7 +3675,7 @@
         <v>https://www.youtube.com/watch?v=AHm1i212UP4</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3713,7 +3713,7 @@
         <v>https://www.youtube.com/watch?v=Srb2P9efFHY</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3751,7 +3751,7 @@
         <v>https://www.youtube.com/watch?v=NvHXKIrBiR8</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3789,7 +3789,7 @@
         <v>https://www.youtube.com/watch?v=D2-t5SDV1IE</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -3827,7 +3827,7 @@
         <v>https://www.youtube.com/watch?v=BouRN2QuXV8</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -3865,7 +3865,7 @@
         <v>https://www.youtube.com/watch?v=IyPD6AnWlRg</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -3903,7 +3903,7 @@
         <v>https://www.youtube.com/watch?v=7_i2R-EU-Eg</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E93" t="str">
         <v/>
@@ -3941,7 +3941,7 @@
         <v>https://www.youtube.com/watch?v=McaD2PG8jOE</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E94" t="str">
         <v/>
@@ -3979,7 +3979,7 @@
         <v>https://www.youtube.com/watch?v=07SeT_QSJ08</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E95" t="str">
         <v/>
@@ -4017,7 +4017,7 @@
         <v>https://www.youtube.com/watch?v=mhw8eAtgnRk</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E96" t="str">
         <v/>
@@ -4055,7 +4055,7 @@
         <v>https://www.youtube.com/watch?v=plbNzv3KvWs</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E97" t="str">
         <v/>
@@ -4093,7 +4093,7 @@
         <v>https://www.youtube.com/watch?v=GSkO7B_RbQE</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E98" t="str">
         <v/>
@@ -4131,7 +4131,7 @@
         <v>https://www.youtube.com/watch?v=vH5ewjAQfNc</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E99" t="str">
         <v/>
@@ -4169,7 +4169,7 @@
         <v>https://www.youtube.com/watch?v=R0vVYP8tSIw</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E100" t="str">
         <v/>
@@ -4207,7 +4207,7 @@
         <v>https://www.youtube.com/watch?v=upfuNpZvNZc</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E101" t="str">
         <v/>
@@ -4245,7 +4245,7 @@
         <v>https://music.apple.com/us/song/body/1871258331</v>
       </c>
       <c r="D102" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E102" t="str">
         <v/>
@@ -4283,7 +4283,7 @@
         <v>https://music.apple.com/us/song/dandelion/1869436838</v>
       </c>
       <c r="D103" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E103" t="str">
         <v/>
@@ -4321,7 +4321,7 @@
         <v>https://music.apple.com/us/song/lights-go-out/1870833473</v>
       </c>
       <c r="D104" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E104" t="str">
         <v/>
@@ -4359,7 +4359,7 @@
         <v>https://music.apple.com/us/song/the-great-divide/1872239886</v>
       </c>
       <c r="D105" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E105" t="str">
         <v/>
@@ -4397,7 +4397,7 @@
         <v>https://music.apple.com/us/song/trist%C3%B3n/1872585947</v>
       </c>
       <c r="D106" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E106" t="str">
         <v/>
@@ -4435,7 +4435,7 @@
         <v>https://music.apple.com/us/song/feed-the-streets/1869462051</v>
       </c>
       <c r="D107" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E107" t="str">
         <v/>
@@ -4473,7 +4473,7 @@
         <v>https://music.apple.com/us/song/i-did-this-to-myself/1861531672</v>
       </c>
       <c r="D108" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E108" t="str">
         <v/>
@@ -4511,7 +4511,7 @@
         <v>https://music.apple.com/us/song/for-hire/1870722567</v>
       </c>
       <c r="D109" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E109" t="str">
         <v/>
@@ -4549,7 +4549,7 @@
         <v>https://music.apple.com/us/song/mcarthur/1871231844</v>
       </c>
       <c r="D110" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E110" t="str">
         <v/>
@@ -4587,7 +4587,7 @@
         <v>https://music.apple.com/us/song/debris/1853069633</v>
       </c>
       <c r="D111" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E111" t="str">
         <v/>
@@ -4625,7 +4625,7 @@
         <v>https://music.apple.com/us/song/god-owes-me-money-live-at-apple-music-radio/1871521120</v>
       </c>
       <c r="D112" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E112" t="str">
         <v/>
@@ -4663,7 +4663,7 @@
         <v>https://music.apple.com/us/song/rockstar-raging-feat-swae-lee/1873028187</v>
       </c>
       <c r="D113" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E113" t="str">
         <v/>
@@ -4701,7 +4701,7 @@
         <v>https://music.apple.com/us/song/1-1/1870378316</v>
       </c>
       <c r="D114" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E114" t="str">
         <v/>
@@ -4739,7 +4739,7 @@
         <v>https://music.apple.com/us/song/still-sincere-feat-pinkpantheress/1862228374</v>
       </c>
       <c r="D115" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E115" t="str">
         <v/>
@@ -4777,7 +4777,7 @@
         <v>https://music.apple.com/us/song/two-car-garage/1869137588</v>
       </c>
       <c r="D116" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E116" t="str">
         <v/>
@@ -4815,7 +4815,7 @@
         <v>https://music.apple.com/us/song/fml/1872686260</v>
       </c>
       <c r="D117" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E117" t="str">
         <v/>
@@ -4853,7 +4853,7 @@
         <v>https://music.apple.com/us/song/faked-it-all-the-time/1871050032</v>
       </c>
       <c r="D118" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E118" t="str">
         <v/>
@@ -4891,7 +4891,7 @@
         <v>https://music.apple.com/us/song/house-of-the-rising-sun/1872111857</v>
       </c>
       <c r="D119" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E119" t="str">
         <v/>
@@ -4929,7 +4929,7 @@
         <v>https://music.apple.com/us/song/lorelei/1867640808</v>
       </c>
       <c r="D120" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E120" t="str">
         <v/>
@@ -4967,7 +4967,7 @@
         <v>https://music.apple.com/us/song/free/1870703329</v>
       </c>
       <c r="D121" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E121" t="str">
         <v/>
@@ -5005,7 +5005,7 @@
         <v>https://music.apple.com/us/song/professional-heartbreaker/1871053476</v>
       </c>
       <c r="D122" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E122" t="str">
         <v/>
@@ -5043,7 +5043,7 @@
         <v>https://music.apple.com/us/song/tell-me-what-you-want/1871463892</v>
       </c>
       <c r="D123" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E123" t="str">
         <v/>
@@ -5081,7 +5081,7 @@
         <v>https://music.apple.com/us/song/aguas/1869455857</v>
       </c>
       <c r="D124" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E124" t="str">
         <v/>
@@ -5119,7 +5119,7 @@
         <v>https://music.apple.com/us/song/ants-in-my-room/1870967813</v>
       </c>
       <c r="D125" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E125" t="str">
         <v/>
@@ -5157,7 +5157,7 @@
         <v>https://music.apple.com/us/song/baddie/1849760827</v>
       </c>
       <c r="D126" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E126" t="str">
         <v/>
@@ -5195,7 +5195,7 @@
         <v>https://music.apple.com/us/song/what-you-need-a-colors-show/1870990925</v>
       </c>
       <c r="D127" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E127" t="str">
         <v/>
@@ -5233,7 +5233,7 @@
         <v>https://music.apple.com/us/song/ok-ok-hamdi-remix/1871538130</v>
       </c>
       <c r="D128" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E128" t="str">
         <v/>
@@ -5271,7 +5271,7 @@
         <v>https://music.apple.com/us/song/ever-and-ever-before-feat-m%C5%8Driah-courtney/1869383260</v>
       </c>
       <c r="D129" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E129" t="str">
         <v/>
@@ -5309,7 +5309,7 @@
         <v>https://music.apple.com/us/song/for-the-first-time-again/1834736723</v>
       </c>
       <c r="D130" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E130" t="str">
         <v/>
@@ -5347,7 +5347,7 @@
         <v>https://music.apple.com/us/song/liars-tale/1862207951</v>
       </c>
       <c r="D131" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E131" t="str">
         <v/>
@@ -5385,7 +5385,7 @@
         <v>https://music.apple.com/us/song/afraid-of-the-dark/1872184048</v>
       </c>
       <c r="D132" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E132" t="str">
         <v/>
@@ -5423,7 +5423,7 @@
         <v>https://music.apple.com/us/song/wake-up-calling/1862338150</v>
       </c>
       <c r="D133" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E133" t="str">
         <v/>
@@ -5461,7 +5461,7 @@
         <v>https://music.apple.com/us/song/high/1867202644</v>
       </c>
       <c r="D134" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E134" t="str">
         <v/>
@@ -5499,7 +5499,7 @@
         <v>https://music.apple.com/us/song/villain/1860126455</v>
       </c>
       <c r="D135" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E135" t="str">
         <v/>
@@ -5537,7 +5537,7 @@
         <v>https://music.apple.com/us/song/bad-idea-right/1869792549</v>
       </c>
       <c r="D136" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E136" t="str">
         <v/>
@@ -5575,7 +5575,7 @@
         <v>https://music.apple.com/us/song/residue/1863786787</v>
       </c>
       <c r="D137" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E137" t="str">
         <v/>
@@ -5613,7 +5613,7 @@
         <v>https://music.apple.com/us/song/i-used-to-go-to-this-bar/1839918872</v>
       </c>
       <c r="D138" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E138" t="str">
         <v/>
@@ -5651,7 +5651,7 @@
         <v>https://music.apple.com/us/song/starlight/1870989674</v>
       </c>
       <c r="D139" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E139" t="str">
         <v/>
@@ -5689,7 +5689,7 @@
         <v>https://music.apple.com/us/song/dandelion/1863154133</v>
       </c>
       <c r="D140" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E140" t="str">
         <v/>
@@ -5727,7 +5727,7 @@
         <v>https://music.apple.com/us/song/themselves/1845287173</v>
       </c>
       <c r="D141" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E141" t="str">
         <v/>
@@ -5765,7 +5765,7 @@
         <v>https://music.apple.com/us/song/high-maintenance/1872497656</v>
       </c>
       <c r="D142" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E142" t="str">
         <v/>
@@ -5803,7 +5803,7 @@
         <v>https://music.apple.com/us/song/trackhawk/1860991724</v>
       </c>
       <c r="D143" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E143" t="str">
         <v/>
@@ -5841,7 +5841,7 @@
         <v>https://music.apple.com/us/song/wheel-man/1872178895</v>
       </c>
       <c r="D144" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E144" t="str">
         <v/>
@@ -5879,7 +5879,7 @@
         <v>https://music.apple.com/us/song/natural-disaster/1871263211</v>
       </c>
       <c r="D145" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E145" t="str">
         <v/>
@@ -5917,7 +5917,7 @@
         <v>https://music.apple.com/us/song/prettier/1869745409</v>
       </c>
       <c r="D146" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E146" t="str">
         <v/>
@@ -5955,7 +5955,7 @@
         <v>https://music.apple.com/us/song/shotta-flow-8/1872760524</v>
       </c>
       <c r="D147" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E147" t="str">
         <v/>
@@ -5993,7 +5993,7 @@
         <v>https://music.apple.com/us/song/die-to-fall/1866902681</v>
       </c>
       <c r="D148" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E148" t="str">
         <v/>
@@ -6031,7 +6031,7 @@
         <v>https://music.apple.com/us/song/the-cruel-angels-thesis-neon-genesis-evangelion/1864932139</v>
       </c>
       <c r="D149" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E149" t="str">
         <v/>
@@ -6069,7 +6069,7 @@
         <v>https://music.apple.com/us/song/slow-burn/1851033862</v>
       </c>
       <c r="D150" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E150" t="str">
         <v/>
@@ -6098,1983 +6098,2021 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Mono (feat. skaiwater)</v>
+        <v>Too Late</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/mono-feat-skaiwater/1869130804</v>
+        <v>https://music.apple.com/us/song/too-late/1857999860</v>
       </c>
       <c r="D151" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E151" t="str">
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>Mono (feat. skaiwater) - Single</v>
+        <v>Evergreen</v>
       </c>
       <c r="G151" t="str">
-        <v>2:50</v>
+        <v>2:56</v>
       </c>
       <c r="H151" t="str">
-        <v>i-dle</v>
+        <v>Hunter Hayes</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/i-dle/1378887586</v>
+        <v>https://music.apple.com/us/artist/hunter-hayes/429231434</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/mono-feat-skaiwater/1869130801</v>
+        <v>https://music.apple.com/us/album/too-late/1857999850</v>
       </c>
       <c r="L151" t="str">
-        <v>Mono (feat. skaiwater) - i-dle</v>
+        <v>Too Late - Hunter Hayes</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Thank You Is Enough</v>
+        <v>Mono (feat. skaiwater)</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/thank-you-is-enough/1870679042</v>
+        <v>https://music.apple.com/us/song/mono-feat-skaiwater/1869130804</v>
       </c>
       <c r="D152" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E152" t="str">
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>Yo Gabba GabbaLand! (Season 2) [Apple TV+ Original Series Soundtrack]</v>
+        <v>Mono (feat. skaiwater) - Single</v>
       </c>
       <c r="G152" t="str">
-        <v>1:55</v>
+        <v>2:50</v>
       </c>
       <c r="H152" t="str">
-        <v>Yo Gabba Gabba</v>
+        <v>i-dle</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/yo-gabba-gabba/433108373</v>
+        <v>https://music.apple.com/us/artist/i-dle/1378887586</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/thank-you-is-enough/1870678950</v>
+        <v>https://music.apple.com/us/album/mono-feat-skaiwater/1869130801</v>
       </c>
       <c r="L152" t="str">
-        <v>Thank You Is Enough - Yo Gabba Gabba</v>
+        <v>Mono (feat. skaiwater) - i-dle</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>RIDIN</v>
+        <v>Thank You Is Enough</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/ridin/1869786726</v>
+        <v>https://music.apple.com/us/song/thank-you-is-enough/1870679042</v>
       </c>
       <c r="D153" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E153" t="str">
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>RIDIN - Single</v>
+        <v>Yo Gabba GabbaLand! (Season 2) [Apple TV+ Original Series Soundtrack]</v>
       </c>
       <c r="G153" t="str">
-        <v>2:00</v>
+        <v>1:55</v>
       </c>
       <c r="H153" t="str">
-        <v>Tokischa</v>
+        <v>Yo Gabba Gabba</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/tokischa/1414103446</v>
+        <v>https://music.apple.com/us/artist/yo-gabba-gabba/433108373</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/ridin/1869786725</v>
+        <v>https://music.apple.com/us/album/thank-you-is-enough/1870678950</v>
       </c>
       <c r="L153" t="str">
-        <v>RIDIN - Tokischa</v>
+        <v>Thank You Is Enough - Yo Gabba Gabba</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>POSSESSION</v>
+        <v>RIDIN</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/possession/1872536200</v>
+        <v>https://music.apple.com/us/song/ridin/1869786726</v>
       </c>
       <c r="D154" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E154" t="str">
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>POSSESSION - Single</v>
+        <v>RIDIN - Single</v>
       </c>
       <c r="G154" t="str">
-        <v>3:07</v>
+        <v>2:00</v>
       </c>
       <c r="H154" t="str">
-        <v>Melanie Martinez</v>
+        <v>Tokischa</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/melanie-martinez/993014053</v>
+        <v>https://music.apple.com/us/artist/tokischa/1414103446</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/possession/1872536199</v>
+        <v>https://music.apple.com/us/album/ridin/1869786725</v>
       </c>
       <c r="L154" t="str">
-        <v>POSSESSION - Melanie Martinez</v>
+        <v>RIDIN - Tokischa</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Poema</v>
+        <v>POSSESSION</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/poema/1872723644</v>
+        <v>https://music.apple.com/us/song/possession/1872536200</v>
       </c>
       <c r="D155" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E155" t="str">
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>Poema - Single</v>
+        <v>POSSESSION - Single</v>
       </c>
       <c r="G155" t="str">
-        <v>3:14</v>
+        <v>3:07</v>
       </c>
       <c r="H155" t="str">
-        <v>Óscar Maydon</v>
+        <v>Melanie Martinez</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/%C3%B3scar-maydon/1524147696</v>
+        <v>https://music.apple.com/us/artist/melanie-martinez/993014053</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/poema/1872723468</v>
+        <v>https://music.apple.com/us/album/possession/1872536199</v>
       </c>
       <c r="L155" t="str">
-        <v>Poema - Óscar Maydon</v>
+        <v>POSSESSION - Melanie Martinez</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Live Without</v>
+        <v>Poema</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/live-without/1862777625</v>
+        <v>https://music.apple.com/us/song/poema/1872723644</v>
       </c>
       <c r="D156" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E156" t="str">
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>WORRIED SICK (Deluxe Edition)</v>
+        <v>Poema - Single</v>
       </c>
       <c r="G156" t="str">
-        <v>2:55</v>
+        <v>3:14</v>
       </c>
       <c r="H156" t="str">
-        <v>Meet Me @ The Altar</v>
+        <v>Óscar Maydon</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/meet-me-the-altar/1109900880</v>
+        <v>https://music.apple.com/us/artist/%C3%B3scar-maydon/1524147696</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/live-without/1862777608</v>
+        <v>https://music.apple.com/us/album/poema/1872723468</v>
       </c>
       <c r="L156" t="str">
-        <v>Live Without - Meet Me @ The Altar</v>
+        <v>Poema - Óscar Maydon</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>FANÁTICO</v>
+        <v>Live Without</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/fan%C3%A1tico/1871611852</v>
+        <v>https://music.apple.com/us/song/live-without/1862777625</v>
       </c>
       <c r="D157" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E157" t="str">
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>FANÁTICO - Single</v>
+        <v>WORRIED SICK (Deluxe Edition)</v>
       </c>
       <c r="G157" t="str">
-        <v>3:55</v>
+        <v>2:55</v>
       </c>
       <c r="H157" t="str">
-        <v>Blessd</v>
+        <v>Meet Me @ The Altar</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/blessd/1481245915</v>
+        <v>https://music.apple.com/us/artist/meet-me-the-altar/1109900880</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/fan%C3%A1tico/1871611851</v>
+        <v>https://music.apple.com/us/album/live-without/1862777608</v>
       </c>
       <c r="L157" t="str">
-        <v>FANÁTICO - Blessd</v>
+        <v>Live Without - Meet Me @ The Altar</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Frozen Lake</v>
+        <v>FANÁTICO</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/frozen-lake/1867287070</v>
+        <v>https://music.apple.com/us/song/fan%C3%A1tico/1871611852</v>
       </c>
       <c r="D158" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E158" t="str">
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>Frozen Lake - Single</v>
+        <v>FANÁTICO - Single</v>
       </c>
       <c r="G158" t="str">
-        <v>3:29</v>
+        <v>3:55</v>
       </c>
       <c r="H158" t="str">
-        <v>VOILÀ</v>
+        <v>Blessd</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/voil%C3%A0/1333272109</v>
+        <v>https://music.apple.com/us/artist/blessd/1481245915</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/frozen-lake/1867287069</v>
+        <v>https://music.apple.com/us/album/fan%C3%A1tico/1871611851</v>
       </c>
       <c r="L158" t="str">
-        <v>Frozen Lake - VOILÀ</v>
+        <v>FANÁTICO - Blessd</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Fine Shyt (EB Remix) [feat. Eric Bellinger]</v>
+        <v>Frozen Lake</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/fine-shyt-eb-remix-feat-eric-bellinger/1870964385</v>
+        <v>https://music.apple.com/us/song/frozen-lake/1867287070</v>
       </c>
       <c r="D159" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E159" t="str">
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>Fine Shyt (EB Remix) [feat. Eric Bellinger] - Single</v>
+        <v>Frozen Lake - Single</v>
       </c>
       <c r="G159" t="str">
-        <v>2:45</v>
+        <v>3:29</v>
       </c>
       <c r="H159" t="str">
-        <v>VEDO</v>
+        <v>VOILÀ</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/vedo/267769510</v>
+        <v>https://music.apple.com/us/artist/voil%C3%A0/1333272109</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/fine-shyt-eb-remix-feat-eric-bellinger/1870964384</v>
+        <v>https://music.apple.com/us/album/frozen-lake/1867287069</v>
       </c>
       <c r="L159" t="str">
-        <v>Fine Shyt (EB Remix) [feat. Eric Bellinger] - VEDO</v>
+        <v>Frozen Lake - VOILÀ</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Hell Yeah (Feat. Waxmaster)</v>
+        <v>Fine Shyt (EB Remix) [feat. Eric Bellinger]</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/hell-yeah-feat-waxmaster/1866602820</v>
+        <v>https://music.apple.com/us/song/fine-shyt-eb-remix-feat-eric-bellinger/1870964385</v>
       </c>
       <c r="D160" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E160" t="str">
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>Hell Yeah (Feat. Waxmaster) - Single</v>
+        <v>Fine Shyt (EB Remix) [feat. Eric Bellinger] - Single</v>
       </c>
       <c r="G160" t="str">
-        <v>3:32</v>
+        <v>2:45</v>
       </c>
       <c r="H160" t="str">
-        <v>Chris Lorenzo</v>
+        <v>VEDO</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/chris-lorenzo/621431022</v>
+        <v>https://music.apple.com/us/artist/vedo/267769510</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/hell-yeah-feat-waxmaster/1866602819</v>
+        <v>https://music.apple.com/us/album/fine-shyt-eb-remix-feat-eric-bellinger/1870964384</v>
       </c>
       <c r="L160" t="str">
-        <v>Hell Yeah (Feat. Waxmaster) - Chris Lorenzo</v>
+        <v>Fine Shyt (EB Remix) [feat. Eric Bellinger] - VEDO</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>It’s Like That</v>
+        <v>Hell Yeah (Feat. Waxmaster)</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/its-like-that/1858689757</v>
+        <v>https://music.apple.com/us/song/hell-yeah-feat-waxmaster/1866602820</v>
       </c>
       <c r="D161" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E161" t="str">
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>A Pound of Feathers</v>
+        <v>Hell Yeah (Feat. Waxmaster) - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>3:20</v>
+        <v>3:32</v>
       </c>
       <c r="H161" t="str">
-        <v>The Black Crowes</v>
+        <v>Chris Lorenzo</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/the-black-crowes/2969371</v>
+        <v>https://music.apple.com/us/artist/chris-lorenzo/621431022</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/its-like-that/1858689485</v>
+        <v>https://music.apple.com/us/album/hell-yeah-feat-waxmaster/1866602819</v>
       </c>
       <c r="L161" t="str">
-        <v>It’s Like That - The Black Crowes</v>
+        <v>Hell Yeah (Feat. Waxmaster) - Chris Lorenzo</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>A.S.A.P.</v>
+        <v>It’s Like That</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/a-s-a-p/1833414737</v>
+        <v>https://music.apple.com/us/song/its-like-that/1858689757</v>
       </c>
       <c r="D162" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E162" t="str">
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>A.S.A.P. - Single</v>
+        <v>A Pound of Feathers</v>
       </c>
       <c r="G162" t="str">
-        <v>2:48</v>
+        <v>3:20</v>
       </c>
       <c r="H162" t="str">
-        <v>Mýa</v>
+        <v>The Black Crowes</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/m%C3%BDa/108751</v>
+        <v>https://music.apple.com/us/artist/the-black-crowes/2969371</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/a-s-a-p/1833414736</v>
+        <v>https://music.apple.com/us/album/its-like-that/1858689485</v>
       </c>
       <c r="L162" t="str">
-        <v>A.S.A.P. - Mýa</v>
+        <v>It’s Like That - The Black Crowes</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Once I Say</v>
+        <v>A.S.A.P.</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/once-i-say/1867855025</v>
+        <v>https://music.apple.com/us/song/a-s-a-p/1833414737</v>
       </c>
       <c r="D163" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E163" t="str">
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>PASSION</v>
+        <v>A.S.A.P. - Single</v>
       </c>
       <c r="G163" t="str">
-        <v>3:21</v>
+        <v>2:48</v>
       </c>
       <c r="H163" t="str">
-        <v>Terrace Martin</v>
+        <v>Mýa</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/terrace-martin/27522754</v>
+        <v>https://music.apple.com/us/artist/m%C3%BDa/108751</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/once-i-say/1867854756</v>
+        <v>https://music.apple.com/us/album/a-s-a-p/1833414736</v>
       </c>
       <c r="L163" t="str">
-        <v>Once I Say - Terrace Martin</v>
+        <v>A.S.A.P. - Mýa</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>believer</v>
+        <v>Once I Say</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/believer/1862797080</v>
+        <v>https://music.apple.com/us/song/once-i-say/1867855025</v>
       </c>
       <c r="D164" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E164" t="str">
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>believer - Single</v>
+        <v>PASSION</v>
       </c>
       <c r="G164" t="str">
-        <v>2:57</v>
+        <v>3:21</v>
       </c>
       <c r="H164" t="str">
-        <v>Yuna</v>
+        <v>Terrace Martin</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/yuna/423966062</v>
+        <v>https://music.apple.com/us/artist/terrace-martin/27522754</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/believer/1862796978</v>
+        <v>https://music.apple.com/us/album/once-i-say/1867854756</v>
       </c>
       <c r="L164" t="str">
-        <v>believer - Yuna</v>
+        <v>Once I Say - Terrace Martin</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>I Envy The Wind</v>
+        <v>believer</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/i-envy-the-wind/1863202477</v>
+        <v>https://music.apple.com/us/song/believer/1862797080</v>
       </c>
       <c r="D165" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E165" t="str">
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>I Envy The Wind - Single</v>
+        <v>believer - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>3:51</v>
+        <v>2:57</v>
       </c>
       <c r="H165" t="str">
-        <v>Molly Parden</v>
+        <v>Yuna</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/molly-parden/374789677</v>
+        <v>https://music.apple.com/us/artist/yuna/423966062</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/i-envy-the-wind/1863202476</v>
+        <v>https://music.apple.com/us/album/believer/1862796978</v>
       </c>
       <c r="L165" t="str">
-        <v>I Envy The Wind - Molly Parden</v>
+        <v>believer - Yuna</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>The Alchemist</v>
+        <v>I Envy The Wind</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/the-alchemist/1831827347</v>
+        <v>https://music.apple.com/us/song/i-envy-the-wind/1863202477</v>
       </c>
       <c r="D166" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E166" t="str">
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>The Alchemist</v>
+        <v>I Envy The Wind - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>3:13</v>
+        <v>3:51</v>
       </c>
       <c r="H166" t="str">
-        <v>Bre Kennedy</v>
+        <v>Molly Parden</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/bre-kennedy/1242283415</v>
+        <v>https://music.apple.com/us/artist/molly-parden/374789677</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/the-alchemist/1831827332</v>
+        <v>https://music.apple.com/us/album/i-envy-the-wind/1863202476</v>
       </c>
       <c r="L166" t="str">
-        <v>The Alchemist - Bre Kennedy</v>
+        <v>I Envy The Wind - Molly Parden</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Daysa</v>
+        <v>The Alchemist</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/daysa/1861575845</v>
+        <v>https://music.apple.com/us/song/the-alchemist/1831827347</v>
       </c>
       <c r="D167" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E167" t="str">
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Daysa - Single</v>
+        <v>The Alchemist</v>
       </c>
       <c r="G167" t="str">
-        <v>4:36</v>
+        <v>3:13</v>
       </c>
       <c r="H167" t="str">
-        <v>⌭ IceMorph ⌬</v>
+        <v>Bre Kennedy</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/icemorph/1733236411</v>
+        <v>https://music.apple.com/us/artist/bre-kennedy/1242283415</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/daysa/1861575844</v>
+        <v>https://music.apple.com/us/album/the-alchemist/1831827332</v>
       </c>
       <c r="L167" t="str">
-        <v>Daysa - ⌭ IceMorph ⌬</v>
+        <v>The Alchemist - Bre Kennedy</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Fabulous</v>
+        <v>Daysa</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/fabulous/1862804005</v>
+        <v>https://music.apple.com/us/song/daysa/1861575845</v>
       </c>
       <c r="D168" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E168" t="str">
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Fabulous - Single</v>
+        <v>Daysa - Single</v>
       </c>
       <c r="G168" t="str">
-        <v>2:33</v>
+        <v>4:36</v>
       </c>
       <c r="H168" t="str">
-        <v>MEEK</v>
+        <v>⌭ IceMorph ⌬</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/meek/1784432868</v>
+        <v>https://music.apple.com/us/artist/icemorph/1733236411</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/fabulous/1862804004</v>
+        <v>https://music.apple.com/us/album/daysa/1861575844</v>
       </c>
       <c r="L168" t="str">
-        <v>Fabulous - MEEK</v>
+        <v>Daysa - ⌭ IceMorph ⌬</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Me Asusta Amar Tanto la Soledad</v>
+        <v>Fabulous</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/me-asusta-amar-tanto-la-soledad/1866982109</v>
+        <v>https://music.apple.com/us/song/fabulous/1862804005</v>
       </c>
       <c r="D169" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E169" t="str">
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Me Asusta Amar Tanto la Soledad - Single</v>
+        <v>Fabulous - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>3:22</v>
+        <v>2:33</v>
       </c>
       <c r="H169" t="str">
-        <v>RUBIO</v>
+        <v>MEEK</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/rubio/34747724</v>
+        <v>https://music.apple.com/us/artist/meek/1784432868</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/me-asusta-amar-tanto-la-soledad/1866981907</v>
+        <v>https://music.apple.com/us/album/fabulous/1862804004</v>
       </c>
       <c r="L169" t="str">
-        <v>Me Asusta Amar Tanto la Soledad - RUBIO</v>
+        <v>Fabulous - MEEK</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>brainchem</v>
+        <v>Me Asusta Amar Tanto la Soledad</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/brainchem/1870656942</v>
+        <v>https://music.apple.com/us/song/me-asusta-amar-tanto-la-soledad/1866982109</v>
       </c>
       <c r="D170" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E170" t="str">
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>brainchem - Single</v>
+        <v>Me Asusta Amar Tanto la Soledad - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>2:28</v>
+        <v>3:22</v>
       </c>
       <c r="H170" t="str">
-        <v>EMJAY</v>
+        <v>RUBIO</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/emjay/1517993423</v>
+        <v>https://music.apple.com/us/artist/rubio/34747724</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/brainchem/1870656608</v>
+        <v>https://music.apple.com/us/album/me-asusta-amar-tanto-la-soledad/1866981907</v>
       </c>
       <c r="L170" t="str">
-        <v>brainchem - EMJAY</v>
+        <v>Me Asusta Amar Tanto la Soledad - RUBIO</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Boyfriend In Yo Brain (Notice Me)</v>
+        <v>brainchem</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/boyfriend-in-yo-brain-notice-me/1871675026</v>
+        <v>https://music.apple.com/us/song/brainchem/1870656942</v>
       </c>
       <c r="D171" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E171" t="str">
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>With No Due Respect</v>
+        <v>brainchem - Single</v>
       </c>
       <c r="G171" t="str">
-        <v>2:48</v>
+        <v>2:28</v>
       </c>
       <c r="H171" t="str">
-        <v>Foggieraw</v>
+        <v>EMJAY</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/foggieraw/1152021457</v>
+        <v>https://music.apple.com/us/artist/emjay/1517993423</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/boyfriend-in-yo-brain-notice-me/1871675010</v>
+        <v>https://music.apple.com/us/album/brainchem/1870656608</v>
       </c>
       <c r="L171" t="str">
-        <v>Boyfriend In Yo Brain (Notice Me) - Foggieraw</v>
+        <v>brainchem - EMJAY</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Giants</v>
+        <v>Boyfriend In Yo Brain (Notice Me)</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/giants/1869154957</v>
+        <v>https://music.apple.com/us/song/boyfriend-in-yo-brain-notice-me/1871675026</v>
       </c>
       <c r="D172" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E172" t="str">
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Giants - Single</v>
+        <v>With No Due Respect</v>
       </c>
       <c r="G172" t="str">
-        <v>3:12</v>
+        <v>2:48</v>
       </c>
       <c r="H172" t="str">
-        <v>Picture This</v>
+        <v>Foggieraw</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/picture-this/1194282721</v>
+        <v>https://music.apple.com/us/artist/foggieraw/1152021457</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/giants/1869154821</v>
+        <v>https://music.apple.com/us/album/boyfriend-in-yo-brain-notice-me/1871675010</v>
       </c>
       <c r="L172" t="str">
-        <v>Giants - Picture This</v>
+        <v>Boyfriend In Yo Brain (Notice Me) - Foggieraw</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Scooby</v>
+        <v>Giants</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/scooby/1872510752</v>
+        <v>https://music.apple.com/us/song/giants/1869154957</v>
       </c>
       <c r="D173" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E173" t="str">
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Scooby - Single</v>
+        <v>Giants - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>3:41</v>
+        <v>3:12</v>
       </c>
       <c r="H173" t="str">
-        <v>corook</v>
+        <v>Picture This</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/corook/1514463762</v>
+        <v>https://music.apple.com/us/artist/picture-this/1194282721</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/scooby/1872510751</v>
+        <v>https://music.apple.com/us/album/giants/1869154821</v>
       </c>
       <c r="L173" t="str">
-        <v>Scooby - corook</v>
+        <v>Giants - Picture This</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>La Racha</v>
+        <v>Scooby</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/la-racha/1868757762</v>
+        <v>https://music.apple.com/us/song/scooby/1872510752</v>
       </c>
       <c r="D174" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E174" t="str">
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>La Racha - Single</v>
+        <v>Scooby - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>2:48</v>
+        <v>3:41</v>
       </c>
       <c r="H174" t="str">
-        <v>Hermanos Espinoza</v>
+        <v>corook</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/hermanos-espinoza/1613044599</v>
+        <v>https://music.apple.com/us/artist/corook/1514463762</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/la-racha/1868757747</v>
+        <v>https://music.apple.com/us/album/scooby/1872510751</v>
       </c>
       <c r="L174" t="str">
-        <v>La Racha - Hermanos Espinoza</v>
+        <v>Scooby - corook</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>So Am I</v>
+        <v>La Racha</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/so-am-i/1867012209</v>
+        <v>https://music.apple.com/us/song/la-racha/1868757762</v>
       </c>
       <c r="D175" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E175" t="str">
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>Tell Me How You Really Feel</v>
+        <v>La Racha - Single</v>
       </c>
       <c r="G175" t="str">
-        <v>2:50</v>
+        <v>2:48</v>
       </c>
       <c r="H175" t="str">
-        <v>Katelyn Tarver</v>
+        <v>Hermanos Espinoza</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/katelyn-tarver/2356378</v>
+        <v>https://music.apple.com/us/artist/hermanos-espinoza/1613044599</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/so-am-i/1867012005</v>
+        <v>https://music.apple.com/us/album/la-racha/1868757747</v>
       </c>
       <c r="L175" t="str">
-        <v>So Am I - Katelyn Tarver</v>
+        <v>La Racha - Hermanos Espinoza</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>best thing</v>
+        <v>So Am I</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/best-thing/1860673616</v>
+        <v>https://music.apple.com/us/song/so-am-i/1867012209</v>
       </c>
       <c r="D176" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E176" t="str">
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>best thing - Single</v>
+        <v>Tell Me How You Really Feel</v>
       </c>
       <c r="G176" t="str">
-        <v>4:27</v>
+        <v>2:50</v>
       </c>
       <c r="H176" t="str">
-        <v>WRABEL</v>
+        <v>Katelyn Tarver</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/wrabel/435072161</v>
+        <v>https://music.apple.com/us/artist/katelyn-tarver/2356378</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/best-thing/1860673615</v>
+        <v>https://music.apple.com/us/album/so-am-i/1867012005</v>
       </c>
       <c r="L176" t="str">
-        <v>best thing - WRABEL</v>
+        <v>So Am I - Katelyn Tarver</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Count It Back</v>
+        <v>best thing</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/count-it-back/1855219865</v>
+        <v>https://music.apple.com/us/song/best-thing/1860673616</v>
       </c>
       <c r="D177" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E177" t="str">
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Magic Boy</v>
+        <v>best thing - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>2:52</v>
+        <v>4:27</v>
       </c>
       <c r="H177" t="str">
-        <v>Bartees Strange</v>
+        <v>WRABEL</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/bartees-strange/1450776625</v>
+        <v>https://music.apple.com/us/artist/wrabel/435072161</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/count-it-back/1855219618</v>
+        <v>https://music.apple.com/us/album/best-thing/1860673615</v>
       </c>
       <c r="L177" t="str">
-        <v>Count It Back - Bartees Strange</v>
+        <v>best thing - WRABEL</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Good Girl</v>
+        <v>Count It Back</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/good-girl/1862640697</v>
+        <v>https://music.apple.com/us/song/count-it-back/1855219865</v>
       </c>
       <c r="D178" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E178" t="str">
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Good Girl - Single</v>
+        <v>Magic Boy</v>
       </c>
       <c r="G178" t="str">
-        <v>4:23</v>
+        <v>2:52</v>
       </c>
       <c r="H178" t="str">
-        <v>Paris Paloma</v>
+        <v>Bartees Strange</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/paris-paloma/1530898376</v>
+        <v>https://music.apple.com/us/artist/bartees-strange/1450776625</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/good-girl/1862640694</v>
+        <v>https://music.apple.com/us/album/count-it-back/1855219618</v>
       </c>
       <c r="L178" t="str">
-        <v>Good Girl - Paris Paloma</v>
+        <v>Count It Back - Bartees Strange</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>MY REVIVAL</v>
+        <v>Good Girl</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/my-revival/1869465104</v>
+        <v>https://music.apple.com/us/song/good-girl/1862640697</v>
       </c>
       <c r="D179" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E179" t="str">
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>HEARTLAND (Deluxe Version)</v>
+        <v>Good Girl - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>3:34</v>
+        <v>4:23</v>
       </c>
       <c r="H179" t="str">
-        <v>MORGXN</v>
+        <v>Paris Paloma</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/morgxn/1116360149</v>
+        <v>https://music.apple.com/us/artist/paris-paloma/1530898376</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/my-revival/1869464853</v>
+        <v>https://music.apple.com/us/album/good-girl/1862640694</v>
       </c>
       <c r="L179" t="str">
-        <v>MY REVIVAL - MORGXN</v>
+        <v>Good Girl - Paris Paloma</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Run My Way</v>
+        <v>MY REVIVAL</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/run-my-way/1860964996</v>
+        <v>https://music.apple.com/us/song/my-revival/1869465104</v>
       </c>
       <c r="D180" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E180" t="str">
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Run My Way - Single</v>
+        <v>HEARTLAND (Deluxe Version)</v>
       </c>
       <c r="G180" t="str">
-        <v>2:44</v>
+        <v>3:34</v>
       </c>
       <c r="H180" t="str">
-        <v>December 10</v>
+        <v>MORGXN</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/december-10/1414032285</v>
+        <v>https://music.apple.com/us/artist/morgxn/1116360149</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/run-my-way/1860964992</v>
+        <v>https://music.apple.com/us/album/my-revival/1869464853</v>
       </c>
       <c r="L180" t="str">
-        <v>Run My Way - December 10</v>
+        <v>MY REVIVAL - MORGXN</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Cold Night</v>
+        <v>Run My Way</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/cold-night/1867687787</v>
+        <v>https://music.apple.com/us/song/run-my-way/1860964996</v>
       </c>
       <c r="D181" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E181" t="str">
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Cold Night - Single</v>
+        <v>Run My Way - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>3:12</v>
+        <v>2:44</v>
       </c>
       <c r="H181" t="str">
-        <v>HANA</v>
+        <v>December 10</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/hana/1792783458</v>
+        <v>https://music.apple.com/us/artist/december-10/1414032285</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/cold-night/1867687784</v>
+        <v>https://music.apple.com/us/album/run-my-way/1860964992</v>
       </c>
       <c r="L181" t="str">
-        <v>Cold Night - HANA</v>
+        <v>Run My Way - December 10</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Away With The Fairies</v>
+        <v>Cold Night</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/away-with-the-fairies/1870603474</v>
+        <v>https://music.apple.com/us/song/cold-night/1867687787</v>
       </c>
       <c r="D182" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E182" t="str">
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Away With The Fairies - Single</v>
+        <v>Cold Night - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>2:28</v>
+        <v>3:12</v>
       </c>
       <c r="H182" t="str">
-        <v>LUNA</v>
+        <v>HANA</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/luna/1439101807</v>
+        <v>https://music.apple.com/us/artist/hana/1792783458</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/away-with-the-fairies/1870603470</v>
+        <v>https://music.apple.com/us/album/cold-night/1867687784</v>
       </c>
       <c r="L182" t="str">
-        <v>Away With The Fairies - LUNA</v>
+        <v>Cold Night - HANA</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Fragile</v>
+        <v>Away With The Fairies</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/fragile/1866957569</v>
+        <v>https://music.apple.com/us/song/away-with-the-fairies/1870603474</v>
       </c>
       <c r="D183" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E183" t="str">
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Fragile - Single</v>
+        <v>Away With The Fairies - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>3:10</v>
+        <v>2:28</v>
       </c>
       <c r="H183" t="str">
-        <v>Anajah</v>
+        <v>LUNA</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/anajah/1355166756</v>
+        <v>https://music.apple.com/us/artist/luna/1439101807</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/fragile/1866957565</v>
+        <v>https://music.apple.com/us/album/away-with-the-fairies/1870603470</v>
       </c>
       <c r="L183" t="str">
-        <v>Fragile - Anajah</v>
+        <v>Away With The Fairies - LUNA</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Slow Dancin'</v>
+        <v>Fragile</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/slow-dancin/1871537173</v>
+        <v>https://music.apple.com/us/song/fragile/1866957569</v>
       </c>
       <c r="D184" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E184" t="str">
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>Slow Dancin' - Single</v>
+        <v>Fragile - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>2:04</v>
+        <v>3:10</v>
       </c>
       <c r="H184" t="str">
-        <v>STELLA LEFTY</v>
+        <v>Anajah</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/stella-lefty/1641742186</v>
+        <v>https://music.apple.com/us/artist/anajah/1355166756</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/slow-dancin/1871537170</v>
+        <v>https://music.apple.com/us/album/fragile/1866957565</v>
       </c>
       <c r="L184" t="str">
-        <v>Slow Dancin' - STELLA LEFTY</v>
+        <v>Fragile - Anajah</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Never Kissed a Cowboy</v>
+        <v>Slow Dancin'</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/never-kissed-a-cowboy/1866744530</v>
+        <v>https://music.apple.com/us/song/slow-dancin/1871537173</v>
       </c>
       <c r="D185" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E185" t="str">
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>Never Kissed a Cowboy - Single</v>
+        <v>Slow Dancin' - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>3:04</v>
+        <v>2:04</v>
       </c>
       <c r="H185" t="str">
-        <v>Lily Meola</v>
+        <v>STELLA LEFTY</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/lily-meola/678241726</v>
+        <v>https://music.apple.com/us/artist/stella-lefty/1641742186</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/never-kissed-a-cowboy/1866744528</v>
+        <v>https://music.apple.com/us/album/slow-dancin/1871537170</v>
       </c>
       <c r="L185" t="str">
-        <v>Never Kissed a Cowboy - Lily Meola</v>
+        <v>Slow Dancin' - STELLA LEFTY</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>More Of What Matters</v>
+        <v>Never Kissed a Cowboy</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/more-of-what-matters/1871592720</v>
+        <v>https://music.apple.com/us/song/never-kissed-a-cowboy/1866744530</v>
       </c>
       <c r="D186" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E186" t="str">
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>More Of What Matters - Single</v>
+        <v>Never Kissed a Cowboy - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>3:41</v>
+        <v>3:04</v>
       </c>
       <c r="H186" t="str">
-        <v>Jamey Johnson</v>
+        <v>Lily Meola</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/jamey-johnson/81030634</v>
+        <v>https://music.apple.com/us/artist/lily-meola/678241726</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/more-of-what-matters/1871592717</v>
+        <v>https://music.apple.com/us/album/never-kissed-a-cowboy/1866744528</v>
       </c>
       <c r="L186" t="str">
-        <v>More Of What Matters - Jamey Johnson</v>
+        <v>Never Kissed a Cowboy - Lily Meola</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Is This The Real You</v>
+        <v>More Of What Matters</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/is-this-the-real-you/1869323368</v>
+        <v>https://music.apple.com/us/song/more-of-what-matters/1871592720</v>
       </c>
       <c r="D187" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E187" t="str">
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>ONE</v>
+        <v>More Of What Matters - Single</v>
       </c>
       <c r="G187" t="str">
-        <v>3:46</v>
+        <v>3:41</v>
       </c>
       <c r="H187" t="str">
-        <v>Sevendust</v>
+        <v>Jamey Johnson</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/sevendust/13125174</v>
+        <v>https://music.apple.com/us/artist/jamey-johnson/81030634</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/is-this-the-real-you/1869323199</v>
+        <v>https://music.apple.com/us/album/more-of-what-matters/1871592717</v>
       </c>
       <c r="L187" t="str">
-        <v>Is This The Real You - Sevendust</v>
+        <v>More Of What Matters - Jamey Johnson</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Hud</v>
+        <v>Is This The Real You</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/hud/1842015019</v>
+        <v>https://music.apple.com/us/song/is-this-the-real-you/1869323368</v>
       </c>
       <c r="D188" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E188" t="str">
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>DREAMCRUSH</v>
+        <v>ONE</v>
       </c>
       <c r="G188" t="str">
-        <v>4:46</v>
+        <v>3:46</v>
       </c>
       <c r="H188" t="str">
-        <v>MØL</v>
+        <v>Sevendust</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/m%C3%B8l/975294671</v>
+        <v>https://music.apple.com/us/artist/sevendust/13125174</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/hud/1842014730</v>
+        <v>https://music.apple.com/us/album/is-this-the-real-you/1869323199</v>
       </c>
       <c r="L188" t="str">
-        <v>Hud - MØL</v>
+        <v>Is This The Real You - Sevendust</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Ego Death</v>
+        <v>Hud</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/ego-death/1867855427</v>
+        <v>https://music.apple.com/us/song/hud/1842015019</v>
       </c>
       <c r="D189" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E189" t="str">
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Ego Death - Single</v>
+        <v>DREAMCRUSH</v>
       </c>
       <c r="G189" t="str">
-        <v>2:12</v>
+        <v>4:46</v>
       </c>
       <c r="H189" t="str">
-        <v>Atreyu</v>
+        <v>MØL</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/atreyu/6095061</v>
+        <v>https://music.apple.com/us/artist/m%C3%B8l/975294671</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/ego-death/1867855173</v>
+        <v>https://music.apple.com/us/album/hud/1842014730</v>
       </c>
       <c r="L189" t="str">
-        <v>Ego Death - Atreyu</v>
+        <v>Hud - MØL</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Gas Station Love (remix)</v>
+        <v>Ego Death</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/gas-station-love-remix/1872150728</v>
+        <v>https://music.apple.com/us/song/ego-death/1867855427</v>
       </c>
       <c r="D190" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E190" t="str">
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Gas Station Love (remix) - Single</v>
+        <v>Ego Death - Single</v>
       </c>
       <c r="G190" t="str">
-        <v>4:05</v>
+        <v>2:12</v>
       </c>
       <c r="H190" t="str">
-        <v>EJ Jones</v>
+        <v>Atreyu</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/ej-jones/1781306141</v>
+        <v>https://music.apple.com/us/artist/atreyu/6095061</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/gas-station-love-remix/1872150723</v>
+        <v>https://music.apple.com/us/album/ego-death/1867855173</v>
       </c>
       <c r="L190" t="str">
-        <v>Gas Station Love (remix) - EJ Jones</v>
+        <v>Ego Death - Atreyu</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Disappear</v>
+        <v>Gas Station Love (remix)</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/disappear/1861907311</v>
+        <v>https://music.apple.com/us/song/gas-station-love-remix/1872150728</v>
       </c>
       <c r="D191" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E191" t="str">
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Disappear</v>
+        <v>Gas Station Love (remix) - Single</v>
       </c>
       <c r="G191" t="str">
-        <v>5:50</v>
+        <v>4:05</v>
       </c>
       <c r="H191" t="str">
-        <v>Lane 8</v>
+        <v>EJ Jones</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/lane-8/634763116</v>
+        <v>https://music.apple.com/us/artist/ej-jones/1781306141</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/disappear/1861907305</v>
+        <v>https://music.apple.com/us/album/gas-station-love-remix/1872150723</v>
       </c>
       <c r="L191" t="str">
-        <v>Disappear - Lane 8</v>
+        <v>Gas Station Love (remix) - EJ Jones</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Misbehave</v>
+        <v>Disappear</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/misbehave/1859630128</v>
+        <v>https://music.apple.com/us/song/disappear/1861907311</v>
       </c>
       <c r="D192" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E192" t="str">
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>Misbehave - Single</v>
+        <v>Disappear</v>
       </c>
       <c r="G192" t="str">
-        <v>3:43</v>
+        <v>5:50</v>
       </c>
       <c r="H192" t="str">
-        <v>Aluna</v>
+        <v>Lane 8</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/aluna/1508017201</v>
+        <v>https://music.apple.com/us/artist/lane-8/634763116</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/misbehave/1859630126</v>
+        <v>https://music.apple.com/us/album/disappear/1861907305</v>
       </c>
       <c r="L192" t="str">
-        <v>Misbehave - Aluna</v>
+        <v>Disappear - Lane 8</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Club Bizarre</v>
+        <v>Misbehave</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/club-bizarre/1870355078</v>
+        <v>https://music.apple.com/us/song/misbehave/1859630128</v>
       </c>
       <c r="D193" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E193" t="str">
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>Club Bizarre - Single</v>
+        <v>Misbehave - Single</v>
       </c>
       <c r="G193" t="str">
-        <v>2:47</v>
+        <v>3:43</v>
       </c>
       <c r="H193" t="str">
-        <v>Alok</v>
+        <v>Aluna</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/alok/324709167</v>
+        <v>https://music.apple.com/us/artist/aluna/1508017201</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/club-bizarre/1870355077</v>
+        <v>https://music.apple.com/us/album/misbehave/1859630126</v>
       </c>
       <c r="L193" t="str">
-        <v>Club Bizarre - Alok</v>
+        <v>Misbehave - Aluna</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Fly</v>
+        <v>Club Bizarre</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/fly/1867903625</v>
+        <v>https://music.apple.com/us/song/club-bizarre/1870355078</v>
       </c>
       <c r="D194" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E194" t="str">
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Fly - Single</v>
+        <v>Club Bizarre - Single</v>
       </c>
       <c r="G194" t="str">
-        <v>3:04</v>
+        <v>2:47</v>
       </c>
       <c r="H194" t="str">
-        <v>Stephen Stanley</v>
+        <v>Alok</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/stephen-stanley/28074609</v>
+        <v>https://music.apple.com/us/artist/alok/324709167</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/fly/1867903548</v>
+        <v>https://music.apple.com/us/album/club-bizarre/1870355077</v>
       </c>
       <c r="L194" t="str">
-        <v>Fly - Stephen Stanley</v>
+        <v>Club Bizarre - Alok</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>ily anyway</v>
+        <v>Fly</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/ily-anyway/1870369432</v>
+        <v>https://music.apple.com/us/song/fly/1867903625</v>
       </c>
       <c r="D195" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E195" t="str">
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>ily anyway - Single</v>
+        <v>Fly - Single</v>
       </c>
       <c r="G195" t="str">
-        <v>3:05</v>
+        <v>3:04</v>
       </c>
       <c r="H195" t="str">
-        <v>Strings &amp; Heart</v>
+        <v>Stephen Stanley</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/strings-heart/1435173742</v>
+        <v>https://music.apple.com/us/artist/stephen-stanley/28074609</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/ily-anyway/1870369426</v>
+        <v>https://music.apple.com/us/album/fly/1867903548</v>
       </c>
       <c r="L195" t="str">
-        <v>ily anyway - Strings &amp; Heart</v>
+        <v>Fly - Stephen Stanley</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>George Jones (feat. Angela Autumn)</v>
+        <v>ily anyway</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/george-jones-feat-angela-autumn/1867306007</v>
+        <v>https://music.apple.com/us/song/ily-anyway/1870369432</v>
       </c>
       <c r="D196" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E196" t="str">
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>Nellene - EP</v>
+        <v>ily anyway - Single</v>
       </c>
       <c r="G196" t="str">
-        <v>3:35</v>
+        <v>3:05</v>
       </c>
       <c r="H196" t="str">
-        <v>Deloyd Elze</v>
+        <v>Strings &amp; Heart</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/deloyd-elze/1699032462</v>
+        <v>https://music.apple.com/us/artist/strings-heart/1435173742</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/george-jones-feat-angela-autumn/1867306004</v>
+        <v>https://music.apple.com/us/album/ily-anyway/1870369426</v>
       </c>
       <c r="L196" t="str">
-        <v>George Jones (feat. Angela Autumn) - Deloyd Elze</v>
+        <v>ily anyway - Strings &amp; Heart</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Kiss Big</v>
+        <v>George Jones (feat. Angela Autumn)</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/kiss-big/1837292261</v>
+        <v>https://music.apple.com/us/song/george-jones-feat-angela-autumn/1867306007</v>
       </c>
       <c r="D197" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E197" t="str">
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>Kiss Big</v>
+        <v>Nellene - EP</v>
       </c>
       <c r="G197" t="str">
-        <v>3:41</v>
+        <v>3:35</v>
       </c>
       <c r="H197" t="str">
-        <v>Ailbhe Reddy</v>
+        <v>Deloyd Elze</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/ailbhe-reddy/947186338</v>
+        <v>https://music.apple.com/us/artist/deloyd-elze/1699032462</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/kiss-big/1837292249</v>
+        <v>https://music.apple.com/us/album/george-jones-feat-angela-autumn/1867306004</v>
       </c>
       <c r="L197" t="str">
-        <v>Kiss Big - Ailbhe Reddy</v>
+        <v>George Jones (feat. Angela Autumn) - Deloyd Elze</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>praxis</v>
+        <v>Kiss Big</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/praxis/1845253734</v>
+        <v>https://music.apple.com/us/song/kiss-big/1837292261</v>
       </c>
       <c r="D198" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E198" t="str">
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>Whole World As Vigil</v>
+        <v>Kiss Big</v>
       </c>
       <c r="G198" t="str">
-        <v>3:28</v>
+        <v>3:41</v>
       </c>
       <c r="H198" t="str">
-        <v>Lauren Auder</v>
+        <v>Ailbhe Reddy</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/lauren-auder/1096049552</v>
+        <v>https://music.apple.com/us/artist/ailbhe-reddy/947186338</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/praxis/1845253730</v>
+        <v>https://music.apple.com/us/album/kiss-big/1837292249</v>
       </c>
       <c r="L198" t="str">
-        <v>praxis - Lauren Auder</v>
+        <v>Kiss Big - Ailbhe Reddy</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>House</v>
+        <v>praxis</v>
       </c>
       <c r="B199" t="str">
         <v/>
       </c>
       <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/house/1866696487</v>
+        <v>https://music.apple.com/us/song/praxis/1845253734</v>
       </c>
       <c r="D199" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E199" t="str">
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>House - Single</v>
+        <v>Whole World As Vigil</v>
       </c>
       <c r="G199" t="str">
-        <v>2:30</v>
+        <v>3:28</v>
       </c>
       <c r="H199" t="str">
-        <v>Connie Converse</v>
+        <v>Lauren Auder</v>
       </c>
       <c r="I199" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/connie-converse/308326962</v>
+        <v>https://music.apple.com/us/artist/lauren-auder/1096049552</v>
       </c>
       <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/house/1866696486</v>
+        <v>https://music.apple.com/us/album/praxis/1845253730</v>
       </c>
       <c r="L199" t="str">
-        <v>House - Connie Converse</v>
+        <v>praxis - Lauren Auder</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Cowboy Without a Clue</v>
+        <v>House</v>
       </c>
       <c r="B200" t="str">
         <v/>
       </c>
       <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/cowboy-without-a-clue/1834024322</v>
+        <v>https://music.apple.com/us/song/house/1866696487</v>
       </c>
       <c r="D200" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E200" t="str">
         <v/>
       </c>
       <c r="F200" t="str">
-        <v>No Love Lost to Kindness</v>
+        <v>House - Single</v>
       </c>
       <c r="G200" t="str">
-        <v>3:57</v>
+        <v>2:30</v>
       </c>
       <c r="H200" t="str">
-        <v>Yumi Zouma</v>
+        <v>Connie Converse</v>
       </c>
       <c r="I200" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J200" t="str">
-        <v>https://music.apple.com/us/artist/yumi-zouma/795031200</v>
+        <v>https://music.apple.com/us/artist/connie-converse/308326962</v>
       </c>
       <c r="K200" t="str">
-        <v>https://music.apple.com/us/album/cowboy-without-a-clue/1834024311</v>
+        <v>https://music.apple.com/us/album/house/1866696486</v>
       </c>
       <c r="L200" t="str">
-        <v>Cowboy Without a Clue - Yumi Zouma</v>
+        <v>House - Connie Converse</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Brincar</v>
+        <v>Cowboy Without a Clue</v>
       </c>
       <c r="B201" t="str">
         <v/>
       </c>
       <c r="C201" t="str">
-        <v>https://music.apple.com/us/song/brincar/1871554907</v>
+        <v>https://music.apple.com/us/song/cowboy-without-a-clue/1834024322</v>
       </c>
       <c r="D201" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E201" t="str">
         <v/>
       </c>
       <c r="F201" t="str">
-        <v>JET LAG - EP</v>
+        <v>No Love Lost to Kindness</v>
       </c>
       <c r="G201" t="str">
-        <v>3:06</v>
+        <v>3:57</v>
       </c>
       <c r="H201" t="str">
-        <v>J Castle</v>
+        <v>Yumi Zouma</v>
       </c>
       <c r="I201" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J201" t="str">
-        <v>https://music.apple.com/us/artist/j-castle/309829058</v>
+        <v>https://music.apple.com/us/artist/yumi-zouma/795031200</v>
       </c>
       <c r="K201" t="str">
-        <v>https://music.apple.com/us/album/brincar/1871554901</v>
+        <v>https://music.apple.com/us/album/cowboy-without-a-clue/1834024311</v>
       </c>
       <c r="L201" t="str">
-        <v>Brincar - J Castle</v>
+        <v>Cowboy Without a Clue - Yumi Zouma</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
+        <v>Brincar</v>
+      </c>
+      <c r="B202" t="str">
+        <v/>
+      </c>
+      <c r="C202" t="str">
+        <v>https://music.apple.com/us/song/brincar/1871554907</v>
+      </c>
+      <c r="D202" t="str">
+        <v>2026-02-02</v>
+      </c>
+      <c r="E202" t="str">
+        <v/>
+      </c>
+      <c r="F202" t="str">
+        <v>JET LAG - EP</v>
+      </c>
+      <c r="G202" t="str">
+        <v>3:06</v>
+      </c>
+      <c r="H202" t="str">
+        <v>J Castle</v>
+      </c>
+      <c r="I202" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J202" t="str">
+        <v>https://music.apple.com/us/artist/j-castle/309829058</v>
+      </c>
+      <c r="K202" t="str">
+        <v>https://music.apple.com/us/album/brincar/1871554901</v>
+      </c>
+      <c r="L202" t="str">
+        <v>Brincar - J Castle</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="str">
         <v>Quién</v>
       </c>
-      <c r="B202" t="str">
-        <v/>
-      </c>
-      <c r="C202" t="str">
+      <c r="B203" t="str">
+        <v/>
+      </c>
+      <c r="C203" t="str">
         <v>https://music.apple.com/us/song/qui%C3%A9n/1870329662</v>
       </c>
-      <c r="D202" t="str">
-        <v>2026-02-01</v>
-      </c>
-      <c r="E202" t="str">
-        <v/>
-      </c>
-      <c r="F202" t="str">
+      <c r="D203" t="str">
+        <v>2026-02-02</v>
+      </c>
+      <c r="E203" t="str">
+        <v/>
+      </c>
+      <c r="F203" t="str">
         <v>Quién - Single</v>
       </c>
-      <c r="G202" t="str">
+      <c r="G203" t="str">
         <v>4:19</v>
       </c>
-      <c r="H202" t="str">
+      <c r="H203" t="str">
         <v>Daniela Darcourt</v>
       </c>
-      <c r="I202" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J202" t="str">
+      <c r="I203" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J203" t="str">
         <v>https://music.apple.com/us/artist/daniela-darcourt/1396749684</v>
       </c>
-      <c r="K202" t="str">
+      <c r="K203" t="str">
         <v>https://music.apple.com/us/album/qui%C3%A9n/1870329660</v>
       </c>
-      <c r="L202" t="str">
+      <c r="L203" t="str">
         <v>Quién - Daniela Darcourt</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L202"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L203"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
@@ -1918,7 +1918,7 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>I Had To Explain How Music Works LIVE In Concert</v>
+        <v>I Had To Explain "How Music Works" LIVE In Concert</v>
       </c>
       <c r="B41" t="str">
         <v>4 days ago</v>
@@ -1951,7 +1951,7 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>I Had To Explain How Music Works LIVE In Concert - Marcin</v>
+        <v>I Had To Explain "How Music Works" LIVE In Concert - Marcin</v>
       </c>
     </row>
     <row r="42">
@@ -2073,7 +2073,7 @@
         <v>Clinton Kane - this is my last love song to you (Official Lyric Video)</v>
       </c>
       <c r="B45" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C45" t="str">
         <v>https://www.youtube.com/watch?v=-5Aa8NTiRqE</v>
@@ -2085,7 +2085,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G45" t="str">
         <v>3:34</v>
@@ -3099,7 +3099,7 @@
         <v>Lauren Sanderson - SPELL IT OUT (Official Music Video)</v>
       </c>
       <c r="B72" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C72" t="str">
         <v>https://www.youtube.com/watch?v=kfF0bVZMCw0</v>
@@ -3111,7 +3111,7 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G72" t="str">
         <v>2:34</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
@@ -971,7 +971,7 @@
         <v>SANTOS BRAVOS “KAWASAKI” Performance Video</v>
       </c>
       <c r="B16" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=Cmy8CsYIUL0</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G16" t="str">
         <v>2:41</v>
@@ -1009,7 +1009,7 @@
         <v>Ella Langley - Dandelion (Official Visualizer)</v>
       </c>
       <c r="B17" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=sf6eRmInk1s</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G17" t="str">
         <v>4:01</v>
@@ -1047,7 +1047,7 @@
         <v>Dogpark - Dandelion (Official Music Video)</v>
       </c>
       <c r="B18" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=fv9prIYHHzk</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G18" t="str">
         <v>3:16</v>
@@ -1085,7 +1085,7 @@
         <v>Lauren Spencer Smith - Natural Disaster (Visualizer)</v>
       </c>
       <c r="B19" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=T9YvLA2cdZs</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G19" t="str">
         <v>3:03</v>
@@ -1123,7 +1123,7 @@
         <v>ERNEST - Lorelei (Official Music Video)</v>
       </c>
       <c r="B20" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=dPWc_6IdDJk</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G20" t="str">
         <v>2:41</v>
@@ -1161,7 +1161,7 @@
         <v>Labrinth - I Keep My Promises (Official Audio)</v>
       </c>
       <c r="B21" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=CV5rR9JZK-0</v>
@@ -1173,7 +1173,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G21" t="str">
         <v>3:05</v>
@@ -1199,7 +1199,7 @@
         <v>Grace VanderWaal - Prettier (Official Lyric Video)</v>
       </c>
       <c r="B22" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=9HwTj3NZ16E</v>
@@ -1211,7 +1211,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G22" t="str">
         <v>2:46</v>
@@ -1237,7 +1237,7 @@
         <v>VOILÀ - Frozen Lake (Official Lyric Video)</v>
       </c>
       <c r="B23" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=Lmus-UbL1H0</v>
@@ -1249,7 +1249,7 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G23" t="str">
         <v>3:32</v>
@@ -1275,7 +1275,7 @@
         <v>Cannons - Starlight (Official Video)</v>
       </c>
       <c r="B24" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=bu6WSMDDPGY</v>
@@ -1287,7 +1287,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G24" t="str">
         <v>3:42</v>
@@ -1313,7 +1313,7 @@
         <v>Kylie Morgan - Like My Own (Official Video)</v>
       </c>
       <c r="B25" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=zcYeoGBglC0</v>
@@ -1325,7 +1325,7 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G25" t="str">
         <v>2:38</v>
@@ -1351,7 +1351,7 @@
         <v>Lizzy McAlpine - House of the Rising Sun (Audio)</v>
       </c>
       <c r="B26" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=3igYRj82EiU</v>
@@ -1363,7 +1363,7 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G26" t="str">
         <v>3:10</v>
@@ -1389,7 +1389,7 @@
         <v>Willie Nelson - Heart Of America (From The Gray House Original Soundtrack)</v>
       </c>
       <c r="B27" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C27" t="str">
         <v>https://www.youtube.com/watch?v=0bhcO4Yphuo</v>
@@ -1401,7 +1401,7 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G27" t="str">
         <v>3:57</v>
@@ -1427,7 +1427,7 @@
         <v>Jeremy Camp - No Survivors (Live) ft. Skillet</v>
       </c>
       <c r="B28" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=Jjz1wFe5dMo</v>
@@ -1439,7 +1439,7 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G28" t="str">
         <v>2:19</v>
@@ -2415,7 +2415,7 @@
         <v>Bella White - Dream Song (Official Audio)</v>
       </c>
       <c r="B54" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C54" t="str">
         <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
@@ -2427,7 +2427,7 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G54" t="str">
         <v>4:37</v>
@@ -2453,7 +2453,7 @@
         <v>Ryan Wright - Film School Kids (Official Video)</v>
       </c>
       <c r="B55" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C55" t="str">
         <v>https://www.youtube.com/watch?v=pnAz9RwGSek</v>
@@ -2465,7 +2465,7 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G55" t="str">
         <v>4:06</v>
@@ -2491,7 +2491,7 @@
         <v>Dove Cameron - Do I Wanna Know? (Official Visualizer)</v>
       </c>
       <c r="B56" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C56" t="str">
         <v>https://www.youtube.com/watch?v=u7aPv2saz_I</v>
@@ -2503,7 +2503,7 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G56" t="str">
         <v>3:54</v>
@@ -2529,7 +2529,7 @@
         <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video)</v>
       </c>
       <c r="B57" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C57" t="str">
         <v>https://www.youtube.com/watch?v=WGb8KVdqs6k</v>
@@ -2541,7 +2541,7 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G57" t="str">
         <v>4:10</v>
@@ -2567,7 +2567,7 @@
         <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video)</v>
       </c>
       <c r="B58" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C58" t="str">
         <v>https://www.youtube.com/watch?v=X1ZeY4Y3l1M</v>
@@ -2579,7 +2579,7 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G58" t="str">
         <v>3:26</v>
@@ -2643,7 +2643,7 @@
         <v>Mitchell Tenpenny - You Phase (Official Music Video)</v>
       </c>
       <c r="B60" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C60" t="str">
         <v>https://www.youtube.com/watch?v=UPuK6wV5Zco</v>
@@ -2655,7 +2655,7 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G60" t="str">
         <v>2:56</v>
@@ -2681,7 +2681,7 @@
         <v>Tauren Wells - Breathe On It (Official Lyric Video)</v>
       </c>
       <c r="B61" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C61" t="str">
         <v>https://www.youtube.com/watch?v=9hW9sNMn2A0</v>
@@ -2693,7 +2693,7 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G61" t="str">
         <v>4:01</v>
@@ -2719,7 +2719,7 @@
         <v>Maiah Manser - Feeling it All (Official Music Video)</v>
       </c>
       <c r="B62" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C62" t="str">
         <v>https://www.youtube.com/watch?v=JMYvXleIwfU</v>
@@ -2731,7 +2731,7 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G62" t="str">
         <v>3:05</v>
@@ -2757,7 +2757,7 @@
         <v>Taylor Austin Dye - Man For That (Official Music Video)</v>
       </c>
       <c r="B63" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C63" t="str">
         <v>https://www.youtube.com/watch?v=vOzX-o11seI</v>
@@ -2769,7 +2769,7 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G63" t="str">
         <v>2:27</v>
@@ -2795,7 +2795,7 @@
         <v>Chelsea Cutler - BAD (Official Video)</v>
       </c>
       <c r="B64" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C64" t="str">
         <v>https://www.youtube.com/watch?v=86k4E6ydHVU</v>
@@ -2807,7 +2807,7 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G64" t="str">
         <v>2:34</v>
@@ -2833,7 +2833,7 @@
         <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video)</v>
       </c>
       <c r="B65" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C65" t="str">
         <v>https://www.youtube.com/watch?v=-UWIFAiOOPE</v>
@@ -2845,7 +2845,7 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G65" t="str">
         <v>3:13</v>
@@ -2871,7 +2871,7 @@
         <v>Louis Tomlinson - Dark To Light (Visualiser)</v>
       </c>
       <c r="B66" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C66" t="str">
         <v>https://www.youtube.com/watch?v=02QyA29poAM</v>
@@ -2883,7 +2883,7 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G66" t="str">
         <v>3:13</v>
@@ -2909,7 +2909,7 @@
         <v>CAIN - So Long Sad Songs (Lyric Video)</v>
       </c>
       <c r="B67" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C67" t="str">
         <v>https://www.youtube.com/watch?v=feOv8nufa_I</v>
@@ -2921,7 +2921,7 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G67" t="str">
         <v>3:08</v>
@@ -3213,7 +3213,7 @@
         <v>The Avett Brothers - Matrimony (Official Video)</v>
       </c>
       <c r="B75" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C75" t="str">
         <v>https://www.youtube.com/watch?v=7sD9-MtV9CY</v>
@@ -3225,7 +3225,7 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G75" t="str">
         <v>3:06</v>
@@ -3251,7 +3251,7 @@
         <v>Jordana Bryant - Love Like That (Official Video)</v>
       </c>
       <c r="B76" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C76" t="str">
         <v>https://www.youtube.com/watch?v=3ATlH-Rtzmk</v>
@@ -3263,7 +3263,7 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G76" t="str">
         <v>3:21</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
@@ -895,7 +895,7 @@
         <v>Katelyn Tarver - So Am I (Official Music Video)</v>
       </c>
       <c r="B14" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=MjUiVPzMQHw</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G14" t="str">
         <v>2:52</v>
@@ -933,7 +933,7 @@
         <v>David Guetta, TeddySwims, Tones And I - Gone Gone Gone (Unplugged) [Visualizer]</v>
       </c>
       <c r="B15" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=eWglDE7O5r8</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G15" t="str">
         <v>3:33</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
@@ -553,7 +553,7 @@
         <v>Jessie Ware - I Could Get Used To This (Live on The Graham Norton Show)</v>
       </c>
       <c r="B5" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=kGeamxRf8Gw</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G5" t="str">
         <v>3:50</v>
@@ -819,7 +819,7 @@
         <v>Zara Larsson - Lush Life (Official UGC Compilation Video)</v>
       </c>
       <c r="B12" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=FgAyfRnbbRs</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G12" t="str">
         <v>3:22</v>
@@ -857,7 +857,7 @@
         <v>Only The Poets - Monumental</v>
       </c>
       <c r="B13" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=nwXiAjjl6NE</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G13" t="str">
         <v>2:48</v>
@@ -1959,7 +1959,7 @@
         <v>We Three - Drunk Driving (Official Music Video)</v>
       </c>
       <c r="B42" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C42" t="str">
         <v>https://www.youtube.com/watch?v=BTqRGxSX6AQ</v>
@@ -1971,7 +1971,7 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G42" t="str">
         <v>4:27</v>
@@ -2377,7 +2377,7 @@
         <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
       </c>
       <c r="B53" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C53" t="str">
         <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
@@ -2389,7 +2389,7 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G53" t="str">
         <v>3:46</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
@@ -781,7 +781,7 @@
         <v>Paris Paloma - Good Girl [Official Music Video]</v>
       </c>
       <c r="B11" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=qhO6VMC-nx0</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G11" t="str">
         <v>4:47</v>
@@ -2339,7 +2339,7 @@
         <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
       </c>
       <c r="B52" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C52" t="str">
         <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
@@ -2351,7 +2351,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G52" t="str">
         <v>2:56</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
@@ -2301,7 +2301,7 @@
         <v>Holly Humberstone - To Love Somebody (Official Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C51" t="str">
         <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
@@ -2313,7 +2313,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G51" t="str">
         <v>3:59</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
@@ -743,7 +743,7 @@
         <v>The Kiffness &amp; Matisyahu - ONE DAY (ft. Andel and Nalyn) [OFFICIAL VIDEO]</v>
       </c>
       <c r="B10" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=buS21tVq5r0</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G10" t="str">
         <v>3:07</v>
@@ -3023,7 +3023,7 @@
         <v>DEF LEPPARD - Rejoice (Official Lyric Video)</v>
       </c>
       <c r="B70" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C70" t="str">
         <v>https://www.youtube.com/watch?v=zy2TLLeNgp0</v>
@@ -3035,7 +3035,7 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G70" t="str">
         <v>4:21</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
@@ -705,7 +705,7 @@
         <v>The Cure - Boys Don't Cry (86 Mix) (Official Lyric Video)</v>
       </c>
       <c r="B9" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=isNztTjXQsQ</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G9" t="str">
         <v>2:39</v>
@@ -1997,7 +1997,7 @@
         <v>Timebelle - Top of the World (Mood Video)</v>
       </c>
       <c r="B43" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C43" t="str">
         <v>https://www.youtube.com/watch?v=r9KyYK_E34s</v>
@@ -2009,7 +2009,7 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G43" t="str">
         <v>3:01</v>
@@ -3137,7 +3137,7 @@
         <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show]</v>
       </c>
       <c r="B73" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C73" t="str">
         <v>https://www.youtube.com/watch?v=dLzpNstMHZY</v>
@@ -3149,7 +3149,7 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G73" t="str">
         <v>3:10</v>
@@ -3175,7 +3175,7 @@
         <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel)</v>
       </c>
       <c r="B74" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C74" t="str">
         <v>https://www.youtube.com/watch?v=fo_j8Fqag8I</v>
@@ -3187,7 +3187,7 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G74" t="str">
         <v>3:21</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
@@ -629,7 +629,7 @@
         <v>Dean Lewis - I Am Getting Well (Lyric Video)</v>
       </c>
       <c r="B7" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=6ecgOSOMWzc</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G7" t="str">
         <v>2:44</v>
@@ -667,7 +667,7 @@
         <v>Take That - Take That and Party (Official HD Video)</v>
       </c>
       <c r="B8" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=DAerJcerikU</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G8" t="str">
         <v>2:57</v>
@@ -1883,7 +1883,7 @@
         <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video)</v>
       </c>
       <c r="B40" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=yUAvfo8fpuU</v>
@@ -1895,7 +1895,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G40" t="str">
         <v>3:50</v>
@@ -1921,7 +1921,7 @@
         <v>I Had To Explain "How Music Works" LIVE In Concert</v>
       </c>
       <c r="B41" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=KnsBdAM3HqY</v>
@@ -1933,7 +1933,7 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G41" t="str">
         <v>5:32</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
@@ -591,7 +591,7 @@
         <v>JOSEPH - Water in the Room (Official Music Video)</v>
       </c>
       <c r="B6" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=tNmT47k6MjM</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G6" t="str">
         <v>3:10</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music</v>
+        <v>Nothing But Thieves - Sorry (Official Audio)</v>
       </c>
       <c r="B2" t="str">
-        <v>1 day ago</v>
+        <v>1 hour ago</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=KdsHxyl4bE8</v>
+        <v>https://www.youtube.com/watch?v=D7QfVqo5YqY</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-02</v>
@@ -451,13 +451,13 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>1 day ago</v>
+        <v>1 hour ago</v>
       </c>
       <c r="G2" t="str">
-        <v>4:58</v>
+        <v>3:37</v>
       </c>
       <c r="H2" t="str">
-        <v>The Warning</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I2" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music - The Warning</v>
+        <v>Nothing But Thieves - Sorry (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield CA (2026)</v>
+        <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music</v>
       </c>
       <c r="B3" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=Mwkl_Cz_SG8</v>
+        <v>https://www.youtube.com/watch?v=KdsHxyl4bE8</v>
       </c>
       <c r="D3" t="str">
         <v>2026-02-02</v>
@@ -492,10 +492,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G3" t="str">
-        <v>5:08</v>
+        <v>4:58</v>
       </c>
       <c r="H3" t="str">
-        <v>The Offspring</v>
+        <v>The Warning</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield CA (2026) - The Offspring</v>
+        <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music - The Warning</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered)</v>
+        <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield CA (2026)</v>
       </c>
       <c r="B4" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=I7a-pDZFE7U</v>
+        <v>https://www.youtube.com/watch?v=Mwkl_Cz_SG8</v>
       </c>
       <c r="D4" t="str">
         <v>2026-02-02</v>
@@ -530,10 +530,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G4" t="str">
-        <v>4:38</v>
+        <v>5:08</v>
       </c>
       <c r="H4" t="str">
-        <v>Roxette</v>
+        <v>The Offspring</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered) - Roxette</v>
+        <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield CA (2026) - The Offspring</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Live on The Graham Norton Show)</v>
+        <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered)</v>
       </c>
       <c r="B5" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=kGeamxRf8Gw</v>
+        <v>https://www.youtube.com/watch?v=I7a-pDZFE7U</v>
       </c>
       <c r="D5" t="str">
         <v>2026-02-02</v>
@@ -568,10 +568,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G5" t="str">
-        <v>3:50</v>
+        <v>4:38</v>
       </c>
       <c r="H5" t="str">
-        <v>Jessie Ware</v>
+        <v>Roxette</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Live on The Graham Norton Show) - Jessie Ware</v>
+        <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered) - Roxette</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>JOSEPH - Water in the Room (Official Music Video)</v>
+        <v>Jessie Ware - I Could Get Used To This (Live on The Graham Norton Show)</v>
       </c>
       <c r="B6" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=tNmT47k6MjM</v>
+        <v>https://www.youtube.com/watch?v=kGeamxRf8Gw</v>
       </c>
       <c r="D6" t="str">
         <v>2026-02-02</v>
@@ -603,13 +603,13 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G6" t="str">
-        <v>3:10</v>
+        <v>3:50</v>
       </c>
       <c r="H6" t="str">
-        <v>Joseph</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>JOSEPH - Water in the Room (Official Music Video) - Joseph</v>
+        <v>Jessie Ware - I Could Get Used To This (Live on The Graham Norton Show) - Jessie Ware</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Dean Lewis - I Am Getting Well (Lyric Video)</v>
+        <v>JOSEPH - Water in the Room (Official Music Video)</v>
       </c>
       <c r="B7" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=6ecgOSOMWzc</v>
+        <v>https://www.youtube.com/watch?v=tNmT47k6MjM</v>
       </c>
       <c r="D7" t="str">
         <v>2026-02-02</v>
@@ -644,10 +644,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G7" t="str">
-        <v>2:44</v>
+        <v>3:10</v>
       </c>
       <c r="H7" t="str">
-        <v>Dean Lewis</v>
+        <v>Joseph</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Dean Lewis - I Am Getting Well (Lyric Video) - Dean Lewis</v>
+        <v>JOSEPH - Water in the Room (Official Music Video) - Joseph</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Take That - Take That and Party (Official HD Video)</v>
+        <v>Dean Lewis - I Am Getting Well (Lyric Video)</v>
       </c>
       <c r="B8" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=DAerJcerikU</v>
+        <v>https://www.youtube.com/watch?v=6ecgOSOMWzc</v>
       </c>
       <c r="D8" t="str">
         <v>2026-02-02</v>
@@ -682,10 +682,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G8" t="str">
-        <v>2:57</v>
+        <v>2:44</v>
       </c>
       <c r="H8" t="str">
-        <v>Take That</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Take That - Take That and Party (Official HD Video) - Take That</v>
+        <v>Dean Lewis - I Am Getting Well (Lyric Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>The Cure - Boys Don't Cry (86 Mix) (Official Lyric Video)</v>
+        <v>Take That - Take That and Party (Official HD Video)</v>
       </c>
       <c r="B9" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=isNztTjXQsQ</v>
+        <v>https://www.youtube.com/watch?v=DAerJcerikU</v>
       </c>
       <c r="D9" t="str">
         <v>2026-02-02</v>
@@ -720,10 +720,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G9" t="str">
-        <v>2:39</v>
+        <v>2:57</v>
       </c>
       <c r="H9" t="str">
-        <v>The Cure</v>
+        <v>Take That</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>The Cure - Boys Don't Cry (86 Mix) (Official Lyric Video) - The Cure</v>
+        <v>Take That - Take That and Party (Official HD Video) - Take That</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>The Kiffness &amp; Matisyahu - ONE DAY (ft. Andel and Nalyn) [OFFICIAL VIDEO]</v>
+        <v>The Cure - Boys Don't Cry (86 Mix) (Official Lyric Video)</v>
       </c>
       <c r="B10" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=buS21tVq5r0</v>
+        <v>https://www.youtube.com/watch?v=isNztTjXQsQ</v>
       </c>
       <c r="D10" t="str">
         <v>2026-02-02</v>
@@ -758,10 +758,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G10" t="str">
-        <v>3:07</v>
+        <v>2:39</v>
       </c>
       <c r="H10" t="str">
-        <v>The Kiffness and Matisyahu</v>
+        <v>The Cure</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>The Kiffness &amp; Matisyahu - ONE DAY (ft. Andel and Nalyn) [OFFICIAL VIDEO] - The Kiffness and Matisyahu</v>
+        <v>The Cure - Boys Don't Cry (86 Mix) (Official Lyric Video) - The Cure</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Paris Paloma - Good Girl [Official Music Video]</v>
+        <v>The Kiffness &amp; Matisyahu - ONE DAY (ft. Andel and Nalyn) [OFFICIAL VIDEO]</v>
       </c>
       <c r="B11" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=qhO6VMC-nx0</v>
+        <v>https://www.youtube.com/watch?v=buS21tVq5r0</v>
       </c>
       <c r="D11" t="str">
         <v>2026-02-02</v>
@@ -796,10 +796,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G11" t="str">
-        <v>4:47</v>
+        <v>3:07</v>
       </c>
       <c r="H11" t="str">
-        <v>Paris Paloma</v>
+        <v>The Kiffness and Matisyahu</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Paris Paloma - Good Girl [Official Music Video] - Paris Paloma</v>
+        <v>The Kiffness &amp; Matisyahu - ONE DAY (ft. Andel and Nalyn) [OFFICIAL VIDEO] - The Kiffness and Matisyahu</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Zara Larsson - Lush Life (Official UGC Compilation Video)</v>
+        <v>Paris Paloma - Good Girl [Official Music Video]</v>
       </c>
       <c r="B12" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=FgAyfRnbbRs</v>
+        <v>https://www.youtube.com/watch?v=qhO6VMC-nx0</v>
       </c>
       <c r="D12" t="str">
         <v>2026-02-02</v>
@@ -834,10 +834,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G12" t="str">
-        <v>3:22</v>
+        <v>4:47</v>
       </c>
       <c r="H12" t="str">
-        <v>Zara Larsson</v>
+        <v>Paris Paloma</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Zara Larsson - Lush Life (Official UGC Compilation Video) - Zara Larsson</v>
+        <v>Paris Paloma - Good Girl [Official Music Video] - Paris Paloma</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Only The Poets - Monumental</v>
+        <v>Zara Larsson - Lush Life (Official UGC Compilation Video)</v>
       </c>
       <c r="B13" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=nwXiAjjl6NE</v>
+        <v>https://www.youtube.com/watch?v=FgAyfRnbbRs</v>
       </c>
       <c r="D13" t="str">
         <v>2026-02-02</v>
@@ -872,10 +872,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G13" t="str">
-        <v>2:48</v>
+        <v>3:22</v>
       </c>
       <c r="H13" t="str">
-        <v>only the poets</v>
+        <v>Zara Larsson</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Only The Poets - Monumental - only the poets</v>
+        <v>Zara Larsson - Lush Life (Official UGC Compilation Video) - Zara Larsson</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Katelyn Tarver - So Am I (Official Music Video)</v>
+        <v>Only The Poets - Monumental</v>
       </c>
       <c r="B14" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=MjUiVPzMQHw</v>
+        <v>https://www.youtube.com/watch?v=nwXiAjjl6NE</v>
       </c>
       <c r="D14" t="str">
         <v>2026-02-02</v>
@@ -910,10 +910,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G14" t="str">
-        <v>2:52</v>
+        <v>2:48</v>
       </c>
       <c r="H14" t="str">
-        <v>Katelyn Tarver</v>
+        <v>only the poets</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Katelyn Tarver - So Am I (Official Music Video) - Katelyn Tarver</v>
+        <v>Only The Poets - Monumental - only the poets</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>David Guetta, TeddySwims, Tones And I - Gone Gone Gone (Unplugged) [Visualizer]</v>
+        <v>Katelyn Tarver - So Am I (Official Music Video)</v>
       </c>
       <c r="B15" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=eWglDE7O5r8</v>
+        <v>https://www.youtube.com/watch?v=MjUiVPzMQHw</v>
       </c>
       <c r="D15" t="str">
         <v>2026-02-02</v>
@@ -948,10 +948,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G15" t="str">
-        <v>3:33</v>
+        <v>2:52</v>
       </c>
       <c r="H15" t="str">
-        <v>David Guetta</v>
+        <v>Katelyn Tarver</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>David Guetta, TeddySwims, Tones And I - Gone Gone Gone (Unplugged) [Visualizer] - David Guetta</v>
+        <v>Katelyn Tarver - So Am I (Official Music Video) - Katelyn Tarver</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>SANTOS BRAVOS “KAWASAKI” Performance Video</v>
+        <v>David Guetta, TeddySwims, Tones And I - Gone Gone Gone (Unplugged) [Visualizer]</v>
       </c>
       <c r="B16" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=Cmy8CsYIUL0</v>
+        <v>https://www.youtube.com/watch?v=eWglDE7O5r8</v>
       </c>
       <c r="D16" t="str">
         <v>2026-02-02</v>
@@ -986,10 +986,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G16" t="str">
-        <v>2:41</v>
+        <v>3:33</v>
       </c>
       <c r="H16" t="str">
-        <v>HYBE LABELS and SANTOS BRAVOS</v>
+        <v>David Guetta</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>SANTOS BRAVOS “KAWASAKI” Performance Video - HYBE LABELS and SANTOS BRAVOS</v>
+        <v>David Guetta, TeddySwims, Tones And I - Gone Gone Gone (Unplugged) [Visualizer] - David Guetta</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Ella Langley - Dandelion (Official Visualizer)</v>
+        <v>SANTOS BRAVOS “KAWASAKI” Performance Video</v>
       </c>
       <c r="B17" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=sf6eRmInk1s</v>
+        <v>https://www.youtube.com/watch?v=Cmy8CsYIUL0</v>
       </c>
       <c r="D17" t="str">
         <v>2026-02-02</v>
@@ -1024,10 +1024,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>4:01</v>
+        <v>2:41</v>
       </c>
       <c r="H17" t="str">
-        <v>Ella Langley</v>
+        <v>HYBE LABELS and SANTOS BRAVOS</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Ella Langley - Dandelion (Official Visualizer) - Ella Langley</v>
+        <v>SANTOS BRAVOS “KAWASAKI” Performance Video - HYBE LABELS and SANTOS BRAVOS</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Dogpark - Dandelion (Official Music Video)</v>
+        <v>Ella Langley - Dandelion (Official Visualizer)</v>
       </c>
       <c r="B18" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=fv9prIYHHzk</v>
+        <v>https://www.youtube.com/watch?v=sf6eRmInk1s</v>
       </c>
       <c r="D18" t="str">
         <v>2026-02-02</v>
@@ -1062,10 +1062,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>3:16</v>
+        <v>4:01</v>
       </c>
       <c r="H18" t="str">
-        <v>Dogpark</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Dogpark - Dandelion (Official Music Video) - Dogpark</v>
+        <v>Ella Langley - Dandelion (Official Visualizer) - Ella Langley</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Lauren Spencer Smith - Natural Disaster (Visualizer)</v>
+        <v>Dogpark - Dandelion (Official Music Video)</v>
       </c>
       <c r="B19" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=T9YvLA2cdZs</v>
+        <v>https://www.youtube.com/watch?v=fv9prIYHHzk</v>
       </c>
       <c r="D19" t="str">
         <v>2026-02-02</v>
@@ -1100,10 +1100,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>3:03</v>
+        <v>3:16</v>
       </c>
       <c r="H19" t="str">
-        <v>Lauren Spencer Smith</v>
+        <v>Dogpark</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Lauren Spencer Smith - Natural Disaster (Visualizer) - Lauren Spencer Smith</v>
+        <v>Dogpark - Dandelion (Official Music Video) - Dogpark</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>ERNEST - Lorelei (Official Music Video)</v>
+        <v>Lauren Spencer Smith - Natural Disaster (Visualizer)</v>
       </c>
       <c r="B20" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=dPWc_6IdDJk</v>
+        <v>https://www.youtube.com/watch?v=T9YvLA2cdZs</v>
       </c>
       <c r="D20" t="str">
         <v>2026-02-02</v>
@@ -1138,10 +1138,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>2:41</v>
+        <v>3:03</v>
       </c>
       <c r="H20" t="str">
-        <v>ERNEST</v>
+        <v>Lauren Spencer Smith</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>ERNEST - Lorelei (Official Music Video) - ERNEST</v>
+        <v>Lauren Spencer Smith - Natural Disaster (Visualizer) - Lauren Spencer Smith</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Labrinth - I Keep My Promises (Official Audio)</v>
+        <v>ERNEST - Lorelei (Official Music Video)</v>
       </c>
       <c r="B21" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=CV5rR9JZK-0</v>
+        <v>https://www.youtube.com/watch?v=dPWc_6IdDJk</v>
       </c>
       <c r="D21" t="str">
         <v>2026-02-02</v>
@@ -1176,10 +1176,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>3:05</v>
+        <v>2:41</v>
       </c>
       <c r="H21" t="str">
-        <v>Labrinth</v>
+        <v>ERNEST</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Labrinth - I Keep My Promises (Official Audio) - Labrinth</v>
+        <v>ERNEST - Lorelei (Official Music Video) - ERNEST</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Grace VanderWaal - Prettier (Official Lyric Video)</v>
+        <v>Labrinth - I Keep My Promises (Official Audio)</v>
       </c>
       <c r="B22" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=9HwTj3NZ16E</v>
+        <v>https://www.youtube.com/watch?v=CV5rR9JZK-0</v>
       </c>
       <c r="D22" t="str">
         <v>2026-02-02</v>
@@ -1214,10 +1214,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>2:46</v>
+        <v>3:05</v>
       </c>
       <c r="H22" t="str">
-        <v>Grace VanderWaal</v>
+        <v>Labrinth</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Grace VanderWaal - Prettier (Official Lyric Video) - Grace VanderWaal</v>
+        <v>Labrinth - I Keep My Promises (Official Audio) - Labrinth</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>VOILÀ - Frozen Lake (Official Lyric Video)</v>
+        <v>Grace VanderWaal - Prettier (Official Lyric Video)</v>
       </c>
       <c r="B23" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=Lmus-UbL1H0</v>
+        <v>https://www.youtube.com/watch?v=9HwTj3NZ16E</v>
       </c>
       <c r="D23" t="str">
         <v>2026-02-02</v>
@@ -1252,10 +1252,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>3:32</v>
+        <v>2:46</v>
       </c>
       <c r="H23" t="str">
-        <v>VOILÀ</v>
+        <v>Grace VanderWaal</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>VOILÀ - Frozen Lake (Official Lyric Video) - VOILÀ</v>
+        <v>Grace VanderWaal - Prettier (Official Lyric Video) - Grace VanderWaal</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Cannons - Starlight (Official Video)</v>
+        <v>VOILÀ - Frozen Lake (Official Lyric Video)</v>
       </c>
       <c r="B24" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=bu6WSMDDPGY</v>
+        <v>https://www.youtube.com/watch?v=Lmus-UbL1H0</v>
       </c>
       <c r="D24" t="str">
         <v>2026-02-02</v>
@@ -1290,10 +1290,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>3:42</v>
+        <v>3:32</v>
       </c>
       <c r="H24" t="str">
-        <v>Cannons</v>
+        <v>VOILÀ</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Cannons - Starlight (Official Video) - Cannons</v>
+        <v>VOILÀ - Frozen Lake (Official Lyric Video) - VOILÀ</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Kylie Morgan - Like My Own (Official Video)</v>
+        <v>Cannons - Starlight (Official Video)</v>
       </c>
       <c r="B25" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=zcYeoGBglC0</v>
+        <v>https://www.youtube.com/watch?v=bu6WSMDDPGY</v>
       </c>
       <c r="D25" t="str">
         <v>2026-02-02</v>
@@ -1328,10 +1328,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>2:38</v>
+        <v>3:42</v>
       </c>
       <c r="H25" t="str">
-        <v>Kylie Morgan</v>
+        <v>Cannons</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Kylie Morgan - Like My Own (Official Video) - Kylie Morgan</v>
+        <v>Cannons - Starlight (Official Video) - Cannons</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Lizzy McAlpine - House of the Rising Sun (Audio)</v>
+        <v>Kylie Morgan - Like My Own (Official Video)</v>
       </c>
       <c r="B26" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=3igYRj82EiU</v>
+        <v>https://www.youtube.com/watch?v=zcYeoGBglC0</v>
       </c>
       <c r="D26" t="str">
         <v>2026-02-02</v>
@@ -1366,10 +1366,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>3:10</v>
+        <v>2:38</v>
       </c>
       <c r="H26" t="str">
-        <v>Lizzy McAlpine</v>
+        <v>Kylie Morgan</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Lizzy McAlpine - House of the Rising Sun (Audio) - Lizzy McAlpine</v>
+        <v>Kylie Morgan - Like My Own (Official Video) - Kylie Morgan</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Willie Nelson - Heart Of America (From The Gray House Original Soundtrack)</v>
+        <v>Lizzy McAlpine - House of the Rising Sun (Audio)</v>
       </c>
       <c r="B27" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=0bhcO4Yphuo</v>
+        <v>https://www.youtube.com/watch?v=3igYRj82EiU</v>
       </c>
       <c r="D27" t="str">
         <v>2026-02-02</v>
@@ -1404,10 +1404,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>3:57</v>
+        <v>3:10</v>
       </c>
       <c r="H27" t="str">
-        <v>Willie Nelson</v>
+        <v>Lizzy McAlpine</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Willie Nelson - Heart Of America (From The Gray House Original Soundtrack) - Willie Nelson</v>
+        <v>Lizzy McAlpine - House of the Rising Sun (Audio) - Lizzy McAlpine</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Jeremy Camp - No Survivors (Live) ft. Skillet</v>
+        <v>Willie Nelson - Heart Of America (From The Gray House Original Soundtrack)</v>
       </c>
       <c r="B28" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=Jjz1wFe5dMo</v>
+        <v>https://www.youtube.com/watch?v=0bhcO4Yphuo</v>
       </c>
       <c r="D28" t="str">
         <v>2026-02-02</v>
@@ -1442,10 +1442,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>2:19</v>
+        <v>3:57</v>
       </c>
       <c r="H28" t="str">
-        <v>JeremyCampMusic</v>
+        <v>Willie Nelson</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Jeremy Camp - No Survivors (Live) ft. Skillet - JeremyCampMusic</v>
+        <v>Willie Nelson - Heart Of America (From The Gray House Original Soundtrack) - Willie Nelson</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>India Martinez, Coro ArteSí de Olvidados - Niño Sin Miedo</v>
+        <v>Jeremy Camp - No Survivors (Live) ft. Skillet</v>
       </c>
       <c r="B29" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=Vug_FPbXe9E</v>
+        <v>https://www.youtube.com/watch?v=Jjz1wFe5dMo</v>
       </c>
       <c r="D29" t="str">
         <v>2026-02-02</v>
@@ -1480,10 +1480,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>4:04</v>
+        <v>2:19</v>
       </c>
       <c r="H29" t="str">
-        <v>India Martínez</v>
+        <v>JeremyCampMusic</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>India Martinez, Coro ArteSí de Olvidados - Niño Sin Miedo - India Martínez</v>
+        <v>Jeremy Camp - No Survivors (Live) ft. Skillet - JeremyCampMusic</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Chelsea Cutler - BAD (Official Lyric Video)</v>
+        <v>India Martinez, Coro ArteSí de Olvidados - Niño Sin Miedo</v>
       </c>
       <c r="B30" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=ZIW2vA3Zs1U</v>
+        <v>https://www.youtube.com/watch?v=Vug_FPbXe9E</v>
       </c>
       <c r="D30" t="str">
         <v>2026-02-02</v>
@@ -1518,10 +1518,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>2:16</v>
+        <v>4:04</v>
       </c>
       <c r="H30" t="str">
-        <v>Chelsea Cutler</v>
+        <v>India Martínez</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Chelsea Cutler - BAD (Official Lyric Video) - Chelsea Cutler</v>
+        <v>India Martinez, Coro ArteSí de Olvidados - Niño Sin Miedo - India Martínez</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>TINI - FUTTTURA LIVE - el cielo + fresa</v>
+        <v>Chelsea Cutler - BAD (Official Lyric Video)</v>
       </c>
       <c r="B31" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=q_rrgJZAdNg</v>
+        <v>https://www.youtube.com/watch?v=ZIW2vA3Zs1U</v>
       </c>
       <c r="D31" t="str">
         <v>2026-02-02</v>
@@ -1556,10 +1556,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>5:58</v>
+        <v>2:16</v>
       </c>
       <c r="H31" t="str">
-        <v>TINI</v>
+        <v>Chelsea Cutler</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>TINI - FUTTTURA LIVE - el cielo + fresa - TINI</v>
+        <v>Chelsea Cutler - BAD (Official Lyric Video) - Chelsea Cutler</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Charley - Serial Idealist (Official Video)</v>
+        <v>TINI - FUTTTURA LIVE - el cielo + fresa</v>
       </c>
       <c r="B32" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=uVIuKbPJz0U</v>
+        <v>https://www.youtube.com/watch?v=q_rrgJZAdNg</v>
       </c>
       <c r="D32" t="str">
         <v>2026-02-02</v>
@@ -1594,10 +1594,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>3:26</v>
+        <v>5:58</v>
       </c>
       <c r="H32" t="str">
-        <v>Charley</v>
+        <v>TINI</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Charley - Serial Idealist (Official Video) - Charley</v>
+        <v>TINI - FUTTTURA LIVE - el cielo + fresa - TINI</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Demi Lovato - Ghost (Live)</v>
+        <v>Charley - Serial Idealist (Official Video)</v>
       </c>
       <c r="B33" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=E-ECwdRndVA</v>
+        <v>https://www.youtube.com/watch?v=uVIuKbPJz0U</v>
       </c>
       <c r="D33" t="str">
         <v>2026-02-02</v>
@@ -1632,10 +1632,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>4:05</v>
+        <v>3:26</v>
       </c>
       <c r="H33" t="str">
-        <v>Demi Lovato</v>
+        <v>Charley</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Demi Lovato - Ghost (Live) - Demi Lovato</v>
+        <v>Charley - Serial Idealist (Official Video) - Charley</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Teddy Swims - Need You More (Live - Green Room Sessions)</v>
+        <v>Demi Lovato - Ghost (Live)</v>
       </c>
       <c r="B34" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=1ugf5aaY4pY</v>
+        <v>https://www.youtube.com/watch?v=E-ECwdRndVA</v>
       </c>
       <c r="D34" t="str">
         <v>2026-02-02</v>
@@ -1670,10 +1670,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>3:16</v>
+        <v>4:05</v>
       </c>
       <c r="H34" t="str">
-        <v>Teddy Swims</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Teddy Swims - Need You More (Live - Green Room Sessions) - Teddy Swims</v>
+        <v>Demi Lovato - Ghost (Live) - Demi Lovato</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Beck - Love (Audio)</v>
+        <v>Teddy Swims - Need You More (Live - Green Room Sessions)</v>
       </c>
       <c r="B35" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=ByABj3Xof1I</v>
+        <v>https://www.youtube.com/watch?v=1ugf5aaY4pY</v>
       </c>
       <c r="D35" t="str">
         <v>2026-02-02</v>
@@ -1708,10 +1708,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>3:14</v>
+        <v>3:16</v>
       </c>
       <c r="H35" t="str">
-        <v>Beck</v>
+        <v>Teddy Swims</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Beck - Love (Audio) - Beck</v>
+        <v>Teddy Swims - Need You More (Live - Green Room Sessions) - Teddy Swims</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>The Offspring - Looking Out For #1 | Live in Spokane WA (2026)</v>
+        <v>Beck - Love (Audio)</v>
       </c>
       <c r="B36" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=2HSbo51EFNg</v>
+        <v>https://www.youtube.com/watch?v=ByABj3Xof1I</v>
       </c>
       <c r="D36" t="str">
         <v>2026-02-02</v>
@@ -1746,10 +1746,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>2:57</v>
+        <v>3:14</v>
       </c>
       <c r="H36" t="str">
-        <v>The Offspring</v>
+        <v>Beck</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>The Offspring - Looking Out For #1 | Live in Spokane WA (2026) - The Offspring</v>
+        <v>Beck - Love (Audio) - Beck</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show</v>
+        <v>The Offspring - Looking Out For #1 | Live in Spokane WA (2026)</v>
       </c>
       <c r="B37" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=ylifHFJWJ_c</v>
+        <v>https://www.youtube.com/watch?v=2HSbo51EFNg</v>
       </c>
       <c r="D37" t="str">
         <v>2026-02-02</v>
@@ -1784,10 +1784,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>4:10</v>
+        <v>2:57</v>
       </c>
       <c r="H37" t="str">
-        <v>Sophie Ellis-Bextor</v>
+        <v>The Offspring</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show - Sophie Ellis-Bextor</v>
+        <v>The Offspring - Looking Out For #1 | Live in Spokane WA (2026) - The Offspring</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Jason Derulo - Sexy For Me [Official Music Video]</v>
+        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show</v>
       </c>
       <c r="B38" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=9ST-eBNL0NU</v>
+        <v>https://www.youtube.com/watch?v=ylifHFJWJ_c</v>
       </c>
       <c r="D38" t="str">
         <v>2026-02-02</v>
@@ -1822,10 +1822,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>2:10</v>
+        <v>4:10</v>
       </c>
       <c r="H38" t="str">
-        <v>Jason Derulo</v>
+        <v>Sophie Ellis-Bextor</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Jason Derulo - Sexy For Me [Official Music Video] - Jason Derulo</v>
+        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show - Sophie Ellis-Bextor</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Lights - COME GET YOUR GIRL</v>
+        <v>Jason Derulo - Sexy For Me [Official Music Video]</v>
       </c>
       <c r="B39" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=EhzX2y5MpSM</v>
+        <v>https://www.youtube.com/watch?v=9ST-eBNL0NU</v>
       </c>
       <c r="D39" t="str">
         <v>2026-02-02</v>
@@ -1857,13 +1857,13 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>3:52</v>
+        <v>2:10</v>
       </c>
       <c r="H39" t="str">
-        <v>lights</v>
+        <v>Jason Derulo</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Lights - COME GET YOUR GIRL - lights</v>
+        <v>Jason Derulo - Sexy For Me [Official Music Video] - Jason Derulo</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video)</v>
+        <v>Lights - COME GET YOUR GIRL</v>
       </c>
       <c r="B40" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=yUAvfo8fpuU</v>
+        <v>https://www.youtube.com/watch?v=EhzX2y5MpSM</v>
       </c>
       <c r="D40" t="str">
         <v>2026-02-02</v>
@@ -1898,10 +1898,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>3:50</v>
+        <v>3:52</v>
       </c>
       <c r="H40" t="str">
-        <v>Telenova</v>
+        <v>lights</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video) - Telenova</v>
+        <v>Lights - COME GET YOUR GIRL - lights</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>I Had To Explain "How Music Works" LIVE In Concert</v>
+        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video)</v>
       </c>
       <c r="B41" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=KnsBdAM3HqY</v>
+        <v>https://www.youtube.com/watch?v=yUAvfo8fpuU</v>
       </c>
       <c r="D41" t="str">
         <v>2026-02-02</v>
@@ -1936,10 +1936,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>5:32</v>
+        <v>3:50</v>
       </c>
       <c r="H41" t="str">
-        <v>Marcin</v>
+        <v>Telenova</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>I Had To Explain "How Music Works" LIVE In Concert - Marcin</v>
+        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video) - Telenova</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>We Three - Drunk Driving (Official Music Video)</v>
+        <v>I Had To Explain "How Music Works" LIVE In Concert</v>
       </c>
       <c r="B42" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=BTqRGxSX6AQ</v>
+        <v>https://www.youtube.com/watch?v=KnsBdAM3HqY</v>
       </c>
       <c r="D42" t="str">
         <v>2026-02-02</v>
@@ -1974,10 +1974,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>4:27</v>
+        <v>5:32</v>
       </c>
       <c r="H42" t="str">
-        <v>We Three</v>
+        <v>Marcin</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>We Three - Drunk Driving (Official Music Video) - We Three</v>
+        <v>I Had To Explain "How Music Works" LIVE In Concert - Marcin</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Timebelle - Top of the World (Mood Video)</v>
+        <v>We Three - Drunk Driving (Official Music Video)</v>
       </c>
       <c r="B43" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=r9KyYK_E34s</v>
+        <v>https://www.youtube.com/watch?v=BTqRGxSX6AQ</v>
       </c>
       <c r="D43" t="str">
         <v>2026-02-02</v>
@@ -2009,13 +2009,13 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>3:01</v>
+        <v>4:27</v>
       </c>
       <c r="H43" t="str">
-        <v>Timebelle Official</v>
+        <v>We Three</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Timebelle - Top of the World (Mood Video) - Timebelle Official</v>
+        <v>We Three - Drunk Driving (Official Music Video) - We Three</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop)</v>
+        <v>Timebelle - Top of the World (Mood Video)</v>
       </c>
       <c r="B44" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=57a_OheOlDw</v>
+        <v>https://www.youtube.com/watch?v=r9KyYK_E34s</v>
       </c>
       <c r="D44" t="str">
         <v>2026-02-02</v>
@@ -2050,10 +2050,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>3:20</v>
+        <v>3:01</v>
       </c>
       <c r="H44" t="str">
-        <v>David Guetta and Tones And I</v>
+        <v>Timebelle Official</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop) - David Guetta and Tones And I</v>
+        <v>Timebelle - Top of the World (Mood Video) - Timebelle Official</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Clinton Kane - this is my last love song to you (Official Lyric Video)</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop)</v>
       </c>
       <c r="B45" t="str">
-        <v>9 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=-5Aa8NTiRqE</v>
+        <v>https://www.youtube.com/watch?v=57a_OheOlDw</v>
       </c>
       <c r="D45" t="str">
         <v>2026-02-02</v>
@@ -2085,13 +2085,13 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>9 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>3:34</v>
+        <v>3:20</v>
       </c>
       <c r="H45" t="str">
-        <v>Clinton Kane</v>
+        <v>David Guetta and Tones And I</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Clinton Kane - this is my last love song to you (Official Lyric Video) - Clinton Kane</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop) - David Guetta and Tones And I</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>SIENNA SPIRO - Die On This Hill (Official Music Video)</v>
+        <v>Clinton Kane - this is my last love song to you (Official Lyric Video)</v>
       </c>
       <c r="B46" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=5RNy_1odv20</v>
+        <v>https://www.youtube.com/watch?v=-5Aa8NTiRqE</v>
       </c>
       <c r="D46" t="str">
         <v>2026-02-02</v>
@@ -2126,10 +2126,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>4:01</v>
+        <v>3:34</v>
       </c>
       <c r="H46" t="str">
-        <v>Lyrical Lemonade and SIENNA SPIRO</v>
+        <v>Clinton Kane</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>SIENNA SPIRO - Die On This Hill (Official Music Video) - Lyrical Lemonade and SIENNA SPIRO</v>
+        <v>Clinton Kane - this is my last love song to you (Official Lyric Video) - Clinton Kane</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Amazon Music presents: Sienna Spiro - You Stole The Show</v>
+        <v>SIENNA SPIRO - Die On This Hill (Official Music Video)</v>
       </c>
       <c r="B47" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=stYIRyCLN4Y</v>
+        <v>https://www.youtube.com/watch?v=5RNy_1odv20</v>
       </c>
       <c r="D47" t="str">
         <v>2026-02-02</v>
@@ -2164,10 +2164,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>3:24</v>
+        <v>4:01</v>
       </c>
       <c r="H47" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>Lyrical Lemonade and SIENNA SPIRO</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Amazon Music presents: Sienna Spiro - You Stole The Show - SIENNA SPIRO</v>
+        <v>SIENNA SPIRO - Die On This Hill (Official Music Video) - Lyrical Lemonade and SIENNA SPIRO</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Harry Styles - Aperture (Official Video)</v>
+        <v>Amazon Music presents: Sienna Spiro - You Stole The Show</v>
       </c>
       <c r="B48" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=7sxVHYZ_PnA</v>
+        <v>https://www.youtube.com/watch?v=stYIRyCLN4Y</v>
       </c>
       <c r="D48" t="str">
         <v>2026-02-02</v>
@@ -2202,10 +2202,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>5:52</v>
+        <v>3:24</v>
       </c>
       <c r="H48" t="str">
-        <v>Harry Styles</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Harry Styles - Aperture (Official Video) - Harry Styles</v>
+        <v>Amazon Music presents: Sienna Spiro - You Stole The Show - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Neal Francis - Back It Up (Live At The Salt Shed)</v>
+        <v>Harry Styles - Aperture (Official Video)</v>
       </c>
       <c r="B49" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=46iZEdsxjC0</v>
+        <v>https://www.youtube.com/watch?v=7sxVHYZ_PnA</v>
       </c>
       <c r="D49" t="str">
         <v>2026-02-02</v>
@@ -2240,10 +2240,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>5:01</v>
+        <v>5:52</v>
       </c>
       <c r="H49" t="str">
-        <v>Neal Francis</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Neal Francis - Back It Up (Live At The Salt Shed) - Neal Francis</v>
+        <v>Harry Styles - Aperture (Official Video) - Harry Styles</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
+        <v>Neal Francis - Back It Up (Live At The Salt Shed)</v>
       </c>
       <c r="B50" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=K2nG1Uukz7E</v>
+        <v>https://www.youtube.com/watch?v=46iZEdsxjC0</v>
       </c>
       <c r="D50" t="str">
         <v>2026-02-02</v>
@@ -2278,10 +2278,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>4:12</v>
+        <v>5:01</v>
       </c>
       <c r="H50" t="str">
-        <v>OfficiallyExtreme</v>
+        <v>Neal Francis</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
+        <v>Neal Francis - Back It Up (Live At The Salt Shed) - Neal Francis</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Holly Humberstone - To Love Somebody (Official Video)</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
       </c>
       <c r="B51" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
+        <v>https://www.youtube.com/watch?v=K2nG1Uukz7E</v>
       </c>
       <c r="D51" t="str">
         <v>2026-02-02</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>3:59</v>
+        <v>4:12</v>
       </c>
       <c r="H51" t="str">
-        <v>Holly Humberstone</v>
+        <v>OfficiallyExtreme</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Holly Humberstone - To Love Somebody (Official Video) - Holly Humberstone</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
+        <v>Holly Humberstone - To Love Somebody (Official Video)</v>
       </c>
       <c r="B52" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
+        <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
       </c>
       <c r="D52" t="str">
         <v>2026-02-02</v>
@@ -2354,10 +2354,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>2:56</v>
+        <v>3:59</v>
       </c>
       <c r="H52" t="str">
-        <v>Cliff Richard</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018) - Cliff Richard</v>
+        <v>Holly Humberstone - To Love Somebody (Official Video) - Holly Humberstone</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
+        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
       </c>
       <c r="B53" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
+        <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
       </c>
       <c r="D53" t="str">
         <v>2026-02-02</v>
@@ -2392,10 +2392,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>3:46</v>
+        <v>2:56</v>
       </c>
       <c r="H53" t="str">
-        <v>Jessie Ware</v>
+        <v>Cliff Richard</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Official Video) - Jessie Ware</v>
+        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018) - Cliff Richard</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Bella White - Dream Song (Official Audio)</v>
+        <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
       </c>
       <c r="B54" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
+        <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
       </c>
       <c r="D54" t="str">
         <v>2026-02-02</v>
@@ -2430,10 +2430,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G54" t="str">
-        <v>4:37</v>
+        <v>3:46</v>
       </c>
       <c r="H54" t="str">
-        <v>Bella White</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Bella White - Dream Song (Official Audio) - Bella White</v>
+        <v>Jessie Ware - I Could Get Used To This (Official Video) - Jessie Ware</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Ryan Wright - Film School Kids (Official Video)</v>
+        <v>Bella White - Dream Song (Official Audio)</v>
       </c>
       <c r="B55" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=pnAz9RwGSek</v>
+        <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
       </c>
       <c r="D55" t="str">
         <v>2026-02-02</v>
@@ -2468,10 +2468,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G55" t="str">
-        <v>4:06</v>
+        <v>4:37</v>
       </c>
       <c r="H55" t="str">
-        <v>Ryan Wright</v>
+        <v>Bella White</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Ryan Wright - Film School Kids (Official Video) - Ryan Wright</v>
+        <v>Bella White - Dream Song (Official Audio) - Bella White</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer)</v>
+        <v>Ryan Wright - Film School Kids (Official Video)</v>
       </c>
       <c r="B56" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=u7aPv2saz_I</v>
+        <v>https://www.youtube.com/watch?v=pnAz9RwGSek</v>
       </c>
       <c r="D56" t="str">
         <v>2026-02-02</v>
@@ -2506,10 +2506,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G56" t="str">
-        <v>3:54</v>
+        <v>4:06</v>
       </c>
       <c r="H56" t="str">
-        <v>Dove Cameron</v>
+        <v>Ryan Wright</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer) - Dove Cameron</v>
+        <v>Ryan Wright - Film School Kids (Official Video) - Ryan Wright</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video)</v>
+        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer)</v>
       </c>
       <c r="B57" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=WGb8KVdqs6k</v>
+        <v>https://www.youtube.com/watch?v=u7aPv2saz_I</v>
       </c>
       <c r="D57" t="str">
         <v>2026-02-02</v>
@@ -2544,10 +2544,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G57" t="str">
-        <v>4:10</v>
+        <v>3:54</v>
       </c>
       <c r="H57" t="str">
-        <v>Parker McCollum</v>
+        <v>Dove Cameron</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video) - Parker McCollum</v>
+        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer) - Dove Cameron</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video)</v>
+        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video)</v>
       </c>
       <c r="B58" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=X1ZeY4Y3l1M</v>
+        <v>https://www.youtube.com/watch?v=WGb8KVdqs6k</v>
       </c>
       <c r="D58" t="str">
         <v>2026-02-02</v>
@@ -2582,10 +2582,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G58" t="str">
-        <v>3:26</v>
+        <v>4:10</v>
       </c>
       <c r="H58" t="str">
-        <v>Matt Hansen</v>
+        <v>Parker McCollum</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video) - Matt Hansen</v>
+        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video) - Parker McCollum</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Louis Tomlinson - Imposter (Official Video)</v>
+        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video)</v>
       </c>
       <c r="B59" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=rzuD5szQhso</v>
+        <v>https://www.youtube.com/watch?v=X1ZeY4Y3l1M</v>
       </c>
       <c r="D59" t="str">
         <v>2026-02-02</v>
@@ -2617,13 +2617,13 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G59" t="str">
-        <v>2:56</v>
+        <v>3:26</v>
       </c>
       <c r="H59" t="str">
-        <v>Louis Tomlinson</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Louis Tomlinson - Imposter (Official Video) - Louis Tomlinson</v>
+        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video) - Matt Hansen</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Mitchell Tenpenny - You Phase (Official Music Video)</v>
+        <v>Louis Tomlinson - Imposter (Official Video)</v>
       </c>
       <c r="B60" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=UPuK6wV5Zco</v>
+        <v>https://www.youtube.com/watch?v=rzuD5szQhso</v>
       </c>
       <c r="D60" t="str">
         <v>2026-02-02</v>
@@ -2655,13 +2655,13 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G60" t="str">
         <v>2:56</v>
       </c>
       <c r="H60" t="str">
-        <v>Mitchell Tenpenny</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Mitchell Tenpenny - You Phase (Official Music Video) - Mitchell Tenpenny</v>
+        <v>Louis Tomlinson - Imposter (Official Video) - Louis Tomlinson</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Tauren Wells - Breathe On It (Official Lyric Video)</v>
+        <v>Mitchell Tenpenny - You Phase (Official Music Video)</v>
       </c>
       <c r="B61" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=9hW9sNMn2A0</v>
+        <v>https://www.youtube.com/watch?v=UPuK6wV5Zco</v>
       </c>
       <c r="D61" t="str">
         <v>2026-02-02</v>
@@ -2696,10 +2696,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G61" t="str">
-        <v>4:01</v>
+        <v>2:56</v>
       </c>
       <c r="H61" t="str">
-        <v>Tauren Wells</v>
+        <v>Mitchell Tenpenny</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Tauren Wells - Breathe On It (Official Lyric Video) - Tauren Wells</v>
+        <v>Mitchell Tenpenny - You Phase (Official Music Video) - Mitchell Tenpenny</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Maiah Manser - Feeling it All (Official Music Video)</v>
+        <v>Tauren Wells - Breathe On It (Official Lyric Video)</v>
       </c>
       <c r="B62" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=JMYvXleIwfU</v>
+        <v>https://www.youtube.com/watch?v=9hW9sNMn2A0</v>
       </c>
       <c r="D62" t="str">
         <v>2026-02-02</v>
@@ -2734,10 +2734,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G62" t="str">
-        <v>3:05</v>
+        <v>4:01</v>
       </c>
       <c r="H62" t="str">
-        <v>Maiah Manser</v>
+        <v>Tauren Wells</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Maiah Manser - Feeling it All (Official Music Video) - Maiah Manser</v>
+        <v>Tauren Wells - Breathe On It (Official Lyric Video) - Tauren Wells</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Taylor Austin Dye - Man For That (Official Music Video)</v>
+        <v>Maiah Manser - Feeling it All (Official Music Video)</v>
       </c>
       <c r="B63" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=vOzX-o11seI</v>
+        <v>https://www.youtube.com/watch?v=JMYvXleIwfU</v>
       </c>
       <c r="D63" t="str">
         <v>2026-02-02</v>
@@ -2772,10 +2772,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G63" t="str">
-        <v>2:27</v>
+        <v>3:05</v>
       </c>
       <c r="H63" t="str">
-        <v>Taylor Austin Dye</v>
+        <v>Maiah Manser</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Taylor Austin Dye - Man For That (Official Music Video) - Taylor Austin Dye</v>
+        <v>Maiah Manser - Feeling it All (Official Music Video) - Maiah Manser</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Chelsea Cutler - BAD (Official Video)</v>
+        <v>Taylor Austin Dye - Man For That (Official Music Video)</v>
       </c>
       <c r="B64" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=86k4E6ydHVU</v>
+        <v>https://www.youtube.com/watch?v=vOzX-o11seI</v>
       </c>
       <c r="D64" t="str">
         <v>2026-02-02</v>
@@ -2810,10 +2810,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G64" t="str">
-        <v>2:34</v>
+        <v>2:27</v>
       </c>
       <c r="H64" t="str">
-        <v>Chelsea Cutler</v>
+        <v>Taylor Austin Dye</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Chelsea Cutler - BAD (Official Video) - Chelsea Cutler</v>
+        <v>Taylor Austin Dye - Man For That (Official Music Video) - Taylor Austin Dye</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video)</v>
+        <v>Chelsea Cutler - BAD (Official Video)</v>
       </c>
       <c r="B65" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=-UWIFAiOOPE</v>
+        <v>https://www.youtube.com/watch?v=86k4E6ydHVU</v>
       </c>
       <c r="D65" t="str">
         <v>2026-02-02</v>
@@ -2848,10 +2848,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G65" t="str">
-        <v>3:13</v>
+        <v>2:34</v>
       </c>
       <c r="H65" t="str">
-        <v>Ashley Kutcher</v>
+        <v>Chelsea Cutler</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video) - Ashley Kutcher</v>
+        <v>Chelsea Cutler - BAD (Official Video) - Chelsea Cutler</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Louis Tomlinson - Dark To Light (Visualiser)</v>
+        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video)</v>
       </c>
       <c r="B66" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=02QyA29poAM</v>
+        <v>https://www.youtube.com/watch?v=-UWIFAiOOPE</v>
       </c>
       <c r="D66" t="str">
         <v>2026-02-02</v>
@@ -2889,7 +2889,7 @@
         <v>3:13</v>
       </c>
       <c r="H66" t="str">
-        <v>Louis Tomlinson</v>
+        <v>Ashley Kutcher</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Louis Tomlinson - Dark To Light (Visualiser) - Louis Tomlinson</v>
+        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video) - Ashley Kutcher</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>CAIN - So Long Sad Songs (Lyric Video)</v>
+        <v>Louis Tomlinson - Dark To Light (Visualiser)</v>
       </c>
       <c r="B67" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=feOv8nufa_I</v>
+        <v>https://www.youtube.com/watch?v=02QyA29poAM</v>
       </c>
       <c r="D67" t="str">
         <v>2026-02-02</v>
@@ -2924,10 +2924,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G67" t="str">
-        <v>3:08</v>
+        <v>3:13</v>
       </c>
       <c r="H67" t="str">
-        <v>CAIN</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>CAIN - So Long Sad Songs (Lyric Video) - CAIN</v>
+        <v>Louis Tomlinson - Dark To Light (Visualiser) - Louis Tomlinson</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Harry Styles - Aperture (Official Audio)</v>
+        <v>CAIN - So Long Sad Songs (Lyric Video)</v>
       </c>
       <c r="B68" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=rA_eCxPay7E</v>
+        <v>https://www.youtube.com/watch?v=feOv8nufa_I</v>
       </c>
       <c r="D68" t="str">
         <v>2026-02-02</v>
@@ -2962,10 +2962,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G68" t="str">
-        <v>5:14</v>
+        <v>3:08</v>
       </c>
       <c r="H68" t="str">
-        <v>Harry Styles</v>
+        <v>CAIN</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Harry Styles - Aperture (Official Audio) - Harry Styles</v>
+        <v>CAIN - So Long Sad Songs (Lyric Video) - CAIN</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Lana Lubany - BAD IDEA (Official Video)</v>
+        <v>Harry Styles - Aperture (Official Audio)</v>
       </c>
       <c r="B69" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
+        <v>https://www.youtube.com/watch?v=rA_eCxPay7E</v>
       </c>
       <c r="D69" t="str">
         <v>2026-02-02</v>
@@ -3000,10 +3000,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G69" t="str">
-        <v>2:59</v>
+        <v>5:14</v>
       </c>
       <c r="H69" t="str">
-        <v>Lana Lubany</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Lana Lubany - BAD IDEA (Official Video) - Lana Lubany</v>
+        <v>Harry Styles - Aperture (Official Audio) - Harry Styles</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>DEF LEPPARD - Rejoice (Official Lyric Video)</v>
+        <v>Lana Lubany - BAD IDEA (Official Video)</v>
       </c>
       <c r="B70" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=zy2TLLeNgp0</v>
+        <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
       </c>
       <c r="D70" t="str">
         <v>2026-02-02</v>
@@ -3035,13 +3035,13 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G70" t="str">
-        <v>4:21</v>
+        <v>2:59</v>
       </c>
       <c r="H70" t="str">
-        <v>DEF LEPPARD</v>
+        <v>Lana Lubany</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>DEF LEPPARD - Rejoice (Official Lyric Video) - DEF LEPPARD</v>
+        <v>Lana Lubany - BAD IDEA (Official Video) - Lana Lubany</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Dermot Kennedy - Funeral (Official Music Video)</v>
+        <v>DEF LEPPARD - Rejoice (Official Lyric Video)</v>
       </c>
       <c r="B71" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=JzOUJZPky6o</v>
+        <v>https://www.youtube.com/watch?v=zy2TLLeNgp0</v>
       </c>
       <c r="D71" t="str">
         <v>2026-02-02</v>
@@ -3076,10 +3076,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G71" t="str">
-        <v>4:09</v>
+        <v>4:21</v>
       </c>
       <c r="H71" t="str">
-        <v>Dermot Kennedy</v>
+        <v>DEF LEPPARD</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Dermot Kennedy - Funeral (Official Music Video) - Dermot Kennedy</v>
+        <v>DEF LEPPARD - Rejoice (Official Lyric Video) - DEF LEPPARD</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video)</v>
+        <v>Dermot Kennedy - Funeral (Official Music Video)</v>
       </c>
       <c r="B72" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=kfF0bVZMCw0</v>
+        <v>https://www.youtube.com/watch?v=JzOUJZPky6o</v>
       </c>
       <c r="D72" t="str">
         <v>2026-02-02</v>
@@ -3111,13 +3111,13 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G72" t="str">
-        <v>2:34</v>
+        <v>4:09</v>
       </c>
       <c r="H72" t="str">
-        <v>Lauren Sanderson</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video) - Lauren Sanderson</v>
+        <v>Dermot Kennedy - Funeral (Official Music Video) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show]</v>
+        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video)</v>
       </c>
       <c r="B73" t="str">
-        <v>13 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=dLzpNstMHZY</v>
+        <v>https://www.youtube.com/watch?v=kfF0bVZMCw0</v>
       </c>
       <c r="D73" t="str">
         <v>2026-02-02</v>
@@ -3149,13 +3149,13 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>13 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G73" t="str">
-        <v>3:10</v>
+        <v>2:34</v>
       </c>
       <c r="H73" t="str">
-        <v>Olivia Dean</v>
+        <v>Lauren Sanderson</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show] - Olivia Dean</v>
+        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video) - Lauren Sanderson</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel)</v>
+        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show]</v>
       </c>
       <c r="B74" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=fo_j8Fqag8I</v>
+        <v>https://www.youtube.com/watch?v=dLzpNstMHZY</v>
       </c>
       <c r="D74" t="str">
         <v>2026-02-02</v>
@@ -3190,10 +3190,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G74" t="str">
-        <v>3:21</v>
+        <v>3:10</v>
       </c>
       <c r="H74" t="str">
-        <v>David Guetta and Tones And I</v>
+        <v>Olivia Dean</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel) - David Guetta and Tones And I</v>
+        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show] - Olivia Dean</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>The Avett Brothers - Matrimony (Official Video)</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel)</v>
       </c>
       <c r="B75" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=7sD9-MtV9CY</v>
+        <v>https://www.youtube.com/watch?v=fo_j8Fqag8I</v>
       </c>
       <c r="D75" t="str">
         <v>2026-02-02</v>
@@ -3228,10 +3228,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G75" t="str">
-        <v>3:06</v>
+        <v>3:21</v>
       </c>
       <c r="H75" t="str">
-        <v>The Avett Brothers</v>
+        <v>David Guetta and Tones And I</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>The Avett Brothers - Matrimony (Official Video) - The Avett Brothers</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel) - David Guetta and Tones And I</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Jordana Bryant - Love Like That (Official Video)</v>
+        <v>The Avett Brothers - Matrimony (Official Video)</v>
       </c>
       <c r="B76" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=3ATlH-Rtzmk</v>
+        <v>https://www.youtube.com/watch?v=7sD9-MtV9CY</v>
       </c>
       <c r="D76" t="str">
         <v>2026-02-02</v>
@@ -3266,10 +3266,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G76" t="str">
-        <v>3:21</v>
+        <v>3:06</v>
       </c>
       <c r="H76" t="str">
-        <v>Jordana Bryant</v>
+        <v>The Avett Brothers</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Jordana Bryant - Love Like That (Official Video) - Jordana Bryant</v>
+        <v>The Avett Brothers - Matrimony (Official Video) - The Avett Brothers</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards</v>
+        <v>Jordana Bryant - Love Like That (Official Video)</v>
       </c>
       <c r="B77" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=kIRmKmEb2g0</v>
+        <v>https://www.youtube.com/watch?v=3ATlH-Rtzmk</v>
       </c>
       <c r="D77" t="str">
         <v>2026-02-02</v>
@@ -3304,10 +3304,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G77" t="str">
-        <v>7:21</v>
+        <v>3:21</v>
       </c>
       <c r="H77" t="str">
-        <v>Katy Perry</v>
+        <v>Jordana Bryant</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards - Katy Perry</v>
+        <v>Jordana Bryant - Love Like That (Official Video) - Jordana Bryant</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session)</v>
+        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards</v>
       </c>
       <c r="B78" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=oJ-l2ptQwbQ</v>
+        <v>https://www.youtube.com/watch?v=kIRmKmEb2g0</v>
       </c>
       <c r="D78" t="str">
         <v>2026-02-02</v>
@@ -3342,10 +3342,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G78" t="str">
-        <v>3:17</v>
+        <v>7:21</v>
       </c>
       <c r="H78" t="str">
-        <v>Lauren Watkins</v>
+        <v>Katy Perry</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session) - Lauren Watkins</v>
+        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards - Katy Perry</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Just A Mess (Live acoustic studio session)</v>
+        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session)</v>
       </c>
       <c r="B79" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=ShW-I63KD8w</v>
+        <v>https://www.youtube.com/watch?v=oJ-l2ptQwbQ</v>
       </c>
       <c r="D79" t="str">
         <v>2026-02-02</v>
@@ -3377,13 +3377,13 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G79" t="str">
-        <v>3:45</v>
+        <v>3:17</v>
       </c>
       <c r="H79" t="str">
-        <v>Tones And I</v>
+        <v>Lauren Watkins</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Just A Mess (Live acoustic studio session) - Tones And I</v>
+        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session) - Lauren Watkins</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Ashleigh Dallas - Sail Away (Official Audio)</v>
+        <v>Just A Mess (Live acoustic studio session)</v>
       </c>
       <c r="B80" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=66PDbaI-BVA</v>
+        <v>https://www.youtube.com/watch?v=ShW-I63KD8w</v>
       </c>
       <c r="D80" t="str">
         <v>2026-02-02</v>
@@ -3418,10 +3418,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G80" t="str">
-        <v>3:57</v>
+        <v>3:45</v>
       </c>
       <c r="H80" t="str">
-        <v>Ashleigh Dallas</v>
+        <v>Tones And I</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Ashleigh Dallas - Sail Away (Official Audio) - Ashleigh Dallas</v>
+        <v>Just A Mess (Live acoustic studio session) - Tones And I</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Performance Video)</v>
+        <v>Ashleigh Dallas - Sail Away (Official Audio)</v>
       </c>
       <c r="B81" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=4tmW_JSXHII</v>
+        <v>https://www.youtube.com/watch?v=66PDbaI-BVA</v>
       </c>
       <c r="D81" t="str">
         <v>2026-02-02</v>
@@ -3456,10 +3456,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G81" t="str">
-        <v>3:03</v>
+        <v>3:57</v>
       </c>
       <c r="H81" t="str">
-        <v>Charlie Puth</v>
+        <v>Ashleigh Dallas</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Performance Video) - Charlie Puth</v>
+        <v>Ashleigh Dallas - Sail Away (Official Audio) - Ashleigh Dallas</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Chappell Roan - The Subway (Live from Kansas City)</v>
+        <v>Charlie Puth - Beat Yourself Up (Performance Video)</v>
       </c>
       <c r="B82" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=6kZVtF8iaWw</v>
+        <v>https://www.youtube.com/watch?v=4tmW_JSXHII</v>
       </c>
       <c r="D82" t="str">
         <v>2026-02-02</v>
@@ -3494,10 +3494,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G82" t="str">
-        <v>4:27</v>
+        <v>3:03</v>
       </c>
       <c r="H82" t="str">
-        <v>Chappell Roan</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Chappell Roan - The Subway (Live from Kansas City) - Chappell Roan</v>
+        <v>Charlie Puth - Beat Yourself Up (Performance Video) - Charlie Puth</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar)</v>
+        <v>Chappell Roan - The Subway (Live from Kansas City)</v>
       </c>
       <c r="B83" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=guUvgEKkk1U</v>
+        <v>https://www.youtube.com/watch?v=6kZVtF8iaWw</v>
       </c>
       <c r="D83" t="str">
         <v>2026-02-02</v>
@@ -3532,10 +3532,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G83" t="str">
-        <v>4:34</v>
+        <v>4:27</v>
       </c>
       <c r="H83" t="str">
-        <v>Armik</v>
+        <v>Chappell Roan</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar) - Armik</v>
+        <v>Chappell Roan - The Subway (Live from Kansas City) - Chappell Roan</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>LØLØ - 007 (Official Music Video)</v>
+        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar)</v>
       </c>
       <c r="B84" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=4okJouEbZ_s</v>
+        <v>https://www.youtube.com/watch?v=guUvgEKkk1U</v>
       </c>
       <c r="D84" t="str">
         <v>2026-02-02</v>
@@ -3570,10 +3570,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G84" t="str">
-        <v>2:54</v>
+        <v>4:34</v>
       </c>
       <c r="H84" t="str">
-        <v>LØLØ</v>
+        <v>Armik</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>LØLØ - 007 (Official Music Video) - LØLØ</v>
+        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Tenille Townes - enabling (Official Visualizer)</v>
+        <v>LØLØ - 007 (Official Music Video)</v>
       </c>
       <c r="B85" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=yL_TxDF8WtI</v>
+        <v>https://www.youtube.com/watch?v=4okJouEbZ_s</v>
       </c>
       <c r="D85" t="str">
         <v>2026-02-02</v>
@@ -3608,10 +3608,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G85" t="str">
-        <v>3:25</v>
+        <v>2:54</v>
       </c>
       <c r="H85" t="str">
-        <v>Tenille Townes</v>
+        <v>LØLØ</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Tenille Townes - enabling (Official Visualizer) - Tenille Townes</v>
+        <v>LØLØ - 007 (Official Music Video) - LØLØ</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Alan Walker - Not Home (Official Lyric Video)</v>
+        <v>Tenille Townes - enabling (Official Visualizer)</v>
       </c>
       <c r="B86" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=0m45tTheoCs</v>
+        <v>https://www.youtube.com/watch?v=yL_TxDF8WtI</v>
       </c>
       <c r="D86" t="str">
         <v>2026-02-02</v>
@@ -3646,10 +3646,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G86" t="str">
-        <v>2:01</v>
+        <v>3:25</v>
       </c>
       <c r="H86" t="str">
-        <v>Alan Walker</v>
+        <v>Tenille Townes</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Alan Walker - Not Home (Official Lyric Video) - Alan Walker</v>
+        <v>Tenille Townes - enabling (Official Visualizer) - Tenille Townes</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Charli xcx - Wall of Sound (Official Audio)</v>
+        <v>Alan Walker - Not Home (Official Lyric Video)</v>
       </c>
       <c r="B87" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=AHm1i212UP4</v>
+        <v>https://www.youtube.com/watch?v=0m45tTheoCs</v>
       </c>
       <c r="D87" t="str">
         <v>2026-02-02</v>
@@ -3684,10 +3684,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G87" t="str">
-        <v>2:25</v>
+        <v>2:01</v>
       </c>
       <c r="H87" t="str">
-        <v>Charli xcx</v>
+        <v>Alan Walker</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Charli xcx - Wall of Sound (Official Audio) - Charli xcx</v>
+        <v>Alan Walker - Not Home (Official Lyric Video) - Alan Walker</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Labrinth - God Spoke (Official Visualizer)</v>
+        <v>Charli xcx - Wall of Sound (Official Audio)</v>
       </c>
       <c r="B88" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=Srb2P9efFHY</v>
+        <v>https://www.youtube.com/watch?v=AHm1i212UP4</v>
       </c>
       <c r="D88" t="str">
         <v>2026-02-02</v>
@@ -3722,10 +3722,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G88" t="str">
-        <v>1:14</v>
+        <v>2:25</v>
       </c>
       <c r="H88" t="str">
-        <v>Labrinth</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Labrinth - God Spoke (Official Visualizer) - Labrinth</v>
+        <v>Charli xcx - Wall of Sound (Official Audio) - Charli xcx</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Official Audio)</v>
+        <v>Labrinth - God Spoke (Official Visualizer)</v>
       </c>
       <c r="B89" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=NvHXKIrBiR8</v>
+        <v>https://www.youtube.com/watch?v=Srb2P9efFHY</v>
       </c>
       <c r="D89" t="str">
         <v>2026-02-02</v>
@@ -3760,10 +3760,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G89" t="str">
-        <v>2:59</v>
+        <v>1:14</v>
       </c>
       <c r="H89" t="str">
-        <v>Charlie Puth</v>
+        <v>Labrinth</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Official Audio) - Charlie Puth</v>
+        <v>Labrinth - God Spoke (Official Visualizer) - Labrinth</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Girl Tones - Volcano (Visualizer)</v>
+        <v>Charlie Puth - Beat Yourself Up (Official Audio)</v>
       </c>
       <c r="B90" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=D2-t5SDV1IE</v>
+        <v>https://www.youtube.com/watch?v=NvHXKIrBiR8</v>
       </c>
       <c r="D90" t="str">
         <v>2026-02-02</v>
@@ -3798,10 +3798,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G90" t="str">
-        <v>2:29</v>
+        <v>2:59</v>
       </c>
       <c r="H90" t="str">
-        <v>Girl Tones</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Girl Tones - Volcano (Visualizer) - Girl Tones</v>
+        <v>Charlie Puth - Beat Yourself Up (Official Audio) - Charlie Puth</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer)</v>
+        <v>Girl Tones - Volcano (Visualizer)</v>
       </c>
       <c r="B91" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=BouRN2QuXV8</v>
+        <v>https://www.youtube.com/watch?v=D2-t5SDV1IE</v>
       </c>
       <c r="D91" t="str">
         <v>2026-02-02</v>
@@ -3836,10 +3836,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G91" t="str">
-        <v>2:34</v>
+        <v>2:29</v>
       </c>
       <c r="H91" t="str">
-        <v>Jagwar Twin</v>
+        <v>Girl Tones</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer) - Jagwar Twin</v>
+        <v>Girl Tones - Volcano (Visualizer) - Girl Tones</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video)</v>
+        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer)</v>
       </c>
       <c r="B92" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=IyPD6AnWlRg</v>
+        <v>https://www.youtube.com/watch?v=BouRN2QuXV8</v>
       </c>
       <c r="D92" t="str">
         <v>2026-02-02</v>
@@ -3874,10 +3874,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G92" t="str">
-        <v>3:48</v>
+        <v>2:34</v>
       </c>
       <c r="H92" t="str">
-        <v>Caroline Jones</v>
+        <v>Jagwar Twin</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video) - Caroline Jones</v>
+        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer) - Jagwar Twin</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>The Beaches - I Ran (So Far Away) Official Audio</v>
+        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video)</v>
       </c>
       <c r="B93" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=7_i2R-EU-Eg</v>
+        <v>https://www.youtube.com/watch?v=IyPD6AnWlRg</v>
       </c>
       <c r="D93" t="str">
         <v>2026-02-02</v>
@@ -3912,10 +3912,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G93" t="str">
-        <v>3:32</v>
+        <v>3:48</v>
       </c>
       <c r="H93" t="str">
-        <v>The Beaches</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>The Beaches - I Ran (So Far Away) Official Audio - The Beaches</v>
+        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba</v>
+        <v>The Beaches - I Ran (So Far Away) Official Audio</v>
       </c>
       <c r="B94" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=McaD2PG8jOE</v>
+        <v>https://www.youtube.com/watch?v=7_i2R-EU-Eg</v>
       </c>
       <c r="D94" t="str">
         <v>2026-02-02</v>
@@ -3950,10 +3950,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G94" t="str">
-        <v>3:49</v>
+        <v>3:32</v>
       </c>
       <c r="H94" t="str">
-        <v>Dolly Parton</v>
+        <v>The Beaches</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba - Dolly Parton</v>
+        <v>The Beaches - I Ran (So Far Away) Official Audio - The Beaches</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Madison Beer - bad enough (Official Music Video)</v>
+        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba</v>
       </c>
       <c r="B95" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=07SeT_QSJ08</v>
+        <v>https://www.youtube.com/watch?v=McaD2PG8jOE</v>
       </c>
       <c r="D95" t="str">
         <v>2026-02-02</v>
@@ -3988,10 +3988,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G95" t="str">
-        <v>4:28</v>
+        <v>3:49</v>
       </c>
       <c r="H95" t="str">
-        <v>Madison Beer</v>
+        <v>Dolly Parton</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Madison Beer - bad enough (Official Music Video) - Madison Beer</v>
+        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba - Dolly Parton</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Ty Myers - Message to You (Official Video)</v>
+        <v>Madison Beer - bad enough (Official Music Video)</v>
       </c>
       <c r="B96" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=mhw8eAtgnRk</v>
+        <v>https://www.youtube.com/watch?v=07SeT_QSJ08</v>
       </c>
       <c r="D96" t="str">
         <v>2026-02-02</v>
@@ -4026,10 +4026,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G96" t="str">
-        <v>3:37</v>
+        <v>4:28</v>
       </c>
       <c r="H96" t="str">
-        <v>Ty Myers</v>
+        <v>Madison Beer</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Ty Myers - Message to You (Official Video) - Ty Myers</v>
+        <v>Madison Beer - bad enough (Official Music Video) - Madison Beer</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Megan Moroney - Wish I Didn't (Official Video)</v>
+        <v>Ty Myers - Message to You (Official Video)</v>
       </c>
       <c r="B97" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=plbNzv3KvWs</v>
+        <v>https://www.youtube.com/watch?v=mhw8eAtgnRk</v>
       </c>
       <c r="D97" t="str">
         <v>2026-02-02</v>
@@ -4064,10 +4064,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G97" t="str">
-        <v>3:35</v>
+        <v>3:37</v>
       </c>
       <c r="H97" t="str">
-        <v>Megan Moroney</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Megan Moroney - Wish I Didn't (Official Video) - Megan Moroney</v>
+        <v>Ty Myers - Message to You (Official Video) - Ty Myers</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Julia Cole - What Could Go Wrong (Official Lyric Video)</v>
+        <v>Megan Moroney - Wish I Didn't (Official Video)</v>
       </c>
       <c r="B98" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=GSkO7B_RbQE</v>
+        <v>https://www.youtube.com/watch?v=plbNzv3KvWs</v>
       </c>
       <c r="D98" t="str">
         <v>2026-02-02</v>
@@ -4102,10 +4102,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G98" t="str">
-        <v>2:31</v>
+        <v>3:35</v>
       </c>
       <c r="H98" t="str">
-        <v>Julia Cole Music</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Julia Cole - What Could Go Wrong (Official Lyric Video) - Julia Cole Music</v>
+        <v>Megan Moroney - Wish I Didn't (Official Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Lily Allen - Sleepwalking (Live on SNL)</v>
+        <v>Julia Cole - What Could Go Wrong (Official Lyric Video)</v>
       </c>
       <c r="B99" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=vH5ewjAQfNc</v>
+        <v>https://www.youtube.com/watch?v=GSkO7B_RbQE</v>
       </c>
       <c r="D99" t="str">
         <v>2026-02-02</v>
@@ -4140,10 +4140,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G99" t="str">
-        <v>3:21</v>
+        <v>2:31</v>
       </c>
       <c r="H99" t="str">
-        <v>Lily Allen</v>
+        <v>Julia Cole Music</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Lily Allen - Sleepwalking (Live on SNL) - Lily Allen</v>
+        <v>Julia Cole - What Could Go Wrong (Official Lyric Video) - Julia Cole Music</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios)</v>
+        <v>Lily Allen - Sleepwalking (Live on SNL)</v>
       </c>
       <c r="B100" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=R0vVYP8tSIw</v>
+        <v>https://www.youtube.com/watch?v=vH5ewjAQfNc</v>
       </c>
       <c r="D100" t="str">
         <v>2026-02-02</v>
@@ -4178,10 +4178,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G100" t="str">
-        <v>5:24</v>
+        <v>3:21</v>
       </c>
       <c r="H100" t="str">
-        <v>Nickless</v>
+        <v>Lily Allen</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios) - Nickless</v>
+        <v>Lily Allen - Sleepwalking (Live on SNL) - Lily Allen</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Peach PRC - Back To You (Official Audio)</v>
+        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios)</v>
       </c>
       <c r="B101" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=upfuNpZvNZc</v>
+        <v>https://www.youtube.com/watch?v=R0vVYP8tSIw</v>
       </c>
       <c r="D101" t="str">
         <v>2026-02-02</v>
@@ -4216,10 +4216,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G101" t="str">
-        <v>3:11</v>
+        <v>5:24</v>
       </c>
       <c r="H101" t="str">
-        <v>Peach PRC</v>
+        <v>Nickless</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,7 +4231,7 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Peach PRC - Back To You (Official Audio) - Peach PRC</v>
+        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios) - Nickless</v>
       </c>
     </row>
     <row r="102">

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Nothing But Thieves - Sorry (Official Audio)</v>
       </c>
       <c r="B2" t="str">
-        <v>1 hour ago</v>
+        <v>2 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=D7QfVqo5YqY</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>1 hour ago</v>
+        <v>2 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:37</v>
@@ -1693,7 +1693,7 @@
         <v>Teddy Swims - Need You More (Live - Green Room Sessions)</v>
       </c>
       <c r="B35" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=1ugf5aaY4pY</v>
@@ -1705,7 +1705,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G35" t="str">
         <v>3:16</v>
@@ -1807,7 +1807,7 @@
         <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show</v>
       </c>
       <c r="B38" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=ylifHFJWJ_c</v>
@@ -1819,7 +1819,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G38" t="str">
         <v>4:10</v>
@@ -2263,7 +2263,7 @@
         <v>Neal Francis - Back It Up (Live At The Salt Shed)</v>
       </c>
       <c r="B50" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C50" t="str">
         <v>https://www.youtube.com/watch?v=46iZEdsxjC0</v>
@@ -2275,7 +2275,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G50" t="str">
         <v>5:01</v>
@@ -2301,7 +2301,7 @@
         <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
       </c>
       <c r="B51" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C51" t="str">
         <v>https://www.youtube.com/watch?v=K2nG1Uukz7E</v>
@@ -2313,7 +2313,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G51" t="str">
         <v>4:12</v>
@@ -3023,7 +3023,7 @@
         <v>Lana Lubany - BAD IDEA (Official Video)</v>
       </c>
       <c r="B70" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C70" t="str">
         <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
@@ -3035,7 +3035,7 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G70" t="str">
         <v>2:59</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L203"/>
+  <dimension ref="A1:L205"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -439,7 +439,7 @@
         <v>Nothing But Thieves - Sorry (Official Audio)</v>
       </c>
       <c r="B2" t="str">
-        <v>2 hours ago</v>
+        <v>3 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=D7QfVqo5YqY</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>2 hours ago</v>
+        <v>3 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:37</v>
@@ -477,7 +477,7 @@
         <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music</v>
       </c>
       <c r="B3" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=KdsHxyl4bE8</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G3" t="str">
         <v>4:58</v>
@@ -515,7 +515,7 @@
         <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield CA (2026)</v>
       </c>
       <c r="B4" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=Mwkl_Cz_SG8</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G4" t="str">
         <v>5:08</v>
@@ -1655,7 +1655,7 @@
         <v>Demi Lovato - Ghost (Live)</v>
       </c>
       <c r="B34" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=E-ECwdRndVA</v>
@@ -1667,7 +1667,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G34" t="str">
         <v>4:05</v>
@@ -1769,7 +1769,7 @@
         <v>The Offspring - Looking Out For #1 | Live in Spokane WA (2026)</v>
       </c>
       <c r="B37" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C37" t="str">
         <v>https://www.youtube.com/watch?v=2HSbo51EFNg</v>
@@ -1781,7 +1781,7 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G37" t="str">
         <v>2:57</v>
@@ -2187,7 +2187,7 @@
         <v>Amazon Music presents: Sienna Spiro - You Stole The Show</v>
       </c>
       <c r="B48" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C48" t="str">
         <v>https://www.youtube.com/watch?v=stYIRyCLN4Y</v>
@@ -2199,7 +2199,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G48" t="str">
         <v>3:24</v>
@@ -2225,7 +2225,7 @@
         <v>Harry Styles - Aperture (Official Video)</v>
       </c>
       <c r="B49" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C49" t="str">
         <v>https://www.youtube.com/watch?v=7sxVHYZ_PnA</v>
@@ -2237,7 +2237,7 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G49" t="str">
         <v>5:52</v>
@@ -2643,7 +2643,7 @@
         <v>Louis Tomlinson - Imposter (Official Video)</v>
       </c>
       <c r="B60" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C60" t="str">
         <v>https://www.youtube.com/watch?v=rzuD5szQhso</v>
@@ -2655,7 +2655,7 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G60" t="str">
         <v>2:56</v>
@@ -4236,13 +4236,13 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Body</v>
+        <v>Heaven</v>
       </c>
       <c r="B102" t="str">
         <v/>
       </c>
       <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/body/1871258331</v>
+        <v>https://music.apple.com/us/song/heaven/1862570892</v>
       </c>
       <c r="D102" t="str">
         <v>2026-02-02</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>OCTANE</v>
+        <v>Ambiguous Desire</v>
       </c>
       <c r="G102" t="str">
-        <v>2:35</v>
+        <v>4:26</v>
       </c>
       <c r="H102" t="str">
-        <v>Don Toliver</v>
+        <v>Arlo Parks</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/don-toliver/1237012992</v>
+        <v>https://music.apple.com/us/artist/arlo-parks/1291875084</v>
       </c>
       <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/body/1871258329</v>
+        <v>https://music.apple.com/us/album/heaven/1862570378</v>
       </c>
       <c r="L102" t="str">
-        <v>Body - Don Toliver</v>
+        <v>Heaven - Arlo Parks</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Dandelion</v>
+        <v>Body</v>
       </c>
       <c r="B103" t="str">
         <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/dandelion/1869436838</v>
+        <v>https://music.apple.com/us/song/body/1871258331</v>
       </c>
       <c r="D103" t="str">
         <v>2026-02-02</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>Dandelion</v>
+        <v>OCTANE</v>
       </c>
       <c r="G103" t="str">
-        <v>4:00</v>
+        <v>2:35</v>
       </c>
       <c r="H103" t="str">
-        <v>Ella Langley</v>
+        <v>Don Toliver</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/ella-langley/1384373733</v>
+        <v>https://music.apple.com/us/artist/don-toliver/1237012992</v>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/dandelion/1869436835</v>
+        <v>https://music.apple.com/us/album/body/1871258329</v>
       </c>
       <c r="L103" t="str">
-        <v>Dandelion - Ella Langley</v>
+        <v>Body - Don Toliver</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>LIGHTS GO OUT</v>
+        <v>Dandelion</v>
       </c>
       <c r="B104" t="str">
         <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/lights-go-out/1870833473</v>
+        <v>https://music.apple.com/us/song/dandelion/1869436838</v>
       </c>
       <c r="D104" t="str">
         <v>2026-02-02</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>LIGHTS GO OUT - Single</v>
+        <v>Dandelion</v>
       </c>
       <c r="G104" t="str">
-        <v>2:38</v>
+        <v>4:00</v>
       </c>
       <c r="H104" t="str">
-        <v>John Summit</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
+        <v>https://music.apple.com/us/artist/ella-langley/1384373733</v>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/lights-go-out/1870833462</v>
+        <v>https://music.apple.com/us/album/dandelion/1869436835</v>
       </c>
       <c r="L104" t="str">
-        <v>LIGHTS GO OUT - John Summit</v>
+        <v>Dandelion - Ella Langley</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>The Great Divide</v>
+        <v>LIGHTS GO OUT</v>
       </c>
       <c r="B105" t="str">
         <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/the-great-divide/1872239886</v>
+        <v>https://music.apple.com/us/song/lights-go-out/1870833473</v>
       </c>
       <c r="D105" t="str">
         <v>2026-02-02</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>The Great Divide</v>
+        <v>LIGHTS GO OUT - Single</v>
       </c>
       <c r="G105" t="str">
-        <v>5:17</v>
+        <v>2:38</v>
       </c>
       <c r="H105" t="str">
-        <v>Noah Kahan</v>
+        <v>John Summit</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/noah-kahan/328583953</v>
+        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/the-great-divide/1872239868</v>
+        <v>https://music.apple.com/us/album/lights-go-out/1870833462</v>
       </c>
       <c r="L105" t="str">
-        <v>The Great Divide - Noah Kahan</v>
+        <v>LIGHTS GO OUT - John Summit</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>tristón</v>
+        <v>The Great Divide</v>
       </c>
       <c r="B106" t="str">
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/trist%C3%B3n/1872585947</v>
+        <v>https://music.apple.com/us/song/the-great-divide/1872239886</v>
       </c>
       <c r="D106" t="str">
         <v>2026-02-02</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>tristón - Single</v>
+        <v>The Great Divide</v>
       </c>
       <c r="G106" t="str">
-        <v>3:36</v>
+        <v>5:17</v>
       </c>
       <c r="H106" t="str">
-        <v>Fuerza Regida</v>
+        <v>Noah Kahan</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/fuerza-regida/1275690475</v>
+        <v>https://music.apple.com/us/artist/noah-kahan/328583953</v>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/trist%C3%B3n/1872585761</v>
+        <v>https://music.apple.com/us/album/the-great-divide/1872239868</v>
       </c>
       <c r="L106" t="str">
-        <v>tristón - Fuerza Regida</v>
+        <v>The Great Divide - Noah Kahan</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Feed the Streets</v>
+        <v>tristón</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/feed-the-streets/1869462051</v>
+        <v>https://music.apple.com/us/song/trist%C3%B3n/1872585947</v>
       </c>
       <c r="D107" t="str">
         <v>2026-02-02</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>Feed the Streets - Single</v>
+        <v>tristón - Single</v>
       </c>
       <c r="G107" t="str">
-        <v>2:58</v>
+        <v>3:36</v>
       </c>
       <c r="H107" t="str">
-        <v>Rod Wave</v>
+        <v>Fuerza Regida</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/rod-wave/1140623439</v>
+        <v>https://music.apple.com/us/artist/fuerza-regida/1275690475</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/feed-the-streets/1869462040</v>
+        <v>https://music.apple.com/us/album/trist%C3%B3n/1872585761</v>
       </c>
       <c r="L107" t="str">
-        <v>Feed the Streets - Rod Wave</v>
+        <v>tristón - Fuerza Regida</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>I Did This To Myself</v>
+        <v>Feed the Streets</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/i-did-this-to-myself/1861531672</v>
+        <v>https://music.apple.com/us/song/feed-the-streets/1869462051</v>
       </c>
       <c r="D108" t="str">
         <v>2026-02-02</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>Distracted</v>
+        <v>Feed the Streets - Single</v>
       </c>
       <c r="G108" t="str">
-        <v>2:30</v>
+        <v>2:58</v>
       </c>
       <c r="H108" t="str">
-        <v>Thundercat</v>
+        <v>Rod Wave</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/thundercat/367322286</v>
+        <v>https://music.apple.com/us/artist/rod-wave/1140623439</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/i-did-this-to-myself/1861531667</v>
+        <v>https://music.apple.com/us/album/feed-the-streets/1869462040</v>
       </c>
       <c r="L108" t="str">
-        <v>I Did This To Myself - Thundercat</v>
+        <v>Feed the Streets - Rod Wave</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>For Hire</v>
+        <v>I Did This To Myself</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/for-hire/1870722567</v>
+        <v>https://music.apple.com/us/song/i-did-this-to-myself/1861531672</v>
       </c>
       <c r="D109" t="str">
         <v>2026-02-02</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>For Hire - Single</v>
+        <v>Distracted</v>
       </c>
       <c r="G109" t="str">
-        <v>3:44</v>
+        <v>2:30</v>
       </c>
       <c r="H109" t="str">
-        <v>People I’ve Met</v>
+        <v>Thundercat</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/people-ive-met/1853169947</v>
+        <v>https://music.apple.com/us/artist/thundercat/367322286</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/for-hire/1870722565</v>
+        <v>https://music.apple.com/us/album/i-did-this-to-myself/1861531667</v>
       </c>
       <c r="L109" t="str">
-        <v>For Hire - People I’ve Met</v>
+        <v>I Did This To Myself - Thundercat</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>McArthur</v>
+        <v>For Hire</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/mcarthur/1871231844</v>
+        <v>https://music.apple.com/us/song/for-hire/1870722567</v>
       </c>
       <c r="D110" t="str">
         <v>2026-02-02</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>McArthur - Single</v>
+        <v>For Hire - Single</v>
       </c>
       <c r="G110" t="str">
-        <v>3:51</v>
+        <v>3:44</v>
       </c>
       <c r="H110" t="str">
-        <v>HARDY</v>
+        <v>People I’ve Met</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/hardy/1438874739</v>
+        <v>https://music.apple.com/us/artist/people-ive-met/1853169947</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/mcarthur/1871231823</v>
+        <v>https://music.apple.com/us/album/for-hire/1870722565</v>
       </c>
       <c r="L110" t="str">
-        <v>McArthur - HARDY</v>
+        <v>For Hire - People I’ve Met</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Debris</v>
+        <v>McArthur</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/debris/1853069633</v>
+        <v>https://music.apple.com/us/song/mcarthur/1871231844</v>
       </c>
       <c r="D111" t="str">
         <v>2026-02-02</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>COSMIC OPERA ACT I</v>
+        <v>McArthur - Single</v>
       </c>
       <c r="G111" t="str">
-        <v>2:55</v>
+        <v>3:51</v>
       </c>
       <c r="H111" t="str">
-        <v>Labrinth</v>
+        <v>HARDY</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
+        <v>https://music.apple.com/us/artist/hardy/1438874739</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/debris/1853069628</v>
+        <v>https://music.apple.com/us/album/mcarthur/1871231823</v>
       </c>
       <c r="L111" t="str">
-        <v>Debris - Labrinth</v>
+        <v>McArthur - HARDY</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>God Owes Me Money (Live at Apple Music Radio)</v>
+        <v>Debris</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/god-owes-me-money-live-at-apple-music-radio/1871521120</v>
+        <v>https://music.apple.com/us/song/debris/1853069633</v>
       </c>
       <c r="D112" t="str">
         <v>2026-02-02</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>Throw Me Away / God Owes Me Money (Live at Apple Music Radio)</v>
+        <v>COSMIC OPERA ACT I</v>
       </c>
       <c r="G112" t="str">
-        <v>3:25</v>
+        <v>2:55</v>
       </c>
       <c r="H112" t="str">
-        <v>Militarie Gun</v>
+        <v>Labrinth</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/militarie-gun/1529039426</v>
+        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/god-owes-me-money-live-at-apple-music-radio/1871520929</v>
+        <v>https://music.apple.com/us/album/debris/1853069628</v>
       </c>
       <c r="L112" t="str">
-        <v>God Owes Me Money (Live at Apple Music Radio) - Militarie Gun</v>
+        <v>Debris - Labrinth</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>ROCKSTAR RAGING (feat. Swae Lee)</v>
+        <v>God Owes Me Money (Live at Apple Music Radio)</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/rockstar-raging-feat-swae-lee/1873028187</v>
+        <v>https://music.apple.com/us/song/god-owes-me-money-live-at-apple-music-radio/1871521120</v>
       </c>
       <c r="D113" t="str">
         <v>2026-02-02</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>ROCKSTAR RAGING (feat. Swae Lee) - Single</v>
+        <v>Throw Me Away / God Owes Me Money (Live at Apple Music Radio)</v>
       </c>
       <c r="G113" t="str">
-        <v>4:38</v>
+        <v>3:25</v>
       </c>
       <c r="H113" t="str">
-        <v>Mike WiLL Made-It</v>
+        <v>Militarie Gun</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/mike-will-made-it/511333957</v>
+        <v>https://music.apple.com/us/artist/militarie-gun/1529039426</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/rockstar-raging-feat-swae-lee/1873028186</v>
+        <v>https://music.apple.com/us/album/god-owes-me-money-live-at-apple-music-radio/1871520929</v>
       </c>
       <c r="L113" t="str">
-        <v>ROCKSTAR RAGING (feat. Swae Lee) - Mike WiLL Made-It</v>
+        <v>God Owes Me Money (Live at Apple Music Radio) - Militarie Gun</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>1+1</v>
+        <v>ROCKSTAR RAGING (feat. Swae Lee)</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/1-1/1870378316</v>
+        <v>https://music.apple.com/us/song/rockstar-raging-feat-swae-lee/1873028187</v>
       </c>
       <c r="D114" t="str">
         <v>2026-02-02</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>1+1 - Single</v>
+        <v>ROCKSTAR RAGING (feat. Swae Lee) - Single</v>
       </c>
       <c r="G114" t="str">
-        <v>3:06</v>
+        <v>4:38</v>
       </c>
       <c r="H114" t="str">
-        <v>Maluma</v>
+        <v>Mike WiLL Made-It</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/maluma/448916501</v>
+        <v>https://music.apple.com/us/artist/mike-will-made-it/511333957</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/1-1/1870378315</v>
+        <v>https://music.apple.com/us/album/rockstar-raging-feat-swae-lee/1873028186</v>
       </c>
       <c r="L114" t="str">
-        <v>1+1 - Maluma</v>
+        <v>ROCKSTAR RAGING (feat. Swae Lee) - Mike WiLL Made-It</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Still Sincere (feat. PinkPantheress)</v>
+        <v>1+1</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/still-sincere-feat-pinkpantheress/1862228374</v>
+        <v>https://music.apple.com/us/song/1-1/1870378316</v>
       </c>
       <c r="D115" t="str">
         <v>2026-02-02</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>Still Sincere (feat. PinkPantheress) - Single</v>
+        <v>1+1 - Single</v>
       </c>
       <c r="G115" t="str">
-        <v>3:08</v>
+        <v>3:06</v>
       </c>
       <c r="H115" t="str">
-        <v>MJ Cole</v>
+        <v>Maluma</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/mj-cole/405892</v>
+        <v>https://music.apple.com/us/artist/maluma/448916501</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/still-sincere-feat-pinkpantheress/1862228373</v>
+        <v>https://music.apple.com/us/album/1-1/1870378315</v>
       </c>
       <c r="L115" t="str">
-        <v>Still Sincere (feat. PinkPantheress) - MJ Cole</v>
+        <v>1+1 - Maluma</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Two Car Garage</v>
+        <v>Still Sincere (feat. PinkPantheress)</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/two-car-garage/1869137588</v>
+        <v>https://music.apple.com/us/song/still-sincere-feat-pinkpantheress/1862228374</v>
       </c>
       <c r="D116" t="str">
         <v>2026-02-02</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Two Car Garage - Single</v>
+        <v>Still Sincere (feat. PinkPantheress) - Single</v>
       </c>
       <c r="G116" t="str">
-        <v>3:02</v>
+        <v>3:08</v>
       </c>
       <c r="H116" t="str">
-        <v>Jon Bellion</v>
+        <v>MJ Cole</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/jon-bellion/659289673</v>
+        <v>https://music.apple.com/us/artist/mj-cole/405892</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/two-car-garage/1869137587</v>
+        <v>https://music.apple.com/us/album/still-sincere-feat-pinkpantheress/1862228373</v>
       </c>
       <c r="L116" t="str">
-        <v>Two Car Garage - Jon Bellion</v>
+        <v>Still Sincere (feat. PinkPantheress) - MJ Cole</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>fml .</v>
+        <v>Two Car Garage</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/fml/1872686260</v>
+        <v>https://music.apple.com/us/song/two-car-garage/1869137588</v>
       </c>
       <c r="D117" t="str">
         <v>2026-02-02</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>The Boy who cried Terrified .</v>
+        <v>Two Car Garage - Single</v>
       </c>
       <c r="G117" t="str">
-        <v>2:40</v>
+        <v>3:02</v>
       </c>
       <c r="H117" t="str">
-        <v>fakemink</v>
+        <v>Jon Bellion</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/fakemink/1744500063</v>
+        <v>https://music.apple.com/us/artist/jon-bellion/659289673</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/fml/1872686249</v>
+        <v>https://music.apple.com/us/album/two-car-garage/1869137587</v>
       </c>
       <c r="L117" t="str">
-        <v>fml . - fakemink</v>
+        <v>Two Car Garage - Jon Bellion</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Faked It All The Time</v>
+        <v>fml .</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/faked-it-all-the-time/1871050032</v>
+        <v>https://music.apple.com/us/song/fml/1872686260</v>
       </c>
       <c r="D118" t="str">
         <v>2026-02-02</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>Faked It All The Time - Single</v>
+        <v>The Boy who cried Terrified .</v>
       </c>
       <c r="G118" t="str">
-        <v>3:01</v>
+        <v>2:40</v>
       </c>
       <c r="H118" t="str">
-        <v>Allie Sherlock</v>
+        <v>fakemink</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/allie-sherlock/1314464325</v>
+        <v>https://music.apple.com/us/artist/fakemink/1744500063</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/faked-it-all-the-time/1871050031</v>
+        <v>https://music.apple.com/us/album/fml/1872686249</v>
       </c>
       <c r="L118" t="str">
-        <v>Faked It All The Time - Allie Sherlock</v>
+        <v>fml . - fakemink</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>House of the Rising Sun</v>
+        <v>Faked It All The Time</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/house-of-the-rising-sun/1872111857</v>
+        <v>https://music.apple.com/us/song/faked-it-all-the-time/1871050032</v>
       </c>
       <c r="D119" t="str">
         <v>2026-02-02</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>House of the Rising Sun - Single</v>
+        <v>Faked It All The Time - Single</v>
       </c>
       <c r="G119" t="str">
-        <v>3:08</v>
+        <v>3:01</v>
       </c>
       <c r="H119" t="str">
-        <v>Lizzy McAlpine</v>
+        <v>Allie Sherlock</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/lizzy-mcalpine/1350245112</v>
+        <v>https://music.apple.com/us/artist/allie-sherlock/1314464325</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/house-of-the-rising-sun/1872111734</v>
+        <v>https://music.apple.com/us/album/faked-it-all-the-time/1871050031</v>
       </c>
       <c r="L119" t="str">
-        <v>House of the Rising Sun - Lizzy McAlpine</v>
+        <v>Faked It All The Time - Allie Sherlock</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Lorelei</v>
+        <v>House of the Rising Sun</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/lorelei/1867640808</v>
+        <v>https://music.apple.com/us/song/house-of-the-rising-sun/1872111857</v>
       </c>
       <c r="D120" t="str">
         <v>2026-02-02</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Lorelei - Single</v>
+        <v>House of the Rising Sun - Single</v>
       </c>
       <c r="G120" t="str">
-        <v>2:35</v>
+        <v>3:08</v>
       </c>
       <c r="H120" t="str">
-        <v>ERNEST</v>
+        <v>Lizzy McAlpine</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
+        <v>https://music.apple.com/us/artist/lizzy-mcalpine/1350245112</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/lorelei/1867640583</v>
+        <v>https://music.apple.com/us/album/house-of-the-rising-sun/1872111734</v>
       </c>
       <c r="L120" t="str">
-        <v>Lorelei - ERNEST</v>
+        <v>House of the Rising Sun - Lizzy McAlpine</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Free</v>
+        <v>Lorelei</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/free/1870703329</v>
+        <v>https://music.apple.com/us/song/lorelei/1867640808</v>
       </c>
       <c r="D121" t="str">
         <v>2026-02-02</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Free - Single</v>
+        <v>Lorelei - Single</v>
       </c>
       <c r="G121" t="str">
-        <v>3:56</v>
+        <v>2:35</v>
       </c>
       <c r="H121" t="str">
-        <v>SLANDER</v>
+        <v>ERNEST</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/slander/1051421487</v>
+        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/free/1870703327</v>
+        <v>https://music.apple.com/us/album/lorelei/1867640583</v>
       </c>
       <c r="L121" t="str">
-        <v>Free - SLANDER</v>
+        <v>Lorelei - ERNEST</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>professional heartbreaker</v>
+        <v>Free</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/professional-heartbreaker/1871053476</v>
+        <v>https://music.apple.com/us/song/free/1870703329</v>
       </c>
       <c r="D122" t="str">
         <v>2026-02-02</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>professional heartbreaker - Single</v>
+        <v>Free - Single</v>
       </c>
       <c r="G122" t="str">
-        <v>2:55</v>
+        <v>3:56</v>
       </c>
       <c r="H122" t="str">
-        <v>Artemas</v>
+        <v>SLANDER</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
+        <v>https://music.apple.com/us/artist/slander/1051421487</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/professional-heartbreaker/1871053473</v>
+        <v>https://music.apple.com/us/album/free/1870703327</v>
       </c>
       <c r="L122" t="str">
-        <v>professional heartbreaker - Artemas</v>
+        <v>Free - SLANDER</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>tell me what you want</v>
+        <v>ASSIGNMENT</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/tell-me-what-you-want/1871463892</v>
+        <v>https://music.apple.com/us/song/assignment/1872764440</v>
       </c>
       <c r="D123" t="str">
         <v>2026-02-02</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>ACT II</v>
+        <v>ASSIGNMENT - Single</v>
       </c>
       <c r="G123" t="str">
-        <v>3:56</v>
+        <v>2:23</v>
       </c>
       <c r="H123" t="str">
-        <v>Sasha Keable</v>
+        <v>Power Snatch</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/sasha-keable/325850892</v>
+        <v>https://music.apple.com/us/artist/power-snatch/1872764439</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/tell-me-what-you-want/1871463550</v>
+        <v>https://music.apple.com/us/album/assignment/1872764438</v>
       </c>
       <c r="L123" t="str">
-        <v>tell me what you want - Sasha Keable</v>
+        <v>ASSIGNMENT - Power Snatch</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Aguas</v>
+        <v>professional heartbreaker</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/aguas/1869455857</v>
+        <v>https://music.apple.com/us/song/professional-heartbreaker/1871053476</v>
       </c>
       <c r="D124" t="str">
         <v>2026-02-02</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Aguas - Single</v>
+        <v>professional heartbreaker - Single</v>
       </c>
       <c r="G124" t="str">
-        <v>2:52</v>
+        <v>2:55</v>
       </c>
       <c r="H124" t="str">
-        <v>Luis R Conriquez</v>
+        <v>Artemas</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
+        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/aguas/1869455582</v>
+        <v>https://music.apple.com/us/album/professional-heartbreaker/1871053473</v>
       </c>
       <c r="L124" t="str">
-        <v>Aguas - Luis R Conriquez</v>
+        <v>professional heartbreaker - Artemas</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Ants In My Room</v>
+        <v>tell me what you want</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/ants-in-my-room/1870967813</v>
+        <v>https://music.apple.com/us/song/tell-me-what-you-want/1871463892</v>
       </c>
       <c r="D125" t="str">
         <v>2026-02-02</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Ants In My Room - Single</v>
+        <v>ACT II</v>
       </c>
       <c r="G125" t="str">
-        <v>2:48</v>
+        <v>3:56</v>
       </c>
       <c r="H125" t="str">
-        <v>Carter Vail</v>
+        <v>Sasha Keable</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/carter-vail/1102115053</v>
+        <v>https://music.apple.com/us/artist/sasha-keable/325850892</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/ants-in-my-room/1870967810</v>
+        <v>https://music.apple.com/us/album/tell-me-what-you-want/1871463550</v>
       </c>
       <c r="L125" t="str">
-        <v>Ants In My Room - Carter Vail</v>
+        <v>tell me what you want - Sasha Keable</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Baddie</v>
+        <v>Aguas</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/baddie/1849760827</v>
+        <v>https://music.apple.com/us/song/aguas/1869455857</v>
       </c>
       <c r="D126" t="str">
         <v>2026-02-02</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Bohemio</v>
+        <v>Aguas - Single</v>
       </c>
       <c r="G126" t="str">
-        <v>3:11</v>
+        <v>2:52</v>
       </c>
       <c r="H126" t="str">
-        <v>Nicky Jam</v>
+        <v>Luis R Conriquez</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/nicky-jam/33987470</v>
+        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/baddie/1849760822</v>
+        <v>https://music.apple.com/us/album/aguas/1869455582</v>
       </c>
       <c r="L126" t="str">
-        <v>Baddie - Nicky Jam</v>
+        <v>Aguas - Luis R Conriquez</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>What You Need - A COLORS SHOW</v>
+        <v>Ants In My Room</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/what-you-need-a-colors-show/1870990925</v>
+        <v>https://music.apple.com/us/song/ants-in-my-room/1870967813</v>
       </c>
       <c r="D127" t="str">
         <v>2026-02-02</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>What You Need - A COLORS SHOW - Single</v>
+        <v>Ants In My Room - Single</v>
       </c>
       <c r="G127" t="str">
-        <v>3:51</v>
+        <v>2:48</v>
       </c>
       <c r="H127" t="str">
-        <v>Tems</v>
+        <v>Carter Vail</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/tems/1413909060</v>
+        <v>https://music.apple.com/us/artist/carter-vail/1102115053</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/what-you-need-a-colors-show/1870990923</v>
+        <v>https://music.apple.com/us/album/ants-in-my-room/1870967810</v>
       </c>
       <c r="L127" t="str">
-        <v>What You Need - A COLORS SHOW - Tems</v>
+        <v>Ants In My Room - Carter Vail</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>OK OK (Hamdi Remix)</v>
+        <v>Baddie</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/ok-ok-hamdi-remix/1871538130</v>
+        <v>https://music.apple.com/us/song/baddie/1849760827</v>
       </c>
       <c r="D128" t="str">
         <v>2026-02-02</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>OK OK (Hamdi Remix) - Single</v>
+        <v>Bohemio</v>
       </c>
       <c r="G128" t="str">
-        <v>3:16</v>
+        <v>3:11</v>
       </c>
       <c r="H128" t="str">
-        <v>Fred again..</v>
+        <v>Nicky Jam</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
+        <v>https://music.apple.com/us/artist/nicky-jam/33987470</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/ok-ok-hamdi-remix/1871538128</v>
+        <v>https://music.apple.com/us/album/baddie/1849760822</v>
       </c>
       <c r="L128" t="str">
-        <v>OK OK (Hamdi Remix) - Fred again..</v>
+        <v>Baddie - Nicky Jam</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Ever and Ever Before (feat. MŌRIAH &amp; Courtney)</v>
+        <v>What You Need - A COLORS SHOW</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/ever-and-ever-before-feat-m%C5%8Driah-courtney/1869383260</v>
+        <v>https://music.apple.com/us/song/what-you-need-a-colors-show/1870990925</v>
       </c>
       <c r="D129" t="str">
         <v>2026-02-02</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>Ever and Ever Before (feat. MŌRIAH &amp; Courtney) - Single</v>
+        <v>What You Need - A COLORS SHOW - Single</v>
       </c>
       <c r="G129" t="str">
-        <v>3:50</v>
+        <v>3:51</v>
       </c>
       <c r="H129" t="str">
-        <v>for KING &amp; COUNTRY</v>
+        <v>Tems</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/for-king-country/457871289</v>
+        <v>https://music.apple.com/us/artist/tems/1413909060</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/ever-and-ever-before-feat-m%C5%8Driah-courtney/1869383258</v>
+        <v>https://music.apple.com/us/album/what-you-need-a-colors-show/1870990923</v>
       </c>
       <c r="L129" t="str">
-        <v>Ever and Ever Before (feat. MŌRIAH &amp; Courtney) - for KING &amp; COUNTRY</v>
+        <v>What You Need - A COLORS SHOW - Tems</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>For The First Time, Again</v>
+        <v>OK OK (Hamdi Remix)</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/for-the-first-time-again/1834736723</v>
+        <v>https://music.apple.com/us/song/ok-ok-hamdi-remix/1871538130</v>
       </c>
       <c r="D130" t="str">
         <v>2026-02-02</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>For The First Time, Again</v>
+        <v>OK OK (Hamdi Remix) - Single</v>
       </c>
       <c r="G130" t="str">
-        <v>3:33</v>
+        <v>3:16</v>
       </c>
       <c r="H130" t="str">
-        <v>Tyler Ballgame</v>
+        <v>Fred again..</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/tyler-ballgame/1755347001</v>
+        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/for-the-first-time-again/1834736717</v>
+        <v>https://music.apple.com/us/album/ok-ok-hamdi-remix/1871538128</v>
       </c>
       <c r="L130" t="str">
-        <v>For The First Time, Again - Tyler Ballgame</v>
+        <v>OK OK (Hamdi Remix) - Fred again..</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Liars Tale</v>
+        <v>Ever and Ever Before (feat. MŌRIAH &amp; Courtney)</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/liars-tale/1862207951</v>
+        <v>https://music.apple.com/us/song/ever-and-ever-before-feat-m%C5%8Driah-courtney/1869383260</v>
       </c>
       <c r="D131" t="str">
         <v>2026-02-02</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>Liars Tale - Single</v>
+        <v>Ever and Ever Before (feat. MŌRIAH &amp; Courtney) - Single</v>
       </c>
       <c r="G131" t="str">
-        <v>3:17</v>
+        <v>3:50</v>
       </c>
       <c r="H131" t="str">
-        <v>Kneecap</v>
+        <v>for KING &amp; COUNTRY</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
+        <v>https://music.apple.com/us/artist/for-king-country/457871289</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/liars-tale/1862207946</v>
+        <v>https://music.apple.com/us/album/ever-and-ever-before-feat-m%C5%8Driah-courtney/1869383258</v>
       </c>
       <c r="L131" t="str">
-        <v>Liars Tale - Kneecap</v>
+        <v>Ever and Ever Before (feat. MŌRIAH &amp; Courtney) - for KING &amp; COUNTRY</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Afraid Of The Dark</v>
+        <v>For The First Time, Again</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/afraid-of-the-dark/1872184048</v>
+        <v>https://music.apple.com/us/song/for-the-first-time-again/1834736723</v>
       </c>
       <c r="D132" t="str">
         <v>2026-02-02</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>Afraid Of The Dark - Single</v>
+        <v>For The First Time, Again</v>
       </c>
       <c r="G132" t="str">
-        <v>4:38</v>
+        <v>3:33</v>
       </c>
       <c r="H132" t="str">
-        <v>Motionless In White</v>
+        <v>Tyler Ballgame</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/motionless-in-white/266666216</v>
+        <v>https://music.apple.com/us/artist/tyler-ballgame/1755347001</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/afraid-of-the-dark/1872184047</v>
+        <v>https://music.apple.com/us/album/for-the-first-time-again/1834736717</v>
       </c>
       <c r="L132" t="str">
-        <v>Afraid Of The Dark - Motionless In White</v>
+        <v>For The First Time, Again - Tyler Ballgame</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Wake Up Calling</v>
+        <v>Liars Tale</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/wake-up-calling/1862338150</v>
+        <v>https://music.apple.com/us/song/liars-tale/1862207951</v>
       </c>
       <c r="D133" t="str">
         <v>2026-02-02</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Wake Up Calling - Single</v>
+        <v>Liars Tale - Single</v>
       </c>
       <c r="G133" t="str">
-        <v>3:49</v>
+        <v>3:17</v>
       </c>
       <c r="H133" t="str">
-        <v>Papa Roach</v>
+        <v>Kneecap</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/papa-roach/3445763</v>
+        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/wake-up-calling/1862338148</v>
+        <v>https://music.apple.com/us/album/liars-tale/1862207946</v>
       </c>
       <c r="L133" t="str">
-        <v>Wake Up Calling - Papa Roach</v>
+        <v>Liars Tale - Kneecap</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>HIGH</v>
+        <v>Afraid Of The Dark</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/high/1867202644</v>
+        <v>https://music.apple.com/us/song/afraid-of-the-dark/1872184048</v>
       </c>
       <c r="D134" t="str">
         <v>2026-02-02</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>NIGHTS AFTER VAMP</v>
+        <v>Afraid Of The Dark - Single</v>
       </c>
       <c r="G134" t="str">
-        <v>3:23</v>
+        <v>4:38</v>
       </c>
       <c r="H134" t="str">
-        <v>Magnolia Park</v>
+        <v>Motionless In White</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/magnolia-park/1413545983</v>
+        <v>https://music.apple.com/us/artist/motionless-in-white/266666216</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/high/1867202638</v>
+        <v>https://music.apple.com/us/album/afraid-of-the-dark/1872184047</v>
       </c>
       <c r="L134" t="str">
-        <v>HIGH - Magnolia Park</v>
+        <v>Afraid Of The Dark - Motionless In White</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Villain</v>
+        <v>Wake Up Calling</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/villain/1860126455</v>
+        <v>https://music.apple.com/us/song/wake-up-calling/1862338150</v>
       </c>
       <c r="D135" t="str">
         <v>2026-02-02</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>Reflections</v>
+        <v>Wake Up Calling - Single</v>
       </c>
       <c r="G135" t="str">
-        <v>3:53</v>
+        <v>3:49</v>
       </c>
       <c r="H135" t="str">
-        <v>From Ashes to New</v>
+        <v>Papa Roach</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/from-ashes-to-new/688645097</v>
+        <v>https://music.apple.com/us/artist/papa-roach/3445763</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/villain/1860126452</v>
+        <v>https://music.apple.com/us/album/wake-up-calling/1862338148</v>
       </c>
       <c r="L135" t="str">
-        <v>Villain - From Ashes to New</v>
+        <v>Wake Up Calling - Papa Roach</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Bad Idea Right?</v>
+        <v>HIGH</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/bad-idea-right/1869792549</v>
+        <v>https://music.apple.com/us/song/high/1867202644</v>
       </c>
       <c r="D136" t="str">
         <v>2026-02-02</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>Bridgerton Season Four (Covers from the Netflix Series – Pt. 1) - EP</v>
+        <v>NIGHTS AFTER VAMP</v>
       </c>
       <c r="G136" t="str">
-        <v>3:00</v>
+        <v>3:23</v>
       </c>
       <c r="H136" t="str">
-        <v>Caleb Chan</v>
+        <v>Magnolia Park</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/caleb-chan/1441662972</v>
+        <v>https://music.apple.com/us/artist/magnolia-park/1413545983</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/bad-idea-right/1869792542</v>
+        <v>https://music.apple.com/us/album/high/1867202638</v>
       </c>
       <c r="L136" t="str">
-        <v>Bad Idea Right? - Caleb Chan</v>
+        <v>HIGH - Magnolia Park</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Residue</v>
+        <v>Villain</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/residue/1863786787</v>
+        <v>https://music.apple.com/us/song/villain/1860126455</v>
       </c>
       <c r="D137" t="str">
         <v>2026-02-02</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>The Moment (The Score)</v>
+        <v>Reflections</v>
       </c>
       <c r="G137" t="str">
-        <v>3:28</v>
+        <v>3:53</v>
       </c>
       <c r="H137" t="str">
-        <v>A. G. Cook</v>
+        <v>From Ashes to New</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/a-g-cook/744253464</v>
+        <v>https://music.apple.com/us/artist/from-ashes-to-new/688645097</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/residue/1863786786</v>
+        <v>https://music.apple.com/us/album/villain/1860126452</v>
       </c>
       <c r="L137" t="str">
-        <v>Residue - A. G. Cook</v>
+        <v>Villain - From Ashes to New</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>I Used to Go to This Bar</v>
+        <v>Bad Idea Right?</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/i-used-to-go-to-this-bar/1839918872</v>
+        <v>https://music.apple.com/us/song/bad-idea-right/1869792549</v>
       </c>
       <c r="D138" t="str">
         <v>2026-02-02</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>I Used to Go to This Bar</v>
+        <v>Bridgerton Season Four (Covers from the Netflix Series – Pt. 1) - EP</v>
       </c>
       <c r="G138" t="str">
-        <v>2:12</v>
+        <v>3:00</v>
       </c>
       <c r="H138" t="str">
-        <v>Joyce Manor</v>
+        <v>Caleb Chan</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/joyce-manor/408598559</v>
+        <v>https://music.apple.com/us/artist/caleb-chan/1441662972</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/i-used-to-go-to-this-bar/1839918836</v>
+        <v>https://music.apple.com/us/album/bad-idea-right/1869792542</v>
       </c>
       <c r="L138" t="str">
-        <v>I Used to Go to This Bar - Joyce Manor</v>
+        <v>Bad Idea Right? - Caleb Chan</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Starlight</v>
+        <v>Residue</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/starlight/1870989674</v>
+        <v>https://music.apple.com/us/song/residue/1863786787</v>
       </c>
       <c r="D139" t="str">
         <v>2026-02-02</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>Everything Glows</v>
+        <v>The Moment (The Score)</v>
       </c>
       <c r="G139" t="str">
-        <v>3:21</v>
+        <v>3:28</v>
       </c>
       <c r="H139" t="str">
-        <v>Cannons</v>
+        <v>A. G. Cook</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/cannons/65568551</v>
+        <v>https://music.apple.com/us/artist/a-g-cook/744253464</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/starlight/1870989672</v>
+        <v>https://music.apple.com/us/album/residue/1863786786</v>
       </c>
       <c r="L139" t="str">
-        <v>Starlight - Cannons</v>
+        <v>Residue - A. G. Cook</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Dandelion</v>
+        <v>I Used to Go to This Bar</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/dandelion/1863154133</v>
+        <v>https://music.apple.com/us/song/i-used-to-go-to-this-bar/1839918872</v>
       </c>
       <c r="D140" t="str">
         <v>2026-02-02</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Corporate Pudding - EP</v>
+        <v>I Used to Go to This Bar</v>
       </c>
       <c r="G140" t="str">
-        <v>3:14</v>
+        <v>2:12</v>
       </c>
       <c r="H140" t="str">
-        <v>Dogpark</v>
+        <v>Joyce Manor</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/dogpark/1710263796</v>
+        <v>https://music.apple.com/us/artist/joyce-manor/408598559</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/dandelion/1863154124</v>
+        <v>https://music.apple.com/us/album/i-used-to-go-to-this-bar/1839918836</v>
       </c>
       <c r="L140" t="str">
-        <v>Dandelion - Dogpark</v>
+        <v>I Used to Go to This Bar - Joyce Manor</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>THEMSELVES</v>
+        <v>Starlight</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/themselves/1845287173</v>
+        <v>https://music.apple.com/us/song/starlight/1870989674</v>
       </c>
       <c r="D141" t="str">
         <v>2026-02-02</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>BACKWARD</v>
+        <v>Everything Glows</v>
       </c>
       <c r="G141" t="str">
-        <v>2:46</v>
+        <v>3:21</v>
       </c>
       <c r="H141" t="str">
-        <v>Jordan Ward</v>
+        <v>Cannons</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/jordan-ward/689602960</v>
+        <v>https://music.apple.com/us/artist/cannons/65568551</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/themselves/1845286980</v>
+        <v>https://music.apple.com/us/album/starlight/1870989672</v>
       </c>
       <c r="L141" t="str">
-        <v>THEMSELVES - Jordan Ward</v>
+        <v>Starlight - Cannons</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>High Maintenance</v>
+        <v>Dandelion</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/high-maintenance/1872497656</v>
+        <v>https://music.apple.com/us/song/dandelion/1863154133</v>
       </c>
       <c r="D142" t="str">
         <v>2026-02-02</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Miracle Mile</v>
+        <v>Corporate Pudding - EP</v>
       </c>
       <c r="G142" t="str">
-        <v>2:24</v>
+        <v>3:14</v>
       </c>
       <c r="H142" t="str">
-        <v>Paul Russell</v>
+        <v>Dogpark</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/paul-russell/1304377463</v>
+        <v>https://music.apple.com/us/artist/dogpark/1710263796</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/high-maintenance/1872496993</v>
+        <v>https://music.apple.com/us/album/dandelion/1863154124</v>
       </c>
       <c r="L142" t="str">
-        <v>High Maintenance - Paul Russell</v>
+        <v>Dandelion - Dogpark</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Trackhawk</v>
+        <v>THEMSELVES</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/trackhawk/1860991724</v>
+        <v>https://music.apple.com/us/song/themselves/1845287173</v>
       </c>
       <c r="D143" t="str">
         <v>2026-02-02</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>Da Realest</v>
+        <v>BACKWARD</v>
       </c>
       <c r="G143" t="str">
-        <v>1:59</v>
+        <v>2:46</v>
       </c>
       <c r="H143" t="str">
-        <v>Babyfxce E</v>
+        <v>Jordan Ward</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/babyfxce-e/1573432856</v>
+        <v>https://music.apple.com/us/artist/jordan-ward/689602960</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/trackhawk/1860991661</v>
+        <v>https://music.apple.com/us/album/themselves/1845286980</v>
       </c>
       <c r="L143" t="str">
-        <v>Trackhawk - Babyfxce E</v>
+        <v>THEMSELVES - Jordan Ward</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Wheel Man</v>
+        <v>High Maintenance</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/wheel-man/1872178895</v>
+        <v>https://music.apple.com/us/song/high-maintenance/1872497656</v>
       </c>
       <c r="D144" t="str">
         <v>2026-02-02</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Xavier</v>
+        <v>Miracle Mile</v>
       </c>
       <c r="G144" t="str">
-        <v>3:05</v>
+        <v>2:24</v>
       </c>
       <c r="H144" t="str">
-        <v>xaviersobased</v>
+        <v>Paul Russell</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/xaviersobased/1540848340</v>
+        <v>https://music.apple.com/us/artist/paul-russell/1304377463</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/wheel-man/1872178596</v>
+        <v>https://music.apple.com/us/album/high-maintenance/1872496993</v>
       </c>
       <c r="L144" t="str">
-        <v>Wheel Man - xaviersobased</v>
+        <v>High Maintenance - Paul Russell</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Natural Disaster</v>
+        <v>Trackhawk</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/natural-disaster/1871263211</v>
+        <v>https://music.apple.com/us/song/trackhawk/1860991724</v>
       </c>
       <c r="D145" t="str">
         <v>2026-02-02</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Natural Disaster - Single</v>
+        <v>Da Realest</v>
       </c>
       <c r="G145" t="str">
-        <v>3:02</v>
+        <v>1:59</v>
       </c>
       <c r="H145" t="str">
-        <v>Lauren Spencer Smith</v>
+        <v>Babyfxce E</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/lauren-spencer-smith/1462708784</v>
+        <v>https://music.apple.com/us/artist/babyfxce-e/1573432856</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/natural-disaster/1871263207</v>
+        <v>https://music.apple.com/us/album/trackhawk/1860991661</v>
       </c>
       <c r="L145" t="str">
-        <v>Natural Disaster - Lauren Spencer Smith</v>
+        <v>Trackhawk - Babyfxce E</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Prettier</v>
+        <v>Wheel Man</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/prettier/1869745409</v>
+        <v>https://music.apple.com/us/song/wheel-man/1872178895</v>
       </c>
       <c r="D146" t="str">
         <v>2026-02-02</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>Prettier - Single</v>
+        <v>Xavier</v>
       </c>
       <c r="G146" t="str">
-        <v>2:34</v>
+        <v>3:05</v>
       </c>
       <c r="H146" t="str">
-        <v>Grace VanderWaal</v>
+        <v>xaviersobased</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/grace-vanderwaal/1175539534</v>
+        <v>https://music.apple.com/us/artist/xaviersobased/1540848340</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/prettier/1869745403</v>
+        <v>https://music.apple.com/us/album/wheel-man/1872178596</v>
       </c>
       <c r="L146" t="str">
-        <v>Prettier - Grace VanderWaal</v>
+        <v>Wheel Man - xaviersobased</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Shotta Flow 8</v>
+        <v>Natural Disaster</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/shotta-flow-8/1872760524</v>
+        <v>https://music.apple.com/us/song/natural-disaster/1871263211</v>
       </c>
       <c r="D147" t="str">
         <v>2026-02-02</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Shotta Flow 8 - Single</v>
+        <v>Natural Disaster - Single</v>
       </c>
       <c r="G147" t="str">
-        <v>3:21</v>
+        <v>3:02</v>
       </c>
       <c r="H147" t="str">
-        <v>NLE Choppa</v>
+        <v>Lauren Spencer Smith</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/nle-choppa/1449052753</v>
+        <v>https://music.apple.com/us/artist/lauren-spencer-smith/1462708784</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/shotta-flow-8/1872760520</v>
+        <v>https://music.apple.com/us/album/natural-disaster/1871263207</v>
       </c>
       <c r="L147" t="str">
-        <v>Shotta Flow 8 - NLE Choppa</v>
+        <v>Natural Disaster - Lauren Spencer Smith</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Die To Fall</v>
+        <v>Prettier</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/die-to-fall/1866902681</v>
+        <v>https://music.apple.com/us/song/prettier/1869745409</v>
       </c>
       <c r="D148" t="str">
         <v>2026-02-02</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Die To Fall - Single</v>
+        <v>Prettier - Single</v>
       </c>
       <c r="G148" t="str">
-        <v>3:20</v>
+        <v>2:34</v>
       </c>
       <c r="H148" t="str">
-        <v>The Maine</v>
+        <v>Grace VanderWaal</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
+        <v>https://music.apple.com/us/artist/grace-vanderwaal/1175539534</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/die-to-fall/1866902679</v>
+        <v>https://music.apple.com/us/album/prettier/1869745403</v>
       </c>
       <c r="L148" t="str">
-        <v>Die To Fall - The Maine</v>
+        <v>Prettier - Grace VanderWaal</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>The Cruel Angel's Thesis (Neon Genesis Evangelion)</v>
+        <v>Shotta Flow 8</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/the-cruel-angels-thesis-neon-genesis-evangelion/1864932139</v>
+        <v>https://music.apple.com/us/song/shotta-flow-8/1872760524</v>
       </c>
       <c r="D149" t="str">
         <v>2026-02-02</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>The Cruel Angel's Thesis (Neon Genesis Evangelion) - Single</v>
+        <v>Shotta Flow 8 - Single</v>
       </c>
       <c r="G149" t="str">
-        <v>2:58</v>
+        <v>3:21</v>
       </c>
       <c r="H149" t="str">
-        <v>Steve Aoki</v>
+        <v>NLE Choppa</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/steve-aoki/271066694</v>
+        <v>https://music.apple.com/us/artist/nle-choppa/1449052753</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/the-cruel-angels-thesis-neon-genesis-evangelion/1864932135</v>
+        <v>https://music.apple.com/us/album/shotta-flow-8/1872760520</v>
       </c>
       <c r="L149" t="str">
-        <v>The Cruel Angel's Thesis (Neon Genesis Evangelion) - Steve Aoki</v>
+        <v>Shotta Flow 8 - NLE Choppa</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Slow Burn</v>
+        <v>Die To Fall</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/slow-burn/1851033862</v>
+        <v>https://music.apple.com/us/song/die-to-fall/1866902681</v>
       </c>
       <c r="D150" t="str">
         <v>2026-02-02</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>Still There’s a Glow</v>
+        <v>Die To Fall - Single</v>
       </c>
       <c r="G150" t="str">
-        <v>2:14</v>
+        <v>3:20</v>
       </c>
       <c r="H150" t="str">
-        <v>Sweet Pill</v>
+        <v>The Maine</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/sweet-pill/1459476044</v>
+        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/slow-burn/1851033857</v>
+        <v>https://music.apple.com/us/album/die-to-fall/1866902679</v>
       </c>
       <c r="L150" t="str">
-        <v>Slow Burn - Sweet Pill</v>
+        <v>Die To Fall - The Maine</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Too Late</v>
+        <v>The Cruel Angel's Thesis (Neon Genesis Evangelion)</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/too-late/1857999860</v>
+        <v>https://music.apple.com/us/song/the-cruel-angels-thesis-neon-genesis-evangelion/1864932139</v>
       </c>
       <c r="D151" t="str">
         <v>2026-02-02</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>Evergreen</v>
+        <v>The Cruel Angel's Thesis (Neon Genesis Evangelion) - Single</v>
       </c>
       <c r="G151" t="str">
-        <v>2:56</v>
+        <v>2:58</v>
       </c>
       <c r="H151" t="str">
-        <v>Hunter Hayes</v>
+        <v>Steve Aoki</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/hunter-hayes/429231434</v>
+        <v>https://music.apple.com/us/artist/steve-aoki/271066694</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/too-late/1857999850</v>
+        <v>https://music.apple.com/us/album/the-cruel-angels-thesis-neon-genesis-evangelion/1864932135</v>
       </c>
       <c r="L151" t="str">
-        <v>Too Late - Hunter Hayes</v>
+        <v>The Cruel Angel's Thesis (Neon Genesis Evangelion) - Steve Aoki</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Mono (feat. skaiwater)</v>
+        <v>Slow Burn</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/mono-feat-skaiwater/1869130804</v>
+        <v>https://music.apple.com/us/song/slow-burn/1851033862</v>
       </c>
       <c r="D152" t="str">
         <v>2026-02-02</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>Mono (feat. skaiwater) - Single</v>
+        <v>Still There’s a Glow</v>
       </c>
       <c r="G152" t="str">
-        <v>2:50</v>
+        <v>2:14</v>
       </c>
       <c r="H152" t="str">
-        <v>i-dle</v>
+        <v>Sweet Pill</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/i-dle/1378887586</v>
+        <v>https://music.apple.com/us/artist/sweet-pill/1459476044</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/mono-feat-skaiwater/1869130801</v>
+        <v>https://music.apple.com/us/album/slow-burn/1851033857</v>
       </c>
       <c r="L152" t="str">
-        <v>Mono (feat. skaiwater) - i-dle</v>
+        <v>Slow Burn - Sweet Pill</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Thank You Is Enough</v>
+        <v>Too Late</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/thank-you-is-enough/1870679042</v>
+        <v>https://music.apple.com/us/song/too-late/1857999860</v>
       </c>
       <c r="D153" t="str">
         <v>2026-02-02</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Yo Gabba GabbaLand! (Season 2) [Apple TV+ Original Series Soundtrack]</v>
+        <v>Evergreen</v>
       </c>
       <c r="G153" t="str">
-        <v>1:55</v>
+        <v>2:56</v>
       </c>
       <c r="H153" t="str">
-        <v>Yo Gabba Gabba</v>
+        <v>Hunter Hayes</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/yo-gabba-gabba/433108373</v>
+        <v>https://music.apple.com/us/artist/hunter-hayes/429231434</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/thank-you-is-enough/1870678950</v>
+        <v>https://music.apple.com/us/album/too-late/1857999850</v>
       </c>
       <c r="L153" t="str">
-        <v>Thank You Is Enough - Yo Gabba Gabba</v>
+        <v>Too Late - Hunter Hayes</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>RIDIN</v>
+        <v>Mono (feat. skaiwater)</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/ridin/1869786726</v>
+        <v>https://music.apple.com/us/song/mono-feat-skaiwater/1869130804</v>
       </c>
       <c r="D154" t="str">
         <v>2026-02-02</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>RIDIN - Single</v>
+        <v>Mono (feat. skaiwater) - Single</v>
       </c>
       <c r="G154" t="str">
-        <v>2:00</v>
+        <v>2:50</v>
       </c>
       <c r="H154" t="str">
-        <v>Tokischa</v>
+        <v>i-dle</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/tokischa/1414103446</v>
+        <v>https://music.apple.com/us/artist/i-dle/1378887586</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/ridin/1869786725</v>
+        <v>https://music.apple.com/us/album/mono-feat-skaiwater/1869130801</v>
       </c>
       <c r="L154" t="str">
-        <v>RIDIN - Tokischa</v>
+        <v>Mono (feat. skaiwater) - i-dle</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>POSSESSION</v>
+        <v>Thank You Is Enough</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/possession/1872536200</v>
+        <v>https://music.apple.com/us/song/thank-you-is-enough/1870679042</v>
       </c>
       <c r="D155" t="str">
         <v>2026-02-02</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>POSSESSION - Single</v>
+        <v>Yo Gabba GabbaLand! (Season 2) [Apple TV+ Original Series Soundtrack]</v>
       </c>
       <c r="G155" t="str">
-        <v>3:07</v>
+        <v>1:55</v>
       </c>
       <c r="H155" t="str">
-        <v>Melanie Martinez</v>
+        <v>Yo Gabba Gabba</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/melanie-martinez/993014053</v>
+        <v>https://music.apple.com/us/artist/yo-gabba-gabba/433108373</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/possession/1872536199</v>
+        <v>https://music.apple.com/us/album/thank-you-is-enough/1870678950</v>
       </c>
       <c r="L155" t="str">
-        <v>POSSESSION - Melanie Martinez</v>
+        <v>Thank You Is Enough - Yo Gabba Gabba</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Poema</v>
+        <v>RIDIN</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/poema/1872723644</v>
+        <v>https://music.apple.com/us/song/ridin/1869786726</v>
       </c>
       <c r="D156" t="str">
         <v>2026-02-02</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>Poema - Single</v>
+        <v>RIDIN - Single</v>
       </c>
       <c r="G156" t="str">
-        <v>3:14</v>
+        <v>2:00</v>
       </c>
       <c r="H156" t="str">
-        <v>Óscar Maydon</v>
+        <v>Tokischa</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/%C3%B3scar-maydon/1524147696</v>
+        <v>https://music.apple.com/us/artist/tokischa/1414103446</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/poema/1872723468</v>
+        <v>https://music.apple.com/us/album/ridin/1869786725</v>
       </c>
       <c r="L156" t="str">
-        <v>Poema - Óscar Maydon</v>
+        <v>RIDIN - Tokischa</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Live Without</v>
+        <v>POSSESSION</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/live-without/1862777625</v>
+        <v>https://music.apple.com/us/song/possession/1872536200</v>
       </c>
       <c r="D157" t="str">
         <v>2026-02-02</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>WORRIED SICK (Deluxe Edition)</v>
+        <v>POSSESSION - Single</v>
       </c>
       <c r="G157" t="str">
-        <v>2:55</v>
+        <v>3:07</v>
       </c>
       <c r="H157" t="str">
-        <v>Meet Me @ The Altar</v>
+        <v>Melanie Martinez</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/meet-me-the-altar/1109900880</v>
+        <v>https://music.apple.com/us/artist/melanie-martinez/993014053</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/live-without/1862777608</v>
+        <v>https://music.apple.com/us/album/possession/1872536199</v>
       </c>
       <c r="L157" t="str">
-        <v>Live Without - Meet Me @ The Altar</v>
+        <v>POSSESSION - Melanie Martinez</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>FANÁTICO</v>
+        <v>Poema</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/fan%C3%A1tico/1871611852</v>
+        <v>https://music.apple.com/us/song/poema/1872723644</v>
       </c>
       <c r="D158" t="str">
         <v>2026-02-02</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>FANÁTICO - Single</v>
+        <v>Poema - Single</v>
       </c>
       <c r="G158" t="str">
-        <v>3:55</v>
+        <v>3:14</v>
       </c>
       <c r="H158" t="str">
-        <v>Blessd</v>
+        <v>Óscar Maydon</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/blessd/1481245915</v>
+        <v>https://music.apple.com/us/artist/%C3%B3scar-maydon/1524147696</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/fan%C3%A1tico/1871611851</v>
+        <v>https://music.apple.com/us/album/poema/1872723468</v>
       </c>
       <c r="L158" t="str">
-        <v>FANÁTICO - Blessd</v>
+        <v>Poema - Óscar Maydon</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Frozen Lake</v>
+        <v>Live Without</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/frozen-lake/1867287070</v>
+        <v>https://music.apple.com/us/song/live-without/1862777625</v>
       </c>
       <c r="D159" t="str">
         <v>2026-02-02</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>Frozen Lake - Single</v>
+        <v>WORRIED SICK (Deluxe Edition)</v>
       </c>
       <c r="G159" t="str">
-        <v>3:29</v>
+        <v>2:55</v>
       </c>
       <c r="H159" t="str">
-        <v>VOILÀ</v>
+        <v>Meet Me @ The Altar</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/voil%C3%A0/1333272109</v>
+        <v>https://music.apple.com/us/artist/meet-me-the-altar/1109900880</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/frozen-lake/1867287069</v>
+        <v>https://music.apple.com/us/album/live-without/1862777608</v>
       </c>
       <c r="L159" t="str">
-        <v>Frozen Lake - VOILÀ</v>
+        <v>Live Without - Meet Me @ The Altar</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Fine Shyt (EB Remix) [feat. Eric Bellinger]</v>
+        <v>FANÁTICO</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/fine-shyt-eb-remix-feat-eric-bellinger/1870964385</v>
+        <v>https://music.apple.com/us/song/fan%C3%A1tico/1871611852</v>
       </c>
       <c r="D160" t="str">
         <v>2026-02-02</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>Fine Shyt (EB Remix) [feat. Eric Bellinger] - Single</v>
+        <v>FANÁTICO - Single</v>
       </c>
       <c r="G160" t="str">
-        <v>2:45</v>
+        <v>3:55</v>
       </c>
       <c r="H160" t="str">
-        <v>VEDO</v>
+        <v>Blessd</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/vedo/267769510</v>
+        <v>https://music.apple.com/us/artist/blessd/1481245915</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/fine-shyt-eb-remix-feat-eric-bellinger/1870964384</v>
+        <v>https://music.apple.com/us/album/fan%C3%A1tico/1871611851</v>
       </c>
       <c r="L160" t="str">
-        <v>Fine Shyt (EB Remix) [feat. Eric Bellinger] - VEDO</v>
+        <v>FANÁTICO - Blessd</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Hell Yeah (Feat. Waxmaster)</v>
+        <v>Frozen Lake</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/hell-yeah-feat-waxmaster/1866602820</v>
+        <v>https://music.apple.com/us/song/frozen-lake/1867287070</v>
       </c>
       <c r="D161" t="str">
         <v>2026-02-02</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>Hell Yeah (Feat. Waxmaster) - Single</v>
+        <v>Frozen Lake - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>3:32</v>
+        <v>3:29</v>
       </c>
       <c r="H161" t="str">
-        <v>Chris Lorenzo</v>
+        <v>VOILÀ</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/chris-lorenzo/621431022</v>
+        <v>https://music.apple.com/us/artist/voil%C3%A0/1333272109</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/hell-yeah-feat-waxmaster/1866602819</v>
+        <v>https://music.apple.com/us/album/frozen-lake/1867287069</v>
       </c>
       <c r="L161" t="str">
-        <v>Hell Yeah (Feat. Waxmaster) - Chris Lorenzo</v>
+        <v>Frozen Lake - VOILÀ</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>It’s Like That</v>
+        <v>Fine Shyt (EB Remix) [feat. Eric Bellinger]</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/its-like-that/1858689757</v>
+        <v>https://music.apple.com/us/song/fine-shyt-eb-remix-feat-eric-bellinger/1870964385</v>
       </c>
       <c r="D162" t="str">
         <v>2026-02-02</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>A Pound of Feathers</v>
+        <v>Fine Shyt (EB Remix) [feat. Eric Bellinger] - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>3:20</v>
+        <v>2:45</v>
       </c>
       <c r="H162" t="str">
-        <v>The Black Crowes</v>
+        <v>VEDO</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/the-black-crowes/2969371</v>
+        <v>https://music.apple.com/us/artist/vedo/267769510</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/its-like-that/1858689485</v>
+        <v>https://music.apple.com/us/album/fine-shyt-eb-remix-feat-eric-bellinger/1870964384</v>
       </c>
       <c r="L162" t="str">
-        <v>It’s Like That - The Black Crowes</v>
+        <v>Fine Shyt (EB Remix) [feat. Eric Bellinger] - VEDO</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>A.S.A.P.</v>
+        <v>Hell Yeah (Feat. Waxmaster)</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/a-s-a-p/1833414737</v>
+        <v>https://music.apple.com/us/song/hell-yeah-feat-waxmaster/1866602820</v>
       </c>
       <c r="D163" t="str">
         <v>2026-02-02</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>A.S.A.P. - Single</v>
+        <v>Hell Yeah (Feat. Waxmaster) - Single</v>
       </c>
       <c r="G163" t="str">
-        <v>2:48</v>
+        <v>3:32</v>
       </c>
       <c r="H163" t="str">
-        <v>Mýa</v>
+        <v>Chris Lorenzo</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/m%C3%BDa/108751</v>
+        <v>https://music.apple.com/us/artist/chris-lorenzo/621431022</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/a-s-a-p/1833414736</v>
+        <v>https://music.apple.com/us/album/hell-yeah-feat-waxmaster/1866602819</v>
       </c>
       <c r="L163" t="str">
-        <v>A.S.A.P. - Mýa</v>
+        <v>Hell Yeah (Feat. Waxmaster) - Chris Lorenzo</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Once I Say</v>
+        <v>It’s Like That</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/once-i-say/1867855025</v>
+        <v>https://music.apple.com/us/song/its-like-that/1858689757</v>
       </c>
       <c r="D164" t="str">
         <v>2026-02-02</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>PASSION</v>
+        <v>A Pound of Feathers</v>
       </c>
       <c r="G164" t="str">
-        <v>3:21</v>
+        <v>3:20</v>
       </c>
       <c r="H164" t="str">
-        <v>Terrace Martin</v>
+        <v>The Black Crowes</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/terrace-martin/27522754</v>
+        <v>https://music.apple.com/us/artist/the-black-crowes/2969371</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/once-i-say/1867854756</v>
+        <v>https://music.apple.com/us/album/its-like-that/1858689485</v>
       </c>
       <c r="L164" t="str">
-        <v>Once I Say - Terrace Martin</v>
+        <v>It’s Like That - The Black Crowes</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>believer</v>
+        <v>A.S.A.P.</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/believer/1862797080</v>
+        <v>https://music.apple.com/us/song/a-s-a-p/1833414737</v>
       </c>
       <c r="D165" t="str">
         <v>2026-02-02</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>believer - Single</v>
+        <v>A.S.A.P. - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>2:57</v>
+        <v>2:48</v>
       </c>
       <c r="H165" t="str">
-        <v>Yuna</v>
+        <v>Mýa</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/yuna/423966062</v>
+        <v>https://music.apple.com/us/artist/m%C3%BDa/108751</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/believer/1862796978</v>
+        <v>https://music.apple.com/us/album/a-s-a-p/1833414736</v>
       </c>
       <c r="L165" t="str">
-        <v>believer - Yuna</v>
+        <v>A.S.A.P. - Mýa</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>I Envy The Wind</v>
+        <v>Once I Say</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/i-envy-the-wind/1863202477</v>
+        <v>https://music.apple.com/us/song/once-i-say/1867855025</v>
       </c>
       <c r="D166" t="str">
         <v>2026-02-02</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>I Envy The Wind - Single</v>
+        <v>PASSION</v>
       </c>
       <c r="G166" t="str">
-        <v>3:51</v>
+        <v>3:21</v>
       </c>
       <c r="H166" t="str">
-        <v>Molly Parden</v>
+        <v>Terrace Martin</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/molly-parden/374789677</v>
+        <v>https://music.apple.com/us/artist/terrace-martin/27522754</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/i-envy-the-wind/1863202476</v>
+        <v>https://music.apple.com/us/album/once-i-say/1867854756</v>
       </c>
       <c r="L166" t="str">
-        <v>I Envy The Wind - Molly Parden</v>
+        <v>Once I Say - Terrace Martin</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>The Alchemist</v>
+        <v>believer</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/the-alchemist/1831827347</v>
+        <v>https://music.apple.com/us/song/believer/1862797080</v>
       </c>
       <c r="D167" t="str">
         <v>2026-02-02</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>The Alchemist</v>
+        <v>believer - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>3:13</v>
+        <v>2:57</v>
       </c>
       <c r="H167" t="str">
-        <v>Bre Kennedy</v>
+        <v>Yuna</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/bre-kennedy/1242283415</v>
+        <v>https://music.apple.com/us/artist/yuna/423966062</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/the-alchemist/1831827332</v>
+        <v>https://music.apple.com/us/album/believer/1862796978</v>
       </c>
       <c r="L167" t="str">
-        <v>The Alchemist - Bre Kennedy</v>
+        <v>believer - Yuna</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Daysa</v>
+        <v>I Envy The Wind</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/daysa/1861575845</v>
+        <v>https://music.apple.com/us/song/i-envy-the-wind/1863202477</v>
       </c>
       <c r="D168" t="str">
         <v>2026-02-02</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Daysa - Single</v>
+        <v>I Envy The Wind - Single</v>
       </c>
       <c r="G168" t="str">
-        <v>4:36</v>
+        <v>3:51</v>
       </c>
       <c r="H168" t="str">
-        <v>⌭ IceMorph ⌬</v>
+        <v>Molly Parden</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/icemorph/1733236411</v>
+        <v>https://music.apple.com/us/artist/molly-parden/374789677</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/daysa/1861575844</v>
+        <v>https://music.apple.com/us/album/i-envy-the-wind/1863202476</v>
       </c>
       <c r="L168" t="str">
-        <v>Daysa - ⌭ IceMorph ⌬</v>
+        <v>I Envy The Wind - Molly Parden</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Fabulous</v>
+        <v>The Alchemist</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/fabulous/1862804005</v>
+        <v>https://music.apple.com/us/song/the-alchemist/1831827347</v>
       </c>
       <c r="D169" t="str">
         <v>2026-02-02</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Fabulous - Single</v>
+        <v>The Alchemist</v>
       </c>
       <c r="G169" t="str">
-        <v>2:33</v>
+        <v>3:13</v>
       </c>
       <c r="H169" t="str">
-        <v>MEEK</v>
+        <v>Bre Kennedy</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/meek/1784432868</v>
+        <v>https://music.apple.com/us/artist/bre-kennedy/1242283415</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/fabulous/1862804004</v>
+        <v>https://music.apple.com/us/album/the-alchemist/1831827332</v>
       </c>
       <c r="L169" t="str">
-        <v>Fabulous - MEEK</v>
+        <v>The Alchemist - Bre Kennedy</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Me Asusta Amar Tanto la Soledad</v>
+        <v>Daysa</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/me-asusta-amar-tanto-la-soledad/1866982109</v>
+        <v>https://music.apple.com/us/song/daysa/1861575845</v>
       </c>
       <c r="D170" t="str">
         <v>2026-02-02</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Me Asusta Amar Tanto la Soledad - Single</v>
+        <v>Daysa - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>3:22</v>
+        <v>4:36</v>
       </c>
       <c r="H170" t="str">
-        <v>RUBIO</v>
+        <v>⌭ IceMorph ⌬</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/rubio/34747724</v>
+        <v>https://music.apple.com/us/artist/icemorph/1733236411</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/me-asusta-amar-tanto-la-soledad/1866981907</v>
+        <v>https://music.apple.com/us/album/daysa/1861575844</v>
       </c>
       <c r="L170" t="str">
-        <v>Me Asusta Amar Tanto la Soledad - RUBIO</v>
+        <v>Daysa - ⌭ IceMorph ⌬</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>brainchem</v>
+        <v>Fabulous</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/brainchem/1870656942</v>
+        <v>https://music.apple.com/us/song/fabulous/1862804005</v>
       </c>
       <c r="D171" t="str">
         <v>2026-02-02</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>brainchem - Single</v>
+        <v>Fabulous - Single</v>
       </c>
       <c r="G171" t="str">
-        <v>2:28</v>
+        <v>2:33</v>
       </c>
       <c r="H171" t="str">
-        <v>EMJAY</v>
+        <v>MEEK</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/emjay/1517993423</v>
+        <v>https://music.apple.com/us/artist/meek/1784432868</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/brainchem/1870656608</v>
+        <v>https://music.apple.com/us/album/fabulous/1862804004</v>
       </c>
       <c r="L171" t="str">
-        <v>brainchem - EMJAY</v>
+        <v>Fabulous - MEEK</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Boyfriend In Yo Brain (Notice Me)</v>
+        <v>Me Asusta Amar Tanto la Soledad</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/boyfriend-in-yo-brain-notice-me/1871675026</v>
+        <v>https://music.apple.com/us/song/me-asusta-amar-tanto-la-soledad/1866982109</v>
       </c>
       <c r="D172" t="str">
         <v>2026-02-02</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>With No Due Respect</v>
+        <v>Me Asusta Amar Tanto la Soledad - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>2:48</v>
+        <v>3:22</v>
       </c>
       <c r="H172" t="str">
-        <v>Foggieraw</v>
+        <v>RUBIO</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/foggieraw/1152021457</v>
+        <v>https://music.apple.com/us/artist/rubio/34747724</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/boyfriend-in-yo-brain-notice-me/1871675010</v>
+        <v>https://music.apple.com/us/album/me-asusta-amar-tanto-la-soledad/1866981907</v>
       </c>
       <c r="L172" t="str">
-        <v>Boyfriend In Yo Brain (Notice Me) - Foggieraw</v>
+        <v>Me Asusta Amar Tanto la Soledad - RUBIO</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Giants</v>
+        <v>brainchem</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/giants/1869154957</v>
+        <v>https://music.apple.com/us/song/brainchem/1870656942</v>
       </c>
       <c r="D173" t="str">
         <v>2026-02-02</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Giants - Single</v>
+        <v>brainchem - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>3:12</v>
+        <v>2:28</v>
       </c>
       <c r="H173" t="str">
-        <v>Picture This</v>
+        <v>EMJAY</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/picture-this/1194282721</v>
+        <v>https://music.apple.com/us/artist/emjay/1517993423</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/giants/1869154821</v>
+        <v>https://music.apple.com/us/album/brainchem/1870656608</v>
       </c>
       <c r="L173" t="str">
-        <v>Giants - Picture This</v>
+        <v>brainchem - EMJAY</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Scooby</v>
+        <v>Boyfriend In Yo Brain (Notice Me)</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/scooby/1872510752</v>
+        <v>https://music.apple.com/us/song/boyfriend-in-yo-brain-notice-me/1871675026</v>
       </c>
       <c r="D174" t="str">
         <v>2026-02-02</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>Scooby - Single</v>
+        <v>With No Due Respect</v>
       </c>
       <c r="G174" t="str">
-        <v>3:41</v>
+        <v>2:48</v>
       </c>
       <c r="H174" t="str">
-        <v>corook</v>
+        <v>Foggieraw</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/corook/1514463762</v>
+        <v>https://music.apple.com/us/artist/foggieraw/1152021457</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/scooby/1872510751</v>
+        <v>https://music.apple.com/us/album/boyfriend-in-yo-brain-notice-me/1871675010</v>
       </c>
       <c r="L174" t="str">
-        <v>Scooby - corook</v>
+        <v>Boyfriend In Yo Brain (Notice Me) - Foggieraw</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>La Racha</v>
+        <v>Giants</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/la-racha/1868757762</v>
+        <v>https://music.apple.com/us/song/giants/1869154957</v>
       </c>
       <c r="D175" t="str">
         <v>2026-02-02</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>La Racha - Single</v>
+        <v>Giants - Single</v>
       </c>
       <c r="G175" t="str">
-        <v>2:48</v>
+        <v>3:12</v>
       </c>
       <c r="H175" t="str">
-        <v>Hermanos Espinoza</v>
+        <v>Picture This</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/hermanos-espinoza/1613044599</v>
+        <v>https://music.apple.com/us/artist/picture-this/1194282721</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/la-racha/1868757747</v>
+        <v>https://music.apple.com/us/album/giants/1869154821</v>
       </c>
       <c r="L175" t="str">
-        <v>La Racha - Hermanos Espinoza</v>
+        <v>Giants - Picture This</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>So Am I</v>
+        <v>Scooby</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/so-am-i/1867012209</v>
+        <v>https://music.apple.com/us/song/scooby/1872510752</v>
       </c>
       <c r="D176" t="str">
         <v>2026-02-02</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Tell Me How You Really Feel</v>
+        <v>Scooby - Single</v>
       </c>
       <c r="G176" t="str">
-        <v>2:50</v>
+        <v>3:41</v>
       </c>
       <c r="H176" t="str">
-        <v>Katelyn Tarver</v>
+        <v>corook</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/katelyn-tarver/2356378</v>
+        <v>https://music.apple.com/us/artist/corook/1514463762</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/so-am-i/1867012005</v>
+        <v>https://music.apple.com/us/album/scooby/1872510751</v>
       </c>
       <c r="L176" t="str">
-        <v>So Am I - Katelyn Tarver</v>
+        <v>Scooby - corook</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>best thing</v>
+        <v>La Racha</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/best-thing/1860673616</v>
+        <v>https://music.apple.com/us/song/la-racha/1868757762</v>
       </c>
       <c r="D177" t="str">
         <v>2026-02-02</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>best thing - Single</v>
+        <v>La Racha - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>4:27</v>
+        <v>2:48</v>
       </c>
       <c r="H177" t="str">
-        <v>WRABEL</v>
+        <v>Hermanos Espinoza</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/wrabel/435072161</v>
+        <v>https://music.apple.com/us/artist/hermanos-espinoza/1613044599</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/best-thing/1860673615</v>
+        <v>https://music.apple.com/us/album/la-racha/1868757747</v>
       </c>
       <c r="L177" t="str">
-        <v>best thing - WRABEL</v>
+        <v>La Racha - Hermanos Espinoza</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Count It Back</v>
+        <v>So Am I</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/count-it-back/1855219865</v>
+        <v>https://music.apple.com/us/song/so-am-i/1867012209</v>
       </c>
       <c r="D178" t="str">
         <v>2026-02-02</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Magic Boy</v>
+        <v>Tell Me How You Really Feel</v>
       </c>
       <c r="G178" t="str">
-        <v>2:52</v>
+        <v>2:50</v>
       </c>
       <c r="H178" t="str">
-        <v>Bartees Strange</v>
+        <v>Katelyn Tarver</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/bartees-strange/1450776625</v>
+        <v>https://music.apple.com/us/artist/katelyn-tarver/2356378</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/count-it-back/1855219618</v>
+        <v>https://music.apple.com/us/album/so-am-i/1867012005</v>
       </c>
       <c r="L178" t="str">
-        <v>Count It Back - Bartees Strange</v>
+        <v>So Am I - Katelyn Tarver</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Good Girl</v>
+        <v>best thing</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/good-girl/1862640697</v>
+        <v>https://music.apple.com/us/song/best-thing/1860673616</v>
       </c>
       <c r="D179" t="str">
         <v>2026-02-02</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Good Girl - Single</v>
+        <v>best thing - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>4:23</v>
+        <v>4:27</v>
       </c>
       <c r="H179" t="str">
-        <v>Paris Paloma</v>
+        <v>WRABEL</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/paris-paloma/1530898376</v>
+        <v>https://music.apple.com/us/artist/wrabel/435072161</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/good-girl/1862640694</v>
+        <v>https://music.apple.com/us/album/best-thing/1860673615</v>
       </c>
       <c r="L179" t="str">
-        <v>Good Girl - Paris Paloma</v>
+        <v>best thing - WRABEL</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>MY REVIVAL</v>
+        <v>Count It Back</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/my-revival/1869465104</v>
+        <v>https://music.apple.com/us/song/count-it-back/1855219865</v>
       </c>
       <c r="D180" t="str">
         <v>2026-02-02</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>HEARTLAND (Deluxe Version)</v>
+        <v>Magic Boy</v>
       </c>
       <c r="G180" t="str">
-        <v>3:34</v>
+        <v>2:52</v>
       </c>
       <c r="H180" t="str">
-        <v>MORGXN</v>
+        <v>Bartees Strange</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/morgxn/1116360149</v>
+        <v>https://music.apple.com/us/artist/bartees-strange/1450776625</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/my-revival/1869464853</v>
+        <v>https://music.apple.com/us/album/count-it-back/1855219618</v>
       </c>
       <c r="L180" t="str">
-        <v>MY REVIVAL - MORGXN</v>
+        <v>Count It Back - Bartees Strange</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Run My Way</v>
+        <v>Good Girl</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/run-my-way/1860964996</v>
+        <v>https://music.apple.com/us/song/good-girl/1862640697</v>
       </c>
       <c r="D181" t="str">
         <v>2026-02-02</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Run My Way - Single</v>
+        <v>Good Girl - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>2:44</v>
+        <v>4:23</v>
       </c>
       <c r="H181" t="str">
-        <v>December 10</v>
+        <v>Paris Paloma</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/december-10/1414032285</v>
+        <v>https://music.apple.com/us/artist/paris-paloma/1530898376</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/run-my-way/1860964992</v>
+        <v>https://music.apple.com/us/album/good-girl/1862640694</v>
       </c>
       <c r="L181" t="str">
-        <v>Run My Way - December 10</v>
+        <v>Good Girl - Paris Paloma</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Cold Night</v>
+        <v>MY REVIVAL</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/cold-night/1867687787</v>
+        <v>https://music.apple.com/us/song/my-revival/1869465104</v>
       </c>
       <c r="D182" t="str">
         <v>2026-02-02</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Cold Night - Single</v>
+        <v>HEARTLAND (Deluxe Version)</v>
       </c>
       <c r="G182" t="str">
-        <v>3:12</v>
+        <v>3:34</v>
       </c>
       <c r="H182" t="str">
-        <v>HANA</v>
+        <v>MORGXN</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/hana/1792783458</v>
+        <v>https://music.apple.com/us/artist/morgxn/1116360149</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/cold-night/1867687784</v>
+        <v>https://music.apple.com/us/album/my-revival/1869464853</v>
       </c>
       <c r="L182" t="str">
-        <v>Cold Night - HANA</v>
+        <v>MY REVIVAL - MORGXN</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Away With The Fairies</v>
+        <v>Run My Way</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/away-with-the-fairies/1870603474</v>
+        <v>https://music.apple.com/us/song/run-my-way/1860964996</v>
       </c>
       <c r="D183" t="str">
         <v>2026-02-02</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Away With The Fairies - Single</v>
+        <v>Run My Way - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>2:28</v>
+        <v>2:44</v>
       </c>
       <c r="H183" t="str">
-        <v>LUNA</v>
+        <v>December 10</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/luna/1439101807</v>
+        <v>https://music.apple.com/us/artist/december-10/1414032285</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/away-with-the-fairies/1870603470</v>
+        <v>https://music.apple.com/us/album/run-my-way/1860964992</v>
       </c>
       <c r="L183" t="str">
-        <v>Away With The Fairies - LUNA</v>
+        <v>Run My Way - December 10</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Fragile</v>
+        <v>Cold Night</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/fragile/1866957569</v>
+        <v>https://music.apple.com/us/song/cold-night/1867687787</v>
       </c>
       <c r="D184" t="str">
         <v>2026-02-02</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>Fragile - Single</v>
+        <v>Cold Night - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>3:10</v>
+        <v>3:12</v>
       </c>
       <c r="H184" t="str">
-        <v>Anajah</v>
+        <v>HANA</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/anajah/1355166756</v>
+        <v>https://music.apple.com/us/artist/hana/1792783458</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/fragile/1866957565</v>
+        <v>https://music.apple.com/us/album/cold-night/1867687784</v>
       </c>
       <c r="L184" t="str">
-        <v>Fragile - Anajah</v>
+        <v>Cold Night - HANA</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Slow Dancin'</v>
+        <v>Away With The Fairies</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/slow-dancin/1871537173</v>
+        <v>https://music.apple.com/us/song/away-with-the-fairies/1870603474</v>
       </c>
       <c r="D185" t="str">
         <v>2026-02-02</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>Slow Dancin' - Single</v>
+        <v>Away With The Fairies - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>2:04</v>
+        <v>2:28</v>
       </c>
       <c r="H185" t="str">
-        <v>STELLA LEFTY</v>
+        <v>LUNA</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/stella-lefty/1641742186</v>
+        <v>https://music.apple.com/us/artist/luna/1439101807</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/slow-dancin/1871537170</v>
+        <v>https://music.apple.com/us/album/away-with-the-fairies/1870603470</v>
       </c>
       <c r="L185" t="str">
-        <v>Slow Dancin' - STELLA LEFTY</v>
+        <v>Away With The Fairies - LUNA</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Never Kissed a Cowboy</v>
+        <v>Fragile</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/never-kissed-a-cowboy/1866744530</v>
+        <v>https://music.apple.com/us/song/fragile/1866957569</v>
       </c>
       <c r="D186" t="str">
         <v>2026-02-02</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Never Kissed a Cowboy - Single</v>
+        <v>Fragile - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>3:04</v>
+        <v>3:10</v>
       </c>
       <c r="H186" t="str">
-        <v>Lily Meola</v>
+        <v>Anajah</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/lily-meola/678241726</v>
+        <v>https://music.apple.com/us/artist/anajah/1355166756</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/never-kissed-a-cowboy/1866744528</v>
+        <v>https://music.apple.com/us/album/fragile/1866957565</v>
       </c>
       <c r="L186" t="str">
-        <v>Never Kissed a Cowboy - Lily Meola</v>
+        <v>Fragile - Anajah</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>More Of What Matters</v>
+        <v>Slow Dancin'</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/more-of-what-matters/1871592720</v>
+        <v>https://music.apple.com/us/song/slow-dancin/1871537173</v>
       </c>
       <c r="D187" t="str">
         <v>2026-02-02</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>More Of What Matters - Single</v>
+        <v>Slow Dancin' - Single</v>
       </c>
       <c r="G187" t="str">
-        <v>3:41</v>
+        <v>2:04</v>
       </c>
       <c r="H187" t="str">
-        <v>Jamey Johnson</v>
+        <v>STELLA LEFTY</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/jamey-johnson/81030634</v>
+        <v>https://music.apple.com/us/artist/stella-lefty/1641742186</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/more-of-what-matters/1871592717</v>
+        <v>https://music.apple.com/us/album/slow-dancin/1871537170</v>
       </c>
       <c r="L187" t="str">
-        <v>More Of What Matters - Jamey Johnson</v>
+        <v>Slow Dancin' - STELLA LEFTY</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Is This The Real You</v>
+        <v>Never Kissed a Cowboy</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/is-this-the-real-you/1869323368</v>
+        <v>https://music.apple.com/us/song/never-kissed-a-cowboy/1866744530</v>
       </c>
       <c r="D188" t="str">
         <v>2026-02-02</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>ONE</v>
+        <v>Never Kissed a Cowboy - Single</v>
       </c>
       <c r="G188" t="str">
-        <v>3:46</v>
+        <v>3:04</v>
       </c>
       <c r="H188" t="str">
-        <v>Sevendust</v>
+        <v>Lily Meola</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/sevendust/13125174</v>
+        <v>https://music.apple.com/us/artist/lily-meola/678241726</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/is-this-the-real-you/1869323199</v>
+        <v>https://music.apple.com/us/album/never-kissed-a-cowboy/1866744528</v>
       </c>
       <c r="L188" t="str">
-        <v>Is This The Real You - Sevendust</v>
+        <v>Never Kissed a Cowboy - Lily Meola</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Hud</v>
+        <v>More Of What Matters</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/hud/1842015019</v>
+        <v>https://music.apple.com/us/song/more-of-what-matters/1871592720</v>
       </c>
       <c r="D189" t="str">
         <v>2026-02-02</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>DREAMCRUSH</v>
+        <v>More Of What Matters - Single</v>
       </c>
       <c r="G189" t="str">
-        <v>4:46</v>
+        <v>3:41</v>
       </c>
       <c r="H189" t="str">
-        <v>MØL</v>
+        <v>Jamey Johnson</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/m%C3%B8l/975294671</v>
+        <v>https://music.apple.com/us/artist/jamey-johnson/81030634</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/hud/1842014730</v>
+        <v>https://music.apple.com/us/album/more-of-what-matters/1871592717</v>
       </c>
       <c r="L189" t="str">
-        <v>Hud - MØL</v>
+        <v>More Of What Matters - Jamey Johnson</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Ego Death</v>
+        <v>Is This The Real You</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/ego-death/1867855427</v>
+        <v>https://music.apple.com/us/song/is-this-the-real-you/1869323368</v>
       </c>
       <c r="D190" t="str">
         <v>2026-02-02</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Ego Death - Single</v>
+        <v>ONE</v>
       </c>
       <c r="G190" t="str">
-        <v>2:12</v>
+        <v>3:46</v>
       </c>
       <c r="H190" t="str">
-        <v>Atreyu</v>
+        <v>Sevendust</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/atreyu/6095061</v>
+        <v>https://music.apple.com/us/artist/sevendust/13125174</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/ego-death/1867855173</v>
+        <v>https://music.apple.com/us/album/is-this-the-real-you/1869323199</v>
       </c>
       <c r="L190" t="str">
-        <v>Ego Death - Atreyu</v>
+        <v>Is This The Real You - Sevendust</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Gas Station Love (remix)</v>
+        <v>Hud</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/gas-station-love-remix/1872150728</v>
+        <v>https://music.apple.com/us/song/hud/1842015019</v>
       </c>
       <c r="D191" t="str">
         <v>2026-02-02</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Gas Station Love (remix) - Single</v>
+        <v>DREAMCRUSH</v>
       </c>
       <c r="G191" t="str">
-        <v>4:05</v>
+        <v>4:46</v>
       </c>
       <c r="H191" t="str">
-        <v>EJ Jones</v>
+        <v>MØL</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/ej-jones/1781306141</v>
+        <v>https://music.apple.com/us/artist/m%C3%B8l/975294671</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/gas-station-love-remix/1872150723</v>
+        <v>https://music.apple.com/us/album/hud/1842014730</v>
       </c>
       <c r="L191" t="str">
-        <v>Gas Station Love (remix) - EJ Jones</v>
+        <v>Hud - MØL</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Disappear</v>
+        <v>Ego Death</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/disappear/1861907311</v>
+        <v>https://music.apple.com/us/song/ego-death/1867855427</v>
       </c>
       <c r="D192" t="str">
         <v>2026-02-02</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>Disappear</v>
+        <v>Ego Death - Single</v>
       </c>
       <c r="G192" t="str">
-        <v>5:50</v>
+        <v>2:12</v>
       </c>
       <c r="H192" t="str">
-        <v>Lane 8</v>
+        <v>Atreyu</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/lane-8/634763116</v>
+        <v>https://music.apple.com/us/artist/atreyu/6095061</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/disappear/1861907305</v>
+        <v>https://music.apple.com/us/album/ego-death/1867855173</v>
       </c>
       <c r="L192" t="str">
-        <v>Disappear - Lane 8</v>
+        <v>Ego Death - Atreyu</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Misbehave</v>
+        <v>Gas Station Love (remix)</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/misbehave/1859630128</v>
+        <v>https://music.apple.com/us/song/gas-station-love-remix/1872150728</v>
       </c>
       <c r="D193" t="str">
         <v>2026-02-02</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>Misbehave - Single</v>
+        <v>Gas Station Love (remix) - Single</v>
       </c>
       <c r="G193" t="str">
-        <v>3:43</v>
+        <v>4:05</v>
       </c>
       <c r="H193" t="str">
-        <v>Aluna</v>
+        <v>EJ Jones</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/aluna/1508017201</v>
+        <v>https://music.apple.com/us/artist/ej-jones/1781306141</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/misbehave/1859630126</v>
+        <v>https://music.apple.com/us/album/gas-station-love-remix/1872150723</v>
       </c>
       <c r="L193" t="str">
-        <v>Misbehave - Aluna</v>
+        <v>Gas Station Love (remix) - EJ Jones</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Club Bizarre</v>
+        <v>Disappear</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/club-bizarre/1870355078</v>
+        <v>https://music.apple.com/us/song/disappear/1861907311</v>
       </c>
       <c r="D194" t="str">
         <v>2026-02-02</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Club Bizarre - Single</v>
+        <v>Disappear</v>
       </c>
       <c r="G194" t="str">
-        <v>2:47</v>
+        <v>5:50</v>
       </c>
       <c r="H194" t="str">
-        <v>Alok</v>
+        <v>Lane 8</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/alok/324709167</v>
+        <v>https://music.apple.com/us/artist/lane-8/634763116</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/club-bizarre/1870355077</v>
+        <v>https://music.apple.com/us/album/disappear/1861907305</v>
       </c>
       <c r="L194" t="str">
-        <v>Club Bizarre - Alok</v>
+        <v>Disappear - Lane 8</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Fly</v>
+        <v>Misbehave</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/fly/1867903625</v>
+        <v>https://music.apple.com/us/song/misbehave/1859630128</v>
       </c>
       <c r="D195" t="str">
         <v>2026-02-02</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Fly - Single</v>
+        <v>Misbehave - Single</v>
       </c>
       <c r="G195" t="str">
-        <v>3:04</v>
+        <v>3:43</v>
       </c>
       <c r="H195" t="str">
-        <v>Stephen Stanley</v>
+        <v>Aluna</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/stephen-stanley/28074609</v>
+        <v>https://music.apple.com/us/artist/aluna/1508017201</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/fly/1867903548</v>
+        <v>https://music.apple.com/us/album/misbehave/1859630126</v>
       </c>
       <c r="L195" t="str">
-        <v>Fly - Stephen Stanley</v>
+        <v>Misbehave - Aluna</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>ily anyway</v>
+        <v>Club Bizarre</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/ily-anyway/1870369432</v>
+        <v>https://music.apple.com/us/song/club-bizarre/1870355078</v>
       </c>
       <c r="D196" t="str">
         <v>2026-02-02</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>ily anyway - Single</v>
+        <v>Club Bizarre - Single</v>
       </c>
       <c r="G196" t="str">
-        <v>3:05</v>
+        <v>2:47</v>
       </c>
       <c r="H196" t="str">
-        <v>Strings &amp; Heart</v>
+        <v>Alok</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/strings-heart/1435173742</v>
+        <v>https://music.apple.com/us/artist/alok/324709167</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/ily-anyway/1870369426</v>
+        <v>https://music.apple.com/us/album/club-bizarre/1870355077</v>
       </c>
       <c r="L196" t="str">
-        <v>ily anyway - Strings &amp; Heart</v>
+        <v>Club Bizarre - Alok</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>George Jones (feat. Angela Autumn)</v>
+        <v>Fly</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/george-jones-feat-angela-autumn/1867306007</v>
+        <v>https://music.apple.com/us/song/fly/1867903625</v>
       </c>
       <c r="D197" t="str">
         <v>2026-02-02</v>
@@ -7861,36 +7861,36 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>Nellene - EP</v>
+        <v>Fly - Single</v>
       </c>
       <c r="G197" t="str">
-        <v>3:35</v>
+        <v>3:04</v>
       </c>
       <c r="H197" t="str">
-        <v>Deloyd Elze</v>
+        <v>Stephen Stanley</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/deloyd-elze/1699032462</v>
+        <v>https://music.apple.com/us/artist/stephen-stanley/28074609</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/george-jones-feat-angela-autumn/1867306004</v>
+        <v>https://music.apple.com/us/album/fly/1867903548</v>
       </c>
       <c r="L197" t="str">
-        <v>George Jones (feat. Angela Autumn) - Deloyd Elze</v>
+        <v>Fly - Stephen Stanley</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Kiss Big</v>
+        <v>ily anyway</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/kiss-big/1837292261</v>
+        <v>https://music.apple.com/us/song/ily-anyway/1870369432</v>
       </c>
       <c r="D198" t="str">
         <v>2026-02-02</v>
@@ -7899,36 +7899,36 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>Kiss Big</v>
+        <v>ily anyway - Single</v>
       </c>
       <c r="G198" t="str">
-        <v>3:41</v>
+        <v>3:05</v>
       </c>
       <c r="H198" t="str">
-        <v>Ailbhe Reddy</v>
+        <v>Strings &amp; Heart</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/ailbhe-reddy/947186338</v>
+        <v>https://music.apple.com/us/artist/strings-heart/1435173742</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/kiss-big/1837292249</v>
+        <v>https://music.apple.com/us/album/ily-anyway/1870369426</v>
       </c>
       <c r="L198" t="str">
-        <v>Kiss Big - Ailbhe Reddy</v>
+        <v>ily anyway - Strings &amp; Heart</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>praxis</v>
+        <v>George Jones (feat. Angela Autumn)</v>
       </c>
       <c r="B199" t="str">
         <v/>
       </c>
       <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/praxis/1845253734</v>
+        <v>https://music.apple.com/us/song/george-jones-feat-angela-autumn/1867306007</v>
       </c>
       <c r="D199" t="str">
         <v>2026-02-02</v>
@@ -7937,36 +7937,36 @@
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>Whole World As Vigil</v>
+        <v>Nellene - EP</v>
       </c>
       <c r="G199" t="str">
-        <v>3:28</v>
+        <v>3:35</v>
       </c>
       <c r="H199" t="str">
-        <v>Lauren Auder</v>
+        <v>Deloyd Elze</v>
       </c>
       <c r="I199" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/lauren-auder/1096049552</v>
+        <v>https://music.apple.com/us/artist/deloyd-elze/1699032462</v>
       </c>
       <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/praxis/1845253730</v>
+        <v>https://music.apple.com/us/album/george-jones-feat-angela-autumn/1867306004</v>
       </c>
       <c r="L199" t="str">
-        <v>praxis - Lauren Auder</v>
+        <v>George Jones (feat. Angela Autumn) - Deloyd Elze</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>House</v>
+        <v>Kiss Big</v>
       </c>
       <c r="B200" t="str">
         <v/>
       </c>
       <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/house/1866696487</v>
+        <v>https://music.apple.com/us/song/kiss-big/1837292261</v>
       </c>
       <c r="D200" t="str">
         <v>2026-02-02</v>
@@ -7975,36 +7975,36 @@
         <v/>
       </c>
       <c r="F200" t="str">
-        <v>House - Single</v>
+        <v>Kiss Big</v>
       </c>
       <c r="G200" t="str">
-        <v>2:30</v>
+        <v>3:41</v>
       </c>
       <c r="H200" t="str">
-        <v>Connie Converse</v>
+        <v>Ailbhe Reddy</v>
       </c>
       <c r="I200" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J200" t="str">
-        <v>https://music.apple.com/us/artist/connie-converse/308326962</v>
+        <v>https://music.apple.com/us/artist/ailbhe-reddy/947186338</v>
       </c>
       <c r="K200" t="str">
-        <v>https://music.apple.com/us/album/house/1866696486</v>
+        <v>https://music.apple.com/us/album/kiss-big/1837292249</v>
       </c>
       <c r="L200" t="str">
-        <v>House - Connie Converse</v>
+        <v>Kiss Big - Ailbhe Reddy</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Cowboy Without a Clue</v>
+        <v>praxis</v>
       </c>
       <c r="B201" t="str">
         <v/>
       </c>
       <c r="C201" t="str">
-        <v>https://music.apple.com/us/song/cowboy-without-a-clue/1834024322</v>
+        <v>https://music.apple.com/us/song/praxis/1845253734</v>
       </c>
       <c r="D201" t="str">
         <v>2026-02-02</v>
@@ -8013,36 +8013,36 @@
         <v/>
       </c>
       <c r="F201" t="str">
-        <v>No Love Lost to Kindness</v>
+        <v>Whole World As Vigil</v>
       </c>
       <c r="G201" t="str">
-        <v>3:57</v>
+        <v>3:28</v>
       </c>
       <c r="H201" t="str">
-        <v>Yumi Zouma</v>
+        <v>Lauren Auder</v>
       </c>
       <c r="I201" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J201" t="str">
-        <v>https://music.apple.com/us/artist/yumi-zouma/795031200</v>
+        <v>https://music.apple.com/us/artist/lauren-auder/1096049552</v>
       </c>
       <c r="K201" t="str">
-        <v>https://music.apple.com/us/album/cowboy-without-a-clue/1834024311</v>
+        <v>https://music.apple.com/us/album/praxis/1845253730</v>
       </c>
       <c r="L201" t="str">
-        <v>Cowboy Without a Clue - Yumi Zouma</v>
+        <v>praxis - Lauren Auder</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>Brincar</v>
+        <v>House</v>
       </c>
       <c r="B202" t="str">
         <v/>
       </c>
       <c r="C202" t="str">
-        <v>https://music.apple.com/us/song/brincar/1871554907</v>
+        <v>https://music.apple.com/us/song/house/1866696487</v>
       </c>
       <c r="D202" t="str">
         <v>2026-02-02</v>
@@ -8051,68 +8051,144 @@
         <v/>
       </c>
       <c r="F202" t="str">
-        <v>JET LAG - EP</v>
+        <v>House - Single</v>
       </c>
       <c r="G202" t="str">
-        <v>3:06</v>
+        <v>2:30</v>
       </c>
       <c r="H202" t="str">
-        <v>J Castle</v>
+        <v>Connie Converse</v>
       </c>
       <c r="I202" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J202" t="str">
-        <v>https://music.apple.com/us/artist/j-castle/309829058</v>
+        <v>https://music.apple.com/us/artist/connie-converse/308326962</v>
       </c>
       <c r="K202" t="str">
-        <v>https://music.apple.com/us/album/brincar/1871554901</v>
+        <v>https://music.apple.com/us/album/house/1866696486</v>
       </c>
       <c r="L202" t="str">
-        <v>Brincar - J Castle</v>
+        <v>House - Connie Converse</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
+        <v>Cowboy Without a Clue</v>
+      </c>
+      <c r="B203" t="str">
+        <v/>
+      </c>
+      <c r="C203" t="str">
+        <v>https://music.apple.com/us/song/cowboy-without-a-clue/1834024322</v>
+      </c>
+      <c r="D203" t="str">
+        <v>2026-02-02</v>
+      </c>
+      <c r="E203" t="str">
+        <v/>
+      </c>
+      <c r="F203" t="str">
+        <v>No Love Lost to Kindness</v>
+      </c>
+      <c r="G203" t="str">
+        <v>3:57</v>
+      </c>
+      <c r="H203" t="str">
+        <v>Yumi Zouma</v>
+      </c>
+      <c r="I203" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J203" t="str">
+        <v>https://music.apple.com/us/artist/yumi-zouma/795031200</v>
+      </c>
+      <c r="K203" t="str">
+        <v>https://music.apple.com/us/album/cowboy-without-a-clue/1834024311</v>
+      </c>
+      <c r="L203" t="str">
+        <v>Cowboy Without a Clue - Yumi Zouma</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="str">
+        <v>Brincar</v>
+      </c>
+      <c r="B204" t="str">
+        <v/>
+      </c>
+      <c r="C204" t="str">
+        <v>https://music.apple.com/us/song/brincar/1871554907</v>
+      </c>
+      <c r="D204" t="str">
+        <v>2026-02-02</v>
+      </c>
+      <c r="E204" t="str">
+        <v/>
+      </c>
+      <c r="F204" t="str">
+        <v>JET LAG - EP</v>
+      </c>
+      <c r="G204" t="str">
+        <v>3:06</v>
+      </c>
+      <c r="H204" t="str">
+        <v>J Castle</v>
+      </c>
+      <c r="I204" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J204" t="str">
+        <v>https://music.apple.com/us/artist/j-castle/309829058</v>
+      </c>
+      <c r="K204" t="str">
+        <v>https://music.apple.com/us/album/brincar/1871554901</v>
+      </c>
+      <c r="L204" t="str">
+        <v>Brincar - J Castle</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="str">
         <v>Quién</v>
       </c>
-      <c r="B203" t="str">
-        <v/>
-      </c>
-      <c r="C203" t="str">
+      <c r="B205" t="str">
+        <v/>
+      </c>
+      <c r="C205" t="str">
         <v>https://music.apple.com/us/song/qui%C3%A9n/1870329662</v>
       </c>
-      <c r="D203" t="str">
-        <v>2026-02-02</v>
-      </c>
-      <c r="E203" t="str">
-        <v/>
-      </c>
-      <c r="F203" t="str">
+      <c r="D205" t="str">
+        <v>2026-02-02</v>
+      </c>
+      <c r="E205" t="str">
+        <v/>
+      </c>
+      <c r="F205" t="str">
         <v>Quién - Single</v>
       </c>
-      <c r="G203" t="str">
+      <c r="G205" t="str">
         <v>4:19</v>
       </c>
-      <c r="H203" t="str">
+      <c r="H205" t="str">
         <v>Daniela Darcourt</v>
       </c>
-      <c r="I203" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J203" t="str">
+      <c r="I205" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J205" t="str">
         <v>https://music.apple.com/us/artist/daniela-darcourt/1396749684</v>
       </c>
-      <c r="K203" t="str">
+      <c r="K205" t="str">
         <v>https://music.apple.com/us/album/qui%C3%A9n/1870329660</v>
       </c>
-      <c r="L203" t="str">
+      <c r="L205" t="str">
         <v>Quién - Daniela Darcourt</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L203"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L205"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Nothing But Thieves - Sorry (Official Audio)</v>
       </c>
       <c r="B2" t="str">
-        <v>3 hours ago</v>
+        <v>4 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=D7QfVqo5YqY</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>3 hours ago</v>
+        <v>4 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:37</v>
@@ -2149,7 +2149,7 @@
         <v>SIENNA SPIRO - Die On This Hill (Official Music Video)</v>
       </c>
       <c r="B47" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C47" t="str">
         <v>https://www.youtube.com/watch?v=5RNy_1odv20</v>
@@ -2161,7 +2161,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G47" t="str">
         <v>4:01</v>
@@ -3099,7 +3099,7 @@
         <v>Dermot Kennedy - Funeral (Official Music Video)</v>
       </c>
       <c r="B72" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C72" t="str">
         <v>https://www.youtube.com/watch?v=JzOUJZPky6o</v>
@@ -3111,7 +3111,7 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G72" t="str">
         <v>4:09</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Nothing But Thieves - Sorry (Official Audio)</v>
       </c>
       <c r="B2" t="str">
-        <v>4 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=D7QfVqo5YqY</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>4 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:37</v>
@@ -512,7 +512,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield CA (2026)</v>
+        <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield, CA (2026)</v>
       </c>
       <c r="B4" t="str">
         <v>2 days ago</v>
@@ -545,7 +545,7 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield CA (2026) - The Offspring</v>
+        <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield, CA (2026) - The Offspring</v>
       </c>
     </row>
     <row r="5">
@@ -1503,7 +1503,7 @@
         <v>India Martinez, Coro ArteSí de Olvidados - Niño Sin Miedo</v>
       </c>
       <c r="B30" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=Vug_FPbXe9E</v>
@@ -1515,7 +1515,7 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G30" t="str">
         <v>4:04</v>
@@ -1541,7 +1541,7 @@
         <v>Chelsea Cutler - BAD (Official Lyric Video)</v>
       </c>
       <c r="B31" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=ZIW2vA3Zs1U</v>
@@ -1553,7 +1553,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G31" t="str">
         <v>2:16</v>
@@ -1579,7 +1579,7 @@
         <v>TINI - FUTTTURA LIVE - el cielo + fresa</v>
       </c>
       <c r="B32" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=q_rrgJZAdNg</v>
@@ -1591,7 +1591,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G32" t="str">
         <v>5:58</v>
@@ -1617,7 +1617,7 @@
         <v>Charley - Serial Idealist (Official Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C33" t="str">
         <v>https://www.youtube.com/watch?v=uVIuKbPJz0U</v>
@@ -1629,7 +1629,7 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G33" t="str">
         <v>3:26</v>
@@ -1766,7 +1766,7 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>The Offspring - Looking Out For #1 | Live in Spokane WA (2026)</v>
+        <v>The Offspring - Looking Out For #1 | Live in Spokane, WA (2026)</v>
       </c>
       <c r="B37" t="str">
         <v>5 days ago</v>
@@ -1799,7 +1799,7 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>The Offspring - Looking Out For #1 | Live in Spokane WA (2026) - The Offspring</v>
+        <v>The Offspring - Looking Out For #1 | Live in Spokane, WA (2026) - The Offspring</v>
       </c>
     </row>
     <row r="38">
@@ -2073,7 +2073,7 @@
         <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop)</v>
       </c>
       <c r="B45" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C45" t="str">
         <v>https://www.youtube.com/watch?v=57a_OheOlDw</v>
@@ -2085,7 +2085,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G45" t="str">
         <v>3:20</v>
@@ -3327,7 +3327,7 @@
         <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards</v>
       </c>
       <c r="B78" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C78" t="str">
         <v>https://www.youtube.com/watch?v=kIRmKmEb2g0</v>
@@ -3339,7 +3339,7 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G78" t="str">
         <v>7:21</v>
@@ -3365,7 +3365,7 @@
         <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session)</v>
       </c>
       <c r="B79" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C79" t="str">
         <v>https://www.youtube.com/watch?v=oJ-l2ptQwbQ</v>
@@ -3377,7 +3377,7 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G79" t="str">
         <v>3:17</v>
@@ -5300,7 +5300,7 @@
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>OK OK (Hamdi Remix)</v>
+        <v>OK OK (Hamdi remix)</v>
       </c>
       <c r="B130" t="str">
         <v/>
@@ -5315,7 +5315,7 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>OK OK (Hamdi Remix) - Single</v>
+        <v>OK OK (Hamdi remix) - Single</v>
       </c>
       <c r="G130" t="str">
         <v>3:16</v>
@@ -5333,7 +5333,7 @@
         <v>https://music.apple.com/us/album/ok-ok-hamdi-remix/1871538128</v>
       </c>
       <c r="L130" t="str">
-        <v>OK OK (Hamdi Remix) - Fred again..</v>
+        <v>OK OK (Hamdi remix) - Fred again..</v>
       </c>
     </row>
     <row r="131">

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
@@ -436,28 +436,28 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Nothing But Thieves - Sorry (Official Audio)</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Studio)</v>
       </c>
       <c r="B2" t="str">
-        <v>9 hours ago</v>
+        <v>4 hours ago</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=D7QfVqo5YqY</v>
+        <v>https://www.youtube.com/watch?v=mgsdQI-GVMM</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>9 hours ago</v>
+        <v>4 hours ago</v>
       </c>
       <c r="G2" t="str">
-        <v>3:37</v>
+        <v>3:19</v>
       </c>
       <c r="H2" t="str">
-        <v>Nothing But Thieves</v>
+        <v>David Guetta and Tones And I</v>
       </c>
       <c r="I2" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -469,33 +469,33 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>Nothing But Thieves - Sorry (Official Audio) - Nothing But Thieves</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Studio) - David Guetta and Tones And I</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music</v>
+        <v>Vera Blue - Hold (Live on Sydney Harbour)</v>
       </c>
       <c r="B3" t="str">
-        <v>2 days ago</v>
+        <v>5 hours ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=KdsHxyl4bE8</v>
+        <v>https://www.youtube.com/watch?v=SYEwk-EZJPU</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E3" t="str">
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>2 days ago</v>
+        <v>5 hours ago</v>
       </c>
       <c r="G3" t="str">
-        <v>4:58</v>
+        <v>3:37</v>
       </c>
       <c r="H3" t="str">
-        <v>The Warning</v>
+        <v>Vera Blue</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,33 +507,33 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music - The Warning</v>
+        <v>Vera Blue - Hold (Live on Sydney Harbour) - Vera Blue</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield, CA (2026)</v>
+        <v>Bob Moses - Need You Tonight (INXS Cover) - Brooklyn Mirage 2023</v>
       </c>
       <c r="B4" t="str">
-        <v>2 days ago</v>
+        <v>6 hours ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=Mwkl_Cz_SG8</v>
+        <v>https://www.youtube.com/watch?v=CoCqPwDIBOA</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E4" t="str">
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>2 days ago</v>
+        <v>6 hours ago</v>
       </c>
       <c r="G4" t="str">
-        <v>5:08</v>
+        <v>3:08</v>
       </c>
       <c r="H4" t="str">
-        <v>The Offspring</v>
+        <v>Bob Moses</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,33 +545,33 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield, CA (2026) - The Offspring</v>
+        <v>Bob Moses - Need You Tonight (INXS Cover) - Brooklyn Mirage 2023 - Bob Moses</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered)</v>
+        <v>Marc Anthony - Un Mal Sueño (Visualizer)</v>
       </c>
       <c r="B5" t="str">
-        <v>2 days ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=I7a-pDZFE7U</v>
+        <v>https://www.youtube.com/watch?v=18yZq5xtke4</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E5" t="str">
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>2 days ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="G5" t="str">
-        <v>4:38</v>
+        <v>3:28</v>
       </c>
       <c r="H5" t="str">
-        <v>Roxette</v>
+        <v>Marc Anthony</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,33 +583,33 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered) - Roxette</v>
+        <v>Marc Anthony - Un Mal Sueño (Visualizer) - Marc Anthony</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Live on The Graham Norton Show)</v>
+        <v>Marc Anthony - Contra La Corriente (Visualizer)</v>
       </c>
       <c r="B6" t="str">
-        <v>2 days ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=kGeamxRf8Gw</v>
+        <v>https://www.youtube.com/watch?v=IGLmJ71oHhQ</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E6" t="str">
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>2 days ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="G6" t="str">
-        <v>3:50</v>
+        <v>5:05</v>
       </c>
       <c r="H6" t="str">
-        <v>Jessie Ware</v>
+        <v>Marc Anthony</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,33 +621,33 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Live on The Graham Norton Show) - Jessie Ware</v>
+        <v>Marc Anthony - Contra La Corriente (Visualizer) - Marc Anthony</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>JOSEPH - Water in the Room (Official Music Video)</v>
+        <v>Loreen - Feels Like Heaven</v>
       </c>
       <c r="B7" t="str">
-        <v>3 days ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=tNmT47k6MjM</v>
+        <v>https://www.youtube.com/watch?v=BQc97moyQBg</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E7" t="str">
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>3 days ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="G7" t="str">
-        <v>3:10</v>
+        <v>3:14</v>
       </c>
       <c r="H7" t="str">
-        <v>Joseph</v>
+        <v>Loreen</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,33 +659,33 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>JOSEPH - Water in the Room (Official Music Video) - Joseph</v>
+        <v>Loreen - Feels Like Heaven - Loreen</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Dean Lewis - I Am Getting Well (Lyric Video)</v>
+        <v>Take That - Once You've Tasted Love (Live on Pebble Mill, 1992)</v>
       </c>
       <c r="B8" t="str">
-        <v>3 days ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=6ecgOSOMWzc</v>
+        <v>https://www.youtube.com/watch?v=dOeoDOueESk</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E8" t="str">
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>3 days ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="G8" t="str">
-        <v>2:44</v>
+        <v>3:36</v>
       </c>
       <c r="H8" t="str">
-        <v>Dean Lewis</v>
+        <v>Take That</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,33 +697,33 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Dean Lewis - I Am Getting Well (Lyric Video) - Dean Lewis</v>
+        <v>Take That - Once You've Tasted Love (Live on Pebble Mill, 1992) - Take That</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Take That - Take That and Party (Official HD Video)</v>
+        <v>Paul McCartney, Wings - Nineteen Hundred And Eighty Five (Visualiser)</v>
       </c>
       <c r="B9" t="str">
-        <v>3 days ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=DAerJcerikU</v>
+        <v>https://www.youtube.com/watch?v=a4AIjUHuWpU</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E9" t="str">
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>3 days ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="G9" t="str">
-        <v>2:57</v>
+        <v>5:31</v>
       </c>
       <c r="H9" t="str">
-        <v>Take That</v>
+        <v>PAUL McCARTNEY</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,33 +735,33 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Take That - Take That and Party (Official HD Video) - Take That</v>
+        <v>Paul McCartney, Wings - Nineteen Hundred And Eighty Five (Visualiser) - PAUL McCARTNEY</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>The Cure - Boys Don't Cry (86 Mix) (Official Lyric Video)</v>
+        <v>Nothing But Thieves - Sorry (Official Audio)</v>
       </c>
       <c r="B10" t="str">
-        <v>3 days ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=isNztTjXQsQ</v>
+        <v>https://www.youtube.com/watch?v=D7QfVqo5YqY</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E10" t="str">
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>3 days ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G10" t="str">
-        <v>2:39</v>
+        <v>3:37</v>
       </c>
       <c r="H10" t="str">
-        <v>The Cure</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,33 +773,33 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>The Cure - Boys Don't Cry (86 Mix) (Official Lyric Video) - The Cure</v>
+        <v>Nothing But Thieves - Sorry (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>The Kiffness &amp; Matisyahu - ONE DAY (ft. Andel and Nalyn) [OFFICIAL VIDEO]</v>
+        <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music</v>
       </c>
       <c r="B11" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=buS21tVq5r0</v>
+        <v>https://www.youtube.com/watch?v=KdsHxyl4bE8</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E11" t="str">
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G11" t="str">
-        <v>3:07</v>
+        <v>4:58</v>
       </c>
       <c r="H11" t="str">
-        <v>The Kiffness and Matisyahu</v>
+        <v>The Warning</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,33 +811,33 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>The Kiffness &amp; Matisyahu - ONE DAY (ft. Andel and Nalyn) [OFFICIAL VIDEO] - The Kiffness and Matisyahu</v>
+        <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music - The Warning</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Paris Paloma - Good Girl [Official Music Video]</v>
+        <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield, CA (2026)</v>
       </c>
       <c r="B12" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=qhO6VMC-nx0</v>
+        <v>https://www.youtube.com/watch?v=Mwkl_Cz_SG8</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E12" t="str">
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G12" t="str">
-        <v>4:47</v>
+        <v>5:08</v>
       </c>
       <c r="H12" t="str">
-        <v>Paris Paloma</v>
+        <v>The Offspring</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,33 +849,33 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Paris Paloma - Good Girl [Official Music Video] - Paris Paloma</v>
+        <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield, CA (2026) - The Offspring</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Zara Larsson - Lush Life (Official UGC Compilation Video)</v>
+        <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered)</v>
       </c>
       <c r="B13" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=FgAyfRnbbRs</v>
+        <v>https://www.youtube.com/watch?v=I7a-pDZFE7U</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E13" t="str">
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G13" t="str">
-        <v>3:22</v>
+        <v>4:38</v>
       </c>
       <c r="H13" t="str">
-        <v>Zara Larsson</v>
+        <v>Roxette</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,33 +887,33 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Zara Larsson - Lush Life (Official UGC Compilation Video) - Zara Larsson</v>
+        <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered) - Roxette</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Only The Poets - Monumental</v>
+        <v>Jessie Ware - I Could Get Used To This (Live on The Graham Norton Show)</v>
       </c>
       <c r="B14" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=nwXiAjjl6NE</v>
+        <v>https://www.youtube.com/watch?v=kGeamxRf8Gw</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E14" t="str">
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G14" t="str">
-        <v>2:48</v>
+        <v>3:50</v>
       </c>
       <c r="H14" t="str">
-        <v>only the poets</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,21 +925,21 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Only The Poets - Monumental - only the poets</v>
+        <v>Jessie Ware - I Could Get Used To This (Live on The Graham Norton Show) - Jessie Ware</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Katelyn Tarver - So Am I (Official Music Video)</v>
+        <v>JOSEPH - Water in the Room (Official Music Video)</v>
       </c>
       <c r="B15" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=MjUiVPzMQHw</v>
+        <v>https://www.youtube.com/watch?v=tNmT47k6MjM</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -948,10 +948,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G15" t="str">
-        <v>2:52</v>
+        <v>3:10</v>
       </c>
       <c r="H15" t="str">
-        <v>Katelyn Tarver</v>
+        <v>Joseph</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,21 +963,21 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Katelyn Tarver - So Am I (Official Music Video) - Katelyn Tarver</v>
+        <v>JOSEPH - Water in the Room (Official Music Video) - Joseph</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>David Guetta, TeddySwims, Tones And I - Gone Gone Gone (Unplugged) [Visualizer]</v>
+        <v>Dean Lewis - I Am Getting Well (Lyric Video)</v>
       </c>
       <c r="B16" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=eWglDE7O5r8</v>
+        <v>https://www.youtube.com/watch?v=6ecgOSOMWzc</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -986,10 +986,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G16" t="str">
-        <v>3:33</v>
+        <v>2:44</v>
       </c>
       <c r="H16" t="str">
-        <v>David Guetta</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,21 +1001,21 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>David Guetta, TeddySwims, Tones And I - Gone Gone Gone (Unplugged) [Visualizer] - David Guetta</v>
+        <v>Dean Lewis - I Am Getting Well (Lyric Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>SANTOS BRAVOS “KAWASAKI” Performance Video</v>
+        <v>Take That - Take That and Party (Official HD Video)</v>
       </c>
       <c r="B17" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=Cmy8CsYIUL0</v>
+        <v>https://www.youtube.com/watch?v=DAerJcerikU</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1024,10 +1024,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>2:41</v>
+        <v>2:57</v>
       </c>
       <c r="H17" t="str">
-        <v>HYBE LABELS and SANTOS BRAVOS</v>
+        <v>Take That</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,21 +1039,21 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>SANTOS BRAVOS “KAWASAKI” Performance Video - HYBE LABELS and SANTOS BRAVOS</v>
+        <v>Take That - Take That and Party (Official HD Video) - Take That</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Ella Langley - Dandelion (Official Visualizer)</v>
+        <v>The Cure - Boys Don't Cry (86 Mix) (Official Lyric Video)</v>
       </c>
       <c r="B18" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=sf6eRmInk1s</v>
+        <v>https://www.youtube.com/watch?v=isNztTjXQsQ</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1062,10 +1062,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>4:01</v>
+        <v>2:39</v>
       </c>
       <c r="H18" t="str">
-        <v>Ella Langley</v>
+        <v>The Cure</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,21 +1077,21 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Ella Langley - Dandelion (Official Visualizer) - Ella Langley</v>
+        <v>The Cure - Boys Don't Cry (86 Mix) (Official Lyric Video) - The Cure</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Dogpark - Dandelion (Official Music Video)</v>
+        <v>The Kiffness &amp; Matisyahu - ONE DAY (ft. Andel and Nalyn) [OFFICIAL VIDEO]</v>
       </c>
       <c r="B19" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=fv9prIYHHzk</v>
+        <v>https://www.youtube.com/watch?v=buS21tVq5r0</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1100,10 +1100,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>3:16</v>
+        <v>3:07</v>
       </c>
       <c r="H19" t="str">
-        <v>Dogpark</v>
+        <v>The Kiffness and Matisyahu</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,21 +1115,21 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Dogpark - Dandelion (Official Music Video) - Dogpark</v>
+        <v>The Kiffness &amp; Matisyahu - ONE DAY (ft. Andel and Nalyn) [OFFICIAL VIDEO] - The Kiffness and Matisyahu</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Lauren Spencer Smith - Natural Disaster (Visualizer)</v>
+        <v>Paris Paloma - Good Girl [Official Music Video]</v>
       </c>
       <c r="B20" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=T9YvLA2cdZs</v>
+        <v>https://www.youtube.com/watch?v=qhO6VMC-nx0</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1138,10 +1138,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>3:03</v>
+        <v>4:47</v>
       </c>
       <c r="H20" t="str">
-        <v>Lauren Spencer Smith</v>
+        <v>Paris Paloma</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,21 +1153,21 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Lauren Spencer Smith - Natural Disaster (Visualizer) - Lauren Spencer Smith</v>
+        <v>Paris Paloma - Good Girl [Official Music Video] - Paris Paloma</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>ERNEST - Lorelei (Official Music Video)</v>
+        <v>Zara Larsson - Lush Life (Official UGC Compilation Video)</v>
       </c>
       <c r="B21" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=dPWc_6IdDJk</v>
+        <v>https://www.youtube.com/watch?v=FgAyfRnbbRs</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1176,10 +1176,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>2:41</v>
+        <v>3:22</v>
       </c>
       <c r="H21" t="str">
-        <v>ERNEST</v>
+        <v>Zara Larsson</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,21 +1191,21 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>ERNEST - Lorelei (Official Music Video) - ERNEST</v>
+        <v>Zara Larsson - Lush Life (Official UGC Compilation Video) - Zara Larsson</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Labrinth - I Keep My Promises (Official Audio)</v>
+        <v>Only The Poets - Monumental</v>
       </c>
       <c r="B22" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=CV5rR9JZK-0</v>
+        <v>https://www.youtube.com/watch?v=nwXiAjjl6NE</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1214,10 +1214,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>3:05</v>
+        <v>2:48</v>
       </c>
       <c r="H22" t="str">
-        <v>Labrinth</v>
+        <v>only the poets</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,21 +1229,21 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Labrinth - I Keep My Promises (Official Audio) - Labrinth</v>
+        <v>Only The Poets - Monumental - only the poets</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Grace VanderWaal - Prettier (Official Lyric Video)</v>
+        <v>Katelyn Tarver - So Am I (Official Music Video)</v>
       </c>
       <c r="B23" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=9HwTj3NZ16E</v>
+        <v>https://www.youtube.com/watch?v=MjUiVPzMQHw</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1252,10 +1252,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>2:46</v>
+        <v>2:52</v>
       </c>
       <c r="H23" t="str">
-        <v>Grace VanderWaal</v>
+        <v>Katelyn Tarver</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,21 +1267,21 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Grace VanderWaal - Prettier (Official Lyric Video) - Grace VanderWaal</v>
+        <v>Katelyn Tarver - So Am I (Official Music Video) - Katelyn Tarver</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>VOILÀ - Frozen Lake (Official Lyric Video)</v>
+        <v>David Guetta, TeddySwims, Tones And I - Gone Gone Gone (Unplugged) [Visualizer]</v>
       </c>
       <c r="B24" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=Lmus-UbL1H0</v>
+        <v>https://www.youtube.com/watch?v=eWglDE7O5r8</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1290,10 +1290,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>3:32</v>
+        <v>3:33</v>
       </c>
       <c r="H24" t="str">
-        <v>VOILÀ</v>
+        <v>David Guetta</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,21 +1305,21 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>VOILÀ - Frozen Lake (Official Lyric Video) - VOILÀ</v>
+        <v>David Guetta, TeddySwims, Tones And I - Gone Gone Gone (Unplugged) [Visualizer] - David Guetta</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Cannons - Starlight (Official Video)</v>
+        <v>SANTOS BRAVOS “KAWASAKI” Performance Video</v>
       </c>
       <c r="B25" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=bu6WSMDDPGY</v>
+        <v>https://www.youtube.com/watch?v=Cmy8CsYIUL0</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1328,10 +1328,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>3:42</v>
+        <v>2:41</v>
       </c>
       <c r="H25" t="str">
-        <v>Cannons</v>
+        <v>HYBE LABELS and SANTOS BRAVOS</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,21 +1343,21 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Cannons - Starlight (Official Video) - Cannons</v>
+        <v>SANTOS BRAVOS “KAWASAKI” Performance Video - HYBE LABELS and SANTOS BRAVOS</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Kylie Morgan - Like My Own (Official Video)</v>
+        <v>Ella Langley - Dandelion (Official Visualizer)</v>
       </c>
       <c r="B26" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=zcYeoGBglC0</v>
+        <v>https://www.youtube.com/watch?v=sf6eRmInk1s</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1366,10 +1366,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>2:38</v>
+        <v>4:01</v>
       </c>
       <c r="H26" t="str">
-        <v>Kylie Morgan</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,21 +1381,21 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Kylie Morgan - Like My Own (Official Video) - Kylie Morgan</v>
+        <v>Ella Langley - Dandelion (Official Visualizer) - Ella Langley</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Lizzy McAlpine - House of the Rising Sun (Audio)</v>
+        <v>Dogpark - Dandelion (Official Music Video)</v>
       </c>
       <c r="B27" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=3igYRj82EiU</v>
+        <v>https://www.youtube.com/watch?v=fv9prIYHHzk</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1404,10 +1404,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>3:10</v>
+        <v>3:16</v>
       </c>
       <c r="H27" t="str">
-        <v>Lizzy McAlpine</v>
+        <v>Dogpark</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,21 +1419,21 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Lizzy McAlpine - House of the Rising Sun (Audio) - Lizzy McAlpine</v>
+        <v>Dogpark - Dandelion (Official Music Video) - Dogpark</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Willie Nelson - Heart Of America (From The Gray House Original Soundtrack)</v>
+        <v>Lauren Spencer Smith - Natural Disaster (Visualizer)</v>
       </c>
       <c r="B28" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=0bhcO4Yphuo</v>
+        <v>https://www.youtube.com/watch?v=T9YvLA2cdZs</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1442,10 +1442,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>3:57</v>
+        <v>3:03</v>
       </c>
       <c r="H28" t="str">
-        <v>Willie Nelson</v>
+        <v>Lauren Spencer Smith</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,21 +1457,21 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Willie Nelson - Heart Of America (From The Gray House Original Soundtrack) - Willie Nelson</v>
+        <v>Lauren Spencer Smith - Natural Disaster (Visualizer) - Lauren Spencer Smith</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Jeremy Camp - No Survivors (Live) ft. Skillet</v>
+        <v>ERNEST - Lorelei (Official Music Video)</v>
       </c>
       <c r="B29" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=Jjz1wFe5dMo</v>
+        <v>https://www.youtube.com/watch?v=dPWc_6IdDJk</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1480,10 +1480,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>2:19</v>
+        <v>2:41</v>
       </c>
       <c r="H29" t="str">
-        <v>JeremyCampMusic</v>
+        <v>ERNEST</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,33 +1495,33 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Jeremy Camp - No Survivors (Live) ft. Skillet - JeremyCampMusic</v>
+        <v>ERNEST - Lorelei (Official Music Video) - ERNEST</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>India Martinez, Coro ArteSí de Olvidados - Niño Sin Miedo</v>
+        <v>Labrinth - I Keep My Promises (Official Audio)</v>
       </c>
       <c r="B30" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=Vug_FPbXe9E</v>
+        <v>https://www.youtube.com/watch?v=CV5rR9JZK-0</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E30" t="str">
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>4:04</v>
+        <v>3:05</v>
       </c>
       <c r="H30" t="str">
-        <v>India Martínez</v>
+        <v>Labrinth</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,33 +1533,33 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>India Martinez, Coro ArteSí de Olvidados - Niño Sin Miedo - India Martínez</v>
+        <v>Labrinth - I Keep My Promises (Official Audio) - Labrinth</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Chelsea Cutler - BAD (Official Lyric Video)</v>
+        <v>Grace VanderWaal - Prettier (Official Lyric Video)</v>
       </c>
       <c r="B31" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=ZIW2vA3Zs1U</v>
+        <v>https://www.youtube.com/watch?v=9HwTj3NZ16E</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E31" t="str">
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>2:16</v>
+        <v>2:46</v>
       </c>
       <c r="H31" t="str">
-        <v>Chelsea Cutler</v>
+        <v>Grace VanderWaal</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,33 +1571,33 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Chelsea Cutler - BAD (Official Lyric Video) - Chelsea Cutler</v>
+        <v>Grace VanderWaal - Prettier (Official Lyric Video) - Grace VanderWaal</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>TINI - FUTTTURA LIVE - el cielo + fresa</v>
+        <v>VOILÀ - Frozen Lake (Official Lyric Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=q_rrgJZAdNg</v>
+        <v>https://www.youtube.com/watch?v=Lmus-UbL1H0</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E32" t="str">
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>5:58</v>
+        <v>3:32</v>
       </c>
       <c r="H32" t="str">
-        <v>TINI</v>
+        <v>VOILÀ</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,33 +1609,33 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>TINI - FUTTTURA LIVE - el cielo + fresa - TINI</v>
+        <v>VOILÀ - Frozen Lake (Official Lyric Video) - VOILÀ</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Charley - Serial Idealist (Official Video)</v>
+        <v>Cannons - Starlight (Official Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=uVIuKbPJz0U</v>
+        <v>https://www.youtube.com/watch?v=bu6WSMDDPGY</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E33" t="str">
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>3:26</v>
+        <v>3:42</v>
       </c>
       <c r="H33" t="str">
-        <v>Charley</v>
+        <v>Cannons</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,33 +1647,33 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Charley - Serial Idealist (Official Video) - Charley</v>
+        <v>Cannons - Starlight (Official Video) - Cannons</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Demi Lovato - Ghost (Live)</v>
+        <v>Kylie Morgan - Like My Own (Official Video)</v>
       </c>
       <c r="B34" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=E-ECwdRndVA</v>
+        <v>https://www.youtube.com/watch?v=zcYeoGBglC0</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E34" t="str">
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>4:05</v>
+        <v>2:38</v>
       </c>
       <c r="H34" t="str">
-        <v>Demi Lovato</v>
+        <v>Kylie Morgan</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,33 +1685,33 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Demi Lovato - Ghost (Live) - Demi Lovato</v>
+        <v>Kylie Morgan - Like My Own (Official Video) - Kylie Morgan</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Teddy Swims - Need You More (Live - Green Room Sessions)</v>
+        <v>Lizzy McAlpine - House of the Rising Sun (Audio)</v>
       </c>
       <c r="B35" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=1ugf5aaY4pY</v>
+        <v>https://www.youtube.com/watch?v=3igYRj82EiU</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E35" t="str">
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>3:16</v>
+        <v>3:10</v>
       </c>
       <c r="H35" t="str">
-        <v>Teddy Swims</v>
+        <v>Lizzy McAlpine</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,33 +1723,33 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Teddy Swims - Need You More (Live - Green Room Sessions) - Teddy Swims</v>
+        <v>Lizzy McAlpine - House of the Rising Sun (Audio) - Lizzy McAlpine</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Beck - Love (Audio)</v>
+        <v>Willie Nelson - Heart Of America (From The Gray House Original Soundtrack)</v>
       </c>
       <c r="B36" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=ByABj3Xof1I</v>
+        <v>https://www.youtube.com/watch?v=0bhcO4Yphuo</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E36" t="str">
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>3:14</v>
+        <v>3:57</v>
       </c>
       <c r="H36" t="str">
-        <v>Beck</v>
+        <v>Willie Nelson</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,33 +1761,33 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Beck - Love (Audio) - Beck</v>
+        <v>Willie Nelson - Heart Of America (From The Gray House Original Soundtrack) - Willie Nelson</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>The Offspring - Looking Out For #1 | Live in Spokane, WA (2026)</v>
+        <v>Jeremy Camp - No Survivors (Live) ft. Skillet</v>
       </c>
       <c r="B37" t="str">
-        <v>5 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=2HSbo51EFNg</v>
+        <v>https://www.youtube.com/watch?v=Jjz1wFe5dMo</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E37" t="str">
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>5 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>2:57</v>
+        <v>2:19</v>
       </c>
       <c r="H37" t="str">
-        <v>The Offspring</v>
+        <v>JeremyCampMusic</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,33 +1799,33 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>The Offspring - Looking Out For #1 | Live in Spokane, WA (2026) - The Offspring</v>
+        <v>Jeremy Camp - No Survivors (Live) ft. Skillet - JeremyCampMusic</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show</v>
+        <v>India Martinez, Coro ArteSí de Olvidados - Niño Sin Miedo</v>
       </c>
       <c r="B38" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=ylifHFJWJ_c</v>
+        <v>https://www.youtube.com/watch?v=Vug_FPbXe9E</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E38" t="str">
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>4:10</v>
+        <v>4:04</v>
       </c>
       <c r="H38" t="str">
-        <v>Sophie Ellis-Bextor</v>
+        <v>India Martínez</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,33 +1837,33 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show - Sophie Ellis-Bextor</v>
+        <v>India Martinez, Coro ArteSí de Olvidados - Niño Sin Miedo - India Martínez</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Jason Derulo - Sexy For Me [Official Music Video]</v>
+        <v>Chelsea Cutler - BAD (Official Lyric Video)</v>
       </c>
       <c r="B39" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=9ST-eBNL0NU</v>
+        <v>https://www.youtube.com/watch?v=ZIW2vA3Zs1U</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E39" t="str">
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>2:10</v>
+        <v>2:16</v>
       </c>
       <c r="H39" t="str">
-        <v>Jason Derulo</v>
+        <v>Chelsea Cutler</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,33 +1875,33 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Jason Derulo - Sexy For Me [Official Music Video] - Jason Derulo</v>
+        <v>Chelsea Cutler - BAD (Official Lyric Video) - Chelsea Cutler</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Lights - COME GET YOUR GIRL</v>
+        <v>TINI - FUTTTURA LIVE - el cielo + fresa</v>
       </c>
       <c r="B40" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=EhzX2y5MpSM</v>
+        <v>https://www.youtube.com/watch?v=q_rrgJZAdNg</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E40" t="str">
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>3:52</v>
+        <v>5:58</v>
       </c>
       <c r="H40" t="str">
-        <v>lights</v>
+        <v>TINI</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,33 +1913,33 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Lights - COME GET YOUR GIRL - lights</v>
+        <v>TINI - FUTTTURA LIVE - el cielo + fresa - TINI</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video)</v>
+        <v>Charley - Serial Idealist (Official Video)</v>
       </c>
       <c r="B41" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=yUAvfo8fpuU</v>
+        <v>https://www.youtube.com/watch?v=uVIuKbPJz0U</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E41" t="str">
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>3:50</v>
+        <v>3:26</v>
       </c>
       <c r="H41" t="str">
-        <v>Telenova</v>
+        <v>Charley</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,33 +1951,33 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video) - Telenova</v>
+        <v>Charley - Serial Idealist (Official Video) - Charley</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>I Had To Explain "How Music Works" LIVE In Concert</v>
+        <v>Demi Lovato - Ghost (Live)</v>
       </c>
       <c r="B42" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=KnsBdAM3HqY</v>
+        <v>https://www.youtube.com/watch?v=E-ECwdRndVA</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E42" t="str">
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>5:32</v>
+        <v>4:05</v>
       </c>
       <c r="H42" t="str">
-        <v>Marcin</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,33 +1989,33 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>I Had To Explain "How Music Works" LIVE In Concert - Marcin</v>
+        <v>Demi Lovato - Ghost (Live) - Demi Lovato</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>We Three - Drunk Driving (Official Music Video)</v>
+        <v>Teddy Swims - Need You More (Live - Green Room Sessions)</v>
       </c>
       <c r="B43" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=BTqRGxSX6AQ</v>
+        <v>https://www.youtube.com/watch?v=1ugf5aaY4pY</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E43" t="str">
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>4:27</v>
+        <v>3:16</v>
       </c>
       <c r="H43" t="str">
-        <v>We Three</v>
+        <v>Teddy Swims</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,33 +2027,33 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>We Three - Drunk Driving (Official Music Video) - We Three</v>
+        <v>Teddy Swims - Need You More (Live - Green Room Sessions) - Teddy Swims</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Timebelle - Top of the World (Mood Video)</v>
+        <v>Beck - Love (Audio)</v>
       </c>
       <c r="B44" t="str">
-        <v>6 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=r9KyYK_E34s</v>
+        <v>https://www.youtube.com/watch?v=ByABj3Xof1I</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E44" t="str">
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>6 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>3:01</v>
+        <v>3:14</v>
       </c>
       <c r="H44" t="str">
-        <v>Timebelle Official</v>
+        <v>Beck</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,33 +2065,33 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Timebelle - Top of the World (Mood Video) - Timebelle Official</v>
+        <v>Beck - Love (Audio) - Beck</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop)</v>
+        <v>The Offspring - Looking Out For #1 | Live in Spokane, WA (2026)</v>
       </c>
       <c r="B45" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=57a_OheOlDw</v>
+        <v>https://www.youtube.com/watch?v=2HSbo51EFNg</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E45" t="str">
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>3:20</v>
+        <v>2:57</v>
       </c>
       <c r="H45" t="str">
-        <v>David Guetta and Tones And I</v>
+        <v>The Offspring</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,33 +2103,33 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop) - David Guetta and Tones And I</v>
+        <v>The Offspring - Looking Out For #1 | Live in Spokane, WA (2026) - The Offspring</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Clinton Kane - this is my last love song to you (Official Lyric Video)</v>
+        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show</v>
       </c>
       <c r="B46" t="str">
-        <v>9 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=-5Aa8NTiRqE</v>
+        <v>https://www.youtube.com/watch?v=ylifHFJWJ_c</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E46" t="str">
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>9 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>3:34</v>
+        <v>4:10</v>
       </c>
       <c r="H46" t="str">
-        <v>Clinton Kane</v>
+        <v>Sophie Ellis-Bextor</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,33 +2141,33 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Clinton Kane - this is my last love song to you (Official Lyric Video) - Clinton Kane</v>
+        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show - Sophie Ellis-Bextor</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>SIENNA SPIRO - Die On This Hill (Official Music Video)</v>
+        <v>Jason Derulo - Sexy For Me [Official Music Video]</v>
       </c>
       <c r="B47" t="str">
-        <v>10 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=5RNy_1odv20</v>
+        <v>https://www.youtube.com/watch?v=9ST-eBNL0NU</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E47" t="str">
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>10 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>4:01</v>
+        <v>2:10</v>
       </c>
       <c r="H47" t="str">
-        <v>Lyrical Lemonade and SIENNA SPIRO</v>
+        <v>Jason Derulo</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,33 +2179,33 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>SIENNA SPIRO - Die On This Hill (Official Music Video) - Lyrical Lemonade and SIENNA SPIRO</v>
+        <v>Jason Derulo - Sexy For Me [Official Music Video] - Jason Derulo</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Amazon Music presents: Sienna Spiro - You Stole The Show</v>
+        <v>Lights - COME GET YOUR GIRL</v>
       </c>
       <c r="B48" t="str">
-        <v>10 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=stYIRyCLN4Y</v>
+        <v>https://www.youtube.com/watch?v=EhzX2y5MpSM</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E48" t="str">
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>10 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>3:24</v>
+        <v>3:52</v>
       </c>
       <c r="H48" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>lights</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,33 +2217,33 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Amazon Music presents: Sienna Spiro - You Stole The Show - SIENNA SPIRO</v>
+        <v>Lights - COME GET YOUR GIRL - lights</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Harry Styles - Aperture (Official Video)</v>
+        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video)</v>
       </c>
       <c r="B49" t="str">
-        <v>10 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=7sxVHYZ_PnA</v>
+        <v>https://www.youtube.com/watch?v=yUAvfo8fpuU</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E49" t="str">
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>10 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>5:52</v>
+        <v>3:50</v>
       </c>
       <c r="H49" t="str">
-        <v>Harry Styles</v>
+        <v>Telenova</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,33 +2255,33 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Harry Styles - Aperture (Official Video) - Harry Styles</v>
+        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video) - Telenova</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Neal Francis - Back It Up (Live At The Salt Shed)</v>
+        <v>I Had To Explain "How Music Works" LIVE In Concert</v>
       </c>
       <c r="B50" t="str">
-        <v>10 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=46iZEdsxjC0</v>
+        <v>https://www.youtube.com/watch?v=KnsBdAM3HqY</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E50" t="str">
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>10 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>5:01</v>
+        <v>5:32</v>
       </c>
       <c r="H50" t="str">
-        <v>Neal Francis</v>
+        <v>Marcin</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,33 +2293,33 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Neal Francis - Back It Up (Live At The Salt Shed) - Neal Francis</v>
+        <v>I Had To Explain "How Music Works" LIVE In Concert - Marcin</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
+        <v>We Three - Drunk Driving (Official Music Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>10 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=K2nG1Uukz7E</v>
+        <v>https://www.youtube.com/watch?v=BTqRGxSX6AQ</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E51" t="str">
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>10 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>4:12</v>
+        <v>4:27</v>
       </c>
       <c r="H51" t="str">
-        <v>OfficiallyExtreme</v>
+        <v>We Three</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,33 +2331,33 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
+        <v>We Three - Drunk Driving (Official Music Video) - We Three</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Holly Humberstone - To Love Somebody (Official Video)</v>
+        <v>Timebelle - Top of the World (Mood Video)</v>
       </c>
       <c r="B52" t="str">
-        <v>10 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
+        <v>https://www.youtube.com/watch?v=r9KyYK_E34s</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E52" t="str">
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>10 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>3:59</v>
+        <v>3:01</v>
       </c>
       <c r="H52" t="str">
-        <v>Holly Humberstone</v>
+        <v>Timebelle Official</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,33 +2369,33 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Holly Humberstone - To Love Somebody (Official Video) - Holly Humberstone</v>
+        <v>Timebelle - Top of the World (Mood Video) - Timebelle Official</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop)</v>
       </c>
       <c r="B53" t="str">
-        <v>10 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
+        <v>https://www.youtube.com/watch?v=57a_OheOlDw</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E53" t="str">
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>10 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>2:56</v>
+        <v>3:20</v>
       </c>
       <c r="H53" t="str">
-        <v>Cliff Richard</v>
+        <v>David Guetta and Tones And I</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,21 +2407,21 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018) - Cliff Richard</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop) - David Guetta and Tones And I</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
+        <v>Clinton Kane - this is my last love song to you (Official Lyric Video)</v>
       </c>
       <c r="B54" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
+        <v>https://www.youtube.com/watch?v=-5Aa8NTiRqE</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2430,10 +2430,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G54" t="str">
-        <v>3:46</v>
+        <v>3:34</v>
       </c>
       <c r="H54" t="str">
-        <v>Jessie Ware</v>
+        <v>Clinton Kane</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,21 +2445,21 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Official Video) - Jessie Ware</v>
+        <v>Clinton Kane - this is my last love song to you (Official Lyric Video) - Clinton Kane</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Bella White - Dream Song (Official Audio)</v>
+        <v>SIENNA SPIRO - Die On This Hill (Official Music Video)</v>
       </c>
       <c r="B55" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
+        <v>https://www.youtube.com/watch?v=5RNy_1odv20</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2468,10 +2468,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G55" t="str">
-        <v>4:37</v>
+        <v>4:01</v>
       </c>
       <c r="H55" t="str">
-        <v>Bella White</v>
+        <v>Lyrical Lemonade and SIENNA SPIRO</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,21 +2483,21 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Bella White - Dream Song (Official Audio) - Bella White</v>
+        <v>SIENNA SPIRO - Die On This Hill (Official Music Video) - Lyrical Lemonade and SIENNA SPIRO</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Ryan Wright - Film School Kids (Official Video)</v>
+        <v>Amazon Music presents: Sienna Spiro - You Stole The Show</v>
       </c>
       <c r="B56" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=pnAz9RwGSek</v>
+        <v>https://www.youtube.com/watch?v=stYIRyCLN4Y</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2506,10 +2506,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G56" t="str">
-        <v>4:06</v>
+        <v>3:24</v>
       </c>
       <c r="H56" t="str">
-        <v>Ryan Wright</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,21 +2521,21 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Ryan Wright - Film School Kids (Official Video) - Ryan Wright</v>
+        <v>Amazon Music presents: Sienna Spiro - You Stole The Show - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer)</v>
+        <v>Harry Styles - Aperture (Official Video)</v>
       </c>
       <c r="B57" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=u7aPv2saz_I</v>
+        <v>https://www.youtube.com/watch?v=7sxVHYZ_PnA</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2544,10 +2544,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G57" t="str">
-        <v>3:54</v>
+        <v>5:52</v>
       </c>
       <c r="H57" t="str">
-        <v>Dove Cameron</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,21 +2559,21 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer) - Dove Cameron</v>
+        <v>Harry Styles - Aperture (Official Video) - Harry Styles</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video)</v>
+        <v>Neal Francis - Back It Up (Live At The Salt Shed)</v>
       </c>
       <c r="B58" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=WGb8KVdqs6k</v>
+        <v>https://www.youtube.com/watch?v=46iZEdsxjC0</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2582,10 +2582,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G58" t="str">
-        <v>4:10</v>
+        <v>5:01</v>
       </c>
       <c r="H58" t="str">
-        <v>Parker McCollum</v>
+        <v>Neal Francis</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,21 +2597,21 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video) - Parker McCollum</v>
+        <v>Neal Francis - Back It Up (Live At The Salt Shed) - Neal Francis</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video)</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
       </c>
       <c r="B59" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=X1ZeY4Y3l1M</v>
+        <v>https://www.youtube.com/watch?v=K2nG1Uukz7E</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2620,10 +2620,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G59" t="str">
-        <v>3:26</v>
+        <v>4:12</v>
       </c>
       <c r="H59" t="str">
-        <v>Matt Hansen</v>
+        <v>OfficiallyExtreme</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,33 +2635,33 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video) - Matt Hansen</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Louis Tomlinson - Imposter (Official Video)</v>
+        <v>Holly Humberstone - To Love Somebody (Official Video)</v>
       </c>
       <c r="B60" t="str">
-        <v>12 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=rzuD5szQhso</v>
+        <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E60" t="str">
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>12 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G60" t="str">
-        <v>2:56</v>
+        <v>3:59</v>
       </c>
       <c r="H60" t="str">
-        <v>Louis Tomlinson</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,21 +2673,21 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Louis Tomlinson - Imposter (Official Video) - Louis Tomlinson</v>
+        <v>Holly Humberstone - To Love Somebody (Official Video) - Holly Humberstone</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Mitchell Tenpenny - You Phase (Official Music Video)</v>
+        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
       </c>
       <c r="B61" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=UPuK6wV5Zco</v>
+        <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -2699,7 +2699,7 @@
         <v>2:56</v>
       </c>
       <c r="H61" t="str">
-        <v>Mitchell Tenpenny</v>
+        <v>Cliff Richard</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,21 +2711,21 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Mitchell Tenpenny - You Phase (Official Music Video) - Mitchell Tenpenny</v>
+        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018) - Cliff Richard</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Tauren Wells - Breathe On It (Official Lyric Video)</v>
+        <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
       </c>
       <c r="B62" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=9hW9sNMn2A0</v>
+        <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -2734,10 +2734,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G62" t="str">
-        <v>4:01</v>
+        <v>3:46</v>
       </c>
       <c r="H62" t="str">
-        <v>Tauren Wells</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,21 +2749,21 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Tauren Wells - Breathe On It (Official Lyric Video) - Tauren Wells</v>
+        <v>Jessie Ware - I Could Get Used To This (Official Video) - Jessie Ware</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Maiah Manser - Feeling it All (Official Music Video)</v>
+        <v>Bella White - Dream Song (Official Audio)</v>
       </c>
       <c r="B63" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=JMYvXleIwfU</v>
+        <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -2772,10 +2772,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G63" t="str">
-        <v>3:05</v>
+        <v>4:37</v>
       </c>
       <c r="H63" t="str">
-        <v>Maiah Manser</v>
+        <v>Bella White</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,21 +2787,21 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Maiah Manser - Feeling it All (Official Music Video) - Maiah Manser</v>
+        <v>Bella White - Dream Song (Official Audio) - Bella White</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Taylor Austin Dye - Man For That (Official Music Video)</v>
+        <v>Ryan Wright - Film School Kids (Official Video)</v>
       </c>
       <c r="B64" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=vOzX-o11seI</v>
+        <v>https://www.youtube.com/watch?v=pnAz9RwGSek</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -2810,10 +2810,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G64" t="str">
-        <v>2:27</v>
+        <v>4:06</v>
       </c>
       <c r="H64" t="str">
-        <v>Taylor Austin Dye</v>
+        <v>Ryan Wright</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,21 +2825,21 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Taylor Austin Dye - Man For That (Official Music Video) - Taylor Austin Dye</v>
+        <v>Ryan Wright - Film School Kids (Official Video) - Ryan Wright</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Chelsea Cutler - BAD (Official Video)</v>
+        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer)</v>
       </c>
       <c r="B65" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=86k4E6ydHVU</v>
+        <v>https://www.youtube.com/watch?v=u7aPv2saz_I</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -2848,10 +2848,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G65" t="str">
-        <v>2:34</v>
+        <v>3:54</v>
       </c>
       <c r="H65" t="str">
-        <v>Chelsea Cutler</v>
+        <v>Dove Cameron</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,21 +2863,21 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Chelsea Cutler - BAD (Official Video) - Chelsea Cutler</v>
+        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer) - Dove Cameron</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video)</v>
+        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video)</v>
       </c>
       <c r="B66" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=-UWIFAiOOPE</v>
+        <v>https://www.youtube.com/watch?v=WGb8KVdqs6k</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -2886,10 +2886,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G66" t="str">
-        <v>3:13</v>
+        <v>4:10</v>
       </c>
       <c r="H66" t="str">
-        <v>Ashley Kutcher</v>
+        <v>Parker McCollum</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,21 +2901,21 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video) - Ashley Kutcher</v>
+        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video) - Parker McCollum</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Louis Tomlinson - Dark To Light (Visualiser)</v>
+        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video)</v>
       </c>
       <c r="B67" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=02QyA29poAM</v>
+        <v>https://www.youtube.com/watch?v=X1ZeY4Y3l1M</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -2924,10 +2924,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G67" t="str">
-        <v>3:13</v>
+        <v>3:26</v>
       </c>
       <c r="H67" t="str">
-        <v>Louis Tomlinson</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,33 +2939,33 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Louis Tomlinson - Dark To Light (Visualiser) - Louis Tomlinson</v>
+        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video) - Matt Hansen</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>CAIN - So Long Sad Songs (Lyric Video)</v>
+        <v>Louis Tomlinson - Imposter (Official Video)</v>
       </c>
       <c r="B68" t="str">
-        <v>10 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=feOv8nufa_I</v>
+        <v>https://www.youtube.com/watch?v=rzuD5szQhso</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E68" t="str">
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>10 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G68" t="str">
-        <v>3:08</v>
+        <v>2:56</v>
       </c>
       <c r="H68" t="str">
-        <v>CAIN</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,21 +2977,21 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>CAIN - So Long Sad Songs (Lyric Video) - CAIN</v>
+        <v>Louis Tomlinson - Imposter (Official Video) - Louis Tomlinson</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Harry Styles - Aperture (Official Audio)</v>
+        <v>Mitchell Tenpenny - You Phase (Official Music Video)</v>
       </c>
       <c r="B69" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=rA_eCxPay7E</v>
+        <v>https://www.youtube.com/watch?v=UPuK6wV5Zco</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -3000,10 +3000,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G69" t="str">
-        <v>5:14</v>
+        <v>2:56</v>
       </c>
       <c r="H69" t="str">
-        <v>Harry Styles</v>
+        <v>Mitchell Tenpenny</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,33 +3015,33 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Harry Styles - Aperture (Official Audio) - Harry Styles</v>
+        <v>Mitchell Tenpenny - You Phase (Official Music Video) - Mitchell Tenpenny</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Lana Lubany - BAD IDEA (Official Video)</v>
+        <v>Tauren Wells - Breathe On It (Official Lyric Video)</v>
       </c>
       <c r="B70" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
+        <v>https://www.youtube.com/watch?v=9hW9sNMn2A0</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E70" t="str">
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G70" t="str">
-        <v>2:59</v>
+        <v>4:01</v>
       </c>
       <c r="H70" t="str">
-        <v>Lana Lubany</v>
+        <v>Tauren Wells</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,33 +3053,33 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Lana Lubany - BAD IDEA (Official Video) - Lana Lubany</v>
+        <v>Tauren Wells - Breathe On It (Official Lyric Video) - Tauren Wells</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>DEF LEPPARD - Rejoice (Official Lyric Video)</v>
+        <v>Maiah Manser - Feeling it All (Official Music Video)</v>
       </c>
       <c r="B71" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=zy2TLLeNgp0</v>
+        <v>https://www.youtube.com/watch?v=JMYvXleIwfU</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E71" t="str">
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G71" t="str">
-        <v>4:21</v>
+        <v>3:05</v>
       </c>
       <c r="H71" t="str">
-        <v>DEF LEPPARD</v>
+        <v>Maiah Manser</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,33 +3091,33 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>DEF LEPPARD - Rejoice (Official Lyric Video) - DEF LEPPARD</v>
+        <v>Maiah Manser - Feeling it All (Official Music Video) - Maiah Manser</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Dermot Kennedy - Funeral (Official Music Video)</v>
+        <v>Taylor Austin Dye - Man For That (Official Music Video)</v>
       </c>
       <c r="B72" t="str">
-        <v>12 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=JzOUJZPky6o</v>
+        <v>https://www.youtube.com/watch?v=vOzX-o11seI</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E72" t="str">
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>12 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G72" t="str">
-        <v>4:09</v>
+        <v>2:27</v>
       </c>
       <c r="H72" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Taylor Austin Dye</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,33 +3129,33 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Dermot Kennedy - Funeral (Official Music Video) - Dermot Kennedy</v>
+        <v>Taylor Austin Dye - Man For That (Official Music Video) - Taylor Austin Dye</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video)</v>
+        <v>Chelsea Cutler - BAD (Official Video)</v>
       </c>
       <c r="B73" t="str">
-        <v>12 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=kfF0bVZMCw0</v>
+        <v>https://www.youtube.com/watch?v=86k4E6ydHVU</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E73" t="str">
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>12 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G73" t="str">
         <v>2:34</v>
       </c>
       <c r="H73" t="str">
-        <v>Lauren Sanderson</v>
+        <v>Chelsea Cutler</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,33 +3167,33 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video) - Lauren Sanderson</v>
+        <v>Chelsea Cutler - BAD (Official Video) - Chelsea Cutler</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show]</v>
+        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video)</v>
       </c>
       <c r="B74" t="str">
-        <v>13 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=dLzpNstMHZY</v>
+        <v>https://www.youtube.com/watch?v=-UWIFAiOOPE</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E74" t="str">
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>13 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G74" t="str">
-        <v>3:10</v>
+        <v>3:13</v>
       </c>
       <c r="H74" t="str">
-        <v>Olivia Dean</v>
+        <v>Ashley Kutcher</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,33 +3205,33 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show] - Olivia Dean</v>
+        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video) - Ashley Kutcher</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel)</v>
+        <v>Louis Tomlinson - Dark To Light (Visualiser)</v>
       </c>
       <c r="B75" t="str">
-        <v>13 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=fo_j8Fqag8I</v>
+        <v>https://www.youtube.com/watch?v=02QyA29poAM</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E75" t="str">
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>13 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G75" t="str">
-        <v>3:21</v>
+        <v>3:13</v>
       </c>
       <c r="H75" t="str">
-        <v>David Guetta and Tones And I</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,33 +3243,33 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel) - David Guetta and Tones And I</v>
+        <v>Louis Tomlinson - Dark To Light (Visualiser) - Louis Tomlinson</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>The Avett Brothers - Matrimony (Official Video)</v>
+        <v>CAIN - So Long Sad Songs (Lyric Video)</v>
       </c>
       <c r="B76" t="str">
-        <v>13 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=7sD9-MtV9CY</v>
+        <v>https://www.youtube.com/watch?v=feOv8nufa_I</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E76" t="str">
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>13 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G76" t="str">
-        <v>3:06</v>
+        <v>3:08</v>
       </c>
       <c r="H76" t="str">
-        <v>The Avett Brothers</v>
+        <v>CAIN</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,33 +3281,33 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>The Avett Brothers - Matrimony (Official Video) - The Avett Brothers</v>
+        <v>CAIN - So Long Sad Songs (Lyric Video) - CAIN</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Jordana Bryant - Love Like That (Official Video)</v>
+        <v>Harry Styles - Aperture (Official Audio)</v>
       </c>
       <c r="B77" t="str">
-        <v>13 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=3ATlH-Rtzmk</v>
+        <v>https://www.youtube.com/watch?v=rA_eCxPay7E</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E77" t="str">
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>13 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G77" t="str">
-        <v>3:21</v>
+        <v>5:14</v>
       </c>
       <c r="H77" t="str">
-        <v>Jordana Bryant</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,33 +3319,33 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Jordana Bryant - Love Like That (Official Video) - Jordana Bryant</v>
+        <v>Harry Styles - Aperture (Official Audio) - Harry Styles</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards</v>
+        <v>Lana Lubany - BAD IDEA (Official Video)</v>
       </c>
       <c r="B78" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=kIRmKmEb2g0</v>
+        <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E78" t="str">
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G78" t="str">
-        <v>7:21</v>
+        <v>2:59</v>
       </c>
       <c r="H78" t="str">
-        <v>Katy Perry</v>
+        <v>Lana Lubany</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,33 +3357,33 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards - Katy Perry</v>
+        <v>Lana Lubany - BAD IDEA (Official Video) - Lana Lubany</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session)</v>
+        <v>DEF LEPPARD - Rejoice (Official Lyric Video)</v>
       </c>
       <c r="B79" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=oJ-l2ptQwbQ</v>
+        <v>https://www.youtube.com/watch?v=zy2TLLeNgp0</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E79" t="str">
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G79" t="str">
-        <v>3:17</v>
+        <v>4:21</v>
       </c>
       <c r="H79" t="str">
-        <v>Lauren Watkins</v>
+        <v>DEF LEPPARD</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,33 +3395,33 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session) - Lauren Watkins</v>
+        <v>DEF LEPPARD - Rejoice (Official Lyric Video) - DEF LEPPARD</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Just A Mess (Live acoustic studio session)</v>
+        <v>Dermot Kennedy - Funeral (Official Music Video)</v>
       </c>
       <c r="B80" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=ShW-I63KD8w</v>
+        <v>https://www.youtube.com/watch?v=JzOUJZPky6o</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E80" t="str">
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G80" t="str">
-        <v>3:45</v>
+        <v>4:09</v>
       </c>
       <c r="H80" t="str">
-        <v>Tones And I</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,33 +3433,33 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Just A Mess (Live acoustic studio session) - Tones And I</v>
+        <v>Dermot Kennedy - Funeral (Official Music Video) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Ashleigh Dallas - Sail Away (Official Audio)</v>
+        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video)</v>
       </c>
       <c r="B81" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=66PDbaI-BVA</v>
+        <v>https://www.youtube.com/watch?v=kfF0bVZMCw0</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E81" t="str">
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G81" t="str">
-        <v>3:57</v>
+        <v>2:34</v>
       </c>
       <c r="H81" t="str">
-        <v>Ashleigh Dallas</v>
+        <v>Lauren Sanderson</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,33 +3471,33 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Ashleigh Dallas - Sail Away (Official Audio) - Ashleigh Dallas</v>
+        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video) - Lauren Sanderson</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Performance Video)</v>
+        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show]</v>
       </c>
       <c r="B82" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=4tmW_JSXHII</v>
+        <v>https://www.youtube.com/watch?v=dLzpNstMHZY</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E82" t="str">
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G82" t="str">
-        <v>3:03</v>
+        <v>3:10</v>
       </c>
       <c r="H82" t="str">
-        <v>Charlie Puth</v>
+        <v>Olivia Dean</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,33 +3509,33 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Performance Video) - Charlie Puth</v>
+        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show] - Olivia Dean</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Chappell Roan - The Subway (Live from Kansas City)</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel)</v>
       </c>
       <c r="B83" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=6kZVtF8iaWw</v>
+        <v>https://www.youtube.com/watch?v=fo_j8Fqag8I</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E83" t="str">
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G83" t="str">
-        <v>4:27</v>
+        <v>3:21</v>
       </c>
       <c r="H83" t="str">
-        <v>Chappell Roan</v>
+        <v>David Guetta and Tones And I</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,33 +3547,33 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Chappell Roan - The Subway (Live from Kansas City) - Chappell Roan</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel) - David Guetta and Tones And I</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar)</v>
+        <v>The Avett Brothers - Matrimony (Official Video)</v>
       </c>
       <c r="B84" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=guUvgEKkk1U</v>
+        <v>https://www.youtube.com/watch?v=7sD9-MtV9CY</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E84" t="str">
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G84" t="str">
-        <v>4:34</v>
+        <v>3:06</v>
       </c>
       <c r="H84" t="str">
-        <v>Armik</v>
+        <v>The Avett Brothers</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,33 +3585,33 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar) - Armik</v>
+        <v>The Avett Brothers - Matrimony (Official Video) - The Avett Brothers</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>LØLØ - 007 (Official Music Video)</v>
+        <v>Jordana Bryant - Love Like That (Official Video)</v>
       </c>
       <c r="B85" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=4okJouEbZ_s</v>
+        <v>https://www.youtube.com/watch?v=3ATlH-Rtzmk</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E85" t="str">
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G85" t="str">
-        <v>2:54</v>
+        <v>3:21</v>
       </c>
       <c r="H85" t="str">
-        <v>LØLØ</v>
+        <v>Jordana Bryant</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,21 +3623,21 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>LØLØ - 007 (Official Music Video) - LØLØ</v>
+        <v>Jordana Bryant - Love Like That (Official Video) - Jordana Bryant</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Tenille Townes - enabling (Official Visualizer)</v>
+        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards</v>
       </c>
       <c r="B86" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=yL_TxDF8WtI</v>
+        <v>https://www.youtube.com/watch?v=kIRmKmEb2g0</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3646,10 +3646,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G86" t="str">
-        <v>3:25</v>
+        <v>7:21</v>
       </c>
       <c r="H86" t="str">
-        <v>Tenille Townes</v>
+        <v>Katy Perry</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,21 +3661,21 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Tenille Townes - enabling (Official Visualizer) - Tenille Townes</v>
+        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards - Katy Perry</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Alan Walker - Not Home (Official Lyric Video)</v>
+        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session)</v>
       </c>
       <c r="B87" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=0m45tTheoCs</v>
+        <v>https://www.youtube.com/watch?v=oJ-l2ptQwbQ</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3684,10 +3684,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G87" t="str">
-        <v>2:01</v>
+        <v>3:17</v>
       </c>
       <c r="H87" t="str">
-        <v>Alan Walker</v>
+        <v>Lauren Watkins</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,21 +3699,21 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Alan Walker - Not Home (Official Lyric Video) - Alan Walker</v>
+        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session) - Lauren Watkins</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Charli xcx - Wall of Sound (Official Audio)</v>
+        <v>Just A Mess (Live acoustic studio session)</v>
       </c>
       <c r="B88" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=AHm1i212UP4</v>
+        <v>https://www.youtube.com/watch?v=ShW-I63KD8w</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3722,10 +3722,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G88" t="str">
-        <v>2:25</v>
+        <v>3:45</v>
       </c>
       <c r="H88" t="str">
-        <v>Charli xcx</v>
+        <v>Tones And I</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,21 +3737,21 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Charli xcx - Wall of Sound (Official Audio) - Charli xcx</v>
+        <v>Just A Mess (Live acoustic studio session) - Tones And I</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Labrinth - God Spoke (Official Visualizer)</v>
+        <v>Ashleigh Dallas - Sail Away (Official Audio)</v>
       </c>
       <c r="B89" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=Srb2P9efFHY</v>
+        <v>https://www.youtube.com/watch?v=66PDbaI-BVA</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3760,10 +3760,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G89" t="str">
-        <v>1:14</v>
+        <v>3:57</v>
       </c>
       <c r="H89" t="str">
-        <v>Labrinth</v>
+        <v>Ashleigh Dallas</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,21 +3775,21 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Labrinth - God Spoke (Official Visualizer) - Labrinth</v>
+        <v>Ashleigh Dallas - Sail Away (Official Audio) - Ashleigh Dallas</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Official Audio)</v>
+        <v>Charlie Puth - Beat Yourself Up (Performance Video)</v>
       </c>
       <c r="B90" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=NvHXKIrBiR8</v>
+        <v>https://www.youtube.com/watch?v=4tmW_JSXHII</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -3798,7 +3798,7 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G90" t="str">
-        <v>2:59</v>
+        <v>3:03</v>
       </c>
       <c r="H90" t="str">
         <v>Charlie Puth</v>
@@ -3813,21 +3813,21 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Official Audio) - Charlie Puth</v>
+        <v>Charlie Puth - Beat Yourself Up (Performance Video) - Charlie Puth</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Girl Tones - Volcano (Visualizer)</v>
+        <v>Chappell Roan - The Subway (Live from Kansas City)</v>
       </c>
       <c r="B91" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=D2-t5SDV1IE</v>
+        <v>https://www.youtube.com/watch?v=6kZVtF8iaWw</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -3836,10 +3836,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G91" t="str">
-        <v>2:29</v>
+        <v>4:27</v>
       </c>
       <c r="H91" t="str">
-        <v>Girl Tones</v>
+        <v>Chappell Roan</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,21 +3851,21 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Girl Tones - Volcano (Visualizer) - Girl Tones</v>
+        <v>Chappell Roan - The Subway (Live from Kansas City) - Chappell Roan</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer)</v>
+        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar)</v>
       </c>
       <c r="B92" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=BouRN2QuXV8</v>
+        <v>https://www.youtube.com/watch?v=guUvgEKkk1U</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -3874,10 +3874,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G92" t="str">
-        <v>2:34</v>
+        <v>4:34</v>
       </c>
       <c r="H92" t="str">
-        <v>Jagwar Twin</v>
+        <v>Armik</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,21 +3889,21 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer) - Jagwar Twin</v>
+        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video)</v>
+        <v>LØLØ - 007 (Official Music Video)</v>
       </c>
       <c r="B93" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=IyPD6AnWlRg</v>
+        <v>https://www.youtube.com/watch?v=4okJouEbZ_s</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E93" t="str">
         <v/>
@@ -3912,10 +3912,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G93" t="str">
-        <v>3:48</v>
+        <v>2:54</v>
       </c>
       <c r="H93" t="str">
-        <v>Caroline Jones</v>
+        <v>LØLØ</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,21 +3927,21 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video) - Caroline Jones</v>
+        <v>LØLØ - 007 (Official Music Video) - LØLØ</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>The Beaches - I Ran (So Far Away) Official Audio</v>
+        <v>Tenille Townes - enabling (Official Visualizer)</v>
       </c>
       <c r="B94" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=7_i2R-EU-Eg</v>
+        <v>https://www.youtube.com/watch?v=yL_TxDF8WtI</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E94" t="str">
         <v/>
@@ -3950,10 +3950,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G94" t="str">
-        <v>3:32</v>
+        <v>3:25</v>
       </c>
       <c r="H94" t="str">
-        <v>The Beaches</v>
+        <v>Tenille Townes</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,21 +3965,21 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>The Beaches - I Ran (So Far Away) Official Audio - The Beaches</v>
+        <v>Tenille Townes - enabling (Official Visualizer) - Tenille Townes</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba</v>
+        <v>Alan Walker - Not Home (Official Lyric Video)</v>
       </c>
       <c r="B95" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=McaD2PG8jOE</v>
+        <v>https://www.youtube.com/watch?v=0m45tTheoCs</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E95" t="str">
         <v/>
@@ -3988,10 +3988,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G95" t="str">
-        <v>3:49</v>
+        <v>2:01</v>
       </c>
       <c r="H95" t="str">
-        <v>Dolly Parton</v>
+        <v>Alan Walker</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,21 +4003,21 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba - Dolly Parton</v>
+        <v>Alan Walker - Not Home (Official Lyric Video) - Alan Walker</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Madison Beer - bad enough (Official Music Video)</v>
+        <v>Charli xcx - Wall of Sound (Official Audio)</v>
       </c>
       <c r="B96" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=07SeT_QSJ08</v>
+        <v>https://www.youtube.com/watch?v=AHm1i212UP4</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E96" t="str">
         <v/>
@@ -4026,10 +4026,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G96" t="str">
-        <v>4:28</v>
+        <v>2:25</v>
       </c>
       <c r="H96" t="str">
-        <v>Madison Beer</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,21 +4041,21 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Madison Beer - bad enough (Official Music Video) - Madison Beer</v>
+        <v>Charli xcx - Wall of Sound (Official Audio) - Charli xcx</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Ty Myers - Message to You (Official Video)</v>
+        <v>Labrinth - God Spoke (Official Visualizer)</v>
       </c>
       <c r="B97" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=mhw8eAtgnRk</v>
+        <v>https://www.youtube.com/watch?v=Srb2P9efFHY</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E97" t="str">
         <v/>
@@ -4064,10 +4064,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G97" t="str">
-        <v>3:37</v>
+        <v>1:14</v>
       </c>
       <c r="H97" t="str">
-        <v>Ty Myers</v>
+        <v>Labrinth</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,21 +4079,21 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Ty Myers - Message to You (Official Video) - Ty Myers</v>
+        <v>Labrinth - God Spoke (Official Visualizer) - Labrinth</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Megan Moroney - Wish I Didn't (Official Video)</v>
+        <v>Charlie Puth - Beat Yourself Up (Official Audio)</v>
       </c>
       <c r="B98" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=plbNzv3KvWs</v>
+        <v>https://www.youtube.com/watch?v=NvHXKIrBiR8</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E98" t="str">
         <v/>
@@ -4102,10 +4102,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G98" t="str">
-        <v>3:35</v>
+        <v>2:59</v>
       </c>
       <c r="H98" t="str">
-        <v>Megan Moroney</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,21 +4117,21 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Megan Moroney - Wish I Didn't (Official Video) - Megan Moroney</v>
+        <v>Charlie Puth - Beat Yourself Up (Official Audio) - Charlie Puth</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Julia Cole - What Could Go Wrong (Official Lyric Video)</v>
+        <v>Girl Tones - Volcano (Visualizer)</v>
       </c>
       <c r="B99" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=GSkO7B_RbQE</v>
+        <v>https://www.youtube.com/watch?v=D2-t5SDV1IE</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E99" t="str">
         <v/>
@@ -4140,10 +4140,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G99" t="str">
-        <v>2:31</v>
+        <v>2:29</v>
       </c>
       <c r="H99" t="str">
-        <v>Julia Cole Music</v>
+        <v>Girl Tones</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,21 +4155,21 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Julia Cole - What Could Go Wrong (Official Lyric Video) - Julia Cole Music</v>
+        <v>Girl Tones - Volcano (Visualizer) - Girl Tones</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Lily Allen - Sleepwalking (Live on SNL)</v>
+        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer)</v>
       </c>
       <c r="B100" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=vH5ewjAQfNc</v>
+        <v>https://www.youtube.com/watch?v=BouRN2QuXV8</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E100" t="str">
         <v/>
@@ -4178,10 +4178,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G100" t="str">
-        <v>3:21</v>
+        <v>2:34</v>
       </c>
       <c r="H100" t="str">
-        <v>Lily Allen</v>
+        <v>Jagwar Twin</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,21 +4193,21 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Lily Allen - Sleepwalking (Live on SNL) - Lily Allen</v>
+        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer) - Jagwar Twin</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios)</v>
+        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video)</v>
       </c>
       <c r="B101" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=R0vVYP8tSIw</v>
+        <v>https://www.youtube.com/watch?v=IyPD6AnWlRg</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E101" t="str">
         <v/>
@@ -4216,10 +4216,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G101" t="str">
-        <v>5:24</v>
+        <v>3:48</v>
       </c>
       <c r="H101" t="str">
-        <v>Nickless</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,7 +4231,7 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios) - Nickless</v>
+        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="102">
@@ -4245,7 +4245,7 @@
         <v>https://music.apple.com/us/song/heaven/1862570892</v>
       </c>
       <c r="D102" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E102" t="str">
         <v/>
@@ -4283,7 +4283,7 @@
         <v>https://music.apple.com/us/song/body/1871258331</v>
       </c>
       <c r="D103" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E103" t="str">
         <v/>
@@ -4321,7 +4321,7 @@
         <v>https://music.apple.com/us/song/dandelion/1869436838</v>
       </c>
       <c r="D104" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E104" t="str">
         <v/>
@@ -4359,7 +4359,7 @@
         <v>https://music.apple.com/us/song/lights-go-out/1870833473</v>
       </c>
       <c r="D105" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E105" t="str">
         <v/>
@@ -4397,7 +4397,7 @@
         <v>https://music.apple.com/us/song/the-great-divide/1872239886</v>
       </c>
       <c r="D106" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E106" t="str">
         <v/>
@@ -4435,7 +4435,7 @@
         <v>https://music.apple.com/us/song/trist%C3%B3n/1872585947</v>
       </c>
       <c r="D107" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E107" t="str">
         <v/>
@@ -4473,7 +4473,7 @@
         <v>https://music.apple.com/us/song/feed-the-streets/1869462051</v>
       </c>
       <c r="D108" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E108" t="str">
         <v/>
@@ -4511,7 +4511,7 @@
         <v>https://music.apple.com/us/song/i-did-this-to-myself/1861531672</v>
       </c>
       <c r="D109" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E109" t="str">
         <v/>
@@ -4549,7 +4549,7 @@
         <v>https://music.apple.com/us/song/for-hire/1870722567</v>
       </c>
       <c r="D110" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E110" t="str">
         <v/>
@@ -4587,7 +4587,7 @@
         <v>https://music.apple.com/us/song/mcarthur/1871231844</v>
       </c>
       <c r="D111" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E111" t="str">
         <v/>
@@ -4625,7 +4625,7 @@
         <v>https://music.apple.com/us/song/debris/1853069633</v>
       </c>
       <c r="D112" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E112" t="str">
         <v/>
@@ -4663,7 +4663,7 @@
         <v>https://music.apple.com/us/song/god-owes-me-money-live-at-apple-music-radio/1871521120</v>
       </c>
       <c r="D113" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E113" t="str">
         <v/>
@@ -4701,7 +4701,7 @@
         <v>https://music.apple.com/us/song/rockstar-raging-feat-swae-lee/1873028187</v>
       </c>
       <c r="D114" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E114" t="str">
         <v/>
@@ -4739,7 +4739,7 @@
         <v>https://music.apple.com/us/song/1-1/1870378316</v>
       </c>
       <c r="D115" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E115" t="str">
         <v/>
@@ -4777,7 +4777,7 @@
         <v>https://music.apple.com/us/song/still-sincere-feat-pinkpantheress/1862228374</v>
       </c>
       <c r="D116" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E116" t="str">
         <v/>
@@ -4815,7 +4815,7 @@
         <v>https://music.apple.com/us/song/two-car-garage/1869137588</v>
       </c>
       <c r="D117" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E117" t="str">
         <v/>
@@ -4853,7 +4853,7 @@
         <v>https://music.apple.com/us/song/fml/1872686260</v>
       </c>
       <c r="D118" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E118" t="str">
         <v/>
@@ -4891,7 +4891,7 @@
         <v>https://music.apple.com/us/song/faked-it-all-the-time/1871050032</v>
       </c>
       <c r="D119" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E119" t="str">
         <v/>
@@ -4929,7 +4929,7 @@
         <v>https://music.apple.com/us/song/house-of-the-rising-sun/1872111857</v>
       </c>
       <c r="D120" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E120" t="str">
         <v/>
@@ -4967,7 +4967,7 @@
         <v>https://music.apple.com/us/song/lorelei/1867640808</v>
       </c>
       <c r="D121" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E121" t="str">
         <v/>
@@ -5005,7 +5005,7 @@
         <v>https://music.apple.com/us/song/free/1870703329</v>
       </c>
       <c r="D122" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E122" t="str">
         <v/>
@@ -5043,7 +5043,7 @@
         <v>https://music.apple.com/us/song/assignment/1872764440</v>
       </c>
       <c r="D123" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E123" t="str">
         <v/>
@@ -5081,7 +5081,7 @@
         <v>https://music.apple.com/us/song/professional-heartbreaker/1871053476</v>
       </c>
       <c r="D124" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E124" t="str">
         <v/>
@@ -5119,7 +5119,7 @@
         <v>https://music.apple.com/us/song/tell-me-what-you-want/1871463892</v>
       </c>
       <c r="D125" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E125" t="str">
         <v/>
@@ -5157,7 +5157,7 @@
         <v>https://music.apple.com/us/song/aguas/1869455857</v>
       </c>
       <c r="D126" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E126" t="str">
         <v/>
@@ -5195,7 +5195,7 @@
         <v>https://music.apple.com/us/song/ants-in-my-room/1870967813</v>
       </c>
       <c r="D127" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E127" t="str">
         <v/>
@@ -5233,7 +5233,7 @@
         <v>https://music.apple.com/us/song/baddie/1849760827</v>
       </c>
       <c r="D128" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E128" t="str">
         <v/>
@@ -5271,7 +5271,7 @@
         <v>https://music.apple.com/us/song/what-you-need-a-colors-show/1870990925</v>
       </c>
       <c r="D129" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E129" t="str">
         <v/>
@@ -5309,7 +5309,7 @@
         <v>https://music.apple.com/us/song/ok-ok-hamdi-remix/1871538130</v>
       </c>
       <c r="D130" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E130" t="str">
         <v/>
@@ -5347,7 +5347,7 @@
         <v>https://music.apple.com/us/song/ever-and-ever-before-feat-m%C5%8Driah-courtney/1869383260</v>
       </c>
       <c r="D131" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E131" t="str">
         <v/>
@@ -5385,7 +5385,7 @@
         <v>https://music.apple.com/us/song/for-the-first-time-again/1834736723</v>
       </c>
       <c r="D132" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E132" t="str">
         <v/>
@@ -5423,7 +5423,7 @@
         <v>https://music.apple.com/us/song/liars-tale/1862207951</v>
       </c>
       <c r="D133" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E133" t="str">
         <v/>
@@ -5461,7 +5461,7 @@
         <v>https://music.apple.com/us/song/afraid-of-the-dark/1872184048</v>
       </c>
       <c r="D134" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E134" t="str">
         <v/>
@@ -5499,7 +5499,7 @@
         <v>https://music.apple.com/us/song/wake-up-calling/1862338150</v>
       </c>
       <c r="D135" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E135" t="str">
         <v/>
@@ -5537,7 +5537,7 @@
         <v>https://music.apple.com/us/song/high/1867202644</v>
       </c>
       <c r="D136" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E136" t="str">
         <v/>
@@ -5575,7 +5575,7 @@
         <v>https://music.apple.com/us/song/villain/1860126455</v>
       </c>
       <c r="D137" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E137" t="str">
         <v/>
@@ -5613,7 +5613,7 @@
         <v>https://music.apple.com/us/song/bad-idea-right/1869792549</v>
       </c>
       <c r="D138" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E138" t="str">
         <v/>
@@ -5651,7 +5651,7 @@
         <v>https://music.apple.com/us/song/residue/1863786787</v>
       </c>
       <c r="D139" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E139" t="str">
         <v/>
@@ -5689,7 +5689,7 @@
         <v>https://music.apple.com/us/song/i-used-to-go-to-this-bar/1839918872</v>
       </c>
       <c r="D140" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E140" t="str">
         <v/>
@@ -5727,7 +5727,7 @@
         <v>https://music.apple.com/us/song/starlight/1870989674</v>
       </c>
       <c r="D141" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E141" t="str">
         <v/>
@@ -5765,7 +5765,7 @@
         <v>https://music.apple.com/us/song/dandelion/1863154133</v>
       </c>
       <c r="D142" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E142" t="str">
         <v/>
@@ -5803,7 +5803,7 @@
         <v>https://music.apple.com/us/song/themselves/1845287173</v>
       </c>
       <c r="D143" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E143" t="str">
         <v/>
@@ -5841,7 +5841,7 @@
         <v>https://music.apple.com/us/song/high-maintenance/1872497656</v>
       </c>
       <c r="D144" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E144" t="str">
         <v/>
@@ -5879,7 +5879,7 @@
         <v>https://music.apple.com/us/song/trackhawk/1860991724</v>
       </c>
       <c r="D145" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E145" t="str">
         <v/>
@@ -5917,7 +5917,7 @@
         <v>https://music.apple.com/us/song/wheel-man/1872178895</v>
       </c>
       <c r="D146" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E146" t="str">
         <v/>
@@ -5955,7 +5955,7 @@
         <v>https://music.apple.com/us/song/natural-disaster/1871263211</v>
       </c>
       <c r="D147" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E147" t="str">
         <v/>
@@ -5993,7 +5993,7 @@
         <v>https://music.apple.com/us/song/prettier/1869745409</v>
       </c>
       <c r="D148" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E148" t="str">
         <v/>
@@ -6031,7 +6031,7 @@
         <v>https://music.apple.com/us/song/shotta-flow-8/1872760524</v>
       </c>
       <c r="D149" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E149" t="str">
         <v/>
@@ -6069,7 +6069,7 @@
         <v>https://music.apple.com/us/song/die-to-fall/1866902681</v>
       </c>
       <c r="D150" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E150" t="str">
         <v/>
@@ -6107,7 +6107,7 @@
         <v>https://music.apple.com/us/song/the-cruel-angels-thesis-neon-genesis-evangelion/1864932139</v>
       </c>
       <c r="D151" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E151" t="str">
         <v/>
@@ -6145,7 +6145,7 @@
         <v>https://music.apple.com/us/song/slow-burn/1851033862</v>
       </c>
       <c r="D152" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E152" t="str">
         <v/>
@@ -6183,7 +6183,7 @@
         <v>https://music.apple.com/us/song/too-late/1857999860</v>
       </c>
       <c r="D153" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E153" t="str">
         <v/>
@@ -6221,7 +6221,7 @@
         <v>https://music.apple.com/us/song/mono-feat-skaiwater/1869130804</v>
       </c>
       <c r="D154" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E154" t="str">
         <v/>
@@ -6259,7 +6259,7 @@
         <v>https://music.apple.com/us/song/thank-you-is-enough/1870679042</v>
       </c>
       <c r="D155" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E155" t="str">
         <v/>
@@ -6297,7 +6297,7 @@
         <v>https://music.apple.com/us/song/ridin/1869786726</v>
       </c>
       <c r="D156" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E156" t="str">
         <v/>
@@ -6335,7 +6335,7 @@
         <v>https://music.apple.com/us/song/possession/1872536200</v>
       </c>
       <c r="D157" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E157" t="str">
         <v/>
@@ -6373,7 +6373,7 @@
         <v>https://music.apple.com/us/song/poema/1872723644</v>
       </c>
       <c r="D158" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E158" t="str">
         <v/>
@@ -6411,7 +6411,7 @@
         <v>https://music.apple.com/us/song/live-without/1862777625</v>
       </c>
       <c r="D159" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E159" t="str">
         <v/>
@@ -6449,7 +6449,7 @@
         <v>https://music.apple.com/us/song/fan%C3%A1tico/1871611852</v>
       </c>
       <c r="D160" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E160" t="str">
         <v/>
@@ -6487,7 +6487,7 @@
         <v>https://music.apple.com/us/song/frozen-lake/1867287070</v>
       </c>
       <c r="D161" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E161" t="str">
         <v/>
@@ -6525,7 +6525,7 @@
         <v>https://music.apple.com/us/song/fine-shyt-eb-remix-feat-eric-bellinger/1870964385</v>
       </c>
       <c r="D162" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E162" t="str">
         <v/>
@@ -6563,7 +6563,7 @@
         <v>https://music.apple.com/us/song/hell-yeah-feat-waxmaster/1866602820</v>
       </c>
       <c r="D163" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E163" t="str">
         <v/>
@@ -6601,7 +6601,7 @@
         <v>https://music.apple.com/us/song/its-like-that/1858689757</v>
       </c>
       <c r="D164" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E164" t="str">
         <v/>
@@ -6639,7 +6639,7 @@
         <v>https://music.apple.com/us/song/a-s-a-p/1833414737</v>
       </c>
       <c r="D165" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E165" t="str">
         <v/>
@@ -6677,7 +6677,7 @@
         <v>https://music.apple.com/us/song/once-i-say/1867855025</v>
       </c>
       <c r="D166" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E166" t="str">
         <v/>
@@ -6715,7 +6715,7 @@
         <v>https://music.apple.com/us/song/believer/1862797080</v>
       </c>
       <c r="D167" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E167" t="str">
         <v/>
@@ -6753,7 +6753,7 @@
         <v>https://music.apple.com/us/song/i-envy-the-wind/1863202477</v>
       </c>
       <c r="D168" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E168" t="str">
         <v/>
@@ -6791,7 +6791,7 @@
         <v>https://music.apple.com/us/song/the-alchemist/1831827347</v>
       </c>
       <c r="D169" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E169" t="str">
         <v/>
@@ -6829,7 +6829,7 @@
         <v>https://music.apple.com/us/song/daysa/1861575845</v>
       </c>
       <c r="D170" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E170" t="str">
         <v/>
@@ -6867,7 +6867,7 @@
         <v>https://music.apple.com/us/song/fabulous/1862804005</v>
       </c>
       <c r="D171" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E171" t="str">
         <v/>
@@ -6905,7 +6905,7 @@
         <v>https://music.apple.com/us/song/me-asusta-amar-tanto-la-soledad/1866982109</v>
       </c>
       <c r="D172" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E172" t="str">
         <v/>
@@ -6943,7 +6943,7 @@
         <v>https://music.apple.com/us/song/brainchem/1870656942</v>
       </c>
       <c r="D173" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E173" t="str">
         <v/>
@@ -6981,7 +6981,7 @@
         <v>https://music.apple.com/us/song/boyfriend-in-yo-brain-notice-me/1871675026</v>
       </c>
       <c r="D174" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E174" t="str">
         <v/>
@@ -7019,7 +7019,7 @@
         <v>https://music.apple.com/us/song/giants/1869154957</v>
       </c>
       <c r="D175" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E175" t="str">
         <v/>
@@ -7057,7 +7057,7 @@
         <v>https://music.apple.com/us/song/scooby/1872510752</v>
       </c>
       <c r="D176" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E176" t="str">
         <v/>
@@ -7095,7 +7095,7 @@
         <v>https://music.apple.com/us/song/la-racha/1868757762</v>
       </c>
       <c r="D177" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E177" t="str">
         <v/>
@@ -7133,7 +7133,7 @@
         <v>https://music.apple.com/us/song/so-am-i/1867012209</v>
       </c>
       <c r="D178" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E178" t="str">
         <v/>
@@ -7171,7 +7171,7 @@
         <v>https://music.apple.com/us/song/best-thing/1860673616</v>
       </c>
       <c r="D179" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E179" t="str">
         <v/>
@@ -7209,7 +7209,7 @@
         <v>https://music.apple.com/us/song/count-it-back/1855219865</v>
       </c>
       <c r="D180" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E180" t="str">
         <v/>
@@ -7247,7 +7247,7 @@
         <v>https://music.apple.com/us/song/good-girl/1862640697</v>
       </c>
       <c r="D181" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E181" t="str">
         <v/>
@@ -7285,7 +7285,7 @@
         <v>https://music.apple.com/us/song/my-revival/1869465104</v>
       </c>
       <c r="D182" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E182" t="str">
         <v/>
@@ -7323,7 +7323,7 @@
         <v>https://music.apple.com/us/song/run-my-way/1860964996</v>
       </c>
       <c r="D183" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E183" t="str">
         <v/>
@@ -7361,7 +7361,7 @@
         <v>https://music.apple.com/us/song/cold-night/1867687787</v>
       </c>
       <c r="D184" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E184" t="str">
         <v/>
@@ -7399,7 +7399,7 @@
         <v>https://music.apple.com/us/song/away-with-the-fairies/1870603474</v>
       </c>
       <c r="D185" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E185" t="str">
         <v/>
@@ -7437,7 +7437,7 @@
         <v>https://music.apple.com/us/song/fragile/1866957569</v>
       </c>
       <c r="D186" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E186" t="str">
         <v/>
@@ -7475,7 +7475,7 @@
         <v>https://music.apple.com/us/song/slow-dancin/1871537173</v>
       </c>
       <c r="D187" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E187" t="str">
         <v/>
@@ -7513,7 +7513,7 @@
         <v>https://music.apple.com/us/song/never-kissed-a-cowboy/1866744530</v>
       </c>
       <c r="D188" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E188" t="str">
         <v/>
@@ -7551,7 +7551,7 @@
         <v>https://music.apple.com/us/song/more-of-what-matters/1871592720</v>
       </c>
       <c r="D189" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E189" t="str">
         <v/>
@@ -7589,7 +7589,7 @@
         <v>https://music.apple.com/us/song/is-this-the-real-you/1869323368</v>
       </c>
       <c r="D190" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E190" t="str">
         <v/>
@@ -7627,7 +7627,7 @@
         <v>https://music.apple.com/us/song/hud/1842015019</v>
       </c>
       <c r="D191" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E191" t="str">
         <v/>
@@ -7665,7 +7665,7 @@
         <v>https://music.apple.com/us/song/ego-death/1867855427</v>
       </c>
       <c r="D192" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E192" t="str">
         <v/>
@@ -7703,7 +7703,7 @@
         <v>https://music.apple.com/us/song/gas-station-love-remix/1872150728</v>
       </c>
       <c r="D193" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E193" t="str">
         <v/>
@@ -7741,7 +7741,7 @@
         <v>https://music.apple.com/us/song/disappear/1861907311</v>
       </c>
       <c r="D194" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E194" t="str">
         <v/>
@@ -7779,7 +7779,7 @@
         <v>https://music.apple.com/us/song/misbehave/1859630128</v>
       </c>
       <c r="D195" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E195" t="str">
         <v/>
@@ -7817,7 +7817,7 @@
         <v>https://music.apple.com/us/song/club-bizarre/1870355078</v>
       </c>
       <c r="D196" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E196" t="str">
         <v/>
@@ -7855,7 +7855,7 @@
         <v>https://music.apple.com/us/song/fly/1867903625</v>
       </c>
       <c r="D197" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E197" t="str">
         <v/>
@@ -7893,7 +7893,7 @@
         <v>https://music.apple.com/us/song/ily-anyway/1870369432</v>
       </c>
       <c r="D198" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E198" t="str">
         <v/>
@@ -7931,7 +7931,7 @@
         <v>https://music.apple.com/us/song/george-jones-feat-angela-autumn/1867306007</v>
       </c>
       <c r="D199" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E199" t="str">
         <v/>
@@ -7969,7 +7969,7 @@
         <v>https://music.apple.com/us/song/kiss-big/1837292261</v>
       </c>
       <c r="D200" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E200" t="str">
         <v/>
@@ -8007,7 +8007,7 @@
         <v>https://music.apple.com/us/song/praxis/1845253734</v>
       </c>
       <c r="D201" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E201" t="str">
         <v/>
@@ -8045,7 +8045,7 @@
         <v>https://music.apple.com/us/song/house/1866696487</v>
       </c>
       <c r="D202" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E202" t="str">
         <v/>
@@ -8083,7 +8083,7 @@
         <v>https://music.apple.com/us/song/cowboy-without-a-clue/1834024322</v>
       </c>
       <c r="D203" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E203" t="str">
         <v/>
@@ -8121,7 +8121,7 @@
         <v>https://music.apple.com/us/song/brincar/1871554907</v>
       </c>
       <c r="D204" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E204" t="str">
         <v/>
@@ -8159,7 +8159,7 @@
         <v>https://music.apple.com/us/song/qui%C3%A9n/1870329662</v>
       </c>
       <c r="D205" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E205" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
@@ -439,7 +439,7 @@
         <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Studio)</v>
       </c>
       <c r="B2" t="str">
-        <v>4 hours ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=mgsdQI-GVMM</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>4 hours ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:19</v>
@@ -477,7 +477,7 @@
         <v>Vera Blue - Hold (Live on Sydney Harbour)</v>
       </c>
       <c r="B3" t="str">
-        <v>5 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=SYEwk-EZJPU</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>5 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>3:37</v>
@@ -515,7 +515,7 @@
         <v>Bob Moses - Need You Tonight (INXS Cover) - Brooklyn Mirage 2023</v>
       </c>
       <c r="B4" t="str">
-        <v>6 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=CoCqPwDIBOA</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>6 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>3:08</v>
@@ -553,7 +553,7 @@
         <v>Marc Anthony - Un Mal Sueño (Visualizer)</v>
       </c>
       <c r="B5" t="str">
-        <v>7 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=18yZq5xtke4</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>7 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>3:28</v>
@@ -591,7 +591,7 @@
         <v>Marc Anthony - Contra La Corriente (Visualizer)</v>
       </c>
       <c r="B6" t="str">
-        <v>7 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=IGLmJ71oHhQ</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>7 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v>5:05</v>
@@ -629,7 +629,7 @@
         <v>Loreen - Feels Like Heaven</v>
       </c>
       <c r="B7" t="str">
-        <v>8 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=BQc97moyQBg</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>8 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G7" t="str">
         <v>3:14</v>
@@ -667,7 +667,7 @@
         <v>Take That - Once You've Tasted Love (Live on Pebble Mill, 1992)</v>
       </c>
       <c r="B8" t="str">
-        <v>9 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=dOeoDOueESk</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>9 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G8" t="str">
         <v>3:36</v>
@@ -705,7 +705,7 @@
         <v>Paul McCartney, Wings - Nineteen Hundred And Eighty Five (Visualiser)</v>
       </c>
       <c r="B9" t="str">
-        <v>8 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=a4AIjUHuWpU</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>8 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G9" t="str">
         <v>5:31</v>
@@ -743,7 +743,7 @@
         <v>Nothing But Thieves - Sorry (Official Audio)</v>
       </c>
       <c r="B10" t="str">
-        <v>11 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=D7QfVqo5YqY</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>11 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G10" t="str">
         <v>3:37</v>
@@ -3441,7 +3441,7 @@
         <v>Lauren Sanderson - SPELL IT OUT (Official Music Video)</v>
       </c>
       <c r="B81" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C81" t="str">
         <v>https://www.youtube.com/watch?v=kfF0bVZMCw0</v>
@@ -3453,7 +3453,7 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G81" t="str">
         <v>2:34</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
@@ -439,7 +439,7 @@
         <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Studio)</v>
       </c>
       <c r="B2" t="str">
-        <v>7 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=mgsdQI-GVMM</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>7 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:19</v>
@@ -477,7 +477,7 @@
         <v>Vera Blue - Hold (Live on Sydney Harbour)</v>
       </c>
       <c r="B3" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=SYEwk-EZJPU</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>3:37</v>
@@ -515,7 +515,7 @@
         <v>Bob Moses - Need You Tonight (INXS Cover) - Brooklyn Mirage 2023</v>
       </c>
       <c r="B4" t="str">
-        <v>9 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=CoCqPwDIBOA</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>9 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>3:08</v>
@@ -553,7 +553,7 @@
         <v>Marc Anthony - Un Mal Sueño (Visualizer)</v>
       </c>
       <c r="B5" t="str">
-        <v>9 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=18yZq5xtke4</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>9 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>3:28</v>
@@ -591,7 +591,7 @@
         <v>Marc Anthony - Contra La Corriente (Visualizer)</v>
       </c>
       <c r="B6" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=IGLmJ71oHhQ</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v>5:05</v>
@@ -629,7 +629,7 @@
         <v>Loreen - Feels Like Heaven</v>
       </c>
       <c r="B7" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=BQc97moyQBg</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G7" t="str">
         <v>3:14</v>
@@ -667,7 +667,7 @@
         <v>Take That - Once You've Tasted Love (Live on Pebble Mill, 1992)</v>
       </c>
       <c r="B8" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=dOeoDOueESk</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G8" t="str">
         <v>3:36</v>
@@ -705,7 +705,7 @@
         <v>Paul McCartney, Wings - Nineteen Hundred And Eighty Five (Visualiser)</v>
       </c>
       <c r="B9" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=a4AIjUHuWpU</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G9" t="str">
         <v>5:31</v>
@@ -743,7 +743,7 @@
         <v>Nothing But Thieves - Sorry (Official Audio)</v>
       </c>
       <c r="B10" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=D7QfVqo5YqY</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G10" t="str">
         <v>3:37</v>
@@ -1351,7 +1351,7 @@
         <v>Ella Langley - Dandelion (Official Visualizer)</v>
       </c>
       <c r="B26" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=sf6eRmInk1s</v>
@@ -1363,7 +1363,7 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G26" t="str">
         <v>4:01</v>
@@ -1389,7 +1389,7 @@
         <v>Dogpark - Dandelion (Official Music Video)</v>
       </c>
       <c r="B27" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C27" t="str">
         <v>https://www.youtube.com/watch?v=fv9prIYHHzk</v>
@@ -1401,7 +1401,7 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G27" t="str">
         <v>3:16</v>
@@ -1427,7 +1427,7 @@
         <v>Lauren Spencer Smith - Natural Disaster (Visualizer)</v>
       </c>
       <c r="B28" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=T9YvLA2cdZs</v>
@@ -1439,7 +1439,7 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G28" t="str">
         <v>3:03</v>
@@ -1465,7 +1465,7 @@
         <v>ERNEST - Lorelei (Official Music Video)</v>
       </c>
       <c r="B29" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=dPWc_6IdDJk</v>
@@ -1477,7 +1477,7 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G29" t="str">
         <v>2:41</v>
@@ -1503,7 +1503,7 @@
         <v>Labrinth - I Keep My Promises (Official Audio)</v>
       </c>
       <c r="B30" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=CV5rR9JZK-0</v>
@@ -1515,7 +1515,7 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G30" t="str">
         <v>3:05</v>
@@ -1541,7 +1541,7 @@
         <v>Grace VanderWaal - Prettier (Official Lyric Video)</v>
       </c>
       <c r="B31" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=9HwTj3NZ16E</v>
@@ -1553,7 +1553,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G31" t="str">
         <v>2:46</v>
@@ -1579,7 +1579,7 @@
         <v>VOILÀ - Frozen Lake (Official Lyric Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=Lmus-UbL1H0</v>
@@ -1591,7 +1591,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G32" t="str">
         <v>3:32</v>
@@ -1617,7 +1617,7 @@
         <v>Cannons - Starlight (Official Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C33" t="str">
         <v>https://www.youtube.com/watch?v=bu6WSMDDPGY</v>
@@ -1629,7 +1629,7 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G33" t="str">
         <v>3:42</v>
@@ -1655,7 +1655,7 @@
         <v>Kylie Morgan - Like My Own (Official Video)</v>
       </c>
       <c r="B34" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=zcYeoGBglC0</v>
@@ -1667,7 +1667,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G34" t="str">
         <v>2:38</v>
@@ -1693,7 +1693,7 @@
         <v>Lizzy McAlpine - House of the Rising Sun (Audio)</v>
       </c>
       <c r="B35" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=3igYRj82EiU</v>
@@ -1705,7 +1705,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G35" t="str">
         <v>3:10</v>
@@ -1731,7 +1731,7 @@
         <v>Willie Nelson - Heart Of America (From The Gray House Original Soundtrack)</v>
       </c>
       <c r="B36" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=0bhcO4Yphuo</v>
@@ -1743,7 +1743,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G36" t="str">
         <v>3:57</v>
@@ -1769,7 +1769,7 @@
         <v>Jeremy Camp - No Survivors (Live) ft. Skillet</v>
       </c>
       <c r="B37" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C37" t="str">
         <v>https://www.youtube.com/watch?v=Jjz1wFe5dMo</v>
@@ -1781,7 +1781,7 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G37" t="str">
         <v>2:19</v>
@@ -2757,7 +2757,7 @@
         <v>Bella White - Dream Song (Official Audio)</v>
       </c>
       <c r="B63" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C63" t="str">
         <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
@@ -2769,7 +2769,7 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G63" t="str">
         <v>4:37</v>
@@ -2795,7 +2795,7 @@
         <v>Ryan Wright - Film School Kids (Official Video)</v>
       </c>
       <c r="B64" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C64" t="str">
         <v>https://www.youtube.com/watch?v=pnAz9RwGSek</v>
@@ -2807,7 +2807,7 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G64" t="str">
         <v>4:06</v>
@@ -2833,7 +2833,7 @@
         <v>Dove Cameron - Do I Wanna Know? (Official Visualizer)</v>
       </c>
       <c r="B65" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C65" t="str">
         <v>https://www.youtube.com/watch?v=u7aPv2saz_I</v>
@@ -2845,7 +2845,7 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G65" t="str">
         <v>3:54</v>
@@ -2871,7 +2871,7 @@
         <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video)</v>
       </c>
       <c r="B66" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C66" t="str">
         <v>https://www.youtube.com/watch?v=WGb8KVdqs6k</v>
@@ -2883,7 +2883,7 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G66" t="str">
         <v>4:10</v>
@@ -2909,7 +2909,7 @@
         <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video)</v>
       </c>
       <c r="B67" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C67" t="str">
         <v>https://www.youtube.com/watch?v=X1ZeY4Y3l1M</v>
@@ -2921,7 +2921,7 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G67" t="str">
         <v>3:26</v>
@@ -2985,7 +2985,7 @@
         <v>Mitchell Tenpenny - You Phase (Official Music Video)</v>
       </c>
       <c r="B69" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C69" t="str">
         <v>https://www.youtube.com/watch?v=UPuK6wV5Zco</v>
@@ -2997,7 +2997,7 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G69" t="str">
         <v>2:56</v>
@@ -3023,7 +3023,7 @@
         <v>Tauren Wells - Breathe On It (Official Lyric Video)</v>
       </c>
       <c r="B70" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C70" t="str">
         <v>https://www.youtube.com/watch?v=9hW9sNMn2A0</v>
@@ -3035,7 +3035,7 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G70" t="str">
         <v>4:01</v>
@@ -3061,7 +3061,7 @@
         <v>Maiah Manser - Feeling it All (Official Music Video)</v>
       </c>
       <c r="B71" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C71" t="str">
         <v>https://www.youtube.com/watch?v=JMYvXleIwfU</v>
@@ -3073,7 +3073,7 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G71" t="str">
         <v>3:05</v>
@@ -3099,7 +3099,7 @@
         <v>Taylor Austin Dye - Man For That (Official Music Video)</v>
       </c>
       <c r="B72" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C72" t="str">
         <v>https://www.youtube.com/watch?v=vOzX-o11seI</v>
@@ -3111,7 +3111,7 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G72" t="str">
         <v>2:27</v>
@@ -3137,7 +3137,7 @@
         <v>Chelsea Cutler - BAD (Official Video)</v>
       </c>
       <c r="B73" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C73" t="str">
         <v>https://www.youtube.com/watch?v=86k4E6ydHVU</v>
@@ -3149,7 +3149,7 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G73" t="str">
         <v>2:34</v>
@@ -3175,7 +3175,7 @@
         <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video)</v>
       </c>
       <c r="B74" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C74" t="str">
         <v>https://www.youtube.com/watch?v=-UWIFAiOOPE</v>
@@ -3187,7 +3187,7 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G74" t="str">
         <v>3:13</v>
@@ -3213,7 +3213,7 @@
         <v>Louis Tomlinson - Dark To Light (Visualiser)</v>
       </c>
       <c r="B75" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C75" t="str">
         <v>https://www.youtube.com/watch?v=02QyA29poAM</v>
@@ -3225,7 +3225,7 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G75" t="str">
         <v>3:13</v>
@@ -3251,7 +3251,7 @@
         <v>CAIN - So Long Sad Songs (Lyric Video)</v>
       </c>
       <c r="B76" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C76" t="str">
         <v>https://www.youtube.com/watch?v=feOv8nufa_I</v>
@@ -3263,7 +3263,7 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G76" t="str">
         <v>3:08</v>
@@ -3555,7 +3555,7 @@
         <v>The Avett Brothers - Matrimony (Official Video)</v>
       </c>
       <c r="B84" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C84" t="str">
         <v>https://www.youtube.com/watch?v=7sD9-MtV9CY</v>
@@ -3567,7 +3567,7 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G84" t="str">
         <v>3:06</v>
@@ -3593,7 +3593,7 @@
         <v>Jordana Bryant - Love Like That (Official Video)</v>
       </c>
       <c r="B85" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C85" t="str">
         <v>https://www.youtube.com/watch?v=3ATlH-Rtzmk</v>
@@ -3605,7 +3605,7 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G85" t="str">
         <v>3:21</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
@@ -439,7 +439,7 @@
         <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Studio)</v>
       </c>
       <c r="B2" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=mgsdQI-GVMM</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:19</v>
@@ -477,7 +477,7 @@
         <v>Vera Blue - Hold (Live on Sydney Harbour)</v>
       </c>
       <c r="B3" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=SYEwk-EZJPU</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>3:37</v>
@@ -515,7 +515,7 @@
         <v>Bob Moses - Need You Tonight (INXS Cover) - Brooklyn Mirage 2023</v>
       </c>
       <c r="B4" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=CoCqPwDIBOA</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>3:08</v>
@@ -553,7 +553,7 @@
         <v>Marc Anthony - Un Mal Sueño (Visualizer)</v>
       </c>
       <c r="B5" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=18yZq5xtke4</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>3:28</v>
@@ -591,7 +591,7 @@
         <v>Marc Anthony - Contra La Corriente (Visualizer)</v>
       </c>
       <c r="B6" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=IGLmJ71oHhQ</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v>5:05</v>
@@ -629,7 +629,7 @@
         <v>Loreen - Feels Like Heaven</v>
       </c>
       <c r="B7" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=BQc97moyQBg</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G7" t="str">
         <v>3:14</v>
@@ -667,7 +667,7 @@
         <v>Take That - Once You've Tasted Love (Live on Pebble Mill, 1992)</v>
       </c>
       <c r="B8" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=dOeoDOueESk</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G8" t="str">
         <v>3:36</v>
@@ -705,7 +705,7 @@
         <v>Paul McCartney, Wings - Nineteen Hundred And Eighty Five (Visualiser)</v>
       </c>
       <c r="B9" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=a4AIjUHuWpU</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G9" t="str">
         <v>5:31</v>
@@ -743,7 +743,7 @@
         <v>Nothing But Thieves - Sorry (Official Audio)</v>
       </c>
       <c r="B10" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=D7QfVqo5YqY</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="G10" t="str">
         <v>3:37</v>
@@ -1313,7 +1313,7 @@
         <v>SANTOS BRAVOS “KAWASAKI” Performance Video</v>
       </c>
       <c r="B25" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=Cmy8CsYIUL0</v>
@@ -1325,7 +1325,7 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G25" t="str">
         <v>2:41</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
@@ -439,7 +439,7 @@
         <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Studio)</v>
       </c>
       <c r="B2" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=mgsdQI-GVMM</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:19</v>
@@ -477,7 +477,7 @@
         <v>Vera Blue - Hold (Live on Sydney Harbour)</v>
       </c>
       <c r="B3" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=SYEwk-EZJPU</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>3:37</v>
@@ -515,7 +515,7 @@
         <v>Bob Moses - Need You Tonight (INXS Cover) - Brooklyn Mirage 2023</v>
       </c>
       <c r="B4" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=CoCqPwDIBOA</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>3:08</v>
@@ -553,7 +553,7 @@
         <v>Marc Anthony - Un Mal Sueño (Visualizer)</v>
       </c>
       <c r="B5" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=18yZq5xtke4</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>3:28</v>
@@ -591,7 +591,7 @@
         <v>Marc Anthony - Contra La Corriente (Visualizer)</v>
       </c>
       <c r="B6" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=IGLmJ71oHhQ</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v>5:05</v>
@@ -629,7 +629,7 @@
         <v>Loreen - Feels Like Heaven</v>
       </c>
       <c r="B7" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=BQc97moyQBg</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G7" t="str">
         <v>3:14</v>
@@ -667,7 +667,7 @@
         <v>Take That - Once You've Tasted Love (Live on Pebble Mill, 1992)</v>
       </c>
       <c r="B8" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=dOeoDOueESk</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G8" t="str">
         <v>3:36</v>
@@ -705,7 +705,7 @@
         <v>Paul McCartney, Wings - Nineteen Hundred And Eighty Five (Visualiser)</v>
       </c>
       <c r="B9" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=a4AIjUHuWpU</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G9" t="str">
         <v>5:31</v>
@@ -743,7 +743,7 @@
         <v>Nothing But Thieves - Sorry (Official Audio)</v>
       </c>
       <c r="B10" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=D7QfVqo5YqY</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G10" t="str">
         <v>3:37</v>
@@ -1237,7 +1237,7 @@
         <v>Katelyn Tarver - So Am I (Official Music Video)</v>
       </c>
       <c r="B23" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=MjUiVPzMQHw</v>
@@ -1249,7 +1249,7 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G23" t="str">
         <v>2:52</v>
@@ -1275,7 +1275,7 @@
         <v>David Guetta, TeddySwims, Tones And I - Gone Gone Gone (Unplugged) [Visualizer]</v>
       </c>
       <c r="B24" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=eWglDE7O5r8</v>
@@ -1287,7 +1287,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G24" t="str">
         <v>3:33</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
@@ -439,7 +439,7 @@
         <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Studio)</v>
       </c>
       <c r="B2" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=mgsdQI-GVMM</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:19</v>
@@ -477,7 +477,7 @@
         <v>Vera Blue - Hold (Live on Sydney Harbour)</v>
       </c>
       <c r="B3" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=SYEwk-EZJPU</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>3:37</v>
@@ -515,7 +515,7 @@
         <v>Bob Moses - Need You Tonight (INXS Cover) - Brooklyn Mirage 2023</v>
       </c>
       <c r="B4" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=CoCqPwDIBOA</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>3:08</v>
@@ -553,7 +553,7 @@
         <v>Marc Anthony - Un Mal Sueño (Visualizer)</v>
       </c>
       <c r="B5" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=18yZq5xtke4</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>3:28</v>
@@ -591,7 +591,7 @@
         <v>Marc Anthony - Contra La Corriente (Visualizer)</v>
       </c>
       <c r="B6" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=IGLmJ71oHhQ</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v>5:05</v>
@@ -629,7 +629,7 @@
         <v>Loreen - Feels Like Heaven</v>
       </c>
       <c r="B7" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=BQc97moyQBg</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G7" t="str">
         <v>3:14</v>
@@ -667,7 +667,7 @@
         <v>Take That - Once You've Tasted Love (Live on Pebble Mill, 1992)</v>
       </c>
       <c r="B8" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=dOeoDOueESk</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="G8" t="str">
         <v>3:36</v>
@@ -705,7 +705,7 @@
         <v>Paul McCartney, Wings - Nineteen Hundred And Eighty Five (Visualiser)</v>
       </c>
       <c r="B9" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=a4AIjUHuWpU</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G9" t="str">
         <v>5:31</v>
@@ -743,7 +743,7 @@
         <v>Nothing But Thieves - Sorry (Official Audio)</v>
       </c>
       <c r="B10" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=D7QfVqo5YqY</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G10" t="str">
         <v>3:37</v>
@@ -895,7 +895,7 @@
         <v>Jessie Ware - I Could Get Used To This (Live on The Graham Norton Show)</v>
       </c>
       <c r="B14" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=kGeamxRf8Gw</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G14" t="str">
         <v>3:50</v>
@@ -1161,7 +1161,7 @@
         <v>Zara Larsson - Lush Life (Official UGC Compilation Video)</v>
       </c>
       <c r="B21" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=FgAyfRnbbRs</v>
@@ -1173,7 +1173,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G21" t="str">
         <v>3:22</v>
@@ -1199,7 +1199,7 @@
         <v>Only The Poets - Monumental</v>
       </c>
       <c r="B22" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=nwXiAjjl6NE</v>
@@ -1211,7 +1211,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G22" t="str">
         <v>2:48</v>
@@ -2301,7 +2301,7 @@
         <v>We Three - Drunk Driving (Official Music Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C51" t="str">
         <v>https://www.youtube.com/watch?v=BTqRGxSX6AQ</v>
@@ -2313,7 +2313,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G51" t="str">
         <v>4:27</v>
@@ -2602,7 +2602,7 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
+        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992</v>
       </c>
       <c r="B59" t="str">
         <v>10 days ago</v>
@@ -2635,7 +2635,7 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
+        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992 - OfficiallyExtreme</v>
       </c>
     </row>
     <row r="60">
@@ -2719,7 +2719,7 @@
         <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
       </c>
       <c r="B62" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C62" t="str">
         <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
@@ -2731,7 +2731,7 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G62" t="str">
         <v>3:46</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
@@ -439,7 +439,7 @@
         <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Studio)</v>
       </c>
       <c r="B2" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=mgsdQI-GVMM</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:19</v>
@@ -477,7 +477,7 @@
         <v>Vera Blue - Hold (Live on Sydney Harbour)</v>
       </c>
       <c r="B3" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=SYEwk-EZJPU</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>3:37</v>
@@ -515,7 +515,7 @@
         <v>Bob Moses - Need You Tonight (INXS Cover) - Brooklyn Mirage 2023</v>
       </c>
       <c r="B4" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=CoCqPwDIBOA</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>3:08</v>
@@ -553,7 +553,7 @@
         <v>Marc Anthony - Un Mal Sueño (Visualizer)</v>
       </c>
       <c r="B5" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=18yZq5xtke4</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>3:28</v>
@@ -591,7 +591,7 @@
         <v>Marc Anthony - Contra La Corriente (Visualizer)</v>
       </c>
       <c r="B6" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=IGLmJ71oHhQ</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v>5:05</v>
@@ -629,7 +629,7 @@
         <v>Loreen - Feels Like Heaven</v>
       </c>
       <c r="B7" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=BQc97moyQBg</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="G7" t="str">
         <v>3:14</v>
@@ -667,7 +667,7 @@
         <v>Take That - Once You've Tasted Love (Live on Pebble Mill, 1992)</v>
       </c>
       <c r="B8" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=dOeoDOueESk</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G8" t="str">
         <v>3:36</v>
@@ -705,7 +705,7 @@
         <v>Paul McCartney, Wings - Nineteen Hundred And Eighty Five (Visualiser)</v>
       </c>
       <c r="B9" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=a4AIjUHuWpU</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="G9" t="str">
         <v>5:31</v>
@@ -743,7 +743,7 @@
         <v>Nothing But Thieves - Sorry (Official Audio)</v>
       </c>
       <c r="B10" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=D7QfVqo5YqY</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="G10" t="str">
         <v>3:37</v>
@@ -1123,7 +1123,7 @@
         <v>Paris Paloma - Good Girl [Official Music Video]</v>
       </c>
       <c r="B20" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=qhO6VMC-nx0</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G20" t="str">
         <v>4:47</v>
@@ -2602,7 +2602,7 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
       </c>
       <c r="B59" t="str">
         <v>10 days ago</v>
@@ -2635,7 +2635,7 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992 - OfficiallyExtreme</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
       </c>
     </row>
     <row r="60">
@@ -2681,7 +2681,7 @@
         <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
       </c>
       <c r="B61" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C61" t="str">
         <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
@@ -2693,7 +2693,7 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G61" t="str">
         <v>2:56</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
@@ -439,7 +439,7 @@
         <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Studio)</v>
       </c>
       <c r="B2" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=mgsdQI-GVMM</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:19</v>
@@ -477,7 +477,7 @@
         <v>Vera Blue - Hold (Live on Sydney Harbour)</v>
       </c>
       <c r="B3" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=SYEwk-EZJPU</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>3:37</v>
@@ -515,7 +515,7 @@
         <v>Bob Moses - Need You Tonight (INXS Cover) - Brooklyn Mirage 2023</v>
       </c>
       <c r="B4" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=CoCqPwDIBOA</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>3:08</v>
@@ -553,7 +553,7 @@
         <v>Marc Anthony - Un Mal Sueño (Visualizer)</v>
       </c>
       <c r="B5" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=18yZq5xtke4</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>3:28</v>
@@ -591,7 +591,7 @@
         <v>Marc Anthony - Contra La Corriente (Visualizer)</v>
       </c>
       <c r="B6" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=IGLmJ71oHhQ</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v>5:05</v>
@@ -629,7 +629,7 @@
         <v>Loreen - Feels Like Heaven</v>
       </c>
       <c r="B7" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=BQc97moyQBg</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G7" t="str">
         <v>3:14</v>
@@ -667,7 +667,7 @@
         <v>Take That - Once You've Tasted Love (Live on Pebble Mill, 1992)</v>
       </c>
       <c r="B8" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=dOeoDOueESk</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G8" t="str">
         <v>3:36</v>
@@ -705,7 +705,7 @@
         <v>Paul McCartney, Wings - Nineteen Hundred And Eighty Five (Visualiser)</v>
       </c>
       <c r="B9" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=a4AIjUHuWpU</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G9" t="str">
         <v>5:31</v>
@@ -743,7 +743,7 @@
         <v>Nothing But Thieves - Sorry (Official Audio)</v>
       </c>
       <c r="B10" t="str">
-        <v>19 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=D7QfVqo5YqY</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>19 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="G10" t="str">
         <v>3:37</v>
@@ -2643,7 +2643,7 @@
         <v>Holly Humberstone - To Love Somebody (Official Video)</v>
       </c>
       <c r="B60" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C60" t="str">
         <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
@@ -2655,7 +2655,7 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G60" t="str">
         <v>3:59</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
@@ -439,7 +439,7 @@
         <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Studio)</v>
       </c>
       <c r="B2" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=mgsdQI-GVMM</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:19</v>
@@ -477,7 +477,7 @@
         <v>Vera Blue - Hold (Live on Sydney Harbour)</v>
       </c>
       <c r="B3" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=SYEwk-EZJPU</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>3:37</v>
@@ -515,7 +515,7 @@
         <v>Bob Moses - Need You Tonight (INXS Cover) - Brooklyn Mirage 2023</v>
       </c>
       <c r="B4" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=CoCqPwDIBOA</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>3:08</v>
@@ -553,7 +553,7 @@
         <v>Marc Anthony - Un Mal Sueño (Visualizer)</v>
       </c>
       <c r="B5" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=18yZq5xtke4</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>3:28</v>
@@ -591,7 +591,7 @@
         <v>Marc Anthony - Contra La Corriente (Visualizer)</v>
       </c>
       <c r="B6" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=IGLmJ71oHhQ</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v>5:05</v>
@@ -629,7 +629,7 @@
         <v>Loreen - Feels Like Heaven</v>
       </c>
       <c r="B7" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=BQc97moyQBg</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G7" t="str">
         <v>3:14</v>
@@ -667,7 +667,7 @@
         <v>Take That - Once You've Tasted Love (Live on Pebble Mill, 1992)</v>
       </c>
       <c r="B8" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=dOeoDOueESk</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="G8" t="str">
         <v>3:36</v>
@@ -705,7 +705,7 @@
         <v>Paul McCartney, Wings - Nineteen Hundred And Eighty Five (Visualiser)</v>
       </c>
       <c r="B9" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=a4AIjUHuWpU</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G9" t="str">
         <v>5:31</v>
@@ -743,7 +743,7 @@
         <v>Nothing But Thieves - Sorry (Official Audio)</v>
       </c>
       <c r="B10" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=D7QfVqo5YqY</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G10" t="str">
         <v>3:37</v>
@@ -1085,7 +1085,7 @@
         <v>The Kiffness &amp; Matisyahu - ONE DAY (ft. Andel and Nalyn) [OFFICIAL VIDEO]</v>
       </c>
       <c r="B19" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=buS21tVq5r0</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G19" t="str">
         <v>3:07</v>
@@ -3365,7 +3365,7 @@
         <v>DEF LEPPARD - Rejoice (Official Lyric Video)</v>
       </c>
       <c r="B79" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C79" t="str">
         <v>https://www.youtube.com/watch?v=zy2TLLeNgp0</v>
@@ -3377,7 +3377,7 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G79" t="str">
         <v>4:21</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
@@ -439,7 +439,7 @@
         <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Studio)</v>
       </c>
       <c r="B2" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=mgsdQI-GVMM</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:19</v>
@@ -477,7 +477,7 @@
         <v>Vera Blue - Hold (Live on Sydney Harbour)</v>
       </c>
       <c r="B3" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=SYEwk-EZJPU</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>3:37</v>
@@ -515,7 +515,7 @@
         <v>Bob Moses - Need You Tonight (INXS Cover) - Brooklyn Mirage 2023</v>
       </c>
       <c r="B4" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=CoCqPwDIBOA</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>3:08</v>
@@ -553,7 +553,7 @@
         <v>Marc Anthony - Un Mal Sueño (Visualizer)</v>
       </c>
       <c r="B5" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=18yZq5xtke4</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>3:28</v>
@@ -591,7 +591,7 @@
         <v>Marc Anthony - Contra La Corriente (Visualizer)</v>
       </c>
       <c r="B6" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=IGLmJ71oHhQ</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v>5:05</v>
@@ -629,7 +629,7 @@
         <v>Loreen - Feels Like Heaven</v>
       </c>
       <c r="B7" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=BQc97moyQBg</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="G7" t="str">
         <v>3:14</v>
@@ -667,7 +667,7 @@
         <v>Take That - Once You've Tasted Love (Live on Pebble Mill, 1992)</v>
       </c>
       <c r="B8" t="str">
-        <v>19 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=dOeoDOueESk</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>19 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="G8" t="str">
         <v>3:36</v>
@@ -705,7 +705,7 @@
         <v>Paul McCartney, Wings - Nineteen Hundred And Eighty Five (Visualiser)</v>
       </c>
       <c r="B9" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=a4AIjUHuWpU</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="G9" t="str">
         <v>5:31</v>
@@ -743,7 +743,7 @@
         <v>Nothing But Thieves - Sorry (Official Audio)</v>
       </c>
       <c r="B10" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=D7QfVqo5YqY</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G10" t="str">
         <v>3:37</v>
@@ -1047,7 +1047,7 @@
         <v>The Cure - Boys Don't Cry (86 Mix) (Official Lyric Video)</v>
       </c>
       <c r="B18" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=isNztTjXQsQ</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G18" t="str">
         <v>2:39</v>
@@ -2339,7 +2339,7 @@
         <v>Timebelle - Top of the World (Mood Video)</v>
       </c>
       <c r="B52" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C52" t="str">
         <v>https://www.youtube.com/watch?v=r9KyYK_E34s</v>
@@ -2351,7 +2351,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G52" t="str">
         <v>3:01</v>
@@ -3479,7 +3479,7 @@
         <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show]</v>
       </c>
       <c r="B82" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C82" t="str">
         <v>https://www.youtube.com/watch?v=dLzpNstMHZY</v>
@@ -3491,7 +3491,7 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G82" t="str">
         <v>3:10</v>
@@ -3517,7 +3517,7 @@
         <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel)</v>
       </c>
       <c r="B83" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C83" t="str">
         <v>https://www.youtube.com/watch?v=fo_j8Fqag8I</v>
@@ -3529,7 +3529,7 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G83" t="str">
         <v>3:21</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
@@ -439,7 +439,7 @@
         <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Studio)</v>
       </c>
       <c r="B2" t="str">
-        <v>15 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=mgsdQI-GVMM</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>15 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:19</v>
@@ -477,7 +477,7 @@
         <v>Vera Blue - Hold (Live on Sydney Harbour)</v>
       </c>
       <c r="B3" t="str">
-        <v>16 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=SYEwk-EZJPU</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>16 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>3:37</v>
@@ -515,7 +515,7 @@
         <v>Bob Moses - Need You Tonight (INXS Cover) - Brooklyn Mirage 2023</v>
       </c>
       <c r="B4" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=CoCqPwDIBOA</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>3:08</v>
@@ -553,7 +553,7 @@
         <v>Marc Anthony - Un Mal Sueño (Visualizer)</v>
       </c>
       <c r="B5" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=18yZq5xtke4</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>3:28</v>
@@ -591,7 +591,7 @@
         <v>Marc Anthony - Contra La Corriente (Visualizer)</v>
       </c>
       <c r="B6" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=IGLmJ71oHhQ</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v>5:05</v>
@@ -629,7 +629,7 @@
         <v>Loreen - Feels Like Heaven</v>
       </c>
       <c r="B7" t="str">
-        <v>19 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=BQc97moyQBg</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>19 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G7" t="str">
         <v>3:14</v>
@@ -667,7 +667,7 @@
         <v>Take That - Once You've Tasted Love (Live on Pebble Mill, 1992)</v>
       </c>
       <c r="B8" t="str">
-        <v>20 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=dOeoDOueESk</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>20 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G8" t="str">
         <v>3:36</v>
@@ -705,7 +705,7 @@
         <v>Paul McCartney, Wings - Nineteen Hundred And Eighty Five (Visualiser)</v>
       </c>
       <c r="B9" t="str">
-        <v>19 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=a4AIjUHuWpU</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>19 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G9" t="str">
         <v>5:31</v>
@@ -743,7 +743,7 @@
         <v>Nothing But Thieves - Sorry (Official Audio)</v>
       </c>
       <c r="B10" t="str">
-        <v>22 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=D7QfVqo5YqY</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>22 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G10" t="str">
         <v>3:37</v>
@@ -971,7 +971,7 @@
         <v>Dean Lewis - I Am Getting Well (Lyric Video)</v>
       </c>
       <c r="B16" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=6ecgOSOMWzc</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G16" t="str">
         <v>2:44</v>
@@ -1009,7 +1009,7 @@
         <v>Take That - Take That and Party (Official HD Video)</v>
       </c>
       <c r="B17" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=DAerJcerikU</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G17" t="str">
         <v>2:57</v>
@@ -2225,7 +2225,7 @@
         <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video)</v>
       </c>
       <c r="B49" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C49" t="str">
         <v>https://www.youtube.com/watch?v=yUAvfo8fpuU</v>
@@ -2237,7 +2237,7 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G49" t="str">
         <v>3:50</v>
@@ -2263,7 +2263,7 @@
         <v>I Had To Explain "How Music Works" LIVE In Concert</v>
       </c>
       <c r="B50" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C50" t="str">
         <v>https://www.youtube.com/watch?v=KnsBdAM3HqY</v>
@@ -2275,7 +2275,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G50" t="str">
         <v>5:32</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
@@ -515,7 +515,7 @@
         <v>Bob Moses - Need You Tonight (INXS Cover) - Brooklyn Mirage 2023</v>
       </c>
       <c r="B4" t="str">
-        <v>19 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=CoCqPwDIBOA</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>19 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>3:08</v>
@@ -553,7 +553,7 @@
         <v>Marc Anthony - Un Mal Sueño (Visualizer)</v>
       </c>
       <c r="B5" t="str">
-        <v>19 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=18yZq5xtke4</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>19 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>3:28</v>
@@ -591,7 +591,7 @@
         <v>Marc Anthony - Contra La Corriente (Visualizer)</v>
       </c>
       <c r="B6" t="str">
-        <v>19 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=IGLmJ71oHhQ</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>19 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v>5:05</v>
@@ -933,7 +933,7 @@
         <v>JOSEPH - Water in the Room (Official Music Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=tNmT47k6MjM</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G15" t="str">
         <v>3:10</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
@@ -439,7 +439,7 @@
         <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Studio)</v>
       </c>
       <c r="B2" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=mgsdQI-GVMM</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:19</v>
@@ -477,7 +477,7 @@
         <v>Vera Blue - Hold (Live on Sydney Harbour)</v>
       </c>
       <c r="B3" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=SYEwk-EZJPU</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>3:37</v>
@@ -515,7 +515,7 @@
         <v>Bob Moses - Need You Tonight (INXS Cover) - Brooklyn Mirage 2023</v>
       </c>
       <c r="B4" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=CoCqPwDIBOA</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>3:08</v>
@@ -553,7 +553,7 @@
         <v>Marc Anthony - Un Mal Sueño (Visualizer)</v>
       </c>
       <c r="B5" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=18yZq5xtke4</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>3:28</v>
@@ -591,7 +591,7 @@
         <v>Marc Anthony - Contra La Corriente (Visualizer)</v>
       </c>
       <c r="B6" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=IGLmJ71oHhQ</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v>5:05</v>
@@ -629,7 +629,7 @@
         <v>Loreen - Feels Like Heaven</v>
       </c>
       <c r="B7" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=BQc97moyQBg</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G7" t="str">
         <v>3:14</v>
@@ -667,7 +667,7 @@
         <v>Take That - Once You've Tasted Love (Live on Pebble Mill, 1992)</v>
       </c>
       <c r="B8" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=dOeoDOueESk</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G8" t="str">
         <v>3:36</v>
@@ -705,7 +705,7 @@
         <v>Paul McCartney, Wings - Nineteen Hundred And Eighty Five (Visualiser)</v>
       </c>
       <c r="B9" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=a4AIjUHuWpU</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G9" t="str">
         <v>5:31</v>
@@ -857,7 +857,7 @@
         <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered)</v>
       </c>
       <c r="B13" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=I7a-pDZFE7U</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G13" t="str">
         <v>4:38</v>
@@ -2035,7 +2035,7 @@
         <v>Beck - Love (Audio)</v>
       </c>
       <c r="B44" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C44" t="str">
         <v>https://www.youtube.com/watch?v=ByABj3Xof1I</v>
@@ -2047,7 +2047,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G44" t="str">
         <v>3:14</v>
@@ -2149,7 +2149,7 @@
         <v>Jason Derulo - Sexy For Me [Official Music Video]</v>
       </c>
       <c r="B47" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C47" t="str">
         <v>https://www.youtube.com/watch?v=9ST-eBNL0NU</v>
@@ -2161,7 +2161,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G47" t="str">
         <v>2:10</v>
@@ -2187,7 +2187,7 @@
         <v>Lights - COME GET YOUR GIRL</v>
       </c>
       <c r="B48" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C48" t="str">
         <v>https://www.youtube.com/watch?v=EhzX2y5MpSM</v>
@@ -2199,7 +2199,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G48" t="str">
         <v>3:52</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
@@ -439,7 +439,7 @@
         <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Studio)</v>
       </c>
       <c r="B2" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=mgsdQI-GVMM</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:19</v>
@@ -477,7 +477,7 @@
         <v>Vera Blue - Hold (Live on Sydney Harbour)</v>
       </c>
       <c r="B3" t="str">
-        <v>19 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=SYEwk-EZJPU</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>19 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>3:37</v>
@@ -515,7 +515,7 @@
         <v>Bob Moses - Need You Tonight (INXS Cover) - Brooklyn Mirage 2023</v>
       </c>
       <c r="B4" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=CoCqPwDIBOA</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>3:08</v>
@@ -553,7 +553,7 @@
         <v>Marc Anthony - Un Mal Sueño (Visualizer)</v>
       </c>
       <c r="B5" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=18yZq5xtke4</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>3:28</v>
@@ -591,7 +591,7 @@
         <v>Marc Anthony - Contra La Corriente (Visualizer)</v>
       </c>
       <c r="B6" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=IGLmJ71oHhQ</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v>5:05</v>
@@ -629,7 +629,7 @@
         <v>Loreen - Feels Like Heaven</v>
       </c>
       <c r="B7" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=BQc97moyQBg</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G7" t="str">
         <v>3:14</v>
@@ -667,7 +667,7 @@
         <v>Take That - Once You've Tasted Love (Live on Pebble Mill, 1992)</v>
       </c>
       <c r="B8" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=dOeoDOueESk</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G8" t="str">
         <v>3:36</v>
@@ -705,7 +705,7 @@
         <v>Paul McCartney, Wings - Nineteen Hundred And Eighty Five (Visualiser)</v>
       </c>
       <c r="B9" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=a4AIjUHuWpU</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G9" t="str">
         <v>5:31</v>
@@ -1997,7 +1997,7 @@
         <v>Teddy Swims - Need You More (Live - Green Room Sessions)</v>
       </c>
       <c r="B43" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C43" t="str">
         <v>https://www.youtube.com/watch?v=1ugf5aaY4pY</v>
@@ -2009,7 +2009,7 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G43" t="str">
         <v>3:16</v>
@@ -2111,7 +2111,7 @@
         <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show</v>
       </c>
       <c r="B46" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=ylifHFJWJ_c</v>
@@ -2123,7 +2123,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G46" t="str">
         <v>4:10</v>
@@ -2567,7 +2567,7 @@
         <v>Neal Francis - Back It Up (Live At The Salt Shed)</v>
       </c>
       <c r="B58" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C58" t="str">
         <v>https://www.youtube.com/watch?v=46iZEdsxjC0</v>
@@ -2579,7 +2579,7 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G58" t="str">
         <v>5:01</v>
@@ -2605,7 +2605,7 @@
         <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
       </c>
       <c r="B59" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C59" t="str">
         <v>https://www.youtube.com/watch?v=K2nG1Uukz7E</v>
@@ -2617,7 +2617,7 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G59" t="str">
         <v>4:12</v>
@@ -3327,7 +3327,7 @@
         <v>Lana Lubany - BAD IDEA (Official Video)</v>
       </c>
       <c r="B78" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C78" t="str">
         <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
@@ -3339,7 +3339,7 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G78" t="str">
         <v>2:59</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L205"/>
+  <dimension ref="A1:L206"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -439,7 +439,7 @@
         <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Studio)</v>
       </c>
       <c r="B2" t="str">
-        <v>19 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=mgsdQI-GVMM</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>19 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:19</v>
@@ -477,7 +477,7 @@
         <v>Vera Blue - Hold (Live on Sydney Harbour)</v>
       </c>
       <c r="B3" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=SYEwk-EZJPU</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>3:37</v>
@@ -515,7 +515,7 @@
         <v>Bob Moses - Need You Tonight (INXS Cover) - Brooklyn Mirage 2023</v>
       </c>
       <c r="B4" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=CoCqPwDIBOA</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>3:08</v>
@@ -553,7 +553,7 @@
         <v>Marc Anthony - Un Mal Sueño (Visualizer)</v>
       </c>
       <c r="B5" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=18yZq5xtke4</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>3:28</v>
@@ -591,7 +591,7 @@
         <v>Marc Anthony - Contra La Corriente (Visualizer)</v>
       </c>
       <c r="B6" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=IGLmJ71oHhQ</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v>5:05</v>
@@ -629,7 +629,7 @@
         <v>Loreen - Feels Like Heaven</v>
       </c>
       <c r="B7" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=BQc97moyQBg</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G7" t="str">
         <v>3:14</v>
@@ -705,7 +705,7 @@
         <v>Paul McCartney, Wings - Nineteen Hundred And Eighty Five (Visualiser)</v>
       </c>
       <c r="B9" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=a4AIjUHuWpU</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G9" t="str">
         <v>5:31</v>
@@ -781,7 +781,7 @@
         <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music</v>
       </c>
       <c r="B11" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=KdsHxyl4bE8</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G11" t="str">
         <v>4:58</v>
@@ -819,7 +819,7 @@
         <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield, CA (2026)</v>
       </c>
       <c r="B12" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=Mwkl_Cz_SG8</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G12" t="str">
         <v>5:08</v>
@@ -1959,7 +1959,7 @@
         <v>Demi Lovato - Ghost (Live)</v>
       </c>
       <c r="B42" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C42" t="str">
         <v>https://www.youtube.com/watch?v=E-ECwdRndVA</v>
@@ -1971,7 +1971,7 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G42" t="str">
         <v>4:05</v>
@@ -2073,7 +2073,7 @@
         <v>The Offspring - Looking Out For #1 | Live in Spokane, WA (2026)</v>
       </c>
       <c r="B45" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C45" t="str">
         <v>https://www.youtube.com/watch?v=2HSbo51EFNg</v>
@@ -2085,7 +2085,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G45" t="str">
         <v>2:57</v>
@@ -2491,7 +2491,7 @@
         <v>Amazon Music presents: Sienna Spiro - You Stole The Show</v>
       </c>
       <c r="B56" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C56" t="str">
         <v>https://www.youtube.com/watch?v=stYIRyCLN4Y</v>
@@ -2503,7 +2503,7 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G56" t="str">
         <v>3:24</v>
@@ -2529,7 +2529,7 @@
         <v>Harry Styles - Aperture (Official Video)</v>
       </c>
       <c r="B57" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C57" t="str">
         <v>https://www.youtube.com/watch?v=7sxVHYZ_PnA</v>
@@ -2541,7 +2541,7 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G57" t="str">
         <v>5:52</v>
@@ -2947,7 +2947,7 @@
         <v>Louis Tomlinson - Imposter (Official Video)</v>
       </c>
       <c r="B68" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C68" t="str">
         <v>https://www.youtube.com/watch?v=rzuD5szQhso</v>
@@ -2959,7 +2959,7 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G68" t="str">
         <v>2:56</v>
@@ -4236,13 +4236,13 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Heaven</v>
+        <v>Penny in the Lake</v>
       </c>
       <c r="B102" t="str">
         <v/>
       </c>
       <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/heaven/1862570892</v>
+        <v>https://music.apple.com/us/song/penny-in-the-lake/1844710053</v>
       </c>
       <c r="D102" t="str">
         <v>2026-02-03</v>
@@ -4251,25 +4251,25 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>Ambiguous Desire</v>
+        <v>Singin’ to an Empty Chair</v>
       </c>
       <c r="G102" t="str">
-        <v>4:26</v>
+        <v>3:51</v>
       </c>
       <c r="H102" t="str">
-        <v>Arlo Parks</v>
+        <v>Ratboys</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/arlo-parks/1291875084</v>
+        <v>https://music.apple.com/us/artist/ratboys/997909855</v>
       </c>
       <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/heaven/1862570378</v>
+        <v>https://music.apple.com/us/album/penny-in-the-lake/1844710034</v>
       </c>
       <c r="L102" t="str">
-        <v>Heaven - Arlo Parks</v>
+        <v>Penny in the Lake - Ratboys</v>
       </c>
     </row>
     <row r="103">
@@ -4540,13 +4540,13 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>For Hire</v>
+        <v>Heaven</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/for-hire/1870722567</v>
+        <v>https://music.apple.com/us/song/heaven/1862570892</v>
       </c>
       <c r="D110" t="str">
         <v>2026-02-03</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>For Hire - Single</v>
+        <v>Ambiguous Desire</v>
       </c>
       <c r="G110" t="str">
-        <v>3:44</v>
+        <v>4:26</v>
       </c>
       <c r="H110" t="str">
-        <v>People I’ve Met</v>
+        <v>Arlo Parks</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/people-ive-met/1853169947</v>
+        <v>https://music.apple.com/us/artist/arlo-parks/1291875084</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/for-hire/1870722565</v>
+        <v>https://music.apple.com/us/album/heaven/1862570378</v>
       </c>
       <c r="L110" t="str">
-        <v>For Hire - People I’ve Met</v>
+        <v>Heaven - Arlo Parks</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>McArthur</v>
+        <v>For Hire</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/mcarthur/1871231844</v>
+        <v>https://music.apple.com/us/song/for-hire/1870722567</v>
       </c>
       <c r="D111" t="str">
         <v>2026-02-03</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>McArthur - Single</v>
+        <v>For Hire - Single</v>
       </c>
       <c r="G111" t="str">
-        <v>3:51</v>
+        <v>3:44</v>
       </c>
       <c r="H111" t="str">
-        <v>HARDY</v>
+        <v>People I’ve Met</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/hardy/1438874739</v>
+        <v>https://music.apple.com/us/artist/people-ive-met/1853169947</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/mcarthur/1871231823</v>
+        <v>https://music.apple.com/us/album/for-hire/1870722565</v>
       </c>
       <c r="L111" t="str">
-        <v>McArthur - HARDY</v>
+        <v>For Hire - People I’ve Met</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Debris</v>
+        <v>McArthur</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/debris/1853069633</v>
+        <v>https://music.apple.com/us/song/mcarthur/1871231844</v>
       </c>
       <c r="D112" t="str">
         <v>2026-02-03</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>COSMIC OPERA ACT I</v>
+        <v>McArthur - Single</v>
       </c>
       <c r="G112" t="str">
-        <v>2:55</v>
+        <v>3:51</v>
       </c>
       <c r="H112" t="str">
-        <v>Labrinth</v>
+        <v>HARDY</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
+        <v>https://music.apple.com/us/artist/hardy/1438874739</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/debris/1853069628</v>
+        <v>https://music.apple.com/us/album/mcarthur/1871231823</v>
       </c>
       <c r="L112" t="str">
-        <v>Debris - Labrinth</v>
+        <v>McArthur - HARDY</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>God Owes Me Money (Live at Apple Music Radio)</v>
+        <v>Debris</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/god-owes-me-money-live-at-apple-music-radio/1871521120</v>
+        <v>https://music.apple.com/us/song/debris/1853069633</v>
       </c>
       <c r="D113" t="str">
         <v>2026-02-03</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>Throw Me Away / God Owes Me Money (Live at Apple Music Radio)</v>
+        <v>COSMIC OPERA ACT I</v>
       </c>
       <c r="G113" t="str">
-        <v>3:25</v>
+        <v>2:55</v>
       </c>
       <c r="H113" t="str">
-        <v>Militarie Gun</v>
+        <v>Labrinth</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/militarie-gun/1529039426</v>
+        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/god-owes-me-money-live-at-apple-music-radio/1871520929</v>
+        <v>https://music.apple.com/us/album/debris/1853069628</v>
       </c>
       <c r="L113" t="str">
-        <v>God Owes Me Money (Live at Apple Music Radio) - Militarie Gun</v>
+        <v>Debris - Labrinth</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>ROCKSTAR RAGING (feat. Swae Lee)</v>
+        <v>God Owes Me Money (Live at Apple Music Radio)</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/rockstar-raging-feat-swae-lee/1873028187</v>
+        <v>https://music.apple.com/us/song/god-owes-me-money-live-at-apple-music-radio/1871521120</v>
       </c>
       <c r="D114" t="str">
         <v>2026-02-03</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>ROCKSTAR RAGING (feat. Swae Lee) - Single</v>
+        <v>Throw Me Away / God Owes Me Money (Live at Apple Music Radio)</v>
       </c>
       <c r="G114" t="str">
-        <v>4:38</v>
+        <v>3:25</v>
       </c>
       <c r="H114" t="str">
-        <v>Mike WiLL Made-It</v>
+        <v>Militarie Gun</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/mike-will-made-it/511333957</v>
+        <v>https://music.apple.com/us/artist/militarie-gun/1529039426</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/rockstar-raging-feat-swae-lee/1873028186</v>
+        <v>https://music.apple.com/us/album/god-owes-me-money-live-at-apple-music-radio/1871520929</v>
       </c>
       <c r="L114" t="str">
-        <v>ROCKSTAR RAGING (feat. Swae Lee) - Mike WiLL Made-It</v>
+        <v>God Owes Me Money (Live at Apple Music Radio) - Militarie Gun</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>1+1</v>
+        <v>ROCKSTAR RAGING (feat. Swae Lee)</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/1-1/1870378316</v>
+        <v>https://music.apple.com/us/song/rockstar-raging-feat-swae-lee/1873028187</v>
       </c>
       <c r="D115" t="str">
         <v>2026-02-03</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>1+1 - Single</v>
+        <v>ROCKSTAR RAGING (feat. Swae Lee) - Single</v>
       </c>
       <c r="G115" t="str">
-        <v>3:06</v>
+        <v>4:38</v>
       </c>
       <c r="H115" t="str">
-        <v>Maluma</v>
+        <v>Mike WiLL Made-It</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/maluma/448916501</v>
+        <v>https://music.apple.com/us/artist/mike-will-made-it/511333957</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/1-1/1870378315</v>
+        <v>https://music.apple.com/us/album/rockstar-raging-feat-swae-lee/1873028186</v>
       </c>
       <c r="L115" t="str">
-        <v>1+1 - Maluma</v>
+        <v>ROCKSTAR RAGING (feat. Swae Lee) - Mike WiLL Made-It</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Still Sincere (feat. PinkPantheress)</v>
+        <v>1+1</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/still-sincere-feat-pinkpantheress/1862228374</v>
+        <v>https://music.apple.com/us/song/1-1/1870378316</v>
       </c>
       <c r="D116" t="str">
         <v>2026-02-03</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Still Sincere (feat. PinkPantheress) - Single</v>
+        <v>1+1 - Single</v>
       </c>
       <c r="G116" t="str">
-        <v>3:08</v>
+        <v>3:06</v>
       </c>
       <c r="H116" t="str">
-        <v>MJ Cole</v>
+        <v>Maluma</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/mj-cole/405892</v>
+        <v>https://music.apple.com/us/artist/maluma/448916501</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/still-sincere-feat-pinkpantheress/1862228373</v>
+        <v>https://music.apple.com/us/album/1-1/1870378315</v>
       </c>
       <c r="L116" t="str">
-        <v>Still Sincere (feat. PinkPantheress) - MJ Cole</v>
+        <v>1+1 - Maluma</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Two Car Garage</v>
+        <v>Still Sincere (feat. PinkPantheress)</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/two-car-garage/1869137588</v>
+        <v>https://music.apple.com/us/song/still-sincere-feat-pinkpantheress/1862228374</v>
       </c>
       <c r="D117" t="str">
         <v>2026-02-03</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>Two Car Garage - Single</v>
+        <v>Still Sincere (feat. PinkPantheress) - Single</v>
       </c>
       <c r="G117" t="str">
-        <v>3:02</v>
+        <v>3:08</v>
       </c>
       <c r="H117" t="str">
-        <v>Jon Bellion</v>
+        <v>MJ Cole</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/jon-bellion/659289673</v>
+        <v>https://music.apple.com/us/artist/mj-cole/405892</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/two-car-garage/1869137587</v>
+        <v>https://music.apple.com/us/album/still-sincere-feat-pinkpantheress/1862228373</v>
       </c>
       <c r="L117" t="str">
-        <v>Two Car Garage - Jon Bellion</v>
+        <v>Still Sincere (feat. PinkPantheress) - MJ Cole</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>fml .</v>
+        <v>Two Car Garage</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/fml/1872686260</v>
+        <v>https://music.apple.com/us/song/two-car-garage/1869137588</v>
       </c>
       <c r="D118" t="str">
         <v>2026-02-03</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>The Boy who cried Terrified .</v>
+        <v>Two Car Garage - Single</v>
       </c>
       <c r="G118" t="str">
-        <v>2:40</v>
+        <v>3:02</v>
       </c>
       <c r="H118" t="str">
-        <v>fakemink</v>
+        <v>Jon Bellion</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/fakemink/1744500063</v>
+        <v>https://music.apple.com/us/artist/jon-bellion/659289673</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/fml/1872686249</v>
+        <v>https://music.apple.com/us/album/two-car-garage/1869137587</v>
       </c>
       <c r="L118" t="str">
-        <v>fml . - fakemink</v>
+        <v>Two Car Garage - Jon Bellion</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Faked It All The Time</v>
+        <v>fml .</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/faked-it-all-the-time/1871050032</v>
+        <v>https://music.apple.com/us/song/fml/1872686260</v>
       </c>
       <c r="D119" t="str">
         <v>2026-02-03</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>Faked It All The Time - Single</v>
+        <v>The Boy who cried Terrified .</v>
       </c>
       <c r="G119" t="str">
-        <v>3:01</v>
+        <v>2:40</v>
       </c>
       <c r="H119" t="str">
-        <v>Allie Sherlock</v>
+        <v>fakemink</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/allie-sherlock/1314464325</v>
+        <v>https://music.apple.com/us/artist/fakemink/1744500063</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/faked-it-all-the-time/1871050031</v>
+        <v>https://music.apple.com/us/album/fml/1872686249</v>
       </c>
       <c r="L119" t="str">
-        <v>Faked It All The Time - Allie Sherlock</v>
+        <v>fml . - fakemink</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>House of the Rising Sun</v>
+        <v>Faked It All The Time</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/house-of-the-rising-sun/1872111857</v>
+        <v>https://music.apple.com/us/song/faked-it-all-the-time/1871050032</v>
       </c>
       <c r="D120" t="str">
         <v>2026-02-03</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>House of the Rising Sun - Single</v>
+        <v>Faked It All The Time - Single</v>
       </c>
       <c r="G120" t="str">
-        <v>3:08</v>
+        <v>3:01</v>
       </c>
       <c r="H120" t="str">
-        <v>Lizzy McAlpine</v>
+        <v>Allie Sherlock</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/lizzy-mcalpine/1350245112</v>
+        <v>https://music.apple.com/us/artist/allie-sherlock/1314464325</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/house-of-the-rising-sun/1872111734</v>
+        <v>https://music.apple.com/us/album/faked-it-all-the-time/1871050031</v>
       </c>
       <c r="L120" t="str">
-        <v>House of the Rising Sun - Lizzy McAlpine</v>
+        <v>Faked It All The Time - Allie Sherlock</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Lorelei</v>
+        <v>House of the Rising Sun</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/lorelei/1867640808</v>
+        <v>https://music.apple.com/us/song/house-of-the-rising-sun/1872111857</v>
       </c>
       <c r="D121" t="str">
         <v>2026-02-03</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Lorelei - Single</v>
+        <v>House of the Rising Sun - Single</v>
       </c>
       <c r="G121" t="str">
-        <v>2:35</v>
+        <v>3:08</v>
       </c>
       <c r="H121" t="str">
-        <v>ERNEST</v>
+        <v>Lizzy McAlpine</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
+        <v>https://music.apple.com/us/artist/lizzy-mcalpine/1350245112</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/lorelei/1867640583</v>
+        <v>https://music.apple.com/us/album/house-of-the-rising-sun/1872111734</v>
       </c>
       <c r="L121" t="str">
-        <v>Lorelei - ERNEST</v>
+        <v>House of the Rising Sun - Lizzy McAlpine</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Free</v>
+        <v>Lorelei</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/free/1870703329</v>
+        <v>https://music.apple.com/us/song/lorelei/1867640808</v>
       </c>
       <c r="D122" t="str">
         <v>2026-02-03</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Free - Single</v>
+        <v>Lorelei - Single</v>
       </c>
       <c r="G122" t="str">
-        <v>3:56</v>
+        <v>2:35</v>
       </c>
       <c r="H122" t="str">
-        <v>SLANDER</v>
+        <v>ERNEST</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/slander/1051421487</v>
+        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/free/1870703327</v>
+        <v>https://music.apple.com/us/album/lorelei/1867640583</v>
       </c>
       <c r="L122" t="str">
-        <v>Free - SLANDER</v>
+        <v>Lorelei - ERNEST</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>ASSIGNMENT</v>
+        <v>Free</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/assignment/1872764440</v>
+        <v>https://music.apple.com/us/song/free/1870703329</v>
       </c>
       <c r="D123" t="str">
         <v>2026-02-03</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>ASSIGNMENT - Single</v>
+        <v>Free - Single</v>
       </c>
       <c r="G123" t="str">
-        <v>2:23</v>
+        <v>3:56</v>
       </c>
       <c r="H123" t="str">
-        <v>Power Snatch</v>
+        <v>SLANDER</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/power-snatch/1872764439</v>
+        <v>https://music.apple.com/us/artist/slander/1051421487</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/assignment/1872764438</v>
+        <v>https://music.apple.com/us/album/free/1870703327</v>
       </c>
       <c r="L123" t="str">
-        <v>ASSIGNMENT - Power Snatch</v>
+        <v>Free - SLANDER</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>professional heartbreaker</v>
+        <v>ASSIGNMENT</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/professional-heartbreaker/1871053476</v>
+        <v>https://music.apple.com/us/song/assignment/1872764440</v>
       </c>
       <c r="D124" t="str">
         <v>2026-02-03</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>professional heartbreaker - Single</v>
+        <v>ASSIGNMENT - Single</v>
       </c>
       <c r="G124" t="str">
-        <v>2:55</v>
+        <v>2:23</v>
       </c>
       <c r="H124" t="str">
-        <v>Artemas</v>
+        <v>Power Snatch</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
+        <v>https://music.apple.com/us/artist/power-snatch/1872764439</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/professional-heartbreaker/1871053473</v>
+        <v>https://music.apple.com/us/album/assignment/1872764438</v>
       </c>
       <c r="L124" t="str">
-        <v>professional heartbreaker - Artemas</v>
+        <v>ASSIGNMENT - Power Snatch</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>tell me what you want</v>
+        <v>professional heartbreaker</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/tell-me-what-you-want/1871463892</v>
+        <v>https://music.apple.com/us/song/professional-heartbreaker/1871053476</v>
       </c>
       <c r="D125" t="str">
         <v>2026-02-03</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>ACT II</v>
+        <v>professional heartbreaker - Single</v>
       </c>
       <c r="G125" t="str">
-        <v>3:56</v>
+        <v>2:55</v>
       </c>
       <c r="H125" t="str">
-        <v>Sasha Keable</v>
+        <v>Artemas</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/sasha-keable/325850892</v>
+        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/tell-me-what-you-want/1871463550</v>
+        <v>https://music.apple.com/us/album/professional-heartbreaker/1871053473</v>
       </c>
       <c r="L125" t="str">
-        <v>tell me what you want - Sasha Keable</v>
+        <v>professional heartbreaker - Artemas</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Aguas</v>
+        <v>tell me what you want</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/aguas/1869455857</v>
+        <v>https://music.apple.com/us/song/tell-me-what-you-want/1871463892</v>
       </c>
       <c r="D126" t="str">
         <v>2026-02-03</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Aguas - Single</v>
+        <v>ACT II</v>
       </c>
       <c r="G126" t="str">
-        <v>2:52</v>
+        <v>3:56</v>
       </c>
       <c r="H126" t="str">
-        <v>Luis R Conriquez</v>
+        <v>Sasha Keable</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
+        <v>https://music.apple.com/us/artist/sasha-keable/325850892</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/aguas/1869455582</v>
+        <v>https://music.apple.com/us/album/tell-me-what-you-want/1871463550</v>
       </c>
       <c r="L126" t="str">
-        <v>Aguas - Luis R Conriquez</v>
+        <v>tell me what you want - Sasha Keable</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Ants In My Room</v>
+        <v>Aguas</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/ants-in-my-room/1870967813</v>
+        <v>https://music.apple.com/us/song/aguas/1869455857</v>
       </c>
       <c r="D127" t="str">
         <v>2026-02-03</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>Ants In My Room - Single</v>
+        <v>Aguas - Single</v>
       </c>
       <c r="G127" t="str">
-        <v>2:48</v>
+        <v>2:52</v>
       </c>
       <c r="H127" t="str">
-        <v>Carter Vail</v>
+        <v>Luis R Conriquez</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/carter-vail/1102115053</v>
+        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/ants-in-my-room/1870967810</v>
+        <v>https://music.apple.com/us/album/aguas/1869455582</v>
       </c>
       <c r="L127" t="str">
-        <v>Ants In My Room - Carter Vail</v>
+        <v>Aguas - Luis R Conriquez</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Baddie</v>
+        <v>Ants In My Room</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/baddie/1849760827</v>
+        <v>https://music.apple.com/us/song/ants-in-my-room/1870967813</v>
       </c>
       <c r="D128" t="str">
         <v>2026-02-03</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>Bohemio</v>
+        <v>Ants In My Room - Single</v>
       </c>
       <c r="G128" t="str">
-        <v>3:11</v>
+        <v>2:48</v>
       </c>
       <c r="H128" t="str">
-        <v>Nicky Jam</v>
+        <v>Carter Vail</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/nicky-jam/33987470</v>
+        <v>https://music.apple.com/us/artist/carter-vail/1102115053</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/baddie/1849760822</v>
+        <v>https://music.apple.com/us/album/ants-in-my-room/1870967810</v>
       </c>
       <c r="L128" t="str">
-        <v>Baddie - Nicky Jam</v>
+        <v>Ants In My Room - Carter Vail</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>What You Need - A COLORS SHOW</v>
+        <v>Baddie</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/what-you-need-a-colors-show/1870990925</v>
+        <v>https://music.apple.com/us/song/baddie/1849760827</v>
       </c>
       <c r="D129" t="str">
         <v>2026-02-03</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>What You Need - A COLORS SHOW - Single</v>
+        <v>Bohemio</v>
       </c>
       <c r="G129" t="str">
-        <v>3:51</v>
+        <v>3:11</v>
       </c>
       <c r="H129" t="str">
-        <v>Tems</v>
+        <v>Nicky Jam</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/tems/1413909060</v>
+        <v>https://music.apple.com/us/artist/nicky-jam/33987470</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/what-you-need-a-colors-show/1870990923</v>
+        <v>https://music.apple.com/us/album/baddie/1849760822</v>
       </c>
       <c r="L129" t="str">
-        <v>What You Need - A COLORS SHOW - Tems</v>
+        <v>Baddie - Nicky Jam</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>OK OK (Hamdi remix)</v>
+        <v>What You Need - A COLORS SHOW</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/ok-ok-hamdi-remix/1871538130</v>
+        <v>https://music.apple.com/us/song/what-you-need-a-colors-show/1870990925</v>
       </c>
       <c r="D130" t="str">
         <v>2026-02-03</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>OK OK (Hamdi remix) - Single</v>
+        <v>What You Need - A COLORS SHOW - Single</v>
       </c>
       <c r="G130" t="str">
-        <v>3:16</v>
+        <v>3:51</v>
       </c>
       <c r="H130" t="str">
-        <v>Fred again..</v>
+        <v>Tems</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
+        <v>https://music.apple.com/us/artist/tems/1413909060</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/ok-ok-hamdi-remix/1871538128</v>
+        <v>https://music.apple.com/us/album/what-you-need-a-colors-show/1870990923</v>
       </c>
       <c r="L130" t="str">
-        <v>OK OK (Hamdi remix) - Fred again..</v>
+        <v>What You Need - A COLORS SHOW - Tems</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Ever and Ever Before (feat. MŌRIAH &amp; Courtney)</v>
+        <v>OK OK (Hamdi remix)</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/ever-and-ever-before-feat-m%C5%8Driah-courtney/1869383260</v>
+        <v>https://music.apple.com/us/song/ok-ok-hamdi-remix/1871538130</v>
       </c>
       <c r="D131" t="str">
         <v>2026-02-03</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>Ever and Ever Before (feat. MŌRIAH &amp; Courtney) - Single</v>
+        <v>OK OK (Hamdi remix) - Single</v>
       </c>
       <c r="G131" t="str">
-        <v>3:50</v>
+        <v>3:16</v>
       </c>
       <c r="H131" t="str">
-        <v>for KING &amp; COUNTRY</v>
+        <v>Fred again..</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/for-king-country/457871289</v>
+        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/ever-and-ever-before-feat-m%C5%8Driah-courtney/1869383258</v>
+        <v>https://music.apple.com/us/album/ok-ok-hamdi-remix/1871538128</v>
       </c>
       <c r="L131" t="str">
-        <v>Ever and Ever Before (feat. MŌRIAH &amp; Courtney) - for KING &amp; COUNTRY</v>
+        <v>OK OK (Hamdi remix) - Fred again..</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>For The First Time, Again</v>
+        <v>Ever and Ever Before (feat. MŌRIAH &amp; Courtney)</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/for-the-first-time-again/1834736723</v>
+        <v>https://music.apple.com/us/song/ever-and-ever-before-feat-m%C5%8Driah-courtney/1869383260</v>
       </c>
       <c r="D132" t="str">
         <v>2026-02-03</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>For The First Time, Again</v>
+        <v>Ever and Ever Before (feat. MŌRIAH &amp; Courtney) - Single</v>
       </c>
       <c r="G132" t="str">
-        <v>3:33</v>
+        <v>3:50</v>
       </c>
       <c r="H132" t="str">
-        <v>Tyler Ballgame</v>
+        <v>for KING &amp; COUNTRY</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/tyler-ballgame/1755347001</v>
+        <v>https://music.apple.com/us/artist/for-king-country/457871289</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/for-the-first-time-again/1834736717</v>
+        <v>https://music.apple.com/us/album/ever-and-ever-before-feat-m%C5%8Driah-courtney/1869383258</v>
       </c>
       <c r="L132" t="str">
-        <v>For The First Time, Again - Tyler Ballgame</v>
+        <v>Ever and Ever Before (feat. MŌRIAH &amp; Courtney) - for KING &amp; COUNTRY</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Liars Tale</v>
+        <v>For The First Time, Again</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/liars-tale/1862207951</v>
+        <v>https://music.apple.com/us/song/for-the-first-time-again/1834736723</v>
       </c>
       <c r="D133" t="str">
         <v>2026-02-03</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Liars Tale - Single</v>
+        <v>For The First Time, Again</v>
       </c>
       <c r="G133" t="str">
-        <v>3:17</v>
+        <v>3:33</v>
       </c>
       <c r="H133" t="str">
-        <v>Kneecap</v>
+        <v>Tyler Ballgame</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
+        <v>https://music.apple.com/us/artist/tyler-ballgame/1755347001</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/liars-tale/1862207946</v>
+        <v>https://music.apple.com/us/album/for-the-first-time-again/1834736717</v>
       </c>
       <c r="L133" t="str">
-        <v>Liars Tale - Kneecap</v>
+        <v>For The First Time, Again - Tyler Ballgame</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Afraid Of The Dark</v>
+        <v>Liars Tale</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/afraid-of-the-dark/1872184048</v>
+        <v>https://music.apple.com/us/song/liars-tale/1862207951</v>
       </c>
       <c r="D134" t="str">
         <v>2026-02-03</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>Afraid Of The Dark - Single</v>
+        <v>Liars Tale - Single</v>
       </c>
       <c r="G134" t="str">
-        <v>4:38</v>
+        <v>3:17</v>
       </c>
       <c r="H134" t="str">
-        <v>Motionless In White</v>
+        <v>Kneecap</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/motionless-in-white/266666216</v>
+        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/afraid-of-the-dark/1872184047</v>
+        <v>https://music.apple.com/us/album/liars-tale/1862207946</v>
       </c>
       <c r="L134" t="str">
-        <v>Afraid Of The Dark - Motionless In White</v>
+        <v>Liars Tale - Kneecap</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Wake Up Calling</v>
+        <v>Afraid Of The Dark</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/wake-up-calling/1862338150</v>
+        <v>https://music.apple.com/us/song/afraid-of-the-dark/1872184048</v>
       </c>
       <c r="D135" t="str">
         <v>2026-02-03</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>Wake Up Calling - Single</v>
+        <v>Afraid Of The Dark - Single</v>
       </c>
       <c r="G135" t="str">
-        <v>3:49</v>
+        <v>4:38</v>
       </c>
       <c r="H135" t="str">
-        <v>Papa Roach</v>
+        <v>Motionless In White</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/papa-roach/3445763</v>
+        <v>https://music.apple.com/us/artist/motionless-in-white/266666216</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/wake-up-calling/1862338148</v>
+        <v>https://music.apple.com/us/album/afraid-of-the-dark/1872184047</v>
       </c>
       <c r="L135" t="str">
-        <v>Wake Up Calling - Papa Roach</v>
+        <v>Afraid Of The Dark - Motionless In White</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>HIGH</v>
+        <v>Wake Up Calling</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/high/1867202644</v>
+        <v>https://music.apple.com/us/song/wake-up-calling/1862338150</v>
       </c>
       <c r="D136" t="str">
         <v>2026-02-03</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>NIGHTS AFTER VAMP</v>
+        <v>Wake Up Calling - Single</v>
       </c>
       <c r="G136" t="str">
-        <v>3:23</v>
+        <v>3:49</v>
       </c>
       <c r="H136" t="str">
-        <v>Magnolia Park</v>
+        <v>Papa Roach</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/magnolia-park/1413545983</v>
+        <v>https://music.apple.com/us/artist/papa-roach/3445763</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/high/1867202638</v>
+        <v>https://music.apple.com/us/album/wake-up-calling/1862338148</v>
       </c>
       <c r="L136" t="str">
-        <v>HIGH - Magnolia Park</v>
+        <v>Wake Up Calling - Papa Roach</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Villain</v>
+        <v>HIGH</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/villain/1860126455</v>
+        <v>https://music.apple.com/us/song/high/1867202644</v>
       </c>
       <c r="D137" t="str">
         <v>2026-02-03</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>Reflections</v>
+        <v>NIGHTS AFTER VAMP</v>
       </c>
       <c r="G137" t="str">
-        <v>3:53</v>
+        <v>3:23</v>
       </c>
       <c r="H137" t="str">
-        <v>From Ashes to New</v>
+        <v>Magnolia Park</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/from-ashes-to-new/688645097</v>
+        <v>https://music.apple.com/us/artist/magnolia-park/1413545983</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/villain/1860126452</v>
+        <v>https://music.apple.com/us/album/high/1867202638</v>
       </c>
       <c r="L137" t="str">
-        <v>Villain - From Ashes to New</v>
+        <v>HIGH - Magnolia Park</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Bad Idea Right?</v>
+        <v>Villain</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/bad-idea-right/1869792549</v>
+        <v>https://music.apple.com/us/song/villain/1860126455</v>
       </c>
       <c r="D138" t="str">
         <v>2026-02-03</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>Bridgerton Season Four (Covers from the Netflix Series – Pt. 1) - EP</v>
+        <v>Reflections</v>
       </c>
       <c r="G138" t="str">
-        <v>3:00</v>
+        <v>3:53</v>
       </c>
       <c r="H138" t="str">
-        <v>Caleb Chan</v>
+        <v>From Ashes to New</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/caleb-chan/1441662972</v>
+        <v>https://music.apple.com/us/artist/from-ashes-to-new/688645097</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/bad-idea-right/1869792542</v>
+        <v>https://music.apple.com/us/album/villain/1860126452</v>
       </c>
       <c r="L138" t="str">
-        <v>Bad Idea Right? - Caleb Chan</v>
+        <v>Villain - From Ashes to New</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Residue</v>
+        <v>Bad Idea Right?</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/residue/1863786787</v>
+        <v>https://music.apple.com/us/song/bad-idea-right/1869792549</v>
       </c>
       <c r="D139" t="str">
         <v>2026-02-03</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>The Moment (The Score)</v>
+        <v>Bridgerton Season Four (Covers from the Netflix Series – Pt. 1) - EP</v>
       </c>
       <c r="G139" t="str">
-        <v>3:28</v>
+        <v>3:00</v>
       </c>
       <c r="H139" t="str">
-        <v>A. G. Cook</v>
+        <v>Caleb Chan</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/a-g-cook/744253464</v>
+        <v>https://music.apple.com/us/artist/caleb-chan/1441662972</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/residue/1863786786</v>
+        <v>https://music.apple.com/us/album/bad-idea-right/1869792542</v>
       </c>
       <c r="L139" t="str">
-        <v>Residue - A. G. Cook</v>
+        <v>Bad Idea Right? - Caleb Chan</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>I Used to Go to This Bar</v>
+        <v>Residue</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/i-used-to-go-to-this-bar/1839918872</v>
+        <v>https://music.apple.com/us/song/residue/1863786787</v>
       </c>
       <c r="D140" t="str">
         <v>2026-02-03</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>I Used to Go to This Bar</v>
+        <v>The Moment (The Score)</v>
       </c>
       <c r="G140" t="str">
-        <v>2:12</v>
+        <v>3:28</v>
       </c>
       <c r="H140" t="str">
-        <v>Joyce Manor</v>
+        <v>A. G. Cook</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/joyce-manor/408598559</v>
+        <v>https://music.apple.com/us/artist/a-g-cook/744253464</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/i-used-to-go-to-this-bar/1839918836</v>
+        <v>https://music.apple.com/us/album/residue/1863786786</v>
       </c>
       <c r="L140" t="str">
-        <v>I Used to Go to This Bar - Joyce Manor</v>
+        <v>Residue - A. G. Cook</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Starlight</v>
+        <v>I Used to Go to This Bar</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/starlight/1870989674</v>
+        <v>https://music.apple.com/us/song/i-used-to-go-to-this-bar/1839918872</v>
       </c>
       <c r="D141" t="str">
         <v>2026-02-03</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Everything Glows</v>
+        <v>I Used to Go to This Bar</v>
       </c>
       <c r="G141" t="str">
-        <v>3:21</v>
+        <v>2:12</v>
       </c>
       <c r="H141" t="str">
-        <v>Cannons</v>
+        <v>Joyce Manor</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/cannons/65568551</v>
+        <v>https://music.apple.com/us/artist/joyce-manor/408598559</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/starlight/1870989672</v>
+        <v>https://music.apple.com/us/album/i-used-to-go-to-this-bar/1839918836</v>
       </c>
       <c r="L141" t="str">
-        <v>Starlight - Cannons</v>
+        <v>I Used to Go to This Bar - Joyce Manor</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Dandelion</v>
+        <v>Starlight</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/dandelion/1863154133</v>
+        <v>https://music.apple.com/us/song/starlight/1870989674</v>
       </c>
       <c r="D142" t="str">
         <v>2026-02-03</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Corporate Pudding - EP</v>
+        <v>Everything Glows</v>
       </c>
       <c r="G142" t="str">
-        <v>3:14</v>
+        <v>3:21</v>
       </c>
       <c r="H142" t="str">
-        <v>Dogpark</v>
+        <v>Cannons</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/dogpark/1710263796</v>
+        <v>https://music.apple.com/us/artist/cannons/65568551</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/dandelion/1863154124</v>
+        <v>https://music.apple.com/us/album/starlight/1870989672</v>
       </c>
       <c r="L142" t="str">
-        <v>Dandelion - Dogpark</v>
+        <v>Starlight - Cannons</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>THEMSELVES</v>
+        <v>Dandelion</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/themselves/1845287173</v>
+        <v>https://music.apple.com/us/song/dandelion/1863154133</v>
       </c>
       <c r="D143" t="str">
         <v>2026-02-03</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>BACKWARD</v>
+        <v>Corporate Pudding - EP</v>
       </c>
       <c r="G143" t="str">
-        <v>2:46</v>
+        <v>3:14</v>
       </c>
       <c r="H143" t="str">
-        <v>Jordan Ward</v>
+        <v>Dogpark</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/jordan-ward/689602960</v>
+        <v>https://music.apple.com/us/artist/dogpark/1710263796</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/themselves/1845286980</v>
+        <v>https://music.apple.com/us/album/dandelion/1863154124</v>
       </c>
       <c r="L143" t="str">
-        <v>THEMSELVES - Jordan Ward</v>
+        <v>Dandelion - Dogpark</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>High Maintenance</v>
+        <v>THEMSELVES</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/high-maintenance/1872497656</v>
+        <v>https://music.apple.com/us/song/themselves/1845287173</v>
       </c>
       <c r="D144" t="str">
         <v>2026-02-03</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Miracle Mile</v>
+        <v>BACKWARD</v>
       </c>
       <c r="G144" t="str">
-        <v>2:24</v>
+        <v>2:46</v>
       </c>
       <c r="H144" t="str">
-        <v>Paul Russell</v>
+        <v>Jordan Ward</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/paul-russell/1304377463</v>
+        <v>https://music.apple.com/us/artist/jordan-ward/689602960</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/high-maintenance/1872496993</v>
+        <v>https://music.apple.com/us/album/themselves/1845286980</v>
       </c>
       <c r="L144" t="str">
-        <v>High Maintenance - Paul Russell</v>
+        <v>THEMSELVES - Jordan Ward</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Trackhawk</v>
+        <v>High Maintenance</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/trackhawk/1860991724</v>
+        <v>https://music.apple.com/us/song/high-maintenance/1872497656</v>
       </c>
       <c r="D145" t="str">
         <v>2026-02-03</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Da Realest</v>
+        <v>Miracle Mile</v>
       </c>
       <c r="G145" t="str">
-        <v>1:59</v>
+        <v>2:24</v>
       </c>
       <c r="H145" t="str">
-        <v>Babyfxce E</v>
+        <v>Paul Russell</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/babyfxce-e/1573432856</v>
+        <v>https://music.apple.com/us/artist/paul-russell/1304377463</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/trackhawk/1860991661</v>
+        <v>https://music.apple.com/us/album/high-maintenance/1872496993</v>
       </c>
       <c r="L145" t="str">
-        <v>Trackhawk - Babyfxce E</v>
+        <v>High Maintenance - Paul Russell</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Wheel Man</v>
+        <v>Trackhawk</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/wheel-man/1872178895</v>
+        <v>https://music.apple.com/us/song/trackhawk/1860991724</v>
       </c>
       <c r="D146" t="str">
         <v>2026-02-03</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>Xavier</v>
+        <v>Da Realest</v>
       </c>
       <c r="G146" t="str">
-        <v>3:05</v>
+        <v>1:59</v>
       </c>
       <c r="H146" t="str">
-        <v>xaviersobased</v>
+        <v>Babyfxce E</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/xaviersobased/1540848340</v>
+        <v>https://music.apple.com/us/artist/babyfxce-e/1573432856</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/wheel-man/1872178596</v>
+        <v>https://music.apple.com/us/album/trackhawk/1860991661</v>
       </c>
       <c r="L146" t="str">
-        <v>Wheel Man - xaviersobased</v>
+        <v>Trackhawk - Babyfxce E</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Natural Disaster</v>
+        <v>Wheel Man</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/natural-disaster/1871263211</v>
+        <v>https://music.apple.com/us/song/wheel-man/1872178895</v>
       </c>
       <c r="D147" t="str">
         <v>2026-02-03</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Natural Disaster - Single</v>
+        <v>Xavier</v>
       </c>
       <c r="G147" t="str">
-        <v>3:02</v>
+        <v>3:05</v>
       </c>
       <c r="H147" t="str">
-        <v>Lauren Spencer Smith</v>
+        <v>xaviersobased</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/lauren-spencer-smith/1462708784</v>
+        <v>https://music.apple.com/us/artist/xaviersobased/1540848340</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/natural-disaster/1871263207</v>
+        <v>https://music.apple.com/us/album/wheel-man/1872178596</v>
       </c>
       <c r="L147" t="str">
-        <v>Natural Disaster - Lauren Spencer Smith</v>
+        <v>Wheel Man - xaviersobased</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Prettier</v>
+        <v>Natural Disaster</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/prettier/1869745409</v>
+        <v>https://music.apple.com/us/song/natural-disaster/1871263211</v>
       </c>
       <c r="D148" t="str">
         <v>2026-02-03</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Prettier - Single</v>
+        <v>Natural Disaster - Single</v>
       </c>
       <c r="G148" t="str">
-        <v>2:34</v>
+        <v>3:02</v>
       </c>
       <c r="H148" t="str">
-        <v>Grace VanderWaal</v>
+        <v>Lauren Spencer Smith</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/grace-vanderwaal/1175539534</v>
+        <v>https://music.apple.com/us/artist/lauren-spencer-smith/1462708784</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/prettier/1869745403</v>
+        <v>https://music.apple.com/us/album/natural-disaster/1871263207</v>
       </c>
       <c r="L148" t="str">
-        <v>Prettier - Grace VanderWaal</v>
+        <v>Natural Disaster - Lauren Spencer Smith</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Shotta Flow 8</v>
+        <v>Prettier</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/shotta-flow-8/1872760524</v>
+        <v>https://music.apple.com/us/song/prettier/1869745409</v>
       </c>
       <c r="D149" t="str">
         <v>2026-02-03</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>Shotta Flow 8 - Single</v>
+        <v>Prettier - Single</v>
       </c>
       <c r="G149" t="str">
-        <v>3:21</v>
+        <v>2:34</v>
       </c>
       <c r="H149" t="str">
-        <v>NLE Choppa</v>
+        <v>Grace VanderWaal</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/nle-choppa/1449052753</v>
+        <v>https://music.apple.com/us/artist/grace-vanderwaal/1175539534</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/shotta-flow-8/1872760520</v>
+        <v>https://music.apple.com/us/album/prettier/1869745403</v>
       </c>
       <c r="L149" t="str">
-        <v>Shotta Flow 8 - NLE Choppa</v>
+        <v>Prettier - Grace VanderWaal</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Die To Fall</v>
+        <v>Shotta Flow 8</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/die-to-fall/1866902681</v>
+        <v>https://music.apple.com/us/song/shotta-flow-8/1872760524</v>
       </c>
       <c r="D150" t="str">
         <v>2026-02-03</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>Die To Fall - Single</v>
+        <v>Shotta Flow 8 - Single</v>
       </c>
       <c r="G150" t="str">
-        <v>3:20</v>
+        <v>3:21</v>
       </c>
       <c r="H150" t="str">
-        <v>The Maine</v>
+        <v>NLE Choppa</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
+        <v>https://music.apple.com/us/artist/nle-choppa/1449052753</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/die-to-fall/1866902679</v>
+        <v>https://music.apple.com/us/album/shotta-flow-8/1872760520</v>
       </c>
       <c r="L150" t="str">
-        <v>Die To Fall - The Maine</v>
+        <v>Shotta Flow 8 - NLE Choppa</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>The Cruel Angel's Thesis (Neon Genesis Evangelion)</v>
+        <v>Die To Fall</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/the-cruel-angels-thesis-neon-genesis-evangelion/1864932139</v>
+        <v>https://music.apple.com/us/song/die-to-fall/1866902681</v>
       </c>
       <c r="D151" t="str">
         <v>2026-02-03</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>The Cruel Angel's Thesis (Neon Genesis Evangelion) - Single</v>
+        <v>Die To Fall - Single</v>
       </c>
       <c r="G151" t="str">
-        <v>2:58</v>
+        <v>3:20</v>
       </c>
       <c r="H151" t="str">
-        <v>Steve Aoki</v>
+        <v>The Maine</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/steve-aoki/271066694</v>
+        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/the-cruel-angels-thesis-neon-genesis-evangelion/1864932135</v>
+        <v>https://music.apple.com/us/album/die-to-fall/1866902679</v>
       </c>
       <c r="L151" t="str">
-        <v>The Cruel Angel's Thesis (Neon Genesis Evangelion) - Steve Aoki</v>
+        <v>Die To Fall - The Maine</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Slow Burn</v>
+        <v>The Cruel Angel's Thesis (Neon Genesis Evangelion)</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/slow-burn/1851033862</v>
+        <v>https://music.apple.com/us/song/the-cruel-angels-thesis-neon-genesis-evangelion/1864932139</v>
       </c>
       <c r="D152" t="str">
         <v>2026-02-03</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>Still There’s a Glow</v>
+        <v>The Cruel Angel's Thesis (Neon Genesis Evangelion) - Single</v>
       </c>
       <c r="G152" t="str">
-        <v>2:14</v>
+        <v>2:58</v>
       </c>
       <c r="H152" t="str">
-        <v>Sweet Pill</v>
+        <v>Steve Aoki</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/sweet-pill/1459476044</v>
+        <v>https://music.apple.com/us/artist/steve-aoki/271066694</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/slow-burn/1851033857</v>
+        <v>https://music.apple.com/us/album/the-cruel-angels-thesis-neon-genesis-evangelion/1864932135</v>
       </c>
       <c r="L152" t="str">
-        <v>Slow Burn - Sweet Pill</v>
+        <v>The Cruel Angel's Thesis (Neon Genesis Evangelion) - Steve Aoki</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Too Late</v>
+        <v>Slow Burn</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/too-late/1857999860</v>
+        <v>https://music.apple.com/us/song/slow-burn/1851033862</v>
       </c>
       <c r="D153" t="str">
         <v>2026-02-03</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Evergreen</v>
+        <v>Still There’s a Glow</v>
       </c>
       <c r="G153" t="str">
-        <v>2:56</v>
+        <v>2:14</v>
       </c>
       <c r="H153" t="str">
-        <v>Hunter Hayes</v>
+        <v>Sweet Pill</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/hunter-hayes/429231434</v>
+        <v>https://music.apple.com/us/artist/sweet-pill/1459476044</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/too-late/1857999850</v>
+        <v>https://music.apple.com/us/album/slow-burn/1851033857</v>
       </c>
       <c r="L153" t="str">
-        <v>Too Late - Hunter Hayes</v>
+        <v>Slow Burn - Sweet Pill</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Mono (feat. skaiwater)</v>
+        <v>Too Late</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/mono-feat-skaiwater/1869130804</v>
+        <v>https://music.apple.com/us/song/too-late/1857999860</v>
       </c>
       <c r="D154" t="str">
         <v>2026-02-03</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>Mono (feat. skaiwater) - Single</v>
+        <v>Evergreen</v>
       </c>
       <c r="G154" t="str">
-        <v>2:50</v>
+        <v>2:56</v>
       </c>
       <c r="H154" t="str">
-        <v>i-dle</v>
+        <v>Hunter Hayes</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/i-dle/1378887586</v>
+        <v>https://music.apple.com/us/artist/hunter-hayes/429231434</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/mono-feat-skaiwater/1869130801</v>
+        <v>https://music.apple.com/us/album/too-late/1857999850</v>
       </c>
       <c r="L154" t="str">
-        <v>Mono (feat. skaiwater) - i-dle</v>
+        <v>Too Late - Hunter Hayes</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Thank You Is Enough</v>
+        <v>Mono (feat. skaiwater)</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/thank-you-is-enough/1870679042</v>
+        <v>https://music.apple.com/us/song/mono-feat-skaiwater/1869130804</v>
       </c>
       <c r="D155" t="str">
         <v>2026-02-03</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>Yo Gabba GabbaLand! (Season 2) [Apple TV+ Original Series Soundtrack]</v>
+        <v>Mono (feat. skaiwater) - Single</v>
       </c>
       <c r="G155" t="str">
-        <v>1:55</v>
+        <v>2:50</v>
       </c>
       <c r="H155" t="str">
-        <v>Yo Gabba Gabba</v>
+        <v>i-dle</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/yo-gabba-gabba/433108373</v>
+        <v>https://music.apple.com/us/artist/i-dle/1378887586</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/thank-you-is-enough/1870678950</v>
+        <v>https://music.apple.com/us/album/mono-feat-skaiwater/1869130801</v>
       </c>
       <c r="L155" t="str">
-        <v>Thank You Is Enough - Yo Gabba Gabba</v>
+        <v>Mono (feat. skaiwater) - i-dle</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>RIDIN</v>
+        <v>Thank You Is Enough</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/ridin/1869786726</v>
+        <v>https://music.apple.com/us/song/thank-you-is-enough/1870679042</v>
       </c>
       <c r="D156" t="str">
         <v>2026-02-03</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>RIDIN - Single</v>
+        <v>Yo Gabba GabbaLand! (Season 2) [Apple TV+ Original Series Soundtrack]</v>
       </c>
       <c r="G156" t="str">
-        <v>2:00</v>
+        <v>1:55</v>
       </c>
       <c r="H156" t="str">
-        <v>Tokischa</v>
+        <v>Yo Gabba Gabba</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/tokischa/1414103446</v>
+        <v>https://music.apple.com/us/artist/yo-gabba-gabba/433108373</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/ridin/1869786725</v>
+        <v>https://music.apple.com/us/album/thank-you-is-enough/1870678950</v>
       </c>
       <c r="L156" t="str">
-        <v>RIDIN - Tokischa</v>
+        <v>Thank You Is Enough - Yo Gabba Gabba</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>POSSESSION</v>
+        <v>RIDIN</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/possession/1872536200</v>
+        <v>https://music.apple.com/us/song/ridin/1869786726</v>
       </c>
       <c r="D157" t="str">
         <v>2026-02-03</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>POSSESSION - Single</v>
+        <v>RIDIN - Single</v>
       </c>
       <c r="G157" t="str">
-        <v>3:07</v>
+        <v>2:00</v>
       </c>
       <c r="H157" t="str">
-        <v>Melanie Martinez</v>
+        <v>Tokischa</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/melanie-martinez/993014053</v>
+        <v>https://music.apple.com/us/artist/tokischa/1414103446</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/possession/1872536199</v>
+        <v>https://music.apple.com/us/album/ridin/1869786725</v>
       </c>
       <c r="L157" t="str">
-        <v>POSSESSION - Melanie Martinez</v>
+        <v>RIDIN - Tokischa</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Poema</v>
+        <v>POSSESSION</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/poema/1872723644</v>
+        <v>https://music.apple.com/us/song/possession/1872536200</v>
       </c>
       <c r="D158" t="str">
         <v>2026-02-03</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>Poema - Single</v>
+        <v>POSSESSION - Single</v>
       </c>
       <c r="G158" t="str">
-        <v>3:14</v>
+        <v>3:07</v>
       </c>
       <c r="H158" t="str">
-        <v>Óscar Maydon</v>
+        <v>Melanie Martinez</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/%C3%B3scar-maydon/1524147696</v>
+        <v>https://music.apple.com/us/artist/melanie-martinez/993014053</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/poema/1872723468</v>
+        <v>https://music.apple.com/us/album/possession/1872536199</v>
       </c>
       <c r="L158" t="str">
-        <v>Poema - Óscar Maydon</v>
+        <v>POSSESSION - Melanie Martinez</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Live Without</v>
+        <v>Poema</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/live-without/1862777625</v>
+        <v>https://music.apple.com/us/song/poema/1872723644</v>
       </c>
       <c r="D159" t="str">
         <v>2026-02-03</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>WORRIED SICK (Deluxe Edition)</v>
+        <v>Poema - Single</v>
       </c>
       <c r="G159" t="str">
-        <v>2:55</v>
+        <v>3:14</v>
       </c>
       <c r="H159" t="str">
-        <v>Meet Me @ The Altar</v>
+        <v>Óscar Maydon</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/meet-me-the-altar/1109900880</v>
+        <v>https://music.apple.com/us/artist/%C3%B3scar-maydon/1524147696</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/live-without/1862777608</v>
+        <v>https://music.apple.com/us/album/poema/1872723468</v>
       </c>
       <c r="L159" t="str">
-        <v>Live Without - Meet Me @ The Altar</v>
+        <v>Poema - Óscar Maydon</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>FANÁTICO</v>
+        <v>Live Without</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/fan%C3%A1tico/1871611852</v>
+        <v>https://music.apple.com/us/song/live-without/1862777625</v>
       </c>
       <c r="D160" t="str">
         <v>2026-02-03</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>FANÁTICO - Single</v>
+        <v>WORRIED SICK (Deluxe Edition)</v>
       </c>
       <c r="G160" t="str">
-        <v>3:55</v>
+        <v>2:55</v>
       </c>
       <c r="H160" t="str">
-        <v>Blessd</v>
+        <v>Meet Me @ The Altar</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/blessd/1481245915</v>
+        <v>https://music.apple.com/us/artist/meet-me-the-altar/1109900880</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/fan%C3%A1tico/1871611851</v>
+        <v>https://music.apple.com/us/album/live-without/1862777608</v>
       </c>
       <c r="L160" t="str">
-        <v>FANÁTICO - Blessd</v>
+        <v>Live Without - Meet Me @ The Altar</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Frozen Lake</v>
+        <v>FANÁTICO</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/frozen-lake/1867287070</v>
+        <v>https://music.apple.com/us/song/fan%C3%A1tico/1871611852</v>
       </c>
       <c r="D161" t="str">
         <v>2026-02-03</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>Frozen Lake - Single</v>
+        <v>FANÁTICO - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>3:29</v>
+        <v>3:55</v>
       </c>
       <c r="H161" t="str">
-        <v>VOILÀ</v>
+        <v>Blessd</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/voil%C3%A0/1333272109</v>
+        <v>https://music.apple.com/us/artist/blessd/1481245915</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/frozen-lake/1867287069</v>
+        <v>https://music.apple.com/us/album/fan%C3%A1tico/1871611851</v>
       </c>
       <c r="L161" t="str">
-        <v>Frozen Lake - VOILÀ</v>
+        <v>FANÁTICO - Blessd</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Fine Shyt (EB Remix) [feat. Eric Bellinger]</v>
+        <v>Frozen Lake</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/fine-shyt-eb-remix-feat-eric-bellinger/1870964385</v>
+        <v>https://music.apple.com/us/song/frozen-lake/1867287070</v>
       </c>
       <c r="D162" t="str">
         <v>2026-02-03</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>Fine Shyt (EB Remix) [feat. Eric Bellinger] - Single</v>
+        <v>Frozen Lake - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>2:45</v>
+        <v>3:29</v>
       </c>
       <c r="H162" t="str">
-        <v>VEDO</v>
+        <v>VOILÀ</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/vedo/267769510</v>
+        <v>https://music.apple.com/us/artist/voil%C3%A0/1333272109</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/fine-shyt-eb-remix-feat-eric-bellinger/1870964384</v>
+        <v>https://music.apple.com/us/album/frozen-lake/1867287069</v>
       </c>
       <c r="L162" t="str">
-        <v>Fine Shyt (EB Remix) [feat. Eric Bellinger] - VEDO</v>
+        <v>Frozen Lake - VOILÀ</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Hell Yeah (Feat. Waxmaster)</v>
+        <v>Fine Shyt (EB Remix) [feat. Eric Bellinger]</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/hell-yeah-feat-waxmaster/1866602820</v>
+        <v>https://music.apple.com/us/song/fine-shyt-eb-remix-feat-eric-bellinger/1870964385</v>
       </c>
       <c r="D163" t="str">
         <v>2026-02-03</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>Hell Yeah (Feat. Waxmaster) - Single</v>
+        <v>Fine Shyt (EB Remix) [feat. Eric Bellinger] - Single</v>
       </c>
       <c r="G163" t="str">
-        <v>3:32</v>
+        <v>2:45</v>
       </c>
       <c r="H163" t="str">
-        <v>Chris Lorenzo</v>
+        <v>VEDO</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/chris-lorenzo/621431022</v>
+        <v>https://music.apple.com/us/artist/vedo/267769510</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/hell-yeah-feat-waxmaster/1866602819</v>
+        <v>https://music.apple.com/us/album/fine-shyt-eb-remix-feat-eric-bellinger/1870964384</v>
       </c>
       <c r="L163" t="str">
-        <v>Hell Yeah (Feat. Waxmaster) - Chris Lorenzo</v>
+        <v>Fine Shyt (EB Remix) [feat. Eric Bellinger] - VEDO</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>It’s Like That</v>
+        <v>Hell Yeah (Feat. Waxmaster)</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/its-like-that/1858689757</v>
+        <v>https://music.apple.com/us/song/hell-yeah-feat-waxmaster/1866602820</v>
       </c>
       <c r="D164" t="str">
         <v>2026-02-03</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>A Pound of Feathers</v>
+        <v>Hell Yeah (Feat. Waxmaster) - Single</v>
       </c>
       <c r="G164" t="str">
-        <v>3:20</v>
+        <v>3:32</v>
       </c>
       <c r="H164" t="str">
-        <v>The Black Crowes</v>
+        <v>Chris Lorenzo</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/the-black-crowes/2969371</v>
+        <v>https://music.apple.com/us/artist/chris-lorenzo/621431022</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/its-like-that/1858689485</v>
+        <v>https://music.apple.com/us/album/hell-yeah-feat-waxmaster/1866602819</v>
       </c>
       <c r="L164" t="str">
-        <v>It’s Like That - The Black Crowes</v>
+        <v>Hell Yeah (Feat. Waxmaster) - Chris Lorenzo</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>A.S.A.P.</v>
+        <v>It’s Like That</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/a-s-a-p/1833414737</v>
+        <v>https://music.apple.com/us/song/its-like-that/1858689757</v>
       </c>
       <c r="D165" t="str">
         <v>2026-02-03</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>A.S.A.P. - Single</v>
+        <v>A Pound of Feathers</v>
       </c>
       <c r="G165" t="str">
-        <v>2:48</v>
+        <v>3:20</v>
       </c>
       <c r="H165" t="str">
-        <v>Mýa</v>
+        <v>The Black Crowes</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/m%C3%BDa/108751</v>
+        <v>https://music.apple.com/us/artist/the-black-crowes/2969371</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/a-s-a-p/1833414736</v>
+        <v>https://music.apple.com/us/album/its-like-that/1858689485</v>
       </c>
       <c r="L165" t="str">
-        <v>A.S.A.P. - Mýa</v>
+        <v>It’s Like That - The Black Crowes</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Once I Say</v>
+        <v>A.S.A.P.</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/once-i-say/1867855025</v>
+        <v>https://music.apple.com/us/song/a-s-a-p/1833414737</v>
       </c>
       <c r="D166" t="str">
         <v>2026-02-03</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>PASSION</v>
+        <v>A.S.A.P. - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>3:21</v>
+        <v>2:48</v>
       </c>
       <c r="H166" t="str">
-        <v>Terrace Martin</v>
+        <v>Mýa</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/terrace-martin/27522754</v>
+        <v>https://music.apple.com/us/artist/m%C3%BDa/108751</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/once-i-say/1867854756</v>
+        <v>https://music.apple.com/us/album/a-s-a-p/1833414736</v>
       </c>
       <c r="L166" t="str">
-        <v>Once I Say - Terrace Martin</v>
+        <v>A.S.A.P. - Mýa</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>believer</v>
+        <v>Once I Say</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/believer/1862797080</v>
+        <v>https://music.apple.com/us/song/once-i-say/1867855025</v>
       </c>
       <c r="D167" t="str">
         <v>2026-02-03</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>believer - Single</v>
+        <v>PASSION</v>
       </c>
       <c r="G167" t="str">
-        <v>2:57</v>
+        <v>3:21</v>
       </c>
       <c r="H167" t="str">
-        <v>Yuna</v>
+        <v>Terrace Martin</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/yuna/423966062</v>
+        <v>https://music.apple.com/us/artist/terrace-martin/27522754</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/believer/1862796978</v>
+        <v>https://music.apple.com/us/album/once-i-say/1867854756</v>
       </c>
       <c r="L167" t="str">
-        <v>believer - Yuna</v>
+        <v>Once I Say - Terrace Martin</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>I Envy The Wind</v>
+        <v>believer</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/i-envy-the-wind/1863202477</v>
+        <v>https://music.apple.com/us/song/believer/1862797080</v>
       </c>
       <c r="D168" t="str">
         <v>2026-02-03</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>I Envy The Wind - Single</v>
+        <v>believer - Single</v>
       </c>
       <c r="G168" t="str">
-        <v>3:51</v>
+        <v>2:57</v>
       </c>
       <c r="H168" t="str">
-        <v>Molly Parden</v>
+        <v>Yuna</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/molly-parden/374789677</v>
+        <v>https://music.apple.com/us/artist/yuna/423966062</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/i-envy-the-wind/1863202476</v>
+        <v>https://music.apple.com/us/album/believer/1862796978</v>
       </c>
       <c r="L168" t="str">
-        <v>I Envy The Wind - Molly Parden</v>
+        <v>believer - Yuna</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>The Alchemist</v>
+        <v>I Envy The Wind</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/the-alchemist/1831827347</v>
+        <v>https://music.apple.com/us/song/i-envy-the-wind/1863202477</v>
       </c>
       <c r="D169" t="str">
         <v>2026-02-03</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>The Alchemist</v>
+        <v>I Envy The Wind - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>3:13</v>
+        <v>3:51</v>
       </c>
       <c r="H169" t="str">
-        <v>Bre Kennedy</v>
+        <v>Molly Parden</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/bre-kennedy/1242283415</v>
+        <v>https://music.apple.com/us/artist/molly-parden/374789677</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/the-alchemist/1831827332</v>
+        <v>https://music.apple.com/us/album/i-envy-the-wind/1863202476</v>
       </c>
       <c r="L169" t="str">
-        <v>The Alchemist - Bre Kennedy</v>
+        <v>I Envy The Wind - Molly Parden</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Daysa</v>
+        <v>The Alchemist</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/daysa/1861575845</v>
+        <v>https://music.apple.com/us/song/the-alchemist/1831827347</v>
       </c>
       <c r="D170" t="str">
         <v>2026-02-03</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Daysa - Single</v>
+        <v>The Alchemist</v>
       </c>
       <c r="G170" t="str">
-        <v>4:36</v>
+        <v>3:13</v>
       </c>
       <c r="H170" t="str">
-        <v>⌭ IceMorph ⌬</v>
+        <v>Bre Kennedy</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/icemorph/1733236411</v>
+        <v>https://music.apple.com/us/artist/bre-kennedy/1242283415</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/daysa/1861575844</v>
+        <v>https://music.apple.com/us/album/the-alchemist/1831827332</v>
       </c>
       <c r="L170" t="str">
-        <v>Daysa - ⌭ IceMorph ⌬</v>
+        <v>The Alchemist - Bre Kennedy</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Fabulous</v>
+        <v>Daysa</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/fabulous/1862804005</v>
+        <v>https://music.apple.com/us/song/daysa/1861575845</v>
       </c>
       <c r="D171" t="str">
         <v>2026-02-03</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Fabulous - Single</v>
+        <v>Daysa - Single</v>
       </c>
       <c r="G171" t="str">
-        <v>2:33</v>
+        <v>4:36</v>
       </c>
       <c r="H171" t="str">
-        <v>MEEK</v>
+        <v>⌭ IceMorph ⌬</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/meek/1784432868</v>
+        <v>https://music.apple.com/us/artist/icemorph/1733236411</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/fabulous/1862804004</v>
+        <v>https://music.apple.com/us/album/daysa/1861575844</v>
       </c>
       <c r="L171" t="str">
-        <v>Fabulous - MEEK</v>
+        <v>Daysa - ⌭ IceMorph ⌬</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Me Asusta Amar Tanto la Soledad</v>
+        <v>Fabulous</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/me-asusta-amar-tanto-la-soledad/1866982109</v>
+        <v>https://music.apple.com/us/song/fabulous/1862804005</v>
       </c>
       <c r="D172" t="str">
         <v>2026-02-03</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Me Asusta Amar Tanto la Soledad - Single</v>
+        <v>Fabulous - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>3:22</v>
+        <v>2:33</v>
       </c>
       <c r="H172" t="str">
-        <v>RUBIO</v>
+        <v>MEEK</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/rubio/34747724</v>
+        <v>https://music.apple.com/us/artist/meek/1784432868</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/me-asusta-amar-tanto-la-soledad/1866981907</v>
+        <v>https://music.apple.com/us/album/fabulous/1862804004</v>
       </c>
       <c r="L172" t="str">
-        <v>Me Asusta Amar Tanto la Soledad - RUBIO</v>
+        <v>Fabulous - MEEK</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>brainchem</v>
+        <v>Me Asusta Amar Tanto la Soledad</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/brainchem/1870656942</v>
+        <v>https://music.apple.com/us/song/me-asusta-amar-tanto-la-soledad/1866982109</v>
       </c>
       <c r="D173" t="str">
         <v>2026-02-03</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>brainchem - Single</v>
+        <v>Me Asusta Amar Tanto la Soledad - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>2:28</v>
+        <v>3:22</v>
       </c>
       <c r="H173" t="str">
-        <v>EMJAY</v>
+        <v>RUBIO</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/emjay/1517993423</v>
+        <v>https://music.apple.com/us/artist/rubio/34747724</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/brainchem/1870656608</v>
+        <v>https://music.apple.com/us/album/me-asusta-amar-tanto-la-soledad/1866981907</v>
       </c>
       <c r="L173" t="str">
-        <v>brainchem - EMJAY</v>
+        <v>Me Asusta Amar Tanto la Soledad - RUBIO</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Boyfriend In Yo Brain (Notice Me)</v>
+        <v>brainchem</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/boyfriend-in-yo-brain-notice-me/1871675026</v>
+        <v>https://music.apple.com/us/song/brainchem/1870656942</v>
       </c>
       <c r="D174" t="str">
         <v>2026-02-03</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>With No Due Respect</v>
+        <v>brainchem - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>2:48</v>
+        <v>2:28</v>
       </c>
       <c r="H174" t="str">
-        <v>Foggieraw</v>
+        <v>EMJAY</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/foggieraw/1152021457</v>
+        <v>https://music.apple.com/us/artist/emjay/1517993423</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/boyfriend-in-yo-brain-notice-me/1871675010</v>
+        <v>https://music.apple.com/us/album/brainchem/1870656608</v>
       </c>
       <c r="L174" t="str">
-        <v>Boyfriend In Yo Brain (Notice Me) - Foggieraw</v>
+        <v>brainchem - EMJAY</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Giants</v>
+        <v>Boyfriend In Yo Brain (Notice Me)</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/giants/1869154957</v>
+        <v>https://music.apple.com/us/song/boyfriend-in-yo-brain-notice-me/1871675026</v>
       </c>
       <c r="D175" t="str">
         <v>2026-02-03</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>Giants - Single</v>
+        <v>With No Due Respect</v>
       </c>
       <c r="G175" t="str">
-        <v>3:12</v>
+        <v>2:48</v>
       </c>
       <c r="H175" t="str">
-        <v>Picture This</v>
+        <v>Foggieraw</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/picture-this/1194282721</v>
+        <v>https://music.apple.com/us/artist/foggieraw/1152021457</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/giants/1869154821</v>
+        <v>https://music.apple.com/us/album/boyfriend-in-yo-brain-notice-me/1871675010</v>
       </c>
       <c r="L175" t="str">
-        <v>Giants - Picture This</v>
+        <v>Boyfriend In Yo Brain (Notice Me) - Foggieraw</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Scooby</v>
+        <v>Giants</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/scooby/1872510752</v>
+        <v>https://music.apple.com/us/song/giants/1869154957</v>
       </c>
       <c r="D176" t="str">
         <v>2026-02-03</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Scooby - Single</v>
+        <v>Giants - Single</v>
       </c>
       <c r="G176" t="str">
-        <v>3:41</v>
+        <v>3:12</v>
       </c>
       <c r="H176" t="str">
-        <v>corook</v>
+        <v>Picture This</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/corook/1514463762</v>
+        <v>https://music.apple.com/us/artist/picture-this/1194282721</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/scooby/1872510751</v>
+        <v>https://music.apple.com/us/album/giants/1869154821</v>
       </c>
       <c r="L176" t="str">
-        <v>Scooby - corook</v>
+        <v>Giants - Picture This</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>La Racha</v>
+        <v>Scooby</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/la-racha/1868757762</v>
+        <v>https://music.apple.com/us/song/scooby/1872510752</v>
       </c>
       <c r="D177" t="str">
         <v>2026-02-03</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>La Racha - Single</v>
+        <v>Scooby - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>2:48</v>
+        <v>3:41</v>
       </c>
       <c r="H177" t="str">
-        <v>Hermanos Espinoza</v>
+        <v>corook</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/hermanos-espinoza/1613044599</v>
+        <v>https://music.apple.com/us/artist/corook/1514463762</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/la-racha/1868757747</v>
+        <v>https://music.apple.com/us/album/scooby/1872510751</v>
       </c>
       <c r="L177" t="str">
-        <v>La Racha - Hermanos Espinoza</v>
+        <v>Scooby - corook</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>So Am I</v>
+        <v>La Racha</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/so-am-i/1867012209</v>
+        <v>https://music.apple.com/us/song/la-racha/1868757762</v>
       </c>
       <c r="D178" t="str">
         <v>2026-02-03</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Tell Me How You Really Feel</v>
+        <v>La Racha - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>2:50</v>
+        <v>2:48</v>
       </c>
       <c r="H178" t="str">
-        <v>Katelyn Tarver</v>
+        <v>Hermanos Espinoza</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/katelyn-tarver/2356378</v>
+        <v>https://music.apple.com/us/artist/hermanos-espinoza/1613044599</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/so-am-i/1867012005</v>
+        <v>https://music.apple.com/us/album/la-racha/1868757747</v>
       </c>
       <c r="L178" t="str">
-        <v>So Am I - Katelyn Tarver</v>
+        <v>La Racha - Hermanos Espinoza</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>best thing</v>
+        <v>So Am I</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/best-thing/1860673616</v>
+        <v>https://music.apple.com/us/song/so-am-i/1867012209</v>
       </c>
       <c r="D179" t="str">
         <v>2026-02-03</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>best thing - Single</v>
+        <v>Tell Me How You Really Feel</v>
       </c>
       <c r="G179" t="str">
-        <v>4:27</v>
+        <v>2:50</v>
       </c>
       <c r="H179" t="str">
-        <v>WRABEL</v>
+        <v>Katelyn Tarver</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/wrabel/435072161</v>
+        <v>https://music.apple.com/us/artist/katelyn-tarver/2356378</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/best-thing/1860673615</v>
+        <v>https://music.apple.com/us/album/so-am-i/1867012005</v>
       </c>
       <c r="L179" t="str">
-        <v>best thing - WRABEL</v>
+        <v>So Am I - Katelyn Tarver</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Count It Back</v>
+        <v>best thing</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/count-it-back/1855219865</v>
+        <v>https://music.apple.com/us/song/best-thing/1860673616</v>
       </c>
       <c r="D180" t="str">
         <v>2026-02-03</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Magic Boy</v>
+        <v>best thing - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>2:52</v>
+        <v>4:27</v>
       </c>
       <c r="H180" t="str">
-        <v>Bartees Strange</v>
+        <v>WRABEL</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/bartees-strange/1450776625</v>
+        <v>https://music.apple.com/us/artist/wrabel/435072161</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/count-it-back/1855219618</v>
+        <v>https://music.apple.com/us/album/best-thing/1860673615</v>
       </c>
       <c r="L180" t="str">
-        <v>Count It Back - Bartees Strange</v>
+        <v>best thing - WRABEL</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Good Girl</v>
+        <v>Count It Back</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/good-girl/1862640697</v>
+        <v>https://music.apple.com/us/song/count-it-back/1855219865</v>
       </c>
       <c r="D181" t="str">
         <v>2026-02-03</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Good Girl - Single</v>
+        <v>Magic Boy</v>
       </c>
       <c r="G181" t="str">
-        <v>4:23</v>
+        <v>2:52</v>
       </c>
       <c r="H181" t="str">
-        <v>Paris Paloma</v>
+        <v>Bartees Strange</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/paris-paloma/1530898376</v>
+        <v>https://music.apple.com/us/artist/bartees-strange/1450776625</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/good-girl/1862640694</v>
+        <v>https://music.apple.com/us/album/count-it-back/1855219618</v>
       </c>
       <c r="L181" t="str">
-        <v>Good Girl - Paris Paloma</v>
+        <v>Count It Back - Bartees Strange</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>MY REVIVAL</v>
+        <v>Good Girl</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/my-revival/1869465104</v>
+        <v>https://music.apple.com/us/song/good-girl/1862640697</v>
       </c>
       <c r="D182" t="str">
         <v>2026-02-03</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>HEARTLAND (Deluxe Version)</v>
+        <v>Good Girl - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>3:34</v>
+        <v>4:23</v>
       </c>
       <c r="H182" t="str">
-        <v>MORGXN</v>
+        <v>Paris Paloma</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/morgxn/1116360149</v>
+        <v>https://music.apple.com/us/artist/paris-paloma/1530898376</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/my-revival/1869464853</v>
+        <v>https://music.apple.com/us/album/good-girl/1862640694</v>
       </c>
       <c r="L182" t="str">
-        <v>MY REVIVAL - MORGXN</v>
+        <v>Good Girl - Paris Paloma</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Run My Way</v>
+        <v>MY REVIVAL</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/run-my-way/1860964996</v>
+        <v>https://music.apple.com/us/song/my-revival/1869465104</v>
       </c>
       <c r="D183" t="str">
         <v>2026-02-03</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Run My Way - Single</v>
+        <v>HEARTLAND (Deluxe Version)</v>
       </c>
       <c r="G183" t="str">
-        <v>2:44</v>
+        <v>3:34</v>
       </c>
       <c r="H183" t="str">
-        <v>December 10</v>
+        <v>MORGXN</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/december-10/1414032285</v>
+        <v>https://music.apple.com/us/artist/morgxn/1116360149</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/run-my-way/1860964992</v>
+        <v>https://music.apple.com/us/album/my-revival/1869464853</v>
       </c>
       <c r="L183" t="str">
-        <v>Run My Way - December 10</v>
+        <v>MY REVIVAL - MORGXN</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Cold Night</v>
+        <v>Run My Way</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/cold-night/1867687787</v>
+        <v>https://music.apple.com/us/song/run-my-way/1860964996</v>
       </c>
       <c r="D184" t="str">
         <v>2026-02-03</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>Cold Night - Single</v>
+        <v>Run My Way - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>3:12</v>
+        <v>2:44</v>
       </c>
       <c r="H184" t="str">
-        <v>HANA</v>
+        <v>December 10</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/hana/1792783458</v>
+        <v>https://music.apple.com/us/artist/december-10/1414032285</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/cold-night/1867687784</v>
+        <v>https://music.apple.com/us/album/run-my-way/1860964992</v>
       </c>
       <c r="L184" t="str">
-        <v>Cold Night - HANA</v>
+        <v>Run My Way - December 10</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Away With The Fairies</v>
+        <v>Cold Night</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/away-with-the-fairies/1870603474</v>
+        <v>https://music.apple.com/us/song/cold-night/1867687787</v>
       </c>
       <c r="D185" t="str">
         <v>2026-02-03</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>Away With The Fairies - Single</v>
+        <v>Cold Night - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>2:28</v>
+        <v>3:12</v>
       </c>
       <c r="H185" t="str">
-        <v>LUNA</v>
+        <v>HANA</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/luna/1439101807</v>
+        <v>https://music.apple.com/us/artist/hana/1792783458</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/away-with-the-fairies/1870603470</v>
+        <v>https://music.apple.com/us/album/cold-night/1867687784</v>
       </c>
       <c r="L185" t="str">
-        <v>Away With The Fairies - LUNA</v>
+        <v>Cold Night - HANA</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Fragile</v>
+        <v>Away With The Fairies</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/fragile/1866957569</v>
+        <v>https://music.apple.com/us/song/away-with-the-fairies/1870603474</v>
       </c>
       <c r="D186" t="str">
         <v>2026-02-03</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Fragile - Single</v>
+        <v>Away With The Fairies - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>3:10</v>
+        <v>2:28</v>
       </c>
       <c r="H186" t="str">
-        <v>Anajah</v>
+        <v>LUNA</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/anajah/1355166756</v>
+        <v>https://music.apple.com/us/artist/luna/1439101807</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/fragile/1866957565</v>
+        <v>https://music.apple.com/us/album/away-with-the-fairies/1870603470</v>
       </c>
       <c r="L186" t="str">
-        <v>Fragile - Anajah</v>
+        <v>Away With The Fairies - LUNA</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Slow Dancin'</v>
+        <v>Fragile</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/slow-dancin/1871537173</v>
+        <v>https://music.apple.com/us/song/fragile/1866957569</v>
       </c>
       <c r="D187" t="str">
         <v>2026-02-03</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Slow Dancin' - Single</v>
+        <v>Fragile - Single</v>
       </c>
       <c r="G187" t="str">
-        <v>2:04</v>
+        <v>3:10</v>
       </c>
       <c r="H187" t="str">
-        <v>STELLA LEFTY</v>
+        <v>Anajah</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/stella-lefty/1641742186</v>
+        <v>https://music.apple.com/us/artist/anajah/1355166756</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/slow-dancin/1871537170</v>
+        <v>https://music.apple.com/us/album/fragile/1866957565</v>
       </c>
       <c r="L187" t="str">
-        <v>Slow Dancin' - STELLA LEFTY</v>
+        <v>Fragile - Anajah</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Never Kissed a Cowboy</v>
+        <v>Slow Dancin'</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/never-kissed-a-cowboy/1866744530</v>
+        <v>https://music.apple.com/us/song/slow-dancin/1871537173</v>
       </c>
       <c r="D188" t="str">
         <v>2026-02-03</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Never Kissed a Cowboy - Single</v>
+        <v>Slow Dancin' - Single</v>
       </c>
       <c r="G188" t="str">
-        <v>3:04</v>
+        <v>2:04</v>
       </c>
       <c r="H188" t="str">
-        <v>Lily Meola</v>
+        <v>STELLA LEFTY</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/lily-meola/678241726</v>
+        <v>https://music.apple.com/us/artist/stella-lefty/1641742186</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/never-kissed-a-cowboy/1866744528</v>
+        <v>https://music.apple.com/us/album/slow-dancin/1871537170</v>
       </c>
       <c r="L188" t="str">
-        <v>Never Kissed a Cowboy - Lily Meola</v>
+        <v>Slow Dancin' - STELLA LEFTY</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>More Of What Matters</v>
+        <v>Never Kissed a Cowboy</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/more-of-what-matters/1871592720</v>
+        <v>https://music.apple.com/us/song/never-kissed-a-cowboy/1866744530</v>
       </c>
       <c r="D189" t="str">
         <v>2026-02-03</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>More Of What Matters - Single</v>
+        <v>Never Kissed a Cowboy - Single</v>
       </c>
       <c r="G189" t="str">
-        <v>3:41</v>
+        <v>3:04</v>
       </c>
       <c r="H189" t="str">
-        <v>Jamey Johnson</v>
+        <v>Lily Meola</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/jamey-johnson/81030634</v>
+        <v>https://music.apple.com/us/artist/lily-meola/678241726</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/more-of-what-matters/1871592717</v>
+        <v>https://music.apple.com/us/album/never-kissed-a-cowboy/1866744528</v>
       </c>
       <c r="L189" t="str">
-        <v>More Of What Matters - Jamey Johnson</v>
+        <v>Never Kissed a Cowboy - Lily Meola</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Is This The Real You</v>
+        <v>More Of What Matters</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/is-this-the-real-you/1869323368</v>
+        <v>https://music.apple.com/us/song/more-of-what-matters/1871592720</v>
       </c>
       <c r="D190" t="str">
         <v>2026-02-03</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>ONE</v>
+        <v>More Of What Matters - Single</v>
       </c>
       <c r="G190" t="str">
-        <v>3:46</v>
+        <v>3:41</v>
       </c>
       <c r="H190" t="str">
-        <v>Sevendust</v>
+        <v>Jamey Johnson</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/sevendust/13125174</v>
+        <v>https://music.apple.com/us/artist/jamey-johnson/81030634</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/is-this-the-real-you/1869323199</v>
+        <v>https://music.apple.com/us/album/more-of-what-matters/1871592717</v>
       </c>
       <c r="L190" t="str">
-        <v>Is This The Real You - Sevendust</v>
+        <v>More Of What Matters - Jamey Johnson</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Hud</v>
+        <v>Is This The Real You</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/hud/1842015019</v>
+        <v>https://music.apple.com/us/song/is-this-the-real-you/1869323368</v>
       </c>
       <c r="D191" t="str">
         <v>2026-02-03</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>DREAMCRUSH</v>
+        <v>ONE</v>
       </c>
       <c r="G191" t="str">
-        <v>4:46</v>
+        <v>3:46</v>
       </c>
       <c r="H191" t="str">
-        <v>MØL</v>
+        <v>Sevendust</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/m%C3%B8l/975294671</v>
+        <v>https://music.apple.com/us/artist/sevendust/13125174</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/hud/1842014730</v>
+        <v>https://music.apple.com/us/album/is-this-the-real-you/1869323199</v>
       </c>
       <c r="L191" t="str">
-        <v>Hud - MØL</v>
+        <v>Is This The Real You - Sevendust</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Ego Death</v>
+        <v>Hud</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/ego-death/1867855427</v>
+        <v>https://music.apple.com/us/song/hud/1842015019</v>
       </c>
       <c r="D192" t="str">
         <v>2026-02-03</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>Ego Death - Single</v>
+        <v>DREAMCRUSH</v>
       </c>
       <c r="G192" t="str">
-        <v>2:12</v>
+        <v>4:46</v>
       </c>
       <c r="H192" t="str">
-        <v>Atreyu</v>
+        <v>MØL</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/atreyu/6095061</v>
+        <v>https://music.apple.com/us/artist/m%C3%B8l/975294671</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/ego-death/1867855173</v>
+        <v>https://music.apple.com/us/album/hud/1842014730</v>
       </c>
       <c r="L192" t="str">
-        <v>Ego Death - Atreyu</v>
+        <v>Hud - MØL</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Gas Station Love (remix)</v>
+        <v>Ego Death</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/gas-station-love-remix/1872150728</v>
+        <v>https://music.apple.com/us/song/ego-death/1867855427</v>
       </c>
       <c r="D193" t="str">
         <v>2026-02-03</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>Gas Station Love (remix) - Single</v>
+        <v>Ego Death - Single</v>
       </c>
       <c r="G193" t="str">
-        <v>4:05</v>
+        <v>2:12</v>
       </c>
       <c r="H193" t="str">
-        <v>EJ Jones</v>
+        <v>Atreyu</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/ej-jones/1781306141</v>
+        <v>https://music.apple.com/us/artist/atreyu/6095061</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/gas-station-love-remix/1872150723</v>
+        <v>https://music.apple.com/us/album/ego-death/1867855173</v>
       </c>
       <c r="L193" t="str">
-        <v>Gas Station Love (remix) - EJ Jones</v>
+        <v>Ego Death - Atreyu</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Disappear</v>
+        <v>Gas Station Love (remix)</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/disappear/1861907311</v>
+        <v>https://music.apple.com/us/song/gas-station-love-remix/1872150728</v>
       </c>
       <c r="D194" t="str">
         <v>2026-02-03</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Disappear</v>
+        <v>Gas Station Love (remix) - Single</v>
       </c>
       <c r="G194" t="str">
-        <v>5:50</v>
+        <v>4:05</v>
       </c>
       <c r="H194" t="str">
-        <v>Lane 8</v>
+        <v>EJ Jones</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/lane-8/634763116</v>
+        <v>https://music.apple.com/us/artist/ej-jones/1781306141</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/disappear/1861907305</v>
+        <v>https://music.apple.com/us/album/gas-station-love-remix/1872150723</v>
       </c>
       <c r="L194" t="str">
-        <v>Disappear - Lane 8</v>
+        <v>Gas Station Love (remix) - EJ Jones</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Misbehave</v>
+        <v>Disappear</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/misbehave/1859630128</v>
+        <v>https://music.apple.com/us/song/disappear/1861907311</v>
       </c>
       <c r="D195" t="str">
         <v>2026-02-03</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Misbehave - Single</v>
+        <v>Disappear</v>
       </c>
       <c r="G195" t="str">
-        <v>3:43</v>
+        <v>5:50</v>
       </c>
       <c r="H195" t="str">
-        <v>Aluna</v>
+        <v>Lane 8</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/aluna/1508017201</v>
+        <v>https://music.apple.com/us/artist/lane-8/634763116</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/misbehave/1859630126</v>
+        <v>https://music.apple.com/us/album/disappear/1861907305</v>
       </c>
       <c r="L195" t="str">
-        <v>Misbehave - Aluna</v>
+        <v>Disappear - Lane 8</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Club Bizarre</v>
+        <v>Misbehave</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/club-bizarre/1870355078</v>
+        <v>https://music.apple.com/us/song/misbehave/1859630128</v>
       </c>
       <c r="D196" t="str">
         <v>2026-02-03</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>Club Bizarre - Single</v>
+        <v>Misbehave - Single</v>
       </c>
       <c r="G196" t="str">
-        <v>2:47</v>
+        <v>3:43</v>
       </c>
       <c r="H196" t="str">
-        <v>Alok</v>
+        <v>Aluna</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/alok/324709167</v>
+        <v>https://music.apple.com/us/artist/aluna/1508017201</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/club-bizarre/1870355077</v>
+        <v>https://music.apple.com/us/album/misbehave/1859630126</v>
       </c>
       <c r="L196" t="str">
-        <v>Club Bizarre - Alok</v>
+        <v>Misbehave - Aluna</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Fly</v>
+        <v>Club Bizarre</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/fly/1867903625</v>
+        <v>https://music.apple.com/us/song/club-bizarre/1870355078</v>
       </c>
       <c r="D197" t="str">
         <v>2026-02-03</v>
@@ -7861,36 +7861,36 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>Fly - Single</v>
+        <v>Club Bizarre - Single</v>
       </c>
       <c r="G197" t="str">
-        <v>3:04</v>
+        <v>2:47</v>
       </c>
       <c r="H197" t="str">
-        <v>Stephen Stanley</v>
+        <v>Alok</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/stephen-stanley/28074609</v>
+        <v>https://music.apple.com/us/artist/alok/324709167</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/fly/1867903548</v>
+        <v>https://music.apple.com/us/album/club-bizarre/1870355077</v>
       </c>
       <c r="L197" t="str">
-        <v>Fly - Stephen Stanley</v>
+        <v>Club Bizarre - Alok</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>ily anyway</v>
+        <v>Fly</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/ily-anyway/1870369432</v>
+        <v>https://music.apple.com/us/song/fly/1867903625</v>
       </c>
       <c r="D198" t="str">
         <v>2026-02-03</v>
@@ -7899,36 +7899,36 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>ily anyway - Single</v>
+        <v>Fly - Single</v>
       </c>
       <c r="G198" t="str">
-        <v>3:05</v>
+        <v>3:04</v>
       </c>
       <c r="H198" t="str">
-        <v>Strings &amp; Heart</v>
+        <v>Stephen Stanley</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/strings-heart/1435173742</v>
+        <v>https://music.apple.com/us/artist/stephen-stanley/28074609</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/ily-anyway/1870369426</v>
+        <v>https://music.apple.com/us/album/fly/1867903548</v>
       </c>
       <c r="L198" t="str">
-        <v>ily anyway - Strings &amp; Heart</v>
+        <v>Fly - Stephen Stanley</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>George Jones (feat. Angela Autumn)</v>
+        <v>ily anyway</v>
       </c>
       <c r="B199" t="str">
         <v/>
       </c>
       <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/george-jones-feat-angela-autumn/1867306007</v>
+        <v>https://music.apple.com/us/song/ily-anyway/1870369432</v>
       </c>
       <c r="D199" t="str">
         <v>2026-02-03</v>
@@ -7937,36 +7937,36 @@
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>Nellene - EP</v>
+        <v>ily anyway - Single</v>
       </c>
       <c r="G199" t="str">
-        <v>3:35</v>
+        <v>3:05</v>
       </c>
       <c r="H199" t="str">
-        <v>Deloyd Elze</v>
+        <v>Strings &amp; Heart</v>
       </c>
       <c r="I199" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/deloyd-elze/1699032462</v>
+        <v>https://music.apple.com/us/artist/strings-heart/1435173742</v>
       </c>
       <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/george-jones-feat-angela-autumn/1867306004</v>
+        <v>https://music.apple.com/us/album/ily-anyway/1870369426</v>
       </c>
       <c r="L199" t="str">
-        <v>George Jones (feat. Angela Autumn) - Deloyd Elze</v>
+        <v>ily anyway - Strings &amp; Heart</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Kiss Big</v>
+        <v>George Jones (feat. Angela Autumn)</v>
       </c>
       <c r="B200" t="str">
         <v/>
       </c>
       <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/kiss-big/1837292261</v>
+        <v>https://music.apple.com/us/song/george-jones-feat-angela-autumn/1867306007</v>
       </c>
       <c r="D200" t="str">
         <v>2026-02-03</v>
@@ -7975,36 +7975,36 @@
         <v/>
       </c>
       <c r="F200" t="str">
-        <v>Kiss Big</v>
+        <v>Nellene - EP</v>
       </c>
       <c r="G200" t="str">
-        <v>3:41</v>
+        <v>3:35</v>
       </c>
       <c r="H200" t="str">
-        <v>Ailbhe Reddy</v>
+        <v>Deloyd Elze</v>
       </c>
       <c r="I200" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J200" t="str">
-        <v>https://music.apple.com/us/artist/ailbhe-reddy/947186338</v>
+        <v>https://music.apple.com/us/artist/deloyd-elze/1699032462</v>
       </c>
       <c r="K200" t="str">
-        <v>https://music.apple.com/us/album/kiss-big/1837292249</v>
+        <v>https://music.apple.com/us/album/george-jones-feat-angela-autumn/1867306004</v>
       </c>
       <c r="L200" t="str">
-        <v>Kiss Big - Ailbhe Reddy</v>
+        <v>George Jones (feat. Angela Autumn) - Deloyd Elze</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>praxis</v>
+        <v>Kiss Big</v>
       </c>
       <c r="B201" t="str">
         <v/>
       </c>
       <c r="C201" t="str">
-        <v>https://music.apple.com/us/song/praxis/1845253734</v>
+        <v>https://music.apple.com/us/song/kiss-big/1837292261</v>
       </c>
       <c r="D201" t="str">
         <v>2026-02-03</v>
@@ -8013,36 +8013,36 @@
         <v/>
       </c>
       <c r="F201" t="str">
-        <v>Whole World As Vigil</v>
+        <v>Kiss Big</v>
       </c>
       <c r="G201" t="str">
-        <v>3:28</v>
+        <v>3:41</v>
       </c>
       <c r="H201" t="str">
-        <v>Lauren Auder</v>
+        <v>Ailbhe Reddy</v>
       </c>
       <c r="I201" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J201" t="str">
-        <v>https://music.apple.com/us/artist/lauren-auder/1096049552</v>
+        <v>https://music.apple.com/us/artist/ailbhe-reddy/947186338</v>
       </c>
       <c r="K201" t="str">
-        <v>https://music.apple.com/us/album/praxis/1845253730</v>
+        <v>https://music.apple.com/us/album/kiss-big/1837292249</v>
       </c>
       <c r="L201" t="str">
-        <v>praxis - Lauren Auder</v>
+        <v>Kiss Big - Ailbhe Reddy</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>House</v>
+        <v>praxis</v>
       </c>
       <c r="B202" t="str">
         <v/>
       </c>
       <c r="C202" t="str">
-        <v>https://music.apple.com/us/song/house/1866696487</v>
+        <v>https://music.apple.com/us/song/praxis/1845253734</v>
       </c>
       <c r="D202" t="str">
         <v>2026-02-03</v>
@@ -8051,36 +8051,36 @@
         <v/>
       </c>
       <c r="F202" t="str">
-        <v>House - Single</v>
+        <v>Whole World As Vigil</v>
       </c>
       <c r="G202" t="str">
-        <v>2:30</v>
+        <v>3:28</v>
       </c>
       <c r="H202" t="str">
-        <v>Connie Converse</v>
+        <v>Lauren Auder</v>
       </c>
       <c r="I202" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J202" t="str">
-        <v>https://music.apple.com/us/artist/connie-converse/308326962</v>
+        <v>https://music.apple.com/us/artist/lauren-auder/1096049552</v>
       </c>
       <c r="K202" t="str">
-        <v>https://music.apple.com/us/album/house/1866696486</v>
+        <v>https://music.apple.com/us/album/praxis/1845253730</v>
       </c>
       <c r="L202" t="str">
-        <v>House - Connie Converse</v>
+        <v>praxis - Lauren Auder</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>Cowboy Without a Clue</v>
+        <v>House</v>
       </c>
       <c r="B203" t="str">
         <v/>
       </c>
       <c r="C203" t="str">
-        <v>https://music.apple.com/us/song/cowboy-without-a-clue/1834024322</v>
+        <v>https://music.apple.com/us/song/house/1866696487</v>
       </c>
       <c r="D203" t="str">
         <v>2026-02-03</v>
@@ -8089,36 +8089,36 @@
         <v/>
       </c>
       <c r="F203" t="str">
-        <v>No Love Lost to Kindness</v>
+        <v>House - Single</v>
       </c>
       <c r="G203" t="str">
-        <v>3:57</v>
+        <v>2:30</v>
       </c>
       <c r="H203" t="str">
-        <v>Yumi Zouma</v>
+        <v>Connie Converse</v>
       </c>
       <c r="I203" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J203" t="str">
-        <v>https://music.apple.com/us/artist/yumi-zouma/795031200</v>
+        <v>https://music.apple.com/us/artist/connie-converse/308326962</v>
       </c>
       <c r="K203" t="str">
-        <v>https://music.apple.com/us/album/cowboy-without-a-clue/1834024311</v>
+        <v>https://music.apple.com/us/album/house/1866696486</v>
       </c>
       <c r="L203" t="str">
-        <v>Cowboy Without a Clue - Yumi Zouma</v>
+        <v>House - Connie Converse</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>Brincar</v>
+        <v>Cowboy Without a Clue</v>
       </c>
       <c r="B204" t="str">
         <v/>
       </c>
       <c r="C204" t="str">
-        <v>https://music.apple.com/us/song/brincar/1871554907</v>
+        <v>https://music.apple.com/us/song/cowboy-without-a-clue/1834024322</v>
       </c>
       <c r="D204" t="str">
         <v>2026-02-03</v>
@@ -8127,68 +8127,106 @@
         <v/>
       </c>
       <c r="F204" t="str">
-        <v>JET LAG - EP</v>
+        <v>No Love Lost to Kindness</v>
       </c>
       <c r="G204" t="str">
-        <v>3:06</v>
+        <v>3:57</v>
       </c>
       <c r="H204" t="str">
-        <v>J Castle</v>
+        <v>Yumi Zouma</v>
       </c>
       <c r="I204" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J204" t="str">
-        <v>https://music.apple.com/us/artist/j-castle/309829058</v>
+        <v>https://music.apple.com/us/artist/yumi-zouma/795031200</v>
       </c>
       <c r="K204" t="str">
-        <v>https://music.apple.com/us/album/brincar/1871554901</v>
+        <v>https://music.apple.com/us/album/cowboy-without-a-clue/1834024311</v>
       </c>
       <c r="L204" t="str">
-        <v>Brincar - J Castle</v>
+        <v>Cowboy Without a Clue - Yumi Zouma</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
+        <v>Brincar</v>
+      </c>
+      <c r="B205" t="str">
+        <v/>
+      </c>
+      <c r="C205" t="str">
+        <v>https://music.apple.com/us/song/brincar/1871554907</v>
+      </c>
+      <c r="D205" t="str">
+        <v>2026-02-03</v>
+      </c>
+      <c r="E205" t="str">
+        <v/>
+      </c>
+      <c r="F205" t="str">
+        <v>JET LAG - EP</v>
+      </c>
+      <c r="G205" t="str">
+        <v>3:06</v>
+      </c>
+      <c r="H205" t="str">
+        <v>J Castle</v>
+      </c>
+      <c r="I205" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J205" t="str">
+        <v>https://music.apple.com/us/artist/j-castle/309829058</v>
+      </c>
+      <c r="K205" t="str">
+        <v>https://music.apple.com/us/album/brincar/1871554901</v>
+      </c>
+      <c r="L205" t="str">
+        <v>Brincar - J Castle</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="str">
         <v>Quién</v>
       </c>
-      <c r="B205" t="str">
-        <v/>
-      </c>
-      <c r="C205" t="str">
+      <c r="B206" t="str">
+        <v/>
+      </c>
+      <c r="C206" t="str">
         <v>https://music.apple.com/us/song/qui%C3%A9n/1870329662</v>
       </c>
-      <c r="D205" t="str">
-        <v>2026-02-03</v>
-      </c>
-      <c r="E205" t="str">
-        <v/>
-      </c>
-      <c r="F205" t="str">
+      <c r="D206" t="str">
+        <v>2026-02-03</v>
+      </c>
+      <c r="E206" t="str">
+        <v/>
+      </c>
+      <c r="F206" t="str">
         <v>Quién - Single</v>
       </c>
-      <c r="G205" t="str">
+      <c r="G206" t="str">
         <v>4:19</v>
       </c>
-      <c r="H205" t="str">
+      <c r="H206" t="str">
         <v>Daniela Darcourt</v>
       </c>
-      <c r="I205" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J205" t="str">
+      <c r="I206" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J206" t="str">
         <v>https://music.apple.com/us/artist/daniela-darcourt/1396749684</v>
       </c>
-      <c r="K205" t="str">
+      <c r="K206" t="str">
         <v>https://music.apple.com/us/album/qui%C3%A9n/1870329660</v>
       </c>
-      <c r="L205" t="str">
+      <c r="L206" t="str">
         <v>Quién - Daniela Darcourt</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L205"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L206"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
@@ -439,7 +439,7 @@
         <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Studio)</v>
       </c>
       <c r="B2" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=mgsdQI-GVMM</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:19</v>
@@ -477,7 +477,7 @@
         <v>Vera Blue - Hold (Live on Sydney Harbour)</v>
       </c>
       <c r="B3" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=SYEwk-EZJPU</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>3:37</v>
@@ -515,7 +515,7 @@
         <v>Bob Moses - Need You Tonight (INXS Cover) - Brooklyn Mirage 2023</v>
       </c>
       <c r="B4" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=CoCqPwDIBOA</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G4" t="str">
         <v>3:08</v>
@@ -553,7 +553,7 @@
         <v>Marc Anthony - Un Mal Sueño (Visualizer)</v>
       </c>
       <c r="B5" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=18yZq5xtke4</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G5" t="str">
         <v>3:28</v>
@@ -591,7 +591,7 @@
         <v>Marc Anthony - Contra La Corriente (Visualizer)</v>
       </c>
       <c r="B6" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=IGLmJ71oHhQ</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G6" t="str">
         <v>5:05</v>
@@ -2453,7 +2453,7 @@
         <v>SIENNA SPIRO - Die On This Hill (Official Music Video)</v>
       </c>
       <c r="B55" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C55" t="str">
         <v>https://www.youtube.com/watch?v=5RNy_1odv20</v>
@@ -2465,7 +2465,7 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G55" t="str">
         <v>4:01</v>
@@ -3403,7 +3403,7 @@
         <v>Dermot Kennedy - Funeral (Official Music Video)</v>
       </c>
       <c r="B80" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C80" t="str">
         <v>https://www.youtube.com/watch?v=JzOUJZPky6o</v>
@@ -3415,7 +3415,7 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G80" t="str">
         <v>4:09</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
@@ -439,7 +439,7 @@
         <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Studio)</v>
       </c>
       <c r="B2" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=mgsdQI-GVMM</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:19</v>
@@ -477,7 +477,7 @@
         <v>Vera Blue - Hold (Live on Sydney Harbour)</v>
       </c>
       <c r="B3" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=SYEwk-EZJPU</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>3:37</v>
@@ -3362,7 +3362,7 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>DEF LEPPARD - Rejoice (Official Lyric Video)</v>
+        <v>Def Leppard - Rejoice (Lyric Video)</v>
       </c>
       <c r="B79" t="str">
         <v>12 days ago</v>
@@ -3395,7 +3395,7 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>DEF LEPPARD - Rejoice (Official Lyric Video) - DEF LEPPARD</v>
+        <v>Def Leppard - Rejoice (Lyric Video) - DEF LEPPARD</v>
       </c>
     </row>
     <row r="80">

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
@@ -439,7 +439,7 @@
         <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Studio)</v>
       </c>
       <c r="B2" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=mgsdQI-GVMM</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:19</v>
@@ -477,7 +477,7 @@
         <v>Vera Blue - Hold (Live on Sydney Harbour)</v>
       </c>
       <c r="B3" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=SYEwk-EZJPU</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G3" t="str">
         <v>3:37</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
@@ -439,7 +439,7 @@
         <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Studio)</v>
       </c>
       <c r="B2" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=mgsdQI-GVMM</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:19</v>
@@ -1883,7 +1883,7 @@
         <v>TINI - FUTTTURA LIVE - el cielo + fresa</v>
       </c>
       <c r="B40" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=q_rrgJZAdNg</v>
@@ -1895,7 +1895,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G40" t="str">
         <v>5:58</v>
@@ -1921,7 +1921,7 @@
         <v>Charley - Serial Idealist (Official Video)</v>
       </c>
       <c r="B41" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=uVIuKbPJz0U</v>
@@ -1933,7 +1933,7 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G41" t="str">
         <v>3:26</v>
@@ -2377,7 +2377,7 @@
         <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop)</v>
       </c>
       <c r="B53" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C53" t="str">
         <v>https://www.youtube.com/watch?v=57a_OheOlDw</v>
@@ -2389,7 +2389,7 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G53" t="str">
         <v>3:20</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
@@ -1807,7 +1807,7 @@
         <v>India Martinez, Coro ArteSí de Olvidados - Niño Sin Miedo</v>
       </c>
       <c r="B38" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=Vug_FPbXe9E</v>
@@ -1819,7 +1819,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G38" t="str">
         <v>4:04</v>
@@ -1845,7 +1845,7 @@
         <v>Chelsea Cutler - BAD (Official Lyric Video)</v>
       </c>
       <c r="B39" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=ZIW2vA3Zs1U</v>
@@ -1857,7 +1857,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G39" t="str">
         <v>2:16</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
@@ -436,28 +436,28 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Studio)</v>
+        <v>Marc Anthony - Make It With You (Visualizer)</v>
       </c>
       <c r="B2" t="str">
-        <v>1 day ago</v>
+        <v>1 hour ago</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=mgsdQI-GVMM</v>
+        <v>https://www.youtube.com/watch?v=WHnz1jDrxw8</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>1 day ago</v>
+        <v>1 hour ago</v>
       </c>
       <c r="G2" t="str">
-        <v>3:19</v>
+        <v>4:24</v>
       </c>
       <c r="H2" t="str">
-        <v>David Guetta and Tones And I</v>
+        <v>Marc Anthony</v>
       </c>
       <c r="I2" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -469,33 +469,33 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Studio) - David Guetta and Tones And I</v>
+        <v>Marc Anthony - Make It With You (Visualizer) - Marc Anthony</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Vera Blue - Hold (Live on Sydney Harbour)</v>
+        <v>Clara Mae - Never Been Yours ft. Bob John Holt</v>
       </c>
       <c r="B3" t="str">
-        <v>1 day ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=SYEwk-EZJPU</v>
+        <v>https://www.youtube.com/watch?v=HtVuKBlBuPg</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E3" t="str">
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>1 day ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="G3" t="str">
-        <v>3:37</v>
+        <v>2:33</v>
       </c>
       <c r="H3" t="str">
-        <v>Vera Blue</v>
+        <v>Clara Mae</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,33 +507,33 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Vera Blue - Hold (Live on Sydney Harbour) - Vera Blue</v>
+        <v>Clara Mae - Never Been Yours ft. Bob John Holt - Clara Mae</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Bob Moses - Need You Tonight (INXS Cover) - Brooklyn Mirage 2023</v>
+        <v>Metric - Victim of Luck (Official Music Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>1 day ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=CoCqPwDIBOA</v>
+        <v>https://www.youtube.com/watch?v=shmhTOUd8mA</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E4" t="str">
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>1 day ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="G4" t="str">
-        <v>3:08</v>
+        <v>3:25</v>
       </c>
       <c r="H4" t="str">
-        <v>Bob Moses</v>
+        <v>metricmusic</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,33 +545,33 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Bob Moses - Need You Tonight (INXS Cover) - Brooklyn Mirage 2023 - Bob Moses</v>
+        <v>Metric - Victim of Luck (Official Music Video) - metricmusic</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Marc Anthony - Un Mal Sueño (Visualizer)</v>
+        <v>Kesha - RED FLAG. (Red Carpet) OFFICIAL MUSIC VIDEO</v>
       </c>
       <c r="B5" t="str">
-        <v>1 day ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=18yZq5xtke4</v>
+        <v>https://www.youtube.com/watch?v=pvrJ5RnPAEA</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E5" t="str">
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>1 day ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G5" t="str">
-        <v>3:28</v>
+        <v>3:41</v>
       </c>
       <c r="H5" t="str">
-        <v>Marc Anthony</v>
+        <v>kesha</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,21 +583,21 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Marc Anthony - Un Mal Sueño (Visualizer) - Marc Anthony</v>
+        <v>Kesha - RED FLAG. (Red Carpet) OFFICIAL MUSIC VIDEO - kesha</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Marc Anthony - Contra La Corriente (Visualizer)</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Studio)</v>
       </c>
       <c r="B6" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=IGLmJ71oHhQ</v>
+        <v>https://www.youtube.com/watch?v=mgsdQI-GVMM</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -606,10 +606,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G6" t="str">
-        <v>5:05</v>
+        <v>3:19</v>
       </c>
       <c r="H6" t="str">
-        <v>Marc Anthony</v>
+        <v>David Guetta and Tones And I</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,21 +621,21 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Marc Anthony - Contra La Corriente (Visualizer) - Marc Anthony</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Studio) - David Guetta and Tones And I</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Loreen - Feels Like Heaven</v>
+        <v>Vera Blue - Hold (Live on Sydney Harbour)</v>
       </c>
       <c r="B7" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=BQc97moyQBg</v>
+        <v>https://www.youtube.com/watch?v=SYEwk-EZJPU</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -644,10 +644,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G7" t="str">
-        <v>3:14</v>
+        <v>3:37</v>
       </c>
       <c r="H7" t="str">
-        <v>Loreen</v>
+        <v>Vera Blue</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,21 +659,21 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Loreen - Feels Like Heaven - Loreen</v>
+        <v>Vera Blue - Hold (Live on Sydney Harbour) - Vera Blue</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Take That - Once You've Tasted Love (Live on Pebble Mill, 1992)</v>
+        <v>Bob Moses - Need You Tonight (INXS Cover) - Brooklyn Mirage 2023</v>
       </c>
       <c r="B8" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=dOeoDOueESk</v>
+        <v>https://www.youtube.com/watch?v=CoCqPwDIBOA</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -682,10 +682,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G8" t="str">
-        <v>3:36</v>
+        <v>3:08</v>
       </c>
       <c r="H8" t="str">
-        <v>Take That</v>
+        <v>Bob Moses</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,21 +697,21 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Take That - Once You've Tasted Love (Live on Pebble Mill, 1992) - Take That</v>
+        <v>Bob Moses - Need You Tonight (INXS Cover) - Brooklyn Mirage 2023 - Bob Moses</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Paul McCartney, Wings - Nineteen Hundred And Eighty Five (Visualiser)</v>
+        <v>Marc Anthony - Un Mal Sueño (Visualizer)</v>
       </c>
       <c r="B9" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=a4AIjUHuWpU</v>
+        <v>https://www.youtube.com/watch?v=18yZq5xtke4</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -720,10 +720,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G9" t="str">
-        <v>5:31</v>
+        <v>3:28</v>
       </c>
       <c r="H9" t="str">
-        <v>PAUL McCARTNEY</v>
+        <v>Marc Anthony</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,21 +735,21 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Paul McCartney, Wings - Nineteen Hundred And Eighty Five (Visualiser) - PAUL McCARTNEY</v>
+        <v>Marc Anthony - Un Mal Sueño (Visualizer) - Marc Anthony</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Nothing But Thieves - Sorry (Official Audio)</v>
+        <v>Marc Anthony - Contra La Corriente (Visualizer)</v>
       </c>
       <c r="B10" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=D7QfVqo5YqY</v>
+        <v>https://www.youtube.com/watch?v=IGLmJ71oHhQ</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -758,10 +758,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G10" t="str">
-        <v>3:37</v>
+        <v>5:05</v>
       </c>
       <c r="H10" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Marc Anthony</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,33 +773,33 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Nothing But Thieves - Sorry (Official Audio) - Nothing But Thieves</v>
+        <v>Marc Anthony - Contra La Corriente (Visualizer) - Marc Anthony</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music</v>
+        <v>Loreen - Feels Like Heaven</v>
       </c>
       <c r="B11" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=KdsHxyl4bE8</v>
+        <v>https://www.youtube.com/watch?v=BQc97moyQBg</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E11" t="str">
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G11" t="str">
-        <v>4:58</v>
+        <v>3:14</v>
       </c>
       <c r="H11" t="str">
-        <v>The Warning</v>
+        <v>Loreen</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,33 +811,33 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music - The Warning</v>
+        <v>Loreen - Feels Like Heaven - Loreen</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield, CA (2026)</v>
+        <v>Take That - Once You've Tasted Love (Live on Pebble Mill, 1992)</v>
       </c>
       <c r="B12" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=Mwkl_Cz_SG8</v>
+        <v>https://www.youtube.com/watch?v=dOeoDOueESk</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E12" t="str">
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G12" t="str">
-        <v>5:08</v>
+        <v>3:36</v>
       </c>
       <c r="H12" t="str">
-        <v>The Offspring</v>
+        <v>Take That</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,33 +849,33 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield, CA (2026) - The Offspring</v>
+        <v>Take That - Once You've Tasted Love (Live on Pebble Mill, 1992) - Take That</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered)</v>
+        <v>Paul McCartney, Wings - Nineteen Hundred And Eighty Five (Visualiser)</v>
       </c>
       <c r="B13" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=I7a-pDZFE7U</v>
+        <v>https://www.youtube.com/watch?v=a4AIjUHuWpU</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E13" t="str">
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G13" t="str">
-        <v>4:38</v>
+        <v>5:31</v>
       </c>
       <c r="H13" t="str">
-        <v>Roxette</v>
+        <v>PAUL McCARTNEY</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,33 +887,33 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered) - Roxette</v>
+        <v>Paul McCartney, Wings - Nineteen Hundred And Eighty Five (Visualiser) - PAUL McCARTNEY</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Live on The Graham Norton Show)</v>
+        <v>Nothing But Thieves - Sorry (Official Audio)</v>
       </c>
       <c r="B14" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=kGeamxRf8Gw</v>
+        <v>https://www.youtube.com/watch?v=D7QfVqo5YqY</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E14" t="str">
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G14" t="str">
-        <v>3:50</v>
+        <v>3:37</v>
       </c>
       <c r="H14" t="str">
-        <v>Jessie Ware</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,33 +925,33 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Live on The Graham Norton Show) - Jessie Ware</v>
+        <v>Nothing But Thieves - Sorry (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>JOSEPH - Water in the Room (Official Music Video)</v>
+        <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music</v>
       </c>
       <c r="B15" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=tNmT47k6MjM</v>
+        <v>https://www.youtube.com/watch?v=KdsHxyl4bE8</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E15" t="str">
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G15" t="str">
-        <v>3:10</v>
+        <v>4:58</v>
       </c>
       <c r="H15" t="str">
-        <v>Joseph</v>
+        <v>The Warning</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,33 +963,33 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>JOSEPH - Water in the Room (Official Music Video) - Joseph</v>
+        <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music - The Warning</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Dean Lewis - I Am Getting Well (Lyric Video)</v>
+        <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield, CA (2026)</v>
       </c>
       <c r="B16" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=6ecgOSOMWzc</v>
+        <v>https://www.youtube.com/watch?v=Mwkl_Cz_SG8</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E16" t="str">
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G16" t="str">
-        <v>2:44</v>
+        <v>5:08</v>
       </c>
       <c r="H16" t="str">
-        <v>Dean Lewis</v>
+        <v>The Offspring</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,33 +1001,33 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Dean Lewis - I Am Getting Well (Lyric Video) - Dean Lewis</v>
+        <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield, CA (2026) - The Offspring</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Take That - Take That and Party (Official HD Video)</v>
+        <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered)</v>
       </c>
       <c r="B17" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=DAerJcerikU</v>
+        <v>https://www.youtube.com/watch?v=I7a-pDZFE7U</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E17" t="str">
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>2:57</v>
+        <v>4:38</v>
       </c>
       <c r="H17" t="str">
-        <v>Take That</v>
+        <v>Roxette</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,33 +1039,33 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Take That - Take That and Party (Official HD Video) - Take That</v>
+        <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered) - Roxette</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>The Cure - Boys Don't Cry (86 Mix) (Official Lyric Video)</v>
+        <v>Jessie Ware - I Could Get Used To This (Live on The Graham Norton Show)</v>
       </c>
       <c r="B18" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=isNztTjXQsQ</v>
+        <v>https://www.youtube.com/watch?v=kGeamxRf8Gw</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E18" t="str">
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>2:39</v>
+        <v>3:50</v>
       </c>
       <c r="H18" t="str">
-        <v>The Cure</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,21 +1077,21 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>The Cure - Boys Don't Cry (86 Mix) (Official Lyric Video) - The Cure</v>
+        <v>Jessie Ware - I Could Get Used To This (Live on The Graham Norton Show) - Jessie Ware</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>The Kiffness &amp; Matisyahu - ONE DAY (ft. Andel and Nalyn) [OFFICIAL VIDEO]</v>
+        <v>JOSEPH - Water in the Room (Official Music Video)</v>
       </c>
       <c r="B19" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=buS21tVq5r0</v>
+        <v>https://www.youtube.com/watch?v=tNmT47k6MjM</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1100,10 +1100,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>3:07</v>
+        <v>3:10</v>
       </c>
       <c r="H19" t="str">
-        <v>The Kiffness and Matisyahu</v>
+        <v>Joseph</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,21 +1115,21 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>The Kiffness &amp; Matisyahu - ONE DAY (ft. Andel and Nalyn) [OFFICIAL VIDEO] - The Kiffness and Matisyahu</v>
+        <v>JOSEPH - Water in the Room (Official Music Video) - Joseph</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Paris Paloma - Good Girl [Official Music Video]</v>
+        <v>Dean Lewis - I Am Getting Well (Lyric Video)</v>
       </c>
       <c r="B20" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=qhO6VMC-nx0</v>
+        <v>https://www.youtube.com/watch?v=6ecgOSOMWzc</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1138,10 +1138,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>4:47</v>
+        <v>2:44</v>
       </c>
       <c r="H20" t="str">
-        <v>Paris Paloma</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,21 +1153,21 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Paris Paloma - Good Girl [Official Music Video] - Paris Paloma</v>
+        <v>Dean Lewis - I Am Getting Well (Lyric Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Zara Larsson - Lush Life (Official UGC Compilation Video)</v>
+        <v>Take That - Take That and Party (Official HD Video)</v>
       </c>
       <c r="B21" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=FgAyfRnbbRs</v>
+        <v>https://www.youtube.com/watch?v=DAerJcerikU</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1176,10 +1176,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>3:22</v>
+        <v>2:57</v>
       </c>
       <c r="H21" t="str">
-        <v>Zara Larsson</v>
+        <v>Take That</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,21 +1191,21 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Zara Larsson - Lush Life (Official UGC Compilation Video) - Zara Larsson</v>
+        <v>Take That - Take That and Party (Official HD Video) - Take That</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Only The Poets - Monumental</v>
+        <v>The Cure - Boys Don't Cry (86 Mix) (Official Lyric Video)</v>
       </c>
       <c r="B22" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=nwXiAjjl6NE</v>
+        <v>https://www.youtube.com/watch?v=isNztTjXQsQ</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1214,10 +1214,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>2:48</v>
+        <v>2:39</v>
       </c>
       <c r="H22" t="str">
-        <v>only the poets</v>
+        <v>The Cure</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,21 +1229,21 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Only The Poets - Monumental - only the poets</v>
+        <v>The Cure - Boys Don't Cry (86 Mix) (Official Lyric Video) - The Cure</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Katelyn Tarver - So Am I (Official Music Video)</v>
+        <v>The Kiffness &amp; Matisyahu - ONE DAY (ft. Andel and Nalyn) [OFFICIAL VIDEO]</v>
       </c>
       <c r="B23" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=MjUiVPzMQHw</v>
+        <v>https://www.youtube.com/watch?v=buS21tVq5r0</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1252,10 +1252,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>2:52</v>
+        <v>3:07</v>
       </c>
       <c r="H23" t="str">
-        <v>Katelyn Tarver</v>
+        <v>The Kiffness and Matisyahu</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,21 +1267,21 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Katelyn Tarver - So Am I (Official Music Video) - Katelyn Tarver</v>
+        <v>The Kiffness &amp; Matisyahu - ONE DAY (ft. Andel and Nalyn) [OFFICIAL VIDEO] - The Kiffness and Matisyahu</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>David Guetta, TeddySwims, Tones And I - Gone Gone Gone (Unplugged) [Visualizer]</v>
+        <v>Paris Paloma - Good Girl [Official Music Video]</v>
       </c>
       <c r="B24" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=eWglDE7O5r8</v>
+        <v>https://www.youtube.com/watch?v=qhO6VMC-nx0</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1290,10 +1290,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>3:33</v>
+        <v>4:47</v>
       </c>
       <c r="H24" t="str">
-        <v>David Guetta</v>
+        <v>Paris Paloma</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,21 +1305,21 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>David Guetta, TeddySwims, Tones And I - Gone Gone Gone (Unplugged) [Visualizer] - David Guetta</v>
+        <v>Paris Paloma - Good Girl [Official Music Video] - Paris Paloma</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>SANTOS BRAVOS “KAWASAKI” Performance Video</v>
+        <v>Zara Larsson - Lush Life (Official UGC Compilation Video)</v>
       </c>
       <c r="B25" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=Cmy8CsYIUL0</v>
+        <v>https://www.youtube.com/watch?v=FgAyfRnbbRs</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1328,10 +1328,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>2:41</v>
+        <v>3:22</v>
       </c>
       <c r="H25" t="str">
-        <v>HYBE LABELS and SANTOS BRAVOS</v>
+        <v>Zara Larsson</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,21 +1343,21 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>SANTOS BRAVOS “KAWASAKI” Performance Video - HYBE LABELS and SANTOS BRAVOS</v>
+        <v>Zara Larsson - Lush Life (Official UGC Compilation Video) - Zara Larsson</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Ella Langley - Dandelion (Official Visualizer)</v>
+        <v>Only The Poets - Monumental</v>
       </c>
       <c r="B26" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=sf6eRmInk1s</v>
+        <v>https://www.youtube.com/watch?v=nwXiAjjl6NE</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1366,10 +1366,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>4:01</v>
+        <v>2:48</v>
       </c>
       <c r="H26" t="str">
-        <v>Ella Langley</v>
+        <v>only the poets</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,21 +1381,21 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Ella Langley - Dandelion (Official Visualizer) - Ella Langley</v>
+        <v>Only The Poets - Monumental - only the poets</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Dogpark - Dandelion (Official Music Video)</v>
+        <v>Katelyn Tarver - So Am I (Official Music Video)</v>
       </c>
       <c r="B27" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=fv9prIYHHzk</v>
+        <v>https://www.youtube.com/watch?v=MjUiVPzMQHw</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1404,10 +1404,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>3:16</v>
+        <v>2:52</v>
       </c>
       <c r="H27" t="str">
-        <v>Dogpark</v>
+        <v>Katelyn Tarver</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,21 +1419,21 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Dogpark - Dandelion (Official Music Video) - Dogpark</v>
+        <v>Katelyn Tarver - So Am I (Official Music Video) - Katelyn Tarver</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Lauren Spencer Smith - Natural Disaster (Visualizer)</v>
+        <v>David Guetta, TeddySwims, Tones And I - Gone Gone Gone (Unplugged) [Visualizer]</v>
       </c>
       <c r="B28" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=T9YvLA2cdZs</v>
+        <v>https://www.youtube.com/watch?v=eWglDE7O5r8</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1442,10 +1442,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>3:03</v>
+        <v>3:33</v>
       </c>
       <c r="H28" t="str">
-        <v>Lauren Spencer Smith</v>
+        <v>David Guetta</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,21 +1457,21 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Lauren Spencer Smith - Natural Disaster (Visualizer) - Lauren Spencer Smith</v>
+        <v>David Guetta, TeddySwims, Tones And I - Gone Gone Gone (Unplugged) [Visualizer] - David Guetta</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>ERNEST - Lorelei (Official Music Video)</v>
+        <v>SANTOS BRAVOS “KAWASAKI” Performance Video</v>
       </c>
       <c r="B29" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=dPWc_6IdDJk</v>
+        <v>https://www.youtube.com/watch?v=Cmy8CsYIUL0</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1483,7 +1483,7 @@
         <v>2:41</v>
       </c>
       <c r="H29" t="str">
-        <v>ERNEST</v>
+        <v>HYBE LABELS and SANTOS BRAVOS</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,21 +1495,21 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>ERNEST - Lorelei (Official Music Video) - ERNEST</v>
+        <v>SANTOS BRAVOS “KAWASAKI” Performance Video - HYBE LABELS and SANTOS BRAVOS</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Labrinth - I Keep My Promises (Official Audio)</v>
+        <v>Ella Langley - Dandelion (Official Visualizer)</v>
       </c>
       <c r="B30" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=CV5rR9JZK-0</v>
+        <v>https://www.youtube.com/watch?v=sf6eRmInk1s</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1518,10 +1518,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>3:05</v>
+        <v>4:01</v>
       </c>
       <c r="H30" t="str">
-        <v>Labrinth</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,21 +1533,21 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Labrinth - I Keep My Promises (Official Audio) - Labrinth</v>
+        <v>Ella Langley - Dandelion (Official Visualizer) - Ella Langley</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Grace VanderWaal - Prettier (Official Lyric Video)</v>
+        <v>Dogpark - Dandelion (Official Music Video)</v>
       </c>
       <c r="B31" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=9HwTj3NZ16E</v>
+        <v>https://www.youtube.com/watch?v=fv9prIYHHzk</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1556,10 +1556,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>2:46</v>
+        <v>3:16</v>
       </c>
       <c r="H31" t="str">
-        <v>Grace VanderWaal</v>
+        <v>Dogpark</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,21 +1571,21 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Grace VanderWaal - Prettier (Official Lyric Video) - Grace VanderWaal</v>
+        <v>Dogpark - Dandelion (Official Music Video) - Dogpark</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>VOILÀ - Frozen Lake (Official Lyric Video)</v>
+        <v>Lauren Spencer Smith - Natural Disaster (Visualizer)</v>
       </c>
       <c r="B32" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=Lmus-UbL1H0</v>
+        <v>https://www.youtube.com/watch?v=T9YvLA2cdZs</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1594,10 +1594,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>3:32</v>
+        <v>3:03</v>
       </c>
       <c r="H32" t="str">
-        <v>VOILÀ</v>
+        <v>Lauren Spencer Smith</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,21 +1609,21 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>VOILÀ - Frozen Lake (Official Lyric Video) - VOILÀ</v>
+        <v>Lauren Spencer Smith - Natural Disaster (Visualizer) - Lauren Spencer Smith</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Cannons - Starlight (Official Video)</v>
+        <v>ERNEST - Lorelei (Official Music Video)</v>
       </c>
       <c r="B33" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=bu6WSMDDPGY</v>
+        <v>https://www.youtube.com/watch?v=dPWc_6IdDJk</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1632,10 +1632,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>3:42</v>
+        <v>2:41</v>
       </c>
       <c r="H33" t="str">
-        <v>Cannons</v>
+        <v>ERNEST</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,21 +1647,21 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Cannons - Starlight (Official Video) - Cannons</v>
+        <v>ERNEST - Lorelei (Official Music Video) - ERNEST</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Kylie Morgan - Like My Own (Official Video)</v>
+        <v>Labrinth - I Keep My Promises (Official Audio)</v>
       </c>
       <c r="B34" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=zcYeoGBglC0</v>
+        <v>https://www.youtube.com/watch?v=CV5rR9JZK-0</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1670,10 +1670,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>2:38</v>
+        <v>3:05</v>
       </c>
       <c r="H34" t="str">
-        <v>Kylie Morgan</v>
+        <v>Labrinth</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,21 +1685,21 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Kylie Morgan - Like My Own (Official Video) - Kylie Morgan</v>
+        <v>Labrinth - I Keep My Promises (Official Audio) - Labrinth</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Lizzy McAlpine - House of the Rising Sun (Audio)</v>
+        <v>Grace VanderWaal - Prettier (Official Lyric Video)</v>
       </c>
       <c r="B35" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=3igYRj82EiU</v>
+        <v>https://www.youtube.com/watch?v=9HwTj3NZ16E</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1708,10 +1708,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>3:10</v>
+        <v>2:46</v>
       </c>
       <c r="H35" t="str">
-        <v>Lizzy McAlpine</v>
+        <v>Grace VanderWaal</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,21 +1723,21 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Lizzy McAlpine - House of the Rising Sun (Audio) - Lizzy McAlpine</v>
+        <v>Grace VanderWaal - Prettier (Official Lyric Video) - Grace VanderWaal</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Willie Nelson - Heart Of America (From The Gray House Original Soundtrack)</v>
+        <v>VOILÀ - Frozen Lake (Official Lyric Video)</v>
       </c>
       <c r="B36" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=0bhcO4Yphuo</v>
+        <v>https://www.youtube.com/watch?v=Lmus-UbL1H0</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1746,10 +1746,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>3:57</v>
+        <v>3:32</v>
       </c>
       <c r="H36" t="str">
-        <v>Willie Nelson</v>
+        <v>VOILÀ</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,21 +1761,21 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Willie Nelson - Heart Of America (From The Gray House Original Soundtrack) - Willie Nelson</v>
+        <v>VOILÀ - Frozen Lake (Official Lyric Video) - VOILÀ</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Jeremy Camp - No Survivors (Live) ft. Skillet</v>
+        <v>Cannons - Starlight (Official Video)</v>
       </c>
       <c r="B37" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=Jjz1wFe5dMo</v>
+        <v>https://www.youtube.com/watch?v=bu6WSMDDPGY</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1784,10 +1784,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>2:19</v>
+        <v>3:42</v>
       </c>
       <c r="H37" t="str">
-        <v>JeremyCampMusic</v>
+        <v>Cannons</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,33 +1799,33 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Jeremy Camp - No Survivors (Live) ft. Skillet - JeremyCampMusic</v>
+        <v>Cannons - Starlight (Official Video) - Cannons</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>India Martinez, Coro ArteSí de Olvidados - Niño Sin Miedo</v>
+        <v>Kylie Morgan - Like My Own (Official Video)</v>
       </c>
       <c r="B38" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=Vug_FPbXe9E</v>
+        <v>https://www.youtube.com/watch?v=zcYeoGBglC0</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E38" t="str">
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>4:04</v>
+        <v>2:38</v>
       </c>
       <c r="H38" t="str">
-        <v>India Martínez</v>
+        <v>Kylie Morgan</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,33 +1837,33 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>India Martinez, Coro ArteSí de Olvidados - Niño Sin Miedo - India Martínez</v>
+        <v>Kylie Morgan - Like My Own (Official Video) - Kylie Morgan</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Chelsea Cutler - BAD (Official Lyric Video)</v>
+        <v>Lizzy McAlpine - House of the Rising Sun (Audio)</v>
       </c>
       <c r="B39" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=ZIW2vA3Zs1U</v>
+        <v>https://www.youtube.com/watch?v=3igYRj82EiU</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E39" t="str">
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>2:16</v>
+        <v>3:10</v>
       </c>
       <c r="H39" t="str">
-        <v>Chelsea Cutler</v>
+        <v>Lizzy McAlpine</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,33 +1875,33 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Chelsea Cutler - BAD (Official Lyric Video) - Chelsea Cutler</v>
+        <v>Lizzy McAlpine - House of the Rising Sun (Audio) - Lizzy McAlpine</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>TINI - FUTTTURA LIVE - el cielo + fresa</v>
+        <v>Willie Nelson - Heart Of America (From The Gray House Original Soundtrack)</v>
       </c>
       <c r="B40" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=q_rrgJZAdNg</v>
+        <v>https://www.youtube.com/watch?v=0bhcO4Yphuo</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E40" t="str">
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>5:58</v>
+        <v>3:57</v>
       </c>
       <c r="H40" t="str">
-        <v>TINI</v>
+        <v>Willie Nelson</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,33 +1913,33 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>TINI - FUTTTURA LIVE - el cielo + fresa - TINI</v>
+        <v>Willie Nelson - Heart Of America (From The Gray House Original Soundtrack) - Willie Nelson</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Charley - Serial Idealist (Official Video)</v>
+        <v>Jeremy Camp - No Survivors (Live) ft. Skillet</v>
       </c>
       <c r="B41" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=uVIuKbPJz0U</v>
+        <v>https://www.youtube.com/watch?v=Jjz1wFe5dMo</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E41" t="str">
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>3:26</v>
+        <v>2:19</v>
       </c>
       <c r="H41" t="str">
-        <v>Charley</v>
+        <v>JeremyCampMusic</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,21 +1951,21 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Charley - Serial Idealist (Official Video) - Charley</v>
+        <v>Jeremy Camp - No Survivors (Live) ft. Skillet - JeremyCampMusic</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Demi Lovato - Ghost (Live)</v>
+        <v>India Martinez, Coro ArteSí de Olvidados - Niño Sin Miedo</v>
       </c>
       <c r="B42" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=E-ECwdRndVA</v>
+        <v>https://www.youtube.com/watch?v=Vug_FPbXe9E</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -1974,10 +1974,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>4:05</v>
+        <v>4:04</v>
       </c>
       <c r="H42" t="str">
-        <v>Demi Lovato</v>
+        <v>India Martínez</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,21 +1989,21 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Demi Lovato - Ghost (Live) - Demi Lovato</v>
+        <v>India Martinez, Coro ArteSí de Olvidados - Niño Sin Miedo - India Martínez</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Teddy Swims - Need You More (Live - Green Room Sessions)</v>
+        <v>Chelsea Cutler - BAD (Official Lyric Video)</v>
       </c>
       <c r="B43" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=1ugf5aaY4pY</v>
+        <v>https://www.youtube.com/watch?v=ZIW2vA3Zs1U</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -2012,10 +2012,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>3:16</v>
+        <v>2:16</v>
       </c>
       <c r="H43" t="str">
-        <v>Teddy Swims</v>
+        <v>Chelsea Cutler</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,21 +2027,21 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Teddy Swims - Need You More (Live - Green Room Sessions) - Teddy Swims</v>
+        <v>Chelsea Cutler - BAD (Official Lyric Video) - Chelsea Cutler</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Beck - Love (Audio)</v>
+        <v>TINI - FUTTTURA LIVE - el cielo + fresa</v>
       </c>
       <c r="B44" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=ByABj3Xof1I</v>
+        <v>https://www.youtube.com/watch?v=q_rrgJZAdNg</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2050,10 +2050,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>3:14</v>
+        <v>5:58</v>
       </c>
       <c r="H44" t="str">
-        <v>Beck</v>
+        <v>TINI</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,33 +2065,33 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Beck - Love (Audio) - Beck</v>
+        <v>TINI - FUTTTURA LIVE - el cielo + fresa - TINI</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>The Offspring - Looking Out For #1 | Live in Spokane, WA (2026)</v>
+        <v>Charley - Serial Idealist (Official Video)</v>
       </c>
       <c r="B45" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=2HSbo51EFNg</v>
+        <v>https://www.youtube.com/watch?v=uVIuKbPJz0U</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E45" t="str">
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>2:57</v>
+        <v>3:26</v>
       </c>
       <c r="H45" t="str">
-        <v>The Offspring</v>
+        <v>Charley</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,33 +2103,33 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>The Offspring - Looking Out For #1 | Live in Spokane, WA (2026) - The Offspring</v>
+        <v>Charley - Serial Idealist (Official Video) - Charley</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show</v>
+        <v>Demi Lovato - Ghost (Live)</v>
       </c>
       <c r="B46" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=ylifHFJWJ_c</v>
+        <v>https://www.youtube.com/watch?v=E-ECwdRndVA</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E46" t="str">
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>4:10</v>
+        <v>4:05</v>
       </c>
       <c r="H46" t="str">
-        <v>Sophie Ellis-Bextor</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,33 +2141,33 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show - Sophie Ellis-Bextor</v>
+        <v>Demi Lovato - Ghost (Live) - Demi Lovato</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Jason Derulo - Sexy For Me [Official Music Video]</v>
+        <v>Teddy Swims - Need You More (Live - Green Room Sessions)</v>
       </c>
       <c r="B47" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=9ST-eBNL0NU</v>
+        <v>https://www.youtube.com/watch?v=1ugf5aaY4pY</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E47" t="str">
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>2:10</v>
+        <v>3:16</v>
       </c>
       <c r="H47" t="str">
-        <v>Jason Derulo</v>
+        <v>Teddy Swims</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,33 +2179,33 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Jason Derulo - Sexy For Me [Official Music Video] - Jason Derulo</v>
+        <v>Teddy Swims - Need You More (Live - Green Room Sessions) - Teddy Swims</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Lights - COME GET YOUR GIRL</v>
+        <v>Beck - Love (Audio)</v>
       </c>
       <c r="B48" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=EhzX2y5MpSM</v>
+        <v>https://www.youtube.com/watch?v=ByABj3Xof1I</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E48" t="str">
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>3:52</v>
+        <v>3:14</v>
       </c>
       <c r="H48" t="str">
-        <v>lights</v>
+        <v>Beck</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,21 +2217,21 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Lights - COME GET YOUR GIRL - lights</v>
+        <v>Beck - Love (Audio) - Beck</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video)</v>
+        <v>The Offspring - Looking Out For #1 | Live in Spokane, WA (2026)</v>
       </c>
       <c r="B49" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=yUAvfo8fpuU</v>
+        <v>https://www.youtube.com/watch?v=2HSbo51EFNg</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -2240,10 +2240,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>3:50</v>
+        <v>2:57</v>
       </c>
       <c r="H49" t="str">
-        <v>Telenova</v>
+        <v>The Offspring</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,21 +2255,21 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video) - Telenova</v>
+        <v>The Offspring - Looking Out For #1 | Live in Spokane, WA (2026) - The Offspring</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>I Had To Explain "How Music Works" LIVE In Concert</v>
+        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show</v>
       </c>
       <c r="B50" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=KnsBdAM3HqY</v>
+        <v>https://www.youtube.com/watch?v=ylifHFJWJ_c</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2278,10 +2278,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>5:32</v>
+        <v>4:10</v>
       </c>
       <c r="H50" t="str">
-        <v>Marcin</v>
+        <v>Sophie Ellis-Bextor</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,21 +2293,21 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>I Had To Explain "How Music Works" LIVE In Concert - Marcin</v>
+        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show - Sophie Ellis-Bextor</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>We Three - Drunk Driving (Official Music Video)</v>
+        <v>Jason Derulo - Sexy For Me [Official Music Video]</v>
       </c>
       <c r="B51" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=BTqRGxSX6AQ</v>
+        <v>https://www.youtube.com/watch?v=9ST-eBNL0NU</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2316,10 +2316,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>4:27</v>
+        <v>2:10</v>
       </c>
       <c r="H51" t="str">
-        <v>We Three</v>
+        <v>Jason Derulo</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,33 +2331,33 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>We Three - Drunk Driving (Official Music Video) - We Three</v>
+        <v>Jason Derulo - Sexy For Me [Official Music Video] - Jason Derulo</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Timebelle - Top of the World (Mood Video)</v>
+        <v>Lights - COME GET YOUR GIRL</v>
       </c>
       <c r="B52" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=r9KyYK_E34s</v>
+        <v>https://www.youtube.com/watch?v=EhzX2y5MpSM</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E52" t="str">
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>3:01</v>
+        <v>3:52</v>
       </c>
       <c r="H52" t="str">
-        <v>Timebelle Official</v>
+        <v>lights</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,33 +2369,33 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Timebelle - Top of the World (Mood Video) - Timebelle Official</v>
+        <v>Lights - COME GET YOUR GIRL - lights</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop)</v>
+        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video)</v>
       </c>
       <c r="B53" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=57a_OheOlDw</v>
+        <v>https://www.youtube.com/watch?v=yUAvfo8fpuU</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E53" t="str">
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>3:20</v>
+        <v>3:50</v>
       </c>
       <c r="H53" t="str">
-        <v>David Guetta and Tones And I</v>
+        <v>Telenova</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,33 +2407,33 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop) - David Guetta and Tones And I</v>
+        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video) - Telenova</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Clinton Kane - this is my last love song to you (Official Lyric Video)</v>
+        <v>I Had To Explain "How Music Works" LIVE In Concert</v>
       </c>
       <c r="B54" t="str">
-        <v>10 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=-5Aa8NTiRqE</v>
+        <v>https://www.youtube.com/watch?v=KnsBdAM3HqY</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E54" t="str">
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>10 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G54" t="str">
-        <v>3:34</v>
+        <v>5:32</v>
       </c>
       <c r="H54" t="str">
-        <v>Clinton Kane</v>
+        <v>Marcin</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,33 +2445,33 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Clinton Kane - this is my last love song to you (Official Lyric Video) - Clinton Kane</v>
+        <v>I Had To Explain "How Music Works" LIVE In Concert - Marcin</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>SIENNA SPIRO - Die On This Hill (Official Music Video)</v>
+        <v>We Three - Drunk Driving (Official Music Video)</v>
       </c>
       <c r="B55" t="str">
-        <v>11 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=5RNy_1odv20</v>
+        <v>https://www.youtube.com/watch?v=BTqRGxSX6AQ</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E55" t="str">
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>11 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G55" t="str">
-        <v>4:01</v>
+        <v>4:27</v>
       </c>
       <c r="H55" t="str">
-        <v>Lyrical Lemonade and SIENNA SPIRO</v>
+        <v>We Three</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,33 +2483,33 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>SIENNA SPIRO - Die On This Hill (Official Music Video) - Lyrical Lemonade and SIENNA SPIRO</v>
+        <v>We Three - Drunk Driving (Official Music Video) - We Three</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Amazon Music presents: Sienna Spiro - You Stole The Show</v>
+        <v>Timebelle - Top of the World (Mood Video)</v>
       </c>
       <c r="B56" t="str">
-        <v>11 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=stYIRyCLN4Y</v>
+        <v>https://www.youtube.com/watch?v=r9KyYK_E34s</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E56" t="str">
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>11 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G56" t="str">
-        <v>3:24</v>
+        <v>3:01</v>
       </c>
       <c r="H56" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>Timebelle Official</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,33 +2521,33 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Amazon Music presents: Sienna Spiro - You Stole The Show - SIENNA SPIRO</v>
+        <v>Timebelle - Top of the World (Mood Video) - Timebelle Official</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Harry Styles - Aperture (Official Video)</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop)</v>
       </c>
       <c r="B57" t="str">
-        <v>11 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=7sxVHYZ_PnA</v>
+        <v>https://www.youtube.com/watch?v=57a_OheOlDw</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E57" t="str">
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>11 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G57" t="str">
-        <v>5:52</v>
+        <v>3:20</v>
       </c>
       <c r="H57" t="str">
-        <v>Harry Styles</v>
+        <v>David Guetta and Tones And I</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,33 +2559,33 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Harry Styles - Aperture (Official Video) - Harry Styles</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop) - David Guetta and Tones And I</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Neal Francis - Back It Up (Live At The Salt Shed)</v>
+        <v>Clinton Kane - this is my last love song to you (Official Lyric Video)</v>
       </c>
       <c r="B58" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=46iZEdsxjC0</v>
+        <v>https://www.youtube.com/watch?v=-5Aa8NTiRqE</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E58" t="str">
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G58" t="str">
-        <v>5:01</v>
+        <v>3:34</v>
       </c>
       <c r="H58" t="str">
-        <v>Neal Francis</v>
+        <v>Clinton Kane</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,21 +2597,21 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Neal Francis - Back It Up (Live At The Salt Shed) - Neal Francis</v>
+        <v>Clinton Kane - this is my last love song to you (Official Lyric Video) - Clinton Kane</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
+        <v>SIENNA SPIRO - Die On This Hill (Official Music Video)</v>
       </c>
       <c r="B59" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=K2nG1Uukz7E</v>
+        <v>https://www.youtube.com/watch?v=5RNy_1odv20</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2620,10 +2620,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G59" t="str">
-        <v>4:12</v>
+        <v>4:01</v>
       </c>
       <c r="H59" t="str">
-        <v>OfficiallyExtreme</v>
+        <v>Lyrical Lemonade and SIENNA SPIRO</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,21 +2635,21 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
+        <v>SIENNA SPIRO - Die On This Hill (Official Music Video) - Lyrical Lemonade and SIENNA SPIRO</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Holly Humberstone - To Love Somebody (Official Video)</v>
+        <v>Amazon Music presents: Sienna Spiro - You Stole The Show</v>
       </c>
       <c r="B60" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
+        <v>https://www.youtube.com/watch?v=stYIRyCLN4Y</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -2658,10 +2658,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G60" t="str">
-        <v>3:59</v>
+        <v>3:24</v>
       </c>
       <c r="H60" t="str">
-        <v>Holly Humberstone</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,21 +2673,21 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Holly Humberstone - To Love Somebody (Official Video) - Holly Humberstone</v>
+        <v>Amazon Music presents: Sienna Spiro - You Stole The Show - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
+        <v>Harry Styles - Aperture (Official Video)</v>
       </c>
       <c r="B61" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
+        <v>https://www.youtube.com/watch?v=7sxVHYZ_PnA</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -2696,10 +2696,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G61" t="str">
-        <v>2:56</v>
+        <v>5:52</v>
       </c>
       <c r="H61" t="str">
-        <v>Cliff Richard</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,21 +2711,21 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018) - Cliff Richard</v>
+        <v>Harry Styles - Aperture (Official Video) - Harry Styles</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
+        <v>Neal Francis - Back It Up (Live At The Salt Shed)</v>
       </c>
       <c r="B62" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
+        <v>https://www.youtube.com/watch?v=46iZEdsxjC0</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -2734,10 +2734,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G62" t="str">
-        <v>3:46</v>
+        <v>5:01</v>
       </c>
       <c r="H62" t="str">
-        <v>Jessie Ware</v>
+        <v>Neal Francis</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,21 +2749,21 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Official Video) - Jessie Ware</v>
+        <v>Neal Francis - Back It Up (Live At The Salt Shed) - Neal Francis</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Bella White - Dream Song (Official Audio)</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
       </c>
       <c r="B63" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
+        <v>https://www.youtube.com/watch?v=K2nG1Uukz7E</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -2772,10 +2772,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G63" t="str">
-        <v>4:37</v>
+        <v>4:12</v>
       </c>
       <c r="H63" t="str">
-        <v>Bella White</v>
+        <v>OfficiallyExtreme</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,21 +2787,21 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Bella White - Dream Song (Official Audio) - Bella White</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Ryan Wright - Film School Kids (Official Video)</v>
+        <v>Holly Humberstone - To Love Somebody (Official Video)</v>
       </c>
       <c r="B64" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=pnAz9RwGSek</v>
+        <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -2810,10 +2810,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G64" t="str">
-        <v>4:06</v>
+        <v>3:59</v>
       </c>
       <c r="H64" t="str">
-        <v>Ryan Wright</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,21 +2825,21 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Ryan Wright - Film School Kids (Official Video) - Ryan Wright</v>
+        <v>Holly Humberstone - To Love Somebody (Official Video) - Holly Humberstone</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer)</v>
+        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
       </c>
       <c r="B65" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=u7aPv2saz_I</v>
+        <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -2848,10 +2848,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G65" t="str">
-        <v>3:54</v>
+        <v>2:56</v>
       </c>
       <c r="H65" t="str">
-        <v>Dove Cameron</v>
+        <v>Cliff Richard</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,21 +2863,21 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer) - Dove Cameron</v>
+        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018) - Cliff Richard</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video)</v>
+        <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
       </c>
       <c r="B66" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=WGb8KVdqs6k</v>
+        <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -2886,10 +2886,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G66" t="str">
-        <v>4:10</v>
+        <v>3:46</v>
       </c>
       <c r="H66" t="str">
-        <v>Parker McCollum</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,21 +2901,21 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video) - Parker McCollum</v>
+        <v>Jessie Ware - I Could Get Used To This (Official Video) - Jessie Ware</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video)</v>
+        <v>Bella White - Dream Song (Official Audio)</v>
       </c>
       <c r="B67" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=X1ZeY4Y3l1M</v>
+        <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -2924,10 +2924,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G67" t="str">
-        <v>3:26</v>
+        <v>4:37</v>
       </c>
       <c r="H67" t="str">
-        <v>Matt Hansen</v>
+        <v>Bella White</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,33 +2939,33 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video) - Matt Hansen</v>
+        <v>Bella White - Dream Song (Official Audio) - Bella White</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Louis Tomlinson - Imposter (Official Video)</v>
+        <v>Ryan Wright - Film School Kids (Official Video)</v>
       </c>
       <c r="B68" t="str">
-        <v>13 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=rzuD5szQhso</v>
+        <v>https://www.youtube.com/watch?v=pnAz9RwGSek</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E68" t="str">
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>13 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G68" t="str">
-        <v>2:56</v>
+        <v>4:06</v>
       </c>
       <c r="H68" t="str">
-        <v>Louis Tomlinson</v>
+        <v>Ryan Wright</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,21 +2977,21 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Louis Tomlinson - Imposter (Official Video) - Louis Tomlinson</v>
+        <v>Ryan Wright - Film School Kids (Official Video) - Ryan Wright</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Mitchell Tenpenny - You Phase (Official Music Video)</v>
+        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer)</v>
       </c>
       <c r="B69" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=UPuK6wV5Zco</v>
+        <v>https://www.youtube.com/watch?v=u7aPv2saz_I</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -3000,10 +3000,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G69" t="str">
-        <v>2:56</v>
+        <v>3:54</v>
       </c>
       <c r="H69" t="str">
-        <v>Mitchell Tenpenny</v>
+        <v>Dove Cameron</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,21 +3015,21 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Mitchell Tenpenny - You Phase (Official Music Video) - Mitchell Tenpenny</v>
+        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer) - Dove Cameron</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Tauren Wells - Breathe On It (Official Lyric Video)</v>
+        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video)</v>
       </c>
       <c r="B70" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=9hW9sNMn2A0</v>
+        <v>https://www.youtube.com/watch?v=WGb8KVdqs6k</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -3038,10 +3038,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G70" t="str">
-        <v>4:01</v>
+        <v>4:10</v>
       </c>
       <c r="H70" t="str">
-        <v>Tauren Wells</v>
+        <v>Parker McCollum</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,21 +3053,21 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Tauren Wells - Breathe On It (Official Lyric Video) - Tauren Wells</v>
+        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video) - Parker McCollum</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Maiah Manser - Feeling it All (Official Music Video)</v>
+        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video)</v>
       </c>
       <c r="B71" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=JMYvXleIwfU</v>
+        <v>https://www.youtube.com/watch?v=X1ZeY4Y3l1M</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -3076,10 +3076,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G71" t="str">
-        <v>3:05</v>
+        <v>3:26</v>
       </c>
       <c r="H71" t="str">
-        <v>Maiah Manser</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,33 +3091,33 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Maiah Manser - Feeling it All (Official Music Video) - Maiah Manser</v>
+        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video) - Matt Hansen</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Taylor Austin Dye - Man For That (Official Music Video)</v>
+        <v>Louis Tomlinson - Imposter (Official Video)</v>
       </c>
       <c r="B72" t="str">
-        <v>11 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=vOzX-o11seI</v>
+        <v>https://www.youtube.com/watch?v=rzuD5szQhso</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E72" t="str">
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>11 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G72" t="str">
-        <v>2:27</v>
+        <v>2:56</v>
       </c>
       <c r="H72" t="str">
-        <v>Taylor Austin Dye</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,21 +3129,21 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Taylor Austin Dye - Man For That (Official Music Video) - Taylor Austin Dye</v>
+        <v>Louis Tomlinson - Imposter (Official Video) - Louis Tomlinson</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Chelsea Cutler - BAD (Official Video)</v>
+        <v>Mitchell Tenpenny - You Phase (Official Music Video)</v>
       </c>
       <c r="B73" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=86k4E6ydHVU</v>
+        <v>https://www.youtube.com/watch?v=UPuK6wV5Zco</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -3152,10 +3152,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G73" t="str">
-        <v>2:34</v>
+        <v>2:56</v>
       </c>
       <c r="H73" t="str">
-        <v>Chelsea Cutler</v>
+        <v>Mitchell Tenpenny</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,21 +3167,21 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Chelsea Cutler - BAD (Official Video) - Chelsea Cutler</v>
+        <v>Mitchell Tenpenny - You Phase (Official Music Video) - Mitchell Tenpenny</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video)</v>
+        <v>Tauren Wells - Breathe On It (Official Lyric Video)</v>
       </c>
       <c r="B74" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=-UWIFAiOOPE</v>
+        <v>https://www.youtube.com/watch?v=9hW9sNMn2A0</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -3190,10 +3190,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G74" t="str">
-        <v>3:13</v>
+        <v>4:01</v>
       </c>
       <c r="H74" t="str">
-        <v>Ashley Kutcher</v>
+        <v>Tauren Wells</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,21 +3205,21 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video) - Ashley Kutcher</v>
+        <v>Tauren Wells - Breathe On It (Official Lyric Video) - Tauren Wells</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Louis Tomlinson - Dark To Light (Visualiser)</v>
+        <v>Maiah Manser - Feeling it All (Official Music Video)</v>
       </c>
       <c r="B75" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=02QyA29poAM</v>
+        <v>https://www.youtube.com/watch?v=JMYvXleIwfU</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -3228,10 +3228,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G75" t="str">
-        <v>3:13</v>
+        <v>3:05</v>
       </c>
       <c r="H75" t="str">
-        <v>Louis Tomlinson</v>
+        <v>Maiah Manser</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,21 +3243,21 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Louis Tomlinson - Dark To Light (Visualiser) - Louis Tomlinson</v>
+        <v>Maiah Manser - Feeling it All (Official Music Video) - Maiah Manser</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>CAIN - So Long Sad Songs (Lyric Video)</v>
+        <v>Taylor Austin Dye - Man For That (Official Music Video)</v>
       </c>
       <c r="B76" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=feOv8nufa_I</v>
+        <v>https://www.youtube.com/watch?v=vOzX-o11seI</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -3266,10 +3266,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G76" t="str">
-        <v>3:08</v>
+        <v>2:27</v>
       </c>
       <c r="H76" t="str">
-        <v>CAIN</v>
+        <v>Taylor Austin Dye</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,21 +3281,21 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>CAIN - So Long Sad Songs (Lyric Video) - CAIN</v>
+        <v>Taylor Austin Dye - Man For That (Official Music Video) - Taylor Austin Dye</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Harry Styles - Aperture (Official Audio)</v>
+        <v>Chelsea Cutler - BAD (Official Video)</v>
       </c>
       <c r="B77" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=rA_eCxPay7E</v>
+        <v>https://www.youtube.com/watch?v=86k4E6ydHVU</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -3304,10 +3304,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G77" t="str">
-        <v>5:14</v>
+        <v>2:34</v>
       </c>
       <c r="H77" t="str">
-        <v>Harry Styles</v>
+        <v>Chelsea Cutler</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,33 +3319,33 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Harry Styles - Aperture (Official Audio) - Harry Styles</v>
+        <v>Chelsea Cutler - BAD (Official Video) - Chelsea Cutler</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Lana Lubany - BAD IDEA (Official Video)</v>
+        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video)</v>
       </c>
       <c r="B78" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
+        <v>https://www.youtube.com/watch?v=-UWIFAiOOPE</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E78" t="str">
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G78" t="str">
-        <v>2:59</v>
+        <v>3:13</v>
       </c>
       <c r="H78" t="str">
-        <v>Lana Lubany</v>
+        <v>Ashley Kutcher</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,33 +3357,33 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Lana Lubany - BAD IDEA (Official Video) - Lana Lubany</v>
+        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video) - Ashley Kutcher</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Def Leppard - Rejoice (Lyric Video)</v>
+        <v>Louis Tomlinson - Dark To Light (Visualiser)</v>
       </c>
       <c r="B79" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=zy2TLLeNgp0</v>
+        <v>https://www.youtube.com/watch?v=02QyA29poAM</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E79" t="str">
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G79" t="str">
-        <v>4:21</v>
+        <v>3:13</v>
       </c>
       <c r="H79" t="str">
-        <v>DEF LEPPARD</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,33 +3395,33 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Def Leppard - Rejoice (Lyric Video) - DEF LEPPARD</v>
+        <v>Louis Tomlinson - Dark To Light (Visualiser) - Louis Tomlinson</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Dermot Kennedy - Funeral (Official Music Video)</v>
+        <v>CAIN - So Long Sad Songs (Lyric Video)</v>
       </c>
       <c r="B80" t="str">
-        <v>13 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=JzOUJZPky6o</v>
+        <v>https://www.youtube.com/watch?v=feOv8nufa_I</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E80" t="str">
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>13 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G80" t="str">
-        <v>4:09</v>
+        <v>3:08</v>
       </c>
       <c r="H80" t="str">
-        <v>Dermot Kennedy</v>
+        <v>CAIN</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,33 +3433,33 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Dermot Kennedy - Funeral (Official Music Video) - Dermot Kennedy</v>
+        <v>CAIN - So Long Sad Songs (Lyric Video) - CAIN</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video)</v>
+        <v>Harry Styles - Aperture (Official Audio)</v>
       </c>
       <c r="B81" t="str">
-        <v>13 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=kfF0bVZMCw0</v>
+        <v>https://www.youtube.com/watch?v=rA_eCxPay7E</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E81" t="str">
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>13 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G81" t="str">
-        <v>2:34</v>
+        <v>5:14</v>
       </c>
       <c r="H81" t="str">
-        <v>Lauren Sanderson</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,33 +3471,33 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video) - Lauren Sanderson</v>
+        <v>Harry Styles - Aperture (Official Audio) - Harry Styles</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show]</v>
+        <v>Lana Lubany - BAD IDEA (Official Video)</v>
       </c>
       <c r="B82" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=dLzpNstMHZY</v>
+        <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E82" t="str">
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G82" t="str">
-        <v>3:10</v>
+        <v>2:59</v>
       </c>
       <c r="H82" t="str">
-        <v>Olivia Dean</v>
+        <v>Lana Lubany</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,33 +3509,33 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show] - Olivia Dean</v>
+        <v>Lana Lubany - BAD IDEA (Official Video) - Lana Lubany</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel)</v>
+        <v>Def Leppard - Rejoice (Lyric Video)</v>
       </c>
       <c r="B83" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=fo_j8Fqag8I</v>
+        <v>https://www.youtube.com/watch?v=zy2TLLeNgp0</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E83" t="str">
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G83" t="str">
-        <v>3:21</v>
+        <v>4:21</v>
       </c>
       <c r="H83" t="str">
-        <v>David Guetta and Tones And I</v>
+        <v>DEF LEPPARD</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,33 +3547,33 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel) - David Guetta and Tones And I</v>
+        <v>Def Leppard - Rejoice (Lyric Video) - DEF LEPPARD</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>The Avett Brothers - Matrimony (Official Video)</v>
+        <v>Dermot Kennedy - Funeral (Official Music Video)</v>
       </c>
       <c r="B84" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=7sD9-MtV9CY</v>
+        <v>https://www.youtube.com/watch?v=JzOUJZPky6o</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E84" t="str">
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G84" t="str">
-        <v>3:06</v>
+        <v>4:09</v>
       </c>
       <c r="H84" t="str">
-        <v>The Avett Brothers</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,33 +3585,33 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>The Avett Brothers - Matrimony (Official Video) - The Avett Brothers</v>
+        <v>Dermot Kennedy - Funeral (Official Music Video) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Jordana Bryant - Love Like That (Official Video)</v>
+        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video)</v>
       </c>
       <c r="B85" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=3ATlH-Rtzmk</v>
+        <v>https://www.youtube.com/watch?v=kfF0bVZMCw0</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E85" t="str">
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G85" t="str">
-        <v>3:21</v>
+        <v>2:34</v>
       </c>
       <c r="H85" t="str">
-        <v>Jordana Bryant</v>
+        <v>Lauren Sanderson</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,21 +3623,21 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Jordana Bryant - Love Like That (Official Video) - Jordana Bryant</v>
+        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video) - Lauren Sanderson</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards</v>
+        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show]</v>
       </c>
       <c r="B86" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=kIRmKmEb2g0</v>
+        <v>https://www.youtube.com/watch?v=dLzpNstMHZY</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3646,10 +3646,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G86" t="str">
-        <v>7:21</v>
+        <v>3:10</v>
       </c>
       <c r="H86" t="str">
-        <v>Katy Perry</v>
+        <v>Olivia Dean</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,21 +3661,21 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards - Katy Perry</v>
+        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show] - Olivia Dean</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session)</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel)</v>
       </c>
       <c r="B87" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=oJ-l2ptQwbQ</v>
+        <v>https://www.youtube.com/watch?v=fo_j8Fqag8I</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3684,10 +3684,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G87" t="str">
-        <v>3:17</v>
+        <v>3:21</v>
       </c>
       <c r="H87" t="str">
-        <v>Lauren Watkins</v>
+        <v>David Guetta and Tones And I</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,21 +3699,21 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session) - Lauren Watkins</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel) - David Guetta and Tones And I</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Just A Mess (Live acoustic studio session)</v>
+        <v>The Avett Brothers - Matrimony (Official Video)</v>
       </c>
       <c r="B88" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=ShW-I63KD8w</v>
+        <v>https://www.youtube.com/watch?v=7sD9-MtV9CY</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3722,10 +3722,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G88" t="str">
-        <v>3:45</v>
+        <v>3:06</v>
       </c>
       <c r="H88" t="str">
-        <v>Tones And I</v>
+        <v>The Avett Brothers</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,21 +3737,21 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Just A Mess (Live acoustic studio session) - Tones And I</v>
+        <v>The Avett Brothers - Matrimony (Official Video) - The Avett Brothers</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Ashleigh Dallas - Sail Away (Official Audio)</v>
+        <v>Jordana Bryant - Love Like That (Official Video)</v>
       </c>
       <c r="B89" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=66PDbaI-BVA</v>
+        <v>https://www.youtube.com/watch?v=3ATlH-Rtzmk</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3760,10 +3760,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G89" t="str">
-        <v>3:57</v>
+        <v>3:21</v>
       </c>
       <c r="H89" t="str">
-        <v>Ashleigh Dallas</v>
+        <v>Jordana Bryant</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,21 +3775,21 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Ashleigh Dallas - Sail Away (Official Audio) - Ashleigh Dallas</v>
+        <v>Jordana Bryant - Love Like That (Official Video) - Jordana Bryant</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Performance Video)</v>
+        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards</v>
       </c>
       <c r="B90" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=4tmW_JSXHII</v>
+        <v>https://www.youtube.com/watch?v=kIRmKmEb2g0</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -3798,10 +3798,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G90" t="str">
-        <v>3:03</v>
+        <v>7:21</v>
       </c>
       <c r="H90" t="str">
-        <v>Charlie Puth</v>
+        <v>Katy Perry</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,21 +3813,21 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Performance Video) - Charlie Puth</v>
+        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards - Katy Perry</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Chappell Roan - The Subway (Live from Kansas City)</v>
+        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session)</v>
       </c>
       <c r="B91" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=6kZVtF8iaWw</v>
+        <v>https://www.youtube.com/watch?v=oJ-l2ptQwbQ</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -3836,10 +3836,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G91" t="str">
-        <v>4:27</v>
+        <v>3:17</v>
       </c>
       <c r="H91" t="str">
-        <v>Chappell Roan</v>
+        <v>Lauren Watkins</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,21 +3851,21 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Chappell Roan - The Subway (Live from Kansas City) - Chappell Roan</v>
+        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session) - Lauren Watkins</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar)</v>
+        <v>Just A Mess (Live acoustic studio session)</v>
       </c>
       <c r="B92" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=guUvgEKkk1U</v>
+        <v>https://www.youtube.com/watch?v=ShW-I63KD8w</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -3874,10 +3874,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G92" t="str">
-        <v>4:34</v>
+        <v>3:45</v>
       </c>
       <c r="H92" t="str">
-        <v>Armik</v>
+        <v>Tones And I</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,21 +3889,21 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar) - Armik</v>
+        <v>Just A Mess (Live acoustic studio session) - Tones And I</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>LØLØ - 007 (Official Music Video)</v>
+        <v>Ashleigh Dallas - Sail Away (Official Audio)</v>
       </c>
       <c r="B93" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=4okJouEbZ_s</v>
+        <v>https://www.youtube.com/watch?v=66PDbaI-BVA</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E93" t="str">
         <v/>
@@ -3912,10 +3912,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G93" t="str">
-        <v>2:54</v>
+        <v>3:57</v>
       </c>
       <c r="H93" t="str">
-        <v>LØLØ</v>
+        <v>Ashleigh Dallas</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,21 +3927,21 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>LØLØ - 007 (Official Music Video) - LØLØ</v>
+        <v>Ashleigh Dallas - Sail Away (Official Audio) - Ashleigh Dallas</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Tenille Townes - enabling (Official Visualizer)</v>
+        <v>Charlie Puth - Beat Yourself Up (Performance Video)</v>
       </c>
       <c r="B94" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=yL_TxDF8WtI</v>
+        <v>https://www.youtube.com/watch?v=4tmW_JSXHII</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E94" t="str">
         <v/>
@@ -3950,10 +3950,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G94" t="str">
-        <v>3:25</v>
+        <v>3:03</v>
       </c>
       <c r="H94" t="str">
-        <v>Tenille Townes</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,21 +3965,21 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Tenille Townes - enabling (Official Visualizer) - Tenille Townes</v>
+        <v>Charlie Puth - Beat Yourself Up (Performance Video) - Charlie Puth</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Alan Walker - Not Home (Official Lyric Video)</v>
+        <v>Chappell Roan - The Subway (Live from Kansas City)</v>
       </c>
       <c r="B95" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=0m45tTheoCs</v>
+        <v>https://www.youtube.com/watch?v=6kZVtF8iaWw</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E95" t="str">
         <v/>
@@ -3988,10 +3988,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G95" t="str">
-        <v>2:01</v>
+        <v>4:27</v>
       </c>
       <c r="H95" t="str">
-        <v>Alan Walker</v>
+        <v>Chappell Roan</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,21 +4003,21 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Alan Walker - Not Home (Official Lyric Video) - Alan Walker</v>
+        <v>Chappell Roan - The Subway (Live from Kansas City) - Chappell Roan</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Charli xcx - Wall of Sound (Official Audio)</v>
+        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar)</v>
       </c>
       <c r="B96" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=AHm1i212UP4</v>
+        <v>https://www.youtube.com/watch?v=guUvgEKkk1U</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E96" t="str">
         <v/>
@@ -4026,10 +4026,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G96" t="str">
-        <v>2:25</v>
+        <v>4:34</v>
       </c>
       <c r="H96" t="str">
-        <v>Charli xcx</v>
+        <v>Armik</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,21 +4041,21 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Charli xcx - Wall of Sound (Official Audio) - Charli xcx</v>
+        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Labrinth - God Spoke (Official Visualizer)</v>
+        <v>LØLØ - 007 (Official Music Video)</v>
       </c>
       <c r="B97" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=Srb2P9efFHY</v>
+        <v>https://www.youtube.com/watch?v=4okJouEbZ_s</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E97" t="str">
         <v/>
@@ -4064,10 +4064,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G97" t="str">
-        <v>1:14</v>
+        <v>2:54</v>
       </c>
       <c r="H97" t="str">
-        <v>Labrinth</v>
+        <v>LØLØ</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,21 +4079,21 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Labrinth - God Spoke (Official Visualizer) - Labrinth</v>
+        <v>LØLØ - 007 (Official Music Video) - LØLØ</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Official Audio)</v>
+        <v>Tenille Townes - enabling (Official Visualizer)</v>
       </c>
       <c r="B98" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=NvHXKIrBiR8</v>
+        <v>https://www.youtube.com/watch?v=yL_TxDF8WtI</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E98" t="str">
         <v/>
@@ -4102,10 +4102,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G98" t="str">
-        <v>2:59</v>
+        <v>3:25</v>
       </c>
       <c r="H98" t="str">
-        <v>Charlie Puth</v>
+        <v>Tenille Townes</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,21 +4117,21 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Official Audio) - Charlie Puth</v>
+        <v>Tenille Townes - enabling (Official Visualizer) - Tenille Townes</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Girl Tones - Volcano (Visualizer)</v>
+        <v>Alan Walker - Not Home (Official Lyric Video)</v>
       </c>
       <c r="B99" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=D2-t5SDV1IE</v>
+        <v>https://www.youtube.com/watch?v=0m45tTheoCs</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E99" t="str">
         <v/>
@@ -4140,10 +4140,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G99" t="str">
-        <v>2:29</v>
+        <v>2:01</v>
       </c>
       <c r="H99" t="str">
-        <v>Girl Tones</v>
+        <v>Alan Walker</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,21 +4155,21 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Girl Tones - Volcano (Visualizer) - Girl Tones</v>
+        <v>Alan Walker - Not Home (Official Lyric Video) - Alan Walker</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer)</v>
+        <v>Charli xcx - Wall of Sound (Official Audio)</v>
       </c>
       <c r="B100" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=BouRN2QuXV8</v>
+        <v>https://www.youtube.com/watch?v=AHm1i212UP4</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E100" t="str">
         <v/>
@@ -4178,10 +4178,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G100" t="str">
-        <v>2:34</v>
+        <v>2:25</v>
       </c>
       <c r="H100" t="str">
-        <v>Jagwar Twin</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,21 +4193,21 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer) - Jagwar Twin</v>
+        <v>Charli xcx - Wall of Sound (Official Audio) - Charli xcx</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video)</v>
+        <v>Labrinth - God Spoke (Official Visualizer)</v>
       </c>
       <c r="B101" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=IyPD6AnWlRg</v>
+        <v>https://www.youtube.com/watch?v=Srb2P9efFHY</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E101" t="str">
         <v/>
@@ -4216,10 +4216,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G101" t="str">
-        <v>3:48</v>
+        <v>1:14</v>
       </c>
       <c r="H101" t="str">
-        <v>Caroline Jones</v>
+        <v>Labrinth</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,7 +4231,7 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video) - Caroline Jones</v>
+        <v>Labrinth - God Spoke (Official Visualizer) - Labrinth</v>
       </c>
     </row>
     <row r="102">
@@ -4245,7 +4245,7 @@
         <v>https://music.apple.com/us/song/penny-in-the-lake/1844710053</v>
       </c>
       <c r="D102" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E102" t="str">
         <v/>
@@ -4283,7 +4283,7 @@
         <v>https://music.apple.com/us/song/body/1871258331</v>
       </c>
       <c r="D103" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E103" t="str">
         <v/>
@@ -4321,7 +4321,7 @@
         <v>https://music.apple.com/us/song/dandelion/1869436838</v>
       </c>
       <c r="D104" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E104" t="str">
         <v/>
@@ -4359,7 +4359,7 @@
         <v>https://music.apple.com/us/song/lights-go-out/1870833473</v>
       </c>
       <c r="D105" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E105" t="str">
         <v/>
@@ -4397,7 +4397,7 @@
         <v>https://music.apple.com/us/song/the-great-divide/1872239886</v>
       </c>
       <c r="D106" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E106" t="str">
         <v/>
@@ -4435,7 +4435,7 @@
         <v>https://music.apple.com/us/song/trist%C3%B3n/1872585947</v>
       </c>
       <c r="D107" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E107" t="str">
         <v/>
@@ -4473,7 +4473,7 @@
         <v>https://music.apple.com/us/song/feed-the-streets/1869462051</v>
       </c>
       <c r="D108" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E108" t="str">
         <v/>
@@ -4511,7 +4511,7 @@
         <v>https://music.apple.com/us/song/i-did-this-to-myself/1861531672</v>
       </c>
       <c r="D109" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E109" t="str">
         <v/>
@@ -4549,7 +4549,7 @@
         <v>https://music.apple.com/us/song/heaven/1862570892</v>
       </c>
       <c r="D110" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E110" t="str">
         <v/>
@@ -4587,7 +4587,7 @@
         <v>https://music.apple.com/us/song/for-hire/1870722567</v>
       </c>
       <c r="D111" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E111" t="str">
         <v/>
@@ -4625,7 +4625,7 @@
         <v>https://music.apple.com/us/song/mcarthur/1871231844</v>
       </c>
       <c r="D112" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E112" t="str">
         <v/>
@@ -4663,7 +4663,7 @@
         <v>https://music.apple.com/us/song/debris/1853069633</v>
       </c>
       <c r="D113" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E113" t="str">
         <v/>
@@ -4701,7 +4701,7 @@
         <v>https://music.apple.com/us/song/god-owes-me-money-live-at-apple-music-radio/1871521120</v>
       </c>
       <c r="D114" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E114" t="str">
         <v/>
@@ -4739,7 +4739,7 @@
         <v>https://music.apple.com/us/song/rockstar-raging-feat-swae-lee/1873028187</v>
       </c>
       <c r="D115" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E115" t="str">
         <v/>
@@ -4777,7 +4777,7 @@
         <v>https://music.apple.com/us/song/1-1/1870378316</v>
       </c>
       <c r="D116" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E116" t="str">
         <v/>
@@ -4815,7 +4815,7 @@
         <v>https://music.apple.com/us/song/still-sincere-feat-pinkpantheress/1862228374</v>
       </c>
       <c r="D117" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E117" t="str">
         <v/>
@@ -4853,7 +4853,7 @@
         <v>https://music.apple.com/us/song/two-car-garage/1869137588</v>
       </c>
       <c r="D118" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E118" t="str">
         <v/>
@@ -4891,7 +4891,7 @@
         <v>https://music.apple.com/us/song/fml/1872686260</v>
       </c>
       <c r="D119" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E119" t="str">
         <v/>
@@ -4929,7 +4929,7 @@
         <v>https://music.apple.com/us/song/faked-it-all-the-time/1871050032</v>
       </c>
       <c r="D120" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E120" t="str">
         <v/>
@@ -4967,7 +4967,7 @@
         <v>https://music.apple.com/us/song/house-of-the-rising-sun/1872111857</v>
       </c>
       <c r="D121" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E121" t="str">
         <v/>
@@ -5005,7 +5005,7 @@
         <v>https://music.apple.com/us/song/lorelei/1867640808</v>
       </c>
       <c r="D122" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E122" t="str">
         <v/>
@@ -5043,7 +5043,7 @@
         <v>https://music.apple.com/us/song/free/1870703329</v>
       </c>
       <c r="D123" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E123" t="str">
         <v/>
@@ -5081,7 +5081,7 @@
         <v>https://music.apple.com/us/song/assignment/1872764440</v>
       </c>
       <c r="D124" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E124" t="str">
         <v/>
@@ -5119,7 +5119,7 @@
         <v>https://music.apple.com/us/song/professional-heartbreaker/1871053476</v>
       </c>
       <c r="D125" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E125" t="str">
         <v/>
@@ -5157,7 +5157,7 @@
         <v>https://music.apple.com/us/song/tell-me-what-you-want/1871463892</v>
       </c>
       <c r="D126" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E126" t="str">
         <v/>
@@ -5195,7 +5195,7 @@
         <v>https://music.apple.com/us/song/aguas/1869455857</v>
       </c>
       <c r="D127" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E127" t="str">
         <v/>
@@ -5233,7 +5233,7 @@
         <v>https://music.apple.com/us/song/ants-in-my-room/1870967813</v>
       </c>
       <c r="D128" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E128" t="str">
         <v/>
@@ -5271,7 +5271,7 @@
         <v>https://music.apple.com/us/song/baddie/1849760827</v>
       </c>
       <c r="D129" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E129" t="str">
         <v/>
@@ -5309,7 +5309,7 @@
         <v>https://music.apple.com/us/song/what-you-need-a-colors-show/1870990925</v>
       </c>
       <c r="D130" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E130" t="str">
         <v/>
@@ -5347,7 +5347,7 @@
         <v>https://music.apple.com/us/song/ok-ok-hamdi-remix/1871538130</v>
       </c>
       <c r="D131" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E131" t="str">
         <v/>
@@ -5385,7 +5385,7 @@
         <v>https://music.apple.com/us/song/ever-and-ever-before-feat-m%C5%8Driah-courtney/1869383260</v>
       </c>
       <c r="D132" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E132" t="str">
         <v/>
@@ -5423,7 +5423,7 @@
         <v>https://music.apple.com/us/song/for-the-first-time-again/1834736723</v>
       </c>
       <c r="D133" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E133" t="str">
         <v/>
@@ -5461,7 +5461,7 @@
         <v>https://music.apple.com/us/song/liars-tale/1862207951</v>
       </c>
       <c r="D134" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E134" t="str">
         <v/>
@@ -5499,7 +5499,7 @@
         <v>https://music.apple.com/us/song/afraid-of-the-dark/1872184048</v>
       </c>
       <c r="D135" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E135" t="str">
         <v/>
@@ -5537,7 +5537,7 @@
         <v>https://music.apple.com/us/song/wake-up-calling/1862338150</v>
       </c>
       <c r="D136" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E136" t="str">
         <v/>
@@ -5575,7 +5575,7 @@
         <v>https://music.apple.com/us/song/high/1867202644</v>
       </c>
       <c r="D137" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E137" t="str">
         <v/>
@@ -5613,7 +5613,7 @@
         <v>https://music.apple.com/us/song/villain/1860126455</v>
       </c>
       <c r="D138" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E138" t="str">
         <v/>
@@ -5651,7 +5651,7 @@
         <v>https://music.apple.com/us/song/bad-idea-right/1869792549</v>
       </c>
       <c r="D139" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E139" t="str">
         <v/>
@@ -5689,7 +5689,7 @@
         <v>https://music.apple.com/us/song/residue/1863786787</v>
       </c>
       <c r="D140" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E140" t="str">
         <v/>
@@ -5727,7 +5727,7 @@
         <v>https://music.apple.com/us/song/i-used-to-go-to-this-bar/1839918872</v>
       </c>
       <c r="D141" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E141" t="str">
         <v/>
@@ -5765,7 +5765,7 @@
         <v>https://music.apple.com/us/song/starlight/1870989674</v>
       </c>
       <c r="D142" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E142" t="str">
         <v/>
@@ -5803,7 +5803,7 @@
         <v>https://music.apple.com/us/song/dandelion/1863154133</v>
       </c>
       <c r="D143" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E143" t="str">
         <v/>
@@ -5841,7 +5841,7 @@
         <v>https://music.apple.com/us/song/themselves/1845287173</v>
       </c>
       <c r="D144" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E144" t="str">
         <v/>
@@ -5879,7 +5879,7 @@
         <v>https://music.apple.com/us/song/high-maintenance/1872497656</v>
       </c>
       <c r="D145" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E145" t="str">
         <v/>
@@ -5917,7 +5917,7 @@
         <v>https://music.apple.com/us/song/trackhawk/1860991724</v>
       </c>
       <c r="D146" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E146" t="str">
         <v/>
@@ -5955,7 +5955,7 @@
         <v>https://music.apple.com/us/song/wheel-man/1872178895</v>
       </c>
       <c r="D147" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E147" t="str">
         <v/>
@@ -5993,7 +5993,7 @@
         <v>https://music.apple.com/us/song/natural-disaster/1871263211</v>
       </c>
       <c r="D148" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E148" t="str">
         <v/>
@@ -6031,7 +6031,7 @@
         <v>https://music.apple.com/us/song/prettier/1869745409</v>
       </c>
       <c r="D149" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E149" t="str">
         <v/>
@@ -6069,7 +6069,7 @@
         <v>https://music.apple.com/us/song/shotta-flow-8/1872760524</v>
       </c>
       <c r="D150" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E150" t="str">
         <v/>
@@ -6107,7 +6107,7 @@
         <v>https://music.apple.com/us/song/die-to-fall/1866902681</v>
       </c>
       <c r="D151" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E151" t="str">
         <v/>
@@ -6145,7 +6145,7 @@
         <v>https://music.apple.com/us/song/the-cruel-angels-thesis-neon-genesis-evangelion/1864932139</v>
       </c>
       <c r="D152" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E152" t="str">
         <v/>
@@ -6183,7 +6183,7 @@
         <v>https://music.apple.com/us/song/slow-burn/1851033862</v>
       </c>
       <c r="D153" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E153" t="str">
         <v/>
@@ -6221,7 +6221,7 @@
         <v>https://music.apple.com/us/song/too-late/1857999860</v>
       </c>
       <c r="D154" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E154" t="str">
         <v/>
@@ -6259,7 +6259,7 @@
         <v>https://music.apple.com/us/song/mono-feat-skaiwater/1869130804</v>
       </c>
       <c r="D155" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E155" t="str">
         <v/>
@@ -6297,7 +6297,7 @@
         <v>https://music.apple.com/us/song/thank-you-is-enough/1870679042</v>
       </c>
       <c r="D156" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E156" t="str">
         <v/>
@@ -6335,7 +6335,7 @@
         <v>https://music.apple.com/us/song/ridin/1869786726</v>
       </c>
       <c r="D157" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E157" t="str">
         <v/>
@@ -6373,7 +6373,7 @@
         <v>https://music.apple.com/us/song/possession/1872536200</v>
       </c>
       <c r="D158" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E158" t="str">
         <v/>
@@ -6411,7 +6411,7 @@
         <v>https://music.apple.com/us/song/poema/1872723644</v>
       </c>
       <c r="D159" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E159" t="str">
         <v/>
@@ -6449,7 +6449,7 @@
         <v>https://music.apple.com/us/song/live-without/1862777625</v>
       </c>
       <c r="D160" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E160" t="str">
         <v/>
@@ -6487,7 +6487,7 @@
         <v>https://music.apple.com/us/song/fan%C3%A1tico/1871611852</v>
       </c>
       <c r="D161" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E161" t="str">
         <v/>
@@ -6525,7 +6525,7 @@
         <v>https://music.apple.com/us/song/frozen-lake/1867287070</v>
       </c>
       <c r="D162" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E162" t="str">
         <v/>
@@ -6563,7 +6563,7 @@
         <v>https://music.apple.com/us/song/fine-shyt-eb-remix-feat-eric-bellinger/1870964385</v>
       </c>
       <c r="D163" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E163" t="str">
         <v/>
@@ -6601,7 +6601,7 @@
         <v>https://music.apple.com/us/song/hell-yeah-feat-waxmaster/1866602820</v>
       </c>
       <c r="D164" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E164" t="str">
         <v/>
@@ -6639,7 +6639,7 @@
         <v>https://music.apple.com/us/song/its-like-that/1858689757</v>
       </c>
       <c r="D165" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E165" t="str">
         <v/>
@@ -6677,7 +6677,7 @@
         <v>https://music.apple.com/us/song/a-s-a-p/1833414737</v>
       </c>
       <c r="D166" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E166" t="str">
         <v/>
@@ -6715,7 +6715,7 @@
         <v>https://music.apple.com/us/song/once-i-say/1867855025</v>
       </c>
       <c r="D167" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E167" t="str">
         <v/>
@@ -6753,7 +6753,7 @@
         <v>https://music.apple.com/us/song/believer/1862797080</v>
       </c>
       <c r="D168" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E168" t="str">
         <v/>
@@ -6791,7 +6791,7 @@
         <v>https://music.apple.com/us/song/i-envy-the-wind/1863202477</v>
       </c>
       <c r="D169" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E169" t="str">
         <v/>
@@ -6829,7 +6829,7 @@
         <v>https://music.apple.com/us/song/the-alchemist/1831827347</v>
       </c>
       <c r="D170" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E170" t="str">
         <v/>
@@ -6867,7 +6867,7 @@
         <v>https://music.apple.com/us/song/daysa/1861575845</v>
       </c>
       <c r="D171" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E171" t="str">
         <v/>
@@ -6905,7 +6905,7 @@
         <v>https://music.apple.com/us/song/fabulous/1862804005</v>
       </c>
       <c r="D172" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E172" t="str">
         <v/>
@@ -6943,7 +6943,7 @@
         <v>https://music.apple.com/us/song/me-asusta-amar-tanto-la-soledad/1866982109</v>
       </c>
       <c r="D173" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E173" t="str">
         <v/>
@@ -6981,7 +6981,7 @@
         <v>https://music.apple.com/us/song/brainchem/1870656942</v>
       </c>
       <c r="D174" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E174" t="str">
         <v/>
@@ -7019,7 +7019,7 @@
         <v>https://music.apple.com/us/song/boyfriend-in-yo-brain-notice-me/1871675026</v>
       </c>
       <c r="D175" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E175" t="str">
         <v/>
@@ -7057,7 +7057,7 @@
         <v>https://music.apple.com/us/song/giants/1869154957</v>
       </c>
       <c r="D176" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E176" t="str">
         <v/>
@@ -7095,7 +7095,7 @@
         <v>https://music.apple.com/us/song/scooby/1872510752</v>
       </c>
       <c r="D177" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E177" t="str">
         <v/>
@@ -7133,7 +7133,7 @@
         <v>https://music.apple.com/us/song/la-racha/1868757762</v>
       </c>
       <c r="D178" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E178" t="str">
         <v/>
@@ -7171,7 +7171,7 @@
         <v>https://music.apple.com/us/song/so-am-i/1867012209</v>
       </c>
       <c r="D179" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E179" t="str">
         <v/>
@@ -7209,7 +7209,7 @@
         <v>https://music.apple.com/us/song/best-thing/1860673616</v>
       </c>
       <c r="D180" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E180" t="str">
         <v/>
@@ -7247,7 +7247,7 @@
         <v>https://music.apple.com/us/song/count-it-back/1855219865</v>
       </c>
       <c r="D181" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E181" t="str">
         <v/>
@@ -7285,7 +7285,7 @@
         <v>https://music.apple.com/us/song/good-girl/1862640697</v>
       </c>
       <c r="D182" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E182" t="str">
         <v/>
@@ -7323,7 +7323,7 @@
         <v>https://music.apple.com/us/song/my-revival/1869465104</v>
       </c>
       <c r="D183" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E183" t="str">
         <v/>
@@ -7361,7 +7361,7 @@
         <v>https://music.apple.com/us/song/run-my-way/1860964996</v>
       </c>
       <c r="D184" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E184" t="str">
         <v/>
@@ -7399,7 +7399,7 @@
         <v>https://music.apple.com/us/song/cold-night/1867687787</v>
       </c>
       <c r="D185" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E185" t="str">
         <v/>
@@ -7437,7 +7437,7 @@
         <v>https://music.apple.com/us/song/away-with-the-fairies/1870603474</v>
       </c>
       <c r="D186" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E186" t="str">
         <v/>
@@ -7475,7 +7475,7 @@
         <v>https://music.apple.com/us/song/fragile/1866957569</v>
       </c>
       <c r="D187" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E187" t="str">
         <v/>
@@ -7513,7 +7513,7 @@
         <v>https://music.apple.com/us/song/slow-dancin/1871537173</v>
       </c>
       <c r="D188" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E188" t="str">
         <v/>
@@ -7551,7 +7551,7 @@
         <v>https://music.apple.com/us/song/never-kissed-a-cowboy/1866744530</v>
       </c>
       <c r="D189" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E189" t="str">
         <v/>
@@ -7589,7 +7589,7 @@
         <v>https://music.apple.com/us/song/more-of-what-matters/1871592720</v>
       </c>
       <c r="D190" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E190" t="str">
         <v/>
@@ -7627,7 +7627,7 @@
         <v>https://music.apple.com/us/song/is-this-the-real-you/1869323368</v>
       </c>
       <c r="D191" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E191" t="str">
         <v/>
@@ -7665,7 +7665,7 @@
         <v>https://music.apple.com/us/song/hud/1842015019</v>
       </c>
       <c r="D192" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E192" t="str">
         <v/>
@@ -7703,7 +7703,7 @@
         <v>https://music.apple.com/us/song/ego-death/1867855427</v>
       </c>
       <c r="D193" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E193" t="str">
         <v/>
@@ -7741,7 +7741,7 @@
         <v>https://music.apple.com/us/song/gas-station-love-remix/1872150728</v>
       </c>
       <c r="D194" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E194" t="str">
         <v/>
@@ -7779,7 +7779,7 @@
         <v>https://music.apple.com/us/song/disappear/1861907311</v>
       </c>
       <c r="D195" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E195" t="str">
         <v/>
@@ -7817,7 +7817,7 @@
         <v>https://music.apple.com/us/song/misbehave/1859630128</v>
       </c>
       <c r="D196" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E196" t="str">
         <v/>
@@ -7855,7 +7855,7 @@
         <v>https://music.apple.com/us/song/club-bizarre/1870355078</v>
       </c>
       <c r="D197" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E197" t="str">
         <v/>
@@ -7893,7 +7893,7 @@
         <v>https://music.apple.com/us/song/fly/1867903625</v>
       </c>
       <c r="D198" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E198" t="str">
         <v/>
@@ -7931,7 +7931,7 @@
         <v>https://music.apple.com/us/song/ily-anyway/1870369432</v>
       </c>
       <c r="D199" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E199" t="str">
         <v/>
@@ -7969,7 +7969,7 @@
         <v>https://music.apple.com/us/song/george-jones-feat-angela-autumn/1867306007</v>
       </c>
       <c r="D200" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E200" t="str">
         <v/>
@@ -8007,7 +8007,7 @@
         <v>https://music.apple.com/us/song/kiss-big/1837292261</v>
       </c>
       <c r="D201" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E201" t="str">
         <v/>
@@ -8045,7 +8045,7 @@
         <v>https://music.apple.com/us/song/praxis/1845253734</v>
       </c>
       <c r="D202" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E202" t="str">
         <v/>
@@ -8083,7 +8083,7 @@
         <v>https://music.apple.com/us/song/house/1866696487</v>
       </c>
       <c r="D203" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E203" t="str">
         <v/>
@@ -8121,7 +8121,7 @@
         <v>https://music.apple.com/us/song/cowboy-without-a-clue/1834024322</v>
       </c>
       <c r="D204" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E204" t="str">
         <v/>
@@ -8159,7 +8159,7 @@
         <v>https://music.apple.com/us/song/brincar/1871554907</v>
       </c>
       <c r="D205" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E205" t="str">
         <v/>
@@ -8197,7 +8197,7 @@
         <v>https://music.apple.com/us/song/qui%C3%A9n/1870329662</v>
       </c>
       <c r="D206" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E206" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Marc Anthony - Make It With You (Visualizer)</v>
       </c>
       <c r="B2" t="str">
-        <v>1 hour ago</v>
+        <v>4 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=WHnz1jDrxw8</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>1 hour ago</v>
+        <v>4 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>4:24</v>
@@ -477,7 +477,7 @@
         <v>Clara Mae - Never Been Yours ft. Bob John Holt</v>
       </c>
       <c r="B3" t="str">
-        <v>8 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=HtVuKBlBuPg</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>8 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>2:33</v>
@@ -515,7 +515,7 @@
         <v>Metric - Victim of Luck (Official Music Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>8 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=shmhTOUd8mA</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>8 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>3:25</v>
@@ -553,7 +553,7 @@
         <v>Kesha - RED FLAG. (Red Carpet) OFFICIAL MUSIC VIDEO</v>
       </c>
       <c r="B5" t="str">
-        <v>12 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=pvrJ5RnPAEA</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>12 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>3:41</v>
@@ -2567,7 +2567,7 @@
         <v>Clinton Kane - this is my last love song to you (Official Lyric Video)</v>
       </c>
       <c r="B58" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C58" t="str">
         <v>https://www.youtube.com/watch?v=-5Aa8NTiRqE</v>
@@ -2579,7 +2579,7 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G58" t="str">
         <v>3:34</v>
@@ -3593,7 +3593,7 @@
         <v>Lauren Sanderson - SPELL IT OUT (Official Music Video)</v>
       </c>
       <c r="B85" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C85" t="str">
         <v>https://www.youtube.com/watch?v=kfF0bVZMCw0</v>
@@ -3605,7 +3605,7 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G85" t="str">
         <v>2:34</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Marc Anthony - Make It With You (Visualizer)</v>
       </c>
       <c r="B2" t="str">
-        <v>4 hours ago</v>
+        <v>5 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=WHnz1jDrxw8</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>4 hours ago</v>
+        <v>5 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>4:24</v>
@@ -477,7 +477,7 @@
         <v>Clara Mae - Never Been Yours ft. Bob John Holt</v>
       </c>
       <c r="B3" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=HtVuKBlBuPg</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>2:33</v>
@@ -515,7 +515,7 @@
         <v>Metric - Victim of Luck (Official Music Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=shmhTOUd8mA</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>3:25</v>
@@ -553,7 +553,7 @@
         <v>Kesha - RED FLAG. (Red Carpet) OFFICIAL MUSIC VIDEO</v>
       </c>
       <c r="B5" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=pvrJ5RnPAEA</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>3:41</v>
@@ -1503,7 +1503,7 @@
         <v>Ella Langley - Dandelion (Official Visualizer)</v>
       </c>
       <c r="B30" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=sf6eRmInk1s</v>
@@ -1515,7 +1515,7 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G30" t="str">
         <v>4:01</v>
@@ -1541,7 +1541,7 @@
         <v>Dogpark - Dandelion (Official Music Video)</v>
       </c>
       <c r="B31" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=fv9prIYHHzk</v>
@@ -1553,7 +1553,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G31" t="str">
         <v>3:16</v>
@@ -1579,7 +1579,7 @@
         <v>Lauren Spencer Smith - Natural Disaster (Visualizer)</v>
       </c>
       <c r="B32" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=T9YvLA2cdZs</v>
@@ -1591,7 +1591,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G32" t="str">
         <v>3:03</v>
@@ -1617,7 +1617,7 @@
         <v>ERNEST - Lorelei (Official Music Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C33" t="str">
         <v>https://www.youtube.com/watch?v=dPWc_6IdDJk</v>
@@ -1629,7 +1629,7 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G33" t="str">
         <v>2:41</v>
@@ -1655,7 +1655,7 @@
         <v>Labrinth - I Keep My Promises (Official Audio)</v>
       </c>
       <c r="B34" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=CV5rR9JZK-0</v>
@@ -1667,7 +1667,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G34" t="str">
         <v>3:05</v>
@@ -1693,7 +1693,7 @@
         <v>Grace VanderWaal - Prettier (Official Lyric Video)</v>
       </c>
       <c r="B35" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=9HwTj3NZ16E</v>
@@ -1705,7 +1705,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G35" t="str">
         <v>2:46</v>
@@ -1731,7 +1731,7 @@
         <v>VOILÀ - Frozen Lake (Official Lyric Video)</v>
       </c>
       <c r="B36" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=Lmus-UbL1H0</v>
@@ -1743,7 +1743,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G36" t="str">
         <v>3:32</v>
@@ -1769,7 +1769,7 @@
         <v>Cannons - Starlight (Official Video)</v>
       </c>
       <c r="B37" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C37" t="str">
         <v>https://www.youtube.com/watch?v=bu6WSMDDPGY</v>
@@ -1781,7 +1781,7 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G37" t="str">
         <v>3:42</v>
@@ -1807,7 +1807,7 @@
         <v>Kylie Morgan - Like My Own (Official Video)</v>
       </c>
       <c r="B38" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=zcYeoGBglC0</v>
@@ -1819,7 +1819,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G38" t="str">
         <v>2:38</v>
@@ -1845,7 +1845,7 @@
         <v>Lizzy McAlpine - House of the Rising Sun (Audio)</v>
       </c>
       <c r="B39" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=3igYRj82EiU</v>
@@ -1857,7 +1857,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G39" t="str">
         <v>3:10</v>
@@ -1883,7 +1883,7 @@
         <v>Willie Nelson - Heart Of America (From The Gray House Original Soundtrack)</v>
       </c>
       <c r="B40" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=0bhcO4Yphuo</v>
@@ -1895,7 +1895,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G40" t="str">
         <v>3:57</v>
@@ -1921,7 +1921,7 @@
         <v>Jeremy Camp - No Survivors (Live) ft. Skillet</v>
       </c>
       <c r="B41" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=Jjz1wFe5dMo</v>
@@ -1933,7 +1933,7 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G41" t="str">
         <v>2:19</v>
@@ -2909,7 +2909,7 @@
         <v>Bella White - Dream Song (Official Audio)</v>
       </c>
       <c r="B67" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C67" t="str">
         <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
@@ -2921,7 +2921,7 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G67" t="str">
         <v>4:37</v>
@@ -2947,7 +2947,7 @@
         <v>Ryan Wright - Film School Kids (Official Video)</v>
       </c>
       <c r="B68" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C68" t="str">
         <v>https://www.youtube.com/watch?v=pnAz9RwGSek</v>
@@ -2959,7 +2959,7 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G68" t="str">
         <v>4:06</v>
@@ -2985,7 +2985,7 @@
         <v>Dove Cameron - Do I Wanna Know? (Official Visualizer)</v>
       </c>
       <c r="B69" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C69" t="str">
         <v>https://www.youtube.com/watch?v=u7aPv2saz_I</v>
@@ -2997,7 +2997,7 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G69" t="str">
         <v>3:54</v>
@@ -3023,7 +3023,7 @@
         <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video)</v>
       </c>
       <c r="B70" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C70" t="str">
         <v>https://www.youtube.com/watch?v=WGb8KVdqs6k</v>
@@ -3035,7 +3035,7 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G70" t="str">
         <v>4:10</v>
@@ -3061,7 +3061,7 @@
         <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video)</v>
       </c>
       <c r="B71" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C71" t="str">
         <v>https://www.youtube.com/watch?v=X1ZeY4Y3l1M</v>
@@ -3073,7 +3073,7 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G71" t="str">
         <v>3:26</v>
@@ -3137,7 +3137,7 @@
         <v>Mitchell Tenpenny - You Phase (Official Music Video)</v>
       </c>
       <c r="B73" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C73" t="str">
         <v>https://www.youtube.com/watch?v=UPuK6wV5Zco</v>
@@ -3149,7 +3149,7 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G73" t="str">
         <v>2:56</v>
@@ -3175,7 +3175,7 @@
         <v>Tauren Wells - Breathe On It (Official Lyric Video)</v>
       </c>
       <c r="B74" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C74" t="str">
         <v>https://www.youtube.com/watch?v=9hW9sNMn2A0</v>
@@ -3187,7 +3187,7 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G74" t="str">
         <v>4:01</v>
@@ -3213,7 +3213,7 @@
         <v>Maiah Manser - Feeling it All (Official Music Video)</v>
       </c>
       <c r="B75" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C75" t="str">
         <v>https://www.youtube.com/watch?v=JMYvXleIwfU</v>
@@ -3225,7 +3225,7 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G75" t="str">
         <v>3:05</v>
@@ -3251,7 +3251,7 @@
         <v>Taylor Austin Dye - Man For That (Official Music Video)</v>
       </c>
       <c r="B76" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C76" t="str">
         <v>https://www.youtube.com/watch?v=vOzX-o11seI</v>
@@ -3263,7 +3263,7 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G76" t="str">
         <v>2:27</v>
@@ -3289,7 +3289,7 @@
         <v>Chelsea Cutler - BAD (Official Video)</v>
       </c>
       <c r="B77" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C77" t="str">
         <v>https://www.youtube.com/watch?v=86k4E6ydHVU</v>
@@ -3301,7 +3301,7 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G77" t="str">
         <v>2:34</v>
@@ -3327,7 +3327,7 @@
         <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video)</v>
       </c>
       <c r="B78" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C78" t="str">
         <v>https://www.youtube.com/watch?v=-UWIFAiOOPE</v>
@@ -3339,7 +3339,7 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G78" t="str">
         <v>3:13</v>
@@ -3365,7 +3365,7 @@
         <v>Louis Tomlinson - Dark To Light (Visualiser)</v>
       </c>
       <c r="B79" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C79" t="str">
         <v>https://www.youtube.com/watch?v=02QyA29poAM</v>
@@ -3377,7 +3377,7 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G79" t="str">
         <v>3:13</v>
@@ -3403,7 +3403,7 @@
         <v>CAIN - So Long Sad Songs (Lyric Video)</v>
       </c>
       <c r="B80" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C80" t="str">
         <v>https://www.youtube.com/watch?v=feOv8nufa_I</v>
@@ -3415,7 +3415,7 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G80" t="str">
         <v>3:08</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Marc Anthony - Make It With You (Visualizer)</v>
       </c>
       <c r="B2" t="str">
-        <v>5 hours ago</v>
+        <v>6 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=WHnz1jDrxw8</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>5 hours ago</v>
+        <v>6 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>4:24</v>
@@ -477,7 +477,7 @@
         <v>Clara Mae - Never Been Yours ft. Bob John Holt</v>
       </c>
       <c r="B3" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=HtVuKBlBuPg</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>2:33</v>
@@ -515,7 +515,7 @@
         <v>Metric - Victim of Luck (Official Music Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=shmhTOUd8mA</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>3:25</v>
@@ -553,7 +553,7 @@
         <v>Kesha - RED FLAG. (Red Carpet) OFFICIAL MUSIC VIDEO</v>
       </c>
       <c r="B5" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=pvrJ5RnPAEA</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>3:41</v>
@@ -1465,7 +1465,7 @@
         <v>SANTOS BRAVOS “KAWASAKI” Performance Video</v>
       </c>
       <c r="B29" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=Cmy8CsYIUL0</v>
@@ -1477,7 +1477,7 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G29" t="str">
         <v>2:41</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Marc Anthony - Make It With You (Visualizer)</v>
       </c>
       <c r="B2" t="str">
-        <v>6 hours ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=WHnz1jDrxw8</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>6 hours ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>4:24</v>
@@ -477,7 +477,7 @@
         <v>Clara Mae - Never Been Yours ft. Bob John Holt</v>
       </c>
       <c r="B3" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=HtVuKBlBuPg</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>2:33</v>
@@ -515,7 +515,7 @@
         <v>Metric - Victim of Luck (Official Music Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=shmhTOUd8mA</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>3:25</v>
@@ -553,7 +553,7 @@
         <v>Kesha - RED FLAG. (Red Carpet) OFFICIAL MUSIC VIDEO</v>
       </c>
       <c r="B5" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=pvrJ5RnPAEA</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>3:41</v>
@@ -1389,7 +1389,7 @@
         <v>Katelyn Tarver - So Am I (Official Music Video)</v>
       </c>
       <c r="B27" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C27" t="str">
         <v>https://www.youtube.com/watch?v=MjUiVPzMQHw</v>
@@ -1401,7 +1401,7 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G27" t="str">
         <v>2:52</v>
@@ -1427,7 +1427,7 @@
         <v>David Guetta, TeddySwims, Tones And I - Gone Gone Gone (Unplugged) [Visualizer]</v>
       </c>
       <c r="B28" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=eWglDE7O5r8</v>
@@ -1439,7 +1439,7 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G28" t="str">
         <v>3:33</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Marc Anthony - Make It With You (Visualizer)</v>
       </c>
       <c r="B2" t="str">
-        <v>7 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=WHnz1jDrxw8</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>7 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>4:24</v>
@@ -477,7 +477,7 @@
         <v>Clara Mae - Never Been Yours ft. Bob John Holt</v>
       </c>
       <c r="B3" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=HtVuKBlBuPg</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>2:33</v>
@@ -515,7 +515,7 @@
         <v>Metric - Victim of Luck (Official Music Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=shmhTOUd8mA</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>3:25</v>
@@ -553,7 +553,7 @@
         <v>Kesha - RED FLAG. (Red Carpet) OFFICIAL MUSIC VIDEO</v>
       </c>
       <c r="B5" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=pvrJ5RnPAEA</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>3:41</v>
@@ -1047,7 +1047,7 @@
         <v>Jessie Ware - I Could Get Used To This (Live on The Graham Norton Show)</v>
       </c>
       <c r="B18" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=kGeamxRf8Gw</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G18" t="str">
         <v>3:50</v>
@@ -1313,7 +1313,7 @@
         <v>Zara Larsson - Lush Life (Official UGC Compilation Video)</v>
       </c>
       <c r="B25" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=FgAyfRnbbRs</v>
@@ -1325,7 +1325,7 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G25" t="str">
         <v>3:22</v>
@@ -1351,7 +1351,7 @@
         <v>Only The Poets - Monumental</v>
       </c>
       <c r="B26" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=nwXiAjjl6NE</v>
@@ -1363,7 +1363,7 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G26" t="str">
         <v>2:48</v>
@@ -2453,7 +2453,7 @@
         <v>We Three - Drunk Driving (Official Music Video)</v>
       </c>
       <c r="B55" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C55" t="str">
         <v>https://www.youtube.com/watch?v=BTqRGxSX6AQ</v>
@@ -2465,7 +2465,7 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G55" t="str">
         <v>4:27</v>
@@ -2871,7 +2871,7 @@
         <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
       </c>
       <c r="B66" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C66" t="str">
         <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
@@ -2883,7 +2883,7 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G66" t="str">
         <v>3:46</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Marc Anthony - Make It With You (Visualizer)</v>
       </c>
       <c r="B2" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=WHnz1jDrxw8</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>4:24</v>
@@ -477,7 +477,7 @@
         <v>Clara Mae - Never Been Yours ft. Bob John Holt</v>
       </c>
       <c r="B3" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=HtVuKBlBuPg</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>2:33</v>
@@ -515,7 +515,7 @@
         <v>Metric - Victim of Luck (Official Music Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=shmhTOUd8mA</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>3:25</v>
@@ -553,7 +553,7 @@
         <v>Kesha - RED FLAG. (Red Carpet) OFFICIAL MUSIC VIDEO</v>
       </c>
       <c r="B5" t="str">
-        <v>19 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=pvrJ5RnPAEA</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>19 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>3:41</v>
@@ -1275,7 +1275,7 @@
         <v>Paris Paloma - Good Girl [Official Music Video]</v>
       </c>
       <c r="B24" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=qhO6VMC-nx0</v>
@@ -1287,7 +1287,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G24" t="str">
         <v>4:47</v>
@@ -2754,7 +2754,7 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
+        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992</v>
       </c>
       <c r="B63" t="str">
         <v>11 days ago</v>
@@ -2787,7 +2787,7 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
+        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992 - OfficiallyExtreme</v>
       </c>
     </row>
     <row r="64">
@@ -2833,7 +2833,7 @@
         <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
       </c>
       <c r="B65" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C65" t="str">
         <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
@@ -2845,7 +2845,7 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G65" t="str">
         <v>2:56</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Marc Anthony - Make It With You (Visualizer)</v>
       </c>
       <c r="B2" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=WHnz1jDrxw8</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>4:24</v>
@@ -477,7 +477,7 @@
         <v>Clara Mae - Never Been Yours ft. Bob John Holt</v>
       </c>
       <c r="B3" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=HtVuKBlBuPg</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>2:33</v>
@@ -515,7 +515,7 @@
         <v>Metric - Victim of Luck (Official Music Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=shmhTOUd8mA</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>3:25</v>
@@ -553,7 +553,7 @@
         <v>Kesha - RED FLAG. (Red Carpet) OFFICIAL MUSIC VIDEO</v>
       </c>
       <c r="B5" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=pvrJ5RnPAEA</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>3:41</v>
@@ -2754,7 +2754,7 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
       </c>
       <c r="B63" t="str">
         <v>11 days ago</v>
@@ -2787,7 +2787,7 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992 - OfficiallyExtreme</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
       </c>
     </row>
     <row r="64">
@@ -2795,7 +2795,7 @@
         <v>Holly Humberstone - To Love Somebody (Official Video)</v>
       </c>
       <c r="B64" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C64" t="str">
         <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
@@ -2807,7 +2807,7 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G64" t="str">
         <v>3:59</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Marc Anthony - Make It With You (Visualizer)</v>
       </c>
       <c r="B2" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=WHnz1jDrxw8</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>4:24</v>
@@ -477,7 +477,7 @@
         <v>Clara Mae - Never Been Yours ft. Bob John Holt</v>
       </c>
       <c r="B3" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=HtVuKBlBuPg</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>2:33</v>
@@ -515,7 +515,7 @@
         <v>Metric - Victim of Luck (Official Music Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=shmhTOUd8mA</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>3:25</v>
@@ -553,7 +553,7 @@
         <v>Kesha - RED FLAG. (Red Carpet) OFFICIAL MUSIC VIDEO</v>
       </c>
       <c r="B5" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=pvrJ5RnPAEA</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>3:41</v>
@@ -1237,7 +1237,7 @@
         <v>The Kiffness &amp; Matisyahu - ONE DAY (ft. Andel and Nalyn) [OFFICIAL VIDEO]</v>
       </c>
       <c r="B23" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=buS21tVq5r0</v>
@@ -1249,7 +1249,7 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G23" t="str">
         <v>3:07</v>
@@ -3517,7 +3517,7 @@
         <v>Def Leppard - Rejoice (Lyric Video)</v>
       </c>
       <c r="B83" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C83" t="str">
         <v>https://www.youtube.com/watch?v=zy2TLLeNgp0</v>
@@ -3529,7 +3529,7 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G83" t="str">
         <v>4:21</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Marc Anthony - Make It With You (Visualizer)</v>
       </c>
       <c r="B2" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=WHnz1jDrxw8</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>4:24</v>
@@ -477,7 +477,7 @@
         <v>Clara Mae - Never Been Yours ft. Bob John Holt</v>
       </c>
       <c r="B3" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=HtVuKBlBuPg</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>2:33</v>
@@ -515,7 +515,7 @@
         <v>Metric - Victim of Luck (Official Music Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=shmhTOUd8mA</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>3:25</v>
@@ -553,7 +553,7 @@
         <v>Kesha - RED FLAG. (Red Carpet) OFFICIAL MUSIC VIDEO</v>
       </c>
       <c r="B5" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=pvrJ5RnPAEA</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>3:41</v>
@@ -1199,7 +1199,7 @@
         <v>The Cure - Boys Don't Cry (86 Mix) (Official Lyric Video)</v>
       </c>
       <c r="B22" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=isNztTjXQsQ</v>
@@ -1211,7 +1211,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G22" t="str">
         <v>2:39</v>
@@ -2491,7 +2491,7 @@
         <v>Timebelle - Top of the World (Mood Video)</v>
       </c>
       <c r="B56" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C56" t="str">
         <v>https://www.youtube.com/watch?v=r9KyYK_E34s</v>
@@ -2503,7 +2503,7 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G56" t="str">
         <v>3:01</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Marc Anthony - Make It With You (Visualizer)</v>
       </c>
       <c r="B2" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=WHnz1jDrxw8</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>4:24</v>
@@ -477,7 +477,7 @@
         <v>Clara Mae - Never Been Yours ft. Bob John Holt</v>
       </c>
       <c r="B3" t="str">
-        <v>19 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=HtVuKBlBuPg</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>19 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>2:33</v>
@@ -515,7 +515,7 @@
         <v>Metric - Victim of Luck (Official Music Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>19 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=shmhTOUd8mA</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>19 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>3:25</v>
@@ -553,7 +553,7 @@
         <v>Kesha - RED FLAG. (Red Carpet) OFFICIAL MUSIC VIDEO</v>
       </c>
       <c r="B5" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=pvrJ5RnPAEA</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G5" t="str">
         <v>3:41</v>
@@ -895,7 +895,7 @@
         <v>Nothing But Thieves - Sorry (Official Audio)</v>
       </c>
       <c r="B14" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=D7QfVqo5YqY</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G14" t="str">
         <v>3:37</v>
@@ -1123,7 +1123,7 @@
         <v>Dean Lewis - I Am Getting Well (Lyric Video)</v>
       </c>
       <c r="B20" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=6ecgOSOMWzc</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G20" t="str">
         <v>2:44</v>
@@ -1161,7 +1161,7 @@
         <v>Take That - Take That and Party (Official HD Video)</v>
       </c>
       <c r="B21" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=DAerJcerikU</v>
@@ -1173,7 +1173,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G21" t="str">
         <v>2:57</v>
@@ -2377,7 +2377,7 @@
         <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video)</v>
       </c>
       <c r="B53" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C53" t="str">
         <v>https://www.youtube.com/watch?v=yUAvfo8fpuU</v>
@@ -2389,7 +2389,7 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G53" t="str">
         <v>3:50</v>
@@ -2415,7 +2415,7 @@
         <v>I Had To Explain "How Music Works" LIVE In Concert</v>
       </c>
       <c r="B54" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C54" t="str">
         <v>https://www.youtube.com/watch?v=KnsBdAM3HqY</v>
@@ -2427,7 +2427,7 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G54" t="str">
         <v>5:32</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Marc Anthony - Make It With You (Visualizer)</v>
       </c>
       <c r="B2" t="str">
-        <v>13 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=WHnz1jDrxw8</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>13 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>4:24</v>
@@ -477,7 +477,7 @@
         <v>Clara Mae - Never Been Yours ft. Bob John Holt</v>
       </c>
       <c r="B3" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=HtVuKBlBuPg</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>2:33</v>
@@ -515,7 +515,7 @@
         <v>Metric - Victim of Luck (Official Music Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=shmhTOUd8mA</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>3:25</v>
@@ -1009,7 +1009,7 @@
         <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered)</v>
       </c>
       <c r="B17" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=I7a-pDZFE7U</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G17" t="str">
         <v>4:38</v>
@@ -1085,7 +1085,7 @@
         <v>JOSEPH - Water in the Room (Official Music Video)</v>
       </c>
       <c r="B19" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=tNmT47k6MjM</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G19" t="str">
         <v>3:10</v>
@@ -2187,7 +2187,7 @@
         <v>Beck - Love (Audio)</v>
       </c>
       <c r="B48" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C48" t="str">
         <v>https://www.youtube.com/watch?v=ByABj3Xof1I</v>
@@ -2199,7 +2199,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G48" t="str">
         <v>3:14</v>
@@ -2301,7 +2301,7 @@
         <v>Jason Derulo - Sexy For Me [Official Music Video]</v>
       </c>
       <c r="B51" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C51" t="str">
         <v>https://www.youtube.com/watch?v=9ST-eBNL0NU</v>
@@ -2313,7 +2313,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G51" t="str">
         <v>2:10</v>
@@ -2339,7 +2339,7 @@
         <v>Lights - COME GET YOUR GIRL</v>
       </c>
       <c r="B52" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C52" t="str">
         <v>https://www.youtube.com/watch?v=EhzX2y5MpSM</v>
@@ -2351,7 +2351,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G52" t="str">
         <v>3:52</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Marc Anthony - Make It With You (Visualizer)</v>
       </c>
       <c r="B2" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=WHnz1jDrxw8</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>4:24</v>
@@ -477,7 +477,7 @@
         <v>Clara Mae - Never Been Yours ft. Bob John Holt</v>
       </c>
       <c r="B3" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=HtVuKBlBuPg</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>2:33</v>
@@ -515,7 +515,7 @@
         <v>Metric - Victim of Luck (Official Music Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=shmhTOUd8mA</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>3:25</v>
@@ -819,7 +819,7 @@
         <v>Take That - Once You've Tasted Love (Live on Pebble Mill, 1992)</v>
       </c>
       <c r="B12" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=dOeoDOueESk</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G12" t="str">
         <v>3:36</v>
@@ -2149,7 +2149,7 @@
         <v>Teddy Swims - Need You More (Live - Green Room Sessions)</v>
       </c>
       <c r="B47" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C47" t="str">
         <v>https://www.youtube.com/watch?v=1ugf5aaY4pY</v>
@@ -2161,7 +2161,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G47" t="str">
         <v>3:16</v>
@@ -2263,7 +2263,7 @@
         <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show</v>
       </c>
       <c r="B50" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C50" t="str">
         <v>https://www.youtube.com/watch?v=ylifHFJWJ_c</v>
@@ -2275,7 +2275,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G50" t="str">
         <v>4:10</v>
@@ -2719,7 +2719,7 @@
         <v>Neal Francis - Back It Up (Live At The Salt Shed)</v>
       </c>
       <c r="B62" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C62" t="str">
         <v>https://www.youtube.com/watch?v=46iZEdsxjC0</v>
@@ -2731,7 +2731,7 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G62" t="str">
         <v>5:01</v>
@@ -2757,7 +2757,7 @@
         <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
       </c>
       <c r="B63" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C63" t="str">
         <v>https://www.youtube.com/watch?v=K2nG1Uukz7E</v>
@@ -2769,7 +2769,7 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G63" t="str">
         <v>4:12</v>
@@ -3479,7 +3479,7 @@
         <v>Lana Lubany - BAD IDEA (Official Video)</v>
       </c>
       <c r="B82" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C82" t="str">
         <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
@@ -3491,7 +3491,7 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G82" t="str">
         <v>2:59</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L206"/>
+  <dimension ref="A1:L207"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -439,7 +439,7 @@
         <v>Marc Anthony - Make It With You (Visualizer)</v>
       </c>
       <c r="B2" t="str">
-        <v>16 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=WHnz1jDrxw8</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>16 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>4:24</v>
@@ -477,7 +477,7 @@
         <v>Clara Mae - Never Been Yours ft. Bob John Holt</v>
       </c>
       <c r="B3" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=HtVuKBlBuPg</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G3" t="str">
         <v>2:33</v>
@@ -515,7 +515,7 @@
         <v>Metric - Victim of Luck (Official Music Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=shmhTOUd8mA</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G4" t="str">
         <v>3:25</v>
@@ -667,7 +667,7 @@
         <v>Bob Moses - Need You Tonight (INXS Cover) - Brooklyn Mirage 2023</v>
       </c>
       <c r="B8" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=CoCqPwDIBOA</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G8" t="str">
         <v>3:08</v>
@@ -705,7 +705,7 @@
         <v>Marc Anthony - Un Mal Sueño (Visualizer)</v>
       </c>
       <c r="B9" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=18yZq5xtke4</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G9" t="str">
         <v>3:28</v>
@@ -743,7 +743,7 @@
         <v>Marc Anthony - Contra La Corriente (Visualizer)</v>
       </c>
       <c r="B10" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=IGLmJ71oHhQ</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G10" t="str">
         <v>5:05</v>
@@ -781,7 +781,7 @@
         <v>Loreen - Feels Like Heaven</v>
       </c>
       <c r="B11" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=BQc97moyQBg</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G11" t="str">
         <v>3:14</v>
@@ -857,7 +857,7 @@
         <v>Paul McCartney, Wings - Nineteen Hundred And Eighty Five (Visualiser)</v>
       </c>
       <c r="B13" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=a4AIjUHuWpU</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G13" t="str">
         <v>5:31</v>
@@ -933,7 +933,7 @@
         <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music</v>
       </c>
       <c r="B15" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=KdsHxyl4bE8</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G15" t="str">
         <v>4:58</v>
@@ -971,7 +971,7 @@
         <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield, CA (2026)</v>
       </c>
       <c r="B16" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=Mwkl_Cz_SG8</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G16" t="str">
         <v>5:08</v>
@@ -2111,7 +2111,7 @@
         <v>Demi Lovato - Ghost (Live)</v>
       </c>
       <c r="B46" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=E-ECwdRndVA</v>
@@ -2123,7 +2123,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G46" t="str">
         <v>4:05</v>
@@ -2225,7 +2225,7 @@
         <v>The Offspring - Looking Out For #1 | Live in Spokane, WA (2026)</v>
       </c>
       <c r="B49" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C49" t="str">
         <v>https://www.youtube.com/watch?v=2HSbo51EFNg</v>
@@ -2237,7 +2237,7 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G49" t="str">
         <v>2:57</v>
@@ -2605,7 +2605,7 @@
         <v>SIENNA SPIRO - Die On This Hill (Official Music Video)</v>
       </c>
       <c r="B59" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C59" t="str">
         <v>https://www.youtube.com/watch?v=5RNy_1odv20</v>
@@ -2617,7 +2617,7 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G59" t="str">
         <v>4:01</v>
@@ -2643,7 +2643,7 @@
         <v>Amazon Music presents: Sienna Spiro - You Stole The Show</v>
       </c>
       <c r="B60" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C60" t="str">
         <v>https://www.youtube.com/watch?v=stYIRyCLN4Y</v>
@@ -2655,7 +2655,7 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G60" t="str">
         <v>3:24</v>
@@ -2681,7 +2681,7 @@
         <v>Harry Styles - Aperture (Official Video)</v>
       </c>
       <c r="B61" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C61" t="str">
         <v>https://www.youtube.com/watch?v=7sxVHYZ_PnA</v>
@@ -2693,7 +2693,7 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G61" t="str">
         <v>5:52</v>
@@ -3099,7 +3099,7 @@
         <v>Louis Tomlinson - Imposter (Official Video)</v>
       </c>
       <c r="B72" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C72" t="str">
         <v>https://www.youtube.com/watch?v=rzuD5szQhso</v>
@@ -3111,7 +3111,7 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G72" t="str">
         <v>2:56</v>
@@ -3555,7 +3555,7 @@
         <v>Dermot Kennedy - Funeral (Official Music Video)</v>
       </c>
       <c r="B84" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C84" t="str">
         <v>https://www.youtube.com/watch?v=JzOUJZPky6o</v>
@@ -3567,7 +3567,7 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G84" t="str">
         <v>4:09</v>
@@ -4236,13 +4236,13 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Penny in the Lake</v>
+        <v>golden boy</v>
       </c>
       <c r="B102" t="str">
         <v/>
       </c>
       <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/penny-in-the-lake/1844710053</v>
+        <v>https://music.apple.com/us/song/golden-boy/1872543012</v>
       </c>
       <c r="D102" t="str">
         <v>2026-02-04</v>
@@ -4251,25 +4251,25 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>Singin’ to an Empty Chair</v>
+        <v>stardust - EP</v>
       </c>
       <c r="G102" t="str">
-        <v>3:51</v>
+        <v>3:17</v>
       </c>
       <c r="H102" t="str">
-        <v>Ratboys</v>
+        <v>Freya Skye</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/ratboys/997909855</v>
+        <v>https://music.apple.com/us/artist/freya-skye/1541643053</v>
       </c>
       <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/penny-in-the-lake/1844710034</v>
+        <v>https://music.apple.com/us/album/golden-boy/1872542998</v>
       </c>
       <c r="L102" t="str">
-        <v>Penny in the Lake - Ratboys</v>
+        <v>golden boy - Freya Skye</v>
       </c>
     </row>
     <row r="103">
@@ -4540,13 +4540,13 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Heaven</v>
+        <v>Penny in the Lake</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/heaven/1862570892</v>
+        <v>https://music.apple.com/us/song/penny-in-the-lake/1844710053</v>
       </c>
       <c r="D110" t="str">
         <v>2026-02-04</v>
@@ -4555,25 +4555,25 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>Ambiguous Desire</v>
+        <v>Singin’ to an Empty Chair</v>
       </c>
       <c r="G110" t="str">
-        <v>4:26</v>
+        <v>3:51</v>
       </c>
       <c r="H110" t="str">
-        <v>Arlo Parks</v>
+        <v>Ratboys</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/arlo-parks/1291875084</v>
+        <v>https://music.apple.com/us/artist/ratboys/997909855</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/heaven/1862570378</v>
+        <v>https://music.apple.com/us/album/penny-in-the-lake/1844710034</v>
       </c>
       <c r="L110" t="str">
-        <v>Heaven - Arlo Parks</v>
+        <v>Penny in the Lake - Ratboys</v>
       </c>
     </row>
     <row r="111">
@@ -4616,13 +4616,13 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>McArthur</v>
+        <v>Heaven</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/mcarthur/1871231844</v>
+        <v>https://music.apple.com/us/song/heaven/1862570892</v>
       </c>
       <c r="D112" t="str">
         <v>2026-02-04</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>McArthur - Single</v>
+        <v>Ambiguous Desire</v>
       </c>
       <c r="G112" t="str">
-        <v>3:51</v>
+        <v>4:26</v>
       </c>
       <c r="H112" t="str">
-        <v>HARDY</v>
+        <v>Arlo Parks</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/hardy/1438874739</v>
+        <v>https://music.apple.com/us/artist/arlo-parks/1291875084</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/mcarthur/1871231823</v>
+        <v>https://music.apple.com/us/album/heaven/1862570378</v>
       </c>
       <c r="L112" t="str">
-        <v>McArthur - HARDY</v>
+        <v>Heaven - Arlo Parks</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Debris</v>
+        <v>McArthur</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/debris/1853069633</v>
+        <v>https://music.apple.com/us/song/mcarthur/1871231844</v>
       </c>
       <c r="D113" t="str">
         <v>2026-02-04</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>COSMIC OPERA ACT I</v>
+        <v>McArthur - Single</v>
       </c>
       <c r="G113" t="str">
-        <v>2:55</v>
+        <v>3:51</v>
       </c>
       <c r="H113" t="str">
-        <v>Labrinth</v>
+        <v>HARDY</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
+        <v>https://music.apple.com/us/artist/hardy/1438874739</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/debris/1853069628</v>
+        <v>https://music.apple.com/us/album/mcarthur/1871231823</v>
       </c>
       <c r="L113" t="str">
-        <v>Debris - Labrinth</v>
+        <v>McArthur - HARDY</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>God Owes Me Money (Live at Apple Music Radio)</v>
+        <v>Debris</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/god-owes-me-money-live-at-apple-music-radio/1871521120</v>
+        <v>https://music.apple.com/us/song/debris/1853069633</v>
       </c>
       <c r="D114" t="str">
         <v>2026-02-04</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>Throw Me Away / God Owes Me Money (Live at Apple Music Radio)</v>
+        <v>COSMIC OPERA ACT I</v>
       </c>
       <c r="G114" t="str">
-        <v>3:25</v>
+        <v>2:55</v>
       </c>
       <c r="H114" t="str">
-        <v>Militarie Gun</v>
+        <v>Labrinth</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/militarie-gun/1529039426</v>
+        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/god-owes-me-money-live-at-apple-music-radio/1871520929</v>
+        <v>https://music.apple.com/us/album/debris/1853069628</v>
       </c>
       <c r="L114" t="str">
-        <v>God Owes Me Money (Live at Apple Music Radio) - Militarie Gun</v>
+        <v>Debris - Labrinth</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>ROCKSTAR RAGING (feat. Swae Lee)</v>
+        <v>God Owes Me Money (Live at Apple Music Radio)</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/rockstar-raging-feat-swae-lee/1873028187</v>
+        <v>https://music.apple.com/us/song/god-owes-me-money-live-at-apple-music-radio/1871521120</v>
       </c>
       <c r="D115" t="str">
         <v>2026-02-04</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>ROCKSTAR RAGING (feat. Swae Lee) - Single</v>
+        <v>Throw Me Away / God Owes Me Money (Live at Apple Music Radio)</v>
       </c>
       <c r="G115" t="str">
-        <v>4:38</v>
+        <v>3:25</v>
       </c>
       <c r="H115" t="str">
-        <v>Mike WiLL Made-It</v>
+        <v>Militarie Gun</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/mike-will-made-it/511333957</v>
+        <v>https://music.apple.com/us/artist/militarie-gun/1529039426</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/rockstar-raging-feat-swae-lee/1873028186</v>
+        <v>https://music.apple.com/us/album/god-owes-me-money-live-at-apple-music-radio/1871520929</v>
       </c>
       <c r="L115" t="str">
-        <v>ROCKSTAR RAGING (feat. Swae Lee) - Mike WiLL Made-It</v>
+        <v>God Owes Me Money (Live at Apple Music Radio) - Militarie Gun</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>1+1</v>
+        <v>ROCKSTAR RAGING (feat. Swae Lee)</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/1-1/1870378316</v>
+        <v>https://music.apple.com/us/song/rockstar-raging-feat-swae-lee/1873028187</v>
       </c>
       <c r="D116" t="str">
         <v>2026-02-04</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>1+1 - Single</v>
+        <v>ROCKSTAR RAGING (feat. Swae Lee) - Single</v>
       </c>
       <c r="G116" t="str">
-        <v>3:06</v>
+        <v>4:38</v>
       </c>
       <c r="H116" t="str">
-        <v>Maluma</v>
+        <v>Mike WiLL Made-It</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/maluma/448916501</v>
+        <v>https://music.apple.com/us/artist/mike-will-made-it/511333957</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/1-1/1870378315</v>
+        <v>https://music.apple.com/us/album/rockstar-raging-feat-swae-lee/1873028186</v>
       </c>
       <c r="L116" t="str">
-        <v>1+1 - Maluma</v>
+        <v>ROCKSTAR RAGING (feat. Swae Lee) - Mike WiLL Made-It</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Still Sincere (feat. PinkPantheress)</v>
+        <v>1+1</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/still-sincere-feat-pinkpantheress/1862228374</v>
+        <v>https://music.apple.com/us/song/1-1/1870378316</v>
       </c>
       <c r="D117" t="str">
         <v>2026-02-04</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>Still Sincere (feat. PinkPantheress) - Single</v>
+        <v>1+1 - Single</v>
       </c>
       <c r="G117" t="str">
-        <v>3:08</v>
+        <v>3:06</v>
       </c>
       <c r="H117" t="str">
-        <v>MJ Cole</v>
+        <v>Maluma</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/mj-cole/405892</v>
+        <v>https://music.apple.com/us/artist/maluma/448916501</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/still-sincere-feat-pinkpantheress/1862228373</v>
+        <v>https://music.apple.com/us/album/1-1/1870378315</v>
       </c>
       <c r="L117" t="str">
-        <v>Still Sincere (feat. PinkPantheress) - MJ Cole</v>
+        <v>1+1 - Maluma</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Two Car Garage</v>
+        <v>Still Sincere (feat. PinkPantheress)</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/two-car-garage/1869137588</v>
+        <v>https://music.apple.com/us/song/still-sincere-feat-pinkpantheress/1862228374</v>
       </c>
       <c r="D118" t="str">
         <v>2026-02-04</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>Two Car Garage - Single</v>
+        <v>Still Sincere (feat. PinkPantheress) - Single</v>
       </c>
       <c r="G118" t="str">
-        <v>3:02</v>
+        <v>3:08</v>
       </c>
       <c r="H118" t="str">
-        <v>Jon Bellion</v>
+        <v>MJ Cole</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/jon-bellion/659289673</v>
+        <v>https://music.apple.com/us/artist/mj-cole/405892</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/two-car-garage/1869137587</v>
+        <v>https://music.apple.com/us/album/still-sincere-feat-pinkpantheress/1862228373</v>
       </c>
       <c r="L118" t="str">
-        <v>Two Car Garage - Jon Bellion</v>
+        <v>Still Sincere (feat. PinkPantheress) - MJ Cole</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>fml .</v>
+        <v>Two Car Garage</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/fml/1872686260</v>
+        <v>https://music.apple.com/us/song/two-car-garage/1869137588</v>
       </c>
       <c r="D119" t="str">
         <v>2026-02-04</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>The Boy who cried Terrified .</v>
+        <v>Two Car Garage - Single</v>
       </c>
       <c r="G119" t="str">
-        <v>2:40</v>
+        <v>3:02</v>
       </c>
       <c r="H119" t="str">
-        <v>fakemink</v>
+        <v>Jon Bellion</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/fakemink/1744500063</v>
+        <v>https://music.apple.com/us/artist/jon-bellion/659289673</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/fml/1872686249</v>
+        <v>https://music.apple.com/us/album/two-car-garage/1869137587</v>
       </c>
       <c r="L119" t="str">
-        <v>fml . - fakemink</v>
+        <v>Two Car Garage - Jon Bellion</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Faked It All The Time</v>
+        <v>fml .</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/faked-it-all-the-time/1871050032</v>
+        <v>https://music.apple.com/us/song/fml/1872686260</v>
       </c>
       <c r="D120" t="str">
         <v>2026-02-04</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Faked It All The Time - Single</v>
+        <v>The Boy who cried Terrified .</v>
       </c>
       <c r="G120" t="str">
-        <v>3:01</v>
+        <v>2:40</v>
       </c>
       <c r="H120" t="str">
-        <v>Allie Sherlock</v>
+        <v>fakemink</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/allie-sherlock/1314464325</v>
+        <v>https://music.apple.com/us/artist/fakemink/1744500063</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/faked-it-all-the-time/1871050031</v>
+        <v>https://music.apple.com/us/album/fml/1872686249</v>
       </c>
       <c r="L120" t="str">
-        <v>Faked It All The Time - Allie Sherlock</v>
+        <v>fml . - fakemink</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>House of the Rising Sun</v>
+        <v>Faked It All The Time</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/house-of-the-rising-sun/1872111857</v>
+        <v>https://music.apple.com/us/song/faked-it-all-the-time/1871050032</v>
       </c>
       <c r="D121" t="str">
         <v>2026-02-04</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>House of the Rising Sun - Single</v>
+        <v>Faked It All The Time - Single</v>
       </c>
       <c r="G121" t="str">
-        <v>3:08</v>
+        <v>3:01</v>
       </c>
       <c r="H121" t="str">
-        <v>Lizzy McAlpine</v>
+        <v>Allie Sherlock</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/lizzy-mcalpine/1350245112</v>
+        <v>https://music.apple.com/us/artist/allie-sherlock/1314464325</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/house-of-the-rising-sun/1872111734</v>
+        <v>https://music.apple.com/us/album/faked-it-all-the-time/1871050031</v>
       </c>
       <c r="L121" t="str">
-        <v>House of the Rising Sun - Lizzy McAlpine</v>
+        <v>Faked It All The Time - Allie Sherlock</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Lorelei</v>
+        <v>House of the Rising Sun</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/lorelei/1867640808</v>
+        <v>https://music.apple.com/us/song/house-of-the-rising-sun/1872111857</v>
       </c>
       <c r="D122" t="str">
         <v>2026-02-04</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Lorelei - Single</v>
+        <v>House of the Rising Sun - Single</v>
       </c>
       <c r="G122" t="str">
-        <v>2:35</v>
+        <v>3:08</v>
       </c>
       <c r="H122" t="str">
-        <v>ERNEST</v>
+        <v>Lizzy McAlpine</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
+        <v>https://music.apple.com/us/artist/lizzy-mcalpine/1350245112</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/lorelei/1867640583</v>
+        <v>https://music.apple.com/us/album/house-of-the-rising-sun/1872111734</v>
       </c>
       <c r="L122" t="str">
-        <v>Lorelei - ERNEST</v>
+        <v>House of the Rising Sun - Lizzy McAlpine</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Free</v>
+        <v>Lorelei</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/free/1870703329</v>
+        <v>https://music.apple.com/us/song/lorelei/1867640808</v>
       </c>
       <c r="D123" t="str">
         <v>2026-02-04</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>Free - Single</v>
+        <v>Lorelei - Single</v>
       </c>
       <c r="G123" t="str">
-        <v>3:56</v>
+        <v>2:35</v>
       </c>
       <c r="H123" t="str">
-        <v>SLANDER</v>
+        <v>ERNEST</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/slander/1051421487</v>
+        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/free/1870703327</v>
+        <v>https://music.apple.com/us/album/lorelei/1867640583</v>
       </c>
       <c r="L123" t="str">
-        <v>Free - SLANDER</v>
+        <v>Lorelei - ERNEST</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>ASSIGNMENT</v>
+        <v>Free</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/assignment/1872764440</v>
+        <v>https://music.apple.com/us/song/free/1870703329</v>
       </c>
       <c r="D124" t="str">
         <v>2026-02-04</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>ASSIGNMENT - Single</v>
+        <v>Free - Single</v>
       </c>
       <c r="G124" t="str">
-        <v>2:23</v>
+        <v>3:56</v>
       </c>
       <c r="H124" t="str">
-        <v>Power Snatch</v>
+        <v>SLANDER</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/power-snatch/1872764439</v>
+        <v>https://music.apple.com/us/artist/slander/1051421487</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/assignment/1872764438</v>
+        <v>https://music.apple.com/us/album/free/1870703327</v>
       </c>
       <c r="L124" t="str">
-        <v>ASSIGNMENT - Power Snatch</v>
+        <v>Free - SLANDER</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>professional heartbreaker</v>
+        <v>ASSIGNMENT</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/professional-heartbreaker/1871053476</v>
+        <v>https://music.apple.com/us/song/assignment/1872764440</v>
       </c>
       <c r="D125" t="str">
         <v>2026-02-04</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>professional heartbreaker - Single</v>
+        <v>ASSIGNMENT - Single</v>
       </c>
       <c r="G125" t="str">
-        <v>2:55</v>
+        <v>2:23</v>
       </c>
       <c r="H125" t="str">
-        <v>Artemas</v>
+        <v>Power Snatch</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
+        <v>https://music.apple.com/us/artist/power-snatch/1872764439</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/professional-heartbreaker/1871053473</v>
+        <v>https://music.apple.com/us/album/assignment/1872764438</v>
       </c>
       <c r="L125" t="str">
-        <v>professional heartbreaker - Artemas</v>
+        <v>ASSIGNMENT - Power Snatch</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>tell me what you want</v>
+        <v>professional heartbreaker</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/tell-me-what-you-want/1871463892</v>
+        <v>https://music.apple.com/us/song/professional-heartbreaker/1871053476</v>
       </c>
       <c r="D126" t="str">
         <v>2026-02-04</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>ACT II</v>
+        <v>professional heartbreaker - Single</v>
       </c>
       <c r="G126" t="str">
-        <v>3:56</v>
+        <v>2:55</v>
       </c>
       <c r="H126" t="str">
-        <v>Sasha Keable</v>
+        <v>Artemas</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/sasha-keable/325850892</v>
+        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/tell-me-what-you-want/1871463550</v>
+        <v>https://music.apple.com/us/album/professional-heartbreaker/1871053473</v>
       </c>
       <c r="L126" t="str">
-        <v>tell me what you want - Sasha Keable</v>
+        <v>professional heartbreaker - Artemas</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Aguas</v>
+        <v>tell me what you want</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/aguas/1869455857</v>
+        <v>https://music.apple.com/us/song/tell-me-what-you-want/1871463892</v>
       </c>
       <c r="D127" t="str">
         <v>2026-02-04</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>Aguas - Single</v>
+        <v>ACT II</v>
       </c>
       <c r="G127" t="str">
-        <v>2:52</v>
+        <v>3:56</v>
       </c>
       <c r="H127" t="str">
-        <v>Luis R Conriquez</v>
+        <v>Sasha Keable</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
+        <v>https://music.apple.com/us/artist/sasha-keable/325850892</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/aguas/1869455582</v>
+        <v>https://music.apple.com/us/album/tell-me-what-you-want/1871463550</v>
       </c>
       <c r="L127" t="str">
-        <v>Aguas - Luis R Conriquez</v>
+        <v>tell me what you want - Sasha Keable</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Ants In My Room</v>
+        <v>Aguas</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/ants-in-my-room/1870967813</v>
+        <v>https://music.apple.com/us/song/aguas/1869455857</v>
       </c>
       <c r="D128" t="str">
         <v>2026-02-04</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>Ants In My Room - Single</v>
+        <v>Aguas - Single</v>
       </c>
       <c r="G128" t="str">
-        <v>2:48</v>
+        <v>2:52</v>
       </c>
       <c r="H128" t="str">
-        <v>Carter Vail</v>
+        <v>Luis R Conriquez</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/carter-vail/1102115053</v>
+        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/ants-in-my-room/1870967810</v>
+        <v>https://music.apple.com/us/album/aguas/1869455582</v>
       </c>
       <c r="L128" t="str">
-        <v>Ants In My Room - Carter Vail</v>
+        <v>Aguas - Luis R Conriquez</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Baddie</v>
+        <v>Ants In My Room</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/baddie/1849760827</v>
+        <v>https://music.apple.com/us/song/ants-in-my-room/1870967813</v>
       </c>
       <c r="D129" t="str">
         <v>2026-02-04</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>Bohemio</v>
+        <v>Ants In My Room - Single</v>
       </c>
       <c r="G129" t="str">
-        <v>3:11</v>
+        <v>2:48</v>
       </c>
       <c r="H129" t="str">
-        <v>Nicky Jam</v>
+        <v>Carter Vail</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/nicky-jam/33987470</v>
+        <v>https://music.apple.com/us/artist/carter-vail/1102115053</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/baddie/1849760822</v>
+        <v>https://music.apple.com/us/album/ants-in-my-room/1870967810</v>
       </c>
       <c r="L129" t="str">
-        <v>Baddie - Nicky Jam</v>
+        <v>Ants In My Room - Carter Vail</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>What You Need - A COLORS SHOW</v>
+        <v>Baddie</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/what-you-need-a-colors-show/1870990925</v>
+        <v>https://music.apple.com/us/song/baddie/1849760827</v>
       </c>
       <c r="D130" t="str">
         <v>2026-02-04</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>What You Need - A COLORS SHOW - Single</v>
+        <v>Bohemio</v>
       </c>
       <c r="G130" t="str">
-        <v>3:51</v>
+        <v>3:11</v>
       </c>
       <c r="H130" t="str">
-        <v>Tems</v>
+        <v>Nicky Jam</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/tems/1413909060</v>
+        <v>https://music.apple.com/us/artist/nicky-jam/33987470</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/what-you-need-a-colors-show/1870990923</v>
+        <v>https://music.apple.com/us/album/baddie/1849760822</v>
       </c>
       <c r="L130" t="str">
-        <v>What You Need - A COLORS SHOW - Tems</v>
+        <v>Baddie - Nicky Jam</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>OK OK (Hamdi remix)</v>
+        <v>What You Need - A COLORS SHOW</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/ok-ok-hamdi-remix/1871538130</v>
+        <v>https://music.apple.com/us/song/what-you-need-a-colors-show/1870990925</v>
       </c>
       <c r="D131" t="str">
         <v>2026-02-04</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>OK OK (Hamdi remix) - Single</v>
+        <v>What You Need - A COLORS SHOW - Single</v>
       </c>
       <c r="G131" t="str">
-        <v>3:16</v>
+        <v>3:51</v>
       </c>
       <c r="H131" t="str">
-        <v>Fred again..</v>
+        <v>Tems</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
+        <v>https://music.apple.com/us/artist/tems/1413909060</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/ok-ok-hamdi-remix/1871538128</v>
+        <v>https://music.apple.com/us/album/what-you-need-a-colors-show/1870990923</v>
       </c>
       <c r="L131" t="str">
-        <v>OK OK (Hamdi remix) - Fred again..</v>
+        <v>What You Need - A COLORS SHOW - Tems</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Ever and Ever Before (feat. MŌRIAH &amp; Courtney)</v>
+        <v>OK OK (Hamdi remix)</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/ever-and-ever-before-feat-m%C5%8Driah-courtney/1869383260</v>
+        <v>https://music.apple.com/us/song/ok-ok-hamdi-remix/1871538130</v>
       </c>
       <c r="D132" t="str">
         <v>2026-02-04</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>Ever and Ever Before (feat. MŌRIAH &amp; Courtney) - Single</v>
+        <v>OK OK (Hamdi remix) - Single</v>
       </c>
       <c r="G132" t="str">
-        <v>3:50</v>
+        <v>3:16</v>
       </c>
       <c r="H132" t="str">
-        <v>for KING &amp; COUNTRY</v>
+        <v>Fred again..</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/for-king-country/457871289</v>
+        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/ever-and-ever-before-feat-m%C5%8Driah-courtney/1869383258</v>
+        <v>https://music.apple.com/us/album/ok-ok-hamdi-remix/1871538128</v>
       </c>
       <c r="L132" t="str">
-        <v>Ever and Ever Before (feat. MŌRIAH &amp; Courtney) - for KING &amp; COUNTRY</v>
+        <v>OK OK (Hamdi remix) - Fred again..</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>For The First Time, Again</v>
+        <v>Ever and Ever Before (feat. MŌRIAH &amp; Courtney)</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/for-the-first-time-again/1834736723</v>
+        <v>https://music.apple.com/us/song/ever-and-ever-before-feat-m%C5%8Driah-courtney/1869383260</v>
       </c>
       <c r="D133" t="str">
         <v>2026-02-04</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>For The First Time, Again</v>
+        <v>Ever and Ever Before (feat. MŌRIAH &amp; Courtney) - Single</v>
       </c>
       <c r="G133" t="str">
-        <v>3:33</v>
+        <v>3:50</v>
       </c>
       <c r="H133" t="str">
-        <v>Tyler Ballgame</v>
+        <v>for KING &amp; COUNTRY</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/tyler-ballgame/1755347001</v>
+        <v>https://music.apple.com/us/artist/for-king-country/457871289</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/for-the-first-time-again/1834736717</v>
+        <v>https://music.apple.com/us/album/ever-and-ever-before-feat-m%C5%8Driah-courtney/1869383258</v>
       </c>
       <c r="L133" t="str">
-        <v>For The First Time, Again - Tyler Ballgame</v>
+        <v>Ever and Ever Before (feat. MŌRIAH &amp; Courtney) - for KING &amp; COUNTRY</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Liars Tale</v>
+        <v>For The First Time, Again</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/liars-tale/1862207951</v>
+        <v>https://music.apple.com/us/song/for-the-first-time-again/1834736723</v>
       </c>
       <c r="D134" t="str">
         <v>2026-02-04</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>Liars Tale - Single</v>
+        <v>For The First Time, Again</v>
       </c>
       <c r="G134" t="str">
-        <v>3:17</v>
+        <v>3:33</v>
       </c>
       <c r="H134" t="str">
-        <v>Kneecap</v>
+        <v>Tyler Ballgame</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
+        <v>https://music.apple.com/us/artist/tyler-ballgame/1755347001</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/liars-tale/1862207946</v>
+        <v>https://music.apple.com/us/album/for-the-first-time-again/1834736717</v>
       </c>
       <c r="L134" t="str">
-        <v>Liars Tale - Kneecap</v>
+        <v>For The First Time, Again - Tyler Ballgame</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Afraid Of The Dark</v>
+        <v>Liars Tale</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/afraid-of-the-dark/1872184048</v>
+        <v>https://music.apple.com/us/song/liars-tale/1862207951</v>
       </c>
       <c r="D135" t="str">
         <v>2026-02-04</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>Afraid Of The Dark - Single</v>
+        <v>Liars Tale - Single</v>
       </c>
       <c r="G135" t="str">
-        <v>4:38</v>
+        <v>3:17</v>
       </c>
       <c r="H135" t="str">
-        <v>Motionless In White</v>
+        <v>Kneecap</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/motionless-in-white/266666216</v>
+        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/afraid-of-the-dark/1872184047</v>
+        <v>https://music.apple.com/us/album/liars-tale/1862207946</v>
       </c>
       <c r="L135" t="str">
-        <v>Afraid Of The Dark - Motionless In White</v>
+        <v>Liars Tale - Kneecap</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Wake Up Calling</v>
+        <v>Afraid Of The Dark</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/wake-up-calling/1862338150</v>
+        <v>https://music.apple.com/us/song/afraid-of-the-dark/1872184048</v>
       </c>
       <c r="D136" t="str">
         <v>2026-02-04</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>Wake Up Calling - Single</v>
+        <v>Afraid Of The Dark - Single</v>
       </c>
       <c r="G136" t="str">
-        <v>3:49</v>
+        <v>4:38</v>
       </c>
       <c r="H136" t="str">
-        <v>Papa Roach</v>
+        <v>Motionless In White</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/papa-roach/3445763</v>
+        <v>https://music.apple.com/us/artist/motionless-in-white/266666216</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/wake-up-calling/1862338148</v>
+        <v>https://music.apple.com/us/album/afraid-of-the-dark/1872184047</v>
       </c>
       <c r="L136" t="str">
-        <v>Wake Up Calling - Papa Roach</v>
+        <v>Afraid Of The Dark - Motionless In White</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>HIGH</v>
+        <v>Wake Up Calling</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/high/1867202644</v>
+        <v>https://music.apple.com/us/song/wake-up-calling/1862338150</v>
       </c>
       <c r="D137" t="str">
         <v>2026-02-04</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>NIGHTS AFTER VAMP</v>
+        <v>Wake Up Calling - Single</v>
       </c>
       <c r="G137" t="str">
-        <v>3:23</v>
+        <v>3:49</v>
       </c>
       <c r="H137" t="str">
-        <v>Magnolia Park</v>
+        <v>Papa Roach</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/magnolia-park/1413545983</v>
+        <v>https://music.apple.com/us/artist/papa-roach/3445763</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/high/1867202638</v>
+        <v>https://music.apple.com/us/album/wake-up-calling/1862338148</v>
       </c>
       <c r="L137" t="str">
-        <v>HIGH - Magnolia Park</v>
+        <v>Wake Up Calling - Papa Roach</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Villain</v>
+        <v>HIGH</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/villain/1860126455</v>
+        <v>https://music.apple.com/us/song/high/1867202644</v>
       </c>
       <c r="D138" t="str">
         <v>2026-02-04</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>Reflections</v>
+        <v>NIGHTS AFTER VAMP</v>
       </c>
       <c r="G138" t="str">
-        <v>3:53</v>
+        <v>3:23</v>
       </c>
       <c r="H138" t="str">
-        <v>From Ashes to New</v>
+        <v>Magnolia Park</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/from-ashes-to-new/688645097</v>
+        <v>https://music.apple.com/us/artist/magnolia-park/1413545983</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/villain/1860126452</v>
+        <v>https://music.apple.com/us/album/high/1867202638</v>
       </c>
       <c r="L138" t="str">
-        <v>Villain - From Ashes to New</v>
+        <v>HIGH - Magnolia Park</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Bad Idea Right?</v>
+        <v>Villain</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/bad-idea-right/1869792549</v>
+        <v>https://music.apple.com/us/song/villain/1860126455</v>
       </c>
       <c r="D139" t="str">
         <v>2026-02-04</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>Bridgerton Season Four (Covers from the Netflix Series – Pt. 1) - EP</v>
+        <v>Reflections</v>
       </c>
       <c r="G139" t="str">
-        <v>3:00</v>
+        <v>3:53</v>
       </c>
       <c r="H139" t="str">
-        <v>Caleb Chan</v>
+        <v>From Ashes to New</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/caleb-chan/1441662972</v>
+        <v>https://music.apple.com/us/artist/from-ashes-to-new/688645097</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/bad-idea-right/1869792542</v>
+        <v>https://music.apple.com/us/album/villain/1860126452</v>
       </c>
       <c r="L139" t="str">
-        <v>Bad Idea Right? - Caleb Chan</v>
+        <v>Villain - From Ashes to New</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Residue</v>
+        <v>Bad Idea Right?</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/residue/1863786787</v>
+        <v>https://music.apple.com/us/song/bad-idea-right/1869792549</v>
       </c>
       <c r="D140" t="str">
         <v>2026-02-04</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>The Moment (The Score)</v>
+        <v>Bridgerton Season Four (Covers from the Netflix Series – Pt. 1) - EP</v>
       </c>
       <c r="G140" t="str">
-        <v>3:28</v>
+        <v>3:00</v>
       </c>
       <c r="H140" t="str">
-        <v>A. G. Cook</v>
+        <v>Caleb Chan</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/a-g-cook/744253464</v>
+        <v>https://music.apple.com/us/artist/caleb-chan/1441662972</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/residue/1863786786</v>
+        <v>https://music.apple.com/us/album/bad-idea-right/1869792542</v>
       </c>
       <c r="L140" t="str">
-        <v>Residue - A. G. Cook</v>
+        <v>Bad Idea Right? - Caleb Chan</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>I Used to Go to This Bar</v>
+        <v>Residue</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/i-used-to-go-to-this-bar/1839918872</v>
+        <v>https://music.apple.com/us/song/residue/1863786787</v>
       </c>
       <c r="D141" t="str">
         <v>2026-02-04</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>I Used to Go to This Bar</v>
+        <v>The Moment (The Score)</v>
       </c>
       <c r="G141" t="str">
-        <v>2:12</v>
+        <v>3:28</v>
       </c>
       <c r="H141" t="str">
-        <v>Joyce Manor</v>
+        <v>A. G. Cook</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/joyce-manor/408598559</v>
+        <v>https://music.apple.com/us/artist/a-g-cook/744253464</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/i-used-to-go-to-this-bar/1839918836</v>
+        <v>https://music.apple.com/us/album/residue/1863786786</v>
       </c>
       <c r="L141" t="str">
-        <v>I Used to Go to This Bar - Joyce Manor</v>
+        <v>Residue - A. G. Cook</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Starlight</v>
+        <v>I Used to Go to This Bar</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/starlight/1870989674</v>
+        <v>https://music.apple.com/us/song/i-used-to-go-to-this-bar/1839918872</v>
       </c>
       <c r="D142" t="str">
         <v>2026-02-04</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Everything Glows</v>
+        <v>I Used to Go to This Bar</v>
       </c>
       <c r="G142" t="str">
-        <v>3:21</v>
+        <v>2:12</v>
       </c>
       <c r="H142" t="str">
-        <v>Cannons</v>
+        <v>Joyce Manor</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/cannons/65568551</v>
+        <v>https://music.apple.com/us/artist/joyce-manor/408598559</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/starlight/1870989672</v>
+        <v>https://music.apple.com/us/album/i-used-to-go-to-this-bar/1839918836</v>
       </c>
       <c r="L142" t="str">
-        <v>Starlight - Cannons</v>
+        <v>I Used to Go to This Bar - Joyce Manor</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Dandelion</v>
+        <v>Starlight</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/dandelion/1863154133</v>
+        <v>https://music.apple.com/us/song/starlight/1870989674</v>
       </c>
       <c r="D143" t="str">
         <v>2026-02-04</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>Corporate Pudding - EP</v>
+        <v>Everything Glows</v>
       </c>
       <c r="G143" t="str">
-        <v>3:14</v>
+        <v>3:21</v>
       </c>
       <c r="H143" t="str">
-        <v>Dogpark</v>
+        <v>Cannons</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/dogpark/1710263796</v>
+        <v>https://music.apple.com/us/artist/cannons/65568551</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/dandelion/1863154124</v>
+        <v>https://music.apple.com/us/album/starlight/1870989672</v>
       </c>
       <c r="L143" t="str">
-        <v>Dandelion - Dogpark</v>
+        <v>Starlight - Cannons</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>THEMSELVES</v>
+        <v>Dandelion</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/themselves/1845287173</v>
+        <v>https://music.apple.com/us/song/dandelion/1863154133</v>
       </c>
       <c r="D144" t="str">
         <v>2026-02-04</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>BACKWARD</v>
+        <v>Corporate Pudding - EP</v>
       </c>
       <c r="G144" t="str">
-        <v>2:46</v>
+        <v>3:14</v>
       </c>
       <c r="H144" t="str">
-        <v>Jordan Ward</v>
+        <v>Dogpark</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/jordan-ward/689602960</v>
+        <v>https://music.apple.com/us/artist/dogpark/1710263796</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/themselves/1845286980</v>
+        <v>https://music.apple.com/us/album/dandelion/1863154124</v>
       </c>
       <c r="L144" t="str">
-        <v>THEMSELVES - Jordan Ward</v>
+        <v>Dandelion - Dogpark</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>High Maintenance</v>
+        <v>THEMSELVES</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/high-maintenance/1872497656</v>
+        <v>https://music.apple.com/us/song/themselves/1845287173</v>
       </c>
       <c r="D145" t="str">
         <v>2026-02-04</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Miracle Mile</v>
+        <v>BACKWARD</v>
       </c>
       <c r="G145" t="str">
-        <v>2:24</v>
+        <v>2:46</v>
       </c>
       <c r="H145" t="str">
-        <v>Paul Russell</v>
+        <v>Jordan Ward</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/paul-russell/1304377463</v>
+        <v>https://music.apple.com/us/artist/jordan-ward/689602960</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/high-maintenance/1872496993</v>
+        <v>https://music.apple.com/us/album/themselves/1845286980</v>
       </c>
       <c r="L145" t="str">
-        <v>High Maintenance - Paul Russell</v>
+        <v>THEMSELVES - Jordan Ward</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Trackhawk</v>
+        <v>High Maintenance</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/trackhawk/1860991724</v>
+        <v>https://music.apple.com/us/song/high-maintenance/1872497656</v>
       </c>
       <c r="D146" t="str">
         <v>2026-02-04</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>Da Realest</v>
+        <v>Miracle Mile</v>
       </c>
       <c r="G146" t="str">
-        <v>1:59</v>
+        <v>2:24</v>
       </c>
       <c r="H146" t="str">
-        <v>Babyfxce E</v>
+        <v>Paul Russell</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/babyfxce-e/1573432856</v>
+        <v>https://music.apple.com/us/artist/paul-russell/1304377463</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/trackhawk/1860991661</v>
+        <v>https://music.apple.com/us/album/high-maintenance/1872496993</v>
       </c>
       <c r="L146" t="str">
-        <v>Trackhawk - Babyfxce E</v>
+        <v>High Maintenance - Paul Russell</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Wheel Man</v>
+        <v>Trackhawk</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/wheel-man/1872178895</v>
+        <v>https://music.apple.com/us/song/trackhawk/1860991724</v>
       </c>
       <c r="D147" t="str">
         <v>2026-02-04</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Xavier</v>
+        <v>Da Realest</v>
       </c>
       <c r="G147" t="str">
-        <v>3:05</v>
+        <v>1:59</v>
       </c>
       <c r="H147" t="str">
-        <v>xaviersobased</v>
+        <v>Babyfxce E</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/xaviersobased/1540848340</v>
+        <v>https://music.apple.com/us/artist/babyfxce-e/1573432856</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/wheel-man/1872178596</v>
+        <v>https://music.apple.com/us/album/trackhawk/1860991661</v>
       </c>
       <c r="L147" t="str">
-        <v>Wheel Man - xaviersobased</v>
+        <v>Trackhawk - Babyfxce E</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Natural Disaster</v>
+        <v>Wheel Man</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/natural-disaster/1871263211</v>
+        <v>https://music.apple.com/us/song/wheel-man/1872178895</v>
       </c>
       <c r="D148" t="str">
         <v>2026-02-04</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Natural Disaster - Single</v>
+        <v>Xavier</v>
       </c>
       <c r="G148" t="str">
-        <v>3:02</v>
+        <v>3:05</v>
       </c>
       <c r="H148" t="str">
-        <v>Lauren Spencer Smith</v>
+        <v>xaviersobased</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/lauren-spencer-smith/1462708784</v>
+        <v>https://music.apple.com/us/artist/xaviersobased/1540848340</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/natural-disaster/1871263207</v>
+        <v>https://music.apple.com/us/album/wheel-man/1872178596</v>
       </c>
       <c r="L148" t="str">
-        <v>Natural Disaster - Lauren Spencer Smith</v>
+        <v>Wheel Man - xaviersobased</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Prettier</v>
+        <v>Natural Disaster</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/prettier/1869745409</v>
+        <v>https://music.apple.com/us/song/natural-disaster/1871263211</v>
       </c>
       <c r="D149" t="str">
         <v>2026-02-04</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>Prettier - Single</v>
+        <v>Natural Disaster - Single</v>
       </c>
       <c r="G149" t="str">
-        <v>2:34</v>
+        <v>3:02</v>
       </c>
       <c r="H149" t="str">
-        <v>Grace VanderWaal</v>
+        <v>Lauren Spencer Smith</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/grace-vanderwaal/1175539534</v>
+        <v>https://music.apple.com/us/artist/lauren-spencer-smith/1462708784</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/prettier/1869745403</v>
+        <v>https://music.apple.com/us/album/natural-disaster/1871263207</v>
       </c>
       <c r="L149" t="str">
-        <v>Prettier - Grace VanderWaal</v>
+        <v>Natural Disaster - Lauren Spencer Smith</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Shotta Flow 8</v>
+        <v>Prettier</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/shotta-flow-8/1872760524</v>
+        <v>https://music.apple.com/us/song/prettier/1869745409</v>
       </c>
       <c r="D150" t="str">
         <v>2026-02-04</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>Shotta Flow 8 - Single</v>
+        <v>Prettier - Single</v>
       </c>
       <c r="G150" t="str">
-        <v>3:21</v>
+        <v>2:34</v>
       </c>
       <c r="H150" t="str">
-        <v>NLE Choppa</v>
+        <v>Grace VanderWaal</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/nle-choppa/1449052753</v>
+        <v>https://music.apple.com/us/artist/grace-vanderwaal/1175539534</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/shotta-flow-8/1872760520</v>
+        <v>https://music.apple.com/us/album/prettier/1869745403</v>
       </c>
       <c r="L150" t="str">
-        <v>Shotta Flow 8 - NLE Choppa</v>
+        <v>Prettier - Grace VanderWaal</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Die To Fall</v>
+        <v>Shotta Flow 8</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/die-to-fall/1866902681</v>
+        <v>https://music.apple.com/us/song/shotta-flow-8/1872760524</v>
       </c>
       <c r="D151" t="str">
         <v>2026-02-04</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>Die To Fall - Single</v>
+        <v>Shotta Flow 8 - Single</v>
       </c>
       <c r="G151" t="str">
-        <v>3:20</v>
+        <v>3:21</v>
       </c>
       <c r="H151" t="str">
-        <v>The Maine</v>
+        <v>NLE Choppa</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
+        <v>https://music.apple.com/us/artist/nle-choppa/1449052753</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/die-to-fall/1866902679</v>
+        <v>https://music.apple.com/us/album/shotta-flow-8/1872760520</v>
       </c>
       <c r="L151" t="str">
-        <v>Die To Fall - The Maine</v>
+        <v>Shotta Flow 8 - NLE Choppa</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>The Cruel Angel's Thesis (Neon Genesis Evangelion)</v>
+        <v>Die To Fall</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/the-cruel-angels-thesis-neon-genesis-evangelion/1864932139</v>
+        <v>https://music.apple.com/us/song/die-to-fall/1866902681</v>
       </c>
       <c r="D152" t="str">
         <v>2026-02-04</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>The Cruel Angel's Thesis (Neon Genesis Evangelion) - Single</v>
+        <v>Die To Fall - Single</v>
       </c>
       <c r="G152" t="str">
-        <v>2:58</v>
+        <v>3:20</v>
       </c>
       <c r="H152" t="str">
-        <v>Steve Aoki</v>
+        <v>The Maine</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/steve-aoki/271066694</v>
+        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/the-cruel-angels-thesis-neon-genesis-evangelion/1864932135</v>
+        <v>https://music.apple.com/us/album/die-to-fall/1866902679</v>
       </c>
       <c r="L152" t="str">
-        <v>The Cruel Angel's Thesis (Neon Genesis Evangelion) - Steve Aoki</v>
+        <v>Die To Fall - The Maine</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Slow Burn</v>
+        <v>The Cruel Angel's Thesis (Neon Genesis Evangelion)</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/slow-burn/1851033862</v>
+        <v>https://music.apple.com/us/song/the-cruel-angels-thesis-neon-genesis-evangelion/1864932139</v>
       </c>
       <c r="D153" t="str">
         <v>2026-02-04</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Still There’s a Glow</v>
+        <v>The Cruel Angel's Thesis (Neon Genesis Evangelion) - Single</v>
       </c>
       <c r="G153" t="str">
-        <v>2:14</v>
+        <v>2:58</v>
       </c>
       <c r="H153" t="str">
-        <v>Sweet Pill</v>
+        <v>Steve Aoki</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/sweet-pill/1459476044</v>
+        <v>https://music.apple.com/us/artist/steve-aoki/271066694</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/slow-burn/1851033857</v>
+        <v>https://music.apple.com/us/album/the-cruel-angels-thesis-neon-genesis-evangelion/1864932135</v>
       </c>
       <c r="L153" t="str">
-        <v>Slow Burn - Sweet Pill</v>
+        <v>The Cruel Angel's Thesis (Neon Genesis Evangelion) - Steve Aoki</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Too Late</v>
+        <v>Slow Burn</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/too-late/1857999860</v>
+        <v>https://music.apple.com/us/song/slow-burn/1851033862</v>
       </c>
       <c r="D154" t="str">
         <v>2026-02-04</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>Evergreen</v>
+        <v>Still There’s a Glow</v>
       </c>
       <c r="G154" t="str">
-        <v>2:56</v>
+        <v>2:14</v>
       </c>
       <c r="H154" t="str">
-        <v>Hunter Hayes</v>
+        <v>Sweet Pill</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/hunter-hayes/429231434</v>
+        <v>https://music.apple.com/us/artist/sweet-pill/1459476044</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/too-late/1857999850</v>
+        <v>https://music.apple.com/us/album/slow-burn/1851033857</v>
       </c>
       <c r="L154" t="str">
-        <v>Too Late - Hunter Hayes</v>
+        <v>Slow Burn - Sweet Pill</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Mono (feat. skaiwater)</v>
+        <v>Too Late</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/mono-feat-skaiwater/1869130804</v>
+        <v>https://music.apple.com/us/song/too-late/1857999860</v>
       </c>
       <c r="D155" t="str">
         <v>2026-02-04</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>Mono (feat. skaiwater) - Single</v>
+        <v>Evergreen</v>
       </c>
       <c r="G155" t="str">
-        <v>2:50</v>
+        <v>2:56</v>
       </c>
       <c r="H155" t="str">
-        <v>i-dle</v>
+        <v>Hunter Hayes</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/i-dle/1378887586</v>
+        <v>https://music.apple.com/us/artist/hunter-hayes/429231434</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/mono-feat-skaiwater/1869130801</v>
+        <v>https://music.apple.com/us/album/too-late/1857999850</v>
       </c>
       <c r="L155" t="str">
-        <v>Mono (feat. skaiwater) - i-dle</v>
+        <v>Too Late - Hunter Hayes</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Thank You Is Enough</v>
+        <v>Mono (feat. skaiwater)</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/thank-you-is-enough/1870679042</v>
+        <v>https://music.apple.com/us/song/mono-feat-skaiwater/1869130804</v>
       </c>
       <c r="D156" t="str">
         <v>2026-02-04</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>Yo Gabba GabbaLand! (Season 2) [Apple TV+ Original Series Soundtrack]</v>
+        <v>Mono (feat. skaiwater) - Single</v>
       </c>
       <c r="G156" t="str">
-        <v>1:55</v>
+        <v>2:50</v>
       </c>
       <c r="H156" t="str">
-        <v>Yo Gabba Gabba</v>
+        <v>i-dle</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/yo-gabba-gabba/433108373</v>
+        <v>https://music.apple.com/us/artist/i-dle/1378887586</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/thank-you-is-enough/1870678950</v>
+        <v>https://music.apple.com/us/album/mono-feat-skaiwater/1869130801</v>
       </c>
       <c r="L156" t="str">
-        <v>Thank You Is Enough - Yo Gabba Gabba</v>
+        <v>Mono (feat. skaiwater) - i-dle</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>RIDIN</v>
+        <v>Thank You Is Enough</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/ridin/1869786726</v>
+        <v>https://music.apple.com/us/song/thank-you-is-enough/1870679042</v>
       </c>
       <c r="D157" t="str">
         <v>2026-02-04</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>RIDIN - Single</v>
+        <v>Yo Gabba GabbaLand! (Season 2) [Apple TV+ Original Series Soundtrack]</v>
       </c>
       <c r="G157" t="str">
-        <v>2:00</v>
+        <v>1:55</v>
       </c>
       <c r="H157" t="str">
-        <v>Tokischa</v>
+        <v>Yo Gabba Gabba</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/tokischa/1414103446</v>
+        <v>https://music.apple.com/us/artist/yo-gabba-gabba/433108373</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/ridin/1869786725</v>
+        <v>https://music.apple.com/us/album/thank-you-is-enough/1870678950</v>
       </c>
       <c r="L157" t="str">
-        <v>RIDIN - Tokischa</v>
+        <v>Thank You Is Enough - Yo Gabba Gabba</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>POSSESSION</v>
+        <v>RIDIN</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/possession/1872536200</v>
+        <v>https://music.apple.com/us/song/ridin/1869786726</v>
       </c>
       <c r="D158" t="str">
         <v>2026-02-04</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>POSSESSION - Single</v>
+        <v>RIDIN - Single</v>
       </c>
       <c r="G158" t="str">
-        <v>3:07</v>
+        <v>2:00</v>
       </c>
       <c r="H158" t="str">
-        <v>Melanie Martinez</v>
+        <v>Tokischa</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/melanie-martinez/993014053</v>
+        <v>https://music.apple.com/us/artist/tokischa/1414103446</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/possession/1872536199</v>
+        <v>https://music.apple.com/us/album/ridin/1869786725</v>
       </c>
       <c r="L158" t="str">
-        <v>POSSESSION - Melanie Martinez</v>
+        <v>RIDIN - Tokischa</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Poema</v>
+        <v>POSSESSION</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/poema/1872723644</v>
+        <v>https://music.apple.com/us/song/possession/1872536200</v>
       </c>
       <c r="D159" t="str">
         <v>2026-02-04</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>Poema - Single</v>
+        <v>POSSESSION - Single</v>
       </c>
       <c r="G159" t="str">
-        <v>3:14</v>
+        <v>3:07</v>
       </c>
       <c r="H159" t="str">
-        <v>Óscar Maydon</v>
+        <v>Melanie Martinez</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/%C3%B3scar-maydon/1524147696</v>
+        <v>https://music.apple.com/us/artist/melanie-martinez/993014053</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/poema/1872723468</v>
+        <v>https://music.apple.com/us/album/possession/1872536199</v>
       </c>
       <c r="L159" t="str">
-        <v>Poema - Óscar Maydon</v>
+        <v>POSSESSION - Melanie Martinez</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Live Without</v>
+        <v>Poema</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/live-without/1862777625</v>
+        <v>https://music.apple.com/us/song/poema/1872723644</v>
       </c>
       <c r="D160" t="str">
         <v>2026-02-04</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>WORRIED SICK (Deluxe Edition)</v>
+        <v>Poema - Single</v>
       </c>
       <c r="G160" t="str">
-        <v>2:55</v>
+        <v>3:14</v>
       </c>
       <c r="H160" t="str">
-        <v>Meet Me @ The Altar</v>
+        <v>Óscar Maydon</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/meet-me-the-altar/1109900880</v>
+        <v>https://music.apple.com/us/artist/%C3%B3scar-maydon/1524147696</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/live-without/1862777608</v>
+        <v>https://music.apple.com/us/album/poema/1872723468</v>
       </c>
       <c r="L160" t="str">
-        <v>Live Without - Meet Me @ The Altar</v>
+        <v>Poema - Óscar Maydon</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>FANÁTICO</v>
+        <v>Live Without</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/fan%C3%A1tico/1871611852</v>
+        <v>https://music.apple.com/us/song/live-without/1862777625</v>
       </c>
       <c r="D161" t="str">
         <v>2026-02-04</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>FANÁTICO - Single</v>
+        <v>WORRIED SICK (Deluxe Edition)</v>
       </c>
       <c r="G161" t="str">
-        <v>3:55</v>
+        <v>2:55</v>
       </c>
       <c r="H161" t="str">
-        <v>Blessd</v>
+        <v>Meet Me @ The Altar</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/blessd/1481245915</v>
+        <v>https://music.apple.com/us/artist/meet-me-the-altar/1109900880</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/fan%C3%A1tico/1871611851</v>
+        <v>https://music.apple.com/us/album/live-without/1862777608</v>
       </c>
       <c r="L161" t="str">
-        <v>FANÁTICO - Blessd</v>
+        <v>Live Without - Meet Me @ The Altar</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Frozen Lake</v>
+        <v>FANÁTICO</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/frozen-lake/1867287070</v>
+        <v>https://music.apple.com/us/song/fan%C3%A1tico/1871611852</v>
       </c>
       <c r="D162" t="str">
         <v>2026-02-04</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>Frozen Lake - Single</v>
+        <v>FANÁTICO - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>3:29</v>
+        <v>3:55</v>
       </c>
       <c r="H162" t="str">
-        <v>VOILÀ</v>
+        <v>Blessd</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/voil%C3%A0/1333272109</v>
+        <v>https://music.apple.com/us/artist/blessd/1481245915</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/frozen-lake/1867287069</v>
+        <v>https://music.apple.com/us/album/fan%C3%A1tico/1871611851</v>
       </c>
       <c r="L162" t="str">
-        <v>Frozen Lake - VOILÀ</v>
+        <v>FANÁTICO - Blessd</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Fine Shyt (EB Remix) [feat. Eric Bellinger]</v>
+        <v>Frozen Lake</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/fine-shyt-eb-remix-feat-eric-bellinger/1870964385</v>
+        <v>https://music.apple.com/us/song/frozen-lake/1867287070</v>
       </c>
       <c r="D163" t="str">
         <v>2026-02-04</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>Fine Shyt (EB Remix) [feat. Eric Bellinger] - Single</v>
+        <v>Frozen Lake - Single</v>
       </c>
       <c r="G163" t="str">
-        <v>2:45</v>
+        <v>3:29</v>
       </c>
       <c r="H163" t="str">
-        <v>VEDO</v>
+        <v>VOILÀ</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/vedo/267769510</v>
+        <v>https://music.apple.com/us/artist/voil%C3%A0/1333272109</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/fine-shyt-eb-remix-feat-eric-bellinger/1870964384</v>
+        <v>https://music.apple.com/us/album/frozen-lake/1867287069</v>
       </c>
       <c r="L163" t="str">
-        <v>Fine Shyt (EB Remix) [feat. Eric Bellinger] - VEDO</v>
+        <v>Frozen Lake - VOILÀ</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Hell Yeah (Feat. Waxmaster)</v>
+        <v>Fine Shyt (EB Remix) [feat. Eric Bellinger]</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/hell-yeah-feat-waxmaster/1866602820</v>
+        <v>https://music.apple.com/us/song/fine-shyt-eb-remix-feat-eric-bellinger/1870964385</v>
       </c>
       <c r="D164" t="str">
         <v>2026-02-04</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>Hell Yeah (Feat. Waxmaster) - Single</v>
+        <v>Fine Shyt (EB Remix) [feat. Eric Bellinger] - Single</v>
       </c>
       <c r="G164" t="str">
-        <v>3:32</v>
+        <v>2:45</v>
       </c>
       <c r="H164" t="str">
-        <v>Chris Lorenzo</v>
+        <v>VEDO</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/chris-lorenzo/621431022</v>
+        <v>https://music.apple.com/us/artist/vedo/267769510</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/hell-yeah-feat-waxmaster/1866602819</v>
+        <v>https://music.apple.com/us/album/fine-shyt-eb-remix-feat-eric-bellinger/1870964384</v>
       </c>
       <c r="L164" t="str">
-        <v>Hell Yeah (Feat. Waxmaster) - Chris Lorenzo</v>
+        <v>Fine Shyt (EB Remix) [feat. Eric Bellinger] - VEDO</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>It’s Like That</v>
+        <v>Hell Yeah (Feat. Waxmaster)</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/its-like-that/1858689757</v>
+        <v>https://music.apple.com/us/song/hell-yeah-feat-waxmaster/1866602820</v>
       </c>
       <c r="D165" t="str">
         <v>2026-02-04</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>A Pound of Feathers</v>
+        <v>Hell Yeah (Feat. Waxmaster) - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>3:20</v>
+        <v>3:32</v>
       </c>
       <c r="H165" t="str">
-        <v>The Black Crowes</v>
+        <v>Chris Lorenzo</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/the-black-crowes/2969371</v>
+        <v>https://music.apple.com/us/artist/chris-lorenzo/621431022</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/its-like-that/1858689485</v>
+        <v>https://music.apple.com/us/album/hell-yeah-feat-waxmaster/1866602819</v>
       </c>
       <c r="L165" t="str">
-        <v>It’s Like That - The Black Crowes</v>
+        <v>Hell Yeah (Feat. Waxmaster) - Chris Lorenzo</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>A.S.A.P.</v>
+        <v>It’s Like That</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/a-s-a-p/1833414737</v>
+        <v>https://music.apple.com/us/song/its-like-that/1858689757</v>
       </c>
       <c r="D166" t="str">
         <v>2026-02-04</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>A.S.A.P. - Single</v>
+        <v>A Pound of Feathers</v>
       </c>
       <c r="G166" t="str">
-        <v>2:48</v>
+        <v>3:20</v>
       </c>
       <c r="H166" t="str">
-        <v>Mýa</v>
+        <v>The Black Crowes</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/m%C3%BDa/108751</v>
+        <v>https://music.apple.com/us/artist/the-black-crowes/2969371</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/a-s-a-p/1833414736</v>
+        <v>https://music.apple.com/us/album/its-like-that/1858689485</v>
       </c>
       <c r="L166" t="str">
-        <v>A.S.A.P. - Mýa</v>
+        <v>It’s Like That - The Black Crowes</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Once I Say</v>
+        <v>A.S.A.P.</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/once-i-say/1867855025</v>
+        <v>https://music.apple.com/us/song/a-s-a-p/1833414737</v>
       </c>
       <c r="D167" t="str">
         <v>2026-02-04</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>PASSION</v>
+        <v>A.S.A.P. - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>3:21</v>
+        <v>2:48</v>
       </c>
       <c r="H167" t="str">
-        <v>Terrace Martin</v>
+        <v>Mýa</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/terrace-martin/27522754</v>
+        <v>https://music.apple.com/us/artist/m%C3%BDa/108751</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/once-i-say/1867854756</v>
+        <v>https://music.apple.com/us/album/a-s-a-p/1833414736</v>
       </c>
       <c r="L167" t="str">
-        <v>Once I Say - Terrace Martin</v>
+        <v>A.S.A.P. - Mýa</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>believer</v>
+        <v>Once I Say</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/believer/1862797080</v>
+        <v>https://music.apple.com/us/song/once-i-say/1867855025</v>
       </c>
       <c r="D168" t="str">
         <v>2026-02-04</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>believer - Single</v>
+        <v>PASSION</v>
       </c>
       <c r="G168" t="str">
-        <v>2:57</v>
+        <v>3:21</v>
       </c>
       <c r="H168" t="str">
-        <v>Yuna</v>
+        <v>Terrace Martin</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/yuna/423966062</v>
+        <v>https://music.apple.com/us/artist/terrace-martin/27522754</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/believer/1862796978</v>
+        <v>https://music.apple.com/us/album/once-i-say/1867854756</v>
       </c>
       <c r="L168" t="str">
-        <v>believer - Yuna</v>
+        <v>Once I Say - Terrace Martin</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>I Envy The Wind</v>
+        <v>believer</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/i-envy-the-wind/1863202477</v>
+        <v>https://music.apple.com/us/song/believer/1862797080</v>
       </c>
       <c r="D169" t="str">
         <v>2026-02-04</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>I Envy The Wind - Single</v>
+        <v>believer - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>3:51</v>
+        <v>2:57</v>
       </c>
       <c r="H169" t="str">
-        <v>Molly Parden</v>
+        <v>Yuna</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/molly-parden/374789677</v>
+        <v>https://music.apple.com/us/artist/yuna/423966062</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/i-envy-the-wind/1863202476</v>
+        <v>https://music.apple.com/us/album/believer/1862796978</v>
       </c>
       <c r="L169" t="str">
-        <v>I Envy The Wind - Molly Parden</v>
+        <v>believer - Yuna</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>The Alchemist</v>
+        <v>I Envy The Wind</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/the-alchemist/1831827347</v>
+        <v>https://music.apple.com/us/song/i-envy-the-wind/1863202477</v>
       </c>
       <c r="D170" t="str">
         <v>2026-02-04</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>The Alchemist</v>
+        <v>I Envy The Wind - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>3:13</v>
+        <v>3:51</v>
       </c>
       <c r="H170" t="str">
-        <v>Bre Kennedy</v>
+        <v>Molly Parden</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/bre-kennedy/1242283415</v>
+        <v>https://music.apple.com/us/artist/molly-parden/374789677</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/the-alchemist/1831827332</v>
+        <v>https://music.apple.com/us/album/i-envy-the-wind/1863202476</v>
       </c>
       <c r="L170" t="str">
-        <v>The Alchemist - Bre Kennedy</v>
+        <v>I Envy The Wind - Molly Parden</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Daysa</v>
+        <v>The Alchemist</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/daysa/1861575845</v>
+        <v>https://music.apple.com/us/song/the-alchemist/1831827347</v>
       </c>
       <c r="D171" t="str">
         <v>2026-02-04</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Daysa - Single</v>
+        <v>The Alchemist</v>
       </c>
       <c r="G171" t="str">
-        <v>4:36</v>
+        <v>3:13</v>
       </c>
       <c r="H171" t="str">
-        <v>⌭ IceMorph ⌬</v>
+        <v>Bre Kennedy</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/icemorph/1733236411</v>
+        <v>https://music.apple.com/us/artist/bre-kennedy/1242283415</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/daysa/1861575844</v>
+        <v>https://music.apple.com/us/album/the-alchemist/1831827332</v>
       </c>
       <c r="L171" t="str">
-        <v>Daysa - ⌭ IceMorph ⌬</v>
+        <v>The Alchemist - Bre Kennedy</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Fabulous</v>
+        <v>Daysa</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/fabulous/1862804005</v>
+        <v>https://music.apple.com/us/song/daysa/1861575845</v>
       </c>
       <c r="D172" t="str">
         <v>2026-02-04</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Fabulous - Single</v>
+        <v>Daysa - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>2:33</v>
+        <v>4:36</v>
       </c>
       <c r="H172" t="str">
-        <v>MEEK</v>
+        <v>⌭ IceMorph ⌬</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/meek/1784432868</v>
+        <v>https://music.apple.com/us/artist/icemorph/1733236411</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/fabulous/1862804004</v>
+        <v>https://music.apple.com/us/album/daysa/1861575844</v>
       </c>
       <c r="L172" t="str">
-        <v>Fabulous - MEEK</v>
+        <v>Daysa - ⌭ IceMorph ⌬</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Me Asusta Amar Tanto la Soledad</v>
+        <v>Fabulous</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/me-asusta-amar-tanto-la-soledad/1866982109</v>
+        <v>https://music.apple.com/us/song/fabulous/1862804005</v>
       </c>
       <c r="D173" t="str">
         <v>2026-02-04</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Me Asusta Amar Tanto la Soledad - Single</v>
+        <v>Fabulous - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>3:22</v>
+        <v>2:33</v>
       </c>
       <c r="H173" t="str">
-        <v>RUBIO</v>
+        <v>MEEK</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/rubio/34747724</v>
+        <v>https://music.apple.com/us/artist/meek/1784432868</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/me-asusta-amar-tanto-la-soledad/1866981907</v>
+        <v>https://music.apple.com/us/album/fabulous/1862804004</v>
       </c>
       <c r="L173" t="str">
-        <v>Me Asusta Amar Tanto la Soledad - RUBIO</v>
+        <v>Fabulous - MEEK</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>brainchem</v>
+        <v>Me Asusta Amar Tanto la Soledad</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/brainchem/1870656942</v>
+        <v>https://music.apple.com/us/song/me-asusta-amar-tanto-la-soledad/1866982109</v>
       </c>
       <c r="D174" t="str">
         <v>2026-02-04</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>brainchem - Single</v>
+        <v>Me Asusta Amar Tanto la Soledad - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>2:28</v>
+        <v>3:22</v>
       </c>
       <c r="H174" t="str">
-        <v>EMJAY</v>
+        <v>RUBIO</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/emjay/1517993423</v>
+        <v>https://music.apple.com/us/artist/rubio/34747724</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/brainchem/1870656608</v>
+        <v>https://music.apple.com/us/album/me-asusta-amar-tanto-la-soledad/1866981907</v>
       </c>
       <c r="L174" t="str">
-        <v>brainchem - EMJAY</v>
+        <v>Me Asusta Amar Tanto la Soledad - RUBIO</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Boyfriend In Yo Brain (Notice Me)</v>
+        <v>brainchem</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/boyfriend-in-yo-brain-notice-me/1871675026</v>
+        <v>https://music.apple.com/us/song/brainchem/1870656942</v>
       </c>
       <c r="D175" t="str">
         <v>2026-02-04</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>With No Due Respect</v>
+        <v>brainchem - Single</v>
       </c>
       <c r="G175" t="str">
-        <v>2:48</v>
+        <v>2:28</v>
       </c>
       <c r="H175" t="str">
-        <v>Foggieraw</v>
+        <v>EMJAY</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/foggieraw/1152021457</v>
+        <v>https://music.apple.com/us/artist/emjay/1517993423</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/boyfriend-in-yo-brain-notice-me/1871675010</v>
+        <v>https://music.apple.com/us/album/brainchem/1870656608</v>
       </c>
       <c r="L175" t="str">
-        <v>Boyfriend In Yo Brain (Notice Me) - Foggieraw</v>
+        <v>brainchem - EMJAY</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Giants</v>
+        <v>Boyfriend In Yo Brain (Notice Me)</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/giants/1869154957</v>
+        <v>https://music.apple.com/us/song/boyfriend-in-yo-brain-notice-me/1871675026</v>
       </c>
       <c r="D176" t="str">
         <v>2026-02-04</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Giants - Single</v>
+        <v>With No Due Respect</v>
       </c>
       <c r="G176" t="str">
-        <v>3:12</v>
+        <v>2:48</v>
       </c>
       <c r="H176" t="str">
-        <v>Picture This</v>
+        <v>Foggieraw</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/picture-this/1194282721</v>
+        <v>https://music.apple.com/us/artist/foggieraw/1152021457</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/giants/1869154821</v>
+        <v>https://music.apple.com/us/album/boyfriend-in-yo-brain-notice-me/1871675010</v>
       </c>
       <c r="L176" t="str">
-        <v>Giants - Picture This</v>
+        <v>Boyfriend In Yo Brain (Notice Me) - Foggieraw</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Scooby</v>
+        <v>Giants</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/scooby/1872510752</v>
+        <v>https://music.apple.com/us/song/giants/1869154957</v>
       </c>
       <c r="D177" t="str">
         <v>2026-02-04</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Scooby - Single</v>
+        <v>Giants - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>3:41</v>
+        <v>3:12</v>
       </c>
       <c r="H177" t="str">
-        <v>corook</v>
+        <v>Picture This</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/corook/1514463762</v>
+        <v>https://music.apple.com/us/artist/picture-this/1194282721</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/scooby/1872510751</v>
+        <v>https://music.apple.com/us/album/giants/1869154821</v>
       </c>
       <c r="L177" t="str">
-        <v>Scooby - corook</v>
+        <v>Giants - Picture This</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>La Racha</v>
+        <v>Scooby</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/la-racha/1868757762</v>
+        <v>https://music.apple.com/us/song/scooby/1872510752</v>
       </c>
       <c r="D178" t="str">
         <v>2026-02-04</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>La Racha - Single</v>
+        <v>Scooby - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>2:48</v>
+        <v>3:41</v>
       </c>
       <c r="H178" t="str">
-        <v>Hermanos Espinoza</v>
+        <v>corook</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/hermanos-espinoza/1613044599</v>
+        <v>https://music.apple.com/us/artist/corook/1514463762</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/la-racha/1868757747</v>
+        <v>https://music.apple.com/us/album/scooby/1872510751</v>
       </c>
       <c r="L178" t="str">
-        <v>La Racha - Hermanos Espinoza</v>
+        <v>Scooby - corook</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>So Am I</v>
+        <v>La Racha</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/so-am-i/1867012209</v>
+        <v>https://music.apple.com/us/song/la-racha/1868757762</v>
       </c>
       <c r="D179" t="str">
         <v>2026-02-04</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Tell Me How You Really Feel</v>
+        <v>La Racha - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>2:50</v>
+        <v>2:48</v>
       </c>
       <c r="H179" t="str">
-        <v>Katelyn Tarver</v>
+        <v>Hermanos Espinoza</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/katelyn-tarver/2356378</v>
+        <v>https://music.apple.com/us/artist/hermanos-espinoza/1613044599</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/so-am-i/1867012005</v>
+        <v>https://music.apple.com/us/album/la-racha/1868757747</v>
       </c>
       <c r="L179" t="str">
-        <v>So Am I - Katelyn Tarver</v>
+        <v>La Racha - Hermanos Espinoza</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>best thing</v>
+        <v>So Am I</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/best-thing/1860673616</v>
+        <v>https://music.apple.com/us/song/so-am-i/1867012209</v>
       </c>
       <c r="D180" t="str">
         <v>2026-02-04</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>best thing - Single</v>
+        <v>Tell Me How You Really Feel</v>
       </c>
       <c r="G180" t="str">
-        <v>4:27</v>
+        <v>2:50</v>
       </c>
       <c r="H180" t="str">
-        <v>WRABEL</v>
+        <v>Katelyn Tarver</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/wrabel/435072161</v>
+        <v>https://music.apple.com/us/artist/katelyn-tarver/2356378</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/best-thing/1860673615</v>
+        <v>https://music.apple.com/us/album/so-am-i/1867012005</v>
       </c>
       <c r="L180" t="str">
-        <v>best thing - WRABEL</v>
+        <v>So Am I - Katelyn Tarver</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Count It Back</v>
+        <v>best thing</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/count-it-back/1855219865</v>
+        <v>https://music.apple.com/us/song/best-thing/1860673616</v>
       </c>
       <c r="D181" t="str">
         <v>2026-02-04</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Magic Boy</v>
+        <v>best thing - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>2:52</v>
+        <v>4:27</v>
       </c>
       <c r="H181" t="str">
-        <v>Bartees Strange</v>
+        <v>WRABEL</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/bartees-strange/1450776625</v>
+        <v>https://music.apple.com/us/artist/wrabel/435072161</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/count-it-back/1855219618</v>
+        <v>https://music.apple.com/us/album/best-thing/1860673615</v>
       </c>
       <c r="L181" t="str">
-        <v>Count It Back - Bartees Strange</v>
+        <v>best thing - WRABEL</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Good Girl</v>
+        <v>Count It Back</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/good-girl/1862640697</v>
+        <v>https://music.apple.com/us/song/count-it-back/1855219865</v>
       </c>
       <c r="D182" t="str">
         <v>2026-02-04</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Good Girl - Single</v>
+        <v>Magic Boy</v>
       </c>
       <c r="G182" t="str">
-        <v>4:23</v>
+        <v>2:52</v>
       </c>
       <c r="H182" t="str">
-        <v>Paris Paloma</v>
+        <v>Bartees Strange</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/paris-paloma/1530898376</v>
+        <v>https://music.apple.com/us/artist/bartees-strange/1450776625</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/good-girl/1862640694</v>
+        <v>https://music.apple.com/us/album/count-it-back/1855219618</v>
       </c>
       <c r="L182" t="str">
-        <v>Good Girl - Paris Paloma</v>
+        <v>Count It Back - Bartees Strange</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>MY REVIVAL</v>
+        <v>Good Girl</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/my-revival/1869465104</v>
+        <v>https://music.apple.com/us/song/good-girl/1862640697</v>
       </c>
       <c r="D183" t="str">
         <v>2026-02-04</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>HEARTLAND (Deluxe Version)</v>
+        <v>Good Girl - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>3:34</v>
+        <v>4:23</v>
       </c>
       <c r="H183" t="str">
-        <v>MORGXN</v>
+        <v>Paris Paloma</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/morgxn/1116360149</v>
+        <v>https://music.apple.com/us/artist/paris-paloma/1530898376</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/my-revival/1869464853</v>
+        <v>https://music.apple.com/us/album/good-girl/1862640694</v>
       </c>
       <c r="L183" t="str">
-        <v>MY REVIVAL - MORGXN</v>
+        <v>Good Girl - Paris Paloma</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Run My Way</v>
+        <v>MY REVIVAL</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/run-my-way/1860964996</v>
+        <v>https://music.apple.com/us/song/my-revival/1869465104</v>
       </c>
       <c r="D184" t="str">
         <v>2026-02-04</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>Run My Way - Single</v>
+        <v>HEARTLAND (Deluxe Version)</v>
       </c>
       <c r="G184" t="str">
-        <v>2:44</v>
+        <v>3:34</v>
       </c>
       <c r="H184" t="str">
-        <v>December 10</v>
+        <v>MORGXN</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/december-10/1414032285</v>
+        <v>https://music.apple.com/us/artist/morgxn/1116360149</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/run-my-way/1860964992</v>
+        <v>https://music.apple.com/us/album/my-revival/1869464853</v>
       </c>
       <c r="L184" t="str">
-        <v>Run My Way - December 10</v>
+        <v>MY REVIVAL - MORGXN</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Cold Night</v>
+        <v>Run My Way</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/cold-night/1867687787</v>
+        <v>https://music.apple.com/us/song/run-my-way/1860964996</v>
       </c>
       <c r="D185" t="str">
         <v>2026-02-04</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>Cold Night - Single</v>
+        <v>Run My Way - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>3:12</v>
+        <v>2:44</v>
       </c>
       <c r="H185" t="str">
-        <v>HANA</v>
+        <v>December 10</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/hana/1792783458</v>
+        <v>https://music.apple.com/us/artist/december-10/1414032285</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/cold-night/1867687784</v>
+        <v>https://music.apple.com/us/album/run-my-way/1860964992</v>
       </c>
       <c r="L185" t="str">
-        <v>Cold Night - HANA</v>
+        <v>Run My Way - December 10</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Away With The Fairies</v>
+        <v>Cold Night</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/away-with-the-fairies/1870603474</v>
+        <v>https://music.apple.com/us/song/cold-night/1867687787</v>
       </c>
       <c r="D186" t="str">
         <v>2026-02-04</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Away With The Fairies - Single</v>
+        <v>Cold Night - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>2:28</v>
+        <v>3:12</v>
       </c>
       <c r="H186" t="str">
-        <v>LUNA</v>
+        <v>HANA</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/luna/1439101807</v>
+        <v>https://music.apple.com/us/artist/hana/1792783458</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/away-with-the-fairies/1870603470</v>
+        <v>https://music.apple.com/us/album/cold-night/1867687784</v>
       </c>
       <c r="L186" t="str">
-        <v>Away With The Fairies - LUNA</v>
+        <v>Cold Night - HANA</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Fragile</v>
+        <v>Away With The Fairies</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/fragile/1866957569</v>
+        <v>https://music.apple.com/us/song/away-with-the-fairies/1870603474</v>
       </c>
       <c r="D187" t="str">
         <v>2026-02-04</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Fragile - Single</v>
+        <v>Away With The Fairies - Single</v>
       </c>
       <c r="G187" t="str">
-        <v>3:10</v>
+        <v>2:28</v>
       </c>
       <c r="H187" t="str">
-        <v>Anajah</v>
+        <v>LUNA</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/anajah/1355166756</v>
+        <v>https://music.apple.com/us/artist/luna/1439101807</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/fragile/1866957565</v>
+        <v>https://music.apple.com/us/album/away-with-the-fairies/1870603470</v>
       </c>
       <c r="L187" t="str">
-        <v>Fragile - Anajah</v>
+        <v>Away With The Fairies - LUNA</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Slow Dancin'</v>
+        <v>Fragile</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/slow-dancin/1871537173</v>
+        <v>https://music.apple.com/us/song/fragile/1866957569</v>
       </c>
       <c r="D188" t="str">
         <v>2026-02-04</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Slow Dancin' - Single</v>
+        <v>Fragile - Single</v>
       </c>
       <c r="G188" t="str">
-        <v>2:04</v>
+        <v>3:10</v>
       </c>
       <c r="H188" t="str">
-        <v>STELLA LEFTY</v>
+        <v>Anajah</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/stella-lefty/1641742186</v>
+        <v>https://music.apple.com/us/artist/anajah/1355166756</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/slow-dancin/1871537170</v>
+        <v>https://music.apple.com/us/album/fragile/1866957565</v>
       </c>
       <c r="L188" t="str">
-        <v>Slow Dancin' - STELLA LEFTY</v>
+        <v>Fragile - Anajah</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Never Kissed a Cowboy</v>
+        <v>Slow Dancin'</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/never-kissed-a-cowboy/1866744530</v>
+        <v>https://music.apple.com/us/song/slow-dancin/1871537173</v>
       </c>
       <c r="D189" t="str">
         <v>2026-02-04</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Never Kissed a Cowboy - Single</v>
+        <v>Slow Dancin' - Single</v>
       </c>
       <c r="G189" t="str">
-        <v>3:04</v>
+        <v>2:04</v>
       </c>
       <c r="H189" t="str">
-        <v>Lily Meola</v>
+        <v>STELLA LEFTY</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/lily-meola/678241726</v>
+        <v>https://music.apple.com/us/artist/stella-lefty/1641742186</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/never-kissed-a-cowboy/1866744528</v>
+        <v>https://music.apple.com/us/album/slow-dancin/1871537170</v>
       </c>
       <c r="L189" t="str">
-        <v>Never Kissed a Cowboy - Lily Meola</v>
+        <v>Slow Dancin' - STELLA LEFTY</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>More Of What Matters</v>
+        <v>Never Kissed a Cowboy</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/more-of-what-matters/1871592720</v>
+        <v>https://music.apple.com/us/song/never-kissed-a-cowboy/1866744530</v>
       </c>
       <c r="D190" t="str">
         <v>2026-02-04</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>More Of What Matters - Single</v>
+        <v>Never Kissed a Cowboy - Single</v>
       </c>
       <c r="G190" t="str">
-        <v>3:41</v>
+        <v>3:04</v>
       </c>
       <c r="H190" t="str">
-        <v>Jamey Johnson</v>
+        <v>Lily Meola</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/jamey-johnson/81030634</v>
+        <v>https://music.apple.com/us/artist/lily-meola/678241726</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/more-of-what-matters/1871592717</v>
+        <v>https://music.apple.com/us/album/never-kissed-a-cowboy/1866744528</v>
       </c>
       <c r="L190" t="str">
-        <v>More Of What Matters - Jamey Johnson</v>
+        <v>Never Kissed a Cowboy - Lily Meola</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Is This The Real You</v>
+        <v>More Of What Matters</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/is-this-the-real-you/1869323368</v>
+        <v>https://music.apple.com/us/song/more-of-what-matters/1871592720</v>
       </c>
       <c r="D191" t="str">
         <v>2026-02-04</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>ONE</v>
+        <v>More Of What Matters - Single</v>
       </c>
       <c r="G191" t="str">
-        <v>3:46</v>
+        <v>3:41</v>
       </c>
       <c r="H191" t="str">
-        <v>Sevendust</v>
+        <v>Jamey Johnson</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/sevendust/13125174</v>
+        <v>https://music.apple.com/us/artist/jamey-johnson/81030634</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/is-this-the-real-you/1869323199</v>
+        <v>https://music.apple.com/us/album/more-of-what-matters/1871592717</v>
       </c>
       <c r="L191" t="str">
-        <v>Is This The Real You - Sevendust</v>
+        <v>More Of What Matters - Jamey Johnson</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Hud</v>
+        <v>Is This The Real You</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/hud/1842015019</v>
+        <v>https://music.apple.com/us/song/is-this-the-real-you/1869323368</v>
       </c>
       <c r="D192" t="str">
         <v>2026-02-04</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>DREAMCRUSH</v>
+        <v>ONE</v>
       </c>
       <c r="G192" t="str">
-        <v>4:46</v>
+        <v>3:46</v>
       </c>
       <c r="H192" t="str">
-        <v>MØL</v>
+        <v>Sevendust</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/m%C3%B8l/975294671</v>
+        <v>https://music.apple.com/us/artist/sevendust/13125174</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/hud/1842014730</v>
+        <v>https://music.apple.com/us/album/is-this-the-real-you/1869323199</v>
       </c>
       <c r="L192" t="str">
-        <v>Hud - MØL</v>
+        <v>Is This The Real You - Sevendust</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Ego Death</v>
+        <v>Hud</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/ego-death/1867855427</v>
+        <v>https://music.apple.com/us/song/hud/1842015019</v>
       </c>
       <c r="D193" t="str">
         <v>2026-02-04</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>Ego Death - Single</v>
+        <v>DREAMCRUSH</v>
       </c>
       <c r="G193" t="str">
-        <v>2:12</v>
+        <v>4:46</v>
       </c>
       <c r="H193" t="str">
-        <v>Atreyu</v>
+        <v>MØL</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/atreyu/6095061</v>
+        <v>https://music.apple.com/us/artist/m%C3%B8l/975294671</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/ego-death/1867855173</v>
+        <v>https://music.apple.com/us/album/hud/1842014730</v>
       </c>
       <c r="L193" t="str">
-        <v>Ego Death - Atreyu</v>
+        <v>Hud - MØL</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Gas Station Love (remix)</v>
+        <v>Ego Death</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/gas-station-love-remix/1872150728</v>
+        <v>https://music.apple.com/us/song/ego-death/1867855427</v>
       </c>
       <c r="D194" t="str">
         <v>2026-02-04</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Gas Station Love (remix) - Single</v>
+        <v>Ego Death - Single</v>
       </c>
       <c r="G194" t="str">
-        <v>4:05</v>
+        <v>2:12</v>
       </c>
       <c r="H194" t="str">
-        <v>EJ Jones</v>
+        <v>Atreyu</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/ej-jones/1781306141</v>
+        <v>https://music.apple.com/us/artist/atreyu/6095061</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/gas-station-love-remix/1872150723</v>
+        <v>https://music.apple.com/us/album/ego-death/1867855173</v>
       </c>
       <c r="L194" t="str">
-        <v>Gas Station Love (remix) - EJ Jones</v>
+        <v>Ego Death - Atreyu</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Disappear</v>
+        <v>Gas Station Love (remix)</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/disappear/1861907311</v>
+        <v>https://music.apple.com/us/song/gas-station-love-remix/1872150728</v>
       </c>
       <c r="D195" t="str">
         <v>2026-02-04</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Disappear</v>
+        <v>Gas Station Love (remix) - Single</v>
       </c>
       <c r="G195" t="str">
-        <v>5:50</v>
+        <v>4:05</v>
       </c>
       <c r="H195" t="str">
-        <v>Lane 8</v>
+        <v>EJ Jones</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/lane-8/634763116</v>
+        <v>https://music.apple.com/us/artist/ej-jones/1781306141</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/disappear/1861907305</v>
+        <v>https://music.apple.com/us/album/gas-station-love-remix/1872150723</v>
       </c>
       <c r="L195" t="str">
-        <v>Disappear - Lane 8</v>
+        <v>Gas Station Love (remix) - EJ Jones</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Misbehave</v>
+        <v>Disappear</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/misbehave/1859630128</v>
+        <v>https://music.apple.com/us/song/disappear/1861907311</v>
       </c>
       <c r="D196" t="str">
         <v>2026-02-04</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>Misbehave - Single</v>
+        <v>Disappear</v>
       </c>
       <c r="G196" t="str">
-        <v>3:43</v>
+        <v>5:50</v>
       </c>
       <c r="H196" t="str">
-        <v>Aluna</v>
+        <v>Lane 8</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/aluna/1508017201</v>
+        <v>https://music.apple.com/us/artist/lane-8/634763116</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/misbehave/1859630126</v>
+        <v>https://music.apple.com/us/album/disappear/1861907305</v>
       </c>
       <c r="L196" t="str">
-        <v>Misbehave - Aluna</v>
+        <v>Disappear - Lane 8</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Club Bizarre</v>
+        <v>Misbehave</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/club-bizarre/1870355078</v>
+        <v>https://music.apple.com/us/song/misbehave/1859630128</v>
       </c>
       <c r="D197" t="str">
         <v>2026-02-04</v>
@@ -7861,36 +7861,36 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>Club Bizarre - Single</v>
+        <v>Misbehave - Single</v>
       </c>
       <c r="G197" t="str">
-        <v>2:47</v>
+        <v>3:43</v>
       </c>
       <c r="H197" t="str">
-        <v>Alok</v>
+        <v>Aluna</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/alok/324709167</v>
+        <v>https://music.apple.com/us/artist/aluna/1508017201</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/club-bizarre/1870355077</v>
+        <v>https://music.apple.com/us/album/misbehave/1859630126</v>
       </c>
       <c r="L197" t="str">
-        <v>Club Bizarre - Alok</v>
+        <v>Misbehave - Aluna</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Fly</v>
+        <v>Club Bizarre</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/fly/1867903625</v>
+        <v>https://music.apple.com/us/song/club-bizarre/1870355078</v>
       </c>
       <c r="D198" t="str">
         <v>2026-02-04</v>
@@ -7899,36 +7899,36 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>Fly - Single</v>
+        <v>Club Bizarre - Single</v>
       </c>
       <c r="G198" t="str">
-        <v>3:04</v>
+        <v>2:47</v>
       </c>
       <c r="H198" t="str">
-        <v>Stephen Stanley</v>
+        <v>Alok</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/stephen-stanley/28074609</v>
+        <v>https://music.apple.com/us/artist/alok/324709167</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/fly/1867903548</v>
+        <v>https://music.apple.com/us/album/club-bizarre/1870355077</v>
       </c>
       <c r="L198" t="str">
-        <v>Fly - Stephen Stanley</v>
+        <v>Club Bizarre - Alok</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>ily anyway</v>
+        <v>Fly</v>
       </c>
       <c r="B199" t="str">
         <v/>
       </c>
       <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/ily-anyway/1870369432</v>
+        <v>https://music.apple.com/us/song/fly/1867903625</v>
       </c>
       <c r="D199" t="str">
         <v>2026-02-04</v>
@@ -7937,36 +7937,36 @@
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>ily anyway - Single</v>
+        <v>Fly - Single</v>
       </c>
       <c r="G199" t="str">
-        <v>3:05</v>
+        <v>3:04</v>
       </c>
       <c r="H199" t="str">
-        <v>Strings &amp; Heart</v>
+        <v>Stephen Stanley</v>
       </c>
       <c r="I199" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/strings-heart/1435173742</v>
+        <v>https://music.apple.com/us/artist/stephen-stanley/28074609</v>
       </c>
       <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/ily-anyway/1870369426</v>
+        <v>https://music.apple.com/us/album/fly/1867903548</v>
       </c>
       <c r="L199" t="str">
-        <v>ily anyway - Strings &amp; Heart</v>
+        <v>Fly - Stephen Stanley</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>George Jones (feat. Angela Autumn)</v>
+        <v>ily anyway</v>
       </c>
       <c r="B200" t="str">
         <v/>
       </c>
       <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/george-jones-feat-angela-autumn/1867306007</v>
+        <v>https://music.apple.com/us/song/ily-anyway/1870369432</v>
       </c>
       <c r="D200" t="str">
         <v>2026-02-04</v>
@@ -7975,36 +7975,36 @@
         <v/>
       </c>
       <c r="F200" t="str">
-        <v>Nellene - EP</v>
+        <v>ily anyway - Single</v>
       </c>
       <c r="G200" t="str">
-        <v>3:35</v>
+        <v>3:05</v>
       </c>
       <c r="H200" t="str">
-        <v>Deloyd Elze</v>
+        <v>Strings &amp; Heart</v>
       </c>
       <c r="I200" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J200" t="str">
-        <v>https://music.apple.com/us/artist/deloyd-elze/1699032462</v>
+        <v>https://music.apple.com/us/artist/strings-heart/1435173742</v>
       </c>
       <c r="K200" t="str">
-        <v>https://music.apple.com/us/album/george-jones-feat-angela-autumn/1867306004</v>
+        <v>https://music.apple.com/us/album/ily-anyway/1870369426</v>
       </c>
       <c r="L200" t="str">
-        <v>George Jones (feat. Angela Autumn) - Deloyd Elze</v>
+        <v>ily anyway - Strings &amp; Heart</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Kiss Big</v>
+        <v>George Jones (feat. Angela Autumn)</v>
       </c>
       <c r="B201" t="str">
         <v/>
       </c>
       <c r="C201" t="str">
-        <v>https://music.apple.com/us/song/kiss-big/1837292261</v>
+        <v>https://music.apple.com/us/song/george-jones-feat-angela-autumn/1867306007</v>
       </c>
       <c r="D201" t="str">
         <v>2026-02-04</v>
@@ -8013,36 +8013,36 @@
         <v/>
       </c>
       <c r="F201" t="str">
-        <v>Kiss Big</v>
+        <v>Nellene - EP</v>
       </c>
       <c r="G201" t="str">
-        <v>3:41</v>
+        <v>3:35</v>
       </c>
       <c r="H201" t="str">
-        <v>Ailbhe Reddy</v>
+        <v>Deloyd Elze</v>
       </c>
       <c r="I201" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J201" t="str">
-        <v>https://music.apple.com/us/artist/ailbhe-reddy/947186338</v>
+        <v>https://music.apple.com/us/artist/deloyd-elze/1699032462</v>
       </c>
       <c r="K201" t="str">
-        <v>https://music.apple.com/us/album/kiss-big/1837292249</v>
+        <v>https://music.apple.com/us/album/george-jones-feat-angela-autumn/1867306004</v>
       </c>
       <c r="L201" t="str">
-        <v>Kiss Big - Ailbhe Reddy</v>
+        <v>George Jones (feat. Angela Autumn) - Deloyd Elze</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>praxis</v>
+        <v>Kiss Big</v>
       </c>
       <c r="B202" t="str">
         <v/>
       </c>
       <c r="C202" t="str">
-        <v>https://music.apple.com/us/song/praxis/1845253734</v>
+        <v>https://music.apple.com/us/song/kiss-big/1837292261</v>
       </c>
       <c r="D202" t="str">
         <v>2026-02-04</v>
@@ -8051,36 +8051,36 @@
         <v/>
       </c>
       <c r="F202" t="str">
-        <v>Whole World As Vigil</v>
+        <v>Kiss Big</v>
       </c>
       <c r="G202" t="str">
-        <v>3:28</v>
+        <v>3:41</v>
       </c>
       <c r="H202" t="str">
-        <v>Lauren Auder</v>
+        <v>Ailbhe Reddy</v>
       </c>
       <c r="I202" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J202" t="str">
-        <v>https://music.apple.com/us/artist/lauren-auder/1096049552</v>
+        <v>https://music.apple.com/us/artist/ailbhe-reddy/947186338</v>
       </c>
       <c r="K202" t="str">
-        <v>https://music.apple.com/us/album/praxis/1845253730</v>
+        <v>https://music.apple.com/us/album/kiss-big/1837292249</v>
       </c>
       <c r="L202" t="str">
-        <v>praxis - Lauren Auder</v>
+        <v>Kiss Big - Ailbhe Reddy</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>House</v>
+        <v>praxis</v>
       </c>
       <c r="B203" t="str">
         <v/>
       </c>
       <c r="C203" t="str">
-        <v>https://music.apple.com/us/song/house/1866696487</v>
+        <v>https://music.apple.com/us/song/praxis/1845253734</v>
       </c>
       <c r="D203" t="str">
         <v>2026-02-04</v>
@@ -8089,36 +8089,36 @@
         <v/>
       </c>
       <c r="F203" t="str">
-        <v>House - Single</v>
+        <v>Whole World As Vigil</v>
       </c>
       <c r="G203" t="str">
-        <v>2:30</v>
+        <v>3:28</v>
       </c>
       <c r="H203" t="str">
-        <v>Connie Converse</v>
+        <v>Lauren Auder</v>
       </c>
       <c r="I203" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J203" t="str">
-        <v>https://music.apple.com/us/artist/connie-converse/308326962</v>
+        <v>https://music.apple.com/us/artist/lauren-auder/1096049552</v>
       </c>
       <c r="K203" t="str">
-        <v>https://music.apple.com/us/album/house/1866696486</v>
+        <v>https://music.apple.com/us/album/praxis/1845253730</v>
       </c>
       <c r="L203" t="str">
-        <v>House - Connie Converse</v>
+        <v>praxis - Lauren Auder</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>Cowboy Without a Clue</v>
+        <v>House</v>
       </c>
       <c r="B204" t="str">
         <v/>
       </c>
       <c r="C204" t="str">
-        <v>https://music.apple.com/us/song/cowboy-without-a-clue/1834024322</v>
+        <v>https://music.apple.com/us/song/house/1866696487</v>
       </c>
       <c r="D204" t="str">
         <v>2026-02-04</v>
@@ -8127,36 +8127,36 @@
         <v/>
       </c>
       <c r="F204" t="str">
-        <v>No Love Lost to Kindness</v>
+        <v>House - Single</v>
       </c>
       <c r="G204" t="str">
-        <v>3:57</v>
+        <v>2:30</v>
       </c>
       <c r="H204" t="str">
-        <v>Yumi Zouma</v>
+        <v>Connie Converse</v>
       </c>
       <c r="I204" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J204" t="str">
-        <v>https://music.apple.com/us/artist/yumi-zouma/795031200</v>
+        <v>https://music.apple.com/us/artist/connie-converse/308326962</v>
       </c>
       <c r="K204" t="str">
-        <v>https://music.apple.com/us/album/cowboy-without-a-clue/1834024311</v>
+        <v>https://music.apple.com/us/album/house/1866696486</v>
       </c>
       <c r="L204" t="str">
-        <v>Cowboy Without a Clue - Yumi Zouma</v>
+        <v>House - Connie Converse</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>Brincar</v>
+        <v>Cowboy Without a Clue</v>
       </c>
       <c r="B205" t="str">
         <v/>
       </c>
       <c r="C205" t="str">
-        <v>https://music.apple.com/us/song/brincar/1871554907</v>
+        <v>https://music.apple.com/us/song/cowboy-without-a-clue/1834024322</v>
       </c>
       <c r="D205" t="str">
         <v>2026-02-04</v>
@@ -8165,68 +8165,106 @@
         <v/>
       </c>
       <c r="F205" t="str">
-        <v>JET LAG - EP</v>
+        <v>No Love Lost to Kindness</v>
       </c>
       <c r="G205" t="str">
-        <v>3:06</v>
+        <v>3:57</v>
       </c>
       <c r="H205" t="str">
-        <v>J Castle</v>
+        <v>Yumi Zouma</v>
       </c>
       <c r="I205" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J205" t="str">
-        <v>https://music.apple.com/us/artist/j-castle/309829058</v>
+        <v>https://music.apple.com/us/artist/yumi-zouma/795031200</v>
       </c>
       <c r="K205" t="str">
-        <v>https://music.apple.com/us/album/brincar/1871554901</v>
+        <v>https://music.apple.com/us/album/cowboy-without-a-clue/1834024311</v>
       </c>
       <c r="L205" t="str">
-        <v>Brincar - J Castle</v>
+        <v>Cowboy Without a Clue - Yumi Zouma</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
+        <v>Brincar</v>
+      </c>
+      <c r="B206" t="str">
+        <v/>
+      </c>
+      <c r="C206" t="str">
+        <v>https://music.apple.com/us/song/brincar/1871554907</v>
+      </c>
+      <c r="D206" t="str">
+        <v>2026-02-04</v>
+      </c>
+      <c r="E206" t="str">
+        <v/>
+      </c>
+      <c r="F206" t="str">
+        <v>JET LAG - EP</v>
+      </c>
+      <c r="G206" t="str">
+        <v>3:06</v>
+      </c>
+      <c r="H206" t="str">
+        <v>J Castle</v>
+      </c>
+      <c r="I206" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J206" t="str">
+        <v>https://music.apple.com/us/artist/j-castle/309829058</v>
+      </c>
+      <c r="K206" t="str">
+        <v>https://music.apple.com/us/album/brincar/1871554901</v>
+      </c>
+      <c r="L206" t="str">
+        <v>Brincar - J Castle</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="str">
         <v>Quién</v>
       </c>
-      <c r="B206" t="str">
-        <v/>
-      </c>
-      <c r="C206" t="str">
+      <c r="B207" t="str">
+        <v/>
+      </c>
+      <c r="C207" t="str">
         <v>https://music.apple.com/us/song/qui%C3%A9n/1870329662</v>
       </c>
-      <c r="D206" t="str">
-        <v>2026-02-04</v>
-      </c>
-      <c r="E206" t="str">
-        <v/>
-      </c>
-      <c r="F206" t="str">
+      <c r="D207" t="str">
+        <v>2026-02-04</v>
+      </c>
+      <c r="E207" t="str">
+        <v/>
+      </c>
+      <c r="F207" t="str">
         <v>Quién - Single</v>
       </c>
-      <c r="G206" t="str">
+      <c r="G207" t="str">
         <v>4:19</v>
       </c>
-      <c r="H206" t="str">
+      <c r="H207" t="str">
         <v>Daniela Darcourt</v>
       </c>
-      <c r="I206" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J206" t="str">
+      <c r="I207" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J207" t="str">
         <v>https://music.apple.com/us/artist/daniela-darcourt/1396749684</v>
       </c>
-      <c r="K206" t="str">
+      <c r="K207" t="str">
         <v>https://music.apple.com/us/album/qui%C3%A9n/1870329660</v>
       </c>
-      <c r="L206" t="str">
+      <c r="L207" t="str">
         <v>Quién - Daniela Darcourt</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L206"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L207"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Marc Anthony - Make It With You (Visualizer)</v>
       </c>
       <c r="B2" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=WHnz1jDrxw8</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>4:24</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Marc Anthony - Make It With You (Visualizer)</v>
       </c>
       <c r="B2" t="str">
-        <v>19 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=WHnz1jDrxw8</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>19 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>4:24</v>
@@ -629,7 +629,7 @@
         <v>Vera Blue - Hold (Live on Sydney Harbour)</v>
       </c>
       <c r="B7" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=SYEwk-EZJPU</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G7" t="str">
         <v>3:37</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Marc Anthony - Make It With You (Visualizer)</v>
       </c>
       <c r="B2" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=WHnz1jDrxw8</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>4:24</v>
@@ -591,7 +591,7 @@
         <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Studio)</v>
       </c>
       <c r="B6" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=mgsdQI-GVMM</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G6" t="str">
         <v>3:19</v>
@@ -2035,7 +2035,7 @@
         <v>TINI - FUTTTURA LIVE - el cielo + fresa</v>
       </c>
       <c r="B44" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C44" t="str">
         <v>https://www.youtube.com/watch?v=q_rrgJZAdNg</v>
@@ -2047,7 +2047,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G44" t="str">
         <v>5:58</v>
@@ -2073,7 +2073,7 @@
         <v>Charley - Serial Idealist (Official Video)</v>
       </c>
       <c r="B45" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C45" t="str">
         <v>https://www.youtube.com/watch?v=uVIuKbPJz0U</v>
@@ -2085,7 +2085,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G45" t="str">
         <v>3:26</v>
@@ -2529,7 +2529,7 @@
         <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop)</v>
       </c>
       <c r="B57" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C57" t="str">
         <v>https://www.youtube.com/watch?v=57a_OheOlDw</v>
@@ -2541,7 +2541,7 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G57" t="str">
         <v>3:20</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Marc Anthony - Make It With You (Visualizer)</v>
+        <v>Freya Skye - why'd you have to call</v>
       </c>
       <c r="B2" t="str">
-        <v>21 hours ago</v>
+        <v>5 hours ago</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=WHnz1jDrxw8</v>
+        <v>https://www.youtube.com/watch?v=75o0FuwCdaA</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-04</v>
@@ -451,13 +451,13 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>21 hours ago</v>
+        <v>5 hours ago</v>
       </c>
       <c r="G2" t="str">
-        <v>4:24</v>
+        <v>4:19</v>
       </c>
       <c r="H2" t="str">
-        <v>Marc Anthony</v>
+        <v>Freya Skye</v>
       </c>
       <c r="I2" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>Marc Anthony - Make It With You (Visualizer) - Marc Anthony</v>
+        <v>Freya Skye - why'd you have to call - Freya Skye</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Clara Mae - Never Been Yours ft. Bob John Holt</v>
+        <v>Jessie J - FEEL IT ON ME (Lyric Visualiser) (Official Lyric Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>1 day ago</v>
+        <v>5 hours ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=HtVuKBlBuPg</v>
+        <v>https://www.youtube.com/watch?v=DGmbe49F8aI</v>
       </c>
       <c r="D3" t="str">
         <v>2026-02-04</v>
@@ -489,13 +489,13 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>1 day ago</v>
+        <v>5 hours ago</v>
       </c>
       <c r="G3" t="str">
-        <v>2:33</v>
+        <v>2:30</v>
       </c>
       <c r="H3" t="str">
-        <v>Clara Mae</v>
+        <v>Jessie J</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Clara Mae - Never Been Yours ft. Bob John Holt - Clara Mae</v>
+        <v>Jessie J - FEEL IT ON ME (Lyric Visualiser) (Official Lyric Video) - Jessie J</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Metric - Victim of Luck (Official Music Video)</v>
+        <v>Marc Anthony - Make It With You (Visualizer)</v>
       </c>
       <c r="B4" t="str">
-        <v>1 day ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=shmhTOUd8mA</v>
+        <v>https://www.youtube.com/watch?v=WHnz1jDrxw8</v>
       </c>
       <c r="D4" t="str">
         <v>2026-02-04</v>
@@ -527,13 +527,13 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>1 day ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G4" t="str">
-        <v>3:25</v>
+        <v>4:24</v>
       </c>
       <c r="H4" t="str">
-        <v>metricmusic</v>
+        <v>Marc Anthony</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Metric - Victim of Luck (Official Music Video) - metricmusic</v>
+        <v>Marc Anthony - Make It With You (Visualizer) - Marc Anthony</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Kesha - RED FLAG. (Red Carpet) OFFICIAL MUSIC VIDEO</v>
+        <v>Clara Mae - Never Been Yours ft. Bob John Holt</v>
       </c>
       <c r="B5" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=pvrJ5RnPAEA</v>
+        <v>https://www.youtube.com/watch?v=HtVuKBlBuPg</v>
       </c>
       <c r="D5" t="str">
         <v>2026-02-04</v>
@@ -568,10 +568,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G5" t="str">
-        <v>3:41</v>
+        <v>2:33</v>
       </c>
       <c r="H5" t="str">
-        <v>kesha</v>
+        <v>Clara Mae</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Kesha - RED FLAG. (Red Carpet) OFFICIAL MUSIC VIDEO - kesha</v>
+        <v>Clara Mae - Never Been Yours ft. Bob John Holt - Clara Mae</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Studio)</v>
+        <v>Metric - Victim of Luck (Official Music Video)</v>
       </c>
       <c r="B6" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=mgsdQI-GVMM</v>
+        <v>https://www.youtube.com/watch?v=shmhTOUd8mA</v>
       </c>
       <c r="D6" t="str">
         <v>2026-02-04</v>
@@ -603,13 +603,13 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G6" t="str">
-        <v>3:19</v>
+        <v>3:25</v>
       </c>
       <c r="H6" t="str">
-        <v>David Guetta and Tones And I</v>
+        <v>metricmusic</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Studio) - David Guetta and Tones And I</v>
+        <v>Metric - Victim of Luck (Official Music Video) - metricmusic</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Vera Blue - Hold (Live on Sydney Harbour)</v>
+        <v>Kesha - RED FLAG. (Red Carpet) OFFICIAL MUSIC VIDEO</v>
       </c>
       <c r="B7" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=SYEwk-EZJPU</v>
+        <v>https://www.youtube.com/watch?v=pvrJ5RnPAEA</v>
       </c>
       <c r="D7" t="str">
         <v>2026-02-04</v>
@@ -641,13 +641,13 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G7" t="str">
-        <v>3:37</v>
+        <v>3:41</v>
       </c>
       <c r="H7" t="str">
-        <v>Vera Blue</v>
+        <v>kesha</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Vera Blue - Hold (Live on Sydney Harbour) - Vera Blue</v>
+        <v>Kesha - RED FLAG. (Red Carpet) OFFICIAL MUSIC VIDEO - kesha</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Bob Moses - Need You Tonight (INXS Cover) - Brooklyn Mirage 2023</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Studio)</v>
       </c>
       <c r="B8" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=CoCqPwDIBOA</v>
+        <v>https://www.youtube.com/watch?v=mgsdQI-GVMM</v>
       </c>
       <c r="D8" t="str">
         <v>2026-02-04</v>
@@ -682,10 +682,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G8" t="str">
-        <v>3:08</v>
+        <v>3:19</v>
       </c>
       <c r="H8" t="str">
-        <v>Bob Moses</v>
+        <v>David Guetta and Tones And I</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Bob Moses - Need You Tonight (INXS Cover) - Brooklyn Mirage 2023 - Bob Moses</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Studio) - David Guetta and Tones And I</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Marc Anthony - Un Mal Sueño (Visualizer)</v>
+        <v>Vera Blue - Hold (Live on Sydney Harbour)</v>
       </c>
       <c r="B9" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=18yZq5xtke4</v>
+        <v>https://www.youtube.com/watch?v=SYEwk-EZJPU</v>
       </c>
       <c r="D9" t="str">
         <v>2026-02-04</v>
@@ -720,10 +720,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G9" t="str">
-        <v>3:28</v>
+        <v>3:37</v>
       </c>
       <c r="H9" t="str">
-        <v>Marc Anthony</v>
+        <v>Vera Blue</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Marc Anthony - Un Mal Sueño (Visualizer) - Marc Anthony</v>
+        <v>Vera Blue - Hold (Live on Sydney Harbour) - Vera Blue</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Marc Anthony - Contra La Corriente (Visualizer)</v>
+        <v>Bob Moses - Need You Tonight (INXS Cover) - Brooklyn Mirage 2023</v>
       </c>
       <c r="B10" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=IGLmJ71oHhQ</v>
+        <v>https://www.youtube.com/watch?v=CoCqPwDIBOA</v>
       </c>
       <c r="D10" t="str">
         <v>2026-02-04</v>
@@ -758,10 +758,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G10" t="str">
-        <v>5:05</v>
+        <v>3:08</v>
       </c>
       <c r="H10" t="str">
-        <v>Marc Anthony</v>
+        <v>Bob Moses</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Marc Anthony - Contra La Corriente (Visualizer) - Marc Anthony</v>
+        <v>Bob Moses - Need You Tonight (INXS Cover) - Brooklyn Mirage 2023 - Bob Moses</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Loreen - Feels Like Heaven</v>
+        <v>Marc Anthony - Un Mal Sueño (Visualizer)</v>
       </c>
       <c r="B11" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=BQc97moyQBg</v>
+        <v>https://www.youtube.com/watch?v=18yZq5xtke4</v>
       </c>
       <c r="D11" t="str">
         <v>2026-02-04</v>
@@ -796,10 +796,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G11" t="str">
-        <v>3:14</v>
+        <v>3:28</v>
       </c>
       <c r="H11" t="str">
-        <v>Loreen</v>
+        <v>Marc Anthony</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Loreen - Feels Like Heaven - Loreen</v>
+        <v>Marc Anthony - Un Mal Sueño (Visualizer) - Marc Anthony</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Take That - Once You've Tasted Love (Live on Pebble Mill, 1992)</v>
+        <v>Marc Anthony - Contra La Corriente (Visualizer)</v>
       </c>
       <c r="B12" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=dOeoDOueESk</v>
+        <v>https://www.youtube.com/watch?v=IGLmJ71oHhQ</v>
       </c>
       <c r="D12" t="str">
         <v>2026-02-04</v>
@@ -834,10 +834,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G12" t="str">
-        <v>3:36</v>
+        <v>5:05</v>
       </c>
       <c r="H12" t="str">
-        <v>Take That</v>
+        <v>Marc Anthony</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Take That - Once You've Tasted Love (Live on Pebble Mill, 1992) - Take That</v>
+        <v>Marc Anthony - Contra La Corriente (Visualizer) - Marc Anthony</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Paul McCartney, Wings - Nineteen Hundred And Eighty Five (Visualiser)</v>
+        <v>Loreen - Feels Like Heaven</v>
       </c>
       <c r="B13" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=a4AIjUHuWpU</v>
+        <v>https://www.youtube.com/watch?v=BQc97moyQBg</v>
       </c>
       <c r="D13" t="str">
         <v>2026-02-04</v>
@@ -872,10 +872,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G13" t="str">
-        <v>5:31</v>
+        <v>3:14</v>
       </c>
       <c r="H13" t="str">
-        <v>PAUL McCARTNEY</v>
+        <v>Loreen</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Paul McCartney, Wings - Nineteen Hundred And Eighty Five (Visualiser) - PAUL McCARTNEY</v>
+        <v>Loreen - Feels Like Heaven - Loreen</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Nothing But Thieves - Sorry (Official Audio)</v>
+        <v>Take That - Once You've Tasted Love (Live on Pebble Mill, 1992)</v>
       </c>
       <c r="B14" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=D7QfVqo5YqY</v>
+        <v>https://www.youtube.com/watch?v=dOeoDOueESk</v>
       </c>
       <c r="D14" t="str">
         <v>2026-02-04</v>
@@ -910,10 +910,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G14" t="str">
-        <v>3:37</v>
+        <v>3:36</v>
       </c>
       <c r="H14" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Take That</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Nothing But Thieves - Sorry (Official Audio) - Nothing But Thieves</v>
+        <v>Take That - Once You've Tasted Love (Live on Pebble Mill, 1992) - Take That</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music</v>
+        <v>Paul McCartney, Wings - Nineteen Hundred And Eighty Five (Visualiser)</v>
       </c>
       <c r="B15" t="str">
-        <v>4 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=KdsHxyl4bE8</v>
+        <v>https://www.youtube.com/watch?v=a4AIjUHuWpU</v>
       </c>
       <c r="D15" t="str">
         <v>2026-02-04</v>
@@ -945,13 +945,13 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>4 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G15" t="str">
-        <v>4:58</v>
+        <v>5:31</v>
       </c>
       <c r="H15" t="str">
-        <v>The Warning</v>
+        <v>PAUL McCARTNEY</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music - The Warning</v>
+        <v>Paul McCartney, Wings - Nineteen Hundred And Eighty Five (Visualiser) - PAUL McCARTNEY</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield, CA (2026)</v>
+        <v>Nothing But Thieves - Sorry (Official Audio)</v>
       </c>
       <c r="B16" t="str">
-        <v>4 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=Mwkl_Cz_SG8</v>
+        <v>https://www.youtube.com/watch?v=D7QfVqo5YqY</v>
       </c>
       <c r="D16" t="str">
         <v>2026-02-04</v>
@@ -983,13 +983,13 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>4 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G16" t="str">
-        <v>5:08</v>
+        <v>3:37</v>
       </c>
       <c r="H16" t="str">
-        <v>The Offspring</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield, CA (2026) - The Offspring</v>
+        <v>Nothing But Thieves - Sorry (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered)</v>
+        <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music</v>
       </c>
       <c r="B17" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=I7a-pDZFE7U</v>
+        <v>https://www.youtube.com/watch?v=KdsHxyl4bE8</v>
       </c>
       <c r="D17" t="str">
         <v>2026-02-04</v>
@@ -1024,10 +1024,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>4:38</v>
+        <v>4:58</v>
       </c>
       <c r="H17" t="str">
-        <v>Roxette</v>
+        <v>The Warning</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered) - Roxette</v>
+        <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music - The Warning</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Live on The Graham Norton Show)</v>
+        <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield, CA (2026)</v>
       </c>
       <c r="B18" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=kGeamxRf8Gw</v>
+        <v>https://www.youtube.com/watch?v=Mwkl_Cz_SG8</v>
       </c>
       <c r="D18" t="str">
         <v>2026-02-04</v>
@@ -1062,10 +1062,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>3:50</v>
+        <v>5:08</v>
       </c>
       <c r="H18" t="str">
-        <v>Jessie Ware</v>
+        <v>The Offspring</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Live on The Graham Norton Show) - Jessie Ware</v>
+        <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield, CA (2026) - The Offspring</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>JOSEPH - Water in the Room (Official Music Video)</v>
+        <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered)</v>
       </c>
       <c r="B19" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=tNmT47k6MjM</v>
+        <v>https://www.youtube.com/watch?v=I7a-pDZFE7U</v>
       </c>
       <c r="D19" t="str">
         <v>2026-02-04</v>
@@ -1097,13 +1097,13 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>3:10</v>
+        <v>4:38</v>
       </c>
       <c r="H19" t="str">
-        <v>Joseph</v>
+        <v>Roxette</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>JOSEPH - Water in the Room (Official Music Video) - Joseph</v>
+        <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered) - Roxette</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Dean Lewis - I Am Getting Well (Lyric Video)</v>
+        <v>Jessie Ware - I Could Get Used To This (Live on The Graham Norton Show)</v>
       </c>
       <c r="B20" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=6ecgOSOMWzc</v>
+        <v>https://www.youtube.com/watch?v=kGeamxRf8Gw</v>
       </c>
       <c r="D20" t="str">
         <v>2026-02-04</v>
@@ -1135,13 +1135,13 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>2:44</v>
+        <v>3:50</v>
       </c>
       <c r="H20" t="str">
-        <v>Dean Lewis</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Dean Lewis - I Am Getting Well (Lyric Video) - Dean Lewis</v>
+        <v>Jessie Ware - I Could Get Used To This (Live on The Graham Norton Show) - Jessie Ware</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Take That - Take That and Party (Official HD Video)</v>
+        <v>JOSEPH - Water in the Room (Official Music Video)</v>
       </c>
       <c r="B21" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=DAerJcerikU</v>
+        <v>https://www.youtube.com/watch?v=tNmT47k6MjM</v>
       </c>
       <c r="D21" t="str">
         <v>2026-02-04</v>
@@ -1176,10 +1176,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>2:57</v>
+        <v>3:10</v>
       </c>
       <c r="H21" t="str">
-        <v>Take That</v>
+        <v>Joseph</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Take That - Take That and Party (Official HD Video) - Take That</v>
+        <v>JOSEPH - Water in the Room (Official Music Video) - Joseph</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>The Cure - Boys Don't Cry (86 Mix) (Official Lyric Video)</v>
+        <v>Dean Lewis - I Am Getting Well (Lyric Video)</v>
       </c>
       <c r="B22" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=isNztTjXQsQ</v>
+        <v>https://www.youtube.com/watch?v=6ecgOSOMWzc</v>
       </c>
       <c r="D22" t="str">
         <v>2026-02-04</v>
@@ -1214,10 +1214,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>2:39</v>
+        <v>2:44</v>
       </c>
       <c r="H22" t="str">
-        <v>The Cure</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>The Cure - Boys Don't Cry (86 Mix) (Official Lyric Video) - The Cure</v>
+        <v>Dean Lewis - I Am Getting Well (Lyric Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>The Kiffness &amp; Matisyahu - ONE DAY (ft. Andel and Nalyn) [OFFICIAL VIDEO]</v>
+        <v>Take That - Take That and Party (Official HD Video)</v>
       </c>
       <c r="B23" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=buS21tVq5r0</v>
+        <v>https://www.youtube.com/watch?v=DAerJcerikU</v>
       </c>
       <c r="D23" t="str">
         <v>2026-02-04</v>
@@ -1252,10 +1252,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>3:07</v>
+        <v>2:57</v>
       </c>
       <c r="H23" t="str">
-        <v>The Kiffness and Matisyahu</v>
+        <v>Take That</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>The Kiffness &amp; Matisyahu - ONE DAY (ft. Andel and Nalyn) [OFFICIAL VIDEO] - The Kiffness and Matisyahu</v>
+        <v>Take That - Take That and Party (Official HD Video) - Take That</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Paris Paloma - Good Girl [Official Music Video]</v>
+        <v>The Cure - Boys Don't Cry (86 Mix) (Official Lyric Video)</v>
       </c>
       <c r="B24" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=qhO6VMC-nx0</v>
+        <v>https://www.youtube.com/watch?v=isNztTjXQsQ</v>
       </c>
       <c r="D24" t="str">
         <v>2026-02-04</v>
@@ -1290,10 +1290,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>4:47</v>
+        <v>2:39</v>
       </c>
       <c r="H24" t="str">
-        <v>Paris Paloma</v>
+        <v>The Cure</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Paris Paloma - Good Girl [Official Music Video] - Paris Paloma</v>
+        <v>The Cure - Boys Don't Cry (86 Mix) (Official Lyric Video) - The Cure</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Zara Larsson - Lush Life (Official UGC Compilation Video)</v>
+        <v>The Kiffness &amp; Matisyahu - ONE DAY (ft. Andel and Nalyn) [OFFICIAL VIDEO]</v>
       </c>
       <c r="B25" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=FgAyfRnbbRs</v>
+        <v>https://www.youtube.com/watch?v=buS21tVq5r0</v>
       </c>
       <c r="D25" t="str">
         <v>2026-02-04</v>
@@ -1328,10 +1328,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>3:22</v>
+        <v>3:07</v>
       </c>
       <c r="H25" t="str">
-        <v>Zara Larsson</v>
+        <v>The Kiffness and Matisyahu</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Zara Larsson - Lush Life (Official UGC Compilation Video) - Zara Larsson</v>
+        <v>The Kiffness &amp; Matisyahu - ONE DAY (ft. Andel and Nalyn) [OFFICIAL VIDEO] - The Kiffness and Matisyahu</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Only The Poets - Monumental</v>
+        <v>Paris Paloma - Good Girl [Official Music Video]</v>
       </c>
       <c r="B26" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=nwXiAjjl6NE</v>
+        <v>https://www.youtube.com/watch?v=qhO6VMC-nx0</v>
       </c>
       <c r="D26" t="str">
         <v>2026-02-04</v>
@@ -1366,10 +1366,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>2:48</v>
+        <v>4:47</v>
       </c>
       <c r="H26" t="str">
-        <v>only the poets</v>
+        <v>Paris Paloma</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Only The Poets - Monumental - only the poets</v>
+        <v>Paris Paloma - Good Girl [Official Music Video] - Paris Paloma</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Katelyn Tarver - So Am I (Official Music Video)</v>
+        <v>Zara Larsson - Lush Life (Official UGC Compilation Video)</v>
       </c>
       <c r="B27" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=MjUiVPzMQHw</v>
+        <v>https://www.youtube.com/watch?v=FgAyfRnbbRs</v>
       </c>
       <c r="D27" t="str">
         <v>2026-02-04</v>
@@ -1404,10 +1404,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>2:52</v>
+        <v>3:22</v>
       </c>
       <c r="H27" t="str">
-        <v>Katelyn Tarver</v>
+        <v>Zara Larsson</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Katelyn Tarver - So Am I (Official Music Video) - Katelyn Tarver</v>
+        <v>Zara Larsson - Lush Life (Official UGC Compilation Video) - Zara Larsson</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>David Guetta, TeddySwims, Tones And I - Gone Gone Gone (Unplugged) [Visualizer]</v>
+        <v>Only The Poets - Monumental</v>
       </c>
       <c r="B28" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=eWglDE7O5r8</v>
+        <v>https://www.youtube.com/watch?v=nwXiAjjl6NE</v>
       </c>
       <c r="D28" t="str">
         <v>2026-02-04</v>
@@ -1442,10 +1442,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>3:33</v>
+        <v>2:48</v>
       </c>
       <c r="H28" t="str">
-        <v>David Guetta</v>
+        <v>only the poets</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>David Guetta, TeddySwims, Tones And I - Gone Gone Gone (Unplugged) [Visualizer] - David Guetta</v>
+        <v>Only The Poets - Monumental - only the poets</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>SANTOS BRAVOS “KAWASAKI” Performance Video</v>
+        <v>Katelyn Tarver - So Am I (Official Music Video)</v>
       </c>
       <c r="B29" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=Cmy8CsYIUL0</v>
+        <v>https://www.youtube.com/watch?v=MjUiVPzMQHw</v>
       </c>
       <c r="D29" t="str">
         <v>2026-02-04</v>
@@ -1480,10 +1480,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>2:41</v>
+        <v>2:52</v>
       </c>
       <c r="H29" t="str">
-        <v>HYBE LABELS and SANTOS BRAVOS</v>
+        <v>Katelyn Tarver</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>SANTOS BRAVOS “KAWASAKI” Performance Video - HYBE LABELS and SANTOS BRAVOS</v>
+        <v>Katelyn Tarver - So Am I (Official Music Video) - Katelyn Tarver</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Ella Langley - Dandelion (Official Visualizer)</v>
+        <v>David Guetta, TeddySwims, Tones And I - Gone Gone Gone (Unplugged) [Visualizer]</v>
       </c>
       <c r="B30" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=sf6eRmInk1s</v>
+        <v>https://www.youtube.com/watch?v=eWglDE7O5r8</v>
       </c>
       <c r="D30" t="str">
         <v>2026-02-04</v>
@@ -1518,10 +1518,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>4:01</v>
+        <v>3:33</v>
       </c>
       <c r="H30" t="str">
-        <v>Ella Langley</v>
+        <v>David Guetta</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Ella Langley - Dandelion (Official Visualizer) - Ella Langley</v>
+        <v>David Guetta, TeddySwims, Tones And I - Gone Gone Gone (Unplugged) [Visualizer] - David Guetta</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Dogpark - Dandelion (Official Music Video)</v>
+        <v>SANTOS BRAVOS “KAWASAKI” Performance Video</v>
       </c>
       <c r="B31" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=fv9prIYHHzk</v>
+        <v>https://www.youtube.com/watch?v=Cmy8CsYIUL0</v>
       </c>
       <c r="D31" t="str">
         <v>2026-02-04</v>
@@ -1556,10 +1556,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>3:16</v>
+        <v>2:41</v>
       </c>
       <c r="H31" t="str">
-        <v>Dogpark</v>
+        <v>HYBE LABELS and SANTOS BRAVOS</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Dogpark - Dandelion (Official Music Video) - Dogpark</v>
+        <v>SANTOS BRAVOS “KAWASAKI” Performance Video - HYBE LABELS and SANTOS BRAVOS</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Lauren Spencer Smith - Natural Disaster (Visualizer)</v>
+        <v>Ella Langley - Dandelion (Official Visualizer)</v>
       </c>
       <c r="B32" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=T9YvLA2cdZs</v>
+        <v>https://www.youtube.com/watch?v=sf6eRmInk1s</v>
       </c>
       <c r="D32" t="str">
         <v>2026-02-04</v>
@@ -1594,10 +1594,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>3:03</v>
+        <v>4:01</v>
       </c>
       <c r="H32" t="str">
-        <v>Lauren Spencer Smith</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Lauren Spencer Smith - Natural Disaster (Visualizer) - Lauren Spencer Smith</v>
+        <v>Ella Langley - Dandelion (Official Visualizer) - Ella Langley</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>ERNEST - Lorelei (Official Music Video)</v>
+        <v>Dogpark - Dandelion (Official Music Video)</v>
       </c>
       <c r="B33" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=dPWc_6IdDJk</v>
+        <v>https://www.youtube.com/watch?v=fv9prIYHHzk</v>
       </c>
       <c r="D33" t="str">
         <v>2026-02-04</v>
@@ -1632,10 +1632,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>2:41</v>
+        <v>3:16</v>
       </c>
       <c r="H33" t="str">
-        <v>ERNEST</v>
+        <v>Dogpark</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>ERNEST - Lorelei (Official Music Video) - ERNEST</v>
+        <v>Dogpark - Dandelion (Official Music Video) - Dogpark</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Labrinth - I Keep My Promises (Official Audio)</v>
+        <v>Lauren Spencer Smith - Natural Disaster (Visualizer)</v>
       </c>
       <c r="B34" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=CV5rR9JZK-0</v>
+        <v>https://www.youtube.com/watch?v=T9YvLA2cdZs</v>
       </c>
       <c r="D34" t="str">
         <v>2026-02-04</v>
@@ -1670,10 +1670,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>3:05</v>
+        <v>3:03</v>
       </c>
       <c r="H34" t="str">
-        <v>Labrinth</v>
+        <v>Lauren Spencer Smith</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Labrinth - I Keep My Promises (Official Audio) - Labrinth</v>
+        <v>Lauren Spencer Smith - Natural Disaster (Visualizer) - Lauren Spencer Smith</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Grace VanderWaal - Prettier (Official Lyric Video)</v>
+        <v>ERNEST - Lorelei (Official Music Video)</v>
       </c>
       <c r="B35" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=9HwTj3NZ16E</v>
+        <v>https://www.youtube.com/watch?v=dPWc_6IdDJk</v>
       </c>
       <c r="D35" t="str">
         <v>2026-02-04</v>
@@ -1708,10 +1708,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>2:46</v>
+        <v>2:41</v>
       </c>
       <c r="H35" t="str">
-        <v>Grace VanderWaal</v>
+        <v>ERNEST</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Grace VanderWaal - Prettier (Official Lyric Video) - Grace VanderWaal</v>
+        <v>ERNEST - Lorelei (Official Music Video) - ERNEST</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>VOILÀ - Frozen Lake (Official Lyric Video)</v>
+        <v>Labrinth - I Keep My Promises (Official Audio)</v>
       </c>
       <c r="B36" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=Lmus-UbL1H0</v>
+        <v>https://www.youtube.com/watch?v=CV5rR9JZK-0</v>
       </c>
       <c r="D36" t="str">
         <v>2026-02-04</v>
@@ -1746,10 +1746,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>3:32</v>
+        <v>3:05</v>
       </c>
       <c r="H36" t="str">
-        <v>VOILÀ</v>
+        <v>Labrinth</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>VOILÀ - Frozen Lake (Official Lyric Video) - VOILÀ</v>
+        <v>Labrinth - I Keep My Promises (Official Audio) - Labrinth</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Cannons - Starlight (Official Video)</v>
+        <v>Grace VanderWaal - Prettier (Official Lyric Video)</v>
       </c>
       <c r="B37" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=bu6WSMDDPGY</v>
+        <v>https://www.youtube.com/watch?v=9HwTj3NZ16E</v>
       </c>
       <c r="D37" t="str">
         <v>2026-02-04</v>
@@ -1784,10 +1784,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>3:42</v>
+        <v>2:46</v>
       </c>
       <c r="H37" t="str">
-        <v>Cannons</v>
+        <v>Grace VanderWaal</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Cannons - Starlight (Official Video) - Cannons</v>
+        <v>Grace VanderWaal - Prettier (Official Lyric Video) - Grace VanderWaal</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Kylie Morgan - Like My Own (Official Video)</v>
+        <v>VOILÀ - Frozen Lake (Official Lyric Video)</v>
       </c>
       <c r="B38" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=zcYeoGBglC0</v>
+        <v>https://www.youtube.com/watch?v=Lmus-UbL1H0</v>
       </c>
       <c r="D38" t="str">
         <v>2026-02-04</v>
@@ -1822,10 +1822,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>2:38</v>
+        <v>3:32</v>
       </c>
       <c r="H38" t="str">
-        <v>Kylie Morgan</v>
+        <v>VOILÀ</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Kylie Morgan - Like My Own (Official Video) - Kylie Morgan</v>
+        <v>VOILÀ - Frozen Lake (Official Lyric Video) - VOILÀ</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Lizzy McAlpine - House of the Rising Sun (Audio)</v>
+        <v>Cannons - Starlight (Official Video)</v>
       </c>
       <c r="B39" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=3igYRj82EiU</v>
+        <v>https://www.youtube.com/watch?v=bu6WSMDDPGY</v>
       </c>
       <c r="D39" t="str">
         <v>2026-02-04</v>
@@ -1860,10 +1860,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>3:10</v>
+        <v>3:42</v>
       </c>
       <c r="H39" t="str">
-        <v>Lizzy McAlpine</v>
+        <v>Cannons</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Lizzy McAlpine - House of the Rising Sun (Audio) - Lizzy McAlpine</v>
+        <v>Cannons - Starlight (Official Video) - Cannons</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Willie Nelson - Heart Of America (From The Gray House Original Soundtrack)</v>
+        <v>Kylie Morgan - Like My Own (Official Video)</v>
       </c>
       <c r="B40" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=0bhcO4Yphuo</v>
+        <v>https://www.youtube.com/watch?v=zcYeoGBglC0</v>
       </c>
       <c r="D40" t="str">
         <v>2026-02-04</v>
@@ -1898,10 +1898,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>3:57</v>
+        <v>2:38</v>
       </c>
       <c r="H40" t="str">
-        <v>Willie Nelson</v>
+        <v>Kylie Morgan</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Willie Nelson - Heart Of America (From The Gray House Original Soundtrack) - Willie Nelson</v>
+        <v>Kylie Morgan - Like My Own (Official Video) - Kylie Morgan</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Jeremy Camp - No Survivors (Live) ft. Skillet</v>
+        <v>Lizzy McAlpine - House of the Rising Sun (Audio)</v>
       </c>
       <c r="B41" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=Jjz1wFe5dMo</v>
+        <v>https://www.youtube.com/watch?v=3igYRj82EiU</v>
       </c>
       <c r="D41" t="str">
         <v>2026-02-04</v>
@@ -1936,10 +1936,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>2:19</v>
+        <v>3:10</v>
       </c>
       <c r="H41" t="str">
-        <v>JeremyCampMusic</v>
+        <v>Lizzy McAlpine</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Jeremy Camp - No Survivors (Live) ft. Skillet - JeremyCampMusic</v>
+        <v>Lizzy McAlpine - House of the Rising Sun (Audio) - Lizzy McAlpine</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>India Martinez, Coro ArteSí de Olvidados - Niño Sin Miedo</v>
+        <v>Willie Nelson - Heart Of America (From The Gray House Original Soundtrack)</v>
       </c>
       <c r="B42" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=Vug_FPbXe9E</v>
+        <v>https://www.youtube.com/watch?v=0bhcO4Yphuo</v>
       </c>
       <c r="D42" t="str">
         <v>2026-02-04</v>
@@ -1974,10 +1974,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>4:04</v>
+        <v>3:57</v>
       </c>
       <c r="H42" t="str">
-        <v>India Martínez</v>
+        <v>Willie Nelson</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>India Martinez, Coro ArteSí de Olvidados - Niño Sin Miedo - India Martínez</v>
+        <v>Willie Nelson - Heart Of America (From The Gray House Original Soundtrack) - Willie Nelson</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Chelsea Cutler - BAD (Official Lyric Video)</v>
+        <v>Jeremy Camp - No Survivors (Live) ft. Skillet</v>
       </c>
       <c r="B43" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=ZIW2vA3Zs1U</v>
+        <v>https://www.youtube.com/watch?v=Jjz1wFe5dMo</v>
       </c>
       <c r="D43" t="str">
         <v>2026-02-04</v>
@@ -2012,10 +2012,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>2:16</v>
+        <v>2:19</v>
       </c>
       <c r="H43" t="str">
-        <v>Chelsea Cutler</v>
+        <v>JeremyCampMusic</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Chelsea Cutler - BAD (Official Lyric Video) - Chelsea Cutler</v>
+        <v>Jeremy Camp - No Survivors (Live) ft. Skillet - JeremyCampMusic</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>TINI - FUTTTURA LIVE - el cielo + fresa</v>
+        <v>India Martinez, Coro ArteSí de Olvidados - Niño Sin Miedo</v>
       </c>
       <c r="B44" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=q_rrgJZAdNg</v>
+        <v>https://www.youtube.com/watch?v=Vug_FPbXe9E</v>
       </c>
       <c r="D44" t="str">
         <v>2026-02-04</v>
@@ -2047,13 +2047,13 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>5:58</v>
+        <v>4:04</v>
       </c>
       <c r="H44" t="str">
-        <v>TINI</v>
+        <v>India Martínez</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>TINI - FUTTTURA LIVE - el cielo + fresa - TINI</v>
+        <v>India Martinez, Coro ArteSí de Olvidados - Niño Sin Miedo - India Martínez</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Charley - Serial Idealist (Official Video)</v>
+        <v>Chelsea Cutler - BAD (Official Lyric Video)</v>
       </c>
       <c r="B45" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=uVIuKbPJz0U</v>
+        <v>https://www.youtube.com/watch?v=ZIW2vA3Zs1U</v>
       </c>
       <c r="D45" t="str">
         <v>2026-02-04</v>
@@ -2085,13 +2085,13 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>3:26</v>
+        <v>2:16</v>
       </c>
       <c r="H45" t="str">
-        <v>Charley</v>
+        <v>Chelsea Cutler</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Charley - Serial Idealist (Official Video) - Charley</v>
+        <v>Chelsea Cutler - BAD (Official Lyric Video) - Chelsea Cutler</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Demi Lovato - Ghost (Live)</v>
+        <v>TINI - FUTTTURA LIVE - el cielo + fresa</v>
       </c>
       <c r="B46" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=E-ECwdRndVA</v>
+        <v>https://www.youtube.com/watch?v=q_rrgJZAdNg</v>
       </c>
       <c r="D46" t="str">
         <v>2026-02-04</v>
@@ -2126,10 +2126,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>4:05</v>
+        <v>5:58</v>
       </c>
       <c r="H46" t="str">
-        <v>Demi Lovato</v>
+        <v>TINI</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Demi Lovato - Ghost (Live) - Demi Lovato</v>
+        <v>TINI - FUTTTURA LIVE - el cielo + fresa - TINI</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Teddy Swims - Need You More (Live - Green Room Sessions)</v>
+        <v>Charley - Serial Idealist (Official Video)</v>
       </c>
       <c r="B47" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=1ugf5aaY4pY</v>
+        <v>https://www.youtube.com/watch?v=uVIuKbPJz0U</v>
       </c>
       <c r="D47" t="str">
         <v>2026-02-04</v>
@@ -2164,10 +2164,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>3:16</v>
+        <v>3:26</v>
       </c>
       <c r="H47" t="str">
-        <v>Teddy Swims</v>
+        <v>Charley</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Teddy Swims - Need You More (Live - Green Room Sessions) - Teddy Swims</v>
+        <v>Charley - Serial Idealist (Official Video) - Charley</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Beck - Love (Audio)</v>
+        <v>Demi Lovato - Ghost (Live)</v>
       </c>
       <c r="B48" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=ByABj3Xof1I</v>
+        <v>https://www.youtube.com/watch?v=E-ECwdRndVA</v>
       </c>
       <c r="D48" t="str">
         <v>2026-02-04</v>
@@ -2202,10 +2202,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>3:14</v>
+        <v>4:05</v>
       </c>
       <c r="H48" t="str">
-        <v>Beck</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Beck - Love (Audio) - Beck</v>
+        <v>Demi Lovato - Ghost (Live) - Demi Lovato</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>The Offspring - Looking Out For #1 | Live in Spokane, WA (2026)</v>
+        <v>Teddy Swims - Need You More (Live - Green Room Sessions)</v>
       </c>
       <c r="B49" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=2HSbo51EFNg</v>
+        <v>https://www.youtube.com/watch?v=1ugf5aaY4pY</v>
       </c>
       <c r="D49" t="str">
         <v>2026-02-04</v>
@@ -2237,13 +2237,13 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>2:57</v>
+        <v>3:16</v>
       </c>
       <c r="H49" t="str">
-        <v>The Offspring</v>
+        <v>Teddy Swims</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>The Offspring - Looking Out For #1 | Live in Spokane, WA (2026) - The Offspring</v>
+        <v>Teddy Swims - Need You More (Live - Green Room Sessions) - Teddy Swims</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show</v>
+        <v>Beck - Love (Audio)</v>
       </c>
       <c r="B50" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=ylifHFJWJ_c</v>
+        <v>https://www.youtube.com/watch?v=ByABj3Xof1I</v>
       </c>
       <c r="D50" t="str">
         <v>2026-02-04</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>4:10</v>
+        <v>3:14</v>
       </c>
       <c r="H50" t="str">
-        <v>Sophie Ellis-Bextor</v>
+        <v>Beck</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show - Sophie Ellis-Bextor</v>
+        <v>Beck - Love (Audio) - Beck</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Jason Derulo - Sexy For Me [Official Music Video]</v>
+        <v>The Offspring - Looking Out For #1 | Live in Spokane, WA (2026)</v>
       </c>
       <c r="B51" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=9ST-eBNL0NU</v>
+        <v>https://www.youtube.com/watch?v=2HSbo51EFNg</v>
       </c>
       <c r="D51" t="str">
         <v>2026-02-04</v>
@@ -2316,10 +2316,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>2:10</v>
+        <v>2:57</v>
       </c>
       <c r="H51" t="str">
-        <v>Jason Derulo</v>
+        <v>The Offspring</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Jason Derulo - Sexy For Me [Official Music Video] - Jason Derulo</v>
+        <v>The Offspring - Looking Out For #1 | Live in Spokane, WA (2026) - The Offspring</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Lights - COME GET YOUR GIRL</v>
+        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show</v>
       </c>
       <c r="B52" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=EhzX2y5MpSM</v>
+        <v>https://www.youtube.com/watch?v=ylifHFJWJ_c</v>
       </c>
       <c r="D52" t="str">
         <v>2026-02-04</v>
@@ -2354,10 +2354,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>3:52</v>
+        <v>4:10</v>
       </c>
       <c r="H52" t="str">
-        <v>lights</v>
+        <v>Sophie Ellis-Bextor</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Lights - COME GET YOUR GIRL - lights</v>
+        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show - Sophie Ellis-Bextor</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video)</v>
+        <v>Jason Derulo - Sexy For Me [Official Music Video]</v>
       </c>
       <c r="B53" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=yUAvfo8fpuU</v>
+        <v>https://www.youtube.com/watch?v=9ST-eBNL0NU</v>
       </c>
       <c r="D53" t="str">
         <v>2026-02-04</v>
@@ -2392,10 +2392,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>3:50</v>
+        <v>2:10</v>
       </c>
       <c r="H53" t="str">
-        <v>Telenova</v>
+        <v>Jason Derulo</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video) - Telenova</v>
+        <v>Jason Derulo - Sexy For Me [Official Music Video] - Jason Derulo</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>I Had To Explain "How Music Works" LIVE In Concert</v>
+        <v>Lights - COME GET YOUR GIRL</v>
       </c>
       <c r="B54" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=KnsBdAM3HqY</v>
+        <v>https://www.youtube.com/watch?v=EhzX2y5MpSM</v>
       </c>
       <c r="D54" t="str">
         <v>2026-02-04</v>
@@ -2430,10 +2430,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G54" t="str">
-        <v>5:32</v>
+        <v>3:52</v>
       </c>
       <c r="H54" t="str">
-        <v>Marcin</v>
+        <v>lights</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>I Had To Explain "How Music Works" LIVE In Concert - Marcin</v>
+        <v>Lights - COME GET YOUR GIRL - lights</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>We Three - Drunk Driving (Official Music Video)</v>
+        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video)</v>
       </c>
       <c r="B55" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=BTqRGxSX6AQ</v>
+        <v>https://www.youtube.com/watch?v=yUAvfo8fpuU</v>
       </c>
       <c r="D55" t="str">
         <v>2026-02-04</v>
@@ -2468,10 +2468,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G55" t="str">
-        <v>4:27</v>
+        <v>3:50</v>
       </c>
       <c r="H55" t="str">
-        <v>We Three</v>
+        <v>Telenova</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>We Three - Drunk Driving (Official Music Video) - We Three</v>
+        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video) - Telenova</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Timebelle - Top of the World (Mood Video)</v>
+        <v>I Had To Explain "How Music Works" LIVE In Concert</v>
       </c>
       <c r="B56" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=r9KyYK_E34s</v>
+        <v>https://www.youtube.com/watch?v=KnsBdAM3HqY</v>
       </c>
       <c r="D56" t="str">
         <v>2026-02-04</v>
@@ -2503,13 +2503,13 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G56" t="str">
-        <v>3:01</v>
+        <v>5:32</v>
       </c>
       <c r="H56" t="str">
-        <v>Timebelle Official</v>
+        <v>Marcin</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Timebelle - Top of the World (Mood Video) - Timebelle Official</v>
+        <v>I Had To Explain "How Music Works" LIVE In Concert - Marcin</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop)</v>
+        <v>We Three - Drunk Driving (Official Music Video)</v>
       </c>
       <c r="B57" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=57a_OheOlDw</v>
+        <v>https://www.youtube.com/watch?v=BTqRGxSX6AQ</v>
       </c>
       <c r="D57" t="str">
         <v>2026-02-04</v>
@@ -2541,13 +2541,13 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G57" t="str">
-        <v>3:20</v>
+        <v>4:27</v>
       </c>
       <c r="H57" t="str">
-        <v>David Guetta and Tones And I</v>
+        <v>We Three</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop) - David Guetta and Tones And I</v>
+        <v>We Three - Drunk Driving (Official Music Video) - We Three</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Clinton Kane - this is my last love song to you (Official Lyric Video)</v>
+        <v>Timebelle - Top of the World (Mood Video)</v>
       </c>
       <c r="B58" t="str">
-        <v>11 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=-5Aa8NTiRqE</v>
+        <v>https://www.youtube.com/watch?v=r9KyYK_E34s</v>
       </c>
       <c r="D58" t="str">
         <v>2026-02-04</v>
@@ -2579,13 +2579,13 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>11 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G58" t="str">
-        <v>3:34</v>
+        <v>3:01</v>
       </c>
       <c r="H58" t="str">
-        <v>Clinton Kane</v>
+        <v>Timebelle Official</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Clinton Kane - this is my last love song to you (Official Lyric Video) - Clinton Kane</v>
+        <v>Timebelle - Top of the World (Mood Video) - Timebelle Official</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>SIENNA SPIRO - Die On This Hill (Official Music Video)</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop)</v>
       </c>
       <c r="B59" t="str">
-        <v>12 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=5RNy_1odv20</v>
+        <v>https://www.youtube.com/watch?v=57a_OheOlDw</v>
       </c>
       <c r="D59" t="str">
         <v>2026-02-04</v>
@@ -2617,13 +2617,13 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>12 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G59" t="str">
-        <v>4:01</v>
+        <v>3:20</v>
       </c>
       <c r="H59" t="str">
-        <v>Lyrical Lemonade and SIENNA SPIRO</v>
+        <v>David Guetta and Tones And I</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>SIENNA SPIRO - Die On This Hill (Official Music Video) - Lyrical Lemonade and SIENNA SPIRO</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop) - David Guetta and Tones And I</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Amazon Music presents: Sienna Spiro - You Stole The Show</v>
+        <v>Clinton Kane - this is my last love song to you (Official Lyric Video)</v>
       </c>
       <c r="B60" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=stYIRyCLN4Y</v>
+        <v>https://www.youtube.com/watch?v=-5Aa8NTiRqE</v>
       </c>
       <c r="D60" t="str">
         <v>2026-02-04</v>
@@ -2655,13 +2655,13 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G60" t="str">
-        <v>3:24</v>
+        <v>3:34</v>
       </c>
       <c r="H60" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>Clinton Kane</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Amazon Music presents: Sienna Spiro - You Stole The Show - SIENNA SPIRO</v>
+        <v>Clinton Kane - this is my last love song to you (Official Lyric Video) - Clinton Kane</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Harry Styles - Aperture (Official Video)</v>
+        <v>SIENNA SPIRO - Die On This Hill (Official Music Video)</v>
       </c>
       <c r="B61" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=7sxVHYZ_PnA</v>
+        <v>https://www.youtube.com/watch?v=5RNy_1odv20</v>
       </c>
       <c r="D61" t="str">
         <v>2026-02-04</v>
@@ -2696,10 +2696,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G61" t="str">
-        <v>5:52</v>
+        <v>4:01</v>
       </c>
       <c r="H61" t="str">
-        <v>Harry Styles</v>
+        <v>Lyrical Lemonade and SIENNA SPIRO</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Harry Styles - Aperture (Official Video) - Harry Styles</v>
+        <v>SIENNA SPIRO - Die On This Hill (Official Music Video) - Lyrical Lemonade and SIENNA SPIRO</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Neal Francis - Back It Up (Live At The Salt Shed)</v>
+        <v>Amazon Music presents: Sienna Spiro - You Stole The Show</v>
       </c>
       <c r="B62" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=46iZEdsxjC0</v>
+        <v>https://www.youtube.com/watch?v=stYIRyCLN4Y</v>
       </c>
       <c r="D62" t="str">
         <v>2026-02-04</v>
@@ -2734,10 +2734,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G62" t="str">
-        <v>5:01</v>
+        <v>3:24</v>
       </c>
       <c r="H62" t="str">
-        <v>Neal Francis</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Neal Francis - Back It Up (Live At The Salt Shed) - Neal Francis</v>
+        <v>Amazon Music presents: Sienna Spiro - You Stole The Show - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
+        <v>Harry Styles - Aperture (Official Video)</v>
       </c>
       <c r="B63" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=K2nG1Uukz7E</v>
+        <v>https://www.youtube.com/watch?v=7sxVHYZ_PnA</v>
       </c>
       <c r="D63" t="str">
         <v>2026-02-04</v>
@@ -2772,10 +2772,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G63" t="str">
-        <v>4:12</v>
+        <v>5:52</v>
       </c>
       <c r="H63" t="str">
-        <v>OfficiallyExtreme</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
+        <v>Harry Styles - Aperture (Official Video) - Harry Styles</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Holly Humberstone - To Love Somebody (Official Video)</v>
+        <v>Neal Francis - Back It Up (Live At The Salt Shed)</v>
       </c>
       <c r="B64" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
+        <v>https://www.youtube.com/watch?v=46iZEdsxjC0</v>
       </c>
       <c r="D64" t="str">
         <v>2026-02-04</v>
@@ -2810,10 +2810,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G64" t="str">
-        <v>3:59</v>
+        <v>5:01</v>
       </c>
       <c r="H64" t="str">
-        <v>Holly Humberstone</v>
+        <v>Neal Francis</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Holly Humberstone - To Love Somebody (Official Video) - Holly Humberstone</v>
+        <v>Neal Francis - Back It Up (Live At The Salt Shed) - Neal Francis</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
       </c>
       <c r="B65" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
+        <v>https://www.youtube.com/watch?v=K2nG1Uukz7E</v>
       </c>
       <c r="D65" t="str">
         <v>2026-02-04</v>
@@ -2848,10 +2848,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G65" t="str">
-        <v>2:56</v>
+        <v>4:12</v>
       </c>
       <c r="H65" t="str">
-        <v>Cliff Richard</v>
+        <v>OfficiallyExtreme</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018) - Cliff Richard</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
+        <v>Holly Humberstone - To Love Somebody (Official Video)</v>
       </c>
       <c r="B66" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
+        <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
       </c>
       <c r="D66" t="str">
         <v>2026-02-04</v>
@@ -2886,10 +2886,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G66" t="str">
-        <v>3:46</v>
+        <v>3:59</v>
       </c>
       <c r="H66" t="str">
-        <v>Jessie Ware</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Official Video) - Jessie Ware</v>
+        <v>Holly Humberstone - To Love Somebody (Official Video) - Holly Humberstone</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Bella White - Dream Song (Official Audio)</v>
+        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
       </c>
       <c r="B67" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
+        <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
       </c>
       <c r="D67" t="str">
         <v>2026-02-04</v>
@@ -2924,10 +2924,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G67" t="str">
-        <v>4:37</v>
+        <v>2:56</v>
       </c>
       <c r="H67" t="str">
-        <v>Bella White</v>
+        <v>Cliff Richard</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Bella White - Dream Song (Official Audio) - Bella White</v>
+        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018) - Cliff Richard</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Ryan Wright - Film School Kids (Official Video)</v>
+        <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
       </c>
       <c r="B68" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=pnAz9RwGSek</v>
+        <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
       </c>
       <c r="D68" t="str">
         <v>2026-02-04</v>
@@ -2962,10 +2962,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G68" t="str">
-        <v>4:06</v>
+        <v>3:46</v>
       </c>
       <c r="H68" t="str">
-        <v>Ryan Wright</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Ryan Wright - Film School Kids (Official Video) - Ryan Wright</v>
+        <v>Jessie Ware - I Could Get Used To This (Official Video) - Jessie Ware</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer)</v>
+        <v>Bella White - Dream Song (Official Audio)</v>
       </c>
       <c r="B69" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=u7aPv2saz_I</v>
+        <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
       </c>
       <c r="D69" t="str">
         <v>2026-02-04</v>
@@ -3000,10 +3000,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G69" t="str">
-        <v>3:54</v>
+        <v>4:37</v>
       </c>
       <c r="H69" t="str">
-        <v>Dove Cameron</v>
+        <v>Bella White</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer) - Dove Cameron</v>
+        <v>Bella White - Dream Song (Official Audio) - Bella White</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video)</v>
+        <v>Ryan Wright - Film School Kids (Official Video)</v>
       </c>
       <c r="B70" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=WGb8KVdqs6k</v>
+        <v>https://www.youtube.com/watch?v=pnAz9RwGSek</v>
       </c>
       <c r="D70" t="str">
         <v>2026-02-04</v>
@@ -3038,10 +3038,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G70" t="str">
-        <v>4:10</v>
+        <v>4:06</v>
       </c>
       <c r="H70" t="str">
-        <v>Parker McCollum</v>
+        <v>Ryan Wright</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video) - Parker McCollum</v>
+        <v>Ryan Wright - Film School Kids (Official Video) - Ryan Wright</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video)</v>
+        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer)</v>
       </c>
       <c r="B71" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=X1ZeY4Y3l1M</v>
+        <v>https://www.youtube.com/watch?v=u7aPv2saz_I</v>
       </c>
       <c r="D71" t="str">
         <v>2026-02-04</v>
@@ -3076,10 +3076,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G71" t="str">
-        <v>3:26</v>
+        <v>3:54</v>
       </c>
       <c r="H71" t="str">
-        <v>Matt Hansen</v>
+        <v>Dove Cameron</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video) - Matt Hansen</v>
+        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer) - Dove Cameron</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Louis Tomlinson - Imposter (Official Video)</v>
+        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video)</v>
       </c>
       <c r="B72" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=rzuD5szQhso</v>
+        <v>https://www.youtube.com/watch?v=WGb8KVdqs6k</v>
       </c>
       <c r="D72" t="str">
         <v>2026-02-04</v>
@@ -3111,13 +3111,13 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G72" t="str">
-        <v>2:56</v>
+        <v>4:10</v>
       </c>
       <c r="H72" t="str">
-        <v>Louis Tomlinson</v>
+        <v>Parker McCollum</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Louis Tomlinson - Imposter (Official Video) - Louis Tomlinson</v>
+        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video) - Parker McCollum</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Mitchell Tenpenny - You Phase (Official Music Video)</v>
+        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video)</v>
       </c>
       <c r="B73" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=UPuK6wV5Zco</v>
+        <v>https://www.youtube.com/watch?v=X1ZeY4Y3l1M</v>
       </c>
       <c r="D73" t="str">
         <v>2026-02-04</v>
@@ -3152,10 +3152,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G73" t="str">
-        <v>2:56</v>
+        <v>3:26</v>
       </c>
       <c r="H73" t="str">
-        <v>Mitchell Tenpenny</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Mitchell Tenpenny - You Phase (Official Music Video) - Mitchell Tenpenny</v>
+        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video) - Matt Hansen</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Tauren Wells - Breathe On It (Official Lyric Video)</v>
+        <v>Louis Tomlinson - Imposter (Official Video)</v>
       </c>
       <c r="B74" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=9hW9sNMn2A0</v>
+        <v>https://www.youtube.com/watch?v=rzuD5szQhso</v>
       </c>
       <c r="D74" t="str">
         <v>2026-02-04</v>
@@ -3187,13 +3187,13 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G74" t="str">
-        <v>4:01</v>
+        <v>2:56</v>
       </c>
       <c r="H74" t="str">
-        <v>Tauren Wells</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Tauren Wells - Breathe On It (Official Lyric Video) - Tauren Wells</v>
+        <v>Louis Tomlinson - Imposter (Official Video) - Louis Tomlinson</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Maiah Manser - Feeling it All (Official Music Video)</v>
+        <v>Mitchell Tenpenny - You Phase (Official Music Video)</v>
       </c>
       <c r="B75" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=JMYvXleIwfU</v>
+        <v>https://www.youtube.com/watch?v=UPuK6wV5Zco</v>
       </c>
       <c r="D75" t="str">
         <v>2026-02-04</v>
@@ -3228,10 +3228,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G75" t="str">
-        <v>3:05</v>
+        <v>2:56</v>
       </c>
       <c r="H75" t="str">
-        <v>Maiah Manser</v>
+        <v>Mitchell Tenpenny</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Maiah Manser - Feeling it All (Official Music Video) - Maiah Manser</v>
+        <v>Mitchell Tenpenny - You Phase (Official Music Video) - Mitchell Tenpenny</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Taylor Austin Dye - Man For That (Official Music Video)</v>
+        <v>Tauren Wells - Breathe On It (Official Lyric Video)</v>
       </c>
       <c r="B76" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=vOzX-o11seI</v>
+        <v>https://www.youtube.com/watch?v=9hW9sNMn2A0</v>
       </c>
       <c r="D76" t="str">
         <v>2026-02-04</v>
@@ -3266,10 +3266,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G76" t="str">
-        <v>2:27</v>
+        <v>4:01</v>
       </c>
       <c r="H76" t="str">
-        <v>Taylor Austin Dye</v>
+        <v>Tauren Wells</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Taylor Austin Dye - Man For That (Official Music Video) - Taylor Austin Dye</v>
+        <v>Tauren Wells - Breathe On It (Official Lyric Video) - Tauren Wells</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Chelsea Cutler - BAD (Official Video)</v>
+        <v>Maiah Manser - Feeling it All (Official Music Video)</v>
       </c>
       <c r="B77" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=86k4E6ydHVU</v>
+        <v>https://www.youtube.com/watch?v=JMYvXleIwfU</v>
       </c>
       <c r="D77" t="str">
         <v>2026-02-04</v>
@@ -3304,10 +3304,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G77" t="str">
-        <v>2:34</v>
+        <v>3:05</v>
       </c>
       <c r="H77" t="str">
-        <v>Chelsea Cutler</v>
+        <v>Maiah Manser</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Chelsea Cutler - BAD (Official Video) - Chelsea Cutler</v>
+        <v>Maiah Manser - Feeling it All (Official Music Video) - Maiah Manser</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video)</v>
+        <v>Taylor Austin Dye - Man For That (Official Music Video)</v>
       </c>
       <c r="B78" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=-UWIFAiOOPE</v>
+        <v>https://www.youtube.com/watch?v=vOzX-o11seI</v>
       </c>
       <c r="D78" t="str">
         <v>2026-02-04</v>
@@ -3342,10 +3342,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G78" t="str">
-        <v>3:13</v>
+        <v>2:27</v>
       </c>
       <c r="H78" t="str">
-        <v>Ashley Kutcher</v>
+        <v>Taylor Austin Dye</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video) - Ashley Kutcher</v>
+        <v>Taylor Austin Dye - Man For That (Official Music Video) - Taylor Austin Dye</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Louis Tomlinson - Dark To Light (Visualiser)</v>
+        <v>Chelsea Cutler - BAD (Official Video)</v>
       </c>
       <c r="B79" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=02QyA29poAM</v>
+        <v>https://www.youtube.com/watch?v=86k4E6ydHVU</v>
       </c>
       <c r="D79" t="str">
         <v>2026-02-04</v>
@@ -3380,10 +3380,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G79" t="str">
-        <v>3:13</v>
+        <v>2:34</v>
       </c>
       <c r="H79" t="str">
-        <v>Louis Tomlinson</v>
+        <v>Chelsea Cutler</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Louis Tomlinson - Dark To Light (Visualiser) - Louis Tomlinson</v>
+        <v>Chelsea Cutler - BAD (Official Video) - Chelsea Cutler</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>CAIN - So Long Sad Songs (Lyric Video)</v>
+        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video)</v>
       </c>
       <c r="B80" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=feOv8nufa_I</v>
+        <v>https://www.youtube.com/watch?v=-UWIFAiOOPE</v>
       </c>
       <c r="D80" t="str">
         <v>2026-02-04</v>
@@ -3418,10 +3418,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G80" t="str">
-        <v>3:08</v>
+        <v>3:13</v>
       </c>
       <c r="H80" t="str">
-        <v>CAIN</v>
+        <v>Ashley Kutcher</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>CAIN - So Long Sad Songs (Lyric Video) - CAIN</v>
+        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video) - Ashley Kutcher</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Harry Styles - Aperture (Official Audio)</v>
+        <v>Louis Tomlinson - Dark To Light (Visualiser)</v>
       </c>
       <c r="B81" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=rA_eCxPay7E</v>
+        <v>https://www.youtube.com/watch?v=02QyA29poAM</v>
       </c>
       <c r="D81" t="str">
         <v>2026-02-04</v>
@@ -3456,10 +3456,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G81" t="str">
-        <v>5:14</v>
+        <v>3:13</v>
       </c>
       <c r="H81" t="str">
-        <v>Harry Styles</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Harry Styles - Aperture (Official Audio) - Harry Styles</v>
+        <v>Louis Tomlinson - Dark To Light (Visualiser) - Louis Tomlinson</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Lana Lubany - BAD IDEA (Official Video)</v>
+        <v>CAIN - So Long Sad Songs (Lyric Video)</v>
       </c>
       <c r="B82" t="str">
-        <v>13 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
+        <v>https://www.youtube.com/watch?v=feOv8nufa_I</v>
       </c>
       <c r="D82" t="str">
         <v>2026-02-04</v>
@@ -3491,13 +3491,13 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>13 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G82" t="str">
-        <v>2:59</v>
+        <v>3:08</v>
       </c>
       <c r="H82" t="str">
-        <v>Lana Lubany</v>
+        <v>CAIN</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Lana Lubany - BAD IDEA (Official Video) - Lana Lubany</v>
+        <v>CAIN - So Long Sad Songs (Lyric Video) - CAIN</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Def Leppard - Rejoice (Lyric Video)</v>
+        <v>Harry Styles - Aperture (Official Audio)</v>
       </c>
       <c r="B83" t="str">
-        <v>13 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=zy2TLLeNgp0</v>
+        <v>https://www.youtube.com/watch?v=rA_eCxPay7E</v>
       </c>
       <c r="D83" t="str">
         <v>2026-02-04</v>
@@ -3529,13 +3529,13 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>13 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G83" t="str">
-        <v>4:21</v>
+        <v>5:14</v>
       </c>
       <c r="H83" t="str">
-        <v>DEF LEPPARD</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Def Leppard - Rejoice (Lyric Video) - DEF LEPPARD</v>
+        <v>Harry Styles - Aperture (Official Audio) - Harry Styles</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Dermot Kennedy - Funeral (Official Music Video)</v>
+        <v>Lana Lubany - BAD IDEA (Official Video)</v>
       </c>
       <c r="B84" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=JzOUJZPky6o</v>
+        <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
       </c>
       <c r="D84" t="str">
         <v>2026-02-04</v>
@@ -3567,13 +3567,13 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G84" t="str">
-        <v>4:09</v>
+        <v>2:59</v>
       </c>
       <c r="H84" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Lana Lubany</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Dermot Kennedy - Funeral (Official Music Video) - Dermot Kennedy</v>
+        <v>Lana Lubany - BAD IDEA (Official Video) - Lana Lubany</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video)</v>
+        <v>Def Leppard - Rejoice (Lyric Video)</v>
       </c>
       <c r="B85" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=kfF0bVZMCw0</v>
+        <v>https://www.youtube.com/watch?v=zy2TLLeNgp0</v>
       </c>
       <c r="D85" t="str">
         <v>2026-02-04</v>
@@ -3605,13 +3605,13 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G85" t="str">
-        <v>2:34</v>
+        <v>4:21</v>
       </c>
       <c r="H85" t="str">
-        <v>Lauren Sanderson</v>
+        <v>DEF LEPPARD</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video) - Lauren Sanderson</v>
+        <v>Def Leppard - Rejoice (Lyric Video) - DEF LEPPARD</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show]</v>
+        <v>Dermot Kennedy - Funeral (Official Music Video)</v>
       </c>
       <c r="B86" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=dLzpNstMHZY</v>
+        <v>https://www.youtube.com/watch?v=JzOUJZPky6o</v>
       </c>
       <c r="D86" t="str">
         <v>2026-02-04</v>
@@ -3646,10 +3646,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G86" t="str">
-        <v>3:10</v>
+        <v>4:09</v>
       </c>
       <c r="H86" t="str">
-        <v>Olivia Dean</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show] - Olivia Dean</v>
+        <v>Dermot Kennedy - Funeral (Official Music Video) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel)</v>
+        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video)</v>
       </c>
       <c r="B87" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=fo_j8Fqag8I</v>
+        <v>https://www.youtube.com/watch?v=kfF0bVZMCw0</v>
       </c>
       <c r="D87" t="str">
         <v>2026-02-04</v>
@@ -3684,10 +3684,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G87" t="str">
-        <v>3:21</v>
+        <v>2:34</v>
       </c>
       <c r="H87" t="str">
-        <v>David Guetta and Tones And I</v>
+        <v>Lauren Sanderson</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel) - David Guetta and Tones And I</v>
+        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video) - Lauren Sanderson</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>The Avett Brothers - Matrimony (Official Video)</v>
+        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show]</v>
       </c>
       <c r="B88" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=7sD9-MtV9CY</v>
+        <v>https://www.youtube.com/watch?v=dLzpNstMHZY</v>
       </c>
       <c r="D88" t="str">
         <v>2026-02-04</v>
@@ -3722,10 +3722,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G88" t="str">
-        <v>3:06</v>
+        <v>3:10</v>
       </c>
       <c r="H88" t="str">
-        <v>The Avett Brothers</v>
+        <v>Olivia Dean</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>The Avett Brothers - Matrimony (Official Video) - The Avett Brothers</v>
+        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show] - Olivia Dean</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Jordana Bryant - Love Like That (Official Video)</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel)</v>
       </c>
       <c r="B89" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=3ATlH-Rtzmk</v>
+        <v>https://www.youtube.com/watch?v=fo_j8Fqag8I</v>
       </c>
       <c r="D89" t="str">
         <v>2026-02-04</v>
@@ -3763,7 +3763,7 @@
         <v>3:21</v>
       </c>
       <c r="H89" t="str">
-        <v>Jordana Bryant</v>
+        <v>David Guetta and Tones And I</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Jordana Bryant - Love Like That (Official Video) - Jordana Bryant</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel) - David Guetta and Tones And I</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards</v>
+        <v>The Avett Brothers - Matrimony (Official Video)</v>
       </c>
       <c r="B90" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=kIRmKmEb2g0</v>
+        <v>https://www.youtube.com/watch?v=7sD9-MtV9CY</v>
       </c>
       <c r="D90" t="str">
         <v>2026-02-04</v>
@@ -3798,10 +3798,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G90" t="str">
-        <v>7:21</v>
+        <v>3:06</v>
       </c>
       <c r="H90" t="str">
-        <v>Katy Perry</v>
+        <v>The Avett Brothers</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards - Katy Perry</v>
+        <v>The Avett Brothers - Matrimony (Official Video) - The Avett Brothers</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session)</v>
+        <v>Jordana Bryant - Love Like That (Official Video)</v>
       </c>
       <c r="B91" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=oJ-l2ptQwbQ</v>
+        <v>https://www.youtube.com/watch?v=3ATlH-Rtzmk</v>
       </c>
       <c r="D91" t="str">
         <v>2026-02-04</v>
@@ -3836,10 +3836,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G91" t="str">
-        <v>3:17</v>
+        <v>3:21</v>
       </c>
       <c r="H91" t="str">
-        <v>Lauren Watkins</v>
+        <v>Jordana Bryant</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session) - Lauren Watkins</v>
+        <v>Jordana Bryant - Love Like That (Official Video) - Jordana Bryant</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Just A Mess (Live acoustic studio session)</v>
+        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards</v>
       </c>
       <c r="B92" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=ShW-I63KD8w</v>
+        <v>https://www.youtube.com/watch?v=kIRmKmEb2g0</v>
       </c>
       <c r="D92" t="str">
         <v>2026-02-04</v>
@@ -3874,10 +3874,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G92" t="str">
-        <v>3:45</v>
+        <v>7:21</v>
       </c>
       <c r="H92" t="str">
-        <v>Tones And I</v>
+        <v>Katy Perry</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Just A Mess (Live acoustic studio session) - Tones And I</v>
+        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards - Katy Perry</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Ashleigh Dallas - Sail Away (Official Audio)</v>
+        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session)</v>
       </c>
       <c r="B93" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=66PDbaI-BVA</v>
+        <v>https://www.youtube.com/watch?v=oJ-l2ptQwbQ</v>
       </c>
       <c r="D93" t="str">
         <v>2026-02-04</v>
@@ -3912,10 +3912,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G93" t="str">
-        <v>3:57</v>
+        <v>3:17</v>
       </c>
       <c r="H93" t="str">
-        <v>Ashleigh Dallas</v>
+        <v>Lauren Watkins</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Ashleigh Dallas - Sail Away (Official Audio) - Ashleigh Dallas</v>
+        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session) - Lauren Watkins</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Performance Video)</v>
+        <v>Just A Mess (Live acoustic studio session)</v>
       </c>
       <c r="B94" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=4tmW_JSXHII</v>
+        <v>https://www.youtube.com/watch?v=ShW-I63KD8w</v>
       </c>
       <c r="D94" t="str">
         <v>2026-02-04</v>
@@ -3950,10 +3950,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G94" t="str">
-        <v>3:03</v>
+        <v>3:45</v>
       </c>
       <c r="H94" t="str">
-        <v>Charlie Puth</v>
+        <v>Tones And I</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Performance Video) - Charlie Puth</v>
+        <v>Just A Mess (Live acoustic studio session) - Tones And I</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Chappell Roan - The Subway (Live from Kansas City)</v>
+        <v>Ashleigh Dallas - Sail Away (Official Audio)</v>
       </c>
       <c r="B95" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=6kZVtF8iaWw</v>
+        <v>https://www.youtube.com/watch?v=66PDbaI-BVA</v>
       </c>
       <c r="D95" t="str">
         <v>2026-02-04</v>
@@ -3988,10 +3988,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G95" t="str">
-        <v>4:27</v>
+        <v>3:57</v>
       </c>
       <c r="H95" t="str">
-        <v>Chappell Roan</v>
+        <v>Ashleigh Dallas</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Chappell Roan - The Subway (Live from Kansas City) - Chappell Roan</v>
+        <v>Ashleigh Dallas - Sail Away (Official Audio) - Ashleigh Dallas</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar)</v>
+        <v>Charlie Puth - Beat Yourself Up (Performance Video)</v>
       </c>
       <c r="B96" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=guUvgEKkk1U</v>
+        <v>https://www.youtube.com/watch?v=4tmW_JSXHII</v>
       </c>
       <c r="D96" t="str">
         <v>2026-02-04</v>
@@ -4026,10 +4026,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G96" t="str">
-        <v>4:34</v>
+        <v>3:03</v>
       </c>
       <c r="H96" t="str">
-        <v>Armik</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar) - Armik</v>
+        <v>Charlie Puth - Beat Yourself Up (Performance Video) - Charlie Puth</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>LØLØ - 007 (Official Music Video)</v>
+        <v>Chappell Roan - The Subway (Live from Kansas City)</v>
       </c>
       <c r="B97" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=4okJouEbZ_s</v>
+        <v>https://www.youtube.com/watch?v=6kZVtF8iaWw</v>
       </c>
       <c r="D97" t="str">
         <v>2026-02-04</v>
@@ -4064,10 +4064,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G97" t="str">
-        <v>2:54</v>
+        <v>4:27</v>
       </c>
       <c r="H97" t="str">
-        <v>LØLØ</v>
+        <v>Chappell Roan</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>LØLØ - 007 (Official Music Video) - LØLØ</v>
+        <v>Chappell Roan - The Subway (Live from Kansas City) - Chappell Roan</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Tenille Townes - enabling (Official Visualizer)</v>
+        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar)</v>
       </c>
       <c r="B98" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=yL_TxDF8WtI</v>
+        <v>https://www.youtube.com/watch?v=guUvgEKkk1U</v>
       </c>
       <c r="D98" t="str">
         <v>2026-02-04</v>
@@ -4102,10 +4102,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G98" t="str">
-        <v>3:25</v>
+        <v>4:34</v>
       </c>
       <c r="H98" t="str">
-        <v>Tenille Townes</v>
+        <v>Armik</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Tenille Townes - enabling (Official Visualizer) - Tenille Townes</v>
+        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Alan Walker - Not Home (Official Lyric Video)</v>
+        <v>LØLØ - 007 (Official Music Video)</v>
       </c>
       <c r="B99" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=0m45tTheoCs</v>
+        <v>https://www.youtube.com/watch?v=4okJouEbZ_s</v>
       </c>
       <c r="D99" t="str">
         <v>2026-02-04</v>
@@ -4140,10 +4140,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G99" t="str">
-        <v>2:01</v>
+        <v>2:54</v>
       </c>
       <c r="H99" t="str">
-        <v>Alan Walker</v>
+        <v>LØLØ</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Alan Walker - Not Home (Official Lyric Video) - Alan Walker</v>
+        <v>LØLØ - 007 (Official Music Video) - LØLØ</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Charli xcx - Wall of Sound (Official Audio)</v>
+        <v>Tenille Townes - enabling (Official Visualizer)</v>
       </c>
       <c r="B100" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=AHm1i212UP4</v>
+        <v>https://www.youtube.com/watch?v=yL_TxDF8WtI</v>
       </c>
       <c r="D100" t="str">
         <v>2026-02-04</v>
@@ -4178,10 +4178,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G100" t="str">
-        <v>2:25</v>
+        <v>3:25</v>
       </c>
       <c r="H100" t="str">
-        <v>Charli xcx</v>
+        <v>Tenille Townes</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Charli xcx - Wall of Sound (Official Audio) - Charli xcx</v>
+        <v>Tenille Townes - enabling (Official Visualizer) - Tenille Townes</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Labrinth - God Spoke (Official Visualizer)</v>
+        <v>Alan Walker - Not Home (Official Lyric Video)</v>
       </c>
       <c r="B101" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=Srb2P9efFHY</v>
+        <v>https://www.youtube.com/watch?v=0m45tTheoCs</v>
       </c>
       <c r="D101" t="str">
         <v>2026-02-04</v>
@@ -4216,10 +4216,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G101" t="str">
-        <v>1:14</v>
+        <v>2:01</v>
       </c>
       <c r="H101" t="str">
-        <v>Labrinth</v>
+        <v>Alan Walker</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,7 +4231,7 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Labrinth - God Spoke (Official Visualizer) - Labrinth</v>
+        <v>Alan Walker - Not Home (Official Lyric Video) - Alan Walker</v>
       </c>
     </row>
     <row r="102">

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Freya Skye - why'd you have to call</v>
       </c>
       <c r="B2" t="str">
-        <v>5 hours ago</v>
+        <v>6 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=75o0FuwCdaA</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>5 hours ago</v>
+        <v>6 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>4:19</v>
@@ -477,7 +477,7 @@
         <v>Jessie J - FEEL IT ON ME (Lyric Visualiser) (Official Lyric Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>5 hours ago</v>
+        <v>6 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=DGmbe49F8aI</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>5 hours ago</v>
+        <v>6 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>2:30</v>
@@ -515,7 +515,7 @@
         <v>Marc Anthony - Make It With You (Visualizer)</v>
       </c>
       <c r="B4" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=WHnz1jDrxw8</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>4:24</v>
@@ -2035,7 +2035,7 @@
         <v>India Martinez, Coro ArteSí de Olvidados - Niño Sin Miedo</v>
       </c>
       <c r="B44" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C44" t="str">
         <v>https://www.youtube.com/watch?v=Vug_FPbXe9E</v>
@@ -2047,7 +2047,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G44" t="str">
         <v>4:04</v>
@@ -2073,7 +2073,7 @@
         <v>Chelsea Cutler - BAD (Official Lyric Video)</v>
       </c>
       <c r="B45" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C45" t="str">
         <v>https://www.youtube.com/watch?v=ZIW2vA3Zs1U</v>
@@ -2085,7 +2085,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G45" t="str">
         <v>2:16</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
@@ -439,19 +439,19 @@
         <v>Freya Skye - why'd you have to call</v>
       </c>
       <c r="B2" t="str">
-        <v>6 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=75o0FuwCdaA</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>6 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>4:19</v>
@@ -477,19 +477,19 @@
         <v>Jessie J - FEEL IT ON ME (Lyric Visualiser) (Official Lyric Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>6 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=DGmbe49F8aI</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E3" t="str">
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>6 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>2:30</v>
@@ -515,19 +515,19 @@
         <v>Marc Anthony - Make It With You (Visualizer)</v>
       </c>
       <c r="B4" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=WHnz1jDrxw8</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E4" t="str">
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G4" t="str">
         <v>4:24</v>
@@ -559,7 +559,7 @@
         <v>https://www.youtube.com/watch?v=HtVuKBlBuPg</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -597,7 +597,7 @@
         <v>https://www.youtube.com/watch?v=shmhTOUd8mA</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -635,7 +635,7 @@
         <v>https://www.youtube.com/watch?v=pvrJ5RnPAEA</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -673,7 +673,7 @@
         <v>https://www.youtube.com/watch?v=mgsdQI-GVMM</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -711,7 +711,7 @@
         <v>https://www.youtube.com/watch?v=SYEwk-EZJPU</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -749,7 +749,7 @@
         <v>https://www.youtube.com/watch?v=CoCqPwDIBOA</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -787,7 +787,7 @@
         <v>https://www.youtube.com/watch?v=18yZq5xtke4</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://www.youtube.com/watch?v=IGLmJ71oHhQ</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -863,7 +863,7 @@
         <v>https://www.youtube.com/watch?v=BQc97moyQBg</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -901,7 +901,7 @@
         <v>https://www.youtube.com/watch?v=dOeoDOueESk</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -939,7 +939,7 @@
         <v>https://www.youtube.com/watch?v=a4AIjUHuWpU</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -977,7 +977,7 @@
         <v>https://www.youtube.com/watch?v=D7QfVqo5YqY</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1015,7 +1015,7 @@
         <v>https://www.youtube.com/watch?v=KdsHxyl4bE8</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1053,7 +1053,7 @@
         <v>https://www.youtube.com/watch?v=Mwkl_Cz_SG8</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1091,7 +1091,7 @@
         <v>https://www.youtube.com/watch?v=I7a-pDZFE7U</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1129,7 +1129,7 @@
         <v>https://www.youtube.com/watch?v=kGeamxRf8Gw</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1167,7 +1167,7 @@
         <v>https://www.youtube.com/watch?v=tNmT47k6MjM</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1205,7 +1205,7 @@
         <v>https://www.youtube.com/watch?v=6ecgOSOMWzc</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1243,7 +1243,7 @@
         <v>https://www.youtube.com/watch?v=DAerJcerikU</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1281,7 +1281,7 @@
         <v>https://www.youtube.com/watch?v=isNztTjXQsQ</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1319,7 +1319,7 @@
         <v>https://www.youtube.com/watch?v=buS21tVq5r0</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1357,7 +1357,7 @@
         <v>https://www.youtube.com/watch?v=qhO6VMC-nx0</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1395,7 +1395,7 @@
         <v>https://www.youtube.com/watch?v=FgAyfRnbbRs</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1433,7 +1433,7 @@
         <v>https://www.youtube.com/watch?v=nwXiAjjl6NE</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1471,7 +1471,7 @@
         <v>https://www.youtube.com/watch?v=MjUiVPzMQHw</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1509,7 +1509,7 @@
         <v>https://www.youtube.com/watch?v=eWglDE7O5r8</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1547,7 +1547,7 @@
         <v>https://www.youtube.com/watch?v=Cmy8CsYIUL0</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1585,7 +1585,7 @@
         <v>https://www.youtube.com/watch?v=sf6eRmInk1s</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1623,7 +1623,7 @@
         <v>https://www.youtube.com/watch?v=fv9prIYHHzk</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1661,7 +1661,7 @@
         <v>https://www.youtube.com/watch?v=T9YvLA2cdZs</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1699,7 +1699,7 @@
         <v>https://www.youtube.com/watch?v=dPWc_6IdDJk</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1737,7 +1737,7 @@
         <v>https://www.youtube.com/watch?v=CV5rR9JZK-0</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1775,7 +1775,7 @@
         <v>https://www.youtube.com/watch?v=9HwTj3NZ16E</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1813,7 +1813,7 @@
         <v>https://www.youtube.com/watch?v=Lmus-UbL1H0</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1851,7 +1851,7 @@
         <v>https://www.youtube.com/watch?v=bu6WSMDDPGY</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1889,7 +1889,7 @@
         <v>https://www.youtube.com/watch?v=zcYeoGBglC0</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1927,7 +1927,7 @@
         <v>https://www.youtube.com/watch?v=3igYRj82EiU</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1965,7 +1965,7 @@
         <v>https://www.youtube.com/watch?v=0bhcO4Yphuo</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -2003,7 +2003,7 @@
         <v>https://www.youtube.com/watch?v=Jjz1wFe5dMo</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -2041,7 +2041,7 @@
         <v>https://www.youtube.com/watch?v=Vug_FPbXe9E</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2079,7 +2079,7 @@
         <v>https://www.youtube.com/watch?v=ZIW2vA3Zs1U</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -2117,7 +2117,7 @@
         <v>https://www.youtube.com/watch?v=q_rrgJZAdNg</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -2155,7 +2155,7 @@
         <v>https://www.youtube.com/watch?v=uVIuKbPJz0U</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2193,7 +2193,7 @@
         <v>https://www.youtube.com/watch?v=E-ECwdRndVA</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2231,7 +2231,7 @@
         <v>https://www.youtube.com/watch?v=1ugf5aaY4pY</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -2269,7 +2269,7 @@
         <v>https://www.youtube.com/watch?v=ByABj3Xof1I</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2307,7 +2307,7 @@
         <v>https://www.youtube.com/watch?v=2HSbo51EFNg</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2345,7 +2345,7 @@
         <v>https://www.youtube.com/watch?v=ylifHFJWJ_c</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2383,7 +2383,7 @@
         <v>https://www.youtube.com/watch?v=9ST-eBNL0NU</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2421,7 +2421,7 @@
         <v>https://www.youtube.com/watch?v=EhzX2y5MpSM</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2459,7 +2459,7 @@
         <v>https://www.youtube.com/watch?v=yUAvfo8fpuU</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2497,7 +2497,7 @@
         <v>https://www.youtube.com/watch?v=KnsBdAM3HqY</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2535,7 +2535,7 @@
         <v>https://www.youtube.com/watch?v=BTqRGxSX6AQ</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2573,7 +2573,7 @@
         <v>https://www.youtube.com/watch?v=r9KyYK_E34s</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2611,7 +2611,7 @@
         <v>https://www.youtube.com/watch?v=57a_OheOlDw</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2649,7 +2649,7 @@
         <v>https://www.youtube.com/watch?v=-5Aa8NTiRqE</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -2687,7 +2687,7 @@
         <v>https://www.youtube.com/watch?v=5RNy_1odv20</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -2725,7 +2725,7 @@
         <v>https://www.youtube.com/watch?v=stYIRyCLN4Y</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -2763,7 +2763,7 @@
         <v>https://www.youtube.com/watch?v=7sxVHYZ_PnA</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -2801,7 +2801,7 @@
         <v>https://www.youtube.com/watch?v=46iZEdsxjC0</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -2839,7 +2839,7 @@
         <v>https://www.youtube.com/watch?v=K2nG1Uukz7E</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -2877,7 +2877,7 @@
         <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -2915,7 +2915,7 @@
         <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -2953,7 +2953,7 @@
         <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -2991,7 +2991,7 @@
         <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -3029,7 +3029,7 @@
         <v>https://www.youtube.com/watch?v=pnAz9RwGSek</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -3067,7 +3067,7 @@
         <v>https://www.youtube.com/watch?v=u7aPv2saz_I</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -3105,7 +3105,7 @@
         <v>https://www.youtube.com/watch?v=WGb8KVdqs6k</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -3143,7 +3143,7 @@
         <v>https://www.youtube.com/watch?v=X1ZeY4Y3l1M</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -3181,7 +3181,7 @@
         <v>https://www.youtube.com/watch?v=rzuD5szQhso</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -3219,7 +3219,7 @@
         <v>https://www.youtube.com/watch?v=UPuK6wV5Zco</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -3257,7 +3257,7 @@
         <v>https://www.youtube.com/watch?v=9hW9sNMn2A0</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -3295,7 +3295,7 @@
         <v>https://www.youtube.com/watch?v=JMYvXleIwfU</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -3333,7 +3333,7 @@
         <v>https://www.youtube.com/watch?v=vOzX-o11seI</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -3371,7 +3371,7 @@
         <v>https://www.youtube.com/watch?v=86k4E6ydHVU</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -3409,7 +3409,7 @@
         <v>https://www.youtube.com/watch?v=-UWIFAiOOPE</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -3447,7 +3447,7 @@
         <v>https://www.youtube.com/watch?v=02QyA29poAM</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -3485,7 +3485,7 @@
         <v>https://www.youtube.com/watch?v=feOv8nufa_I</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -3517,19 +3517,19 @@
         <v>Harry Styles - Aperture (Official Audio)</v>
       </c>
       <c r="B83" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C83" t="str">
         <v>https://www.youtube.com/watch?v=rA_eCxPay7E</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E83" t="str">
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G83" t="str">
         <v>5:14</v>
@@ -3561,7 +3561,7 @@
         <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -3599,7 +3599,7 @@
         <v>https://www.youtube.com/watch?v=zy2TLLeNgp0</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E85" t="str">
         <v/>
@@ -3637,7 +3637,7 @@
         <v>https://www.youtube.com/watch?v=JzOUJZPky6o</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3675,7 +3675,7 @@
         <v>https://www.youtube.com/watch?v=kfF0bVZMCw0</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3713,7 +3713,7 @@
         <v>https://www.youtube.com/watch?v=dLzpNstMHZY</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3751,7 +3751,7 @@
         <v>https://www.youtube.com/watch?v=fo_j8Fqag8I</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3789,7 +3789,7 @@
         <v>https://www.youtube.com/watch?v=7sD9-MtV9CY</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -3827,7 +3827,7 @@
         <v>https://www.youtube.com/watch?v=3ATlH-Rtzmk</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -3865,7 +3865,7 @@
         <v>https://www.youtube.com/watch?v=kIRmKmEb2g0</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -3903,7 +3903,7 @@
         <v>https://www.youtube.com/watch?v=oJ-l2ptQwbQ</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E93" t="str">
         <v/>
@@ -3941,7 +3941,7 @@
         <v>https://www.youtube.com/watch?v=ShW-I63KD8w</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E94" t="str">
         <v/>
@@ -3979,7 +3979,7 @@
         <v>https://www.youtube.com/watch?v=66PDbaI-BVA</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E95" t="str">
         <v/>
@@ -4017,7 +4017,7 @@
         <v>https://www.youtube.com/watch?v=4tmW_JSXHII</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E96" t="str">
         <v/>
@@ -4055,7 +4055,7 @@
         <v>https://www.youtube.com/watch?v=6kZVtF8iaWw</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E97" t="str">
         <v/>
@@ -4093,7 +4093,7 @@
         <v>https://www.youtube.com/watch?v=guUvgEKkk1U</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E98" t="str">
         <v/>
@@ -4131,7 +4131,7 @@
         <v>https://www.youtube.com/watch?v=4okJouEbZ_s</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E99" t="str">
         <v/>
@@ -4169,7 +4169,7 @@
         <v>https://www.youtube.com/watch?v=yL_TxDF8WtI</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E100" t="str">
         <v/>
@@ -4207,7 +4207,7 @@
         <v>https://www.youtube.com/watch?v=0m45tTheoCs</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E101" t="str">
         <v/>
@@ -4245,7 +4245,7 @@
         <v>https://music.apple.com/us/song/golden-boy/1872543012</v>
       </c>
       <c r="D102" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E102" t="str">
         <v/>
@@ -4283,7 +4283,7 @@
         <v>https://music.apple.com/us/song/body/1871258331</v>
       </c>
       <c r="D103" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E103" t="str">
         <v/>
@@ -4321,7 +4321,7 @@
         <v>https://music.apple.com/us/song/dandelion/1869436838</v>
       </c>
       <c r="D104" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E104" t="str">
         <v/>
@@ -4359,7 +4359,7 @@
         <v>https://music.apple.com/us/song/lights-go-out/1870833473</v>
       </c>
       <c r="D105" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E105" t="str">
         <v/>
@@ -4397,7 +4397,7 @@
         <v>https://music.apple.com/us/song/the-great-divide/1872239886</v>
       </c>
       <c r="D106" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E106" t="str">
         <v/>
@@ -4435,7 +4435,7 @@
         <v>https://music.apple.com/us/song/trist%C3%B3n/1872585947</v>
       </c>
       <c r="D107" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E107" t="str">
         <v/>
@@ -4473,7 +4473,7 @@
         <v>https://music.apple.com/us/song/feed-the-streets/1869462051</v>
       </c>
       <c r="D108" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E108" t="str">
         <v/>
@@ -4511,7 +4511,7 @@
         <v>https://music.apple.com/us/song/i-did-this-to-myself/1861531672</v>
       </c>
       <c r="D109" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E109" t="str">
         <v/>
@@ -4549,7 +4549,7 @@
         <v>https://music.apple.com/us/song/penny-in-the-lake/1844710053</v>
       </c>
       <c r="D110" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E110" t="str">
         <v/>
@@ -4587,7 +4587,7 @@
         <v>https://music.apple.com/us/song/for-hire/1870722567</v>
       </c>
       <c r="D111" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E111" t="str">
         <v/>
@@ -4625,7 +4625,7 @@
         <v>https://music.apple.com/us/song/heaven/1862570892</v>
       </c>
       <c r="D112" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E112" t="str">
         <v/>
@@ -4663,7 +4663,7 @@
         <v>https://music.apple.com/us/song/mcarthur/1871231844</v>
       </c>
       <c r="D113" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E113" t="str">
         <v/>
@@ -4701,7 +4701,7 @@
         <v>https://music.apple.com/us/song/debris/1853069633</v>
       </c>
       <c r="D114" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E114" t="str">
         <v/>
@@ -4739,7 +4739,7 @@
         <v>https://music.apple.com/us/song/god-owes-me-money-live-at-apple-music-radio/1871521120</v>
       </c>
       <c r="D115" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E115" t="str">
         <v/>
@@ -4777,7 +4777,7 @@
         <v>https://music.apple.com/us/song/rockstar-raging-feat-swae-lee/1873028187</v>
       </c>
       <c r="D116" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E116" t="str">
         <v/>
@@ -4815,7 +4815,7 @@
         <v>https://music.apple.com/us/song/1-1/1870378316</v>
       </c>
       <c r="D117" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E117" t="str">
         <v/>
@@ -4853,7 +4853,7 @@
         <v>https://music.apple.com/us/song/still-sincere-feat-pinkpantheress/1862228374</v>
       </c>
       <c r="D118" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E118" t="str">
         <v/>
@@ -4891,7 +4891,7 @@
         <v>https://music.apple.com/us/song/two-car-garage/1869137588</v>
       </c>
       <c r="D119" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E119" t="str">
         <v/>
@@ -4929,7 +4929,7 @@
         <v>https://music.apple.com/us/song/fml/1872686260</v>
       </c>
       <c r="D120" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E120" t="str">
         <v/>
@@ -4967,7 +4967,7 @@
         <v>https://music.apple.com/us/song/faked-it-all-the-time/1871050032</v>
       </c>
       <c r="D121" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E121" t="str">
         <v/>
@@ -5005,7 +5005,7 @@
         <v>https://music.apple.com/us/song/house-of-the-rising-sun/1872111857</v>
       </c>
       <c r="D122" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E122" t="str">
         <v/>
@@ -5043,7 +5043,7 @@
         <v>https://music.apple.com/us/song/lorelei/1867640808</v>
       </c>
       <c r="D123" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E123" t="str">
         <v/>
@@ -5081,7 +5081,7 @@
         <v>https://music.apple.com/us/song/free/1870703329</v>
       </c>
       <c r="D124" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E124" t="str">
         <v/>
@@ -5119,7 +5119,7 @@
         <v>https://music.apple.com/us/song/assignment/1872764440</v>
       </c>
       <c r="D125" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E125" t="str">
         <v/>
@@ -5157,7 +5157,7 @@
         <v>https://music.apple.com/us/song/professional-heartbreaker/1871053476</v>
       </c>
       <c r="D126" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E126" t="str">
         <v/>
@@ -5195,7 +5195,7 @@
         <v>https://music.apple.com/us/song/tell-me-what-you-want/1871463892</v>
       </c>
       <c r="D127" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E127" t="str">
         <v/>
@@ -5233,7 +5233,7 @@
         <v>https://music.apple.com/us/song/aguas/1869455857</v>
       </c>
       <c r="D128" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E128" t="str">
         <v/>
@@ -5271,7 +5271,7 @@
         <v>https://music.apple.com/us/song/ants-in-my-room/1870967813</v>
       </c>
       <c r="D129" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E129" t="str">
         <v/>
@@ -5309,7 +5309,7 @@
         <v>https://music.apple.com/us/song/baddie/1849760827</v>
       </c>
       <c r="D130" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E130" t="str">
         <v/>
@@ -5347,7 +5347,7 @@
         <v>https://music.apple.com/us/song/what-you-need-a-colors-show/1870990925</v>
       </c>
       <c r="D131" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E131" t="str">
         <v/>
@@ -5385,7 +5385,7 @@
         <v>https://music.apple.com/us/song/ok-ok-hamdi-remix/1871538130</v>
       </c>
       <c r="D132" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E132" t="str">
         <v/>
@@ -5423,7 +5423,7 @@
         <v>https://music.apple.com/us/song/ever-and-ever-before-feat-m%C5%8Driah-courtney/1869383260</v>
       </c>
       <c r="D133" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E133" t="str">
         <v/>
@@ -5461,7 +5461,7 @@
         <v>https://music.apple.com/us/song/for-the-first-time-again/1834736723</v>
       </c>
       <c r="D134" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E134" t="str">
         <v/>
@@ -5499,7 +5499,7 @@
         <v>https://music.apple.com/us/song/liars-tale/1862207951</v>
       </c>
       <c r="D135" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E135" t="str">
         <v/>
@@ -5537,7 +5537,7 @@
         <v>https://music.apple.com/us/song/afraid-of-the-dark/1872184048</v>
       </c>
       <c r="D136" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E136" t="str">
         <v/>
@@ -5575,7 +5575,7 @@
         <v>https://music.apple.com/us/song/wake-up-calling/1862338150</v>
       </c>
       <c r="D137" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E137" t="str">
         <v/>
@@ -5613,7 +5613,7 @@
         <v>https://music.apple.com/us/song/high/1867202644</v>
       </c>
       <c r="D138" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E138" t="str">
         <v/>
@@ -5651,7 +5651,7 @@
         <v>https://music.apple.com/us/song/villain/1860126455</v>
       </c>
       <c r="D139" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E139" t="str">
         <v/>
@@ -5689,7 +5689,7 @@
         <v>https://music.apple.com/us/song/bad-idea-right/1869792549</v>
       </c>
       <c r="D140" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E140" t="str">
         <v/>
@@ -5727,7 +5727,7 @@
         <v>https://music.apple.com/us/song/residue/1863786787</v>
       </c>
       <c r="D141" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E141" t="str">
         <v/>
@@ -5765,7 +5765,7 @@
         <v>https://music.apple.com/us/song/i-used-to-go-to-this-bar/1839918872</v>
       </c>
       <c r="D142" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E142" t="str">
         <v/>
@@ -5803,7 +5803,7 @@
         <v>https://music.apple.com/us/song/starlight/1870989674</v>
       </c>
       <c r="D143" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E143" t="str">
         <v/>
@@ -5841,7 +5841,7 @@
         <v>https://music.apple.com/us/song/dandelion/1863154133</v>
       </c>
       <c r="D144" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E144" t="str">
         <v/>
@@ -5879,7 +5879,7 @@
         <v>https://music.apple.com/us/song/themselves/1845287173</v>
       </c>
       <c r="D145" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E145" t="str">
         <v/>
@@ -5917,7 +5917,7 @@
         <v>https://music.apple.com/us/song/high-maintenance/1872497656</v>
       </c>
       <c r="D146" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E146" t="str">
         <v/>
@@ -5955,7 +5955,7 @@
         <v>https://music.apple.com/us/song/trackhawk/1860991724</v>
       </c>
       <c r="D147" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E147" t="str">
         <v/>
@@ -5993,7 +5993,7 @@
         <v>https://music.apple.com/us/song/wheel-man/1872178895</v>
       </c>
       <c r="D148" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E148" t="str">
         <v/>
@@ -6031,7 +6031,7 @@
         <v>https://music.apple.com/us/song/natural-disaster/1871263211</v>
       </c>
       <c r="D149" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E149" t="str">
         <v/>
@@ -6069,7 +6069,7 @@
         <v>https://music.apple.com/us/song/prettier/1869745409</v>
       </c>
       <c r="D150" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E150" t="str">
         <v/>
@@ -6107,7 +6107,7 @@
         <v>https://music.apple.com/us/song/shotta-flow-8/1872760524</v>
       </c>
       <c r="D151" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E151" t="str">
         <v/>
@@ -6145,7 +6145,7 @@
         <v>https://music.apple.com/us/song/die-to-fall/1866902681</v>
       </c>
       <c r="D152" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E152" t="str">
         <v/>
@@ -6183,7 +6183,7 @@
         <v>https://music.apple.com/us/song/the-cruel-angels-thesis-neon-genesis-evangelion/1864932139</v>
       </c>
       <c r="D153" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E153" t="str">
         <v/>
@@ -6221,7 +6221,7 @@
         <v>https://music.apple.com/us/song/slow-burn/1851033862</v>
       </c>
       <c r="D154" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E154" t="str">
         <v/>
@@ -6259,7 +6259,7 @@
         <v>https://music.apple.com/us/song/too-late/1857999860</v>
       </c>
       <c r="D155" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E155" t="str">
         <v/>
@@ -6297,7 +6297,7 @@
         <v>https://music.apple.com/us/song/mono-feat-skaiwater/1869130804</v>
       </c>
       <c r="D156" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E156" t="str">
         <v/>
@@ -6335,7 +6335,7 @@
         <v>https://music.apple.com/us/song/thank-you-is-enough/1870679042</v>
       </c>
       <c r="D157" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E157" t="str">
         <v/>
@@ -6373,7 +6373,7 @@
         <v>https://music.apple.com/us/song/ridin/1869786726</v>
       </c>
       <c r="D158" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E158" t="str">
         <v/>
@@ -6411,7 +6411,7 @@
         <v>https://music.apple.com/us/song/possession/1872536200</v>
       </c>
       <c r="D159" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E159" t="str">
         <v/>
@@ -6449,7 +6449,7 @@
         <v>https://music.apple.com/us/song/poema/1872723644</v>
       </c>
       <c r="D160" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E160" t="str">
         <v/>
@@ -6487,7 +6487,7 @@
         <v>https://music.apple.com/us/song/live-without/1862777625</v>
       </c>
       <c r="D161" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E161" t="str">
         <v/>
@@ -6525,7 +6525,7 @@
         <v>https://music.apple.com/us/song/fan%C3%A1tico/1871611852</v>
       </c>
       <c r="D162" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E162" t="str">
         <v/>
@@ -6563,7 +6563,7 @@
         <v>https://music.apple.com/us/song/frozen-lake/1867287070</v>
       </c>
       <c r="D163" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E163" t="str">
         <v/>
@@ -6601,7 +6601,7 @@
         <v>https://music.apple.com/us/song/fine-shyt-eb-remix-feat-eric-bellinger/1870964385</v>
       </c>
       <c r="D164" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E164" t="str">
         <v/>
@@ -6639,7 +6639,7 @@
         <v>https://music.apple.com/us/song/hell-yeah-feat-waxmaster/1866602820</v>
       </c>
       <c r="D165" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E165" t="str">
         <v/>
@@ -6677,7 +6677,7 @@
         <v>https://music.apple.com/us/song/its-like-that/1858689757</v>
       </c>
       <c r="D166" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E166" t="str">
         <v/>
@@ -6715,7 +6715,7 @@
         <v>https://music.apple.com/us/song/a-s-a-p/1833414737</v>
       </c>
       <c r="D167" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E167" t="str">
         <v/>
@@ -6753,7 +6753,7 @@
         <v>https://music.apple.com/us/song/once-i-say/1867855025</v>
       </c>
       <c r="D168" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E168" t="str">
         <v/>
@@ -6791,7 +6791,7 @@
         <v>https://music.apple.com/us/song/believer/1862797080</v>
       </c>
       <c r="D169" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E169" t="str">
         <v/>
@@ -6829,7 +6829,7 @@
         <v>https://music.apple.com/us/song/i-envy-the-wind/1863202477</v>
       </c>
       <c r="D170" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E170" t="str">
         <v/>
@@ -6867,7 +6867,7 @@
         <v>https://music.apple.com/us/song/the-alchemist/1831827347</v>
       </c>
       <c r="D171" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E171" t="str">
         <v/>
@@ -6905,7 +6905,7 @@
         <v>https://music.apple.com/us/song/daysa/1861575845</v>
       </c>
       <c r="D172" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E172" t="str">
         <v/>
@@ -6943,7 +6943,7 @@
         <v>https://music.apple.com/us/song/fabulous/1862804005</v>
       </c>
       <c r="D173" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E173" t="str">
         <v/>
@@ -6981,7 +6981,7 @@
         <v>https://music.apple.com/us/song/me-asusta-amar-tanto-la-soledad/1866982109</v>
       </c>
       <c r="D174" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E174" t="str">
         <v/>
@@ -7019,7 +7019,7 @@
         <v>https://music.apple.com/us/song/brainchem/1870656942</v>
       </c>
       <c r="D175" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E175" t="str">
         <v/>
@@ -7057,7 +7057,7 @@
         <v>https://music.apple.com/us/song/boyfriend-in-yo-brain-notice-me/1871675026</v>
       </c>
       <c r="D176" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E176" t="str">
         <v/>
@@ -7095,7 +7095,7 @@
         <v>https://music.apple.com/us/song/giants/1869154957</v>
       </c>
       <c r="D177" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E177" t="str">
         <v/>
@@ -7133,7 +7133,7 @@
         <v>https://music.apple.com/us/song/scooby/1872510752</v>
       </c>
       <c r="D178" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E178" t="str">
         <v/>
@@ -7171,7 +7171,7 @@
         <v>https://music.apple.com/us/song/la-racha/1868757762</v>
       </c>
       <c r="D179" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E179" t="str">
         <v/>
@@ -7209,7 +7209,7 @@
         <v>https://music.apple.com/us/song/so-am-i/1867012209</v>
       </c>
       <c r="D180" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E180" t="str">
         <v/>
@@ -7247,7 +7247,7 @@
         <v>https://music.apple.com/us/song/best-thing/1860673616</v>
       </c>
       <c r="D181" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E181" t="str">
         <v/>
@@ -7285,7 +7285,7 @@
         <v>https://music.apple.com/us/song/count-it-back/1855219865</v>
       </c>
       <c r="D182" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E182" t="str">
         <v/>
@@ -7323,7 +7323,7 @@
         <v>https://music.apple.com/us/song/good-girl/1862640697</v>
       </c>
       <c r="D183" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E183" t="str">
         <v/>
@@ -7361,7 +7361,7 @@
         <v>https://music.apple.com/us/song/my-revival/1869465104</v>
       </c>
       <c r="D184" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E184" t="str">
         <v/>
@@ -7399,7 +7399,7 @@
         <v>https://music.apple.com/us/song/run-my-way/1860964996</v>
       </c>
       <c r="D185" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E185" t="str">
         <v/>
@@ -7437,7 +7437,7 @@
         <v>https://music.apple.com/us/song/cold-night/1867687787</v>
       </c>
       <c r="D186" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E186" t="str">
         <v/>
@@ -7475,7 +7475,7 @@
         <v>https://music.apple.com/us/song/away-with-the-fairies/1870603474</v>
       </c>
       <c r="D187" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E187" t="str">
         <v/>
@@ -7513,7 +7513,7 @@
         <v>https://music.apple.com/us/song/fragile/1866957569</v>
       </c>
       <c r="D188" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E188" t="str">
         <v/>
@@ -7551,7 +7551,7 @@
         <v>https://music.apple.com/us/song/slow-dancin/1871537173</v>
       </c>
       <c r="D189" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E189" t="str">
         <v/>
@@ -7589,7 +7589,7 @@
         <v>https://music.apple.com/us/song/never-kissed-a-cowboy/1866744530</v>
       </c>
       <c r="D190" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E190" t="str">
         <v/>
@@ -7627,7 +7627,7 @@
         <v>https://music.apple.com/us/song/more-of-what-matters/1871592720</v>
       </c>
       <c r="D191" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E191" t="str">
         <v/>
@@ -7665,7 +7665,7 @@
         <v>https://music.apple.com/us/song/is-this-the-real-you/1869323368</v>
       </c>
       <c r="D192" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E192" t="str">
         <v/>
@@ -7703,7 +7703,7 @@
         <v>https://music.apple.com/us/song/hud/1842015019</v>
       </c>
       <c r="D193" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E193" t="str">
         <v/>
@@ -7741,7 +7741,7 @@
         <v>https://music.apple.com/us/song/ego-death/1867855427</v>
       </c>
       <c r="D194" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E194" t="str">
         <v/>
@@ -7779,7 +7779,7 @@
         <v>https://music.apple.com/us/song/gas-station-love-remix/1872150728</v>
       </c>
       <c r="D195" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E195" t="str">
         <v/>
@@ -7817,7 +7817,7 @@
         <v>https://music.apple.com/us/song/disappear/1861907311</v>
       </c>
       <c r="D196" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E196" t="str">
         <v/>
@@ -7855,7 +7855,7 @@
         <v>https://music.apple.com/us/song/misbehave/1859630128</v>
       </c>
       <c r="D197" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E197" t="str">
         <v/>
@@ -7893,7 +7893,7 @@
         <v>https://music.apple.com/us/song/club-bizarre/1870355078</v>
       </c>
       <c r="D198" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E198" t="str">
         <v/>
@@ -7931,7 +7931,7 @@
         <v>https://music.apple.com/us/song/fly/1867903625</v>
       </c>
       <c r="D199" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E199" t="str">
         <v/>
@@ -7969,7 +7969,7 @@
         <v>https://music.apple.com/us/song/ily-anyway/1870369432</v>
       </c>
       <c r="D200" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E200" t="str">
         <v/>
@@ -8007,7 +8007,7 @@
         <v>https://music.apple.com/us/song/george-jones-feat-angela-autumn/1867306007</v>
       </c>
       <c r="D201" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E201" t="str">
         <v/>
@@ -8045,7 +8045,7 @@
         <v>https://music.apple.com/us/song/kiss-big/1837292261</v>
       </c>
       <c r="D202" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E202" t="str">
         <v/>
@@ -8083,7 +8083,7 @@
         <v>https://music.apple.com/us/song/praxis/1845253734</v>
       </c>
       <c r="D203" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E203" t="str">
         <v/>
@@ -8121,7 +8121,7 @@
         <v>https://music.apple.com/us/song/house/1866696487</v>
       </c>
       <c r="D204" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E204" t="str">
         <v/>
@@ -8159,7 +8159,7 @@
         <v>https://music.apple.com/us/song/cowboy-without-a-clue/1834024322</v>
       </c>
       <c r="D205" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E205" t="str">
         <v/>
@@ -8197,7 +8197,7 @@
         <v>https://music.apple.com/us/song/brincar/1871554907</v>
       </c>
       <c r="D206" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E206" t="str">
         <v/>
@@ -8235,7 +8235,7 @@
         <v>https://music.apple.com/us/song/qui%C3%A9n/1870329662</v>
       </c>
       <c r="D207" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E207" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Freya Skye - why'd you have to call</v>
       </c>
       <c r="B2" t="str">
-        <v>8 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=75o0FuwCdaA</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>8 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>4:19</v>
@@ -477,7 +477,7 @@
         <v>Jessie J - FEEL IT ON ME (Lyric Visualiser) (Official Lyric Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>8 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=DGmbe49F8aI</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>8 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>2:30</v>
@@ -2643,7 +2643,7 @@
         <v>Clinton Kane - this is my last love song to you (Official Lyric Video)</v>
       </c>
       <c r="B60" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C60" t="str">
         <v>https://www.youtube.com/watch?v=-5Aa8NTiRqE</v>
@@ -2655,7 +2655,7 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G60" t="str">
         <v>3:34</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Freya Skye - why'd you have to call</v>
       </c>
       <c r="B2" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=75o0FuwCdaA</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>4:19</v>
@@ -477,7 +477,7 @@
         <v>Jessie J - FEEL IT ON ME (Lyric Visualiser) (Official Lyric Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=DGmbe49F8aI</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>2:30</v>
@@ -1579,7 +1579,7 @@
         <v>Ella Langley - Dandelion (Official Visualizer)</v>
       </c>
       <c r="B32" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=sf6eRmInk1s</v>
@@ -1591,7 +1591,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G32" t="str">
         <v>4:01</v>
@@ -1617,7 +1617,7 @@
         <v>Dogpark - Dandelion (Official Music Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C33" t="str">
         <v>https://www.youtube.com/watch?v=fv9prIYHHzk</v>
@@ -1629,7 +1629,7 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G33" t="str">
         <v>3:16</v>
@@ -1655,7 +1655,7 @@
         <v>Lauren Spencer Smith - Natural Disaster (Visualizer)</v>
       </c>
       <c r="B34" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=T9YvLA2cdZs</v>
@@ -1667,7 +1667,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G34" t="str">
         <v>3:03</v>
@@ -1693,7 +1693,7 @@
         <v>ERNEST - Lorelei (Official Music Video)</v>
       </c>
       <c r="B35" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=dPWc_6IdDJk</v>
@@ -1705,7 +1705,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G35" t="str">
         <v>2:41</v>
@@ -1731,7 +1731,7 @@
         <v>Labrinth - I Keep My Promises (Official Audio)</v>
       </c>
       <c r="B36" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=CV5rR9JZK-0</v>
@@ -1743,7 +1743,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G36" t="str">
         <v>3:05</v>
@@ -1769,7 +1769,7 @@
         <v>Grace VanderWaal - Prettier (Official Lyric Video)</v>
       </c>
       <c r="B37" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C37" t="str">
         <v>https://www.youtube.com/watch?v=9HwTj3NZ16E</v>
@@ -1781,7 +1781,7 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G37" t="str">
         <v>2:46</v>
@@ -1807,7 +1807,7 @@
         <v>VOILÀ - Frozen Lake (Official Lyric Video)</v>
       </c>
       <c r="B38" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=Lmus-UbL1H0</v>
@@ -1819,7 +1819,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G38" t="str">
         <v>3:32</v>
@@ -1845,7 +1845,7 @@
         <v>Cannons - Starlight (Official Video)</v>
       </c>
       <c r="B39" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=bu6WSMDDPGY</v>
@@ -1857,7 +1857,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G39" t="str">
         <v>3:42</v>
@@ -1883,7 +1883,7 @@
         <v>Kylie Morgan - Like My Own (Official Video)</v>
       </c>
       <c r="B40" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=zcYeoGBglC0</v>
@@ -1895,7 +1895,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G40" t="str">
         <v>2:38</v>
@@ -1921,7 +1921,7 @@
         <v>Lizzy McAlpine - House of the Rising Sun (Audio)</v>
       </c>
       <c r="B41" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=3igYRj82EiU</v>
@@ -1933,7 +1933,7 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G41" t="str">
         <v>3:10</v>
@@ -1959,7 +1959,7 @@
         <v>Willie Nelson - Heart Of America (From The Gray House Original Soundtrack)</v>
       </c>
       <c r="B42" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C42" t="str">
         <v>https://www.youtube.com/watch?v=0bhcO4Yphuo</v>
@@ -1971,7 +1971,7 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G42" t="str">
         <v>3:57</v>
@@ -1997,7 +1997,7 @@
         <v>Jeremy Camp - No Survivors (Live) ft. Skillet</v>
       </c>
       <c r="B43" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C43" t="str">
         <v>https://www.youtube.com/watch?v=Jjz1wFe5dMo</v>
@@ -2009,7 +2009,7 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G43" t="str">
         <v>2:19</v>
@@ -2985,7 +2985,7 @@
         <v>Bella White - Dream Song (Official Audio)</v>
       </c>
       <c r="B69" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C69" t="str">
         <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
@@ -2997,7 +2997,7 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G69" t="str">
         <v>4:37</v>
@@ -3023,7 +3023,7 @@
         <v>Ryan Wright - Film School Kids (Official Video)</v>
       </c>
       <c r="B70" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C70" t="str">
         <v>https://www.youtube.com/watch?v=pnAz9RwGSek</v>
@@ -3035,7 +3035,7 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G70" t="str">
         <v>4:06</v>
@@ -3061,7 +3061,7 @@
         <v>Dove Cameron - Do I Wanna Know? (Official Visualizer)</v>
       </c>
       <c r="B71" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C71" t="str">
         <v>https://www.youtube.com/watch?v=u7aPv2saz_I</v>
@@ -3073,7 +3073,7 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G71" t="str">
         <v>3:54</v>
@@ -3099,7 +3099,7 @@
         <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video)</v>
       </c>
       <c r="B72" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C72" t="str">
         <v>https://www.youtube.com/watch?v=WGb8KVdqs6k</v>
@@ -3111,7 +3111,7 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G72" t="str">
         <v>4:10</v>
@@ -3137,7 +3137,7 @@
         <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video)</v>
       </c>
       <c r="B73" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C73" t="str">
         <v>https://www.youtube.com/watch?v=X1ZeY4Y3l1M</v>
@@ -3149,7 +3149,7 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G73" t="str">
         <v>3:26</v>
@@ -3213,7 +3213,7 @@
         <v>Mitchell Tenpenny - You Phase (Official Music Video)</v>
       </c>
       <c r="B75" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C75" t="str">
         <v>https://www.youtube.com/watch?v=UPuK6wV5Zco</v>
@@ -3225,7 +3225,7 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G75" t="str">
         <v>2:56</v>
@@ -3251,7 +3251,7 @@
         <v>Tauren Wells - Breathe On It (Official Lyric Video)</v>
       </c>
       <c r="B76" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C76" t="str">
         <v>https://www.youtube.com/watch?v=9hW9sNMn2A0</v>
@@ -3263,7 +3263,7 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G76" t="str">
         <v>4:01</v>
@@ -3289,7 +3289,7 @@
         <v>Maiah Manser - Feeling it All (Official Music Video)</v>
       </c>
       <c r="B77" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C77" t="str">
         <v>https://www.youtube.com/watch?v=JMYvXleIwfU</v>
@@ -3301,7 +3301,7 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G77" t="str">
         <v>3:05</v>
@@ -3327,7 +3327,7 @@
         <v>Taylor Austin Dye - Man For That (Official Music Video)</v>
       </c>
       <c r="B78" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C78" t="str">
         <v>https://www.youtube.com/watch?v=vOzX-o11seI</v>
@@ -3339,7 +3339,7 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G78" t="str">
         <v>2:27</v>
@@ -3365,7 +3365,7 @@
         <v>Chelsea Cutler - BAD (Official Video)</v>
       </c>
       <c r="B79" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C79" t="str">
         <v>https://www.youtube.com/watch?v=86k4E6ydHVU</v>
@@ -3377,7 +3377,7 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G79" t="str">
         <v>2:34</v>
@@ -3403,7 +3403,7 @@
         <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video)</v>
       </c>
       <c r="B80" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C80" t="str">
         <v>https://www.youtube.com/watch?v=-UWIFAiOOPE</v>
@@ -3415,7 +3415,7 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G80" t="str">
         <v>3:13</v>
@@ -3441,7 +3441,7 @@
         <v>Louis Tomlinson - Dark To Light (Visualiser)</v>
       </c>
       <c r="B81" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C81" t="str">
         <v>https://www.youtube.com/watch?v=02QyA29poAM</v>
@@ -3453,7 +3453,7 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G81" t="str">
         <v>3:13</v>
@@ -3479,7 +3479,7 @@
         <v>CAIN - So Long Sad Songs (Lyric Video)</v>
       </c>
       <c r="B82" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C82" t="str">
         <v>https://www.youtube.com/watch?v=feOv8nufa_I</v>
@@ -3491,7 +3491,7 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G82" t="str">
         <v>3:08</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Freya Skye - why'd you have to call</v>
       </c>
       <c r="B2" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=75o0FuwCdaA</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>4:19</v>
@@ -477,7 +477,7 @@
         <v>Jessie J - FEEL IT ON ME (Lyric Visualiser) (Official Lyric Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=DGmbe49F8aI</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>2:30</v>
@@ -1503,7 +1503,7 @@
         <v>David Guetta, TeddySwims, Tones And I - Gone Gone Gone (Unplugged) [Visualizer]</v>
       </c>
       <c r="B30" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=eWglDE7O5r8</v>
@@ -1515,7 +1515,7 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G30" t="str">
         <v>3:33</v>
@@ -1541,7 +1541,7 @@
         <v>SANTOS BRAVOS “KAWASAKI” Performance Video</v>
       </c>
       <c r="B31" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=Cmy8CsYIUL0</v>
@@ -1553,7 +1553,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G31" t="str">
         <v>2:41</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Freya Skye - why'd you have to call</v>
       </c>
       <c r="B2" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=75o0FuwCdaA</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>4:19</v>
@@ -477,7 +477,7 @@
         <v>Jessie J - FEEL IT ON ME (Lyric Visualiser) (Official Lyric Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=DGmbe49F8aI</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>2:30</v>
@@ -1465,7 +1465,7 @@
         <v>Katelyn Tarver - So Am I (Official Music Video)</v>
       </c>
       <c r="B29" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=MjUiVPzMQHw</v>
@@ -1477,7 +1477,7 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G29" t="str">
         <v>2:52</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Freya Skye - why'd you have to call</v>
       </c>
       <c r="B2" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=75o0FuwCdaA</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>4:19</v>
@@ -477,7 +477,7 @@
         <v>Jessie J - FEEL IT ON ME (Lyric Visualiser) (Official Lyric Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=DGmbe49F8aI</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>2:30</v>
@@ -1123,7 +1123,7 @@
         <v>Jessie Ware - I Could Get Used To This (Live on The Graham Norton Show)</v>
       </c>
       <c r="B20" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=kGeamxRf8Gw</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G20" t="str">
         <v>3:50</v>
@@ -1389,7 +1389,7 @@
         <v>Zara Larsson - Lush Life (Official UGC Compilation Video)</v>
       </c>
       <c r="B27" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C27" t="str">
         <v>https://www.youtube.com/watch?v=FgAyfRnbbRs</v>
@@ -1401,7 +1401,7 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G27" t="str">
         <v>3:22</v>
@@ -1427,7 +1427,7 @@
         <v>Only The Poets - Monumental</v>
       </c>
       <c r="B28" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=nwXiAjjl6NE</v>
@@ -1439,7 +1439,7 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G28" t="str">
         <v>2:48</v>
@@ -2529,7 +2529,7 @@
         <v>We Three - Drunk Driving (Official Music Video)</v>
       </c>
       <c r="B57" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C57" t="str">
         <v>https://www.youtube.com/watch?v=BTqRGxSX6AQ</v>
@@ -2541,7 +2541,7 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G57" t="str">
         <v>4:27</v>
@@ -2947,7 +2947,7 @@
         <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
       </c>
       <c r="B68" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C68" t="str">
         <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
@@ -2959,7 +2959,7 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G68" t="str">
         <v>3:46</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Freya Skye - why'd you have to call</v>
       </c>
       <c r="B2" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=75o0FuwCdaA</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>4:19</v>
@@ -477,7 +477,7 @@
         <v>Jessie J - FEEL IT ON ME (Lyric Visualiser) (Official Lyric Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=DGmbe49F8aI</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>2:30</v>
@@ -1351,7 +1351,7 @@
         <v>Paris Paloma - Good Girl [Official Music Video]</v>
       </c>
       <c r="B26" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=qhO6VMC-nx0</v>
@@ -1363,7 +1363,7 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G26" t="str">
         <v>4:47</v>
@@ -2909,7 +2909,7 @@
         <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
       </c>
       <c r="B67" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C67" t="str">
         <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
@@ -2921,7 +2921,7 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G67" t="str">
         <v>2:56</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Freya Skye - why'd you have to call</v>
       </c>
       <c r="B2" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=75o0FuwCdaA</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>4:19</v>
@@ -477,7 +477,7 @@
         <v>Jessie J - FEEL IT ON ME (Lyric Visualiser) (Official Lyric Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=DGmbe49F8aI</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>2:30</v>
@@ -2871,7 +2871,7 @@
         <v>Holly Humberstone - To Love Somebody (Official Video)</v>
       </c>
       <c r="B66" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C66" t="str">
         <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
@@ -2883,7 +2883,7 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G66" t="str">
         <v>3:59</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Freya Skye - why'd you have to call</v>
       </c>
       <c r="B2" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=75o0FuwCdaA</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>4:19</v>
@@ -477,7 +477,7 @@
         <v>Jessie J - FEEL IT ON ME (Lyric Visualiser) (Official Lyric Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=DGmbe49F8aI</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>2:30</v>
@@ -1313,7 +1313,7 @@
         <v>The Kiffness &amp; Matisyahu - ONE DAY (ft. Andel and Nalyn) [OFFICIAL VIDEO]</v>
       </c>
       <c r="B25" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=buS21tVq5r0</v>
@@ -1325,7 +1325,7 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G25" t="str">
         <v>3:07</v>
@@ -3593,7 +3593,7 @@
         <v>Def Leppard - Rejoice (Lyric Video)</v>
       </c>
       <c r="B85" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C85" t="str">
         <v>https://www.youtube.com/watch?v=zy2TLLeNgp0</v>
@@ -3605,7 +3605,7 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G85" t="str">
         <v>4:21</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Freya Skye - why'd you have to call</v>
       </c>
       <c r="B2" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=75o0FuwCdaA</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>4:19</v>
@@ -477,7 +477,7 @@
         <v>Jessie J - FEEL IT ON ME (Lyric Visualiser) (Official Lyric Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=DGmbe49F8aI</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>2:30</v>
@@ -1120,7 +1120,7 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Live on The Graham Norton Show)</v>
+        <v>Jessie Ware - I Could Get Used To This ( Live at Graham Norton)</v>
       </c>
       <c r="B20" t="str">
         <v>5 days ago</v>
@@ -1153,7 +1153,7 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Live on The Graham Norton Show) - Jessie Ware</v>
+        <v>Jessie Ware - I Could Get Used To This ( Live at Graham Norton) - Jessie Ware</v>
       </c>
     </row>
     <row r="21">
@@ -1275,7 +1275,7 @@
         <v>The Cure - Boys Don't Cry (86 Mix) (Official Lyric Video)</v>
       </c>
       <c r="B24" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=isNztTjXQsQ</v>
@@ -1287,7 +1287,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G24" t="str">
         <v>2:39</v>
@@ -2567,7 +2567,7 @@
         <v>Timebelle - Top of the World (Mood Video)</v>
       </c>
       <c r="B58" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C58" t="str">
         <v>https://www.youtube.com/watch?v=r9KyYK_E34s</v>
@@ -2579,7 +2579,7 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G58" t="str">
         <v>3:01</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Freya Skye - why'd you have to call</v>
       </c>
       <c r="B2" t="str">
-        <v>19 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=75o0FuwCdaA</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>19 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>4:19</v>
@@ -477,7 +477,7 @@
         <v>Jessie J - FEEL IT ON ME (Lyric Visualiser) (Official Lyric Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>19 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=DGmbe49F8aI</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>19 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>2:30</v>
@@ -629,7 +629,7 @@
         <v>Kesha - RED FLAG. (Red Carpet) OFFICIAL MUSIC VIDEO</v>
       </c>
       <c r="B7" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=pvrJ5RnPAEA</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G7" t="str">
         <v>3:41</v>
@@ -971,7 +971,7 @@
         <v>Nothing But Thieves - Sorry (Official Audio)</v>
       </c>
       <c r="B16" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=D7QfVqo5YqY</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G16" t="str">
         <v>3:37</v>
@@ -1161,7 +1161,7 @@
         <v>JOSEPH - Water in the Room (Official Music Video)</v>
       </c>
       <c r="B21" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=tNmT47k6MjM</v>
@@ -1173,7 +1173,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G21" t="str">
         <v>3:10</v>
@@ -1199,7 +1199,7 @@
         <v>Dean Lewis - I Am Getting Well (Lyric Video)</v>
       </c>
       <c r="B22" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=6ecgOSOMWzc</v>
@@ -1211,7 +1211,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G22" t="str">
         <v>2:44</v>
@@ -1237,7 +1237,7 @@
         <v>Take That - Take That and Party (Official HD Video)</v>
       </c>
       <c r="B23" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=DAerJcerikU</v>
@@ -1249,7 +1249,7 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G23" t="str">
         <v>2:57</v>
@@ -2453,7 +2453,7 @@
         <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video)</v>
       </c>
       <c r="B55" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C55" t="str">
         <v>https://www.youtube.com/watch?v=yUAvfo8fpuU</v>
@@ -2465,7 +2465,7 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G55" t="str">
         <v>3:50</v>
@@ -2491,7 +2491,7 @@
         <v>I Had To Explain "How Music Works" LIVE In Concert</v>
       </c>
       <c r="B56" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C56" t="str">
         <v>https://www.youtube.com/watch?v=KnsBdAM3HqY</v>
@@ -2503,7 +2503,7 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G56" t="str">
         <v>5:32</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Freya Skye - why'd you have to call</v>
       </c>
       <c r="B2" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=75o0FuwCdaA</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>4:19</v>
@@ -477,7 +477,7 @@
         <v>Jessie J - FEEL IT ON ME (Lyric Visualiser) (Official Lyric Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=DGmbe49F8aI</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>2:30</v>
@@ -1085,7 +1085,7 @@
         <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered)</v>
       </c>
       <c r="B19" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=I7a-pDZFE7U</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G19" t="str">
         <v>4:38</v>
@@ -2263,7 +2263,7 @@
         <v>Beck - Love (Audio)</v>
       </c>
       <c r="B50" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C50" t="str">
         <v>https://www.youtube.com/watch?v=ByABj3Xof1I</v>
@@ -2275,7 +2275,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G50" t="str">
         <v>3:14</v>
@@ -2377,7 +2377,7 @@
         <v>Jason Derulo - Sexy For Me [Official Music Video]</v>
       </c>
       <c r="B53" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C53" t="str">
         <v>https://www.youtube.com/watch?v=9ST-eBNL0NU</v>
@@ -2389,7 +2389,7 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G53" t="str">
         <v>2:10</v>
@@ -2415,7 +2415,7 @@
         <v>Lights - COME GET YOUR GIRL</v>
       </c>
       <c r="B54" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C54" t="str">
         <v>https://www.youtube.com/watch?v=EhzX2y5MpSM</v>
@@ -2427,7 +2427,7 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G54" t="str">
         <v>3:52</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Freya Skye - why'd you have to call</v>
       </c>
       <c r="B2" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=75o0FuwCdaA</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>4:19</v>
@@ -477,7 +477,7 @@
         <v>Jessie J - FEEL IT ON ME (Lyric Visualiser) (Official Lyric Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=DGmbe49F8aI</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>2:30</v>
@@ -895,7 +895,7 @@
         <v>Take That - Once You've Tasted Love (Live on Pebble Mill, 1992)</v>
       </c>
       <c r="B14" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=dOeoDOueESk</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G14" t="str">
         <v>3:36</v>
@@ -2225,7 +2225,7 @@
         <v>Teddy Swims - Need You More (Live - Green Room Sessions)</v>
       </c>
       <c r="B49" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C49" t="str">
         <v>https://www.youtube.com/watch?v=1ugf5aaY4pY</v>
@@ -2237,7 +2237,7 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G49" t="str">
         <v>3:16</v>
@@ -2339,7 +2339,7 @@
         <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show</v>
       </c>
       <c r="B52" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C52" t="str">
         <v>https://www.youtube.com/watch?v=ylifHFJWJ_c</v>
@@ -2351,7 +2351,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G52" t="str">
         <v>4:10</v>
@@ -2795,7 +2795,7 @@
         <v>Neal Francis - Back It Up (Live At The Salt Shed)</v>
       </c>
       <c r="B64" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C64" t="str">
         <v>https://www.youtube.com/watch?v=46iZEdsxjC0</v>
@@ -2807,7 +2807,7 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G64" t="str">
         <v>5:01</v>
@@ -2833,7 +2833,7 @@
         <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
       </c>
       <c r="B65" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C65" t="str">
         <v>https://www.youtube.com/watch?v=K2nG1Uukz7E</v>
@@ -2845,7 +2845,7 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G65" t="str">
         <v>4:12</v>
@@ -3555,7 +3555,7 @@
         <v>Lana Lubany - BAD IDEA (Official Video)</v>
       </c>
       <c r="B84" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C84" t="str">
         <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
@@ -3567,7 +3567,7 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G84" t="str">
         <v>2:59</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L207"/>
+  <dimension ref="A1:L208"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -439,7 +439,7 @@
         <v>Freya Skye - why'd you have to call</v>
       </c>
       <c r="B2" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=75o0FuwCdaA</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G2" t="str">
         <v>4:19</v>
@@ -477,7 +477,7 @@
         <v>Jessie J - FEEL IT ON ME (Lyric Visualiser) (Official Lyric Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=DGmbe49F8aI</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G3" t="str">
         <v>2:30</v>
@@ -553,7 +553,7 @@
         <v>Clara Mae - Never Been Yours ft. Bob John Holt</v>
       </c>
       <c r="B5" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=HtVuKBlBuPg</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G5" t="str">
         <v>2:33</v>
@@ -591,7 +591,7 @@
         <v>Metric - Victim of Luck (Official Music Video)</v>
       </c>
       <c r="B6" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=shmhTOUd8mA</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G6" t="str">
         <v>3:25</v>
@@ -743,7 +743,7 @@
         <v>Bob Moses - Need You Tonight (INXS Cover) - Brooklyn Mirage 2023</v>
       </c>
       <c r="B10" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=CoCqPwDIBOA</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G10" t="str">
         <v>3:08</v>
@@ -781,7 +781,7 @@
         <v>Marc Anthony - Un Mal Sueño (Visualizer)</v>
       </c>
       <c r="B11" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=18yZq5xtke4</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G11" t="str">
         <v>3:28</v>
@@ -819,7 +819,7 @@
         <v>Marc Anthony - Contra La Corriente (Visualizer)</v>
       </c>
       <c r="B12" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=IGLmJ71oHhQ</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G12" t="str">
         <v>5:05</v>
@@ -857,7 +857,7 @@
         <v>Loreen - Feels Like Heaven</v>
       </c>
       <c r="B13" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=BQc97moyQBg</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G13" t="str">
         <v>3:14</v>
@@ -933,7 +933,7 @@
         <v>Paul McCartney, Wings - Nineteen Hundred And Eighty Five (Visualiser)</v>
       </c>
       <c r="B15" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=a4AIjUHuWpU</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G15" t="str">
         <v>5:31</v>
@@ -1009,7 +1009,7 @@
         <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music</v>
       </c>
       <c r="B17" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=KdsHxyl4bE8</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G17" t="str">
         <v>4:58</v>
@@ -1047,7 +1047,7 @@
         <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield, CA (2026)</v>
       </c>
       <c r="B18" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=Mwkl_Cz_SG8</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G18" t="str">
         <v>5:08</v>
@@ -2187,7 +2187,7 @@
         <v>Demi Lovato - Ghost (Live)</v>
       </c>
       <c r="B48" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C48" t="str">
         <v>https://www.youtube.com/watch?v=E-ECwdRndVA</v>
@@ -2199,7 +2199,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G48" t="str">
         <v>4:05</v>
@@ -2301,7 +2301,7 @@
         <v>The Offspring - Looking Out For #1 | Live in Spokane, WA (2026)</v>
       </c>
       <c r="B51" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C51" t="str">
         <v>https://www.youtube.com/watch?v=2HSbo51EFNg</v>
@@ -2313,7 +2313,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G51" t="str">
         <v>2:57</v>
@@ -2681,7 +2681,7 @@
         <v>SIENNA SPIRO - Die On This Hill (Official Music Video)</v>
       </c>
       <c r="B61" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C61" t="str">
         <v>https://www.youtube.com/watch?v=5RNy_1odv20</v>
@@ -2693,7 +2693,7 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G61" t="str">
         <v>4:01</v>
@@ -2719,7 +2719,7 @@
         <v>Amazon Music presents: Sienna Spiro - You Stole The Show</v>
       </c>
       <c r="B62" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C62" t="str">
         <v>https://www.youtube.com/watch?v=stYIRyCLN4Y</v>
@@ -2731,7 +2731,7 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G62" t="str">
         <v>3:24</v>
@@ -2757,7 +2757,7 @@
         <v>Harry Styles - Aperture (Official Video)</v>
       </c>
       <c r="B63" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C63" t="str">
         <v>https://www.youtube.com/watch?v=7sxVHYZ_PnA</v>
@@ -2769,7 +2769,7 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G63" t="str">
         <v>5:52</v>
@@ -4236,13 +4236,13 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>golden boy</v>
+        <v>Como en el Idilio</v>
       </c>
       <c r="B102" t="str">
         <v/>
       </c>
       <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/golden-boy/1872543012</v>
+        <v>https://music.apple.com/us/song/como-en-el-idilio/1870716613</v>
       </c>
       <c r="D102" t="str">
         <v>2026-02-05</v>
@@ -4251,25 +4251,25 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>stardust - EP</v>
+        <v>Como en el Idilio - Single</v>
       </c>
       <c r="G102" t="str">
-        <v>3:17</v>
+        <v>4:27</v>
       </c>
       <c r="H102" t="str">
-        <v>Freya Skye</v>
+        <v>Marc Anthony</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/freya-skye/1541643053</v>
+        <v>https://music.apple.com/us/artist/marc-anthony/217029</v>
       </c>
       <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/golden-boy/1872542998</v>
+        <v>https://music.apple.com/us/album/como-en-el-idilio/1870716612</v>
       </c>
       <c r="L102" t="str">
-        <v>golden boy - Freya Skye</v>
+        <v>Como en el Idilio - Marc Anthony</v>
       </c>
     </row>
     <row r="103">
@@ -4540,13 +4540,13 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Penny in the Lake</v>
+        <v>golden boy</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/penny-in-the-lake/1844710053</v>
+        <v>https://music.apple.com/us/song/golden-boy/1872543012</v>
       </c>
       <c r="D110" t="str">
         <v>2026-02-05</v>
@@ -4555,25 +4555,25 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>Singin’ to an Empty Chair</v>
+        <v>stardust - EP</v>
       </c>
       <c r="G110" t="str">
-        <v>3:51</v>
+        <v>3:17</v>
       </c>
       <c r="H110" t="str">
-        <v>Ratboys</v>
+        <v>Freya Skye</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/ratboys/997909855</v>
+        <v>https://music.apple.com/us/artist/freya-skye/1541643053</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/penny-in-the-lake/1844710034</v>
+        <v>https://music.apple.com/us/album/golden-boy/1872542998</v>
       </c>
       <c r="L110" t="str">
-        <v>Penny in the Lake - Ratboys</v>
+        <v>golden boy - Freya Skye</v>
       </c>
     </row>
     <row r="111">
@@ -4616,13 +4616,13 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Heaven</v>
+        <v>Penny in the Lake</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/heaven/1862570892</v>
+        <v>https://music.apple.com/us/song/penny-in-the-lake/1844710053</v>
       </c>
       <c r="D112" t="str">
         <v>2026-02-05</v>
@@ -4631,25 +4631,25 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>Ambiguous Desire</v>
+        <v>Singin’ to an Empty Chair</v>
       </c>
       <c r="G112" t="str">
-        <v>4:26</v>
+        <v>3:51</v>
       </c>
       <c r="H112" t="str">
-        <v>Arlo Parks</v>
+        <v>Ratboys</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/arlo-parks/1291875084</v>
+        <v>https://music.apple.com/us/artist/ratboys/997909855</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/heaven/1862570378</v>
+        <v>https://music.apple.com/us/album/penny-in-the-lake/1844710034</v>
       </c>
       <c r="L112" t="str">
-        <v>Heaven - Arlo Parks</v>
+        <v>Penny in the Lake - Ratboys</v>
       </c>
     </row>
     <row r="113">
@@ -8262,9 +8262,47 @@
         <v>Quién - Daniela Darcourt</v>
       </c>
     </row>
+    <row r="208">
+      <c r="A208" t="str">
+        <v>Heaven</v>
+      </c>
+      <c r="B208" t="str">
+        <v/>
+      </c>
+      <c r="C208" t="str">
+        <v>https://music.apple.com/us/song/heaven/1862570892</v>
+      </c>
+      <c r="D208" t="str">
+        <v>2026-02-05</v>
+      </c>
+      <c r="E208" t="str">
+        <v/>
+      </c>
+      <c r="F208" t="str">
+        <v>Ambiguous Desire</v>
+      </c>
+      <c r="G208" t="str">
+        <v>4:26</v>
+      </c>
+      <c r="H208" t="str">
+        <v>Arlo Parks</v>
+      </c>
+      <c r="I208" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J208" t="str">
+        <v>https://music.apple.com/us/artist/arlo-parks/1291875084</v>
+      </c>
+      <c r="K208" t="str">
+        <v>https://music.apple.com/us/album/heaven/1862570378</v>
+      </c>
+      <c r="L208" t="str">
+        <v>Heaven - Arlo Parks</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L207"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L208"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
@@ -705,7 +705,7 @@
         <v>Vera Blue - Hold (Live on Sydney Harbour)</v>
       </c>
       <c r="B9" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=SYEwk-EZJPU</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G9" t="str">
         <v>3:37</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
@@ -667,7 +667,7 @@
         <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Studio)</v>
       </c>
       <c r="B8" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=mgsdQI-GVMM</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G8" t="str">
         <v>3:19</v>
@@ -2111,7 +2111,7 @@
         <v>TINI - FUTTTURA LIVE - el cielo + fresa</v>
       </c>
       <c r="B46" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=q_rrgJZAdNg</v>
@@ -2123,7 +2123,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G46" t="str">
         <v>5:58</v>
@@ -2149,7 +2149,7 @@
         <v>Charley - Serial Idealist (Official Video)</v>
       </c>
       <c r="B47" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C47" t="str">
         <v>https://www.youtube.com/watch?v=uVIuKbPJz0U</v>
@@ -2161,7 +2161,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G47" t="str">
         <v>3:26</v>
@@ -2605,7 +2605,7 @@
         <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop)</v>
       </c>
       <c r="B59" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C59" t="str">
         <v>https://www.youtube.com/watch?v=57a_OheOlDw</v>
@@ -2617,7 +2617,7 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G59" t="str">
         <v>3:20</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
@@ -2035,7 +2035,7 @@
         <v>India Martinez, Coro ArteSí de Olvidados - Niño Sin Miedo</v>
       </c>
       <c r="B44" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C44" t="str">
         <v>https://www.youtube.com/watch?v=Vug_FPbXe9E</v>
@@ -2047,7 +2047,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G44" t="str">
         <v>4:04</v>
@@ -2073,7 +2073,7 @@
         <v>Chelsea Cutler - BAD (Official Lyric Video)</v>
       </c>
       <c r="B45" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C45" t="str">
         <v>https://www.youtube.com/watch?v=ZIW2vA3Zs1U</v>
@@ -2085,7 +2085,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G45" t="str">
         <v>2:16</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
@@ -445,7 +445,7 @@
         <v>https://www.youtube.com/watch?v=75o0FuwCdaA</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -483,7 +483,7 @@
         <v>https://www.youtube.com/watch?v=DGmbe49F8aI</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -515,19 +515,19 @@
         <v>Marc Anthony - Make It With You (Visualizer)</v>
       </c>
       <c r="B4" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=WHnz1jDrxw8</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E4" t="str">
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G4" t="str">
         <v>4:24</v>
@@ -559,7 +559,7 @@
         <v>https://www.youtube.com/watch?v=HtVuKBlBuPg</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -597,7 +597,7 @@
         <v>https://www.youtube.com/watch?v=shmhTOUd8mA</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -635,7 +635,7 @@
         <v>https://www.youtube.com/watch?v=pvrJ5RnPAEA</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -673,7 +673,7 @@
         <v>https://www.youtube.com/watch?v=mgsdQI-GVMM</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -711,7 +711,7 @@
         <v>https://www.youtube.com/watch?v=SYEwk-EZJPU</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -749,7 +749,7 @@
         <v>https://www.youtube.com/watch?v=CoCqPwDIBOA</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -787,7 +787,7 @@
         <v>https://www.youtube.com/watch?v=18yZq5xtke4</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://www.youtube.com/watch?v=IGLmJ71oHhQ</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -863,7 +863,7 @@
         <v>https://www.youtube.com/watch?v=BQc97moyQBg</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -901,7 +901,7 @@
         <v>https://www.youtube.com/watch?v=dOeoDOueESk</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -939,7 +939,7 @@
         <v>https://www.youtube.com/watch?v=a4AIjUHuWpU</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -977,7 +977,7 @@
         <v>https://www.youtube.com/watch?v=D7QfVqo5YqY</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1015,7 +1015,7 @@
         <v>https://www.youtube.com/watch?v=KdsHxyl4bE8</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1053,7 +1053,7 @@
         <v>https://www.youtube.com/watch?v=Mwkl_Cz_SG8</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1091,7 +1091,7 @@
         <v>https://www.youtube.com/watch?v=I7a-pDZFE7U</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1129,7 +1129,7 @@
         <v>https://www.youtube.com/watch?v=kGeamxRf8Gw</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1167,7 +1167,7 @@
         <v>https://www.youtube.com/watch?v=tNmT47k6MjM</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1205,7 +1205,7 @@
         <v>https://www.youtube.com/watch?v=6ecgOSOMWzc</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1243,7 +1243,7 @@
         <v>https://www.youtube.com/watch?v=DAerJcerikU</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1281,7 +1281,7 @@
         <v>https://www.youtube.com/watch?v=isNztTjXQsQ</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1319,7 +1319,7 @@
         <v>https://www.youtube.com/watch?v=buS21tVq5r0</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1357,7 +1357,7 @@
         <v>https://www.youtube.com/watch?v=qhO6VMC-nx0</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1395,7 +1395,7 @@
         <v>https://www.youtube.com/watch?v=FgAyfRnbbRs</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1433,7 +1433,7 @@
         <v>https://www.youtube.com/watch?v=nwXiAjjl6NE</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1471,7 +1471,7 @@
         <v>https://www.youtube.com/watch?v=MjUiVPzMQHw</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1509,7 +1509,7 @@
         <v>https://www.youtube.com/watch?v=eWglDE7O5r8</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1547,7 +1547,7 @@
         <v>https://www.youtube.com/watch?v=Cmy8CsYIUL0</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1585,7 +1585,7 @@
         <v>https://www.youtube.com/watch?v=sf6eRmInk1s</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1623,7 +1623,7 @@
         <v>https://www.youtube.com/watch?v=fv9prIYHHzk</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1661,7 +1661,7 @@
         <v>https://www.youtube.com/watch?v=T9YvLA2cdZs</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1699,7 +1699,7 @@
         <v>https://www.youtube.com/watch?v=dPWc_6IdDJk</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1737,7 +1737,7 @@
         <v>https://www.youtube.com/watch?v=CV5rR9JZK-0</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1775,7 +1775,7 @@
         <v>https://www.youtube.com/watch?v=9HwTj3NZ16E</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1813,7 +1813,7 @@
         <v>https://www.youtube.com/watch?v=Lmus-UbL1H0</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1851,7 +1851,7 @@
         <v>https://www.youtube.com/watch?v=bu6WSMDDPGY</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1889,7 +1889,7 @@
         <v>https://www.youtube.com/watch?v=zcYeoGBglC0</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1927,7 +1927,7 @@
         <v>https://www.youtube.com/watch?v=3igYRj82EiU</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1965,7 +1965,7 @@
         <v>https://www.youtube.com/watch?v=0bhcO4Yphuo</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -2003,7 +2003,7 @@
         <v>https://www.youtube.com/watch?v=Jjz1wFe5dMo</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -2041,7 +2041,7 @@
         <v>https://www.youtube.com/watch?v=Vug_FPbXe9E</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2079,7 +2079,7 @@
         <v>https://www.youtube.com/watch?v=ZIW2vA3Zs1U</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -2117,7 +2117,7 @@
         <v>https://www.youtube.com/watch?v=q_rrgJZAdNg</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -2155,7 +2155,7 @@
         <v>https://www.youtube.com/watch?v=uVIuKbPJz0U</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2193,7 +2193,7 @@
         <v>https://www.youtube.com/watch?v=E-ECwdRndVA</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2231,7 +2231,7 @@
         <v>https://www.youtube.com/watch?v=1ugf5aaY4pY</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -2269,7 +2269,7 @@
         <v>https://www.youtube.com/watch?v=ByABj3Xof1I</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2307,7 +2307,7 @@
         <v>https://www.youtube.com/watch?v=2HSbo51EFNg</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2345,7 +2345,7 @@
         <v>https://www.youtube.com/watch?v=ylifHFJWJ_c</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2383,7 +2383,7 @@
         <v>https://www.youtube.com/watch?v=9ST-eBNL0NU</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2421,7 +2421,7 @@
         <v>https://www.youtube.com/watch?v=EhzX2y5MpSM</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2459,7 +2459,7 @@
         <v>https://www.youtube.com/watch?v=yUAvfo8fpuU</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2497,7 +2497,7 @@
         <v>https://www.youtube.com/watch?v=KnsBdAM3HqY</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2535,7 +2535,7 @@
         <v>https://www.youtube.com/watch?v=BTqRGxSX6AQ</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2573,7 +2573,7 @@
         <v>https://www.youtube.com/watch?v=r9KyYK_E34s</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2611,7 +2611,7 @@
         <v>https://www.youtube.com/watch?v=57a_OheOlDw</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2649,7 +2649,7 @@
         <v>https://www.youtube.com/watch?v=-5Aa8NTiRqE</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -2687,7 +2687,7 @@
         <v>https://www.youtube.com/watch?v=5RNy_1odv20</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -2725,7 +2725,7 @@
         <v>https://www.youtube.com/watch?v=stYIRyCLN4Y</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -2763,7 +2763,7 @@
         <v>https://www.youtube.com/watch?v=7sxVHYZ_PnA</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -2801,7 +2801,7 @@
         <v>https://www.youtube.com/watch?v=46iZEdsxjC0</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -2839,7 +2839,7 @@
         <v>https://www.youtube.com/watch?v=K2nG1Uukz7E</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -2877,7 +2877,7 @@
         <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -2915,7 +2915,7 @@
         <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -2953,7 +2953,7 @@
         <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -2991,7 +2991,7 @@
         <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -3029,7 +3029,7 @@
         <v>https://www.youtube.com/watch?v=pnAz9RwGSek</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -3067,7 +3067,7 @@
         <v>https://www.youtube.com/watch?v=u7aPv2saz_I</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -3105,7 +3105,7 @@
         <v>https://www.youtube.com/watch?v=WGb8KVdqs6k</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -3143,7 +3143,7 @@
         <v>https://www.youtube.com/watch?v=X1ZeY4Y3l1M</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -3181,7 +3181,7 @@
         <v>https://www.youtube.com/watch?v=rzuD5szQhso</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -3219,7 +3219,7 @@
         <v>https://www.youtube.com/watch?v=UPuK6wV5Zco</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -3257,7 +3257,7 @@
         <v>https://www.youtube.com/watch?v=9hW9sNMn2A0</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -3295,7 +3295,7 @@
         <v>https://www.youtube.com/watch?v=JMYvXleIwfU</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -3333,7 +3333,7 @@
         <v>https://www.youtube.com/watch?v=vOzX-o11seI</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -3371,7 +3371,7 @@
         <v>https://www.youtube.com/watch?v=86k4E6ydHVU</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -3409,7 +3409,7 @@
         <v>https://www.youtube.com/watch?v=-UWIFAiOOPE</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -3447,7 +3447,7 @@
         <v>https://www.youtube.com/watch?v=02QyA29poAM</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -3485,7 +3485,7 @@
         <v>https://www.youtube.com/watch?v=feOv8nufa_I</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -3517,19 +3517,19 @@
         <v>Harry Styles - Aperture (Official Audio)</v>
       </c>
       <c r="B83" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C83" t="str">
         <v>https://www.youtube.com/watch?v=rA_eCxPay7E</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E83" t="str">
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G83" t="str">
         <v>5:14</v>
@@ -3561,7 +3561,7 @@
         <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -3599,7 +3599,7 @@
         <v>https://www.youtube.com/watch?v=zy2TLLeNgp0</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E85" t="str">
         <v/>
@@ -3637,7 +3637,7 @@
         <v>https://www.youtube.com/watch?v=JzOUJZPky6o</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3675,7 +3675,7 @@
         <v>https://www.youtube.com/watch?v=kfF0bVZMCw0</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3713,7 +3713,7 @@
         <v>https://www.youtube.com/watch?v=dLzpNstMHZY</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3751,7 +3751,7 @@
         <v>https://www.youtube.com/watch?v=fo_j8Fqag8I</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3789,7 +3789,7 @@
         <v>https://www.youtube.com/watch?v=7sD9-MtV9CY</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -3827,7 +3827,7 @@
         <v>https://www.youtube.com/watch?v=3ATlH-Rtzmk</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -3865,7 +3865,7 @@
         <v>https://www.youtube.com/watch?v=kIRmKmEb2g0</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -3903,7 +3903,7 @@
         <v>https://www.youtube.com/watch?v=oJ-l2ptQwbQ</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E93" t="str">
         <v/>
@@ -3941,7 +3941,7 @@
         <v>https://www.youtube.com/watch?v=ShW-I63KD8w</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E94" t="str">
         <v/>
@@ -3979,7 +3979,7 @@
         <v>https://www.youtube.com/watch?v=66PDbaI-BVA</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E95" t="str">
         <v/>
@@ -4017,7 +4017,7 @@
         <v>https://www.youtube.com/watch?v=4tmW_JSXHII</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E96" t="str">
         <v/>
@@ -4055,7 +4055,7 @@
         <v>https://www.youtube.com/watch?v=6kZVtF8iaWw</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E97" t="str">
         <v/>
@@ -4093,7 +4093,7 @@
         <v>https://www.youtube.com/watch?v=guUvgEKkk1U</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E98" t="str">
         <v/>
@@ -4131,7 +4131,7 @@
         <v>https://www.youtube.com/watch?v=4okJouEbZ_s</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E99" t="str">
         <v/>
@@ -4169,7 +4169,7 @@
         <v>https://www.youtube.com/watch?v=yL_TxDF8WtI</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E100" t="str">
         <v/>
@@ -4207,7 +4207,7 @@
         <v>https://www.youtube.com/watch?v=0m45tTheoCs</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E101" t="str">
         <v/>
@@ -4245,7 +4245,7 @@
         <v>https://music.apple.com/us/song/como-en-el-idilio/1870716613</v>
       </c>
       <c r="D102" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E102" t="str">
         <v/>
@@ -4283,7 +4283,7 @@
         <v>https://music.apple.com/us/song/body/1871258331</v>
       </c>
       <c r="D103" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E103" t="str">
         <v/>
@@ -4321,7 +4321,7 @@
         <v>https://music.apple.com/us/song/dandelion/1869436838</v>
       </c>
       <c r="D104" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E104" t="str">
         <v/>
@@ -4359,7 +4359,7 @@
         <v>https://music.apple.com/us/song/lights-go-out/1870833473</v>
       </c>
       <c r="D105" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E105" t="str">
         <v/>
@@ -4397,7 +4397,7 @@
         <v>https://music.apple.com/us/song/the-great-divide/1872239886</v>
       </c>
       <c r="D106" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E106" t="str">
         <v/>
@@ -4435,7 +4435,7 @@
         <v>https://music.apple.com/us/song/trist%C3%B3n/1872585947</v>
       </c>
       <c r="D107" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E107" t="str">
         <v/>
@@ -4473,7 +4473,7 @@
         <v>https://music.apple.com/us/song/feed-the-streets/1869462051</v>
       </c>
       <c r="D108" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E108" t="str">
         <v/>
@@ -4511,7 +4511,7 @@
         <v>https://music.apple.com/us/song/i-did-this-to-myself/1861531672</v>
       </c>
       <c r="D109" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E109" t="str">
         <v/>
@@ -4549,7 +4549,7 @@
         <v>https://music.apple.com/us/song/golden-boy/1872543012</v>
       </c>
       <c r="D110" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E110" t="str">
         <v/>
@@ -4587,7 +4587,7 @@
         <v>https://music.apple.com/us/song/for-hire/1870722567</v>
       </c>
       <c r="D111" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E111" t="str">
         <v/>
@@ -4625,7 +4625,7 @@
         <v>https://music.apple.com/us/song/penny-in-the-lake/1844710053</v>
       </c>
       <c r="D112" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E112" t="str">
         <v/>
@@ -4663,7 +4663,7 @@
         <v>https://music.apple.com/us/song/mcarthur/1871231844</v>
       </c>
       <c r="D113" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E113" t="str">
         <v/>
@@ -4701,7 +4701,7 @@
         <v>https://music.apple.com/us/song/debris/1853069633</v>
       </c>
       <c r="D114" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E114" t="str">
         <v/>
@@ -4739,7 +4739,7 @@
         <v>https://music.apple.com/us/song/god-owes-me-money-live-at-apple-music-radio/1871521120</v>
       </c>
       <c r="D115" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E115" t="str">
         <v/>
@@ -4777,7 +4777,7 @@
         <v>https://music.apple.com/us/song/rockstar-raging-feat-swae-lee/1873028187</v>
       </c>
       <c r="D116" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E116" t="str">
         <v/>
@@ -4815,7 +4815,7 @@
         <v>https://music.apple.com/us/song/1-1/1870378316</v>
       </c>
       <c r="D117" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E117" t="str">
         <v/>
@@ -4853,7 +4853,7 @@
         <v>https://music.apple.com/us/song/still-sincere-feat-pinkpantheress/1862228374</v>
       </c>
       <c r="D118" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E118" t="str">
         <v/>
@@ -4891,7 +4891,7 @@
         <v>https://music.apple.com/us/song/two-car-garage/1869137588</v>
       </c>
       <c r="D119" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E119" t="str">
         <v/>
@@ -4929,7 +4929,7 @@
         <v>https://music.apple.com/us/song/fml/1872686260</v>
       </c>
       <c r="D120" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E120" t="str">
         <v/>
@@ -4967,7 +4967,7 @@
         <v>https://music.apple.com/us/song/faked-it-all-the-time/1871050032</v>
       </c>
       <c r="D121" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E121" t="str">
         <v/>
@@ -5005,7 +5005,7 @@
         <v>https://music.apple.com/us/song/house-of-the-rising-sun/1872111857</v>
       </c>
       <c r="D122" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E122" t="str">
         <v/>
@@ -5043,7 +5043,7 @@
         <v>https://music.apple.com/us/song/lorelei/1867640808</v>
       </c>
       <c r="D123" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E123" t="str">
         <v/>
@@ -5081,7 +5081,7 @@
         <v>https://music.apple.com/us/song/free/1870703329</v>
       </c>
       <c r="D124" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E124" t="str">
         <v/>
@@ -5119,7 +5119,7 @@
         <v>https://music.apple.com/us/song/assignment/1872764440</v>
       </c>
       <c r="D125" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E125" t="str">
         <v/>
@@ -5157,7 +5157,7 @@
         <v>https://music.apple.com/us/song/professional-heartbreaker/1871053476</v>
       </c>
       <c r="D126" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E126" t="str">
         <v/>
@@ -5195,7 +5195,7 @@
         <v>https://music.apple.com/us/song/tell-me-what-you-want/1871463892</v>
       </c>
       <c r="D127" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E127" t="str">
         <v/>
@@ -5233,7 +5233,7 @@
         <v>https://music.apple.com/us/song/aguas/1869455857</v>
       </c>
       <c r="D128" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E128" t="str">
         <v/>
@@ -5271,7 +5271,7 @@
         <v>https://music.apple.com/us/song/ants-in-my-room/1870967813</v>
       </c>
       <c r="D129" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E129" t="str">
         <v/>
@@ -5309,7 +5309,7 @@
         <v>https://music.apple.com/us/song/baddie/1849760827</v>
       </c>
       <c r="D130" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E130" t="str">
         <v/>
@@ -5347,7 +5347,7 @@
         <v>https://music.apple.com/us/song/what-you-need-a-colors-show/1870990925</v>
       </c>
       <c r="D131" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E131" t="str">
         <v/>
@@ -5385,7 +5385,7 @@
         <v>https://music.apple.com/us/song/ok-ok-hamdi-remix/1871538130</v>
       </c>
       <c r="D132" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E132" t="str">
         <v/>
@@ -5423,7 +5423,7 @@
         <v>https://music.apple.com/us/song/ever-and-ever-before-feat-m%C5%8Driah-courtney/1869383260</v>
       </c>
       <c r="D133" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E133" t="str">
         <v/>
@@ -5461,7 +5461,7 @@
         <v>https://music.apple.com/us/song/for-the-first-time-again/1834736723</v>
       </c>
       <c r="D134" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E134" t="str">
         <v/>
@@ -5499,7 +5499,7 @@
         <v>https://music.apple.com/us/song/liars-tale/1862207951</v>
       </c>
       <c r="D135" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E135" t="str">
         <v/>
@@ -5537,7 +5537,7 @@
         <v>https://music.apple.com/us/song/afraid-of-the-dark/1872184048</v>
       </c>
       <c r="D136" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E136" t="str">
         <v/>
@@ -5575,7 +5575,7 @@
         <v>https://music.apple.com/us/song/wake-up-calling/1862338150</v>
       </c>
       <c r="D137" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E137" t="str">
         <v/>
@@ -5613,7 +5613,7 @@
         <v>https://music.apple.com/us/song/high/1867202644</v>
       </c>
       <c r="D138" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E138" t="str">
         <v/>
@@ -5651,7 +5651,7 @@
         <v>https://music.apple.com/us/song/villain/1860126455</v>
       </c>
       <c r="D139" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E139" t="str">
         <v/>
@@ -5689,7 +5689,7 @@
         <v>https://music.apple.com/us/song/bad-idea-right/1869792549</v>
       </c>
       <c r="D140" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E140" t="str">
         <v/>
@@ -5727,7 +5727,7 @@
         <v>https://music.apple.com/us/song/residue/1863786787</v>
       </c>
       <c r="D141" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E141" t="str">
         <v/>
@@ -5765,7 +5765,7 @@
         <v>https://music.apple.com/us/song/i-used-to-go-to-this-bar/1839918872</v>
       </c>
       <c r="D142" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E142" t="str">
         <v/>
@@ -5803,7 +5803,7 @@
         <v>https://music.apple.com/us/song/starlight/1870989674</v>
       </c>
       <c r="D143" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E143" t="str">
         <v/>
@@ -5841,7 +5841,7 @@
         <v>https://music.apple.com/us/song/dandelion/1863154133</v>
       </c>
       <c r="D144" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E144" t="str">
         <v/>
@@ -5879,7 +5879,7 @@
         <v>https://music.apple.com/us/song/themselves/1845287173</v>
       </c>
       <c r="D145" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E145" t="str">
         <v/>
@@ -5917,7 +5917,7 @@
         <v>https://music.apple.com/us/song/high-maintenance/1872497656</v>
       </c>
       <c r="D146" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E146" t="str">
         <v/>
@@ -5955,7 +5955,7 @@
         <v>https://music.apple.com/us/song/trackhawk/1860991724</v>
       </c>
       <c r="D147" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E147" t="str">
         <v/>
@@ -5993,7 +5993,7 @@
         <v>https://music.apple.com/us/song/wheel-man/1872178895</v>
       </c>
       <c r="D148" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E148" t="str">
         <v/>
@@ -6031,7 +6031,7 @@
         <v>https://music.apple.com/us/song/natural-disaster/1871263211</v>
       </c>
       <c r="D149" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E149" t="str">
         <v/>
@@ -6069,7 +6069,7 @@
         <v>https://music.apple.com/us/song/prettier/1869745409</v>
       </c>
       <c r="D150" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E150" t="str">
         <v/>
@@ -6107,7 +6107,7 @@
         <v>https://music.apple.com/us/song/shotta-flow-8/1872760524</v>
       </c>
       <c r="D151" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E151" t="str">
         <v/>
@@ -6145,7 +6145,7 @@
         <v>https://music.apple.com/us/song/die-to-fall/1866902681</v>
       </c>
       <c r="D152" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E152" t="str">
         <v/>
@@ -6183,7 +6183,7 @@
         <v>https://music.apple.com/us/song/the-cruel-angels-thesis-neon-genesis-evangelion/1864932139</v>
       </c>
       <c r="D153" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E153" t="str">
         <v/>
@@ -6221,7 +6221,7 @@
         <v>https://music.apple.com/us/song/slow-burn/1851033862</v>
       </c>
       <c r="D154" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E154" t="str">
         <v/>
@@ -6259,7 +6259,7 @@
         <v>https://music.apple.com/us/song/too-late/1857999860</v>
       </c>
       <c r="D155" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E155" t="str">
         <v/>
@@ -6297,7 +6297,7 @@
         <v>https://music.apple.com/us/song/mono-feat-skaiwater/1869130804</v>
       </c>
       <c r="D156" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E156" t="str">
         <v/>
@@ -6335,7 +6335,7 @@
         <v>https://music.apple.com/us/song/thank-you-is-enough/1870679042</v>
       </c>
       <c r="D157" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E157" t="str">
         <v/>
@@ -6373,7 +6373,7 @@
         <v>https://music.apple.com/us/song/ridin/1869786726</v>
       </c>
       <c r="D158" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E158" t="str">
         <v/>
@@ -6411,7 +6411,7 @@
         <v>https://music.apple.com/us/song/possession/1872536200</v>
       </c>
       <c r="D159" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E159" t="str">
         <v/>
@@ -6449,7 +6449,7 @@
         <v>https://music.apple.com/us/song/poema/1872723644</v>
       </c>
       <c r="D160" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E160" t="str">
         <v/>
@@ -6487,7 +6487,7 @@
         <v>https://music.apple.com/us/song/live-without/1862777625</v>
       </c>
       <c r="D161" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E161" t="str">
         <v/>
@@ -6525,7 +6525,7 @@
         <v>https://music.apple.com/us/song/fan%C3%A1tico/1871611852</v>
       </c>
       <c r="D162" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E162" t="str">
         <v/>
@@ -6563,7 +6563,7 @@
         <v>https://music.apple.com/us/song/frozen-lake/1867287070</v>
       </c>
       <c r="D163" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E163" t="str">
         <v/>
@@ -6601,7 +6601,7 @@
         <v>https://music.apple.com/us/song/fine-shyt-eb-remix-feat-eric-bellinger/1870964385</v>
       </c>
       <c r="D164" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E164" t="str">
         <v/>
@@ -6639,7 +6639,7 @@
         <v>https://music.apple.com/us/song/hell-yeah-feat-waxmaster/1866602820</v>
       </c>
       <c r="D165" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E165" t="str">
         <v/>
@@ -6677,7 +6677,7 @@
         <v>https://music.apple.com/us/song/its-like-that/1858689757</v>
       </c>
       <c r="D166" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E166" t="str">
         <v/>
@@ -6715,7 +6715,7 @@
         <v>https://music.apple.com/us/song/a-s-a-p/1833414737</v>
       </c>
       <c r="D167" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E167" t="str">
         <v/>
@@ -6753,7 +6753,7 @@
         <v>https://music.apple.com/us/song/once-i-say/1867855025</v>
       </c>
       <c r="D168" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E168" t="str">
         <v/>
@@ -6791,7 +6791,7 @@
         <v>https://music.apple.com/us/song/believer/1862797080</v>
       </c>
       <c r="D169" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E169" t="str">
         <v/>
@@ -6829,7 +6829,7 @@
         <v>https://music.apple.com/us/song/i-envy-the-wind/1863202477</v>
       </c>
       <c r="D170" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E170" t="str">
         <v/>
@@ -6867,7 +6867,7 @@
         <v>https://music.apple.com/us/song/the-alchemist/1831827347</v>
       </c>
       <c r="D171" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E171" t="str">
         <v/>
@@ -6905,7 +6905,7 @@
         <v>https://music.apple.com/us/song/daysa/1861575845</v>
       </c>
       <c r="D172" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E172" t="str">
         <v/>
@@ -6943,7 +6943,7 @@
         <v>https://music.apple.com/us/song/fabulous/1862804005</v>
       </c>
       <c r="D173" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E173" t="str">
         <v/>
@@ -6981,7 +6981,7 @@
         <v>https://music.apple.com/us/song/me-asusta-amar-tanto-la-soledad/1866982109</v>
       </c>
       <c r="D174" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E174" t="str">
         <v/>
@@ -7019,7 +7019,7 @@
         <v>https://music.apple.com/us/song/brainchem/1870656942</v>
       </c>
       <c r="D175" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E175" t="str">
         <v/>
@@ -7057,7 +7057,7 @@
         <v>https://music.apple.com/us/song/boyfriend-in-yo-brain-notice-me/1871675026</v>
       </c>
       <c r="D176" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E176" t="str">
         <v/>
@@ -7095,7 +7095,7 @@
         <v>https://music.apple.com/us/song/giants/1869154957</v>
       </c>
       <c r="D177" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E177" t="str">
         <v/>
@@ -7133,7 +7133,7 @@
         <v>https://music.apple.com/us/song/scooby/1872510752</v>
       </c>
       <c r="D178" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E178" t="str">
         <v/>
@@ -7171,7 +7171,7 @@
         <v>https://music.apple.com/us/song/la-racha/1868757762</v>
       </c>
       <c r="D179" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E179" t="str">
         <v/>
@@ -7209,7 +7209,7 @@
         <v>https://music.apple.com/us/song/so-am-i/1867012209</v>
       </c>
       <c r="D180" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E180" t="str">
         <v/>
@@ -7247,7 +7247,7 @@
         <v>https://music.apple.com/us/song/best-thing/1860673616</v>
       </c>
       <c r="D181" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E181" t="str">
         <v/>
@@ -7285,7 +7285,7 @@
         <v>https://music.apple.com/us/song/count-it-back/1855219865</v>
       </c>
       <c r="D182" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E182" t="str">
         <v/>
@@ -7323,7 +7323,7 @@
         <v>https://music.apple.com/us/song/good-girl/1862640697</v>
       </c>
       <c r="D183" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E183" t="str">
         <v/>
@@ -7361,7 +7361,7 @@
         <v>https://music.apple.com/us/song/my-revival/1869465104</v>
       </c>
       <c r="D184" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E184" t="str">
         <v/>
@@ -7399,7 +7399,7 @@
         <v>https://music.apple.com/us/song/run-my-way/1860964996</v>
       </c>
       <c r="D185" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E185" t="str">
         <v/>
@@ -7437,7 +7437,7 @@
         <v>https://music.apple.com/us/song/cold-night/1867687787</v>
       </c>
       <c r="D186" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E186" t="str">
         <v/>
@@ -7475,7 +7475,7 @@
         <v>https://music.apple.com/us/song/away-with-the-fairies/1870603474</v>
       </c>
       <c r="D187" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E187" t="str">
         <v/>
@@ -7513,7 +7513,7 @@
         <v>https://music.apple.com/us/song/fragile/1866957569</v>
       </c>
       <c r="D188" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E188" t="str">
         <v/>
@@ -7551,7 +7551,7 @@
         <v>https://music.apple.com/us/song/slow-dancin/1871537173</v>
       </c>
       <c r="D189" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E189" t="str">
         <v/>
@@ -7589,7 +7589,7 @@
         <v>https://music.apple.com/us/song/never-kissed-a-cowboy/1866744530</v>
       </c>
       <c r="D190" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E190" t="str">
         <v/>
@@ -7627,7 +7627,7 @@
         <v>https://music.apple.com/us/song/more-of-what-matters/1871592720</v>
       </c>
       <c r="D191" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E191" t="str">
         <v/>
@@ -7665,7 +7665,7 @@
         <v>https://music.apple.com/us/song/is-this-the-real-you/1869323368</v>
       </c>
       <c r="D192" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E192" t="str">
         <v/>
@@ -7703,7 +7703,7 @@
         <v>https://music.apple.com/us/song/hud/1842015019</v>
       </c>
       <c r="D193" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E193" t="str">
         <v/>
@@ -7741,7 +7741,7 @@
         <v>https://music.apple.com/us/song/ego-death/1867855427</v>
       </c>
       <c r="D194" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E194" t="str">
         <v/>
@@ -7779,7 +7779,7 @@
         <v>https://music.apple.com/us/song/gas-station-love-remix/1872150728</v>
       </c>
       <c r="D195" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E195" t="str">
         <v/>
@@ -7817,7 +7817,7 @@
         <v>https://music.apple.com/us/song/disappear/1861907311</v>
       </c>
       <c r="D196" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E196" t="str">
         <v/>
@@ -7855,7 +7855,7 @@
         <v>https://music.apple.com/us/song/misbehave/1859630128</v>
       </c>
       <c r="D197" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E197" t="str">
         <v/>
@@ -7893,7 +7893,7 @@
         <v>https://music.apple.com/us/song/club-bizarre/1870355078</v>
       </c>
       <c r="D198" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E198" t="str">
         <v/>
@@ -7931,7 +7931,7 @@
         <v>https://music.apple.com/us/song/fly/1867903625</v>
       </c>
       <c r="D199" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E199" t="str">
         <v/>
@@ -7969,7 +7969,7 @@
         <v>https://music.apple.com/us/song/ily-anyway/1870369432</v>
       </c>
       <c r="D200" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E200" t="str">
         <v/>
@@ -8007,7 +8007,7 @@
         <v>https://music.apple.com/us/song/george-jones-feat-angela-autumn/1867306007</v>
       </c>
       <c r="D201" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E201" t="str">
         <v/>
@@ -8045,7 +8045,7 @@
         <v>https://music.apple.com/us/song/kiss-big/1837292261</v>
       </c>
       <c r="D202" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E202" t="str">
         <v/>
@@ -8083,7 +8083,7 @@
         <v>https://music.apple.com/us/song/praxis/1845253734</v>
       </c>
       <c r="D203" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E203" t="str">
         <v/>
@@ -8121,7 +8121,7 @@
         <v>https://music.apple.com/us/song/house/1866696487</v>
       </c>
       <c r="D204" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E204" t="str">
         <v/>
@@ -8159,7 +8159,7 @@
         <v>https://music.apple.com/us/song/cowboy-without-a-clue/1834024322</v>
       </c>
       <c r="D205" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E205" t="str">
         <v/>
@@ -8197,7 +8197,7 @@
         <v>https://music.apple.com/us/song/brincar/1871554907</v>
       </c>
       <c r="D206" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E206" t="str">
         <v/>
@@ -8235,7 +8235,7 @@
         <v>https://music.apple.com/us/song/qui%C3%A9n/1870329662</v>
       </c>
       <c r="D207" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E207" t="str">
         <v/>
@@ -8273,7 +8273,7 @@
         <v>https://music.apple.com/us/song/heaven/1862570892</v>
       </c>
       <c r="D208" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E208" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Freya Skye - why'd you have to call</v>
+        <v>LADY GAGA - ABRACADABRA (LIVE AT THE 2026 GRAMMYS)</v>
       </c>
       <c r="B2" t="str">
-        <v>1 day ago</v>
+        <v>5 hours ago</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=75o0FuwCdaA</v>
+        <v>https://www.youtube.com/watch?v=Rn89mUndYbo</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-06</v>
@@ -451,13 +451,13 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>1 day ago</v>
+        <v>5 hours ago</v>
       </c>
       <c r="G2" t="str">
-        <v>4:19</v>
+        <v>4:16</v>
       </c>
       <c r="H2" t="str">
-        <v>Freya Skye</v>
+        <v>Lady Gaga</v>
       </c>
       <c r="I2" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>Freya Skye - why'd you have to call - Freya Skye</v>
+        <v>LADY GAGA - ABRACADABRA (LIVE AT THE 2026 GRAMMYS) - Lady Gaga</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Jessie J - FEEL IT ON ME (Lyric Visualiser) (Official Lyric Video)</v>
+        <v>Carlos Vives - Te Dedico (Official Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>1 day ago</v>
+        <v>4 hours ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=DGmbe49F8aI</v>
+        <v>https://www.youtube.com/watch?v=H8KW0SgW99I</v>
       </c>
       <c r="D3" t="str">
         <v>2026-02-06</v>
@@ -489,13 +489,13 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>1 day ago</v>
+        <v>4 hours ago</v>
       </c>
       <c r="G3" t="str">
-        <v>2:30</v>
+        <v>3:53</v>
       </c>
       <c r="H3" t="str">
-        <v>Jessie J</v>
+        <v>Carlos Vives</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Jessie J - FEEL IT ON ME (Lyric Visualiser) (Official Lyric Video) - Jessie J</v>
+        <v>Carlos Vives - Te Dedico (Official Video) - Carlos Vives</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Marc Anthony - Make It With You (Visualizer)</v>
+        <v>Monsieur Periné, Jossman - MUCHO CON DEMASIAO' (Video Oficial)</v>
       </c>
       <c r="B4" t="str">
-        <v>2 days ago</v>
+        <v>4 hours ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=WHnz1jDrxw8</v>
+        <v>https://www.youtube.com/watch?v=mpmrrvhLzZ0</v>
       </c>
       <c r="D4" t="str">
         <v>2026-02-06</v>
@@ -527,13 +527,13 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>2 days ago</v>
+        <v>4 hours ago</v>
       </c>
       <c r="G4" t="str">
-        <v>4:24</v>
+        <v>2:25</v>
       </c>
       <c r="H4" t="str">
-        <v>Marc Anthony</v>
+        <v>Monsieur Periné</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Marc Anthony - Make It With You (Visualizer) - Marc Anthony</v>
+        <v>Monsieur Periné, Jossman - MUCHO CON DEMASIAO' (Video Oficial) - Monsieur Periné</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Clara Mae - Never Been Yours ft. Bob John Holt</v>
+        <v>The Happy Fits - Tenderly (Official Audio)</v>
       </c>
       <c r="B5" t="str">
-        <v>2 days ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=HtVuKBlBuPg</v>
+        <v>https://www.youtube.com/watch?v=10hExzTW4Hc</v>
       </c>
       <c r="D5" t="str">
         <v>2026-02-06</v>
@@ -565,13 +565,13 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>2 days ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="G5" t="str">
-        <v>2:33</v>
+        <v>4:09</v>
       </c>
       <c r="H5" t="str">
-        <v>Clara Mae</v>
+        <v>The Happy Fits</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Clara Mae - Never Been Yours ft. Bob John Holt - Clara Mae</v>
+        <v>The Happy Fits - Tenderly (Official Audio) - The Happy Fits</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Metric - Victim of Luck (Official Music Video)</v>
+        <v>chase (lyric vid) - Michael Aldag</v>
       </c>
       <c r="B6" t="str">
-        <v>2 days ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=shmhTOUd8mA</v>
+        <v>https://www.youtube.com/watch?v=QASMKs97wec</v>
       </c>
       <c r="D6" t="str">
         <v>2026-02-06</v>
@@ -603,13 +603,13 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>2 days ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="G6" t="str">
-        <v>3:25</v>
+        <v>2:45</v>
       </c>
       <c r="H6" t="str">
-        <v>metricmusic</v>
+        <v>Michael Aldag</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Metric - Victim of Luck (Official Music Video) - metricmusic</v>
+        <v>chase (lyric vid) - Michael Aldag - Michael Aldag</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Kesha - RED FLAG. (Red Carpet) OFFICIAL MUSIC VIDEO</v>
+        <v>Dermot Kennedy - Funeral (Live Acoustic Session)</v>
       </c>
       <c r="B7" t="str">
-        <v>2 days ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=pvrJ5RnPAEA</v>
+        <v>https://www.youtube.com/watch?v=RyR1xAw9edU</v>
       </c>
       <c r="D7" t="str">
         <v>2026-02-06</v>
@@ -641,13 +641,13 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>2 days ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="G7" t="str">
-        <v>3:41</v>
+        <v>4:07</v>
       </c>
       <c r="H7" t="str">
-        <v>kesha</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Kesha - RED FLAG. (Red Carpet) OFFICIAL MUSIC VIDEO - kesha</v>
+        <v>Dermot Kennedy - Funeral (Live Acoustic Session) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Studio)</v>
+        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Official Video)</v>
       </c>
       <c r="B8" t="str">
-        <v>3 days ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=mgsdQI-GVMM</v>
+        <v>https://www.youtube.com/watch?v=OYtHvS7n7ic</v>
       </c>
       <c r="D8" t="str">
         <v>2026-02-06</v>
@@ -679,13 +679,13 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>3 days ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G8" t="str">
-        <v>3:19</v>
+        <v>4:34</v>
       </c>
       <c r="H8" t="str">
-        <v>David Guetta and Tones And I</v>
+        <v>Marc Anthony</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Studio) - David Guetta and Tones And I</v>
+        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Official Video) - Marc Anthony</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Vera Blue - Hold (Live on Sydney Harbour)</v>
+        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Official Music Video)</v>
       </c>
       <c r="B9" t="str">
-        <v>3 days ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=SYEwk-EZJPU</v>
+        <v>https://www.youtube.com/watch?v=XKvzT2CTnLE</v>
       </c>
       <c r="D9" t="str">
         <v>2026-02-06</v>
@@ -717,13 +717,13 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>3 days ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G9" t="str">
-        <v>3:37</v>
+        <v>5:14</v>
       </c>
       <c r="H9" t="str">
-        <v>Vera Blue</v>
+        <v>FULL CIRCLE BOYS</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Vera Blue - Hold (Live on Sydney Harbour) - Vera Blue</v>
+        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Official Music Video) - FULL CIRCLE BOYS</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Bob Moses - Need You Tonight (INXS Cover) - Brooklyn Mirage 2023</v>
+        <v>Michael Bolton | Cupid (Official Visualizer)</v>
       </c>
       <c r="B10" t="str">
-        <v>3 days ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=CoCqPwDIBOA</v>
+        <v>https://www.youtube.com/watch?v=1XDIbfJ_OGw</v>
       </c>
       <c r="D10" t="str">
         <v>2026-02-06</v>
@@ -755,13 +755,13 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>3 days ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G10" t="str">
-        <v>3:08</v>
+        <v>3:11</v>
       </c>
       <c r="H10" t="str">
-        <v>Bob Moses</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Bob Moses - Need You Tonight (INXS Cover) - Brooklyn Mirage 2023 - Bob Moses</v>
+        <v>Michael Bolton | Cupid (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Marc Anthony - Un Mal Sueño (Visualizer)</v>
+        <v>Lachie Gill - Last Drive</v>
       </c>
       <c r="B11" t="str">
-        <v>3 days ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=18yZq5xtke4</v>
+        <v>https://www.youtube.com/watch?v=y79kD37Ffic</v>
       </c>
       <c r="D11" t="str">
         <v>2026-02-06</v>
@@ -793,13 +793,13 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>3 days ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G11" t="str">
-        <v>3:28</v>
+        <v>3:40</v>
       </c>
       <c r="H11" t="str">
-        <v>Marc Anthony</v>
+        <v>Lachie Gill</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Marc Anthony - Un Mal Sueño (Visualizer) - Marc Anthony</v>
+        <v>Lachie Gill - Last Drive - Lachie Gill</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Marc Anthony - Contra La Corriente (Visualizer)</v>
+        <v>Eli &amp; Fur - Strange (Official Visualiser)</v>
       </c>
       <c r="B12" t="str">
-        <v>3 days ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=IGLmJ71oHhQ</v>
+        <v>https://www.youtube.com/watch?v=KlgO3kKNc8o</v>
       </c>
       <c r="D12" t="str">
         <v>2026-02-06</v>
@@ -831,13 +831,13 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>3 days ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G12" t="str">
-        <v>5:05</v>
+        <v>3:45</v>
       </c>
       <c r="H12" t="str">
-        <v>Marc Anthony</v>
+        <v>Eli &amp; Fur</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Marc Anthony - Contra La Corriente (Visualizer) - Marc Anthony</v>
+        <v>Eli &amp; Fur - Strange (Official Visualiser) - Eli &amp; Fur</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Loreen - Feels Like Heaven</v>
+        <v>Freya Skye - why'd you have to call</v>
       </c>
       <c r="B13" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=BQc97moyQBg</v>
+        <v>https://www.youtube.com/watch?v=75o0FuwCdaA</v>
       </c>
       <c r="D13" t="str">
         <v>2026-02-06</v>
@@ -869,13 +869,13 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G13" t="str">
-        <v>3:14</v>
+        <v>4:19</v>
       </c>
       <c r="H13" t="str">
-        <v>Loreen</v>
+        <v>Freya Skye</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Loreen - Feels Like Heaven - Loreen</v>
+        <v>Freya Skye - why'd you have to call - Freya Skye</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Take That - Once You've Tasted Love (Live on Pebble Mill, 1992)</v>
+        <v>Jessie J - FEEL IT ON ME (Lyric Visualiser) (Official Lyric Video)</v>
       </c>
       <c r="B14" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=dOeoDOueESk</v>
+        <v>https://www.youtube.com/watch?v=DGmbe49F8aI</v>
       </c>
       <c r="D14" t="str">
         <v>2026-02-06</v>
@@ -907,13 +907,13 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G14" t="str">
-        <v>3:36</v>
+        <v>2:30</v>
       </c>
       <c r="H14" t="str">
-        <v>Take That</v>
+        <v>Jessie J</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Take That - Once You've Tasted Love (Live on Pebble Mill, 1992) - Take That</v>
+        <v>Jessie J - FEEL IT ON ME (Lyric Visualiser) (Official Lyric Video) - Jessie J</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Paul McCartney, Wings - Nineteen Hundred And Eighty Five (Visualiser)</v>
+        <v>Marc Anthony - Make It With You (Visualizer)</v>
       </c>
       <c r="B15" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=a4AIjUHuWpU</v>
+        <v>https://www.youtube.com/watch?v=WHnz1jDrxw8</v>
       </c>
       <c r="D15" t="str">
         <v>2026-02-06</v>
@@ -945,13 +945,13 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G15" t="str">
-        <v>5:31</v>
+        <v>4:24</v>
       </c>
       <c r="H15" t="str">
-        <v>PAUL McCARTNEY</v>
+        <v>Marc Anthony</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Paul McCartney, Wings - Nineteen Hundred And Eighty Five (Visualiser) - PAUL McCARTNEY</v>
+        <v>Marc Anthony - Make It With You (Visualizer) - Marc Anthony</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Nothing But Thieves - Sorry (Official Audio)</v>
+        <v>Clara Mae - Never Been Yours ft. Bob John Holt</v>
       </c>
       <c r="B16" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=D7QfVqo5YqY</v>
+        <v>https://www.youtube.com/watch?v=HtVuKBlBuPg</v>
       </c>
       <c r="D16" t="str">
         <v>2026-02-06</v>
@@ -983,13 +983,13 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G16" t="str">
-        <v>3:37</v>
+        <v>2:33</v>
       </c>
       <c r="H16" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Clara Mae</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Nothing But Thieves - Sorry (Official Audio) - Nothing But Thieves</v>
+        <v>Clara Mae - Never Been Yours ft. Bob John Holt - Clara Mae</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music</v>
+        <v>Metric - Victim of Luck (Official Music Video)</v>
       </c>
       <c r="B17" t="str">
-        <v>5 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=KdsHxyl4bE8</v>
+        <v>https://www.youtube.com/watch?v=shmhTOUd8mA</v>
       </c>
       <c r="D17" t="str">
         <v>2026-02-06</v>
@@ -1021,13 +1021,13 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>5 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>4:58</v>
+        <v>3:25</v>
       </c>
       <c r="H17" t="str">
-        <v>The Warning</v>
+        <v>metricmusic</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music - The Warning</v>
+        <v>Metric - Victim of Luck (Official Music Video) - metricmusic</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield, CA (2026)</v>
+        <v>Kesha - RED FLAG. (Red Carpet) OFFICIAL MUSIC VIDEO</v>
       </c>
       <c r="B18" t="str">
-        <v>5 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=Mwkl_Cz_SG8</v>
+        <v>https://www.youtube.com/watch?v=pvrJ5RnPAEA</v>
       </c>
       <c r="D18" t="str">
         <v>2026-02-06</v>
@@ -1059,13 +1059,13 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>5 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>5:08</v>
+        <v>3:41</v>
       </c>
       <c r="H18" t="str">
-        <v>The Offspring</v>
+        <v>kesha</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield, CA (2026) - The Offspring</v>
+        <v>Kesha - RED FLAG. (Red Carpet) OFFICIAL MUSIC VIDEO - kesha</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered)</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Studio)</v>
       </c>
       <c r="B19" t="str">
-        <v>5 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=I7a-pDZFE7U</v>
+        <v>https://www.youtube.com/watch?v=mgsdQI-GVMM</v>
       </c>
       <c r="D19" t="str">
         <v>2026-02-06</v>
@@ -1097,13 +1097,13 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>5 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>4:38</v>
+        <v>3:19</v>
       </c>
       <c r="H19" t="str">
-        <v>Roxette</v>
+        <v>David Guetta and Tones And I</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered) - Roxette</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Studio) - David Guetta and Tones And I</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Jessie Ware - I Could Get Used To This ( Live at Graham Norton)</v>
+        <v>Vera Blue - Hold (Live on Sydney Harbour)</v>
       </c>
       <c r="B20" t="str">
-        <v>5 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=kGeamxRf8Gw</v>
+        <v>https://www.youtube.com/watch?v=SYEwk-EZJPU</v>
       </c>
       <c r="D20" t="str">
         <v>2026-02-06</v>
@@ -1135,13 +1135,13 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>5 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>3:50</v>
+        <v>3:37</v>
       </c>
       <c r="H20" t="str">
-        <v>Jessie Ware</v>
+        <v>Vera Blue</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Jessie Ware - I Could Get Used To This ( Live at Graham Norton) - Jessie Ware</v>
+        <v>Vera Blue - Hold (Live on Sydney Harbour) - Vera Blue</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>JOSEPH - Water in the Room (Official Music Video)</v>
+        <v>Bob Moses - Need You Tonight (INXS Cover) - Brooklyn Mirage 2023</v>
       </c>
       <c r="B21" t="str">
-        <v>6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=tNmT47k6MjM</v>
+        <v>https://www.youtube.com/watch?v=CoCqPwDIBOA</v>
       </c>
       <c r="D21" t="str">
         <v>2026-02-06</v>
@@ -1173,13 +1173,13 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>3:10</v>
+        <v>3:08</v>
       </c>
       <c r="H21" t="str">
-        <v>Joseph</v>
+        <v>Bob Moses</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>JOSEPH - Water in the Room (Official Music Video) - Joseph</v>
+        <v>Bob Moses - Need You Tonight (INXS Cover) - Brooklyn Mirage 2023 - Bob Moses</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Dean Lewis - I Am Getting Well (Lyric Video)</v>
+        <v>Marc Anthony - Un Mal Sueño (Visualizer)</v>
       </c>
       <c r="B22" t="str">
-        <v>6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=6ecgOSOMWzc</v>
+        <v>https://www.youtube.com/watch?v=18yZq5xtke4</v>
       </c>
       <c r="D22" t="str">
         <v>2026-02-06</v>
@@ -1211,13 +1211,13 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>2:44</v>
+        <v>3:28</v>
       </c>
       <c r="H22" t="str">
-        <v>Dean Lewis</v>
+        <v>Marc Anthony</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Dean Lewis - I Am Getting Well (Lyric Video) - Dean Lewis</v>
+        <v>Marc Anthony - Un Mal Sueño (Visualizer) - Marc Anthony</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Take That - Take That and Party (Official HD Video)</v>
+        <v>Marc Anthony - Contra La Corriente (Visualizer)</v>
       </c>
       <c r="B23" t="str">
-        <v>6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=DAerJcerikU</v>
+        <v>https://www.youtube.com/watch?v=IGLmJ71oHhQ</v>
       </c>
       <c r="D23" t="str">
         <v>2026-02-06</v>
@@ -1249,13 +1249,13 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>2:57</v>
+        <v>5:05</v>
       </c>
       <c r="H23" t="str">
-        <v>Take That</v>
+        <v>Marc Anthony</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Take That - Take That and Party (Official HD Video) - Take That</v>
+        <v>Marc Anthony - Contra La Corriente (Visualizer) - Marc Anthony</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>The Cure - Boys Don't Cry (86 Mix) (Official Lyric Video)</v>
+        <v>Loreen - Feels Like Heaven</v>
       </c>
       <c r="B24" t="str">
-        <v>6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=isNztTjXQsQ</v>
+        <v>https://www.youtube.com/watch?v=BQc97moyQBg</v>
       </c>
       <c r="D24" t="str">
         <v>2026-02-06</v>
@@ -1287,13 +1287,13 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>2:39</v>
+        <v>3:14</v>
       </c>
       <c r="H24" t="str">
-        <v>The Cure</v>
+        <v>Loreen</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>The Cure - Boys Don't Cry (86 Mix) (Official Lyric Video) - The Cure</v>
+        <v>Loreen - Feels Like Heaven - Loreen</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>The Kiffness &amp; Matisyahu - ONE DAY (ft. Andel and Nalyn) [OFFICIAL VIDEO]</v>
+        <v>Take That - Once You've Tasted Love (Live on Pebble Mill, 1992)</v>
       </c>
       <c r="B25" t="str">
-        <v>6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=buS21tVq5r0</v>
+        <v>https://www.youtube.com/watch?v=dOeoDOueESk</v>
       </c>
       <c r="D25" t="str">
         <v>2026-02-06</v>
@@ -1325,13 +1325,13 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>3:07</v>
+        <v>3:36</v>
       </c>
       <c r="H25" t="str">
-        <v>The Kiffness and Matisyahu</v>
+        <v>Take That</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>The Kiffness &amp; Matisyahu - ONE DAY (ft. Andel and Nalyn) [OFFICIAL VIDEO] - The Kiffness and Matisyahu</v>
+        <v>Take That - Once You've Tasted Love (Live on Pebble Mill, 1992) - Take That</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Paris Paloma - Good Girl [Official Music Video]</v>
+        <v>Paul McCartney, Wings - Nineteen Hundred And Eighty Five (Visualiser)</v>
       </c>
       <c r="B26" t="str">
-        <v>6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=qhO6VMC-nx0</v>
+        <v>https://www.youtube.com/watch?v=a4AIjUHuWpU</v>
       </c>
       <c r="D26" t="str">
         <v>2026-02-06</v>
@@ -1363,13 +1363,13 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>4:47</v>
+        <v>5:31</v>
       </c>
       <c r="H26" t="str">
-        <v>Paris Paloma</v>
+        <v>PAUL McCARTNEY</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Paris Paloma - Good Girl [Official Music Video] - Paris Paloma</v>
+        <v>Paul McCartney, Wings - Nineteen Hundred And Eighty Five (Visualiser) - PAUL McCARTNEY</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Zara Larsson - Lush Life (Official UGC Compilation Video)</v>
+        <v>Nothing But Thieves - Sorry (Official Audio)</v>
       </c>
       <c r="B27" t="str">
-        <v>6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=FgAyfRnbbRs</v>
+        <v>https://www.youtube.com/watch?v=D7QfVqo5YqY</v>
       </c>
       <c r="D27" t="str">
         <v>2026-02-06</v>
@@ -1401,13 +1401,13 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>3:22</v>
+        <v>3:37</v>
       </c>
       <c r="H27" t="str">
-        <v>Zara Larsson</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Zara Larsson - Lush Life (Official UGC Compilation Video) - Zara Larsson</v>
+        <v>Nothing But Thieves - Sorry (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Only The Poets - Monumental</v>
+        <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music</v>
       </c>
       <c r="B28" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=nwXiAjjl6NE</v>
+        <v>https://www.youtube.com/watch?v=KdsHxyl4bE8</v>
       </c>
       <c r="D28" t="str">
         <v>2026-02-06</v>
@@ -1439,13 +1439,13 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>2:48</v>
+        <v>4:58</v>
       </c>
       <c r="H28" t="str">
-        <v>only the poets</v>
+        <v>The Warning</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Only The Poets - Monumental - only the poets</v>
+        <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music - The Warning</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Katelyn Tarver - So Am I (Official Music Video)</v>
+        <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield, CA (2026)</v>
       </c>
       <c r="B29" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=MjUiVPzMQHw</v>
+        <v>https://www.youtube.com/watch?v=Mwkl_Cz_SG8</v>
       </c>
       <c r="D29" t="str">
         <v>2026-02-06</v>
@@ -1477,13 +1477,13 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>2:52</v>
+        <v>5:08</v>
       </c>
       <c r="H29" t="str">
-        <v>Katelyn Tarver</v>
+        <v>The Offspring</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Katelyn Tarver - So Am I (Official Music Video) - Katelyn Tarver</v>
+        <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield, CA (2026) - The Offspring</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>David Guetta, TeddySwims, Tones And I - Gone Gone Gone (Unplugged) [Visualizer]</v>
+        <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered)</v>
       </c>
       <c r="B30" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=eWglDE7O5r8</v>
+        <v>https://www.youtube.com/watch?v=I7a-pDZFE7U</v>
       </c>
       <c r="D30" t="str">
         <v>2026-02-06</v>
@@ -1515,13 +1515,13 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>3:33</v>
+        <v>4:38</v>
       </c>
       <c r="H30" t="str">
-        <v>David Guetta</v>
+        <v>Roxette</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>David Guetta, TeddySwims, Tones And I - Gone Gone Gone (Unplugged) [Visualizer] - David Guetta</v>
+        <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered) - Roxette</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>SANTOS BRAVOS “KAWASAKI” Performance Video</v>
+        <v>Jessie Ware - I Could Get Used To This ( Live at Graham Norton)</v>
       </c>
       <c r="B31" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=Cmy8CsYIUL0</v>
+        <v>https://www.youtube.com/watch?v=kGeamxRf8Gw</v>
       </c>
       <c r="D31" t="str">
         <v>2026-02-06</v>
@@ -1553,13 +1553,13 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>2:41</v>
+        <v>3:50</v>
       </c>
       <c r="H31" t="str">
-        <v>HYBE LABELS and SANTOS BRAVOS</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>SANTOS BRAVOS “KAWASAKI” Performance Video - HYBE LABELS and SANTOS BRAVOS</v>
+        <v>Jessie Ware - I Could Get Used To This ( Live at Graham Norton) - Jessie Ware</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Ella Langley - Dandelion (Official Visualizer)</v>
+        <v>JOSEPH - Water in the Room (Official Music Video)</v>
       </c>
       <c r="B32" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=sf6eRmInk1s</v>
+        <v>https://www.youtube.com/watch?v=tNmT47k6MjM</v>
       </c>
       <c r="D32" t="str">
         <v>2026-02-06</v>
@@ -1594,10 +1594,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>4:01</v>
+        <v>3:10</v>
       </c>
       <c r="H32" t="str">
-        <v>Ella Langley</v>
+        <v>Joseph</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Ella Langley - Dandelion (Official Visualizer) - Ella Langley</v>
+        <v>JOSEPH - Water in the Room (Official Music Video) - Joseph</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Dogpark - Dandelion (Official Music Video)</v>
+        <v>Dean Lewis - I Am Getting Well (Lyric Video)</v>
       </c>
       <c r="B33" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=fv9prIYHHzk</v>
+        <v>https://www.youtube.com/watch?v=6ecgOSOMWzc</v>
       </c>
       <c r="D33" t="str">
         <v>2026-02-06</v>
@@ -1632,10 +1632,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>3:16</v>
+        <v>2:44</v>
       </c>
       <c r="H33" t="str">
-        <v>Dogpark</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Dogpark - Dandelion (Official Music Video) - Dogpark</v>
+        <v>Dean Lewis - I Am Getting Well (Lyric Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Lauren Spencer Smith - Natural Disaster (Visualizer)</v>
+        <v>Take That - Take That and Party (Official HD Video)</v>
       </c>
       <c r="B34" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=T9YvLA2cdZs</v>
+        <v>https://www.youtube.com/watch?v=DAerJcerikU</v>
       </c>
       <c r="D34" t="str">
         <v>2026-02-06</v>
@@ -1670,10 +1670,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>3:03</v>
+        <v>2:57</v>
       </c>
       <c r="H34" t="str">
-        <v>Lauren Spencer Smith</v>
+        <v>Take That</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Lauren Spencer Smith - Natural Disaster (Visualizer) - Lauren Spencer Smith</v>
+        <v>Take That - Take That and Party (Official HD Video) - Take That</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>ERNEST - Lorelei (Official Music Video)</v>
+        <v>The Cure - Boys Don't Cry (86 Mix) (Official Lyric Video)</v>
       </c>
       <c r="B35" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=dPWc_6IdDJk</v>
+        <v>https://www.youtube.com/watch?v=isNztTjXQsQ</v>
       </c>
       <c r="D35" t="str">
         <v>2026-02-06</v>
@@ -1708,10 +1708,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>2:41</v>
+        <v>2:39</v>
       </c>
       <c r="H35" t="str">
-        <v>ERNEST</v>
+        <v>The Cure</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>ERNEST - Lorelei (Official Music Video) - ERNEST</v>
+        <v>The Cure - Boys Don't Cry (86 Mix) (Official Lyric Video) - The Cure</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Labrinth - I Keep My Promises (Official Audio)</v>
+        <v>The Kiffness &amp; Matisyahu - ONE DAY (ft. Andel and Nalyn) [OFFICIAL VIDEO]</v>
       </c>
       <c r="B36" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=CV5rR9JZK-0</v>
+        <v>https://www.youtube.com/watch?v=buS21tVq5r0</v>
       </c>
       <c r="D36" t="str">
         <v>2026-02-06</v>
@@ -1746,10 +1746,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>3:05</v>
+        <v>3:07</v>
       </c>
       <c r="H36" t="str">
-        <v>Labrinth</v>
+        <v>The Kiffness and Matisyahu</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Labrinth - I Keep My Promises (Official Audio) - Labrinth</v>
+        <v>The Kiffness &amp; Matisyahu - ONE DAY (ft. Andel and Nalyn) [OFFICIAL VIDEO] - The Kiffness and Matisyahu</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Grace VanderWaal - Prettier (Official Lyric Video)</v>
+        <v>Paris Paloma - Good Girl [Official Music Video]</v>
       </c>
       <c r="B37" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=9HwTj3NZ16E</v>
+        <v>https://www.youtube.com/watch?v=qhO6VMC-nx0</v>
       </c>
       <c r="D37" t="str">
         <v>2026-02-06</v>
@@ -1784,10 +1784,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>2:46</v>
+        <v>4:47</v>
       </c>
       <c r="H37" t="str">
-        <v>Grace VanderWaal</v>
+        <v>Paris Paloma</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Grace VanderWaal - Prettier (Official Lyric Video) - Grace VanderWaal</v>
+        <v>Paris Paloma - Good Girl [Official Music Video] - Paris Paloma</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>VOILÀ - Frozen Lake (Official Lyric Video)</v>
+        <v>Zara Larsson - Lush Life (Official UGC Compilation Video)</v>
       </c>
       <c r="B38" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=Lmus-UbL1H0</v>
+        <v>https://www.youtube.com/watch?v=FgAyfRnbbRs</v>
       </c>
       <c r="D38" t="str">
         <v>2026-02-06</v>
@@ -1822,10 +1822,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>3:32</v>
+        <v>3:22</v>
       </c>
       <c r="H38" t="str">
-        <v>VOILÀ</v>
+        <v>Zara Larsson</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>VOILÀ - Frozen Lake (Official Lyric Video) - VOILÀ</v>
+        <v>Zara Larsson - Lush Life (Official UGC Compilation Video) - Zara Larsson</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Cannons - Starlight (Official Video)</v>
+        <v>Only The Poets - Monumental</v>
       </c>
       <c r="B39" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=bu6WSMDDPGY</v>
+        <v>https://www.youtube.com/watch?v=nwXiAjjl6NE</v>
       </c>
       <c r="D39" t="str">
         <v>2026-02-06</v>
@@ -1860,10 +1860,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>3:42</v>
+        <v>2:48</v>
       </c>
       <c r="H39" t="str">
-        <v>Cannons</v>
+        <v>only the poets</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Cannons - Starlight (Official Video) - Cannons</v>
+        <v>Only The Poets - Monumental - only the poets</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Kylie Morgan - Like My Own (Official Video)</v>
+        <v>Katelyn Tarver - So Am I (Official Music Video)</v>
       </c>
       <c r="B40" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=zcYeoGBglC0</v>
+        <v>https://www.youtube.com/watch?v=MjUiVPzMQHw</v>
       </c>
       <c r="D40" t="str">
         <v>2026-02-06</v>
@@ -1898,10 +1898,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>2:38</v>
+        <v>2:52</v>
       </c>
       <c r="H40" t="str">
-        <v>Kylie Morgan</v>
+        <v>Katelyn Tarver</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Kylie Morgan - Like My Own (Official Video) - Kylie Morgan</v>
+        <v>Katelyn Tarver - So Am I (Official Music Video) - Katelyn Tarver</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Lizzy McAlpine - House of the Rising Sun (Audio)</v>
+        <v>David Guetta, TeddySwims, Tones And I - Gone Gone Gone (Unplugged) [Visualizer]</v>
       </c>
       <c r="B41" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=3igYRj82EiU</v>
+        <v>https://www.youtube.com/watch?v=eWglDE7O5r8</v>
       </c>
       <c r="D41" t="str">
         <v>2026-02-06</v>
@@ -1936,10 +1936,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>3:10</v>
+        <v>3:33</v>
       </c>
       <c r="H41" t="str">
-        <v>Lizzy McAlpine</v>
+        <v>David Guetta</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Lizzy McAlpine - House of the Rising Sun (Audio) - Lizzy McAlpine</v>
+        <v>David Guetta, TeddySwims, Tones And I - Gone Gone Gone (Unplugged) [Visualizer] - David Guetta</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Willie Nelson - Heart Of America (From The Gray House Original Soundtrack)</v>
+        <v>SANTOS BRAVOS “KAWASAKI” Performance Video</v>
       </c>
       <c r="B42" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=0bhcO4Yphuo</v>
+        <v>https://www.youtube.com/watch?v=Cmy8CsYIUL0</v>
       </c>
       <c r="D42" t="str">
         <v>2026-02-06</v>
@@ -1974,10 +1974,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>3:57</v>
+        <v>2:41</v>
       </c>
       <c r="H42" t="str">
-        <v>Willie Nelson</v>
+        <v>HYBE LABELS and SANTOS BRAVOS</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Willie Nelson - Heart Of America (From The Gray House Original Soundtrack) - Willie Nelson</v>
+        <v>SANTOS BRAVOS “KAWASAKI” Performance Video - HYBE LABELS and SANTOS BRAVOS</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Jeremy Camp - No Survivors (Live) ft. Skillet</v>
+        <v>Ella Langley - Dandelion (Official Visualizer)</v>
       </c>
       <c r="B43" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=Jjz1wFe5dMo</v>
+        <v>https://www.youtube.com/watch?v=sf6eRmInk1s</v>
       </c>
       <c r="D43" t="str">
         <v>2026-02-06</v>
@@ -2012,10 +2012,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>2:19</v>
+        <v>4:01</v>
       </c>
       <c r="H43" t="str">
-        <v>JeremyCampMusic</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Jeremy Camp - No Survivors (Live) ft. Skillet - JeremyCampMusic</v>
+        <v>Ella Langley - Dandelion (Official Visualizer) - Ella Langley</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>India Martinez, Coro ArteSí de Olvidados - Niño Sin Miedo</v>
+        <v>Dogpark - Dandelion (Official Music Video)</v>
       </c>
       <c r="B44" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=Vug_FPbXe9E</v>
+        <v>https://www.youtube.com/watch?v=fv9prIYHHzk</v>
       </c>
       <c r="D44" t="str">
         <v>2026-02-06</v>
@@ -2047,13 +2047,13 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>4:04</v>
+        <v>3:16</v>
       </c>
       <c r="H44" t="str">
-        <v>India Martínez</v>
+        <v>Dogpark</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>India Martinez, Coro ArteSí de Olvidados - Niño Sin Miedo - India Martínez</v>
+        <v>Dogpark - Dandelion (Official Music Video) - Dogpark</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Chelsea Cutler - BAD (Official Lyric Video)</v>
+        <v>Lauren Spencer Smith - Natural Disaster (Visualizer)</v>
       </c>
       <c r="B45" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=ZIW2vA3Zs1U</v>
+        <v>https://www.youtube.com/watch?v=T9YvLA2cdZs</v>
       </c>
       <c r="D45" t="str">
         <v>2026-02-06</v>
@@ -2085,13 +2085,13 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>2:16</v>
+        <v>3:03</v>
       </c>
       <c r="H45" t="str">
-        <v>Chelsea Cutler</v>
+        <v>Lauren Spencer Smith</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Chelsea Cutler - BAD (Official Lyric Video) - Chelsea Cutler</v>
+        <v>Lauren Spencer Smith - Natural Disaster (Visualizer) - Lauren Spencer Smith</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>TINI - FUTTTURA LIVE - el cielo + fresa</v>
+        <v>ERNEST - Lorelei (Official Music Video)</v>
       </c>
       <c r="B46" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=q_rrgJZAdNg</v>
+        <v>https://www.youtube.com/watch?v=dPWc_6IdDJk</v>
       </c>
       <c r="D46" t="str">
         <v>2026-02-06</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>5:58</v>
+        <v>2:41</v>
       </c>
       <c r="H46" t="str">
-        <v>TINI</v>
+        <v>ERNEST</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>TINI - FUTTTURA LIVE - el cielo + fresa - TINI</v>
+        <v>ERNEST - Lorelei (Official Music Video) - ERNEST</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Charley - Serial Idealist (Official Video)</v>
+        <v>Labrinth - I Keep My Promises (Official Audio)</v>
       </c>
       <c r="B47" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=uVIuKbPJz0U</v>
+        <v>https://www.youtube.com/watch?v=CV5rR9JZK-0</v>
       </c>
       <c r="D47" t="str">
         <v>2026-02-06</v>
@@ -2161,13 +2161,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>3:26</v>
+        <v>3:05</v>
       </c>
       <c r="H47" t="str">
-        <v>Charley</v>
+        <v>Labrinth</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Charley - Serial Idealist (Official Video) - Charley</v>
+        <v>Labrinth - I Keep My Promises (Official Audio) - Labrinth</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Demi Lovato - Ghost (Live)</v>
+        <v>Grace VanderWaal - Prettier (Official Lyric Video)</v>
       </c>
       <c r="B48" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=E-ECwdRndVA</v>
+        <v>https://www.youtube.com/watch?v=9HwTj3NZ16E</v>
       </c>
       <c r="D48" t="str">
         <v>2026-02-06</v>
@@ -2199,13 +2199,13 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>4:05</v>
+        <v>2:46</v>
       </c>
       <c r="H48" t="str">
-        <v>Demi Lovato</v>
+        <v>Grace VanderWaal</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Demi Lovato - Ghost (Live) - Demi Lovato</v>
+        <v>Grace VanderWaal - Prettier (Official Lyric Video) - Grace VanderWaal</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Teddy Swims - Need You More (Live - Green Room Sessions)</v>
+        <v>VOILÀ - Frozen Lake (Official Lyric Video)</v>
       </c>
       <c r="B49" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=1ugf5aaY4pY</v>
+        <v>https://www.youtube.com/watch?v=Lmus-UbL1H0</v>
       </c>
       <c r="D49" t="str">
         <v>2026-02-06</v>
@@ -2237,13 +2237,13 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>3:16</v>
+        <v>3:32</v>
       </c>
       <c r="H49" t="str">
-        <v>Teddy Swims</v>
+        <v>VOILÀ</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Teddy Swims - Need You More (Live - Green Room Sessions) - Teddy Swims</v>
+        <v>VOILÀ - Frozen Lake (Official Lyric Video) - VOILÀ</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Beck - Love (Audio)</v>
+        <v>Cannons - Starlight (Official Video)</v>
       </c>
       <c r="B50" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=ByABj3Xof1I</v>
+        <v>https://www.youtube.com/watch?v=bu6WSMDDPGY</v>
       </c>
       <c r="D50" t="str">
         <v>2026-02-06</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>3:14</v>
+        <v>3:42</v>
       </c>
       <c r="H50" t="str">
-        <v>Beck</v>
+        <v>Cannons</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Beck - Love (Audio) - Beck</v>
+        <v>Cannons - Starlight (Official Video) - Cannons</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>The Offspring - Looking Out For #1 | Live in Spokane, WA (2026)</v>
+        <v>Kylie Morgan - Like My Own (Official Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=2HSbo51EFNg</v>
+        <v>https://www.youtube.com/watch?v=zcYeoGBglC0</v>
       </c>
       <c r="D51" t="str">
         <v>2026-02-06</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>2:57</v>
+        <v>2:38</v>
       </c>
       <c r="H51" t="str">
-        <v>The Offspring</v>
+        <v>Kylie Morgan</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>The Offspring - Looking Out For #1 | Live in Spokane, WA (2026) - The Offspring</v>
+        <v>Kylie Morgan - Like My Own (Official Video) - Kylie Morgan</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show</v>
+        <v>Lizzy McAlpine - House of the Rising Sun (Audio)</v>
       </c>
       <c r="B52" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=ylifHFJWJ_c</v>
+        <v>https://www.youtube.com/watch?v=3igYRj82EiU</v>
       </c>
       <c r="D52" t="str">
         <v>2026-02-06</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>4:10</v>
+        <v>3:10</v>
       </c>
       <c r="H52" t="str">
-        <v>Sophie Ellis-Bextor</v>
+        <v>Lizzy McAlpine</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show - Sophie Ellis-Bextor</v>
+        <v>Lizzy McAlpine - House of the Rising Sun (Audio) - Lizzy McAlpine</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Jason Derulo - Sexy For Me [Official Music Video]</v>
+        <v>Willie Nelson - Heart Of America (From The Gray House Original Soundtrack)</v>
       </c>
       <c r="B53" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=9ST-eBNL0NU</v>
+        <v>https://www.youtube.com/watch?v=0bhcO4Yphuo</v>
       </c>
       <c r="D53" t="str">
         <v>2026-02-06</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>2:10</v>
+        <v>3:57</v>
       </c>
       <c r="H53" t="str">
-        <v>Jason Derulo</v>
+        <v>Willie Nelson</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Jason Derulo - Sexy For Me [Official Music Video] - Jason Derulo</v>
+        <v>Willie Nelson - Heart Of America (From The Gray House Original Soundtrack) - Willie Nelson</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Lights - COME GET YOUR GIRL</v>
+        <v>Jeremy Camp - No Survivors (Live) ft. Skillet</v>
       </c>
       <c r="B54" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=EhzX2y5MpSM</v>
+        <v>https://www.youtube.com/watch?v=Jjz1wFe5dMo</v>
       </c>
       <c r="D54" t="str">
         <v>2026-02-06</v>
@@ -2427,13 +2427,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G54" t="str">
-        <v>3:52</v>
+        <v>2:19</v>
       </c>
       <c r="H54" t="str">
-        <v>lights</v>
+        <v>JeremyCampMusic</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Lights - COME GET YOUR GIRL - lights</v>
+        <v>Jeremy Camp - No Survivors (Live) ft. Skillet - JeremyCampMusic</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video)</v>
+        <v>India Martinez, Coro ArteSí de Olvidados - Niño Sin Miedo</v>
       </c>
       <c r="B55" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=yUAvfo8fpuU</v>
+        <v>https://www.youtube.com/watch?v=Vug_FPbXe9E</v>
       </c>
       <c r="D55" t="str">
         <v>2026-02-06</v>
@@ -2465,13 +2465,13 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G55" t="str">
-        <v>3:50</v>
+        <v>4:04</v>
       </c>
       <c r="H55" t="str">
-        <v>Telenova</v>
+        <v>India Martínez</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video) - Telenova</v>
+        <v>India Martinez, Coro ArteSí de Olvidados - Niño Sin Miedo - India Martínez</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>I Had To Explain "How Music Works" LIVE In Concert</v>
+        <v>Chelsea Cutler - BAD (Official Lyric Video)</v>
       </c>
       <c r="B56" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=KnsBdAM3HqY</v>
+        <v>https://www.youtube.com/watch?v=ZIW2vA3Zs1U</v>
       </c>
       <c r="D56" t="str">
         <v>2026-02-06</v>
@@ -2503,13 +2503,13 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G56" t="str">
-        <v>5:32</v>
+        <v>2:16</v>
       </c>
       <c r="H56" t="str">
-        <v>Marcin</v>
+        <v>Chelsea Cutler</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>I Had To Explain "How Music Works" LIVE In Concert - Marcin</v>
+        <v>Chelsea Cutler - BAD (Official Lyric Video) - Chelsea Cutler</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>We Three - Drunk Driving (Official Music Video)</v>
+        <v>TINI - FUTTTURA LIVE - el cielo + fresa</v>
       </c>
       <c r="B57" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=BTqRGxSX6AQ</v>
+        <v>https://www.youtube.com/watch?v=q_rrgJZAdNg</v>
       </c>
       <c r="D57" t="str">
         <v>2026-02-06</v>
@@ -2541,13 +2541,13 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G57" t="str">
-        <v>4:27</v>
+        <v>5:58</v>
       </c>
       <c r="H57" t="str">
-        <v>We Three</v>
+        <v>TINI</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>We Three - Drunk Driving (Official Music Video) - We Three</v>
+        <v>TINI - FUTTTURA LIVE - el cielo + fresa - TINI</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Timebelle - Top of the World (Mood Video)</v>
+        <v>Charley - Serial Idealist (Official Video)</v>
       </c>
       <c r="B58" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=r9KyYK_E34s</v>
+        <v>https://www.youtube.com/watch?v=uVIuKbPJz0U</v>
       </c>
       <c r="D58" t="str">
         <v>2026-02-06</v>
@@ -2579,13 +2579,13 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G58" t="str">
-        <v>3:01</v>
+        <v>3:26</v>
       </c>
       <c r="H58" t="str">
-        <v>Timebelle Official</v>
+        <v>Charley</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Timebelle - Top of the World (Mood Video) - Timebelle Official</v>
+        <v>Charley - Serial Idealist (Official Video) - Charley</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop)</v>
+        <v>Demi Lovato - Ghost (Live)</v>
       </c>
       <c r="B59" t="str">
-        <v>10 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=57a_OheOlDw</v>
+        <v>https://www.youtube.com/watch?v=E-ECwdRndVA</v>
       </c>
       <c r="D59" t="str">
         <v>2026-02-06</v>
@@ -2617,13 +2617,13 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>10 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G59" t="str">
-        <v>3:20</v>
+        <v>4:05</v>
       </c>
       <c r="H59" t="str">
-        <v>David Guetta and Tones And I</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop) - David Guetta and Tones And I</v>
+        <v>Demi Lovato - Ghost (Live) - Demi Lovato</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Clinton Kane - this is my last love song to you (Official Lyric Video)</v>
+        <v>Teddy Swims - Need You More (Live - Green Room Sessions)</v>
       </c>
       <c r="B60" t="str">
-        <v>12 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=-5Aa8NTiRqE</v>
+        <v>https://www.youtube.com/watch?v=1ugf5aaY4pY</v>
       </c>
       <c r="D60" t="str">
         <v>2026-02-06</v>
@@ -2655,13 +2655,13 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>12 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G60" t="str">
-        <v>3:34</v>
+        <v>3:16</v>
       </c>
       <c r="H60" t="str">
-        <v>Clinton Kane</v>
+        <v>Teddy Swims</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Clinton Kane - this is my last love song to you (Official Lyric Video) - Clinton Kane</v>
+        <v>Teddy Swims - Need You More (Live - Green Room Sessions) - Teddy Swims</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>SIENNA SPIRO - Die On This Hill (Official Music Video)</v>
+        <v>Beck - Love (Audio)</v>
       </c>
       <c r="B61" t="str">
-        <v>13 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=5RNy_1odv20</v>
+        <v>https://www.youtube.com/watch?v=ByABj3Xof1I</v>
       </c>
       <c r="D61" t="str">
         <v>2026-02-06</v>
@@ -2693,13 +2693,13 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>13 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G61" t="str">
-        <v>4:01</v>
+        <v>3:14</v>
       </c>
       <c r="H61" t="str">
-        <v>Lyrical Lemonade and SIENNA SPIRO</v>
+        <v>Beck</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>SIENNA SPIRO - Die On This Hill (Official Music Video) - Lyrical Lemonade and SIENNA SPIRO</v>
+        <v>Beck - Love (Audio) - Beck</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Amazon Music presents: Sienna Spiro - You Stole The Show</v>
+        <v>The Offspring - Looking Out For #1 | Live in Spokane, WA (2026)</v>
       </c>
       <c r="B62" t="str">
-        <v>13 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=stYIRyCLN4Y</v>
+        <v>https://www.youtube.com/watch?v=2HSbo51EFNg</v>
       </c>
       <c r="D62" t="str">
         <v>2026-02-06</v>
@@ -2731,13 +2731,13 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>13 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G62" t="str">
-        <v>3:24</v>
+        <v>2:57</v>
       </c>
       <c r="H62" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>The Offspring</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Amazon Music presents: Sienna Spiro - You Stole The Show - SIENNA SPIRO</v>
+        <v>The Offspring - Looking Out For #1 | Live in Spokane, WA (2026) - The Offspring</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Harry Styles - Aperture (Official Video)</v>
+        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show</v>
       </c>
       <c r="B63" t="str">
-        <v>13 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=7sxVHYZ_PnA</v>
+        <v>https://www.youtube.com/watch?v=ylifHFJWJ_c</v>
       </c>
       <c r="D63" t="str">
         <v>2026-02-06</v>
@@ -2769,13 +2769,13 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>13 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G63" t="str">
-        <v>5:52</v>
+        <v>4:10</v>
       </c>
       <c r="H63" t="str">
-        <v>Harry Styles</v>
+        <v>Sophie Ellis-Bextor</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Harry Styles - Aperture (Official Video) - Harry Styles</v>
+        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show - Sophie Ellis-Bextor</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Neal Francis - Back It Up (Live At The Salt Shed)</v>
+        <v>Jason Derulo - Sexy For Me [Official Music Video]</v>
       </c>
       <c r="B64" t="str">
-        <v>13 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=46iZEdsxjC0</v>
+        <v>https://www.youtube.com/watch?v=9ST-eBNL0NU</v>
       </c>
       <c r="D64" t="str">
         <v>2026-02-06</v>
@@ -2807,13 +2807,13 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>13 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G64" t="str">
-        <v>5:01</v>
+        <v>2:10</v>
       </c>
       <c r="H64" t="str">
-        <v>Neal Francis</v>
+        <v>Jason Derulo</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Neal Francis - Back It Up (Live At The Salt Shed) - Neal Francis</v>
+        <v>Jason Derulo - Sexy For Me [Official Music Video] - Jason Derulo</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
+        <v>Lights - COME GET YOUR GIRL</v>
       </c>
       <c r="B65" t="str">
-        <v>13 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=K2nG1Uukz7E</v>
+        <v>https://www.youtube.com/watch?v=EhzX2y5MpSM</v>
       </c>
       <c r="D65" t="str">
         <v>2026-02-06</v>
@@ -2845,13 +2845,13 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>13 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G65" t="str">
-        <v>4:12</v>
+        <v>3:52</v>
       </c>
       <c r="H65" t="str">
-        <v>OfficiallyExtreme</v>
+        <v>lights</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
+        <v>Lights - COME GET YOUR GIRL - lights</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Holly Humberstone - To Love Somebody (Official Video)</v>
+        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video)</v>
       </c>
       <c r="B66" t="str">
-        <v>13 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
+        <v>https://www.youtube.com/watch?v=yUAvfo8fpuU</v>
       </c>
       <c r="D66" t="str">
         <v>2026-02-06</v>
@@ -2883,13 +2883,13 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>13 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G66" t="str">
-        <v>3:59</v>
+        <v>3:50</v>
       </c>
       <c r="H66" t="str">
-        <v>Holly Humberstone</v>
+        <v>Telenova</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Holly Humberstone - To Love Somebody (Official Video) - Holly Humberstone</v>
+        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video) - Telenova</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
+        <v>I Had To Explain "How Music Works" LIVE In Concert</v>
       </c>
       <c r="B67" t="str">
-        <v>13 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
+        <v>https://www.youtube.com/watch?v=KnsBdAM3HqY</v>
       </c>
       <c r="D67" t="str">
         <v>2026-02-06</v>
@@ -2921,13 +2921,13 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>13 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G67" t="str">
-        <v>2:56</v>
+        <v>5:32</v>
       </c>
       <c r="H67" t="str">
-        <v>Cliff Richard</v>
+        <v>Marcin</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018) - Cliff Richard</v>
+        <v>I Had To Explain "How Music Works" LIVE In Concert - Marcin</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
+        <v>We Three - Drunk Driving (Official Music Video)</v>
       </c>
       <c r="B68" t="str">
-        <v>13 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
+        <v>https://www.youtube.com/watch?v=BTqRGxSX6AQ</v>
       </c>
       <c r="D68" t="str">
         <v>2026-02-06</v>
@@ -2959,13 +2959,13 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>13 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G68" t="str">
-        <v>3:46</v>
+        <v>4:27</v>
       </c>
       <c r="H68" t="str">
-        <v>Jessie Ware</v>
+        <v>We Three</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Official Video) - Jessie Ware</v>
+        <v>We Three - Drunk Driving (Official Music Video) - We Three</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Bella White - Dream Song (Official Audio)</v>
+        <v>Timebelle - Top of the World (Mood Video)</v>
       </c>
       <c r="B69" t="str">
-        <v>13 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
+        <v>https://www.youtube.com/watch?v=r9KyYK_E34s</v>
       </c>
       <c r="D69" t="str">
         <v>2026-02-06</v>
@@ -2997,13 +2997,13 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>13 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G69" t="str">
-        <v>4:37</v>
+        <v>3:01</v>
       </c>
       <c r="H69" t="str">
-        <v>Bella White</v>
+        <v>Timebelle Official</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Bella White - Dream Song (Official Audio) - Bella White</v>
+        <v>Timebelle - Top of the World (Mood Video) - Timebelle Official</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Ryan Wright - Film School Kids (Official Video)</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop)</v>
       </c>
       <c r="B70" t="str">
-        <v>13 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=pnAz9RwGSek</v>
+        <v>https://www.youtube.com/watch?v=57a_OheOlDw</v>
       </c>
       <c r="D70" t="str">
         <v>2026-02-06</v>
@@ -3035,13 +3035,13 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>13 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G70" t="str">
-        <v>4:06</v>
+        <v>3:20</v>
       </c>
       <c r="H70" t="str">
-        <v>Ryan Wright</v>
+        <v>David Guetta and Tones And I</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Ryan Wright - Film School Kids (Official Video) - Ryan Wright</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop) - David Guetta and Tones And I</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer)</v>
+        <v>Clinton Kane - this is my last love song to you (Official Lyric Video)</v>
       </c>
       <c r="B71" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=u7aPv2saz_I</v>
+        <v>https://www.youtube.com/watch?v=-5Aa8NTiRqE</v>
       </c>
       <c r="D71" t="str">
         <v>2026-02-06</v>
@@ -3076,10 +3076,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G71" t="str">
-        <v>3:54</v>
+        <v>3:34</v>
       </c>
       <c r="H71" t="str">
-        <v>Dove Cameron</v>
+        <v>Clinton Kane</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer) - Dove Cameron</v>
+        <v>Clinton Kane - this is my last love song to you (Official Lyric Video) - Clinton Kane</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video)</v>
+        <v>SIENNA SPIRO - Die On This Hill (Official Music Video)</v>
       </c>
       <c r="B72" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=WGb8KVdqs6k</v>
+        <v>https://www.youtube.com/watch?v=5RNy_1odv20</v>
       </c>
       <c r="D72" t="str">
         <v>2026-02-06</v>
@@ -3114,10 +3114,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G72" t="str">
-        <v>4:10</v>
+        <v>4:01</v>
       </c>
       <c r="H72" t="str">
-        <v>Parker McCollum</v>
+        <v>Lyrical Lemonade and SIENNA SPIRO</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video) - Parker McCollum</v>
+        <v>SIENNA SPIRO - Die On This Hill (Official Music Video) - Lyrical Lemonade and SIENNA SPIRO</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video)</v>
+        <v>Amazon Music presents: Sienna Spiro - You Stole The Show</v>
       </c>
       <c r="B73" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=X1ZeY4Y3l1M</v>
+        <v>https://www.youtube.com/watch?v=stYIRyCLN4Y</v>
       </c>
       <c r="D73" t="str">
         <v>2026-02-06</v>
@@ -3152,10 +3152,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G73" t="str">
-        <v>3:26</v>
+        <v>3:24</v>
       </c>
       <c r="H73" t="str">
-        <v>Matt Hansen</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video) - Matt Hansen</v>
+        <v>Amazon Music presents: Sienna Spiro - You Stole The Show - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Louis Tomlinson - Imposter (Official Video)</v>
+        <v>Harry Styles - Aperture (Official Video)</v>
       </c>
       <c r="B74" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=rzuD5szQhso</v>
+        <v>https://www.youtube.com/watch?v=7sxVHYZ_PnA</v>
       </c>
       <c r="D74" t="str">
         <v>2026-02-06</v>
@@ -3187,13 +3187,13 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G74" t="str">
-        <v>2:56</v>
+        <v>5:52</v>
       </c>
       <c r="H74" t="str">
-        <v>Louis Tomlinson</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Louis Tomlinson - Imposter (Official Video) - Louis Tomlinson</v>
+        <v>Harry Styles - Aperture (Official Video) - Harry Styles</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Mitchell Tenpenny - You Phase (Official Music Video)</v>
+        <v>Neal Francis - Back It Up (Live At The Salt Shed)</v>
       </c>
       <c r="B75" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=UPuK6wV5Zco</v>
+        <v>https://www.youtube.com/watch?v=46iZEdsxjC0</v>
       </c>
       <c r="D75" t="str">
         <v>2026-02-06</v>
@@ -3228,10 +3228,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G75" t="str">
-        <v>2:56</v>
+        <v>5:01</v>
       </c>
       <c r="H75" t="str">
-        <v>Mitchell Tenpenny</v>
+        <v>Neal Francis</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Mitchell Tenpenny - You Phase (Official Music Video) - Mitchell Tenpenny</v>
+        <v>Neal Francis - Back It Up (Live At The Salt Shed) - Neal Francis</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Tauren Wells - Breathe On It (Official Lyric Video)</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
       </c>
       <c r="B76" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=9hW9sNMn2A0</v>
+        <v>https://www.youtube.com/watch?v=K2nG1Uukz7E</v>
       </c>
       <c r="D76" t="str">
         <v>2026-02-06</v>
@@ -3266,10 +3266,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G76" t="str">
-        <v>4:01</v>
+        <v>4:12</v>
       </c>
       <c r="H76" t="str">
-        <v>Tauren Wells</v>
+        <v>OfficiallyExtreme</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Tauren Wells - Breathe On It (Official Lyric Video) - Tauren Wells</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Maiah Manser - Feeling it All (Official Music Video)</v>
+        <v>Holly Humberstone - To Love Somebody (Official Video)</v>
       </c>
       <c r="B77" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=JMYvXleIwfU</v>
+        <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
       </c>
       <c r="D77" t="str">
         <v>2026-02-06</v>
@@ -3304,10 +3304,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G77" t="str">
-        <v>3:05</v>
+        <v>3:59</v>
       </c>
       <c r="H77" t="str">
-        <v>Maiah Manser</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Maiah Manser - Feeling it All (Official Music Video) - Maiah Manser</v>
+        <v>Holly Humberstone - To Love Somebody (Official Video) - Holly Humberstone</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Taylor Austin Dye - Man For That (Official Music Video)</v>
+        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
       </c>
       <c r="B78" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=vOzX-o11seI</v>
+        <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
       </c>
       <c r="D78" t="str">
         <v>2026-02-06</v>
@@ -3342,10 +3342,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G78" t="str">
-        <v>2:27</v>
+        <v>2:56</v>
       </c>
       <c r="H78" t="str">
-        <v>Taylor Austin Dye</v>
+        <v>Cliff Richard</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Taylor Austin Dye - Man For That (Official Music Video) - Taylor Austin Dye</v>
+        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018) - Cliff Richard</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Chelsea Cutler - BAD (Official Video)</v>
+        <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
       </c>
       <c r="B79" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=86k4E6ydHVU</v>
+        <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
       </c>
       <c r="D79" t="str">
         <v>2026-02-06</v>
@@ -3380,10 +3380,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G79" t="str">
-        <v>2:34</v>
+        <v>3:46</v>
       </c>
       <c r="H79" t="str">
-        <v>Chelsea Cutler</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Chelsea Cutler - BAD (Official Video) - Chelsea Cutler</v>
+        <v>Jessie Ware - I Could Get Used To This (Official Video) - Jessie Ware</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video)</v>
+        <v>Bella White - Dream Song (Official Audio)</v>
       </c>
       <c r="B80" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=-UWIFAiOOPE</v>
+        <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
       </c>
       <c r="D80" t="str">
         <v>2026-02-06</v>
@@ -3418,10 +3418,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G80" t="str">
-        <v>3:13</v>
+        <v>4:37</v>
       </c>
       <c r="H80" t="str">
-        <v>Ashley Kutcher</v>
+        <v>Bella White</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video) - Ashley Kutcher</v>
+        <v>Bella White - Dream Song (Official Audio) - Bella White</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Louis Tomlinson - Dark To Light (Visualiser)</v>
+        <v>Ryan Wright - Film School Kids (Official Video)</v>
       </c>
       <c r="B81" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=02QyA29poAM</v>
+        <v>https://www.youtube.com/watch?v=pnAz9RwGSek</v>
       </c>
       <c r="D81" t="str">
         <v>2026-02-06</v>
@@ -3456,10 +3456,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G81" t="str">
-        <v>3:13</v>
+        <v>4:06</v>
       </c>
       <c r="H81" t="str">
-        <v>Louis Tomlinson</v>
+        <v>Ryan Wright</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Louis Tomlinson - Dark To Light (Visualiser) - Louis Tomlinson</v>
+        <v>Ryan Wright - Film School Kids (Official Video) - Ryan Wright</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>CAIN - So Long Sad Songs (Lyric Video)</v>
+        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer)</v>
       </c>
       <c r="B82" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=feOv8nufa_I</v>
+        <v>https://www.youtube.com/watch?v=u7aPv2saz_I</v>
       </c>
       <c r="D82" t="str">
         <v>2026-02-06</v>
@@ -3494,10 +3494,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G82" t="str">
-        <v>3:08</v>
+        <v>3:54</v>
       </c>
       <c r="H82" t="str">
-        <v>CAIN</v>
+        <v>Dove Cameron</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>CAIN - So Long Sad Songs (Lyric Video) - CAIN</v>
+        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer) - Dove Cameron</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Harry Styles - Aperture (Official Audio)</v>
+        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video)</v>
       </c>
       <c r="B83" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=rA_eCxPay7E</v>
+        <v>https://www.youtube.com/watch?v=WGb8KVdqs6k</v>
       </c>
       <c r="D83" t="str">
         <v>2026-02-06</v>
@@ -3529,13 +3529,13 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G83" t="str">
-        <v>5:14</v>
+        <v>4:10</v>
       </c>
       <c r="H83" t="str">
-        <v>Harry Styles</v>
+        <v>Parker McCollum</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Harry Styles - Aperture (Official Audio) - Harry Styles</v>
+        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video) - Parker McCollum</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Lana Lubany - BAD IDEA (Official Video)</v>
+        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video)</v>
       </c>
       <c r="B84" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
+        <v>https://www.youtube.com/watch?v=X1ZeY4Y3l1M</v>
       </c>
       <c r="D84" t="str">
         <v>2026-02-06</v>
@@ -3567,13 +3567,13 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G84" t="str">
-        <v>2:59</v>
+        <v>3:26</v>
       </c>
       <c r="H84" t="str">
-        <v>Lana Lubany</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Lana Lubany - BAD IDEA (Official Video) - Lana Lubany</v>
+        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video) - Matt Hansen</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Def Leppard - Rejoice (Lyric Video)</v>
+        <v>Louis Tomlinson - Imposter (Official Video)</v>
       </c>
       <c r="B85" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=zy2TLLeNgp0</v>
+        <v>https://www.youtube.com/watch?v=rzuD5szQhso</v>
       </c>
       <c r="D85" t="str">
         <v>2026-02-06</v>
@@ -3608,10 +3608,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G85" t="str">
-        <v>4:21</v>
+        <v>2:56</v>
       </c>
       <c r="H85" t="str">
-        <v>DEF LEPPARD</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Def Leppard - Rejoice (Lyric Video) - DEF LEPPARD</v>
+        <v>Louis Tomlinson - Imposter (Official Video) - Louis Tomlinson</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Dermot Kennedy - Funeral (Official Music Video)</v>
+        <v>Mitchell Tenpenny - You Phase (Official Music Video)</v>
       </c>
       <c r="B86" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=JzOUJZPky6o</v>
+        <v>https://www.youtube.com/watch?v=UPuK6wV5Zco</v>
       </c>
       <c r="D86" t="str">
         <v>2026-02-06</v>
@@ -3643,13 +3643,13 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G86" t="str">
-        <v>4:09</v>
+        <v>2:56</v>
       </c>
       <c r="H86" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Mitchell Tenpenny</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Dermot Kennedy - Funeral (Official Music Video) - Dermot Kennedy</v>
+        <v>Mitchell Tenpenny - You Phase (Official Music Video) - Mitchell Tenpenny</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video)</v>
+        <v>Tauren Wells - Breathe On It (Official Lyric Video)</v>
       </c>
       <c r="B87" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=kfF0bVZMCw0</v>
+        <v>https://www.youtube.com/watch?v=9hW9sNMn2A0</v>
       </c>
       <c r="D87" t="str">
         <v>2026-02-06</v>
@@ -3681,13 +3681,13 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G87" t="str">
-        <v>2:34</v>
+        <v>4:01</v>
       </c>
       <c r="H87" t="str">
-        <v>Lauren Sanderson</v>
+        <v>Tauren Wells</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video) - Lauren Sanderson</v>
+        <v>Tauren Wells - Breathe On It (Official Lyric Video) - Tauren Wells</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show]</v>
+        <v>Maiah Manser - Feeling it All (Official Music Video)</v>
       </c>
       <c r="B88" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=dLzpNstMHZY</v>
+        <v>https://www.youtube.com/watch?v=JMYvXleIwfU</v>
       </c>
       <c r="D88" t="str">
         <v>2026-02-06</v>
@@ -3719,13 +3719,13 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G88" t="str">
-        <v>3:10</v>
+        <v>3:05</v>
       </c>
       <c r="H88" t="str">
-        <v>Olivia Dean</v>
+        <v>Maiah Manser</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show] - Olivia Dean</v>
+        <v>Maiah Manser - Feeling it All (Official Music Video) - Maiah Manser</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel)</v>
+        <v>Taylor Austin Dye - Man For That (Official Music Video)</v>
       </c>
       <c r="B89" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=fo_j8Fqag8I</v>
+        <v>https://www.youtube.com/watch?v=vOzX-o11seI</v>
       </c>
       <c r="D89" t="str">
         <v>2026-02-06</v>
@@ -3757,13 +3757,13 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G89" t="str">
-        <v>3:21</v>
+        <v>2:27</v>
       </c>
       <c r="H89" t="str">
-        <v>David Guetta and Tones And I</v>
+        <v>Taylor Austin Dye</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel) - David Guetta and Tones And I</v>
+        <v>Taylor Austin Dye - Man For That (Official Music Video) - Taylor Austin Dye</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>The Avett Brothers - Matrimony (Official Video)</v>
+        <v>Chelsea Cutler - BAD (Official Video)</v>
       </c>
       <c r="B90" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=7sD9-MtV9CY</v>
+        <v>https://www.youtube.com/watch?v=86k4E6ydHVU</v>
       </c>
       <c r="D90" t="str">
         <v>2026-02-06</v>
@@ -3795,13 +3795,13 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G90" t="str">
-        <v>3:06</v>
+        <v>2:34</v>
       </c>
       <c r="H90" t="str">
-        <v>The Avett Brothers</v>
+        <v>Chelsea Cutler</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>The Avett Brothers - Matrimony (Official Video) - The Avett Brothers</v>
+        <v>Chelsea Cutler - BAD (Official Video) - Chelsea Cutler</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Jordana Bryant - Love Like That (Official Video)</v>
+        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video)</v>
       </c>
       <c r="B91" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=3ATlH-Rtzmk</v>
+        <v>https://www.youtube.com/watch?v=-UWIFAiOOPE</v>
       </c>
       <c r="D91" t="str">
         <v>2026-02-06</v>
@@ -3833,13 +3833,13 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G91" t="str">
-        <v>3:21</v>
+        <v>3:13</v>
       </c>
       <c r="H91" t="str">
-        <v>Jordana Bryant</v>
+        <v>Ashley Kutcher</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Jordana Bryant - Love Like That (Official Video) - Jordana Bryant</v>
+        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video) - Ashley Kutcher</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards</v>
+        <v>Louis Tomlinson - Dark To Light (Visualiser)</v>
       </c>
       <c r="B92" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=kIRmKmEb2g0</v>
+        <v>https://www.youtube.com/watch?v=02QyA29poAM</v>
       </c>
       <c r="D92" t="str">
         <v>2026-02-06</v>
@@ -3871,13 +3871,13 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G92" t="str">
-        <v>7:21</v>
+        <v>3:13</v>
       </c>
       <c r="H92" t="str">
-        <v>Katy Perry</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards - Katy Perry</v>
+        <v>Louis Tomlinson - Dark To Light (Visualiser) - Louis Tomlinson</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session)</v>
+        <v>CAIN - So Long Sad Songs (Lyric Video)</v>
       </c>
       <c r="B93" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=oJ-l2ptQwbQ</v>
+        <v>https://www.youtube.com/watch?v=feOv8nufa_I</v>
       </c>
       <c r="D93" t="str">
         <v>2026-02-06</v>
@@ -3909,13 +3909,13 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G93" t="str">
-        <v>3:17</v>
+        <v>3:08</v>
       </c>
       <c r="H93" t="str">
-        <v>Lauren Watkins</v>
+        <v>CAIN</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session) - Lauren Watkins</v>
+        <v>CAIN - So Long Sad Songs (Lyric Video) - CAIN</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Just A Mess (Live acoustic studio session)</v>
+        <v>Harry Styles - Aperture (Official Audio)</v>
       </c>
       <c r="B94" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=ShW-I63KD8w</v>
+        <v>https://www.youtube.com/watch?v=rA_eCxPay7E</v>
       </c>
       <c r="D94" t="str">
         <v>2026-02-06</v>
@@ -3950,10 +3950,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G94" t="str">
-        <v>3:45</v>
+        <v>5:14</v>
       </c>
       <c r="H94" t="str">
-        <v>Tones And I</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Just A Mess (Live acoustic studio session) - Tones And I</v>
+        <v>Harry Styles - Aperture (Official Audio) - Harry Styles</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Ashleigh Dallas - Sail Away (Official Audio)</v>
+        <v>Lana Lubany - BAD IDEA (Official Video)</v>
       </c>
       <c r="B95" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=66PDbaI-BVA</v>
+        <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
       </c>
       <c r="D95" t="str">
         <v>2026-02-06</v>
@@ -3988,10 +3988,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G95" t="str">
-        <v>3:57</v>
+        <v>2:59</v>
       </c>
       <c r="H95" t="str">
-        <v>Ashleigh Dallas</v>
+        <v>Lana Lubany</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Ashleigh Dallas - Sail Away (Official Audio) - Ashleigh Dallas</v>
+        <v>Lana Lubany - BAD IDEA (Official Video) - Lana Lubany</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Performance Video)</v>
+        <v>Def Leppard - Rejoice (Lyric Video)</v>
       </c>
       <c r="B96" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=4tmW_JSXHII</v>
+        <v>https://www.youtube.com/watch?v=zy2TLLeNgp0</v>
       </c>
       <c r="D96" t="str">
         <v>2026-02-06</v>
@@ -4026,10 +4026,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G96" t="str">
-        <v>3:03</v>
+        <v>4:21</v>
       </c>
       <c r="H96" t="str">
-        <v>Charlie Puth</v>
+        <v>DEF LEPPARD</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Performance Video) - Charlie Puth</v>
+        <v>Def Leppard - Rejoice (Lyric Video) - DEF LEPPARD</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Chappell Roan - The Subway (Live from Kansas City)</v>
+        <v>Dermot Kennedy - Funeral (Official Music Video)</v>
       </c>
       <c r="B97" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=6kZVtF8iaWw</v>
+        <v>https://www.youtube.com/watch?v=JzOUJZPky6o</v>
       </c>
       <c r="D97" t="str">
         <v>2026-02-06</v>
@@ -4064,10 +4064,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G97" t="str">
-        <v>4:27</v>
+        <v>4:09</v>
       </c>
       <c r="H97" t="str">
-        <v>Chappell Roan</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Chappell Roan - The Subway (Live from Kansas City) - Chappell Roan</v>
+        <v>Dermot Kennedy - Funeral (Official Music Video) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar)</v>
+        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video)</v>
       </c>
       <c r="B98" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=guUvgEKkk1U</v>
+        <v>https://www.youtube.com/watch?v=kfF0bVZMCw0</v>
       </c>
       <c r="D98" t="str">
         <v>2026-02-06</v>
@@ -4102,10 +4102,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G98" t="str">
-        <v>4:34</v>
+        <v>2:34</v>
       </c>
       <c r="H98" t="str">
-        <v>Armik</v>
+        <v>Lauren Sanderson</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar) - Armik</v>
+        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video) - Lauren Sanderson</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>LØLØ - 007 (Official Music Video)</v>
+        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show]</v>
       </c>
       <c r="B99" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=4okJouEbZ_s</v>
+        <v>https://www.youtube.com/watch?v=dLzpNstMHZY</v>
       </c>
       <c r="D99" t="str">
         <v>2026-02-06</v>
@@ -4140,10 +4140,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G99" t="str">
-        <v>2:54</v>
+        <v>3:10</v>
       </c>
       <c r="H99" t="str">
-        <v>LØLØ</v>
+        <v>Olivia Dean</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>LØLØ - 007 (Official Music Video) - LØLØ</v>
+        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show] - Olivia Dean</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Tenille Townes - enabling (Official Visualizer)</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel)</v>
       </c>
       <c r="B100" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=yL_TxDF8WtI</v>
+        <v>https://www.youtube.com/watch?v=fo_j8Fqag8I</v>
       </c>
       <c r="D100" t="str">
         <v>2026-02-06</v>
@@ -4178,10 +4178,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G100" t="str">
-        <v>3:25</v>
+        <v>3:21</v>
       </c>
       <c r="H100" t="str">
-        <v>Tenille Townes</v>
+        <v>David Guetta and Tones And I</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Tenille Townes - enabling (Official Visualizer) - Tenille Townes</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel) - David Guetta and Tones And I</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Alan Walker - Not Home (Official Lyric Video)</v>
+        <v>The Avett Brothers - Matrimony (Official Video)</v>
       </c>
       <c r="B101" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=0m45tTheoCs</v>
+        <v>https://www.youtube.com/watch?v=7sD9-MtV9CY</v>
       </c>
       <c r="D101" t="str">
         <v>2026-02-06</v>
@@ -4216,10 +4216,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G101" t="str">
-        <v>2:01</v>
+        <v>3:06</v>
       </c>
       <c r="H101" t="str">
-        <v>Alan Walker</v>
+        <v>The Avett Brothers</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,7 +4231,7 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Alan Walker - Not Home (Official Lyric Video) - Alan Walker</v>
+        <v>The Avett Brothers - Matrimony (Official Video) - The Avett Brothers</v>
       </c>
     </row>
     <row r="102">

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L208"/>
+  <dimension ref="A1:L197"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -439,7 +439,7 @@
         <v>LADY GAGA - ABRACADABRA (LIVE AT THE 2026 GRAMMYS)</v>
       </c>
       <c r="B2" t="str">
-        <v>5 hours ago</v>
+        <v>6 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=Rn89mUndYbo</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>5 hours ago</v>
+        <v>6 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>4:16</v>
@@ -477,7 +477,7 @@
         <v>Carlos Vives - Te Dedico (Official Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>4 hours ago</v>
+        <v>5 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=H8KW0SgW99I</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>4 hours ago</v>
+        <v>5 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>3:53</v>
@@ -515,7 +515,7 @@
         <v>Monsieur Periné, Jossman - MUCHO CON DEMASIAO' (Video Oficial)</v>
       </c>
       <c r="B4" t="str">
-        <v>4 hours ago</v>
+        <v>5 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=mpmrrvhLzZ0</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>4 hours ago</v>
+        <v>5 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>2:25</v>
@@ -553,7 +553,7 @@
         <v>The Happy Fits - Tenderly (Official Audio)</v>
       </c>
       <c r="B5" t="str">
-        <v>7 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=10hExzTW4Hc</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>7 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>4:09</v>
@@ -591,7 +591,7 @@
         <v>chase (lyric vid) - Michael Aldag</v>
       </c>
       <c r="B6" t="str">
-        <v>9 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=QASMKs97wec</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>9 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v>2:45</v>
@@ -629,7 +629,7 @@
         <v>Dermot Kennedy - Funeral (Live Acoustic Session)</v>
       </c>
       <c r="B7" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=RyR1xAw9edU</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G7" t="str">
         <v>4:07</v>
@@ -667,7 +667,7 @@
         <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Official Video)</v>
       </c>
       <c r="B8" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=OYtHvS7n7ic</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G8" t="str">
         <v>4:34</v>
@@ -705,7 +705,7 @@
         <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Official Music Video)</v>
       </c>
       <c r="B9" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=XKvzT2CTnLE</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G9" t="str">
         <v>5:14</v>
@@ -743,7 +743,7 @@
         <v>Michael Bolton | Cupid (Official Visualizer)</v>
       </c>
       <c r="B10" t="str">
-        <v>11 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=1XDIbfJ_OGw</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>11 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G10" t="str">
         <v>3:11</v>
@@ -781,7 +781,7 @@
         <v>Lachie Gill - Last Drive</v>
       </c>
       <c r="B11" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=y79kD37Ffic</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="G11" t="str">
         <v>3:40</v>
@@ -819,7 +819,7 @@
         <v>Eli &amp; Fur - Strange (Official Visualiser)</v>
       </c>
       <c r="B12" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=KlgO3kKNc8o</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="G12" t="str">
         <v>3:45</v>
@@ -1997,7 +1997,7 @@
         <v>Ella Langley - Dandelion (Official Visualizer)</v>
       </c>
       <c r="B43" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C43" t="str">
         <v>https://www.youtube.com/watch?v=sf6eRmInk1s</v>
@@ -2009,7 +2009,7 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G43" t="str">
         <v>4:01</v>
@@ -2035,7 +2035,7 @@
         <v>Dogpark - Dandelion (Official Music Video)</v>
       </c>
       <c r="B44" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C44" t="str">
         <v>https://www.youtube.com/watch?v=fv9prIYHHzk</v>
@@ -2047,7 +2047,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G44" t="str">
         <v>3:16</v>
@@ -2073,7 +2073,7 @@
         <v>Lauren Spencer Smith - Natural Disaster (Visualizer)</v>
       </c>
       <c r="B45" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C45" t="str">
         <v>https://www.youtube.com/watch?v=T9YvLA2cdZs</v>
@@ -2085,7 +2085,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G45" t="str">
         <v>3:03</v>
@@ -2111,7 +2111,7 @@
         <v>ERNEST - Lorelei (Official Music Video)</v>
       </c>
       <c r="B46" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=dPWc_6IdDJk</v>
@@ -2123,7 +2123,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G46" t="str">
         <v>2:41</v>
@@ -2149,7 +2149,7 @@
         <v>Labrinth - I Keep My Promises (Official Audio)</v>
       </c>
       <c r="B47" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C47" t="str">
         <v>https://www.youtube.com/watch?v=CV5rR9JZK-0</v>
@@ -2161,7 +2161,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G47" t="str">
         <v>3:05</v>
@@ -2187,7 +2187,7 @@
         <v>Grace VanderWaal - Prettier (Official Lyric Video)</v>
       </c>
       <c r="B48" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C48" t="str">
         <v>https://www.youtube.com/watch?v=9HwTj3NZ16E</v>
@@ -2199,7 +2199,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G48" t="str">
         <v>2:46</v>
@@ -2225,7 +2225,7 @@
         <v>VOILÀ - Frozen Lake (Official Lyric Video)</v>
       </c>
       <c r="B49" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C49" t="str">
         <v>https://www.youtube.com/watch?v=Lmus-UbL1H0</v>
@@ -2237,7 +2237,7 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G49" t="str">
         <v>3:32</v>
@@ -2263,7 +2263,7 @@
         <v>Cannons - Starlight (Official Video)</v>
       </c>
       <c r="B50" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C50" t="str">
         <v>https://www.youtube.com/watch?v=bu6WSMDDPGY</v>
@@ -2275,7 +2275,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G50" t="str">
         <v>3:42</v>
@@ -2301,7 +2301,7 @@
         <v>Kylie Morgan - Like My Own (Official Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C51" t="str">
         <v>https://www.youtube.com/watch?v=zcYeoGBglC0</v>
@@ -2313,7 +2313,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G51" t="str">
         <v>2:38</v>
@@ -2339,7 +2339,7 @@
         <v>Lizzy McAlpine - House of the Rising Sun (Audio)</v>
       </c>
       <c r="B52" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C52" t="str">
         <v>https://www.youtube.com/watch?v=3igYRj82EiU</v>
@@ -2351,7 +2351,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G52" t="str">
         <v>3:10</v>
@@ -2377,7 +2377,7 @@
         <v>Willie Nelson - Heart Of America (From The Gray House Original Soundtrack)</v>
       </c>
       <c r="B53" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C53" t="str">
         <v>https://www.youtube.com/watch?v=0bhcO4Yphuo</v>
@@ -2389,7 +2389,7 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G53" t="str">
         <v>3:57</v>
@@ -2415,7 +2415,7 @@
         <v>Jeremy Camp - No Survivors (Live) ft. Skillet</v>
       </c>
       <c r="B54" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C54" t="str">
         <v>https://www.youtube.com/watch?v=Jjz1wFe5dMo</v>
@@ -2427,7 +2427,7 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G54" t="str">
         <v>2:19</v>
@@ -3403,7 +3403,7 @@
         <v>Bella White - Dream Song (Official Audio)</v>
       </c>
       <c r="B80" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C80" t="str">
         <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
@@ -3415,7 +3415,7 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G80" t="str">
         <v>4:37</v>
@@ -3441,7 +3441,7 @@
         <v>Ryan Wright - Film School Kids (Official Video)</v>
       </c>
       <c r="B81" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C81" t="str">
         <v>https://www.youtube.com/watch?v=pnAz9RwGSek</v>
@@ -3453,7 +3453,7 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G81" t="str">
         <v>4:06</v>
@@ -3479,7 +3479,7 @@
         <v>Dove Cameron - Do I Wanna Know? (Official Visualizer)</v>
       </c>
       <c r="B82" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C82" t="str">
         <v>https://www.youtube.com/watch?v=u7aPv2saz_I</v>
@@ -3491,7 +3491,7 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G82" t="str">
         <v>3:54</v>
@@ -3517,7 +3517,7 @@
         <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video)</v>
       </c>
       <c r="B83" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C83" t="str">
         <v>https://www.youtube.com/watch?v=WGb8KVdqs6k</v>
@@ -3529,7 +3529,7 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G83" t="str">
         <v>4:10</v>
@@ -3555,7 +3555,7 @@
         <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video)</v>
       </c>
       <c r="B84" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C84" t="str">
         <v>https://www.youtube.com/watch?v=X1ZeY4Y3l1M</v>
@@ -3567,7 +3567,7 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G84" t="str">
         <v>3:26</v>
@@ -3631,7 +3631,7 @@
         <v>Mitchell Tenpenny - You Phase (Official Music Video)</v>
       </c>
       <c r="B86" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C86" t="str">
         <v>https://www.youtube.com/watch?v=UPuK6wV5Zco</v>
@@ -3643,7 +3643,7 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G86" t="str">
         <v>2:56</v>
@@ -3669,7 +3669,7 @@
         <v>Tauren Wells - Breathe On It (Official Lyric Video)</v>
       </c>
       <c r="B87" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
         <v>https://www.youtube.com/watch?v=9hW9sNMn2A0</v>
@@ -3681,7 +3681,7 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G87" t="str">
         <v>4:01</v>
@@ -3707,7 +3707,7 @@
         <v>Maiah Manser - Feeling it All (Official Music Video)</v>
       </c>
       <c r="B88" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C88" t="str">
         <v>https://www.youtube.com/watch?v=JMYvXleIwfU</v>
@@ -3719,7 +3719,7 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G88" t="str">
         <v>3:05</v>
@@ -3745,7 +3745,7 @@
         <v>Taylor Austin Dye - Man For That (Official Music Video)</v>
       </c>
       <c r="B89" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C89" t="str">
         <v>https://www.youtube.com/watch?v=vOzX-o11seI</v>
@@ -3757,7 +3757,7 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G89" t="str">
         <v>2:27</v>
@@ -3783,7 +3783,7 @@
         <v>Chelsea Cutler - BAD (Official Video)</v>
       </c>
       <c r="B90" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C90" t="str">
         <v>https://www.youtube.com/watch?v=86k4E6ydHVU</v>
@@ -3795,7 +3795,7 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G90" t="str">
         <v>2:34</v>
@@ -3821,7 +3821,7 @@
         <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video)</v>
       </c>
       <c r="B91" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C91" t="str">
         <v>https://www.youtube.com/watch?v=-UWIFAiOOPE</v>
@@ -3833,7 +3833,7 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G91" t="str">
         <v>3:13</v>
@@ -3859,7 +3859,7 @@
         <v>Louis Tomlinson - Dark To Light (Visualiser)</v>
       </c>
       <c r="B92" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C92" t="str">
         <v>https://www.youtube.com/watch?v=02QyA29poAM</v>
@@ -3871,7 +3871,7 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G92" t="str">
         <v>3:13</v>
@@ -3897,7 +3897,7 @@
         <v>CAIN - So Long Sad Songs (Lyric Video)</v>
       </c>
       <c r="B93" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C93" t="str">
         <v>https://www.youtube.com/watch?v=feOv8nufa_I</v>
@@ -3909,7 +3909,7 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G93" t="str">
         <v>3:08</v>
@@ -4236,13 +4236,13 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Como en el Idilio</v>
+        <v>Die For Me</v>
       </c>
       <c r="B102" t="str">
         <v/>
       </c>
       <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/como-en-el-idilio/1870716613</v>
+        <v>https://music.apple.com/us/song/die-for-me/1872664213</v>
       </c>
       <c r="D102" t="str">
         <v>2026-02-06</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>Como en el Idilio - Single</v>
+        <v>KONNAKOL</v>
       </c>
       <c r="G102" t="str">
-        <v>4:27</v>
+        <v>3:00</v>
       </c>
       <c r="H102" t="str">
-        <v>Marc Anthony</v>
+        <v>ZAYN</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/marc-anthony/217029</v>
+        <v>https://music.apple.com/us/artist/zayn/973181994</v>
       </c>
       <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/como-en-el-idilio/1870716612</v>
+        <v>https://music.apple.com/us/album/die-for-me/1872663947</v>
       </c>
       <c r="L102" t="str">
-        <v>Como en el Idilio - Marc Anthony</v>
+        <v>Die For Me - ZAYN</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Body</v>
+        <v>Two Six</v>
       </c>
       <c r="B103" t="str">
         <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/body/1871258331</v>
+        <v>https://music.apple.com/us/song/two-six/1875080974</v>
       </c>
       <c r="D103" t="str">
         <v>2026-02-06</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>OCTANE</v>
+        <v>The Fall-Off</v>
       </c>
       <c r="G103" t="str">
-        <v>2:35</v>
+        <v>3:16</v>
       </c>
       <c r="H103" t="str">
-        <v>Don Toliver</v>
+        <v>J. Cole</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/don-toliver/1237012992</v>
+        <v>https://music.apple.com/us/artist/j-cole/73705833</v>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/body/1871258329</v>
+        <v>https://music.apple.com/us/album/two-six/1875080726</v>
       </c>
       <c r="L103" t="str">
-        <v>Body - Don Toliver</v>
+        <v>Two Six - J. Cole</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Dandelion</v>
+        <v>Dracula (JENNIE Remix)</v>
       </c>
       <c r="B104" t="str">
         <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/dandelion/1869436838</v>
+        <v>https://music.apple.com/us/song/dracula-jennie-remix/1874125269</v>
       </c>
       <c r="D104" t="str">
         <v>2026-02-06</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>Dandelion</v>
+        <v>Dracula (Remix) - Single</v>
       </c>
       <c r="G104" t="str">
-        <v>4:00</v>
+        <v>3:29</v>
       </c>
       <c r="H104" t="str">
-        <v>Ella Langley</v>
+        <v>Tame Impala</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/ella-langley/1384373733</v>
+        <v>https://music.apple.com/us/artist/tame-impala/290242959</v>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/dandelion/1869436835</v>
+        <v>https://music.apple.com/us/album/dracula-jennie-remix/1874125260</v>
       </c>
       <c r="L104" t="str">
-        <v>Dandelion - Ella Langley</v>
+        <v>Dracula (JENNIE Remix) - Tame Impala</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>LIGHTS GO OUT</v>
+        <v>Hotel California</v>
       </c>
       <c r="B105" t="str">
         <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/lights-go-out/1870833473</v>
+        <v>https://music.apple.com/us/song/hotel-california/1849707040</v>
       </c>
       <c r="D105" t="str">
         <v>2026-02-06</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>LIGHTS GO OUT - Single</v>
+        <v>Piss In The Wind</v>
       </c>
       <c r="G105" t="str">
-        <v>2:38</v>
+        <v>2:08</v>
       </c>
       <c r="H105" t="str">
-        <v>John Summit</v>
+        <v>Joji</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
+        <v>https://music.apple.com/us/artist/joji/1258279972</v>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/lights-go-out/1870833462</v>
+        <v>https://music.apple.com/us/album/hotel-california/1849706656</v>
       </c>
       <c r="L105" t="str">
-        <v>LIGHTS GO OUT - John Summit</v>
+        <v>Hotel California - Joji</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>The Great Divide</v>
+        <v>Homewrecker</v>
       </c>
       <c r="B106" t="str">
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/the-great-divide/1872239886</v>
+        <v>https://music.apple.com/us/song/homewrecker/1871595253</v>
       </c>
       <c r="D106" t="str">
         <v>2026-02-06</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>The Great Divide</v>
+        <v>Homewrecker - Single</v>
       </c>
       <c r="G106" t="str">
-        <v>5:17</v>
+        <v>3:29</v>
       </c>
       <c r="H106" t="str">
-        <v>Noah Kahan</v>
+        <v>sombr</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/noah-kahan/328583953</v>
+        <v>https://music.apple.com/us/artist/sombr/1589842503</v>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/the-great-divide/1872239868</v>
+        <v>https://music.apple.com/us/album/homewrecker/1871595252</v>
       </c>
       <c r="L106" t="str">
-        <v>The Great Divide - Noah Kahan</v>
+        <v>Homewrecker - sombr</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>tristón</v>
+        <v>Might Just</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/trist%C3%B3n/1872585947</v>
+        <v>https://music.apple.com/us/song/might-just/1858755211</v>
       </c>
       <c r="D107" t="str">
         <v>2026-02-06</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>tristón - Single</v>
+        <v>Do You Still Love Me?</v>
       </c>
       <c r="G107" t="str">
-        <v>3:36</v>
+        <v>3:43</v>
       </c>
       <c r="H107" t="str">
-        <v>Fuerza Regida</v>
+        <v>Ella Mai</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/fuerza-regida/1275690475</v>
+        <v>https://music.apple.com/us/artist/ella-mai/1160482144</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/trist%C3%B3n/1872585761</v>
+        <v>https://music.apple.com/us/album/might-just/1858754868</v>
       </c>
       <c r="L107" t="str">
-        <v>tristón - Fuerza Regida</v>
+        <v>Might Just - Ella Mai</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Feed the Streets</v>
+        <v>Cloud 9</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/feed-the-streets/1869462051</v>
+        <v>https://music.apple.com/us/song/cloud-9/1851297055</v>
       </c>
       <c r="D108" t="str">
         <v>2026-02-06</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>Feed the Streets - Single</v>
+        <v>Cloud 9</v>
       </c>
       <c r="G108" t="str">
-        <v>2:58</v>
+        <v>3:33</v>
       </c>
       <c r="H108" t="str">
-        <v>Rod Wave</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/rod-wave/1140623439</v>
+        <v>https://music.apple.com/us/artist/megan-moroney/1552469569</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/feed-the-streets/1869462040</v>
+        <v>https://music.apple.com/us/album/cloud-9/1851296746</v>
       </c>
       <c r="L108" t="str">
-        <v>Feed the Streets - Rod Wave</v>
+        <v>Cloud 9 - Megan Moroney</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>I Did This To Myself</v>
+        <v>Cry</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/i-did-this-to-myself/1861531672</v>
+        <v>https://music.apple.com/us/song/cry/1845189974</v>
       </c>
       <c r="D109" t="str">
         <v>2026-02-06</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>Distracted</v>
+        <v>Whatever's Clever!</v>
       </c>
       <c r="G109" t="str">
-        <v>2:30</v>
+        <v>3:07</v>
       </c>
       <c r="H109" t="str">
-        <v>Thundercat</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/thundercat/367322286</v>
+        <v>https://music.apple.com/us/artist/charlie-puth/336249253</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/i-did-this-to-myself/1861531667</v>
+        <v>https://music.apple.com/us/album/cry/1845189970</v>
       </c>
       <c r="L109" t="str">
-        <v>I Did This To Myself - Thundercat</v>
+        <v>Cry - Charlie Puth</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>golden boy</v>
+        <v>I'll Change for You</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/golden-boy/1872543012</v>
+        <v>https://music.apple.com/us/song/ill-change-for-you/1860622841</v>
       </c>
       <c r="D110" t="str">
         <v>2026-02-06</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>stardust - EP</v>
+        <v>Nothing's About to Happen to Me</v>
       </c>
       <c r="G110" t="str">
-        <v>3:17</v>
+        <v>3:16</v>
       </c>
       <c r="H110" t="str">
-        <v>Freya Skye</v>
+        <v>Mitski</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/freya-skye/1541643053</v>
+        <v>https://music.apple.com/us/artist/mitski/497546276</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/golden-boy/1872542998</v>
+        <v>https://music.apple.com/us/album/ill-change-for-you/1860622550</v>
       </c>
       <c r="L110" t="str">
-        <v>golden boy - Freya Skye</v>
+        <v>I'll Change for You - Mitski</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>For Hire</v>
+        <v>ASSIGNMENT</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/for-hire/1870722567</v>
+        <v>https://music.apple.com/us/song/assignment/1872764440</v>
       </c>
       <c r="D111" t="str">
         <v>2026-02-06</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>For Hire - Single</v>
+        <v>ASSIGNMENT - Single</v>
       </c>
       <c r="G111" t="str">
-        <v>3:44</v>
+        <v>2:23</v>
       </c>
       <c r="H111" t="str">
-        <v>People I’ve Met</v>
+        <v>Power Snatch</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/people-ive-met/1853169947</v>
+        <v>https://music.apple.com/us/artist/power-snatch/1872764439</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/for-hire/1870722565</v>
+        <v>https://music.apple.com/us/album/assignment/1872764438</v>
       </c>
       <c r="L111" t="str">
-        <v>For Hire - People I’ve Met</v>
+        <v>ASSIGNMENT - Power Snatch</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Penny in the Lake</v>
+        <v>Como en el Idilio</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/penny-in-the-lake/1844710053</v>
+        <v>https://music.apple.com/us/song/como-en-el-idilio/1870716613</v>
       </c>
       <c r="D112" t="str">
         <v>2026-02-06</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>Singin’ to an Empty Chair</v>
+        <v>Como en el Idilio - Single</v>
       </c>
       <c r="G112" t="str">
-        <v>3:51</v>
+        <v>4:27</v>
       </c>
       <c r="H112" t="str">
-        <v>Ratboys</v>
+        <v>Marc Anthony</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/ratboys/997909855</v>
+        <v>https://music.apple.com/us/artist/marc-anthony/217029</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/penny-in-the-lake/1844710034</v>
+        <v>https://music.apple.com/us/album/como-en-el-idilio/1870716612</v>
       </c>
       <c r="L112" t="str">
-        <v>Penny in the Lake - Ratboys</v>
+        <v>Como en el Idilio - Marc Anthony</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>McArthur</v>
+        <v>golden boy</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/mcarthur/1871231844</v>
+        <v>https://music.apple.com/us/song/golden-boy/1872543012</v>
       </c>
       <c r="D113" t="str">
         <v>2026-02-06</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>McArthur - Single</v>
+        <v>stardust - EP</v>
       </c>
       <c r="G113" t="str">
-        <v>3:51</v>
+        <v>3:17</v>
       </c>
       <c r="H113" t="str">
-        <v>HARDY</v>
+        <v>Freya Skye</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/hardy/1438874739</v>
+        <v>https://music.apple.com/us/artist/freya-skye/1541643053</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/mcarthur/1871231823</v>
+        <v>https://music.apple.com/us/album/golden-boy/1872542998</v>
       </c>
       <c r="L113" t="str">
-        <v>McArthur - HARDY</v>
+        <v>golden boy - Freya Skye</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Debris</v>
+        <v>Penny in the Lake</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/debris/1853069633</v>
+        <v>https://music.apple.com/us/song/penny-in-the-lake/1844710053</v>
       </c>
       <c r="D114" t="str">
         <v>2026-02-06</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>COSMIC OPERA ACT I</v>
+        <v>Singin’ to an Empty Chair</v>
       </c>
       <c r="G114" t="str">
-        <v>2:55</v>
+        <v>3:51</v>
       </c>
       <c r="H114" t="str">
-        <v>Labrinth</v>
+        <v>Ratboys</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
+        <v>https://music.apple.com/us/artist/ratboys/997909855</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/debris/1853069628</v>
+        <v>https://music.apple.com/us/album/penny-in-the-lake/1844710034</v>
       </c>
       <c r="L114" t="str">
-        <v>Debris - Labrinth</v>
+        <v>Penny in the Lake - Ratboys</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>God Owes Me Money (Live at Apple Music Radio)</v>
+        <v>Heaven</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/god-owes-me-money-live-at-apple-music-radio/1871521120</v>
+        <v>https://music.apple.com/us/song/heaven/1862570892</v>
       </c>
       <c r="D115" t="str">
         <v>2026-02-06</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>Throw Me Away / God Owes Me Money (Live at Apple Music Radio)</v>
+        <v>Ambiguous Desire</v>
       </c>
       <c r="G115" t="str">
-        <v>3:25</v>
+        <v>4:26</v>
       </c>
       <c r="H115" t="str">
-        <v>Militarie Gun</v>
+        <v>Arlo Parks</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/militarie-gun/1529039426</v>
+        <v>https://music.apple.com/us/artist/arlo-parks/1291875084</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/god-owes-me-money-live-at-apple-music-radio/1871520929</v>
+        <v>https://music.apple.com/us/album/heaven/1862570378</v>
       </c>
       <c r="L115" t="str">
-        <v>God Owes Me Money (Live at Apple Music Radio) - Militarie Gun</v>
+        <v>Heaven - Arlo Parks</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>ROCKSTAR RAGING (feat. Swae Lee)</v>
+        <v>Adrenaline</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/rockstar-raging-feat-swae-lee/1873028187</v>
+        <v>https://music.apple.com/us/song/adrenaline/1867153030</v>
       </c>
       <c r="D116" t="str">
         <v>2026-02-06</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>ROCKSTAR RAGING (feat. Swae Lee) - Single</v>
+        <v>GOLDEN HOUR : Part.4 - EP</v>
       </c>
       <c r="G116" t="str">
-        <v>4:38</v>
+        <v>3:39</v>
       </c>
       <c r="H116" t="str">
-        <v>Mike WiLL Made-It</v>
+        <v>ATEEZ</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/mike-will-made-it/511333957</v>
+        <v>https://music.apple.com/us/artist/ateez/1439301205</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/rockstar-raging-feat-swae-lee/1873028186</v>
+        <v>https://music.apple.com/us/album/adrenaline/1867153027</v>
       </c>
       <c r="L116" t="str">
-        <v>ROCKSTAR RAGING (feat. Swae Lee) - Mike WiLL Made-It</v>
+        <v>Adrenaline - ATEEZ</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>1+1</v>
+        <v>Sweet To Me</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/1-1/1870378316</v>
+        <v>https://music.apple.com/us/song/sweet-to-me/1856393194</v>
       </c>
       <c r="D117" t="str">
         <v>2026-02-06</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>1+1 - Single</v>
+        <v>Sunday Best</v>
       </c>
       <c r="G117" t="str">
-        <v>3:06</v>
+        <v>4:17</v>
       </c>
       <c r="H117" t="str">
-        <v>Maluma</v>
+        <v>Nick Jonas</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/maluma/448916501</v>
+        <v>https://music.apple.com/us/artist/nick-jonas/286541773</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/1-1/1870378315</v>
+        <v>https://music.apple.com/us/album/sweet-to-me/1856393193</v>
       </c>
       <c r="L117" t="str">
-        <v>1+1 - Maluma</v>
+        <v>Sweet To Me - Nick Jonas</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Still Sincere (feat. PinkPantheress)</v>
+        <v>Time Goes On</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/still-sincere-feat-pinkpantheress/1862228374</v>
+        <v>https://music.apple.com/us/song/time-goes-on/1872532339</v>
       </c>
       <c r="D118" t="str">
         <v>2026-02-06</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>Still Sincere (feat. PinkPantheress) - Single</v>
+        <v>Time Goes On - Single</v>
       </c>
       <c r="G118" t="str">
-        <v>3:08</v>
+        <v>2:55</v>
       </c>
       <c r="H118" t="str">
-        <v>MJ Cole</v>
+        <v>Koe Wetzel</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/mj-cole/405892</v>
+        <v>https://music.apple.com/us/artist/koe-wetzel/1139953953</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/still-sincere-feat-pinkpantheress/1862228373</v>
+        <v>https://music.apple.com/us/album/time-goes-on/1872532335</v>
       </c>
       <c r="L118" t="str">
-        <v>Still Sincere (feat. PinkPantheress) - MJ Cole</v>
+        <v>Time Goes On - Koe Wetzel</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Two Car Garage</v>
+        <v>Drive Safe</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/two-car-garage/1869137588</v>
+        <v>https://music.apple.com/us/song/drive-safe/1868764975</v>
       </c>
       <c r="D119" t="str">
         <v>2026-02-06</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>Two Car Garage - Single</v>
+        <v>Drive Safe - Single</v>
       </c>
       <c r="G119" t="str">
-        <v>3:02</v>
+        <v>3:21</v>
       </c>
       <c r="H119" t="str">
-        <v>Jon Bellion</v>
+        <v>Myles Smith</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/jon-bellion/659289673</v>
+        <v>https://music.apple.com/us/artist/myles-smith/1249499491</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/two-car-garage/1869137587</v>
+        <v>https://music.apple.com/us/album/drive-safe/1868764971</v>
       </c>
       <c r="L119" t="str">
-        <v>Two Car Garage - Jon Bellion</v>
+        <v>Drive Safe - Myles Smith</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>fml .</v>
+        <v>Love To Be Loved</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/fml/1872686260</v>
+        <v>https://music.apple.com/us/song/love-to-be-loved/1873043629</v>
       </c>
       <c r="D120" t="str">
         <v>2026-02-06</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>The Boy who cried Terrified .</v>
+        <v>Love To Be Loved - Single</v>
       </c>
       <c r="G120" t="str">
-        <v>2:40</v>
+        <v>2:50</v>
       </c>
       <c r="H120" t="str">
-        <v>fakemink</v>
+        <v>The Warning</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/fakemink/1744500063</v>
+        <v>https://music.apple.com/us/artist/the-warning/260719953</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/fml/1872686249</v>
+        <v>https://music.apple.com/us/album/love-to-be-loved/1873043478</v>
       </c>
       <c r="L120" t="str">
-        <v>fml . - fakemink</v>
+        <v>Love To Be Loved - The Warning</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Faked It All The Time</v>
+        <v>Mi Yo de Antes</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/faked-it-all-the-time/1871050032</v>
+        <v>https://music.apple.com/us/song/mi-yo-de-antes/1871552001</v>
       </c>
       <c r="D121" t="str">
         <v>2026-02-06</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Faked It All The Time - Single</v>
+        <v>Mi Yo de Antes - Single</v>
       </c>
       <c r="G121" t="str">
-        <v>3:01</v>
+        <v>3:02</v>
       </c>
       <c r="H121" t="str">
-        <v>Allie Sherlock</v>
+        <v>Eden Muñoz</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/allie-sherlock/1314464325</v>
+        <v>https://music.apple.com/us/artist/eden-mu%C3%B1oz/383984059</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/faked-it-all-the-time/1871050031</v>
+        <v>https://music.apple.com/us/album/mi-yo-de-antes/1871552000</v>
       </c>
       <c r="L121" t="str">
-        <v>Faked It All The Time - Allie Sherlock</v>
+        <v>Mi Yo de Antes - Eden Muñoz</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>House of the Rising Sun</v>
+        <v>Omens</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/house-of-the-rising-sun/1872111857</v>
+        <v>https://music.apple.com/us/song/omens/1872546206</v>
       </c>
       <c r="D122" t="str">
         <v>2026-02-06</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>House of the Rising Sun - Single</v>
+        <v>Omens - Single</v>
       </c>
       <c r="G122" t="str">
-        <v>3:08</v>
+        <v>2:00</v>
       </c>
       <c r="H122" t="str">
-        <v>Lizzy McAlpine</v>
+        <v>EsDeeKid</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/lizzy-mcalpine/1350245112</v>
+        <v>https://music.apple.com/us/artist/esdeekid/1754179834</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/house-of-the-rising-sun/1872111734</v>
+        <v>https://music.apple.com/us/album/omens/1872546204</v>
       </c>
       <c r="L122" t="str">
-        <v>House of the Rising Sun - Lizzy McAlpine</v>
+        <v>Omens - EsDeeKid</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Lorelei</v>
+        <v>My Regards</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/lorelei/1867640808</v>
+        <v>https://music.apple.com/us/song/my-regards/1871502698</v>
       </c>
       <c r="D123" t="str">
         <v>2026-02-06</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>Lorelei - Single</v>
+        <v>Florescence</v>
       </c>
       <c r="G123" t="str">
-        <v>2:35</v>
+        <v>3:11</v>
       </c>
       <c r="H123" t="str">
-        <v>ERNEST</v>
+        <v>Maisie Peters</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
+        <v>https://music.apple.com/us/artist/maisie-peters/1264549322</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/lorelei/1867640583</v>
+        <v>https://music.apple.com/us/album/my-regards/1871502372</v>
       </c>
       <c r="L123" t="str">
-        <v>Lorelei - ERNEST</v>
+        <v>My Regards - Maisie Peters</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Free</v>
+        <v>Time After Time</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/free/1870703329</v>
+        <v>https://music.apple.com/us/song/time-after-time/1869014152</v>
       </c>
       <c r="D124" t="str">
         <v>2026-02-06</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Free - Single</v>
+        <v>Time After Time - Single</v>
       </c>
       <c r="G124" t="str">
-        <v>3:56</v>
+        <v>2:48</v>
       </c>
       <c r="H124" t="str">
-        <v>SLANDER</v>
+        <v>EJAE</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/slander/1051421487</v>
+        <v>https://music.apple.com/us/artist/ejae/1118367711</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/free/1870703327</v>
+        <v>https://music.apple.com/us/album/time-after-time/1869014148</v>
       </c>
       <c r="L124" t="str">
-        <v>Free - SLANDER</v>
+        <v>Time After Time - EJAE</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>ASSIGNMENT</v>
+        <v>Don't Want Your Love</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/assignment/1872764440</v>
+        <v>https://music.apple.com/us/song/dont-want-your-love/1851368163</v>
       </c>
       <c r="D125" t="str">
         <v>2026-02-06</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>ASSIGNMENT - Single</v>
+        <v>ODYSSEY</v>
       </c>
       <c r="G125" t="str">
-        <v>2:23</v>
+        <v>3:12</v>
       </c>
       <c r="H125" t="str">
-        <v>Power Snatch</v>
+        <v>ILLENIUM</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/power-snatch/1872764439</v>
+        <v>https://music.apple.com/us/artist/illenium/645420096</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/assignment/1872764438</v>
+        <v>https://music.apple.com/us/album/dont-want-your-love/1851368154</v>
       </c>
       <c r="L125" t="str">
-        <v>ASSIGNMENT - Power Snatch</v>
+        <v>Don't Want Your Love - ILLENIUM</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>professional heartbreaker</v>
+        <v>Pa' Los Envidiosos</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/professional-heartbreaker/1871053476</v>
+        <v>https://music.apple.com/us/song/pa-los-envidiosos/1867022002</v>
       </c>
       <c r="D126" t="str">
         <v>2026-02-06</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>professional heartbreaker - Single</v>
+        <v>Pa' Los Envidiosos - Single</v>
       </c>
       <c r="G126" t="str">
-        <v>2:55</v>
+        <v>3:37</v>
       </c>
       <c r="H126" t="str">
-        <v>Artemas</v>
+        <v>Pitbull</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
+        <v>https://music.apple.com/us/artist/pitbull/27044968</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/professional-heartbreaker/1871053473</v>
+        <v>https://music.apple.com/us/album/pa-los-envidiosos/1867021988</v>
       </c>
       <c r="L126" t="str">
-        <v>professional heartbreaker - Artemas</v>
+        <v>Pa' Los Envidiosos - Pitbull</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>tell me what you want</v>
+        <v>Plei</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/tell-me-what-you-want/1871463892</v>
+        <v>https://music.apple.com/us/song/plei/1872137577</v>
       </c>
       <c r="D127" t="str">
         <v>2026-02-06</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>ACT II</v>
+        <v>Plei - Single</v>
       </c>
       <c r="G127" t="str">
-        <v>3:56</v>
+        <v>3:22</v>
       </c>
       <c r="H127" t="str">
-        <v>Sasha Keable</v>
+        <v>Chuwi</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/sasha-keable/325850892</v>
+        <v>https://music.apple.com/us/artist/chuwi/1493658688</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/tell-me-what-you-want/1871463550</v>
+        <v>https://music.apple.com/us/album/plei/1872137372</v>
       </c>
       <c r="L127" t="str">
-        <v>tell me what you want - Sasha Keable</v>
+        <v>Plei - Chuwi</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Aguas</v>
+        <v>Flood (feat. Bon Iver)</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/aguas/1869455857</v>
+        <v>https://music.apple.com/us/song/flood-feat-bon-iver/1868826992</v>
       </c>
       <c r="D128" t="str">
         <v>2026-02-06</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>Aguas - Single</v>
+        <v>Of Earth &amp; Wires</v>
       </c>
       <c r="G128" t="str">
-        <v>2:52</v>
+        <v>2:59</v>
       </c>
       <c r="H128" t="str">
-        <v>Luis R Conriquez</v>
+        <v>Dua Saleh</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
+        <v>https://music.apple.com/us/artist/dua-saleh/1442780979</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/aguas/1869455582</v>
+        <v>https://music.apple.com/us/album/flood-feat-bon-iver/1868826829</v>
       </c>
       <c r="L128" t="str">
-        <v>Aguas - Luis R Conriquez</v>
+        <v>Flood (feat. Bon Iver) - Dua Saleh</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Ants In My Room</v>
+        <v>Rain</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/ants-in-my-room/1870967813</v>
+        <v>https://music.apple.com/us/song/rain/1867258289</v>
       </c>
       <c r="D129" t="str">
         <v>2026-02-06</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>Ants In My Room - Single</v>
+        <v>Rain - Single</v>
       </c>
       <c r="G129" t="str">
-        <v>2:48</v>
+        <v>3:28</v>
       </c>
       <c r="H129" t="str">
-        <v>Carter Vail</v>
+        <v>FISHER</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/carter-vail/1102115053</v>
+        <v>https://music.apple.com/us/artist/fisher/1256012920</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/ants-in-my-room/1870967810</v>
+        <v>https://music.apple.com/us/album/rain/1867258288</v>
       </c>
       <c r="L129" t="str">
-        <v>Ants In My Room - Carter Vail</v>
+        <v>Rain - FISHER</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Baddie</v>
+        <v>Release The Pressure</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/baddie/1849760827</v>
+        <v>https://music.apple.com/us/song/release-the-pressure/1869050189</v>
       </c>
       <c r="D130" t="str">
         <v>2026-02-06</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>Bohemio</v>
+        <v>Release The Pressure - Single</v>
       </c>
       <c r="G130" t="str">
-        <v>3:11</v>
+        <v>3:23</v>
       </c>
       <c r="H130" t="str">
-        <v>Nicky Jam</v>
+        <v>Calvin Harris</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/nicky-jam/33987470</v>
+        <v>https://music.apple.com/us/artist/calvin-harris/201955086</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/baddie/1849760822</v>
+        <v>https://music.apple.com/us/album/release-the-pressure/1869050188</v>
       </c>
       <c r="L130" t="str">
-        <v>Baddie - Nicky Jam</v>
+        <v>Release The Pressure - Calvin Harris</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>What You Need - A COLORS SHOW</v>
+        <v>Sexistential (Arca’s Take)</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/what-you-need-a-colors-show/1870990925</v>
+        <v>https://music.apple.com/us/song/sexistential-arcas-take/1871222137</v>
       </c>
       <c r="D131" t="str">
         <v>2026-02-06</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>What You Need - A COLORS SHOW - Single</v>
+        <v>Sexistential (Arca’s Take) - Single</v>
       </c>
       <c r="G131" t="str">
-        <v>3:51</v>
+        <v>3:44</v>
       </c>
       <c r="H131" t="str">
-        <v>Tems</v>
+        <v>Robyn</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/tems/1413909060</v>
+        <v>https://music.apple.com/us/artist/robyn/535211</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/what-you-need-a-colors-show/1870990923</v>
+        <v>https://music.apple.com/us/album/sexistential-arcas-take/1871222136</v>
       </c>
       <c r="L131" t="str">
-        <v>What You Need - A COLORS SHOW - Tems</v>
+        <v>Sexistential (Arca’s Take) - Robyn</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>OK OK (Hamdi remix)</v>
+        <v>heal something</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/ok-ok-hamdi-remix/1871538130</v>
+        <v>https://music.apple.com/us/song/heal-something/1871463897</v>
       </c>
       <c r="D132" t="str">
         <v>2026-02-06</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>OK OK (Hamdi remix) - Single</v>
+        <v>ACT II</v>
       </c>
       <c r="G132" t="str">
-        <v>3:16</v>
+        <v>3:01</v>
       </c>
       <c r="H132" t="str">
-        <v>Fred again..</v>
+        <v>Sasha Keable</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
+        <v>https://music.apple.com/us/artist/sasha-keable/325850892</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/ok-ok-hamdi-remix/1871538128</v>
+        <v>https://music.apple.com/us/album/heal-something/1871463550</v>
       </c>
       <c r="L132" t="str">
-        <v>OK OK (Hamdi remix) - Fred again..</v>
+        <v>heal something - Sasha Keable</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Ever and Ever Before (feat. MŌRIAH &amp; Courtney)</v>
+        <v>Buenos Días</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/ever-and-ever-before-feat-m%C5%8Driah-courtney/1869383260</v>
+        <v>https://music.apple.com/us/song/buenos-d%C3%ADas/1872144122</v>
       </c>
       <c r="D133" t="str">
         <v>2026-02-06</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Ever and Ever Before (feat. MŌRIAH &amp; Courtney) - Single</v>
+        <v>Buenos Días - Single</v>
       </c>
       <c r="G133" t="str">
-        <v>3:50</v>
+        <v>2:39</v>
       </c>
       <c r="H133" t="str">
-        <v>for KING &amp; COUNTRY</v>
+        <v>Eladio Carrión</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/for-king-country/457871289</v>
+        <v>https://music.apple.com/us/artist/eladio-carri%C3%B3n/1024801206</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/ever-and-ever-before-feat-m%C5%8Driah-courtney/1869383258</v>
+        <v>https://music.apple.com/us/album/buenos-d%C3%ADas/1872144118</v>
       </c>
       <c r="L133" t="str">
-        <v>Ever and Ever Before (feat. MŌRIAH &amp; Courtney) - for KING &amp; COUNTRY</v>
+        <v>Buenos Días - Eladio Carrión</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>For The First Time, Again</v>
+        <v>COOK</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/for-the-first-time-again/1834736723</v>
+        <v>https://music.apple.com/us/song/cook/1872816147</v>
       </c>
       <c r="D134" t="str">
         <v>2026-02-06</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>For The First Time, Again</v>
+        <v>COOK - Single</v>
       </c>
       <c r="G134" t="str">
-        <v>3:33</v>
+        <v>2:50</v>
       </c>
       <c r="H134" t="str">
-        <v>Tyler Ballgame</v>
+        <v>SOFI TUKKER</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/tyler-ballgame/1755347001</v>
+        <v>https://music.apple.com/us/artist/sofi-tukker/998656537</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/for-the-first-time-again/1834736717</v>
+        <v>https://music.apple.com/us/album/cook/1872816146</v>
       </c>
       <c r="L134" t="str">
-        <v>For The First Time, Again - Tyler Ballgame</v>
+        <v>COOK - SOFI TUKKER</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Liars Tale</v>
+        <v>You Got to Lose</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/liars-tale/1862207951</v>
+        <v>https://music.apple.com/us/song/you-got-to-lose/1873477955</v>
       </c>
       <c r="D135" t="str">
         <v>2026-02-06</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>Liars Tale - Single</v>
+        <v>Peaches!</v>
       </c>
       <c r="G135" t="str">
         <v>3:17</v>
       </c>
       <c r="H135" t="str">
-        <v>Kneecap</v>
+        <v>The Black Keys</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
+        <v>https://music.apple.com/us/artist/the-black-keys/5893059</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/liars-tale/1862207946</v>
+        <v>https://music.apple.com/us/album/you-got-to-lose/1873477948</v>
       </c>
       <c r="L135" t="str">
-        <v>Liars Tale - Kneecap</v>
+        <v>You Got to Lose - The Black Keys</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Afraid Of The Dark</v>
+        <v>Different Kind Of Love</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/afraid-of-the-dark/1872184048</v>
+        <v>https://music.apple.com/us/song/different-kind-of-love/1866700768</v>
       </c>
       <c r="D136" t="str">
         <v>2026-02-06</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>Afraid Of The Dark - Single</v>
+        <v>Victory Garden</v>
       </c>
       <c r="G136" t="str">
-        <v>4:38</v>
+        <v>3:39</v>
       </c>
       <c r="H136" t="str">
-        <v>Motionless In White</v>
+        <v>Young the Giant</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/motionless-in-white/266666216</v>
+        <v>https://music.apple.com/us/artist/young-the-giant/394582977</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/afraid-of-the-dark/1872184047</v>
+        <v>https://music.apple.com/us/album/different-kind-of-love/1866700309</v>
       </c>
       <c r="L136" t="str">
-        <v>Afraid Of The Dark - Motionless In White</v>
+        <v>Different Kind Of Love - Young the Giant</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Wake Up Calling</v>
+        <v>Living Water</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/wake-up-calling/1862338150</v>
+        <v>https://music.apple.com/us/song/living-water/1871565262</v>
       </c>
       <c r="D137" t="str">
         <v>2026-02-06</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>Wake Up Calling - Single</v>
+        <v>Reconstruction: Second Story</v>
       </c>
       <c r="G137" t="str">
-        <v>3:49</v>
+        <v>2:09</v>
       </c>
       <c r="H137" t="str">
-        <v>Papa Roach</v>
+        <v>Lecrae</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/papa-roach/3445763</v>
+        <v>https://music.apple.com/us/artist/lecrae/130043072</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/wake-up-calling/1862338148</v>
+        <v>https://music.apple.com/us/album/living-water/1871564892</v>
       </c>
       <c r="L137" t="str">
-        <v>Wake Up Calling - Papa Roach</v>
+        <v>Living Water - Lecrae</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>HIGH</v>
+        <v>What It Feels Like (feat. Daya)</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/high/1867202644</v>
+        <v>https://music.apple.com/us/song/what-it-feels-like-feat-daya/1870886919</v>
       </c>
       <c r="D138" t="str">
         <v>2026-02-06</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>NIGHTS AFTER VAMP</v>
+        <v>What It Feels Like (feat. Daya) - Single</v>
       </c>
       <c r="G138" t="str">
-        <v>3:23</v>
+        <v>2:18</v>
       </c>
       <c r="H138" t="str">
-        <v>Magnolia Park</v>
+        <v>Dillon Francis</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/magnolia-park/1413545983</v>
+        <v>https://music.apple.com/us/artist/dillon-francis/366828522</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/high/1867202638</v>
+        <v>https://music.apple.com/us/album/what-it-feels-like-feat-daya/1870886918</v>
       </c>
       <c r="L138" t="str">
-        <v>HIGH - Magnolia Park</v>
+        <v>What It Feels Like (feat. Daya) - Dillon Francis</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Villain</v>
+        <v>neck</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/villain/1860126455</v>
+        <v>https://music.apple.com/us/song/neck/1866953832</v>
       </c>
       <c r="D139" t="str">
         <v>2026-02-06</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>Reflections</v>
+        <v>neck - Single</v>
       </c>
       <c r="G139" t="str">
-        <v>3:53</v>
+        <v>3:40</v>
       </c>
       <c r="H139" t="str">
-        <v>From Ashes to New</v>
+        <v>Mau P</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/from-ashes-to-new/688645097</v>
+        <v>https://music.apple.com/us/artist/mau-p/1636676418</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/villain/1860126452</v>
+        <v>https://music.apple.com/us/album/neck/1866953831</v>
       </c>
       <c r="L139" t="str">
-        <v>Villain - From Ashes to New</v>
+        <v>neck - Mau P</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Bad Idea Right?</v>
+        <v>Colorblind</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/bad-idea-right/1869792549</v>
+        <v>https://music.apple.com/us/song/colorblind/1873445412</v>
       </c>
       <c r="D140" t="str">
         <v>2026-02-06</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Bridgerton Season Four (Covers from the Netflix Series – Pt. 1) - EP</v>
+        <v>Colorblind - Single</v>
       </c>
       <c r="G140" t="str">
-        <v>3:00</v>
+        <v>2:56</v>
       </c>
       <c r="H140" t="str">
-        <v>Caleb Chan</v>
+        <v>Gavin Adcock</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/caleb-chan/1441662972</v>
+        <v>https://music.apple.com/us/artist/gavin-adcock/1580645019</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/bad-idea-right/1869792542</v>
+        <v>https://music.apple.com/us/album/colorblind/1873445402</v>
       </c>
       <c r="L140" t="str">
-        <v>Bad Idea Right? - Caleb Chan</v>
+        <v>Colorblind - Gavin Adcock</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Residue</v>
+        <v>Au Revoir Reservoir</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/residue/1863786787</v>
+        <v>https://music.apple.com/us/song/au-revoir-reservoir/1847573922</v>
       </c>
       <c r="D141" t="str">
         <v>2026-02-06</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>The Moment (The Score)</v>
+        <v>Tenterhooks</v>
       </c>
       <c r="G141" t="str">
-        <v>3:28</v>
+        <v>3:21</v>
       </c>
       <c r="H141" t="str">
-        <v>A. G. Cook</v>
+        <v>Silversun Pickups</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/a-g-cook/744253464</v>
+        <v>https://music.apple.com/us/artist/silversun-pickups/74752665</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/residue/1863786786</v>
+        <v>https://music.apple.com/us/album/au-revoir-reservoir/1847573918</v>
       </c>
       <c r="L141" t="str">
-        <v>Residue - A. G. Cook</v>
+        <v>Au Revoir Reservoir - Silversun Pickups</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>I Used to Go to This Bar</v>
+        <v>Flavorless</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/i-used-to-go-to-this-bar/1839918872</v>
+        <v>https://music.apple.com/us/song/flavorless/1870741358</v>
       </c>
       <c r="D142" t="str">
         <v>2026-02-06</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>I Used to Go to This Bar</v>
+        <v>Flavorless - Single</v>
       </c>
       <c r="G142" t="str">
-        <v>2:12</v>
+        <v>3:31</v>
       </c>
       <c r="H142" t="str">
-        <v>Joyce Manor</v>
+        <v>Dexter and The Moonrocks</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/joyce-manor/408598559</v>
+        <v>https://music.apple.com/us/artist/dexter-and-the-moonrocks/1581657500</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/i-used-to-go-to-this-bar/1839918836</v>
+        <v>https://music.apple.com/us/album/flavorless/1870741357</v>
       </c>
       <c r="L142" t="str">
-        <v>I Used to Go to This Bar - Joyce Manor</v>
+        <v>Flavorless - Dexter and The Moonrocks</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Starlight</v>
+        <v>Nunca</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/starlight/1870989674</v>
+        <v>https://music.apple.com/us/song/nunca/1860691713</v>
       </c>
       <c r="D143" t="str">
         <v>2026-02-06</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>Everything Glows</v>
+        <v>ESCENAS</v>
       </c>
       <c r="G143" t="str">
-        <v>3:21</v>
+        <v>3:05</v>
       </c>
       <c r="H143" t="str">
-        <v>Cannons</v>
+        <v>Sin Bandera</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/cannons/65568551</v>
+        <v>https://music.apple.com/us/artist/sin-bandera/14483319</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/starlight/1870989672</v>
+        <v>https://music.apple.com/us/album/nunca/1860691704</v>
       </c>
       <c r="L143" t="str">
-        <v>Starlight - Cannons</v>
+        <v>Nunca - Sin Bandera</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Dandelion</v>
+        <v>Just In Case</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/dandelion/1863154133</v>
+        <v>https://music.apple.com/us/song/just-in-case/1867548367</v>
       </c>
       <c r="D144" t="str">
         <v>2026-02-06</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Corporate Pudding - EP</v>
+        <v>NO HArD FEELINGS (Deluxe)</v>
       </c>
       <c r="G144" t="str">
-        <v>3:14</v>
+        <v>1:45</v>
       </c>
       <c r="H144" t="str">
-        <v>Dogpark</v>
+        <v>Marc E. Bassy</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/dogpark/1710263796</v>
+        <v>https://music.apple.com/us/artist/marc-e-bassy/899254194</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/dandelion/1863154124</v>
+        <v>https://music.apple.com/us/album/just-in-case/1867547944</v>
       </c>
       <c r="L144" t="str">
-        <v>Dandelion - Dogpark</v>
+        <v>Just In Case - Marc E. Bassy</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>THEMSELVES</v>
+        <v>Thinking of You</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/themselves/1845287173</v>
+        <v>https://music.apple.com/us/song/thinking-of-you/1874128053</v>
       </c>
       <c r="D145" t="str">
         <v>2026-02-06</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>BACKWARD</v>
+        <v>Thinking of You - Single</v>
       </c>
       <c r="G145" t="str">
-        <v>2:46</v>
+        <v>3:00</v>
       </c>
       <c r="H145" t="str">
-        <v>Jordan Ward</v>
+        <v>AP Dhillon</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/jordan-ward/689602960</v>
+        <v>https://music.apple.com/us/artist/ap-dhillon/1484701109</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/themselves/1845286980</v>
+        <v>https://music.apple.com/us/album/thinking-of-you/1874128049</v>
       </c>
       <c r="L145" t="str">
-        <v>THEMSELVES - Jordan Ward</v>
+        <v>Thinking of You - AP Dhillon</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>High Maintenance</v>
+        <v>House Of Cards</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/high-maintenance/1872497656</v>
+        <v>https://music.apple.com/us/song/house-of-cards/1871562986</v>
       </c>
       <c r="D146" t="str">
         <v>2026-02-06</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>Miracle Mile</v>
+        <v>House of Cards</v>
       </c>
       <c r="G146" t="str">
-        <v>2:24</v>
+        <v>3:26</v>
       </c>
       <c r="H146" t="str">
-        <v>Paul Russell</v>
+        <v>The Amity Affliction</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/paul-russell/1304377463</v>
+        <v>https://music.apple.com/us/artist/the-amity-affliction/449513466</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/high-maintenance/1872496993</v>
+        <v>https://music.apple.com/us/album/house-of-cards/1871562765</v>
       </c>
       <c r="L146" t="str">
-        <v>High Maintenance - Paul Russell</v>
+        <v>House Of Cards - The Amity Affliction</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Trackhawk</v>
+        <v>Stay With Me</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/trackhawk/1860991724</v>
+        <v>https://music.apple.com/us/song/stay-with-me/1867490493</v>
       </c>
       <c r="D147" t="str">
         <v>2026-02-06</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Da Realest</v>
+        <v>Stay With Me - Single</v>
       </c>
       <c r="G147" t="str">
-        <v>1:59</v>
+        <v>3:21</v>
       </c>
       <c r="H147" t="str">
-        <v>Babyfxce E</v>
+        <v>Agents Of Time</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/babyfxce-e/1573432856</v>
+        <v>https://music.apple.com/us/artist/agents-of-time/794971951</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/trackhawk/1860991661</v>
+        <v>https://music.apple.com/us/album/stay-with-me/1867490492</v>
       </c>
       <c r="L147" t="str">
-        <v>Trackhawk - Babyfxce E</v>
+        <v>Stay With Me - Agents Of Time</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Wheel Man</v>
+        <v>I had a dream...</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/wheel-man/1872178895</v>
+        <v>https://music.apple.com/us/song/i-had-a-dream/1870971554</v>
       </c>
       <c r="D148" t="str">
         <v>2026-02-06</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Xavier</v>
+        <v>Dream inside a dream…</v>
       </c>
       <c r="G148" t="str">
-        <v>3:05</v>
+        <v>2:39</v>
       </c>
       <c r="H148" t="str">
-        <v>xaviersobased</v>
+        <v>R3HAB</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/xaviersobased/1540848340</v>
+        <v>https://music.apple.com/us/artist/r3hab/331900515</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/wheel-man/1872178596</v>
+        <v>https://music.apple.com/us/album/i-had-a-dream/1870971550</v>
       </c>
       <c r="L148" t="str">
-        <v>Wheel Man - xaviersobased</v>
+        <v>I had a dream... - R3HAB</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Natural Disaster</v>
+        <v>Back to You</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/natural-disaster/1871263211</v>
+        <v>https://music.apple.com/us/song/back-to-you/1855725165</v>
       </c>
       <c r="D149" t="str">
         <v>2026-02-06</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>Natural Disaster - Single</v>
+        <v>Satellite</v>
       </c>
       <c r="G149" t="str">
-        <v>3:02</v>
+        <v>3:10</v>
       </c>
       <c r="H149" t="str">
-        <v>Lauren Spencer Smith</v>
+        <v>Charlotte Sands</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/lauren-spencer-smith/1462708784</v>
+        <v>https://music.apple.com/us/artist/charlotte-sands/1444713487</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/natural-disaster/1871263207</v>
+        <v>https://music.apple.com/us/album/back-to-you/1855724765</v>
       </c>
       <c r="L149" t="str">
-        <v>Natural Disaster - Lauren Spencer Smith</v>
+        <v>Back to You - Charlotte Sands</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Prettier</v>
+        <v>rager</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/prettier/1869745409</v>
+        <v>https://music.apple.com/us/song/rager/1872808801</v>
       </c>
       <c r="D150" t="str">
         <v>2026-02-06</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>Prettier - Single</v>
+        <v>rager</v>
       </c>
       <c r="G150" t="str">
-        <v>2:34</v>
+        <v>2:48</v>
       </c>
       <c r="H150" t="str">
-        <v>Grace VanderWaal</v>
+        <v>Blusher</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/grace-vanderwaal/1175539534</v>
+        <v>https://music.apple.com/us/artist/blusher/485578161</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/prettier/1869745403</v>
+        <v>https://music.apple.com/us/album/rager/1872808800</v>
       </c>
       <c r="L150" t="str">
-        <v>Prettier - Grace VanderWaal</v>
+        <v>rager - Blusher</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Shotta Flow 8</v>
+        <v>If Only</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/shotta-flow-8/1872760524</v>
+        <v>https://music.apple.com/us/song/if-only/1870281318</v>
       </c>
       <c r="D151" t="str">
         <v>2026-02-06</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>Shotta Flow 8 - Single</v>
+        <v>Patchwork</v>
       </c>
       <c r="G151" t="str">
-        <v>3:21</v>
+        <v>3:28</v>
       </c>
       <c r="H151" t="str">
-        <v>NLE Choppa</v>
+        <v>Charlotte Day Wilson</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/nle-choppa/1449052753</v>
+        <v>https://music.apple.com/us/artist/charlotte-day-wilson/1053594538</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/shotta-flow-8/1872760520</v>
+        <v>https://music.apple.com/us/album/if-only/1870281314</v>
       </c>
       <c r="L151" t="str">
-        <v>Shotta Flow 8 - NLE Choppa</v>
+        <v>If Only - Charlotte Day Wilson</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Die To Fall</v>
+        <v>DON'T LOVE ME</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/die-to-fall/1866902681</v>
+        <v>https://music.apple.com/us/song/dont-love-me/1873153612</v>
       </c>
       <c r="D152" t="str">
         <v>2026-02-06</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>Die To Fall - Single</v>
+        <v>DON'T LOVE ME - Single</v>
       </c>
       <c r="G152" t="str">
-        <v>3:20</v>
+        <v>3:01</v>
       </c>
       <c r="H152" t="str">
-        <v>The Maine</v>
+        <v>Omah Lay</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
+        <v>https://music.apple.com/us/artist/omah-lay/1459319359</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/die-to-fall/1866902679</v>
+        <v>https://music.apple.com/us/album/dont-love-me/1873153611</v>
       </c>
       <c r="L152" t="str">
-        <v>Die To Fall - The Maine</v>
+        <v>DON'T LOVE ME - Omah Lay</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>The Cruel Angel's Thesis (Neon Genesis Evangelion)</v>
+        <v>No Sikes, No Tradesies</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/the-cruel-angels-thesis-neon-genesis-evangelion/1864932139</v>
+        <v>https://music.apple.com/us/song/no-sikes-no-tradesies/1871576137</v>
       </c>
       <c r="D153" t="str">
         <v>2026-02-06</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>The Cruel Angel's Thesis (Neon Genesis Evangelion) - Single</v>
+        <v>Sweet Nothings</v>
       </c>
       <c r="G153" t="str">
-        <v>2:58</v>
+        <v>2:32</v>
       </c>
       <c r="H153" t="str">
-        <v>Steve Aoki</v>
+        <v>Jaymin</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/steve-aoki/271066694</v>
+        <v>https://music.apple.com/us/artist/jaymin/1821260030</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/the-cruel-angels-thesis-neon-genesis-evangelion/1864932135</v>
+        <v>https://music.apple.com/us/album/no-sikes-no-tradesies/1871576102</v>
       </c>
       <c r="L153" t="str">
-        <v>The Cruel Angel's Thesis (Neon Genesis Evangelion) - Steve Aoki</v>
+        <v>No Sikes, No Tradesies - Jaymin</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Slow Burn</v>
+        <v>you woke me up</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/slow-burn/1851033862</v>
+        <v>https://music.apple.com/us/song/you-woke-me-up/1873402923</v>
       </c>
       <c r="D154" t="str">
         <v>2026-02-06</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>Still There’s a Glow</v>
+        <v>you woke me up - Single</v>
       </c>
       <c r="G154" t="str">
-        <v>2:14</v>
+        <v>3:14</v>
       </c>
       <c r="H154" t="str">
-        <v>Sweet Pill</v>
+        <v>Kevian Kraemer</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/sweet-pill/1459476044</v>
+        <v>https://music.apple.com/us/artist/kevian-kraemer/1594747842</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/slow-burn/1851033857</v>
+        <v>https://music.apple.com/us/album/you-woke-me-up/1873402690</v>
       </c>
       <c r="L154" t="str">
-        <v>Slow Burn - Sweet Pill</v>
+        <v>you woke me up - Kevian Kraemer</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Too Late</v>
+        <v>No One’s Business</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/too-late/1857999860</v>
+        <v>https://music.apple.com/us/song/no-ones-business/1873059628</v>
       </c>
       <c r="D155" t="str">
         <v>2026-02-06</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>Evergreen</v>
+        <v>No One’s Business - Single</v>
       </c>
       <c r="G155" t="str">
-        <v>2:56</v>
+        <v>3:00</v>
       </c>
       <c r="H155" t="str">
-        <v>Hunter Hayes</v>
+        <v>Alicia Creti</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/hunter-hayes/429231434</v>
+        <v>https://music.apple.com/us/artist/alicia-creti/1593954404</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/too-late/1857999850</v>
+        <v>https://music.apple.com/us/album/no-ones-business/1873059626</v>
       </c>
       <c r="L155" t="str">
-        <v>Too Late - Hunter Hayes</v>
+        <v>No One’s Business - Alicia Creti</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Mono (feat. skaiwater)</v>
+        <v>Don’t Dream It’s Over (From The Movie “GOAT”)</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/mono-feat-skaiwater/1869130804</v>
+        <v>https://music.apple.com/us/song/dont-dream-its-over-from-the-movie-goat/1870623627</v>
       </c>
       <c r="D156" t="str">
         <v>2026-02-06</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>Mono (feat. skaiwater) - Single</v>
+        <v>GOAT (Original Motion Picture Soundtrack)</v>
       </c>
       <c r="G156" t="str">
-        <v>2:50</v>
+        <v>3:13</v>
       </c>
       <c r="H156" t="str">
-        <v>i-dle</v>
+        <v>Bryant Barnes</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/i-dle/1378887586</v>
+        <v>https://music.apple.com/us/artist/bryant-barnes/1579668433</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/mono-feat-skaiwater/1869130801</v>
+        <v>https://music.apple.com/us/album/dont-dream-its-over-from-the-movie-goat/1870623290</v>
       </c>
       <c r="L156" t="str">
-        <v>Mono (feat. skaiwater) - i-dle</v>
+        <v>Don’t Dream It’s Over (From The Movie “GOAT”) - Bryant Barnes</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Thank You Is Enough</v>
+        <v>TWICE</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/thank-you-is-enough/1870679042</v>
+        <v>https://music.apple.com/us/song/twice/1871578107</v>
       </c>
       <c r="D157" t="str">
         <v>2026-02-06</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>Yo Gabba GabbaLand! (Season 2) [Apple TV+ Original Series Soundtrack]</v>
+        <v>KINDA HARD</v>
       </c>
       <c r="G157" t="str">
-        <v>1:55</v>
+        <v>3:44</v>
       </c>
       <c r="H157" t="str">
-        <v>Yo Gabba Gabba</v>
+        <v>Bilmuri</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/yo-gabba-gabba/433108373</v>
+        <v>https://music.apple.com/us/artist/bilmuri/1072442999</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/thank-you-is-enough/1870678950</v>
+        <v>https://music.apple.com/us/album/twice/1871578103</v>
       </c>
       <c r="L157" t="str">
-        <v>Thank You Is Enough - Yo Gabba Gabba</v>
+        <v>TWICE - Bilmuri</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>RIDIN</v>
+        <v>ROOFTOP</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/ridin/1869786726</v>
+        <v>https://music.apple.com/us/song/rooftop/1872534292</v>
       </c>
       <c r="D158" t="str">
         <v>2026-02-06</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>RIDIN - Single</v>
+        <v>ROOFTOP - Single</v>
       </c>
       <c r="G158" t="str">
-        <v>2:00</v>
+        <v>3:22</v>
       </c>
       <c r="H158" t="str">
-        <v>Tokischa</v>
+        <v>Hulvey</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/tokischa/1414103446</v>
+        <v>https://music.apple.com/us/artist/hulvey/1438377315</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/ridin/1869786725</v>
+        <v>https://music.apple.com/us/album/rooftop/1872534291</v>
       </c>
       <c r="L158" t="str">
-        <v>RIDIN - Tokischa</v>
+        <v>ROOFTOP - Hulvey</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>POSSESSION</v>
+        <v>Louisiana Rain</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/possession/1872536200</v>
+        <v>https://music.apple.com/us/song/louisiana-rain/1867848946</v>
       </c>
       <c r="D159" t="str">
         <v>2026-02-06</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>POSSESSION - Single</v>
+        <v>Louisiana Rain - Single</v>
       </c>
       <c r="G159" t="str">
-        <v>3:07</v>
+        <v>3:41</v>
       </c>
       <c r="H159" t="str">
-        <v>Melanie Martinez</v>
+        <v>Hunter Plake</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/melanie-martinez/993014053</v>
+        <v>https://music.apple.com/us/artist/hunter-plake/1213481439</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/possession/1872536199</v>
+        <v>https://music.apple.com/us/album/louisiana-rain/1867848936</v>
       </c>
       <c r="L159" t="str">
-        <v>POSSESSION - Melanie Martinez</v>
+        <v>Louisiana Rain - Hunter Plake</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Poema</v>
+        <v>sharing Jesus with an ex</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/poema/1872723644</v>
+        <v>https://music.apple.com/us/song/sharing-jesus-with-an-ex/1870912832</v>
       </c>
       <c r="D160" t="str">
         <v>2026-02-06</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>Poema - Single</v>
+        <v>sharing Jesus with an ex - Single</v>
       </c>
       <c r="G160" t="str">
-        <v>3:14</v>
+        <v>1:55</v>
       </c>
       <c r="H160" t="str">
-        <v>Óscar Maydon</v>
+        <v>Zoe Levert</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/%C3%B3scar-maydon/1524147696</v>
+        <v>https://music.apple.com/us/artist/zoe-levert/1845343641</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/poema/1872723468</v>
+        <v>https://music.apple.com/us/album/sharing-jesus-with-an-ex/1870912828</v>
       </c>
       <c r="L160" t="str">
-        <v>Poema - Óscar Maydon</v>
+        <v>sharing Jesus with an ex - Zoe Levert</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Live Without</v>
+        <v>Body Control (feat. CHILLS)</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/live-without/1862777625</v>
+        <v>https://music.apple.com/us/song/body-control-feat-chills/1867947671</v>
       </c>
       <c r="D161" t="str">
         <v>2026-02-06</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>WORRIED SICK (Deluxe Edition)</v>
+        <v>Body Control (feat. CHILLS) - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>2:55</v>
+        <v>3:21</v>
       </c>
       <c r="H161" t="str">
-        <v>Meet Me @ The Altar</v>
+        <v>Cole Knight</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/meet-me-the-altar/1109900880</v>
+        <v>https://music.apple.com/us/artist/cole-knight/589962652</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/live-without/1862777608</v>
+        <v>https://music.apple.com/us/album/body-control-feat-chills/1867947668</v>
       </c>
       <c r="L161" t="str">
-        <v>Live Without - Meet Me @ The Altar</v>
+        <v>Body Control (feat. CHILLS) - Cole Knight</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>FANÁTICO</v>
+        <v>A Prayer for the Dancefloor (feat. Conduit)</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/fan%C3%A1tico/1871611852</v>
+        <v>https://music.apple.com/us/song/a-prayer-for-the-dancefloor-feat-conduit/1869372836</v>
       </c>
       <c r="D162" t="str">
         <v>2026-02-06</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>FANÁTICO - Single</v>
+        <v>A Prayer for the Dancefloor - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>3:55</v>
+        <v>6:54</v>
       </c>
       <c r="H162" t="str">
-        <v>Blessd</v>
+        <v>Charlotte de Witte</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/blessd/1481245915</v>
+        <v>https://music.apple.com/us/artist/charlotte-de-witte/768227318</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/fan%C3%A1tico/1871611851</v>
+        <v>https://music.apple.com/us/album/a-prayer-for-the-dancefloor-feat-conduit/1869372833</v>
       </c>
       <c r="L162" t="str">
-        <v>FANÁTICO - Blessd</v>
+        <v>A Prayer for the Dancefloor (feat. Conduit) - Charlotte de Witte</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Frozen Lake</v>
+        <v>Realm of Endless Misery</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/frozen-lake/1867287070</v>
+        <v>https://music.apple.com/us/song/realm-of-endless-misery/1846578506</v>
       </c>
       <c r="D163" t="str">
         <v>2026-02-06</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>Frozen Lake - Single</v>
+        <v>Liturgy of Death</v>
       </c>
       <c r="G163" t="str">
-        <v>3:29</v>
+        <v>4:56</v>
       </c>
       <c r="H163" t="str">
-        <v>VOILÀ</v>
+        <v>Mayhem</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/voil%C3%A0/1333272109</v>
+        <v>https://music.apple.com/us/artist/mayhem/48820563</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/frozen-lake/1867287069</v>
+        <v>https://music.apple.com/us/album/realm-of-endless-misery/1846578494</v>
       </c>
       <c r="L163" t="str">
-        <v>Frozen Lake - VOILÀ</v>
+        <v>Realm of Endless Misery - Mayhem</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Fine Shyt (EB Remix) [feat. Eric Bellinger]</v>
+        <v>BLEACH</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/fine-shyt-eb-remix-feat-eric-bellinger/1870964385</v>
+        <v>https://music.apple.com/us/song/bleach/1869795882</v>
       </c>
       <c r="D164" t="str">
         <v>2026-02-06</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>Fine Shyt (EB Remix) [feat. Eric Bellinger] - Single</v>
+        <v>BLEACH - Single</v>
       </c>
       <c r="G164" t="str">
-        <v>2:45</v>
+        <v>2:28</v>
       </c>
       <c r="H164" t="str">
-        <v>VEDO</v>
+        <v>Ecca Vandal</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/vedo/267769510</v>
+        <v>https://music.apple.com/us/artist/ecca-vandal/878909173</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/fine-shyt-eb-remix-feat-eric-bellinger/1870964384</v>
+        <v>https://music.apple.com/us/album/bleach/1869795874</v>
       </c>
       <c r="L164" t="str">
-        <v>Fine Shyt (EB Remix) [feat. Eric Bellinger] - VEDO</v>
+        <v>BLEACH - Ecca Vandal</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Hell Yeah (Feat. Waxmaster)</v>
+        <v>pretty in pink</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/hell-yeah-feat-waxmaster/1866602820</v>
+        <v>https://music.apple.com/us/song/pretty-in-pink/1847771037</v>
       </c>
       <c r="D165" t="str">
         <v>2026-02-06</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>Hell Yeah (Feat. Waxmaster) - Single</v>
+        <v>AngelPink</v>
       </c>
       <c r="G165" t="str">
-        <v>3:32</v>
+        <v>3:13</v>
       </c>
       <c r="H165" t="str">
-        <v>Chris Lorenzo</v>
+        <v>Keni Titus</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/chris-lorenzo/621431022</v>
+        <v>https://music.apple.com/us/artist/keni-titus/1686236534</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/hell-yeah-feat-waxmaster/1866602819</v>
+        <v>https://music.apple.com/us/album/pretty-in-pink/1847770544</v>
       </c>
       <c r="L165" t="str">
-        <v>Hell Yeah (Feat. Waxmaster) - Chris Lorenzo</v>
+        <v>pretty in pink - Keni Titus</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>It’s Like That</v>
+        <v>Pickup Man</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/its-like-that/1858689757</v>
+        <v>https://music.apple.com/us/song/pickup-man/1870883995</v>
       </c>
       <c r="D166" t="str">
         <v>2026-02-06</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>A Pound of Feathers</v>
+        <v>Pickup Man - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>3:20</v>
+        <v>3:28</v>
       </c>
       <c r="H166" t="str">
-        <v>The Black Crowes</v>
+        <v>Bayker Blankenship</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/the-black-crowes/2969371</v>
+        <v>https://music.apple.com/us/artist/bayker-blankenship/1700165686</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/its-like-that/1858689485</v>
+        <v>https://music.apple.com/us/album/pickup-man/1870883994</v>
       </c>
       <c r="L166" t="str">
-        <v>It’s Like That - The Black Crowes</v>
+        <v>Pickup Man - Bayker Blankenship</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>A.S.A.P.</v>
+        <v>Get To Drinkin'</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/a-s-a-p/1833414737</v>
+        <v>https://music.apple.com/us/song/get-to-drinkin/1871609753</v>
       </c>
       <c r="D167" t="str">
         <v>2026-02-06</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>A.S.A.P. - Single</v>
+        <v>Get To Drinkin' - Single</v>
       </c>
       <c r="G167" t="str">
         <v>2:48</v>
       </c>
       <c r="H167" t="str">
-        <v>Mýa</v>
+        <v>Zach John King</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/m%C3%BDa/108751</v>
+        <v>https://music.apple.com/us/artist/zach-john-king/1671037314</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/a-s-a-p/1833414736</v>
+        <v>https://music.apple.com/us/album/get-to-drinkin/1871609743</v>
       </c>
       <c r="L167" t="str">
-        <v>A.S.A.P. - Mýa</v>
+        <v>Get To Drinkin' - Zach John King</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Once I Say</v>
+        <v>The Roses</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/once-i-say/1867855025</v>
+        <v>https://music.apple.com/us/song/the-roses/1861042789</v>
       </c>
       <c r="D168" t="str">
         <v>2026-02-06</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>PASSION</v>
+        <v>The Roses - Single</v>
       </c>
       <c r="G168" t="str">
-        <v>3:21</v>
+        <v>3:02</v>
       </c>
       <c r="H168" t="str">
-        <v>Terrace Martin</v>
+        <v>Russell Dickerson</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/terrace-martin/27522754</v>
+        <v>https://music.apple.com/us/artist/russell-dickerson/415673786</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/once-i-say/1867854756</v>
+        <v>https://music.apple.com/us/album/the-roses/1861042786</v>
       </c>
       <c r="L168" t="str">
-        <v>Once I Say - Terrace Martin</v>
+        <v>The Roses - Russell Dickerson</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>believer</v>
+        <v>I Should Know Better</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/believer/1862797080</v>
+        <v>https://music.apple.com/us/song/i-should-know-better/1867929284</v>
       </c>
       <c r="D169" t="str">
         <v>2026-02-06</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>believer - Single</v>
+        <v>Under The Streetlights</v>
       </c>
       <c r="G169" t="str">
-        <v>2:57</v>
+        <v>3:33</v>
       </c>
       <c r="H169" t="str">
-        <v>Yuna</v>
+        <v>Michael Marcagi</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/yuna/423966062</v>
+        <v>https://music.apple.com/us/artist/michael-marcagi/1524265962</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/believer/1862796978</v>
+        <v>https://music.apple.com/us/album/i-should-know-better/1867929277</v>
       </c>
       <c r="L169" t="str">
-        <v>believer - Yuna</v>
+        <v>I Should Know Better - Michael Marcagi</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>I Envy The Wind</v>
+        <v>Never Do</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/i-envy-the-wind/1863202477</v>
+        <v>https://music.apple.com/us/song/never-do/1872842226</v>
       </c>
       <c r="D170" t="str">
         <v>2026-02-06</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>I Envy The Wind - Single</v>
+        <v>Never Do - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>3:51</v>
+        <v>1:58</v>
       </c>
       <c r="H170" t="str">
-        <v>Molly Parden</v>
+        <v>charlieonnafriday</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/molly-parden/374789677</v>
+        <v>https://music.apple.com/us/artist/charlieonnafriday/1525971355</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/i-envy-the-wind/1863202476</v>
+        <v>https://music.apple.com/us/album/never-do/1872842225</v>
       </c>
       <c r="L170" t="str">
-        <v>I Envy The Wind - Molly Parden</v>
+        <v>Never Do - charlieonnafriday</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>The Alchemist</v>
+        <v>Primary Colors</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/the-alchemist/1831827347</v>
+        <v>https://music.apple.com/us/song/primary-colors/1858041089</v>
       </c>
       <c r="D171" t="str">
         <v>2026-02-06</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>The Alchemist</v>
+        <v>Lost on You</v>
       </c>
       <c r="G171" t="str">
-        <v>3:13</v>
+        <v>3:37</v>
       </c>
       <c r="H171" t="str">
-        <v>Bre Kennedy</v>
+        <v>Tigers Jaw</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/bre-kennedy/1242283415</v>
+        <v>https://music.apple.com/us/artist/tigers-jaw/266702551</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/the-alchemist/1831827332</v>
+        <v>https://music.apple.com/us/album/primary-colors/1858041075</v>
       </c>
       <c r="L171" t="str">
-        <v>The Alchemist - Bre Kennedy</v>
+        <v>Primary Colors - Tigers Jaw</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Daysa</v>
+        <v>Rock Bottom</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/daysa/1861575845</v>
+        <v>https://music.apple.com/us/song/rock-bottom/1871165476</v>
       </c>
       <c r="D172" t="str">
         <v>2026-02-06</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Daysa - Single</v>
+        <v>Rock Bottom / Octopus - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>4:36</v>
+        <v>4:10</v>
       </c>
       <c r="H172" t="str">
-        <v>⌭ IceMorph ⌬</v>
+        <v>King Krule</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/icemorph/1733236411</v>
+        <v>https://music.apple.com/us/artist/king-krule/474544289</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/daysa/1861575844</v>
+        <v>https://music.apple.com/us/album/rock-bottom/1871165475</v>
       </c>
       <c r="L172" t="str">
-        <v>Daysa - ⌭ IceMorph ⌬</v>
+        <v>Rock Bottom - King Krule</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Fabulous</v>
+        <v>Te Dedico</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/fabulous/1862804005</v>
+        <v>https://music.apple.com/us/song/te-dedico/1873127022</v>
       </c>
       <c r="D173" t="str">
         <v>2026-02-06</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Fabulous - Single</v>
+        <v>Te Dedico - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>2:33</v>
+        <v>3:45</v>
       </c>
       <c r="H173" t="str">
-        <v>MEEK</v>
+        <v>Carlos Vives</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/meek/1784432868</v>
+        <v>https://music.apple.com/us/artist/carlos-vives/554369</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/fabulous/1862804004</v>
+        <v>https://music.apple.com/us/album/te-dedico/1873126777</v>
       </c>
       <c r="L173" t="str">
-        <v>Fabulous - MEEK</v>
+        <v>Te Dedico - Carlos Vives</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Me Asusta Amar Tanto la Soledad</v>
+        <v>AUNQUE SEA EN DOS</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/me-asusta-amar-tanto-la-soledad/1866982109</v>
+        <v>https://music.apple.com/us/song/aunque-sea-en-dos/1867536534</v>
       </c>
       <c r="D174" t="str">
         <v>2026-02-06</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>Me Asusta Amar Tanto la Soledad - Single</v>
+        <v>18</v>
       </c>
       <c r="G174" t="str">
-        <v>3:22</v>
+        <v>2:38</v>
       </c>
       <c r="H174" t="str">
-        <v>RUBIO</v>
+        <v>Conexión Divina</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/rubio/34747724</v>
+        <v>https://music.apple.com/us/artist/conexi%C3%B3n-divina/1641945707</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/me-asusta-amar-tanto-la-soledad/1866981907</v>
+        <v>https://music.apple.com/us/album/aunque-sea-en-dos/1867536522</v>
       </c>
       <c r="L174" t="str">
-        <v>Me Asusta Amar Tanto la Soledad - RUBIO</v>
+        <v>AUNQUE SEA EN DOS - Conexión Divina</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>brainchem</v>
+        <v>I Dare You</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/brainchem/1870656942</v>
+        <v>https://music.apple.com/us/song/i-dare-you/1866987593</v>
       </c>
       <c r="D175" t="str">
         <v>2026-02-06</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>brainchem - Single</v>
+        <v>I Dare You - Single</v>
       </c>
       <c r="G175" t="str">
-        <v>2:28</v>
+        <v>3:25</v>
       </c>
       <c r="H175" t="str">
-        <v>EMJAY</v>
+        <v>Dylan Dunlap</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/emjay/1517993423</v>
+        <v>https://music.apple.com/us/artist/dylan-dunlap/366488583</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/brainchem/1870656608</v>
+        <v>https://music.apple.com/us/album/i-dare-you/1866987592</v>
       </c>
       <c r="L175" t="str">
-        <v>brainchem - EMJAY</v>
+        <v>I Dare You - Dylan Dunlap</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Boyfriend In Yo Brain (Notice Me)</v>
+        <v>new irish boyfriend</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/boyfriend-in-yo-brain-notice-me/1871675026</v>
+        <v>https://music.apple.com/us/song/new-irish-boyfriend/1849476917</v>
       </c>
       <c r="D176" t="str">
         <v>2026-02-06</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>With No Due Respect</v>
+        <v>long time caller, first time listener</v>
       </c>
       <c r="G176" t="str">
-        <v>2:48</v>
+        <v>3:50</v>
       </c>
       <c r="H176" t="str">
-        <v>Foggieraw</v>
+        <v>vegas water taxi</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/foggieraw/1152021457</v>
+        <v>https://music.apple.com/us/artist/vegas-water-taxi/1717868617</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/boyfriend-in-yo-brain-notice-me/1871675010</v>
+        <v>https://music.apple.com/us/album/new-irish-boyfriend/1849476535</v>
       </c>
       <c r="L176" t="str">
-        <v>Boyfriend In Yo Brain (Notice Me) - Foggieraw</v>
+        <v>new irish boyfriend - vegas water taxi</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Giants</v>
+        <v>Everyone Around Me Dancing</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/giants/1869154957</v>
+        <v>https://music.apple.com/us/song/everyone-around-me-dancing/1869047384</v>
       </c>
       <c r="D177" t="str">
         <v>2026-02-06</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Giants - Single</v>
+        <v>Singing</v>
       </c>
       <c r="G177" t="str">
-        <v>3:12</v>
+        <v>3:05</v>
       </c>
       <c r="H177" t="str">
-        <v>Picture This</v>
+        <v>Gia Margaret</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/picture-this/1194282721</v>
+        <v>https://music.apple.com/us/artist/gia-margaret/1460162196</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/giants/1869154821</v>
+        <v>https://music.apple.com/us/album/everyone-around-me-dancing/1869047383</v>
       </c>
       <c r="L177" t="str">
-        <v>Giants - Picture This</v>
+        <v>Everyone Around Me Dancing - Gia Margaret</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Scooby</v>
+        <v>Good Enough (feat. Julie Doiron)</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/scooby/1872510752</v>
+        <v>https://music.apple.com/us/song/good-enough-feat-julie-doiron/1867375846</v>
       </c>
       <c r="D178" t="str">
         <v>2026-02-06</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Scooby - Single</v>
+        <v>Big Changes</v>
       </c>
       <c r="G178" t="str">
-        <v>3:41</v>
+        <v>6:05</v>
       </c>
       <c r="H178" t="str">
-        <v>corook</v>
+        <v>Status/Non-Status</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/corook/1514463762</v>
+        <v>https://music.apple.com/us/artist/status-non-status/1205477155</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/scooby/1872510751</v>
+        <v>https://music.apple.com/us/album/good-enough-feat-julie-doiron/1867375733</v>
       </c>
       <c r="L178" t="str">
-        <v>Scooby - corook</v>
+        <v>Good Enough (feat. Julie Doiron) - Status/Non-Status</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>La Racha</v>
+        <v>Opal (feat. John Medeski, Jorge Roeder &amp; Kenny Wollesen)</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/la-racha/1868757762</v>
+        <v>https://music.apple.com/us/song/opal-feat-john-medeski-jorge-roeder-kenny-wollesen/1849593156</v>
       </c>
       <c r="D179" t="str">
         <v>2026-02-06</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>La Racha - Single</v>
+        <v>Scenes From Above (feat. John Medeski, Jorge Roeder &amp; Kenny Wollesen)</v>
       </c>
       <c r="G179" t="str">
-        <v>2:48</v>
+        <v>4:09</v>
       </c>
       <c r="H179" t="str">
-        <v>Hermanos Espinoza</v>
+        <v>Julian Lage</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/hermanos-espinoza/1613044599</v>
+        <v>https://music.apple.com/us/artist/julian-lage/6937093</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/la-racha/1868757747</v>
+        <v>https://music.apple.com/us/album/opal-feat-john-medeski-jorge-roeder-kenny-wollesen/1849593147</v>
       </c>
       <c r="L179" t="str">
-        <v>La Racha - Hermanos Espinoza</v>
+        <v>Opal (feat. John Medeski, Jorge Roeder &amp; Kenny Wollesen) - Julian Lage</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>So Am I</v>
+        <v>Thecuntiest</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/so-am-i/1867012209</v>
+        <v>https://music.apple.com/us/song/thecuntiest/1873623673</v>
       </c>
       <c r="D180" t="str">
         <v>2026-02-06</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Tell Me How You Really Feel</v>
+        <v>Thecuntiest - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>2:50</v>
+        <v>2:23</v>
       </c>
       <c r="H180" t="str">
-        <v>Katelyn Tarver</v>
+        <v>Spilata</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/katelyn-tarver/2356378</v>
+        <v>https://music.apple.com/us/artist/spilata/1734141692</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/so-am-i/1867012005</v>
+        <v>https://music.apple.com/us/album/thecuntiest/1873623672</v>
       </c>
       <c r="L180" t="str">
-        <v>So Am I - Katelyn Tarver</v>
+        <v>Thecuntiest - Spilata</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>best thing</v>
+        <v>Big Deal</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/best-thing/1860673616</v>
+        <v>https://music.apple.com/us/song/big-deal/1871607668</v>
       </c>
       <c r="D181" t="str">
         <v>2026-02-06</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>best thing - Single</v>
+        <v>Big Deal - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>4:27</v>
+        <v>3:47</v>
       </c>
       <c r="H181" t="str">
-        <v>WRABEL</v>
+        <v>In Color</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/wrabel/435072161</v>
+        <v>https://music.apple.com/us/artist/in-color/1788977129</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/best-thing/1860673615</v>
+        <v>https://music.apple.com/us/album/big-deal/1871607667</v>
       </c>
       <c r="L181" t="str">
-        <v>best thing - WRABEL</v>
+        <v>Big Deal - In Color</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Count It Back</v>
+        <v>Buy What U Want</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/count-it-back/1855219865</v>
+        <v>https://music.apple.com/us/song/buy-what-u-want/1872511530</v>
       </c>
       <c r="D182" t="str">
         <v>2026-02-06</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Magic Boy</v>
+        <v>Road To Osshland III - EP</v>
       </c>
       <c r="G182" t="str">
-        <v>2:52</v>
+        <v>3:47</v>
       </c>
       <c r="H182" t="str">
-        <v>Bartees Strange</v>
+        <v>Black Fortune</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/bartees-strange/1450776625</v>
+        <v>https://music.apple.com/us/artist/black-fortune/557044567</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/count-it-back/1855219618</v>
+        <v>https://music.apple.com/us/album/buy-what-u-want/1872511292</v>
       </c>
       <c r="L182" t="str">
-        <v>Count It Back - Bartees Strange</v>
+        <v>Buy What U Want - Black Fortune</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Good Girl</v>
+        <v>Common Ground</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/good-girl/1862640697</v>
+        <v>https://music.apple.com/us/song/common-ground/1852654933</v>
       </c>
       <c r="D183" t="str">
         <v>2026-02-06</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Good Girl - Single</v>
+        <v>Common Ground - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>4:23</v>
+        <v>1:42</v>
       </c>
       <c r="H183" t="str">
-        <v>Paris Paloma</v>
+        <v>ELIO</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/paris-paloma/1530898376</v>
+        <v>https://music.apple.com/us/artist/elio/1501417625</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/good-girl/1862640694</v>
+        <v>https://music.apple.com/us/album/common-ground/1852654920</v>
       </c>
       <c r="L183" t="str">
-        <v>Good Girl - Paris Paloma</v>
+        <v>Common Ground - ELIO</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>MY REVIVAL</v>
+        <v>Cellophane</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/my-revival/1869465104</v>
+        <v>https://music.apple.com/us/song/cellophane/1868833598</v>
       </c>
       <c r="D184" t="str">
         <v>2026-02-06</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>HEARTLAND (Deluxe Version)</v>
+        <v>Cellophane - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>3:34</v>
+        <v>4:21</v>
       </c>
       <c r="H184" t="str">
-        <v>MORGXN</v>
+        <v>Maddie Zahm</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/morgxn/1116360149</v>
+        <v>https://music.apple.com/us/artist/maddie-zahm/1397016641</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/my-revival/1869464853</v>
+        <v>https://music.apple.com/us/album/cellophane/1868833594</v>
       </c>
       <c r="L184" t="str">
-        <v>MY REVIVAL - MORGXN</v>
+        <v>Cellophane - Maddie Zahm</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Run My Way</v>
+        <v>96 Camry</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/run-my-way/1860964996</v>
+        <v>https://music.apple.com/us/song/96-camry/1867251408</v>
       </c>
       <c r="D185" t="str">
         <v>2026-02-06</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>Run My Way - Single</v>
+        <v>PRAY FOR ME</v>
       </c>
       <c r="G185" t="str">
-        <v>2:44</v>
+        <v>3:15</v>
       </c>
       <c r="H185" t="str">
-        <v>December 10</v>
+        <v>RAAHiiM</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/december-10/1414032285</v>
+        <v>https://music.apple.com/us/artist/raahiim/1539090681</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/run-my-way/1860964992</v>
+        <v>https://music.apple.com/us/album/96-camry/1867251391</v>
       </c>
       <c r="L185" t="str">
-        <v>Run My Way - December 10</v>
+        <v>96 Camry - RAAHiiM</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Cold Night</v>
+        <v>La Allstar</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/cold-night/1867687787</v>
+        <v>https://music.apple.com/us/song/la-allstar/1867796343</v>
       </c>
       <c r="D186" t="str">
         <v>2026-02-06</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Cold Night - Single</v>
+        <v>La Allstar - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>3:12</v>
+        <v>2:49</v>
       </c>
       <c r="H186" t="str">
-        <v>HANA</v>
+        <v>ELIKAI</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/hana/1792783458</v>
+        <v>https://music.apple.com/us/artist/elikai/1764453112</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/cold-night/1867687784</v>
+        <v>https://music.apple.com/us/album/la-allstar/1867796342</v>
       </c>
       <c r="L186" t="str">
-        <v>Cold Night - HANA</v>
+        <v>La Allstar - ELIKAI</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Away With The Fairies</v>
+        <v>Luka</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/away-with-the-fairies/1870603474</v>
+        <v>https://music.apple.com/us/song/luka/1869396162</v>
       </c>
       <c r="D187" t="str">
         <v>2026-02-06</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Away With The Fairies - Single</v>
+        <v>Luka - Single</v>
       </c>
       <c r="G187" t="str">
-        <v>2:28</v>
+        <v>2:07</v>
       </c>
       <c r="H187" t="str">
-        <v>LUNA</v>
+        <v>Fonta</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/luna/1439101807</v>
+        <v>https://music.apple.com/us/artist/fonta/1757885481</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/away-with-the-fairies/1870603470</v>
+        <v>https://music.apple.com/us/album/luka/1869396161</v>
       </c>
       <c r="L187" t="str">
-        <v>Away With The Fairies - LUNA</v>
+        <v>Luka - Fonta</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Fragile</v>
+        <v>Ganas De Tenerla</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/fragile/1866957569</v>
+        <v>https://music.apple.com/us/song/ganas-de-tenerla/1870909222</v>
       </c>
       <c r="D188" t="str">
         <v>2026-02-06</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Fragile - Single</v>
+        <v>Ganas De Tenerla - Single</v>
       </c>
       <c r="G188" t="str">
-        <v>3:10</v>
+        <v>3:06</v>
       </c>
       <c r="H188" t="str">
-        <v>Anajah</v>
+        <v>Silvestre Dangond</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/anajah/1355166756</v>
+        <v>https://music.apple.com/us/artist/silvestre-dangond/311205761</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/fragile/1866957565</v>
+        <v>https://music.apple.com/us/album/ganas-de-tenerla/1870909219</v>
       </c>
       <c r="L188" t="str">
-        <v>Fragile - Anajah</v>
+        <v>Ganas De Tenerla - Silvestre Dangond</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Slow Dancin'</v>
+        <v>In My Blue</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/slow-dancin/1871537173</v>
+        <v>https://music.apple.com/us/song/in-my-blue/1838571293</v>
       </c>
       <c r="D189" t="str">
         <v>2026-02-06</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Slow Dancin' - Single</v>
+        <v>Doomsday...Don't Leave Me Here</v>
       </c>
       <c r="G189" t="str">
-        <v>2:04</v>
+        <v>3:26</v>
       </c>
       <c r="H189" t="str">
-        <v>STELLA LEFTY</v>
+        <v>Rosie Carney</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/stella-lefty/1641742186</v>
+        <v>https://music.apple.com/us/artist/rosie-carney/1057803106</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/slow-dancin/1871537170</v>
+        <v>https://music.apple.com/us/album/in-my-blue/1838571277</v>
       </c>
       <c r="L189" t="str">
-        <v>Slow Dancin' - STELLA LEFTY</v>
+        <v>In My Blue - Rosie Carney</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Never Kissed a Cowboy</v>
+        <v>Living With It (feat. Feist)</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/never-kissed-a-cowboy/1866744530</v>
+        <v>https://music.apple.com/us/song/living-with-it-feat-feist/1860115264</v>
       </c>
       <c r="D190" t="str">
         <v>2026-02-06</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Never Kissed a Cowboy - Single</v>
+        <v>Hurts Like Hell</v>
       </c>
       <c r="G190" t="str">
-        <v>3:04</v>
+        <v>3:20</v>
       </c>
       <c r="H190" t="str">
-        <v>Lily Meola</v>
+        <v>Charlotte Cornfield</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/lily-meola/678241726</v>
+        <v>https://music.apple.com/us/artist/charlotte-cornfield/281901047</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/never-kissed-a-cowboy/1866744528</v>
+        <v>https://music.apple.com/us/album/living-with-it-feat-feist/1860115035</v>
       </c>
       <c r="L190" t="str">
-        <v>Never Kissed a Cowboy - Lily Meola</v>
+        <v>Living With It (feat. Feist) - Charlotte Cornfield</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>More Of What Matters</v>
+        <v>Silently</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/more-of-what-matters/1871592720</v>
+        <v>https://music.apple.com/us/song/silently/1841629898</v>
       </c>
       <c r="D191" t="str">
         <v>2026-02-06</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>More Of What Matters - Single</v>
+        <v>Croak Dream</v>
       </c>
       <c r="G191" t="str">
-        <v>3:41</v>
+        <v>3:29</v>
       </c>
       <c r="H191" t="str">
-        <v>Jamey Johnson</v>
+        <v>Puma Blue</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/jamey-johnson/81030634</v>
+        <v>https://music.apple.com/us/artist/puma-blue/1231178386</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/more-of-what-matters/1871592717</v>
+        <v>https://music.apple.com/us/album/silently/1841629444</v>
       </c>
       <c r="L191" t="str">
-        <v>More Of What Matters - Jamey Johnson</v>
+        <v>Silently - Puma Blue</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Is This The Real You</v>
+        <v>Ashes &amp; Smoke</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/is-this-the-real-you/1869323368</v>
+        <v>https://music.apple.com/us/song/ashes-smoke/1871026508</v>
       </c>
       <c r="D192" t="str">
         <v>2026-02-06</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>ONE</v>
+        <v>Ashes &amp; Smoke - Single</v>
       </c>
       <c r="G192" t="str">
-        <v>3:46</v>
+        <v>3:05</v>
       </c>
       <c r="H192" t="str">
-        <v>Sevendust</v>
+        <v>Anna Graves</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/sevendust/13125174</v>
+        <v>https://music.apple.com/us/artist/anna-graves/1441311957</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/is-this-the-real-you/1869323199</v>
+        <v>https://music.apple.com/us/album/ashes-smoke/1871026507</v>
       </c>
       <c r="L192" t="str">
-        <v>Is This The Real You - Sevendust</v>
+        <v>Ashes &amp; Smoke - Anna Graves</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Hud</v>
+        <v>Tormentor</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/hud/1842015019</v>
+        <v>https://music.apple.com/us/song/tormentor/1847995443</v>
       </c>
       <c r="D193" t="str">
         <v>2026-02-06</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>DREAMCRUSH</v>
+        <v>The Flowers I See You In - EP</v>
       </c>
       <c r="G193" t="str">
-        <v>4:46</v>
+        <v>2:40</v>
       </c>
       <c r="H193" t="str">
-        <v>MØL</v>
+        <v>Ninush</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/m%C3%B8l/975294671</v>
+        <v>https://music.apple.com/us/artist/ninush/1794862552</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/hud/1842014730</v>
+        <v>https://music.apple.com/us/album/tormentor/1847995441</v>
       </c>
       <c r="L193" t="str">
-        <v>Hud - MØL</v>
+        <v>Tormentor - Ninush</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Ego Death</v>
+        <v>Red Rocking Chair</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/ego-death/1867855427</v>
+        <v>https://music.apple.com/us/song/red-rocking-chair/1870654858</v>
       </c>
       <c r="D194" t="str">
         <v>2026-02-06</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Ego Death - Single</v>
+        <v>Red Rocking Chair - Single</v>
       </c>
       <c r="G194" t="str">
-        <v>2:12</v>
+        <v>6:28</v>
       </c>
       <c r="H194" t="str">
-        <v>Atreyu</v>
+        <v>All Them Witches</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/atreyu/6095061</v>
+        <v>https://music.apple.com/us/artist/all-them-witches/534924603</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/ego-death/1867855173</v>
+        <v>https://music.apple.com/us/album/red-rocking-chair/1870654854</v>
       </c>
       <c r="L194" t="str">
-        <v>Ego Death - Atreyu</v>
+        <v>Red Rocking Chair - All Them Witches</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Gas Station Love (remix)</v>
+        <v>To Those Who Have Rode On (feat. Erik Danielsson)</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/gas-station-love-remix/1872150728</v>
+        <v>https://music.apple.com/us/song/to-those-who-have-rode-on-feat-erik-danielsson/1852323086</v>
       </c>
       <c r="D195" t="str">
         <v>2026-02-06</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Gas Station Love (remix) - Single</v>
+        <v>...of Death and Fire</v>
       </c>
       <c r="G195" t="str">
-        <v>4:05</v>
+        <v>7:07</v>
       </c>
       <c r="H195" t="str">
-        <v>EJ Jones</v>
+        <v>In Aeternum</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/ej-jones/1781306141</v>
+        <v>https://music.apple.com/us/artist/in-aeternum/263130305</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/gas-station-love-remix/1872150723</v>
+        <v>https://music.apple.com/us/album/to-those-who-have-rode-on-feat-erik-danielsson/1852322618</v>
       </c>
       <c r="L195" t="str">
-        <v>Gas Station Love (remix) - EJ Jones</v>
+        <v>To Those Who Have Rode On (feat. Erik Danielsson) - In Aeternum</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Disappear</v>
+        <v>Mizantrop</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/disappear/1861907311</v>
+        <v>https://music.apple.com/us/song/mizantrop/1870241244</v>
       </c>
       <c r="D196" t="str">
         <v>2026-02-06</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>Disappear</v>
+        <v>Mizantrop</v>
       </c>
       <c r="G196" t="str">
-        <v>5:50</v>
+        <v>3:42</v>
       </c>
       <c r="H196" t="str">
-        <v>Lane 8</v>
+        <v>She Past Away</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/lane-8/634763116</v>
+        <v>https://music.apple.com/us/artist/she-past-away/347750887</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/disappear/1861907305</v>
+        <v>https://music.apple.com/us/album/mizantrop/1870240904</v>
       </c>
       <c r="L196" t="str">
-        <v>Disappear - Lane 8</v>
+        <v>Mizantrop - She Past Away</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Misbehave</v>
+        <v>In the Name of the Moth</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/misbehave/1859630128</v>
+        <v>https://music.apple.com/us/song/in-the-name-of-the-moth/1866911203</v>
       </c>
       <c r="D197" t="str">
         <v>2026-02-06</v>
@@ -7861,448 +7861,30 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>Misbehave - Single</v>
+        <v>Hidden Fires Burn Hottest</v>
       </c>
       <c r="G197" t="str">
-        <v>3:43</v>
+        <v>7:15</v>
       </c>
       <c r="H197" t="str">
-        <v>Aluna</v>
+        <v>Bosse-de-Nage</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/aluna/1508017201</v>
+        <v>https://music.apple.com/us/artist/bosse-de-nage/465123183</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/misbehave/1859630126</v>
+        <v>https://music.apple.com/us/album/in-the-name-of-the-moth/1866911198</v>
       </c>
       <c r="L197" t="str">
-        <v>Misbehave - Aluna</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="str">
-        <v>Club Bizarre</v>
-      </c>
-      <c r="B198" t="str">
-        <v/>
-      </c>
-      <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/club-bizarre/1870355078</v>
-      </c>
-      <c r="D198" t="str">
-        <v>2026-02-06</v>
-      </c>
-      <c r="E198" t="str">
-        <v/>
-      </c>
-      <c r="F198" t="str">
-        <v>Club Bizarre - Single</v>
-      </c>
-      <c r="G198" t="str">
-        <v>2:47</v>
-      </c>
-      <c r="H198" t="str">
-        <v>Alok</v>
-      </c>
-      <c r="I198" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/alok/324709167</v>
-      </c>
-      <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/club-bizarre/1870355077</v>
-      </c>
-      <c r="L198" t="str">
-        <v>Club Bizarre - Alok</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="str">
-        <v>Fly</v>
-      </c>
-      <c r="B199" t="str">
-        <v/>
-      </c>
-      <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/fly/1867903625</v>
-      </c>
-      <c r="D199" t="str">
-        <v>2026-02-06</v>
-      </c>
-      <c r="E199" t="str">
-        <v/>
-      </c>
-      <c r="F199" t="str">
-        <v>Fly - Single</v>
-      </c>
-      <c r="G199" t="str">
-        <v>3:04</v>
-      </c>
-      <c r="H199" t="str">
-        <v>Stephen Stanley</v>
-      </c>
-      <c r="I199" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/stephen-stanley/28074609</v>
-      </c>
-      <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/fly/1867903548</v>
-      </c>
-      <c r="L199" t="str">
-        <v>Fly - Stephen Stanley</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="str">
-        <v>ily anyway</v>
-      </c>
-      <c r="B200" t="str">
-        <v/>
-      </c>
-      <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/ily-anyway/1870369432</v>
-      </c>
-      <c r="D200" t="str">
-        <v>2026-02-06</v>
-      </c>
-      <c r="E200" t="str">
-        <v/>
-      </c>
-      <c r="F200" t="str">
-        <v>ily anyway - Single</v>
-      </c>
-      <c r="G200" t="str">
-        <v>3:05</v>
-      </c>
-      <c r="H200" t="str">
-        <v>Strings &amp; Heart</v>
-      </c>
-      <c r="I200" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J200" t="str">
-        <v>https://music.apple.com/us/artist/strings-heart/1435173742</v>
-      </c>
-      <c r="K200" t="str">
-        <v>https://music.apple.com/us/album/ily-anyway/1870369426</v>
-      </c>
-      <c r="L200" t="str">
-        <v>ily anyway - Strings &amp; Heart</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="str">
-        <v>George Jones (feat. Angela Autumn)</v>
-      </c>
-      <c r="B201" t="str">
-        <v/>
-      </c>
-      <c r="C201" t="str">
-        <v>https://music.apple.com/us/song/george-jones-feat-angela-autumn/1867306007</v>
-      </c>
-      <c r="D201" t="str">
-        <v>2026-02-06</v>
-      </c>
-      <c r="E201" t="str">
-        <v/>
-      </c>
-      <c r="F201" t="str">
-        <v>Nellene - EP</v>
-      </c>
-      <c r="G201" t="str">
-        <v>3:35</v>
-      </c>
-      <c r="H201" t="str">
-        <v>Deloyd Elze</v>
-      </c>
-      <c r="I201" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J201" t="str">
-        <v>https://music.apple.com/us/artist/deloyd-elze/1699032462</v>
-      </c>
-      <c r="K201" t="str">
-        <v>https://music.apple.com/us/album/george-jones-feat-angela-autumn/1867306004</v>
-      </c>
-      <c r="L201" t="str">
-        <v>George Jones (feat. Angela Autumn) - Deloyd Elze</v>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="str">
-        <v>Kiss Big</v>
-      </c>
-      <c r="B202" t="str">
-        <v/>
-      </c>
-      <c r="C202" t="str">
-        <v>https://music.apple.com/us/song/kiss-big/1837292261</v>
-      </c>
-      <c r="D202" t="str">
-        <v>2026-02-06</v>
-      </c>
-      <c r="E202" t="str">
-        <v/>
-      </c>
-      <c r="F202" t="str">
-        <v>Kiss Big</v>
-      </c>
-      <c r="G202" t="str">
-        <v>3:41</v>
-      </c>
-      <c r="H202" t="str">
-        <v>Ailbhe Reddy</v>
-      </c>
-      <c r="I202" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J202" t="str">
-        <v>https://music.apple.com/us/artist/ailbhe-reddy/947186338</v>
-      </c>
-      <c r="K202" t="str">
-        <v>https://music.apple.com/us/album/kiss-big/1837292249</v>
-      </c>
-      <c r="L202" t="str">
-        <v>Kiss Big - Ailbhe Reddy</v>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="str">
-        <v>praxis</v>
-      </c>
-      <c r="B203" t="str">
-        <v/>
-      </c>
-      <c r="C203" t="str">
-        <v>https://music.apple.com/us/song/praxis/1845253734</v>
-      </c>
-      <c r="D203" t="str">
-        <v>2026-02-06</v>
-      </c>
-      <c r="E203" t="str">
-        <v/>
-      </c>
-      <c r="F203" t="str">
-        <v>Whole World As Vigil</v>
-      </c>
-      <c r="G203" t="str">
-        <v>3:28</v>
-      </c>
-      <c r="H203" t="str">
-        <v>Lauren Auder</v>
-      </c>
-      <c r="I203" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J203" t="str">
-        <v>https://music.apple.com/us/artist/lauren-auder/1096049552</v>
-      </c>
-      <c r="K203" t="str">
-        <v>https://music.apple.com/us/album/praxis/1845253730</v>
-      </c>
-      <c r="L203" t="str">
-        <v>praxis - Lauren Auder</v>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="str">
-        <v>House</v>
-      </c>
-      <c r="B204" t="str">
-        <v/>
-      </c>
-      <c r="C204" t="str">
-        <v>https://music.apple.com/us/song/house/1866696487</v>
-      </c>
-      <c r="D204" t="str">
-        <v>2026-02-06</v>
-      </c>
-      <c r="E204" t="str">
-        <v/>
-      </c>
-      <c r="F204" t="str">
-        <v>House - Single</v>
-      </c>
-      <c r="G204" t="str">
-        <v>2:30</v>
-      </c>
-      <c r="H204" t="str">
-        <v>Connie Converse</v>
-      </c>
-      <c r="I204" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J204" t="str">
-        <v>https://music.apple.com/us/artist/connie-converse/308326962</v>
-      </c>
-      <c r="K204" t="str">
-        <v>https://music.apple.com/us/album/house/1866696486</v>
-      </c>
-      <c r="L204" t="str">
-        <v>House - Connie Converse</v>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="str">
-        <v>Cowboy Without a Clue</v>
-      </c>
-      <c r="B205" t="str">
-        <v/>
-      </c>
-      <c r="C205" t="str">
-        <v>https://music.apple.com/us/song/cowboy-without-a-clue/1834024322</v>
-      </c>
-      <c r="D205" t="str">
-        <v>2026-02-06</v>
-      </c>
-      <c r="E205" t="str">
-        <v/>
-      </c>
-      <c r="F205" t="str">
-        <v>No Love Lost to Kindness</v>
-      </c>
-      <c r="G205" t="str">
-        <v>3:57</v>
-      </c>
-      <c r="H205" t="str">
-        <v>Yumi Zouma</v>
-      </c>
-      <c r="I205" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J205" t="str">
-        <v>https://music.apple.com/us/artist/yumi-zouma/795031200</v>
-      </c>
-      <c r="K205" t="str">
-        <v>https://music.apple.com/us/album/cowboy-without-a-clue/1834024311</v>
-      </c>
-      <c r="L205" t="str">
-        <v>Cowboy Without a Clue - Yumi Zouma</v>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="str">
-        <v>Brincar</v>
-      </c>
-      <c r="B206" t="str">
-        <v/>
-      </c>
-      <c r="C206" t="str">
-        <v>https://music.apple.com/us/song/brincar/1871554907</v>
-      </c>
-      <c r="D206" t="str">
-        <v>2026-02-06</v>
-      </c>
-      <c r="E206" t="str">
-        <v/>
-      </c>
-      <c r="F206" t="str">
-        <v>JET LAG - EP</v>
-      </c>
-      <c r="G206" t="str">
-        <v>3:06</v>
-      </c>
-      <c r="H206" t="str">
-        <v>J Castle</v>
-      </c>
-      <c r="I206" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J206" t="str">
-        <v>https://music.apple.com/us/artist/j-castle/309829058</v>
-      </c>
-      <c r="K206" t="str">
-        <v>https://music.apple.com/us/album/brincar/1871554901</v>
-      </c>
-      <c r="L206" t="str">
-        <v>Brincar - J Castle</v>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="str">
-        <v>Quién</v>
-      </c>
-      <c r="B207" t="str">
-        <v/>
-      </c>
-      <c r="C207" t="str">
-        <v>https://music.apple.com/us/song/qui%C3%A9n/1870329662</v>
-      </c>
-      <c r="D207" t="str">
-        <v>2026-02-06</v>
-      </c>
-      <c r="E207" t="str">
-        <v/>
-      </c>
-      <c r="F207" t="str">
-        <v>Quién - Single</v>
-      </c>
-      <c r="G207" t="str">
-        <v>4:19</v>
-      </c>
-      <c r="H207" t="str">
-        <v>Daniela Darcourt</v>
-      </c>
-      <c r="I207" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J207" t="str">
-        <v>https://music.apple.com/us/artist/daniela-darcourt/1396749684</v>
-      </c>
-      <c r="K207" t="str">
-        <v>https://music.apple.com/us/album/qui%C3%A9n/1870329660</v>
-      </c>
-      <c r="L207" t="str">
-        <v>Quién - Daniela Darcourt</v>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="str">
-        <v>Heaven</v>
-      </c>
-      <c r="B208" t="str">
-        <v/>
-      </c>
-      <c r="C208" t="str">
-        <v>https://music.apple.com/us/song/heaven/1862570892</v>
-      </c>
-      <c r="D208" t="str">
-        <v>2026-02-06</v>
-      </c>
-      <c r="E208" t="str">
-        <v/>
-      </c>
-      <c r="F208" t="str">
-        <v>Ambiguous Desire</v>
-      </c>
-      <c r="G208" t="str">
-        <v>4:26</v>
-      </c>
-      <c r="H208" t="str">
-        <v>Arlo Parks</v>
-      </c>
-      <c r="I208" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J208" t="str">
-        <v>https://music.apple.com/us/artist/arlo-parks/1291875084</v>
-      </c>
-      <c r="K208" t="str">
-        <v>https://music.apple.com/us/album/heaven/1862570378</v>
-      </c>
-      <c r="L208" t="str">
-        <v>Heaven - Arlo Parks</v>
+        <v>In the Name of the Moth - Bosse-de-Nage</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L208"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L197"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
@@ -439,7 +439,7 @@
         <v>LADY GAGA - ABRACADABRA (LIVE AT THE 2026 GRAMMYS)</v>
       </c>
       <c r="B2" t="str">
-        <v>6 hours ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=Rn89mUndYbo</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>6 hours ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>4:16</v>
@@ -477,7 +477,7 @@
         <v>Carlos Vives - Te Dedico (Official Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>5 hours ago</v>
+        <v>6 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=H8KW0SgW99I</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>5 hours ago</v>
+        <v>6 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>3:53</v>
@@ -515,7 +515,7 @@
         <v>Monsieur Periné, Jossman - MUCHO CON DEMASIAO' (Video Oficial)</v>
       </c>
       <c r="B4" t="str">
-        <v>5 hours ago</v>
+        <v>6 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=mpmrrvhLzZ0</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>5 hours ago</v>
+        <v>6 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>2:25</v>
@@ -553,7 +553,7 @@
         <v>The Happy Fits - Tenderly (Official Audio)</v>
       </c>
       <c r="B5" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=10hExzTW4Hc</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>4:09</v>
@@ -591,7 +591,7 @@
         <v>chase (lyric vid) - Michael Aldag</v>
       </c>
       <c r="B6" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=QASMKs97wec</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v>2:45</v>
@@ -629,7 +629,7 @@
         <v>Dermot Kennedy - Funeral (Live Acoustic Session)</v>
       </c>
       <c r="B7" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=RyR1xAw9edU</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G7" t="str">
         <v>4:07</v>
@@ -667,7 +667,7 @@
         <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Official Video)</v>
       </c>
       <c r="B8" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=OYtHvS7n7ic</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G8" t="str">
         <v>4:34</v>
@@ -705,7 +705,7 @@
         <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Official Music Video)</v>
       </c>
       <c r="B9" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=XKvzT2CTnLE</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G9" t="str">
         <v>5:14</v>
@@ -743,7 +743,7 @@
         <v>Michael Bolton | Cupid (Official Visualizer)</v>
       </c>
       <c r="B10" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=1XDIbfJ_OGw</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G10" t="str">
         <v>3:11</v>
@@ -781,7 +781,7 @@
         <v>Lachie Gill - Last Drive</v>
       </c>
       <c r="B11" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=y79kD37Ffic</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G11" t="str">
         <v>3:40</v>
@@ -819,7 +819,7 @@
         <v>Eli &amp; Fur - Strange (Official Visualiser)</v>
       </c>
       <c r="B12" t="str">
-        <v>19 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=KlgO3kKNc8o</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>19 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="G12" t="str">
         <v>3:45</v>
@@ -1921,7 +1921,7 @@
         <v>David Guetta, TeddySwims, Tones And I - Gone Gone Gone (Unplugged) [Visualizer]</v>
       </c>
       <c r="B41" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=eWglDE7O5r8</v>
@@ -1933,7 +1933,7 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G41" t="str">
         <v>3:33</v>
@@ -1959,7 +1959,7 @@
         <v>SANTOS BRAVOS “KAWASAKI” Performance Video</v>
       </c>
       <c r="B42" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C42" t="str">
         <v>https://www.youtube.com/watch?v=Cmy8CsYIUL0</v>
@@ -1971,7 +1971,7 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G42" t="str">
         <v>2:41</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
@@ -439,7 +439,7 @@
         <v>LADY GAGA - ABRACADABRA (LIVE AT THE 2026 GRAMMYS)</v>
       </c>
       <c r="B2" t="str">
-        <v>7 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=Rn89mUndYbo</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>7 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>4:16</v>
@@ -477,7 +477,7 @@
         <v>Carlos Vives - Te Dedico (Official Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>6 hours ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=H8KW0SgW99I</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>6 hours ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>3:53</v>
@@ -515,7 +515,7 @@
         <v>Monsieur Periné, Jossman - MUCHO CON DEMASIAO' (Video Oficial)</v>
       </c>
       <c r="B4" t="str">
-        <v>6 hours ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=mpmrrvhLzZ0</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>6 hours ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>2:25</v>
@@ -553,7 +553,7 @@
         <v>The Happy Fits - Tenderly (Official Audio)</v>
       </c>
       <c r="B5" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=10hExzTW4Hc</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>4:09</v>
@@ -591,7 +591,7 @@
         <v>chase (lyric vid) - Michael Aldag</v>
       </c>
       <c r="B6" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=QASMKs97wec</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v>2:45</v>
@@ -629,7 +629,7 @@
         <v>Dermot Kennedy - Funeral (Live Acoustic Session)</v>
       </c>
       <c r="B7" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=RyR1xAw9edU</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G7" t="str">
         <v>4:07</v>
@@ -667,7 +667,7 @@
         <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Official Video)</v>
       </c>
       <c r="B8" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=OYtHvS7n7ic</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G8" t="str">
         <v>4:34</v>
@@ -705,7 +705,7 @@
         <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Official Music Video)</v>
       </c>
       <c r="B9" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=XKvzT2CTnLE</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G9" t="str">
         <v>5:14</v>
@@ -743,7 +743,7 @@
         <v>Michael Bolton | Cupid (Official Visualizer)</v>
       </c>
       <c r="B10" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=1XDIbfJ_OGw</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G10" t="str">
         <v>3:11</v>
@@ -781,7 +781,7 @@
         <v>Lachie Gill - Last Drive</v>
       </c>
       <c r="B11" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=y79kD37Ffic</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G11" t="str">
         <v>3:40</v>
@@ -819,7 +819,7 @@
         <v>Eli &amp; Fur - Strange (Official Visualiser)</v>
       </c>
       <c r="B12" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=KlgO3kKNc8o</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G12" t="str">
         <v>3:45</v>
@@ -1883,7 +1883,7 @@
         <v>Katelyn Tarver - So Am I (Official Music Video)</v>
       </c>
       <c r="B40" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=MjUiVPzMQHw</v>
@@ -1895,7 +1895,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G40" t="str">
         <v>2:52</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
@@ -439,7 +439,7 @@
         <v>LADY GAGA - ABRACADABRA (LIVE AT THE 2026 GRAMMYS)</v>
       </c>
       <c r="B2" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=Rn89mUndYbo</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>4:16</v>
@@ -477,7 +477,7 @@
         <v>Carlos Vives - Te Dedico (Official Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>7 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=H8KW0SgW99I</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>7 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>3:53</v>
@@ -515,7 +515,7 @@
         <v>Monsieur Periné, Jossman - MUCHO CON DEMASIAO' (Video Oficial)</v>
       </c>
       <c r="B4" t="str">
-        <v>7 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=mpmrrvhLzZ0</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>7 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>2:25</v>
@@ -553,7 +553,7 @@
         <v>The Happy Fits - Tenderly (Official Audio)</v>
       </c>
       <c r="B5" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=10hExzTW4Hc</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>4:09</v>
@@ -591,7 +591,7 @@
         <v>chase (lyric vid) - Michael Aldag</v>
       </c>
       <c r="B6" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=QASMKs97wec</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v>2:45</v>
@@ -629,7 +629,7 @@
         <v>Dermot Kennedy - Funeral (Live Acoustic Session)</v>
       </c>
       <c r="B7" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=RyR1xAw9edU</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G7" t="str">
         <v>4:07</v>
@@ -667,7 +667,7 @@
         <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Official Video)</v>
       </c>
       <c r="B8" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=OYtHvS7n7ic</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G8" t="str">
         <v>4:34</v>
@@ -705,7 +705,7 @@
         <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Official Music Video)</v>
       </c>
       <c r="B9" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=XKvzT2CTnLE</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G9" t="str">
         <v>5:14</v>
@@ -743,7 +743,7 @@
         <v>Michael Bolton | Cupid (Official Visualizer)</v>
       </c>
       <c r="B10" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=1XDIbfJ_OGw</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="G10" t="str">
         <v>3:11</v>
@@ -781,7 +781,7 @@
         <v>Lachie Gill - Last Drive</v>
       </c>
       <c r="B11" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=y79kD37Ffic</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="G11" t="str">
         <v>3:40</v>
@@ -819,7 +819,7 @@
         <v>Eli &amp; Fur - Strange (Official Visualiser)</v>
       </c>
       <c r="B12" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=KlgO3kKNc8o</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G12" t="str">
         <v>3:45</v>
@@ -1541,7 +1541,7 @@
         <v>Jessie Ware - I Could Get Used To This ( Live at Graham Norton)</v>
       </c>
       <c r="B31" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=kGeamxRf8Gw</v>
@@ -1553,7 +1553,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G31" t="str">
         <v>3:50</v>
@@ -1807,7 +1807,7 @@
         <v>Zara Larsson - Lush Life (Official UGC Compilation Video)</v>
       </c>
       <c r="B38" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=FgAyfRnbbRs</v>
@@ -1819,7 +1819,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G38" t="str">
         <v>3:22</v>
@@ -1845,7 +1845,7 @@
         <v>Only The Poets - Monumental</v>
       </c>
       <c r="B39" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=nwXiAjjl6NE</v>
@@ -1857,7 +1857,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G39" t="str">
         <v>2:48</v>
@@ -2947,7 +2947,7 @@
         <v>We Three - Drunk Driving (Official Music Video)</v>
       </c>
       <c r="B68" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C68" t="str">
         <v>https://www.youtube.com/watch?v=BTqRGxSX6AQ</v>
@@ -2959,7 +2959,7 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G68" t="str">
         <v>4:27</v>
@@ -3365,7 +3365,7 @@
         <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
       </c>
       <c r="B79" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C79" t="str">
         <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
@@ -3377,7 +3377,7 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G79" t="str">
         <v>3:46</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
@@ -439,7 +439,7 @@
         <v>LADY GAGA - ABRACADABRA (LIVE AT THE 2026 GRAMMYS)</v>
       </c>
       <c r="B2" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=Rn89mUndYbo</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>4:16</v>
@@ -477,7 +477,7 @@
         <v>Carlos Vives - Te Dedico (Official Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=H8KW0SgW99I</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>3:53</v>
@@ -515,7 +515,7 @@
         <v>Monsieur Periné, Jossman - MUCHO CON DEMASIAO' (Video Oficial)</v>
       </c>
       <c r="B4" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=mpmrrvhLzZ0</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>2:25</v>
@@ -553,7 +553,7 @@
         <v>The Happy Fits - Tenderly (Official Audio)</v>
       </c>
       <c r="B5" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=10hExzTW4Hc</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>4:09</v>
@@ -591,7 +591,7 @@
         <v>chase (lyric vid) - Michael Aldag</v>
       </c>
       <c r="B6" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=QASMKs97wec</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v>2:45</v>
@@ -629,7 +629,7 @@
         <v>Dermot Kennedy - Funeral (Live Acoustic Session)</v>
       </c>
       <c r="B7" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=RyR1xAw9edU</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G7" t="str">
         <v>4:07</v>
@@ -667,7 +667,7 @@
         <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Official Video)</v>
       </c>
       <c r="B8" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=OYtHvS7n7ic</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="G8" t="str">
         <v>4:34</v>
@@ -705,7 +705,7 @@
         <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Official Music Video)</v>
       </c>
       <c r="B9" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=XKvzT2CTnLE</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="G9" t="str">
         <v>5:14</v>
@@ -743,7 +743,7 @@
         <v>Michael Bolton | Cupid (Official Visualizer)</v>
       </c>
       <c r="B10" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=1XDIbfJ_OGw</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G10" t="str">
         <v>3:11</v>
@@ -781,7 +781,7 @@
         <v>Lachie Gill - Last Drive</v>
       </c>
       <c r="B11" t="str">
-        <v>19 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=y79kD37Ffic</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>19 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="G11" t="str">
         <v>3:40</v>
@@ -819,7 +819,7 @@
         <v>Eli &amp; Fur - Strange (Official Visualiser)</v>
       </c>
       <c r="B12" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=KlgO3kKNc8o</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G12" t="str">
         <v>3:45</v>
@@ -1769,7 +1769,7 @@
         <v>Paris Paloma - Good Girl [Official Music Video]</v>
       </c>
       <c r="B37" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C37" t="str">
         <v>https://www.youtube.com/watch?v=qhO6VMC-nx0</v>
@@ -1781,7 +1781,7 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G37" t="str">
         <v>4:47</v>
@@ -3327,7 +3327,7 @@
         <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
       </c>
       <c r="B78" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C78" t="str">
         <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
@@ -3339,7 +3339,7 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G78" t="str">
         <v>2:56</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
@@ -439,7 +439,7 @@
         <v>LADY GAGA - ABRACADABRA (LIVE AT THE 2026 GRAMMYS)</v>
       </c>
       <c r="B2" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=Rn89mUndYbo</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>4:16</v>
@@ -477,7 +477,7 @@
         <v>Carlos Vives - Te Dedico (Official Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=H8KW0SgW99I</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>3:53</v>
@@ -515,7 +515,7 @@
         <v>Monsieur Periné, Jossman - MUCHO CON DEMASIAO' (Video Oficial)</v>
       </c>
       <c r="B4" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=mpmrrvhLzZ0</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>2:25</v>
@@ -553,7 +553,7 @@
         <v>The Happy Fits - Tenderly (Official Audio)</v>
       </c>
       <c r="B5" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=10hExzTW4Hc</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>4:09</v>
@@ -591,7 +591,7 @@
         <v>chase (lyric vid) - Michael Aldag</v>
       </c>
       <c r="B6" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=QASMKs97wec</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v>2:45</v>
@@ -629,7 +629,7 @@
         <v>Dermot Kennedy - Funeral (Live Acoustic Session)</v>
       </c>
       <c r="B7" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=RyR1xAw9edU</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="G7" t="str">
         <v>4:07</v>
@@ -667,7 +667,7 @@
         <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Official Video)</v>
       </c>
       <c r="B8" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=OYtHvS7n7ic</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G8" t="str">
         <v>4:34</v>
@@ -705,7 +705,7 @@
         <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Official Music Video)</v>
       </c>
       <c r="B9" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=XKvzT2CTnLE</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G9" t="str">
         <v>5:14</v>
@@ -743,7 +743,7 @@
         <v>Michael Bolton | Cupid (Official Visualizer)</v>
       </c>
       <c r="B10" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=1XDIbfJ_OGw</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G10" t="str">
         <v>3:11</v>
@@ -781,7 +781,7 @@
         <v>Lachie Gill - Last Drive</v>
       </c>
       <c r="B11" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=y79kD37Ffic</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G11" t="str">
         <v>3:40</v>
@@ -819,7 +819,7 @@
         <v>Eli &amp; Fur - Strange (Official Visualiser)</v>
       </c>
       <c r="B12" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=KlgO3kKNc8o</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G12" t="str">
         <v>3:45</v>
@@ -3289,7 +3289,7 @@
         <v>Holly Humberstone - To Love Somebody (Official Video)</v>
       </c>
       <c r="B77" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C77" t="str">
         <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
@@ -3301,7 +3301,7 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G77" t="str">
         <v>3:59</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
@@ -439,7 +439,7 @@
         <v>LADY GAGA - ABRACADABRA (LIVE AT THE 2026 GRAMMYS)</v>
       </c>
       <c r="B2" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=Rn89mUndYbo</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>4:16</v>
@@ -477,7 +477,7 @@
         <v>Carlos Vives - Te Dedico (Official Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=H8KW0SgW99I</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>3:53</v>
@@ -515,7 +515,7 @@
         <v>Monsieur Periné, Jossman - MUCHO CON DEMASIAO' (Video Oficial)</v>
       </c>
       <c r="B4" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=mpmrrvhLzZ0</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>2:25</v>
@@ -553,7 +553,7 @@
         <v>The Happy Fits - Tenderly (Official Audio)</v>
       </c>
       <c r="B5" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=10hExzTW4Hc</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>4:09</v>
@@ -591,7 +591,7 @@
         <v>chase (lyric vid) - Michael Aldag</v>
       </c>
       <c r="B6" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=QASMKs97wec</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v>2:45</v>
@@ -629,7 +629,7 @@
         <v>Dermot Kennedy - Funeral (Live Acoustic Session)</v>
       </c>
       <c r="B7" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=RyR1xAw9edU</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G7" t="str">
         <v>4:07</v>
@@ -667,7 +667,7 @@
         <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Official Video)</v>
       </c>
       <c r="B8" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=OYtHvS7n7ic</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G8" t="str">
         <v>4:34</v>
@@ -705,7 +705,7 @@
         <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Official Music Video)</v>
       </c>
       <c r="B9" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=XKvzT2CTnLE</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G9" t="str">
         <v>5:14</v>
@@ -743,7 +743,7 @@
         <v>Michael Bolton | Cupid (Official Visualizer)</v>
       </c>
       <c r="B10" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=1XDIbfJ_OGw</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="G10" t="str">
         <v>3:11</v>
@@ -781,7 +781,7 @@
         <v>Lachie Gill - Last Drive</v>
       </c>
       <c r="B11" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=y79kD37Ffic</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G11" t="str">
         <v>3:40</v>
@@ -1731,7 +1731,7 @@
         <v>The Kiffness &amp; Matisyahu - ONE DAY (ft. Andel and Nalyn) [OFFICIAL VIDEO]</v>
       </c>
       <c r="B36" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=buS21tVq5r0</v>
@@ -1743,7 +1743,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G36" t="str">
         <v>3:07</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
@@ -439,7 +439,7 @@
         <v>LADY GAGA - ABRACADABRA (LIVE AT THE 2026 GRAMMYS)</v>
       </c>
       <c r="B2" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=Rn89mUndYbo</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>4:16</v>
@@ -477,7 +477,7 @@
         <v>Carlos Vives - Te Dedico (Official Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=H8KW0SgW99I</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>3:53</v>
@@ -515,7 +515,7 @@
         <v>Monsieur Periné, Jossman - MUCHO CON DEMASIAO' (Video Oficial)</v>
       </c>
       <c r="B4" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=mpmrrvhLzZ0</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>2:25</v>
@@ -553,7 +553,7 @@
         <v>The Happy Fits - Tenderly (Official Audio)</v>
       </c>
       <c r="B5" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=10hExzTW4Hc</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>4:09</v>
@@ -591,7 +591,7 @@
         <v>chase (lyric vid) - Michael Aldag</v>
       </c>
       <c r="B6" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=QASMKs97wec</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v>2:45</v>
@@ -629,7 +629,7 @@
         <v>Dermot Kennedy - Funeral (Live Acoustic Session)</v>
       </c>
       <c r="B7" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=RyR1xAw9edU</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G7" t="str">
         <v>4:07</v>
@@ -667,7 +667,7 @@
         <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Official Video)</v>
       </c>
       <c r="B8" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=OYtHvS7n7ic</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="G8" t="str">
         <v>4:34</v>
@@ -705,7 +705,7 @@
         <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Official Music Video)</v>
       </c>
       <c r="B9" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=XKvzT2CTnLE</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="G9" t="str">
         <v>5:14</v>
@@ -743,7 +743,7 @@
         <v>Michael Bolton | Cupid (Official Visualizer)</v>
       </c>
       <c r="B10" t="str">
-        <v>19 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=1XDIbfJ_OGw</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>19 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="G10" t="str">
         <v>3:11</v>
@@ -781,7 +781,7 @@
         <v>Lachie Gill - Last Drive</v>
       </c>
       <c r="B11" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=y79kD37Ffic</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G11" t="str">
         <v>3:40</v>
@@ -1693,7 +1693,7 @@
         <v>The Cure - Boys Don't Cry (86 Mix) (Official Lyric Video)</v>
       </c>
       <c r="B35" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=isNztTjXQsQ</v>
@@ -1705,7 +1705,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G35" t="str">
         <v>2:39</v>
@@ -2985,7 +2985,7 @@
         <v>Timebelle - Top of the World (Mood Video)</v>
       </c>
       <c r="B69" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C69" t="str">
         <v>https://www.youtube.com/watch?v=r9KyYK_E34s</v>
@@ -2997,7 +2997,7 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G69" t="str">
         <v>3:01</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>LADY GAGA - ABRACADABRA (LIVE AT THE 2026 GRAMMYS)</v>
+        <v>Cliff Richard - Golden (75th Birthday Concert, Royal Albert Hall, 14 Oct 2015)</v>
       </c>
       <c r="B2" t="str">
-        <v>13 hours ago</v>
+        <v>4 hours ago</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=Rn89mUndYbo</v>
+        <v>https://www.youtube.com/watch?v=JZM2tHMmqck</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-06</v>
@@ -451,13 +451,13 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>13 hours ago</v>
+        <v>4 hours ago</v>
       </c>
       <c r="G2" t="str">
-        <v>4:16</v>
+        <v>4:37</v>
       </c>
       <c r="H2" t="str">
-        <v>Lady Gaga</v>
+        <v>Cliff Richard</v>
       </c>
       <c r="I2" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>LADY GAGA - ABRACADABRA (LIVE AT THE 2026 GRAMMYS) - Lady Gaga</v>
+        <v>Cliff Richard - Golden (75th Birthday Concert, Royal Albert Hall, 14 Oct 2015) - Cliff Richard</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Carlos Vives - Te Dedico (Official Video)</v>
+        <v>Bryan Adams - Hey Baby</v>
       </c>
       <c r="B3" t="str">
-        <v>12 hours ago</v>
+        <v>5 hours ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=H8KW0SgW99I</v>
+        <v>https://www.youtube.com/watch?v=aYcAl98fDYk</v>
       </c>
       <c r="D3" t="str">
         <v>2026-02-06</v>
@@ -489,13 +489,13 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>12 hours ago</v>
+        <v>5 hours ago</v>
       </c>
       <c r="G3" t="str">
-        <v>3:53</v>
+        <v>3:54</v>
       </c>
       <c r="H3" t="str">
-        <v>Carlos Vives</v>
+        <v>Bryan Adams</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Carlos Vives - Te Dedico (Official Video) - Carlos Vives</v>
+        <v>Bryan Adams - Hey Baby - Bryan Adams</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Monsieur Periné, Jossman - MUCHO CON DEMASIAO' (Video Oficial)</v>
+        <v>Anna Graves - Ashes &amp; Smoke (Official Audio)</v>
       </c>
       <c r="B4" t="str">
-        <v>12 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=mpmrrvhLzZ0</v>
+        <v>https://www.youtube.com/watch?v=n90qajAa6oQ</v>
       </c>
       <c r="D4" t="str">
         <v>2026-02-06</v>
@@ -527,13 +527,13 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>12 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="G4" t="str">
-        <v>2:25</v>
+        <v>3:06</v>
       </c>
       <c r="H4" t="str">
-        <v>Monsieur Periné</v>
+        <v>Anna Graves</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Monsieur Periné, Jossman - MUCHO CON DEMASIAO' (Video Oficial) - Monsieur Periné</v>
+        <v>Anna Graves - Ashes &amp; Smoke (Official Audio) - Anna Graves</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>The Happy Fits - Tenderly (Official Audio)</v>
+        <v>George Birge - Ride, Ride, Ride (Feat. Luke Bryan) [Official Music Video]</v>
       </c>
       <c r="B5" t="str">
-        <v>16 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=10hExzTW4Hc</v>
+        <v>https://www.youtube.com/watch?v=rWGpexrWhJE</v>
       </c>
       <c r="D5" t="str">
         <v>2026-02-06</v>
@@ -565,13 +565,13 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>16 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="G5" t="str">
-        <v>4:09</v>
+        <v>3:21</v>
       </c>
       <c r="H5" t="str">
-        <v>The Happy Fits</v>
+        <v>George Birge</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>The Happy Fits - Tenderly (Official Audio) - The Happy Fits</v>
+        <v>George Birge - Ride, Ride, Ride (Feat. Luke Bryan) [Official Music Video] - George Birge</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>chase (lyric vid) - Michael Aldag</v>
+        <v>Morrissey - Notre-Dame (Official Lyric Video)</v>
       </c>
       <c r="B6" t="str">
-        <v>18 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=QASMKs97wec</v>
+        <v>https://www.youtube.com/watch?v=Q44JiUwa2Xg</v>
       </c>
       <c r="D6" t="str">
         <v>2026-02-06</v>
@@ -603,13 +603,13 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>18 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="G6" t="str">
-        <v>2:45</v>
+        <v>4:09</v>
       </c>
       <c r="H6" t="str">
-        <v>Michael Aldag</v>
+        <v>Warner Records</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>chase (lyric vid) - Michael Aldag - Michael Aldag</v>
+        <v>Morrissey - Notre-Dame (Official Lyric Video) - Warner Records</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Dermot Kennedy - Funeral (Live Acoustic Session)</v>
+        <v>Nick Jonas - Sweet To Me (Official Lyric Video)</v>
       </c>
       <c r="B7" t="str">
-        <v>18 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=RyR1xAw9edU</v>
+        <v>https://www.youtube.com/watch?v=Jy2dqfKWY-c</v>
       </c>
       <c r="D7" t="str">
         <v>2026-02-06</v>
@@ -641,13 +641,13 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>18 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="G7" t="str">
-        <v>4:07</v>
+        <v>4:18</v>
       </c>
       <c r="H7" t="str">
-        <v>Dermot Kennedy</v>
+        <v>NICK JONAS</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Dermot Kennedy - Funeral (Live Acoustic Session) - Dermot Kennedy</v>
+        <v>Nick Jonas - Sweet To Me (Official Lyric Video) - NICK JONAS</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Official Video)</v>
+        <v>Charlie Puth - Cry (with Kenny G) [Official Audio]</v>
       </c>
       <c r="B8" t="str">
-        <v>19 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=OYtHvS7n7ic</v>
+        <v>https://www.youtube.com/watch?v=Bam3O09kLAQ</v>
       </c>
       <c r="D8" t="str">
         <v>2026-02-06</v>
@@ -679,13 +679,13 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>19 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="G8" t="str">
-        <v>4:34</v>
+        <v>3:08</v>
       </c>
       <c r="H8" t="str">
-        <v>Marc Anthony</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Official Video) - Marc Anthony</v>
+        <v>Charlie Puth - Cry (with Kenny G) [Official Audio] - Charlie Puth</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Official Music Video)</v>
+        <v>Olivia Newton-John - Serenity (Visualizer) (Official)</v>
       </c>
       <c r="B9" t="str">
-        <v>19 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=XKvzT2CTnLE</v>
+        <v>https://www.youtube.com/watch?v=F-usO6XVXcs</v>
       </c>
       <c r="D9" t="str">
         <v>2026-02-06</v>
@@ -717,13 +717,13 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>19 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="G9" t="str">
-        <v>5:14</v>
+        <v>4:03</v>
       </c>
       <c r="H9" t="str">
-        <v>FULL CIRCLE BOYS</v>
+        <v>Olivia Newton-John</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Official Music Video) - FULL CIRCLE BOYS</v>
+        <v>Olivia Newton-John - Serenity (Visualizer) (Official) - Olivia Newton-John</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Michael Bolton | Cupid (Official Visualizer)</v>
+        <v>The Warning, Carín León - Love To Be Loved (Official Video)</v>
       </c>
       <c r="B10" t="str">
-        <v>20 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=1XDIbfJ_OGw</v>
+        <v>https://www.youtube.com/watch?v=8DUQ5vPcz9o</v>
       </c>
       <c r="D10" t="str">
         <v>2026-02-06</v>
@@ -755,13 +755,13 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>20 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="G10" t="str">
-        <v>3:11</v>
+        <v>3:01</v>
       </c>
       <c r="H10" t="str">
-        <v>Michael Bolton</v>
+        <v>The Warning and Carin Leon</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Michael Bolton | Cupid (Official Visualizer) - Michael Bolton</v>
+        <v>The Warning, Carín León - Love To Be Loved (Official Video) - The Warning and Carin Leon</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Lachie Gill - Last Drive</v>
+        <v>Iman Fandi - Tip Toes (Official Dance Visualiser)</v>
       </c>
       <c r="B11" t="str">
-        <v>23 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=y79kD37Ffic</v>
+        <v>https://www.youtube.com/watch?v=WRvCKHSm12Y</v>
       </c>
       <c r="D11" t="str">
         <v>2026-02-06</v>
@@ -793,13 +793,13 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>23 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="G11" t="str">
-        <v>3:40</v>
+        <v>3:05</v>
       </c>
       <c r="H11" t="str">
-        <v>Lachie Gill</v>
+        <v>Iman Fandi</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Lachie Gill - Last Drive - Lachie Gill</v>
+        <v>Iman Fandi - Tip Toes (Official Dance Visualiser) - Iman Fandi</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Eli &amp; Fur - Strange (Official Visualiser)</v>
+        <v>Megan Moroney - Cloud 9 (Official Lyric Video)</v>
       </c>
       <c r="B12" t="str">
-        <v>1 day ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=KlgO3kKNc8o</v>
+        <v>https://www.youtube.com/watch?v=BiNIdrm9miE</v>
       </c>
       <c r="D12" t="str">
         <v>2026-02-06</v>
@@ -831,13 +831,13 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>1 day ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="G12" t="str">
-        <v>3:45</v>
+        <v>3:34</v>
       </c>
       <c r="H12" t="str">
-        <v>Eli &amp; Fur</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Eli &amp; Fur - Strange (Official Visualiser) - Eli &amp; Fur</v>
+        <v>Megan Moroney - Cloud 9 (Official Lyric Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Freya Skye - why'd you have to call</v>
+        <v>Dylan Davidson - Escape Artist</v>
       </c>
       <c r="B13" t="str">
-        <v>1 day ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=75o0FuwCdaA</v>
+        <v>https://www.youtube.com/watch?v=iKW4wCw_LoY</v>
       </c>
       <c r="D13" t="str">
         <v>2026-02-06</v>
@@ -869,13 +869,13 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>1 day ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="G13" t="str">
-        <v>4:19</v>
+        <v>3:15</v>
       </c>
       <c r="H13" t="str">
-        <v>Freya Skye</v>
+        <v>Dylan Davidson</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Freya Skye - why'd you have to call - Freya Skye</v>
+        <v>Dylan Davidson - Escape Artist - Dylan Davidson</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Jessie J - FEEL IT ON ME (Lyric Visualiser) (Official Lyric Video)</v>
+        <v>LADY GAGA - ABRACADABRA (LIVE AT THE 2026 GRAMMYS)</v>
       </c>
       <c r="B14" t="str">
-        <v>1 day ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=DGmbe49F8aI</v>
+        <v>https://www.youtube.com/watch?v=Rn89mUndYbo</v>
       </c>
       <c r="D14" t="str">
         <v>2026-02-06</v>
@@ -907,13 +907,13 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>1 day ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G14" t="str">
-        <v>2:30</v>
+        <v>4:16</v>
       </c>
       <c r="H14" t="str">
-        <v>Jessie J</v>
+        <v>Lady Gaga</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Jessie J - FEEL IT ON ME (Lyric Visualiser) (Official Lyric Video) - Jessie J</v>
+        <v>LADY GAGA - ABRACADABRA (LIVE AT THE 2026 GRAMMYS) - Lady Gaga</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Marc Anthony - Make It With You (Visualizer)</v>
+        <v>Carlos Vives - Te Dedico (Official Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>2 days ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=WHnz1jDrxw8</v>
+        <v>https://www.youtube.com/watch?v=H8KW0SgW99I</v>
       </c>
       <c r="D15" t="str">
         <v>2026-02-06</v>
@@ -945,13 +945,13 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>2 days ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G15" t="str">
-        <v>4:24</v>
+        <v>3:53</v>
       </c>
       <c r="H15" t="str">
-        <v>Marc Anthony</v>
+        <v>Carlos Vives</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Marc Anthony - Make It With You (Visualizer) - Marc Anthony</v>
+        <v>Carlos Vives - Te Dedico (Official Video) - Carlos Vives</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Clara Mae - Never Been Yours ft. Bob John Holt</v>
+        <v>Monsieur Periné, Jossman - MUCHO CON DEMASIAO' (Video Oficial)</v>
       </c>
       <c r="B16" t="str">
-        <v>2 days ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=HtVuKBlBuPg</v>
+        <v>https://www.youtube.com/watch?v=mpmrrvhLzZ0</v>
       </c>
       <c r="D16" t="str">
         <v>2026-02-06</v>
@@ -983,13 +983,13 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>2 days ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G16" t="str">
-        <v>2:33</v>
+        <v>2:25</v>
       </c>
       <c r="H16" t="str">
-        <v>Clara Mae</v>
+        <v>Monsieur Periné</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Clara Mae - Never Been Yours ft. Bob John Holt - Clara Mae</v>
+        <v>Monsieur Periné, Jossman - MUCHO CON DEMASIAO' (Video Oficial) - Monsieur Periné</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Metric - Victim of Luck (Official Music Video)</v>
+        <v>The Happy Fits - Tenderly (Official Audio)</v>
       </c>
       <c r="B17" t="str">
-        <v>2 days ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=shmhTOUd8mA</v>
+        <v>https://www.youtube.com/watch?v=10hExzTW4Hc</v>
       </c>
       <c r="D17" t="str">
         <v>2026-02-06</v>
@@ -1021,13 +1021,13 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>2 days ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G17" t="str">
-        <v>3:25</v>
+        <v>4:09</v>
       </c>
       <c r="H17" t="str">
-        <v>metricmusic</v>
+        <v>The Happy Fits</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Metric - Victim of Luck (Official Music Video) - metricmusic</v>
+        <v>The Happy Fits - Tenderly (Official Audio) - The Happy Fits</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Kesha - RED FLAG. (Red Carpet) OFFICIAL MUSIC VIDEO</v>
+        <v>chase (lyric vid) - Michael Aldag</v>
       </c>
       <c r="B18" t="str">
-        <v>2 days ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=pvrJ5RnPAEA</v>
+        <v>https://www.youtube.com/watch?v=QASMKs97wec</v>
       </c>
       <c r="D18" t="str">
         <v>2026-02-06</v>
@@ -1059,13 +1059,13 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>2 days ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="G18" t="str">
-        <v>3:41</v>
+        <v>2:45</v>
       </c>
       <c r="H18" t="str">
-        <v>kesha</v>
+        <v>Michael Aldag</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Kesha - RED FLAG. (Red Carpet) OFFICIAL MUSIC VIDEO - kesha</v>
+        <v>chase (lyric vid) - Michael Aldag - Michael Aldag</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Studio)</v>
+        <v>Dermot Kennedy - Funeral (Live Acoustic Session)</v>
       </c>
       <c r="B19" t="str">
-        <v>3 days ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=mgsdQI-GVMM</v>
+        <v>https://www.youtube.com/watch?v=RyR1xAw9edU</v>
       </c>
       <c r="D19" t="str">
         <v>2026-02-06</v>
@@ -1097,13 +1097,13 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>3 days ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="G19" t="str">
-        <v>3:19</v>
+        <v>4:07</v>
       </c>
       <c r="H19" t="str">
-        <v>David Guetta and Tones And I</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Studio) - David Guetta and Tones And I</v>
+        <v>Dermot Kennedy - Funeral (Live Acoustic Session) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Vera Blue - Hold (Live on Sydney Harbour)</v>
+        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Official Video)</v>
       </c>
       <c r="B20" t="str">
-        <v>3 days ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=SYEwk-EZJPU</v>
+        <v>https://www.youtube.com/watch?v=OYtHvS7n7ic</v>
       </c>
       <c r="D20" t="str">
         <v>2026-02-06</v>
@@ -1135,13 +1135,13 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>3 days ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="G20" t="str">
-        <v>3:37</v>
+        <v>4:34</v>
       </c>
       <c r="H20" t="str">
-        <v>Vera Blue</v>
+        <v>Marc Anthony</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Vera Blue - Hold (Live on Sydney Harbour) - Vera Blue</v>
+        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Official Video) - Marc Anthony</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Bob Moses - Need You Tonight (INXS Cover) - Brooklyn Mirage 2023</v>
+        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Official Music Video)</v>
       </c>
       <c r="B21" t="str">
-        <v>3 days ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=CoCqPwDIBOA</v>
+        <v>https://www.youtube.com/watch?v=XKvzT2CTnLE</v>
       </c>
       <c r="D21" t="str">
         <v>2026-02-06</v>
@@ -1173,13 +1173,13 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>3 days ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="G21" t="str">
-        <v>3:08</v>
+        <v>5:14</v>
       </c>
       <c r="H21" t="str">
-        <v>Bob Moses</v>
+        <v>FULL CIRCLE BOYS</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Bob Moses - Need You Tonight (INXS Cover) - Brooklyn Mirage 2023 - Bob Moses</v>
+        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Official Music Video) - FULL CIRCLE BOYS</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Marc Anthony - Un Mal Sueño (Visualizer)</v>
+        <v>Michael Bolton | Cupid (Official Visualizer)</v>
       </c>
       <c r="B22" t="str">
-        <v>3 days ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=18yZq5xtke4</v>
+        <v>https://www.youtube.com/watch?v=1XDIbfJ_OGw</v>
       </c>
       <c r="D22" t="str">
         <v>2026-02-06</v>
@@ -1211,13 +1211,13 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>3 days ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G22" t="str">
-        <v>3:28</v>
+        <v>3:11</v>
       </c>
       <c r="H22" t="str">
-        <v>Marc Anthony</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Marc Anthony - Un Mal Sueño (Visualizer) - Marc Anthony</v>
+        <v>Michael Bolton | Cupid (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Marc Anthony - Contra La Corriente (Visualizer)</v>
+        <v>Lachie Gill - Last Drive</v>
       </c>
       <c r="B23" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=IGLmJ71oHhQ</v>
+        <v>https://www.youtube.com/watch?v=y79kD37Ffic</v>
       </c>
       <c r="D23" t="str">
         <v>2026-02-06</v>
@@ -1249,13 +1249,13 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G23" t="str">
-        <v>5:05</v>
+        <v>3:40</v>
       </c>
       <c r="H23" t="str">
-        <v>Marc Anthony</v>
+        <v>Lachie Gill</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Marc Anthony - Contra La Corriente (Visualizer) - Marc Anthony</v>
+        <v>Lachie Gill - Last Drive - Lachie Gill</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Loreen - Feels Like Heaven</v>
+        <v>Eli &amp; Fur - Strange (Official Visualiser)</v>
       </c>
       <c r="B24" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=BQc97moyQBg</v>
+        <v>https://www.youtube.com/watch?v=KlgO3kKNc8o</v>
       </c>
       <c r="D24" t="str">
         <v>2026-02-06</v>
@@ -1287,13 +1287,13 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G24" t="str">
-        <v>3:14</v>
+        <v>3:45</v>
       </c>
       <c r="H24" t="str">
-        <v>Loreen</v>
+        <v>Eli &amp; Fur</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Loreen - Feels Like Heaven - Loreen</v>
+        <v>Eli &amp; Fur - Strange (Official Visualiser) - Eli &amp; Fur</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Take That - Once You've Tasted Love (Live on Pebble Mill, 1992)</v>
+        <v>Freya Skye - why'd you have to call</v>
       </c>
       <c r="B25" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=dOeoDOueESk</v>
+        <v>https://www.youtube.com/watch?v=75o0FuwCdaA</v>
       </c>
       <c r="D25" t="str">
         <v>2026-02-06</v>
@@ -1325,13 +1325,13 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G25" t="str">
-        <v>3:36</v>
+        <v>4:19</v>
       </c>
       <c r="H25" t="str">
-        <v>Take That</v>
+        <v>Freya Skye</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Take That - Once You've Tasted Love (Live on Pebble Mill, 1992) - Take That</v>
+        <v>Freya Skye - why'd you have to call - Freya Skye</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Paul McCartney, Wings - Nineteen Hundred And Eighty Five (Visualiser)</v>
+        <v>Jessie J - FEEL IT ON ME (Lyric Visualiser) (Official Lyric Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=a4AIjUHuWpU</v>
+        <v>https://www.youtube.com/watch?v=DGmbe49F8aI</v>
       </c>
       <c r="D26" t="str">
         <v>2026-02-06</v>
@@ -1363,13 +1363,13 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G26" t="str">
-        <v>5:31</v>
+        <v>2:30</v>
       </c>
       <c r="H26" t="str">
-        <v>PAUL McCARTNEY</v>
+        <v>Jessie J</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Paul McCartney, Wings - Nineteen Hundred And Eighty Five (Visualiser) - PAUL McCARTNEY</v>
+        <v>Jessie J - FEEL IT ON ME (Lyric Visualiser) (Official Lyric Video) - Jessie J</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Nothing But Thieves - Sorry (Official Audio)</v>
+        <v>Marc Anthony - Make It With You (Visualizer)</v>
       </c>
       <c r="B27" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=D7QfVqo5YqY</v>
+        <v>https://www.youtube.com/watch?v=WHnz1jDrxw8</v>
       </c>
       <c r="D27" t="str">
         <v>2026-02-06</v>
@@ -1401,13 +1401,13 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>3:37</v>
+        <v>4:24</v>
       </c>
       <c r="H27" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Marc Anthony</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Nothing But Thieves - Sorry (Official Audio) - Nothing But Thieves</v>
+        <v>Marc Anthony - Make It With You (Visualizer) - Marc Anthony</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music</v>
+        <v>Clara Mae - Never Been Yours ft. Bob John Holt</v>
       </c>
       <c r="B28" t="str">
-        <v>5 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=KdsHxyl4bE8</v>
+        <v>https://www.youtube.com/watch?v=HtVuKBlBuPg</v>
       </c>
       <c r="D28" t="str">
         <v>2026-02-06</v>
@@ -1439,13 +1439,13 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>5 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>4:58</v>
+        <v>2:33</v>
       </c>
       <c r="H28" t="str">
-        <v>The Warning</v>
+        <v>Clara Mae</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music - The Warning</v>
+        <v>Clara Mae - Never Been Yours ft. Bob John Holt - Clara Mae</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield, CA (2026)</v>
+        <v>Metric - Victim of Luck (Official Music Video)</v>
       </c>
       <c r="B29" t="str">
-        <v>5 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=Mwkl_Cz_SG8</v>
+        <v>https://www.youtube.com/watch?v=shmhTOUd8mA</v>
       </c>
       <c r="D29" t="str">
         <v>2026-02-06</v>
@@ -1477,13 +1477,13 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>5 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>5:08</v>
+        <v>3:25</v>
       </c>
       <c r="H29" t="str">
-        <v>The Offspring</v>
+        <v>metricmusic</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield, CA (2026) - The Offspring</v>
+        <v>Metric - Victim of Luck (Official Music Video) - metricmusic</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered)</v>
+        <v>Kesha - RED FLAG. (Red Carpet) OFFICIAL MUSIC VIDEO</v>
       </c>
       <c r="B30" t="str">
-        <v>5 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=I7a-pDZFE7U</v>
+        <v>https://www.youtube.com/watch?v=pvrJ5RnPAEA</v>
       </c>
       <c r="D30" t="str">
         <v>2026-02-06</v>
@@ -1515,13 +1515,13 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>5 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>4:38</v>
+        <v>3:41</v>
       </c>
       <c r="H30" t="str">
-        <v>Roxette</v>
+        <v>kesha</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered) - Roxette</v>
+        <v>Kesha - RED FLAG. (Red Carpet) OFFICIAL MUSIC VIDEO - kesha</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Jessie Ware - I Could Get Used To This ( Live at Graham Norton)</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Studio)</v>
       </c>
       <c r="B31" t="str">
-        <v>6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=kGeamxRf8Gw</v>
+        <v>https://www.youtube.com/watch?v=mgsdQI-GVMM</v>
       </c>
       <c r="D31" t="str">
         <v>2026-02-06</v>
@@ -1553,13 +1553,13 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>3:50</v>
+        <v>3:19</v>
       </c>
       <c r="H31" t="str">
-        <v>Jessie Ware</v>
+        <v>David Guetta and Tones And I</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Jessie Ware - I Could Get Used To This ( Live at Graham Norton) - Jessie Ware</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Studio) - David Guetta and Tones And I</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>JOSEPH - Water in the Room (Official Music Video)</v>
+        <v>Vera Blue - Hold (Live on Sydney Harbour)</v>
       </c>
       <c r="B32" t="str">
-        <v>6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=tNmT47k6MjM</v>
+        <v>https://www.youtube.com/watch?v=SYEwk-EZJPU</v>
       </c>
       <c r="D32" t="str">
         <v>2026-02-06</v>
@@ -1591,13 +1591,13 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>3:10</v>
+        <v>3:37</v>
       </c>
       <c r="H32" t="str">
-        <v>Joseph</v>
+        <v>Vera Blue</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>JOSEPH - Water in the Room (Official Music Video) - Joseph</v>
+        <v>Vera Blue - Hold (Live on Sydney Harbour) - Vera Blue</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Dean Lewis - I Am Getting Well (Lyric Video)</v>
+        <v>Bob Moses - Need You Tonight (INXS Cover) - Brooklyn Mirage 2023</v>
       </c>
       <c r="B33" t="str">
-        <v>6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=6ecgOSOMWzc</v>
+        <v>https://www.youtube.com/watch?v=CoCqPwDIBOA</v>
       </c>
       <c r="D33" t="str">
         <v>2026-02-06</v>
@@ -1629,13 +1629,13 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>2:44</v>
+        <v>3:08</v>
       </c>
       <c r="H33" t="str">
-        <v>Dean Lewis</v>
+        <v>Bob Moses</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Dean Lewis - I Am Getting Well (Lyric Video) - Dean Lewis</v>
+        <v>Bob Moses - Need You Tonight (INXS Cover) - Brooklyn Mirage 2023 - Bob Moses</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Take That - Take That and Party (Official HD Video)</v>
+        <v>Marc Anthony - Un Mal Sueño (Visualizer)</v>
       </c>
       <c r="B34" t="str">
-        <v>6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=DAerJcerikU</v>
+        <v>https://www.youtube.com/watch?v=18yZq5xtke4</v>
       </c>
       <c r="D34" t="str">
         <v>2026-02-06</v>
@@ -1667,13 +1667,13 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>2:57</v>
+        <v>3:28</v>
       </c>
       <c r="H34" t="str">
-        <v>Take That</v>
+        <v>Marc Anthony</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Take That - Take That and Party (Official HD Video) - Take That</v>
+        <v>Marc Anthony - Un Mal Sueño (Visualizer) - Marc Anthony</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>The Cure - Boys Don't Cry (86 Mix) (Official Lyric Video)</v>
+        <v>Marc Anthony - Contra La Corriente (Visualizer)</v>
       </c>
       <c r="B35" t="str">
-        <v>7 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=isNztTjXQsQ</v>
+        <v>https://www.youtube.com/watch?v=IGLmJ71oHhQ</v>
       </c>
       <c r="D35" t="str">
         <v>2026-02-06</v>
@@ -1705,13 +1705,13 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>7 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>2:39</v>
+        <v>5:05</v>
       </c>
       <c r="H35" t="str">
-        <v>The Cure</v>
+        <v>Marc Anthony</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>The Cure - Boys Don't Cry (86 Mix) (Official Lyric Video) - The Cure</v>
+        <v>Marc Anthony - Contra La Corriente (Visualizer) - Marc Anthony</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>The Kiffness &amp; Matisyahu - ONE DAY (ft. Andel and Nalyn) [OFFICIAL VIDEO]</v>
+        <v>Loreen - Feels Like Heaven</v>
       </c>
       <c r="B36" t="str">
-        <v>7 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=buS21tVq5r0</v>
+        <v>https://www.youtube.com/watch?v=BQc97moyQBg</v>
       </c>
       <c r="D36" t="str">
         <v>2026-02-06</v>
@@ -1743,13 +1743,13 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>7 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>3:07</v>
+        <v>3:14</v>
       </c>
       <c r="H36" t="str">
-        <v>The Kiffness and Matisyahu</v>
+        <v>Loreen</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>The Kiffness &amp; Matisyahu - ONE DAY (ft. Andel and Nalyn) [OFFICIAL VIDEO] - The Kiffness and Matisyahu</v>
+        <v>Loreen - Feels Like Heaven - Loreen</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Paris Paloma - Good Girl [Official Music Video]</v>
+        <v>Take That - Once You've Tasted Love (Live on Pebble Mill, 1992)</v>
       </c>
       <c r="B37" t="str">
-        <v>7 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=qhO6VMC-nx0</v>
+        <v>https://www.youtube.com/watch?v=dOeoDOueESk</v>
       </c>
       <c r="D37" t="str">
         <v>2026-02-06</v>
@@ -1781,13 +1781,13 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>7 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>4:47</v>
+        <v>3:36</v>
       </c>
       <c r="H37" t="str">
-        <v>Paris Paloma</v>
+        <v>Take That</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Paris Paloma - Good Girl [Official Music Video] - Paris Paloma</v>
+        <v>Take That - Once You've Tasted Love (Live on Pebble Mill, 1992) - Take That</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Zara Larsson - Lush Life (Official UGC Compilation Video)</v>
+        <v>Paul McCartney, Wings - Nineteen Hundred And Eighty Five (Visualiser)</v>
       </c>
       <c r="B38" t="str">
-        <v>7 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=FgAyfRnbbRs</v>
+        <v>https://www.youtube.com/watch?v=a4AIjUHuWpU</v>
       </c>
       <c r="D38" t="str">
         <v>2026-02-06</v>
@@ -1819,13 +1819,13 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>7 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>3:22</v>
+        <v>5:31</v>
       </c>
       <c r="H38" t="str">
-        <v>Zara Larsson</v>
+        <v>PAUL McCARTNEY</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Zara Larsson - Lush Life (Official UGC Compilation Video) - Zara Larsson</v>
+        <v>Paul McCartney, Wings - Nineteen Hundred And Eighty Five (Visualiser) - PAUL McCARTNEY</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Only The Poets - Monumental</v>
+        <v>Nothing But Thieves - Sorry (Official Audio)</v>
       </c>
       <c r="B39" t="str">
-        <v>7 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=nwXiAjjl6NE</v>
+        <v>https://www.youtube.com/watch?v=D7QfVqo5YqY</v>
       </c>
       <c r="D39" t="str">
         <v>2026-02-06</v>
@@ -1857,13 +1857,13 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>7 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>2:48</v>
+        <v>3:37</v>
       </c>
       <c r="H39" t="str">
-        <v>only the poets</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Only The Poets - Monumental - only the poets</v>
+        <v>Nothing But Thieves - Sorry (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Katelyn Tarver - So Am I (Official Music Video)</v>
+        <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music</v>
       </c>
       <c r="B40" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=MjUiVPzMQHw</v>
+        <v>https://www.youtube.com/watch?v=KdsHxyl4bE8</v>
       </c>
       <c r="D40" t="str">
         <v>2026-02-06</v>
@@ -1895,13 +1895,13 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>2:52</v>
+        <v>4:58</v>
       </c>
       <c r="H40" t="str">
-        <v>Katelyn Tarver</v>
+        <v>The Warning</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Katelyn Tarver - So Am I (Official Music Video) - Katelyn Tarver</v>
+        <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music - The Warning</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>David Guetta, TeddySwims, Tones And I - Gone Gone Gone (Unplugged) [Visualizer]</v>
+        <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield, CA (2026)</v>
       </c>
       <c r="B41" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=eWglDE7O5r8</v>
+        <v>https://www.youtube.com/watch?v=Mwkl_Cz_SG8</v>
       </c>
       <c r="D41" t="str">
         <v>2026-02-06</v>
@@ -1933,13 +1933,13 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>3:33</v>
+        <v>5:08</v>
       </c>
       <c r="H41" t="str">
-        <v>David Guetta</v>
+        <v>The Offspring</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>David Guetta, TeddySwims, Tones And I - Gone Gone Gone (Unplugged) [Visualizer] - David Guetta</v>
+        <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield, CA (2026) - The Offspring</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>SANTOS BRAVOS “KAWASAKI” Performance Video</v>
+        <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered)</v>
       </c>
       <c r="B42" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=Cmy8CsYIUL0</v>
+        <v>https://www.youtube.com/watch?v=I7a-pDZFE7U</v>
       </c>
       <c r="D42" t="str">
         <v>2026-02-06</v>
@@ -1971,13 +1971,13 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>2:41</v>
+        <v>4:38</v>
       </c>
       <c r="H42" t="str">
-        <v>HYBE LABELS and SANTOS BRAVOS</v>
+        <v>Roxette</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>SANTOS BRAVOS “KAWASAKI” Performance Video - HYBE LABELS and SANTOS BRAVOS</v>
+        <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered) - Roxette</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Ella Langley - Dandelion (Official Visualizer)</v>
+        <v>Jessie Ware - I Could Get Used To This ( Live at Graham Norton)</v>
       </c>
       <c r="B43" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=sf6eRmInk1s</v>
+        <v>https://www.youtube.com/watch?v=kGeamxRf8Gw</v>
       </c>
       <c r="D43" t="str">
         <v>2026-02-06</v>
@@ -2009,13 +2009,13 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>4:01</v>
+        <v>3:50</v>
       </c>
       <c r="H43" t="str">
-        <v>Ella Langley</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Ella Langley - Dandelion (Official Visualizer) - Ella Langley</v>
+        <v>Jessie Ware - I Could Get Used To This ( Live at Graham Norton) - Jessie Ware</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Dogpark - Dandelion (Official Music Video)</v>
+        <v>JOSEPH - Water in the Room (Official Music Video)</v>
       </c>
       <c r="B44" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=fv9prIYHHzk</v>
+        <v>https://www.youtube.com/watch?v=tNmT47k6MjM</v>
       </c>
       <c r="D44" t="str">
         <v>2026-02-06</v>
@@ -2047,13 +2047,13 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>3:16</v>
+        <v>3:10</v>
       </c>
       <c r="H44" t="str">
-        <v>Dogpark</v>
+        <v>Joseph</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Dogpark - Dandelion (Official Music Video) - Dogpark</v>
+        <v>JOSEPH - Water in the Room (Official Music Video) - Joseph</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Lauren Spencer Smith - Natural Disaster (Visualizer)</v>
+        <v>Dean Lewis - I Am Getting Well (Lyric Video)</v>
       </c>
       <c r="B45" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=T9YvLA2cdZs</v>
+        <v>https://www.youtube.com/watch?v=6ecgOSOMWzc</v>
       </c>
       <c r="D45" t="str">
         <v>2026-02-06</v>
@@ -2088,10 +2088,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>3:03</v>
+        <v>2:44</v>
       </c>
       <c r="H45" t="str">
-        <v>Lauren Spencer Smith</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Lauren Spencer Smith - Natural Disaster (Visualizer) - Lauren Spencer Smith</v>
+        <v>Dean Lewis - I Am Getting Well (Lyric Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>ERNEST - Lorelei (Official Music Video)</v>
+        <v>Take That - Take That and Party (Official HD Video)</v>
       </c>
       <c r="B46" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=dPWc_6IdDJk</v>
+        <v>https://www.youtube.com/watch?v=DAerJcerikU</v>
       </c>
       <c r="D46" t="str">
         <v>2026-02-06</v>
@@ -2126,10 +2126,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>2:41</v>
+        <v>2:57</v>
       </c>
       <c r="H46" t="str">
-        <v>ERNEST</v>
+        <v>Take That</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>ERNEST - Lorelei (Official Music Video) - ERNEST</v>
+        <v>Take That - Take That and Party (Official HD Video) - Take That</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Labrinth - I Keep My Promises (Official Audio)</v>
+        <v>The Kiffness &amp; Matisyahu - ONE DAY (ft. Andel and Nalyn) [OFFICIAL VIDEO]</v>
       </c>
       <c r="B47" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=CV5rR9JZK-0</v>
+        <v>https://www.youtube.com/watch?v=buS21tVq5r0</v>
       </c>
       <c r="D47" t="str">
         <v>2026-02-06</v>
@@ -2164,10 +2164,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>3:05</v>
+        <v>3:07</v>
       </c>
       <c r="H47" t="str">
-        <v>Labrinth</v>
+        <v>The Kiffness and Matisyahu</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Labrinth - I Keep My Promises (Official Audio) - Labrinth</v>
+        <v>The Kiffness &amp; Matisyahu - ONE DAY (ft. Andel and Nalyn) [OFFICIAL VIDEO] - The Kiffness and Matisyahu</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Grace VanderWaal - Prettier (Official Lyric Video)</v>
+        <v>Paris Paloma - Good Girl [Official Music Video]</v>
       </c>
       <c r="B48" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=9HwTj3NZ16E</v>
+        <v>https://www.youtube.com/watch?v=qhO6VMC-nx0</v>
       </c>
       <c r="D48" t="str">
         <v>2026-02-06</v>
@@ -2202,10 +2202,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>2:46</v>
+        <v>4:47</v>
       </c>
       <c r="H48" t="str">
-        <v>Grace VanderWaal</v>
+        <v>Paris Paloma</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Grace VanderWaal - Prettier (Official Lyric Video) - Grace VanderWaal</v>
+        <v>Paris Paloma - Good Girl [Official Music Video] - Paris Paloma</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>VOILÀ - Frozen Lake (Official Lyric Video)</v>
+        <v>Zara Larsson - Lush Life (Official UGC Compilation Video)</v>
       </c>
       <c r="B49" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=Lmus-UbL1H0</v>
+        <v>https://www.youtube.com/watch?v=FgAyfRnbbRs</v>
       </c>
       <c r="D49" t="str">
         <v>2026-02-06</v>
@@ -2240,10 +2240,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>3:32</v>
+        <v>3:22</v>
       </c>
       <c r="H49" t="str">
-        <v>VOILÀ</v>
+        <v>Zara Larsson</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>VOILÀ - Frozen Lake (Official Lyric Video) - VOILÀ</v>
+        <v>Zara Larsson - Lush Life (Official UGC Compilation Video) - Zara Larsson</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Cannons - Starlight (Official Video)</v>
+        <v>Only The Poets - Monumental</v>
       </c>
       <c r="B50" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=bu6WSMDDPGY</v>
+        <v>https://www.youtube.com/watch?v=nwXiAjjl6NE</v>
       </c>
       <c r="D50" t="str">
         <v>2026-02-06</v>
@@ -2278,10 +2278,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>3:42</v>
+        <v>2:48</v>
       </c>
       <c r="H50" t="str">
-        <v>Cannons</v>
+        <v>only the poets</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Cannons - Starlight (Official Video) - Cannons</v>
+        <v>Only The Poets - Monumental - only the poets</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Kylie Morgan - Like My Own (Official Video)</v>
+        <v>Katelyn Tarver - So Am I (Official Music Video)</v>
       </c>
       <c r="B51" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=zcYeoGBglC0</v>
+        <v>https://www.youtube.com/watch?v=MjUiVPzMQHw</v>
       </c>
       <c r="D51" t="str">
         <v>2026-02-06</v>
@@ -2316,10 +2316,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>2:38</v>
+        <v>2:52</v>
       </c>
       <c r="H51" t="str">
-        <v>Kylie Morgan</v>
+        <v>Katelyn Tarver</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Kylie Morgan - Like My Own (Official Video) - Kylie Morgan</v>
+        <v>Katelyn Tarver - So Am I (Official Music Video) - Katelyn Tarver</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Lizzy McAlpine - House of the Rising Sun (Audio)</v>
+        <v>David Guetta, TeddySwims, Tones And I - Gone Gone Gone (Unplugged) [Visualizer]</v>
       </c>
       <c r="B52" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=3igYRj82EiU</v>
+        <v>https://www.youtube.com/watch?v=eWglDE7O5r8</v>
       </c>
       <c r="D52" t="str">
         <v>2026-02-06</v>
@@ -2354,10 +2354,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>3:10</v>
+        <v>3:33</v>
       </c>
       <c r="H52" t="str">
-        <v>Lizzy McAlpine</v>
+        <v>David Guetta</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Lizzy McAlpine - House of the Rising Sun (Audio) - Lizzy McAlpine</v>
+        <v>David Guetta, TeddySwims, Tones And I - Gone Gone Gone (Unplugged) [Visualizer] - David Guetta</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Willie Nelson - Heart Of America (From The Gray House Original Soundtrack)</v>
+        <v>SANTOS BRAVOS “KAWASAKI” Performance Video</v>
       </c>
       <c r="B53" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=0bhcO4Yphuo</v>
+        <v>https://www.youtube.com/watch?v=Cmy8CsYIUL0</v>
       </c>
       <c r="D53" t="str">
         <v>2026-02-06</v>
@@ -2392,10 +2392,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>3:57</v>
+        <v>2:41</v>
       </c>
       <c r="H53" t="str">
-        <v>Willie Nelson</v>
+        <v>HYBE LABELS and SANTOS BRAVOS</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Willie Nelson - Heart Of America (From The Gray House Original Soundtrack) - Willie Nelson</v>
+        <v>SANTOS BRAVOS “KAWASAKI” Performance Video - HYBE LABELS and SANTOS BRAVOS</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Jeremy Camp - No Survivors (Live) ft. Skillet</v>
+        <v>Ella Langley - Dandelion (Official Visualizer)</v>
       </c>
       <c r="B54" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=Jjz1wFe5dMo</v>
+        <v>https://www.youtube.com/watch?v=sf6eRmInk1s</v>
       </c>
       <c r="D54" t="str">
         <v>2026-02-06</v>
@@ -2430,10 +2430,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G54" t="str">
-        <v>2:19</v>
+        <v>4:01</v>
       </c>
       <c r="H54" t="str">
-        <v>JeremyCampMusic</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Jeremy Camp - No Survivors (Live) ft. Skillet - JeremyCampMusic</v>
+        <v>Ella Langley - Dandelion (Official Visualizer) - Ella Langley</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>India Martinez, Coro ArteSí de Olvidados - Niño Sin Miedo</v>
+        <v>Dogpark - Dandelion (Official Music Video)</v>
       </c>
       <c r="B55" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=Vug_FPbXe9E</v>
+        <v>https://www.youtube.com/watch?v=fv9prIYHHzk</v>
       </c>
       <c r="D55" t="str">
         <v>2026-02-06</v>
@@ -2468,10 +2468,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G55" t="str">
-        <v>4:04</v>
+        <v>3:16</v>
       </c>
       <c r="H55" t="str">
-        <v>India Martínez</v>
+        <v>Dogpark</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>India Martinez, Coro ArteSí de Olvidados - Niño Sin Miedo - India Martínez</v>
+        <v>Dogpark - Dandelion (Official Music Video) - Dogpark</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Chelsea Cutler - BAD (Official Lyric Video)</v>
+        <v>Lauren Spencer Smith - Natural Disaster (Visualizer)</v>
       </c>
       <c r="B56" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=ZIW2vA3Zs1U</v>
+        <v>https://www.youtube.com/watch?v=T9YvLA2cdZs</v>
       </c>
       <c r="D56" t="str">
         <v>2026-02-06</v>
@@ -2506,10 +2506,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G56" t="str">
-        <v>2:16</v>
+        <v>3:03</v>
       </c>
       <c r="H56" t="str">
-        <v>Chelsea Cutler</v>
+        <v>Lauren Spencer Smith</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Chelsea Cutler - BAD (Official Lyric Video) - Chelsea Cutler</v>
+        <v>Lauren Spencer Smith - Natural Disaster (Visualizer) - Lauren Spencer Smith</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>TINI - FUTTTURA LIVE - el cielo + fresa</v>
+        <v>ERNEST - Lorelei (Official Music Video)</v>
       </c>
       <c r="B57" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=q_rrgJZAdNg</v>
+        <v>https://www.youtube.com/watch?v=dPWc_6IdDJk</v>
       </c>
       <c r="D57" t="str">
         <v>2026-02-06</v>
@@ -2544,10 +2544,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G57" t="str">
-        <v>5:58</v>
+        <v>2:41</v>
       </c>
       <c r="H57" t="str">
-        <v>TINI</v>
+        <v>ERNEST</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>TINI - FUTTTURA LIVE - el cielo + fresa - TINI</v>
+        <v>ERNEST - Lorelei (Official Music Video) - ERNEST</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Charley - Serial Idealist (Official Video)</v>
+        <v>Labrinth - I Keep My Promises (Official Audio)</v>
       </c>
       <c r="B58" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=uVIuKbPJz0U</v>
+        <v>https://www.youtube.com/watch?v=CV5rR9JZK-0</v>
       </c>
       <c r="D58" t="str">
         <v>2026-02-06</v>
@@ -2582,10 +2582,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G58" t="str">
-        <v>3:26</v>
+        <v>3:05</v>
       </c>
       <c r="H58" t="str">
-        <v>Charley</v>
+        <v>Labrinth</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Charley - Serial Idealist (Official Video) - Charley</v>
+        <v>Labrinth - I Keep My Promises (Official Audio) - Labrinth</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Demi Lovato - Ghost (Live)</v>
+        <v>Grace VanderWaal - Prettier (Official Lyric Video)</v>
       </c>
       <c r="B59" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=E-ECwdRndVA</v>
+        <v>https://www.youtube.com/watch?v=9HwTj3NZ16E</v>
       </c>
       <c r="D59" t="str">
         <v>2026-02-06</v>
@@ -2620,10 +2620,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G59" t="str">
-        <v>4:05</v>
+        <v>2:46</v>
       </c>
       <c r="H59" t="str">
-        <v>Demi Lovato</v>
+        <v>Grace VanderWaal</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Demi Lovato - Ghost (Live) - Demi Lovato</v>
+        <v>Grace VanderWaal - Prettier (Official Lyric Video) - Grace VanderWaal</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Teddy Swims - Need You More (Live - Green Room Sessions)</v>
+        <v>VOILÀ - Frozen Lake (Official Lyric Video)</v>
       </c>
       <c r="B60" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=1ugf5aaY4pY</v>
+        <v>https://www.youtube.com/watch?v=Lmus-UbL1H0</v>
       </c>
       <c r="D60" t="str">
         <v>2026-02-06</v>
@@ -2658,10 +2658,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G60" t="str">
-        <v>3:16</v>
+        <v>3:32</v>
       </c>
       <c r="H60" t="str">
-        <v>Teddy Swims</v>
+        <v>VOILÀ</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Teddy Swims - Need You More (Live - Green Room Sessions) - Teddy Swims</v>
+        <v>VOILÀ - Frozen Lake (Official Lyric Video) - VOILÀ</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Beck - Love (Audio)</v>
+        <v>Cannons - Starlight (Official Video)</v>
       </c>
       <c r="B61" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=ByABj3Xof1I</v>
+        <v>https://www.youtube.com/watch?v=bu6WSMDDPGY</v>
       </c>
       <c r="D61" t="str">
         <v>2026-02-06</v>
@@ -2696,10 +2696,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G61" t="str">
-        <v>3:14</v>
+        <v>3:42</v>
       </c>
       <c r="H61" t="str">
-        <v>Beck</v>
+        <v>Cannons</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Beck - Love (Audio) - Beck</v>
+        <v>Cannons - Starlight (Official Video) - Cannons</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>The Offspring - Looking Out For #1 | Live in Spokane, WA (2026)</v>
+        <v>Kylie Morgan - Like My Own (Official Video)</v>
       </c>
       <c r="B62" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=2HSbo51EFNg</v>
+        <v>https://www.youtube.com/watch?v=zcYeoGBglC0</v>
       </c>
       <c r="D62" t="str">
         <v>2026-02-06</v>
@@ -2731,13 +2731,13 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G62" t="str">
-        <v>2:57</v>
+        <v>2:38</v>
       </c>
       <c r="H62" t="str">
-        <v>The Offspring</v>
+        <v>Kylie Morgan</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>The Offspring - Looking Out For #1 | Live in Spokane, WA (2026) - The Offspring</v>
+        <v>Kylie Morgan - Like My Own (Official Video) - Kylie Morgan</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show</v>
+        <v>Lizzy McAlpine - House of the Rising Sun (Audio)</v>
       </c>
       <c r="B63" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=ylifHFJWJ_c</v>
+        <v>https://www.youtube.com/watch?v=3igYRj82EiU</v>
       </c>
       <c r="D63" t="str">
         <v>2026-02-06</v>
@@ -2769,13 +2769,13 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G63" t="str">
-        <v>4:10</v>
+        <v>3:10</v>
       </c>
       <c r="H63" t="str">
-        <v>Sophie Ellis-Bextor</v>
+        <v>Lizzy McAlpine</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show - Sophie Ellis-Bextor</v>
+        <v>Lizzy McAlpine - House of the Rising Sun (Audio) - Lizzy McAlpine</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Jason Derulo - Sexy For Me [Official Music Video]</v>
+        <v>Willie Nelson - Heart Of America (From The Gray House Original Soundtrack)</v>
       </c>
       <c r="B64" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=9ST-eBNL0NU</v>
+        <v>https://www.youtube.com/watch?v=0bhcO4Yphuo</v>
       </c>
       <c r="D64" t="str">
         <v>2026-02-06</v>
@@ -2807,13 +2807,13 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G64" t="str">
-        <v>2:10</v>
+        <v>3:57</v>
       </c>
       <c r="H64" t="str">
-        <v>Jason Derulo</v>
+        <v>Willie Nelson</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Jason Derulo - Sexy For Me [Official Music Video] - Jason Derulo</v>
+        <v>Willie Nelson - Heart Of America (From The Gray House Original Soundtrack) - Willie Nelson</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Lights - COME GET YOUR GIRL</v>
+        <v>Jeremy Camp - No Survivors (Live) ft. Skillet</v>
       </c>
       <c r="B65" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=EhzX2y5MpSM</v>
+        <v>https://www.youtube.com/watch?v=Jjz1wFe5dMo</v>
       </c>
       <c r="D65" t="str">
         <v>2026-02-06</v>
@@ -2845,13 +2845,13 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G65" t="str">
-        <v>3:52</v>
+        <v>2:19</v>
       </c>
       <c r="H65" t="str">
-        <v>lights</v>
+        <v>JeremyCampMusic</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Lights - COME GET YOUR GIRL - lights</v>
+        <v>Jeremy Camp - No Survivors (Live) ft. Skillet - JeremyCampMusic</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video)</v>
+        <v>India Martinez, Coro ArteSí de Olvidados - Niño Sin Miedo</v>
       </c>
       <c r="B66" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=yUAvfo8fpuU</v>
+        <v>https://www.youtube.com/watch?v=Vug_FPbXe9E</v>
       </c>
       <c r="D66" t="str">
         <v>2026-02-06</v>
@@ -2883,13 +2883,13 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G66" t="str">
-        <v>3:50</v>
+        <v>4:04</v>
       </c>
       <c r="H66" t="str">
-        <v>Telenova</v>
+        <v>India Martínez</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video) - Telenova</v>
+        <v>India Martinez, Coro ArteSí de Olvidados - Niño Sin Miedo - India Martínez</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>I Had To Explain "How Music Works" LIVE In Concert</v>
+        <v>Chelsea Cutler - BAD (Official Lyric Video)</v>
       </c>
       <c r="B67" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=KnsBdAM3HqY</v>
+        <v>https://www.youtube.com/watch?v=ZIW2vA3Zs1U</v>
       </c>
       <c r="D67" t="str">
         <v>2026-02-06</v>
@@ -2921,13 +2921,13 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G67" t="str">
-        <v>5:32</v>
+        <v>2:16</v>
       </c>
       <c r="H67" t="str">
-        <v>Marcin</v>
+        <v>Chelsea Cutler</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>I Had To Explain "How Music Works" LIVE In Concert - Marcin</v>
+        <v>Chelsea Cutler - BAD (Official Lyric Video) - Chelsea Cutler</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>We Three - Drunk Driving (Official Music Video)</v>
+        <v>TINI - FUTTTURA LIVE - el cielo + fresa</v>
       </c>
       <c r="B68" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=BTqRGxSX6AQ</v>
+        <v>https://www.youtube.com/watch?v=q_rrgJZAdNg</v>
       </c>
       <c r="D68" t="str">
         <v>2026-02-06</v>
@@ -2959,13 +2959,13 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G68" t="str">
-        <v>4:27</v>
+        <v>5:58</v>
       </c>
       <c r="H68" t="str">
-        <v>We Three</v>
+        <v>TINI</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>We Three - Drunk Driving (Official Music Video) - We Three</v>
+        <v>TINI - FUTTTURA LIVE - el cielo + fresa - TINI</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Timebelle - Top of the World (Mood Video)</v>
+        <v>Charley - Serial Idealist (Official Video)</v>
       </c>
       <c r="B69" t="str">
-        <v>10 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=r9KyYK_E34s</v>
+        <v>https://www.youtube.com/watch?v=uVIuKbPJz0U</v>
       </c>
       <c r="D69" t="str">
         <v>2026-02-06</v>
@@ -2997,13 +2997,13 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>10 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G69" t="str">
-        <v>3:01</v>
+        <v>3:26</v>
       </c>
       <c r="H69" t="str">
-        <v>Timebelle Official</v>
+        <v>Charley</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Timebelle - Top of the World (Mood Video) - Timebelle Official</v>
+        <v>Charley - Serial Idealist (Official Video) - Charley</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop)</v>
+        <v>Demi Lovato - Ghost (Live)</v>
       </c>
       <c r="B70" t="str">
-        <v>10 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=57a_OheOlDw</v>
+        <v>https://www.youtube.com/watch?v=E-ECwdRndVA</v>
       </c>
       <c r="D70" t="str">
         <v>2026-02-06</v>
@@ -3035,13 +3035,13 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>10 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G70" t="str">
-        <v>3:20</v>
+        <v>4:05</v>
       </c>
       <c r="H70" t="str">
-        <v>David Guetta and Tones And I</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop) - David Guetta and Tones And I</v>
+        <v>Demi Lovato - Ghost (Live) - Demi Lovato</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Clinton Kane - this is my last love song to you (Official Lyric Video)</v>
+        <v>Teddy Swims - Need You More (Live - Green Room Sessions)</v>
       </c>
       <c r="B71" t="str">
-        <v>13 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=-5Aa8NTiRqE</v>
+        <v>https://www.youtube.com/watch?v=1ugf5aaY4pY</v>
       </c>
       <c r="D71" t="str">
         <v>2026-02-06</v>
@@ -3073,13 +3073,13 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>13 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G71" t="str">
-        <v>3:34</v>
+        <v>3:16</v>
       </c>
       <c r="H71" t="str">
-        <v>Clinton Kane</v>
+        <v>Teddy Swims</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Clinton Kane - this is my last love song to you (Official Lyric Video) - Clinton Kane</v>
+        <v>Teddy Swims - Need You More (Live - Green Room Sessions) - Teddy Swims</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>SIENNA SPIRO - Die On This Hill (Official Music Video)</v>
+        <v>Beck - Love (Audio)</v>
       </c>
       <c r="B72" t="str">
-        <v>13 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=5RNy_1odv20</v>
+        <v>https://www.youtube.com/watch?v=ByABj3Xof1I</v>
       </c>
       <c r="D72" t="str">
         <v>2026-02-06</v>
@@ -3111,13 +3111,13 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>13 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G72" t="str">
-        <v>4:01</v>
+        <v>3:14</v>
       </c>
       <c r="H72" t="str">
-        <v>Lyrical Lemonade and SIENNA SPIRO</v>
+        <v>Beck</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>SIENNA SPIRO - Die On This Hill (Official Music Video) - Lyrical Lemonade and SIENNA SPIRO</v>
+        <v>Beck - Love (Audio) - Beck</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Amazon Music presents: Sienna Spiro - You Stole The Show</v>
+        <v>The Offspring - Looking Out For #1 | Live in Spokane, WA (2026)</v>
       </c>
       <c r="B73" t="str">
-        <v>13 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=stYIRyCLN4Y</v>
+        <v>https://www.youtube.com/watch?v=2HSbo51EFNg</v>
       </c>
       <c r="D73" t="str">
         <v>2026-02-06</v>
@@ -3149,13 +3149,13 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>13 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G73" t="str">
-        <v>3:24</v>
+        <v>2:57</v>
       </c>
       <c r="H73" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>The Offspring</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Amazon Music presents: Sienna Spiro - You Stole The Show - SIENNA SPIRO</v>
+        <v>The Offspring - Looking Out For #1 | Live in Spokane, WA (2026) - The Offspring</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Harry Styles - Aperture (Official Video)</v>
+        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show</v>
       </c>
       <c r="B74" t="str">
-        <v>13 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=7sxVHYZ_PnA</v>
+        <v>https://www.youtube.com/watch?v=ylifHFJWJ_c</v>
       </c>
       <c r="D74" t="str">
         <v>2026-02-06</v>
@@ -3187,13 +3187,13 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>13 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G74" t="str">
-        <v>5:52</v>
+        <v>4:10</v>
       </c>
       <c r="H74" t="str">
-        <v>Harry Styles</v>
+        <v>Sophie Ellis-Bextor</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Harry Styles - Aperture (Official Video) - Harry Styles</v>
+        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show - Sophie Ellis-Bextor</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Neal Francis - Back It Up (Live At The Salt Shed)</v>
+        <v>Jason Derulo - Sexy For Me [Official Music Video]</v>
       </c>
       <c r="B75" t="str">
-        <v>13 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=46iZEdsxjC0</v>
+        <v>https://www.youtube.com/watch?v=9ST-eBNL0NU</v>
       </c>
       <c r="D75" t="str">
         <v>2026-02-06</v>
@@ -3225,13 +3225,13 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>13 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G75" t="str">
-        <v>5:01</v>
+        <v>2:10</v>
       </c>
       <c r="H75" t="str">
-        <v>Neal Francis</v>
+        <v>Jason Derulo</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Neal Francis - Back It Up (Live At The Salt Shed) - Neal Francis</v>
+        <v>Jason Derulo - Sexy For Me [Official Music Video] - Jason Derulo</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
+        <v>Lights - COME GET YOUR GIRL</v>
       </c>
       <c r="B76" t="str">
-        <v>13 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=K2nG1Uukz7E</v>
+        <v>https://www.youtube.com/watch?v=EhzX2y5MpSM</v>
       </c>
       <c r="D76" t="str">
         <v>2026-02-06</v>
@@ -3263,13 +3263,13 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>13 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G76" t="str">
-        <v>4:12</v>
+        <v>3:52</v>
       </c>
       <c r="H76" t="str">
-        <v>OfficiallyExtreme</v>
+        <v>lights</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
+        <v>Lights - COME GET YOUR GIRL - lights</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Holly Humberstone - To Love Somebody (Official Video)</v>
+        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video)</v>
       </c>
       <c r="B77" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
+        <v>https://www.youtube.com/watch?v=yUAvfo8fpuU</v>
       </c>
       <c r="D77" t="str">
         <v>2026-02-06</v>
@@ -3301,13 +3301,13 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G77" t="str">
-        <v>3:59</v>
+        <v>3:50</v>
       </c>
       <c r="H77" t="str">
-        <v>Holly Humberstone</v>
+        <v>Telenova</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Holly Humberstone - To Love Somebody (Official Video) - Holly Humberstone</v>
+        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video) - Telenova</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
+        <v>I Had To Explain "How Music Works" LIVE In Concert</v>
       </c>
       <c r="B78" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
+        <v>https://www.youtube.com/watch?v=KnsBdAM3HqY</v>
       </c>
       <c r="D78" t="str">
         <v>2026-02-06</v>
@@ -3339,13 +3339,13 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G78" t="str">
-        <v>2:56</v>
+        <v>5:32</v>
       </c>
       <c r="H78" t="str">
-        <v>Cliff Richard</v>
+        <v>Marcin</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018) - Cliff Richard</v>
+        <v>I Had To Explain "How Music Works" LIVE In Concert - Marcin</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
+        <v>We Three - Drunk Driving (Official Music Video)</v>
       </c>
       <c r="B79" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
+        <v>https://www.youtube.com/watch?v=BTqRGxSX6AQ</v>
       </c>
       <c r="D79" t="str">
         <v>2026-02-06</v>
@@ -3377,13 +3377,13 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G79" t="str">
-        <v>3:46</v>
+        <v>4:27</v>
       </c>
       <c r="H79" t="str">
-        <v>Jessie Ware</v>
+        <v>We Three</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Official Video) - Jessie Ware</v>
+        <v>We Three - Drunk Driving (Official Music Video) - We Three</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Bella White - Dream Song (Official Audio)</v>
+        <v>Timebelle - Top of the World (Mood Video)</v>
       </c>
       <c r="B80" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
+        <v>https://www.youtube.com/watch?v=r9KyYK_E34s</v>
       </c>
       <c r="D80" t="str">
         <v>2026-02-06</v>
@@ -3415,13 +3415,13 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G80" t="str">
-        <v>4:37</v>
+        <v>3:01</v>
       </c>
       <c r="H80" t="str">
-        <v>Bella White</v>
+        <v>Timebelle Official</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Bella White - Dream Song (Official Audio) - Bella White</v>
+        <v>Timebelle - Top of the World (Mood Video) - Timebelle Official</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Ryan Wright - Film School Kids (Official Video)</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop)</v>
       </c>
       <c r="B81" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=pnAz9RwGSek</v>
+        <v>https://www.youtube.com/watch?v=57a_OheOlDw</v>
       </c>
       <c r="D81" t="str">
         <v>2026-02-06</v>
@@ -3453,13 +3453,13 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G81" t="str">
-        <v>4:06</v>
+        <v>3:20</v>
       </c>
       <c r="H81" t="str">
-        <v>Ryan Wright</v>
+        <v>David Guetta and Tones And I</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Ryan Wright - Film School Kids (Official Video) - Ryan Wright</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop) - David Guetta and Tones And I</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer)</v>
+        <v>Clinton Kane - this is my last love song to you (Official Lyric Video)</v>
       </c>
       <c r="B82" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=u7aPv2saz_I</v>
+        <v>https://www.youtube.com/watch?v=-5Aa8NTiRqE</v>
       </c>
       <c r="D82" t="str">
         <v>2026-02-06</v>
@@ -3491,13 +3491,13 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G82" t="str">
-        <v>3:54</v>
+        <v>3:34</v>
       </c>
       <c r="H82" t="str">
-        <v>Dove Cameron</v>
+        <v>Clinton Kane</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer) - Dove Cameron</v>
+        <v>Clinton Kane - this is my last love song to you (Official Lyric Video) - Clinton Kane</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video)</v>
+        <v>SIENNA SPIRO - Die On This Hill (Official Music Video)</v>
       </c>
       <c r="B83" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=WGb8KVdqs6k</v>
+        <v>https://www.youtube.com/watch?v=5RNy_1odv20</v>
       </c>
       <c r="D83" t="str">
         <v>2026-02-06</v>
@@ -3529,13 +3529,13 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G83" t="str">
-        <v>4:10</v>
+        <v>4:01</v>
       </c>
       <c r="H83" t="str">
-        <v>Parker McCollum</v>
+        <v>Lyrical Lemonade and SIENNA SPIRO</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video) - Parker McCollum</v>
+        <v>SIENNA SPIRO - Die On This Hill (Official Music Video) - Lyrical Lemonade and SIENNA SPIRO</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video)</v>
+        <v>Amazon Music presents: Sienna Spiro - You Stole The Show</v>
       </c>
       <c r="B84" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=X1ZeY4Y3l1M</v>
+        <v>https://www.youtube.com/watch?v=stYIRyCLN4Y</v>
       </c>
       <c r="D84" t="str">
         <v>2026-02-06</v>
@@ -3567,13 +3567,13 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G84" t="str">
-        <v>3:26</v>
+        <v>3:24</v>
       </c>
       <c r="H84" t="str">
-        <v>Matt Hansen</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video) - Matt Hansen</v>
+        <v>Amazon Music presents: Sienna Spiro - You Stole The Show - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Louis Tomlinson - Imposter (Official Video)</v>
+        <v>Harry Styles - Aperture (Official Video)</v>
       </c>
       <c r="B85" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=rzuD5szQhso</v>
+        <v>https://www.youtube.com/watch?v=7sxVHYZ_PnA</v>
       </c>
       <c r="D85" t="str">
         <v>2026-02-06</v>
@@ -3605,13 +3605,13 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G85" t="str">
-        <v>2:56</v>
+        <v>5:52</v>
       </c>
       <c r="H85" t="str">
-        <v>Louis Tomlinson</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Louis Tomlinson - Imposter (Official Video) - Louis Tomlinson</v>
+        <v>Harry Styles - Aperture (Official Video) - Harry Styles</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Mitchell Tenpenny - You Phase (Official Music Video)</v>
+        <v>Neal Francis - Back It Up (Live At The Salt Shed)</v>
       </c>
       <c r="B86" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=UPuK6wV5Zco</v>
+        <v>https://www.youtube.com/watch?v=46iZEdsxjC0</v>
       </c>
       <c r="D86" t="str">
         <v>2026-02-06</v>
@@ -3643,13 +3643,13 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G86" t="str">
-        <v>2:56</v>
+        <v>5:01</v>
       </c>
       <c r="H86" t="str">
-        <v>Mitchell Tenpenny</v>
+        <v>Neal Francis</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Mitchell Tenpenny - You Phase (Official Music Video) - Mitchell Tenpenny</v>
+        <v>Neal Francis - Back It Up (Live At The Salt Shed) - Neal Francis</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Tauren Wells - Breathe On It (Official Lyric Video)</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
       </c>
       <c r="B87" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=9hW9sNMn2A0</v>
+        <v>https://www.youtube.com/watch?v=K2nG1Uukz7E</v>
       </c>
       <c r="D87" t="str">
         <v>2026-02-06</v>
@@ -3681,13 +3681,13 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G87" t="str">
-        <v>4:01</v>
+        <v>4:12</v>
       </c>
       <c r="H87" t="str">
-        <v>Tauren Wells</v>
+        <v>OfficiallyExtreme</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Tauren Wells - Breathe On It (Official Lyric Video) - Tauren Wells</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Maiah Manser - Feeling it All (Official Music Video)</v>
+        <v>Holly Humberstone - To Love Somebody (Official Video)</v>
       </c>
       <c r="B88" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=JMYvXleIwfU</v>
+        <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
       </c>
       <c r="D88" t="str">
         <v>2026-02-06</v>
@@ -3722,10 +3722,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G88" t="str">
-        <v>3:05</v>
+        <v>3:59</v>
       </c>
       <c r="H88" t="str">
-        <v>Maiah Manser</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Maiah Manser - Feeling it All (Official Music Video) - Maiah Manser</v>
+        <v>Holly Humberstone - To Love Somebody (Official Video) - Holly Humberstone</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Taylor Austin Dye - Man For That (Official Music Video)</v>
+        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
       </c>
       <c r="B89" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=vOzX-o11seI</v>
+        <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
       </c>
       <c r="D89" t="str">
         <v>2026-02-06</v>
@@ -3760,10 +3760,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G89" t="str">
-        <v>2:27</v>
+        <v>2:56</v>
       </c>
       <c r="H89" t="str">
-        <v>Taylor Austin Dye</v>
+        <v>Cliff Richard</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Taylor Austin Dye - Man For That (Official Music Video) - Taylor Austin Dye</v>
+        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018) - Cliff Richard</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Chelsea Cutler - BAD (Official Video)</v>
+        <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
       </c>
       <c r="B90" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=86k4E6ydHVU</v>
+        <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
       </c>
       <c r="D90" t="str">
         <v>2026-02-06</v>
@@ -3798,10 +3798,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G90" t="str">
-        <v>2:34</v>
+        <v>3:46</v>
       </c>
       <c r="H90" t="str">
-        <v>Chelsea Cutler</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Chelsea Cutler - BAD (Official Video) - Chelsea Cutler</v>
+        <v>Jessie Ware - I Could Get Used To This (Official Video) - Jessie Ware</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video)</v>
+        <v>Bella White - Dream Song (Official Audio)</v>
       </c>
       <c r="B91" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=-UWIFAiOOPE</v>
+        <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
       </c>
       <c r="D91" t="str">
         <v>2026-02-06</v>
@@ -3836,10 +3836,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G91" t="str">
-        <v>3:13</v>
+        <v>4:37</v>
       </c>
       <c r="H91" t="str">
-        <v>Ashley Kutcher</v>
+        <v>Bella White</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video) - Ashley Kutcher</v>
+        <v>Bella White - Dream Song (Official Audio) - Bella White</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Louis Tomlinson - Dark To Light (Visualiser)</v>
+        <v>Ryan Wright - Film School Kids (Official Video)</v>
       </c>
       <c r="B92" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=02QyA29poAM</v>
+        <v>https://www.youtube.com/watch?v=pnAz9RwGSek</v>
       </c>
       <c r="D92" t="str">
         <v>2026-02-06</v>
@@ -3874,10 +3874,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G92" t="str">
-        <v>3:13</v>
+        <v>4:06</v>
       </c>
       <c r="H92" t="str">
-        <v>Louis Tomlinson</v>
+        <v>Ryan Wright</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Louis Tomlinson - Dark To Light (Visualiser) - Louis Tomlinson</v>
+        <v>Ryan Wright - Film School Kids (Official Video) - Ryan Wright</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>CAIN - So Long Sad Songs (Lyric Video)</v>
+        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer)</v>
       </c>
       <c r="B93" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=feOv8nufa_I</v>
+        <v>https://www.youtube.com/watch?v=u7aPv2saz_I</v>
       </c>
       <c r="D93" t="str">
         <v>2026-02-06</v>
@@ -3912,10 +3912,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G93" t="str">
-        <v>3:08</v>
+        <v>3:54</v>
       </c>
       <c r="H93" t="str">
-        <v>CAIN</v>
+        <v>Dove Cameron</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>CAIN - So Long Sad Songs (Lyric Video) - CAIN</v>
+        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer) - Dove Cameron</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Harry Styles - Aperture (Official Audio)</v>
+        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video)</v>
       </c>
       <c r="B94" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=rA_eCxPay7E</v>
+        <v>https://www.youtube.com/watch?v=WGb8KVdqs6k</v>
       </c>
       <c r="D94" t="str">
         <v>2026-02-06</v>
@@ -3950,10 +3950,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G94" t="str">
-        <v>5:14</v>
+        <v>4:10</v>
       </c>
       <c r="H94" t="str">
-        <v>Harry Styles</v>
+        <v>Parker McCollum</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Harry Styles - Aperture (Official Audio) - Harry Styles</v>
+        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video) - Parker McCollum</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Lana Lubany - BAD IDEA (Official Video)</v>
+        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video)</v>
       </c>
       <c r="B95" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
+        <v>https://www.youtube.com/watch?v=X1ZeY4Y3l1M</v>
       </c>
       <c r="D95" t="str">
         <v>2026-02-06</v>
@@ -3988,10 +3988,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G95" t="str">
-        <v>2:59</v>
+        <v>3:26</v>
       </c>
       <c r="H95" t="str">
-        <v>Lana Lubany</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Lana Lubany - BAD IDEA (Official Video) - Lana Lubany</v>
+        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video) - Matt Hansen</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Def Leppard - Rejoice (Lyric Video)</v>
+        <v>Louis Tomlinson - Imposter (Official Video)</v>
       </c>
       <c r="B96" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=zy2TLLeNgp0</v>
+        <v>https://www.youtube.com/watch?v=rzuD5szQhso</v>
       </c>
       <c r="D96" t="str">
         <v>2026-02-06</v>
@@ -4026,10 +4026,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G96" t="str">
-        <v>4:21</v>
+        <v>2:56</v>
       </c>
       <c r="H96" t="str">
-        <v>DEF LEPPARD</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Def Leppard - Rejoice (Lyric Video) - DEF LEPPARD</v>
+        <v>Louis Tomlinson - Imposter (Official Video) - Louis Tomlinson</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Dermot Kennedy - Funeral (Official Music Video)</v>
+        <v>Mitchell Tenpenny - You Phase (Official Music Video)</v>
       </c>
       <c r="B97" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=JzOUJZPky6o</v>
+        <v>https://www.youtube.com/watch?v=UPuK6wV5Zco</v>
       </c>
       <c r="D97" t="str">
         <v>2026-02-06</v>
@@ -4064,10 +4064,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G97" t="str">
-        <v>4:09</v>
+        <v>2:56</v>
       </c>
       <c r="H97" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Mitchell Tenpenny</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Dermot Kennedy - Funeral (Official Music Video) - Dermot Kennedy</v>
+        <v>Mitchell Tenpenny - You Phase (Official Music Video) - Mitchell Tenpenny</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video)</v>
+        <v>Tauren Wells - Breathe On It (Official Lyric Video)</v>
       </c>
       <c r="B98" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=kfF0bVZMCw0</v>
+        <v>https://www.youtube.com/watch?v=9hW9sNMn2A0</v>
       </c>
       <c r="D98" t="str">
         <v>2026-02-06</v>
@@ -4102,10 +4102,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G98" t="str">
-        <v>2:34</v>
+        <v>4:01</v>
       </c>
       <c r="H98" t="str">
-        <v>Lauren Sanderson</v>
+        <v>Tauren Wells</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video) - Lauren Sanderson</v>
+        <v>Tauren Wells - Breathe On It (Official Lyric Video) - Tauren Wells</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show]</v>
+        <v>Maiah Manser - Feeling it All (Official Music Video)</v>
       </c>
       <c r="B99" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=dLzpNstMHZY</v>
+        <v>https://www.youtube.com/watch?v=JMYvXleIwfU</v>
       </c>
       <c r="D99" t="str">
         <v>2026-02-06</v>
@@ -4140,10 +4140,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G99" t="str">
-        <v>3:10</v>
+        <v>3:05</v>
       </c>
       <c r="H99" t="str">
-        <v>Olivia Dean</v>
+        <v>Maiah Manser</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show] - Olivia Dean</v>
+        <v>Maiah Manser - Feeling it All (Official Music Video) - Maiah Manser</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel)</v>
+        <v>Taylor Austin Dye - Man For That (Official Music Video)</v>
       </c>
       <c r="B100" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=fo_j8Fqag8I</v>
+        <v>https://www.youtube.com/watch?v=vOzX-o11seI</v>
       </c>
       <c r="D100" t="str">
         <v>2026-02-06</v>
@@ -4178,10 +4178,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G100" t="str">
-        <v>3:21</v>
+        <v>2:27</v>
       </c>
       <c r="H100" t="str">
-        <v>David Guetta and Tones And I</v>
+        <v>Taylor Austin Dye</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel) - David Guetta and Tones And I</v>
+        <v>Taylor Austin Dye - Man For That (Official Music Video) - Taylor Austin Dye</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>The Avett Brothers - Matrimony (Official Video)</v>
+        <v>Chelsea Cutler - BAD (Official Video)</v>
       </c>
       <c r="B101" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=7sD9-MtV9CY</v>
+        <v>https://www.youtube.com/watch?v=86k4E6ydHVU</v>
       </c>
       <c r="D101" t="str">
         <v>2026-02-06</v>
@@ -4216,10 +4216,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G101" t="str">
-        <v>3:06</v>
+        <v>2:34</v>
       </c>
       <c r="H101" t="str">
-        <v>The Avett Brothers</v>
+        <v>Chelsea Cutler</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,7 +4231,7 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>The Avett Brothers - Matrimony (Official Video) - The Avett Brothers</v>
+        <v>Chelsea Cutler - BAD (Official Video) - Chelsea Cutler</v>
       </c>
     </row>
     <row r="102">

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Cliff Richard - Golden (75th Birthday Concert, Royal Albert Hall, 14 Oct 2015)</v>
       </c>
       <c r="B2" t="str">
-        <v>4 hours ago</v>
+        <v>5 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=JZM2tHMmqck</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>4 hours ago</v>
+        <v>5 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>4:37</v>
@@ -477,7 +477,7 @@
         <v>Bryan Adams - Hey Baby</v>
       </c>
       <c r="B3" t="str">
-        <v>5 hours ago</v>
+        <v>6 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=aYcAl98fDYk</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>5 hours ago</v>
+        <v>6 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>3:54</v>
@@ -515,7 +515,7 @@
         <v>Anna Graves - Ashes &amp; Smoke (Official Audio)</v>
       </c>
       <c r="B4" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=n90qajAa6oQ</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>3:06</v>
@@ -553,7 +553,7 @@
         <v>George Birge - Ride, Ride, Ride (Feat. Luke Bryan) [Official Music Video]</v>
       </c>
       <c r="B5" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=rWGpexrWhJE</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>3:21</v>
@@ -591,7 +591,7 @@
         <v>Morrissey - Notre-Dame (Official Lyric Video)</v>
       </c>
       <c r="B6" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=Q44JiUwa2Xg</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v>4:09</v>
@@ -629,7 +629,7 @@
         <v>Nick Jonas - Sweet To Me (Official Lyric Video)</v>
       </c>
       <c r="B7" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=Jy2dqfKWY-c</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="G7" t="str">
         <v>4:18</v>
@@ -667,7 +667,7 @@
         <v>Charlie Puth - Cry (with Kenny G) [Official Audio]</v>
       </c>
       <c r="B8" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=Bam3O09kLAQ</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="G8" t="str">
         <v>3:08</v>
@@ -705,7 +705,7 @@
         <v>Olivia Newton-John - Serenity (Visualizer) (Official)</v>
       </c>
       <c r="B9" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=F-usO6XVXcs</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="G9" t="str">
         <v>4:03</v>
@@ -743,7 +743,7 @@
         <v>The Warning, Carín León - Love To Be Loved (Official Video)</v>
       </c>
       <c r="B10" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=8DUQ5vPcz9o</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="G10" t="str">
         <v>3:01</v>
@@ -781,7 +781,7 @@
         <v>Iman Fandi - Tip Toes (Official Dance Visualiser)</v>
       </c>
       <c r="B11" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=WRvCKHSm12Y</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="G11" t="str">
         <v>3:05</v>
@@ -819,7 +819,7 @@
         <v>Megan Moroney - Cloud 9 (Official Lyric Video)</v>
       </c>
       <c r="B12" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=BiNIdrm9miE</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="G12" t="str">
         <v>3:34</v>
@@ -857,7 +857,7 @@
         <v>Dylan Davidson - Escape Artist</v>
       </c>
       <c r="B13" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=iKW4wCw_LoY</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="G13" t="str">
         <v>3:15</v>
@@ -895,7 +895,7 @@
         <v>LADY GAGA - ABRACADABRA (LIVE AT THE 2026 GRAMMYS)</v>
       </c>
       <c r="B14" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=Rn89mUndYbo</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G14" t="str">
         <v>4:16</v>
@@ -933,7 +933,7 @@
         <v>Carlos Vives - Te Dedico (Official Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=H8KW0SgW99I</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G15" t="str">
         <v>3:53</v>
@@ -971,7 +971,7 @@
         <v>Monsieur Periné, Jossman - MUCHO CON DEMASIAO' (Video Oficial)</v>
       </c>
       <c r="B16" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=mpmrrvhLzZ0</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G16" t="str">
         <v>2:25</v>
@@ -1009,7 +1009,7 @@
         <v>The Happy Fits - Tenderly (Official Audio)</v>
       </c>
       <c r="B17" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=10hExzTW4Hc</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G17" t="str">
         <v>4:09</v>
@@ -1047,7 +1047,7 @@
         <v>chase (lyric vid) - Michael Aldag</v>
       </c>
       <c r="B18" t="str">
-        <v>19 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=QASMKs97wec</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>19 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="G18" t="str">
         <v>2:45</v>
@@ -1085,7 +1085,7 @@
         <v>Dermot Kennedy - Funeral (Live Acoustic Session)</v>
       </c>
       <c r="B19" t="str">
-        <v>19 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=RyR1xAw9edU</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>19 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="G19" t="str">
         <v>4:07</v>
@@ -1123,7 +1123,7 @@
         <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Official Video)</v>
       </c>
       <c r="B20" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=OYtHvS7n7ic</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G20" t="str">
         <v>4:34</v>
@@ -1161,7 +1161,7 @@
         <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Official Music Video)</v>
       </c>
       <c r="B21" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=XKvzT2CTnLE</v>
@@ -1173,7 +1173,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G21" t="str">
         <v>5:14</v>
@@ -1199,7 +1199,7 @@
         <v>Michael Bolton | Cupid (Official Visualizer)</v>
       </c>
       <c r="B22" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=1XDIbfJ_OGw</v>
@@ -1211,7 +1211,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G22" t="str">
         <v>3:11</v>
@@ -2035,7 +2035,7 @@
         <v>JOSEPH - Water in the Room (Official Music Video)</v>
       </c>
       <c r="B44" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C44" t="str">
         <v>https://www.youtube.com/watch?v=tNmT47k6MjM</v>
@@ -2047,7 +2047,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G44" t="str">
         <v>3:10</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Cliff Richard - Golden (75th Birthday Concert, Royal Albert Hall, 14 Oct 2015)</v>
       </c>
       <c r="B2" t="str">
-        <v>5 hours ago</v>
+        <v>6 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=JZM2tHMmqck</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>5 hours ago</v>
+        <v>6 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>4:37</v>
@@ -477,7 +477,7 @@
         <v>Bryan Adams - Hey Baby</v>
       </c>
       <c r="B3" t="str">
-        <v>6 hours ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=aYcAl98fDYk</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>6 hours ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>3:54</v>
@@ -515,7 +515,7 @@
         <v>Anna Graves - Ashes &amp; Smoke (Official Audio)</v>
       </c>
       <c r="B4" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=n90qajAa6oQ</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>3:06</v>
@@ -553,7 +553,7 @@
         <v>George Birge - Ride, Ride, Ride (Feat. Luke Bryan) [Official Music Video]</v>
       </c>
       <c r="B5" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=rWGpexrWhJE</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>3:21</v>
@@ -591,7 +591,7 @@
         <v>Morrissey - Notre-Dame (Official Lyric Video)</v>
       </c>
       <c r="B6" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=Q44JiUwa2Xg</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v>4:09</v>
@@ -629,7 +629,7 @@
         <v>Nick Jonas - Sweet To Me (Official Lyric Video)</v>
       </c>
       <c r="B7" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=Jy2dqfKWY-c</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="G7" t="str">
         <v>4:18</v>
@@ -667,7 +667,7 @@
         <v>Charlie Puth - Cry (with Kenny G) [Official Audio]</v>
       </c>
       <c r="B8" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=Bam3O09kLAQ</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="G8" t="str">
         <v>3:08</v>
@@ -705,7 +705,7 @@
         <v>Olivia Newton-John - Serenity (Visualizer) (Official)</v>
       </c>
       <c r="B9" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=F-usO6XVXcs</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="G9" t="str">
         <v>4:03</v>
@@ -743,7 +743,7 @@
         <v>The Warning, Carín León - Love To Be Loved (Official Video)</v>
       </c>
       <c r="B10" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=8DUQ5vPcz9o</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="G10" t="str">
         <v>3:01</v>
@@ -781,7 +781,7 @@
         <v>Iman Fandi - Tip Toes (Official Dance Visualiser)</v>
       </c>
       <c r="B11" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=WRvCKHSm12Y</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="G11" t="str">
         <v>3:05</v>
@@ -819,7 +819,7 @@
         <v>Megan Moroney - Cloud 9 (Official Lyric Video)</v>
       </c>
       <c r="B12" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=BiNIdrm9miE</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="G12" t="str">
         <v>3:34</v>
@@ -857,7 +857,7 @@
         <v>Dylan Davidson - Escape Artist</v>
       </c>
       <c r="B13" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=iKW4wCw_LoY</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="G13" t="str">
         <v>3:15</v>
@@ -895,7 +895,7 @@
         <v>LADY GAGA - ABRACADABRA (LIVE AT THE 2026 GRAMMYS)</v>
       </c>
       <c r="B14" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=Rn89mUndYbo</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="G14" t="str">
         <v>4:16</v>
@@ -933,7 +933,7 @@
         <v>Carlos Vives - Te Dedico (Official Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=H8KW0SgW99I</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G15" t="str">
         <v>3:53</v>
@@ -971,7 +971,7 @@
         <v>Monsieur Periné, Jossman - MUCHO CON DEMASIAO' (Video Oficial)</v>
       </c>
       <c r="B16" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=mpmrrvhLzZ0</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G16" t="str">
         <v>2:25</v>
@@ -1009,7 +1009,7 @@
         <v>The Happy Fits - Tenderly (Official Audio)</v>
       </c>
       <c r="B17" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=10hExzTW4Hc</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="G17" t="str">
         <v>4:09</v>
@@ -1047,7 +1047,7 @@
         <v>chase (lyric vid) - Michael Aldag</v>
       </c>
       <c r="B18" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=QASMKs97wec</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G18" t="str">
         <v>2:45</v>
@@ -1085,7 +1085,7 @@
         <v>Dermot Kennedy - Funeral (Live Acoustic Session)</v>
       </c>
       <c r="B19" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=RyR1xAw9edU</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G19" t="str">
         <v>4:07</v>
@@ -1123,7 +1123,7 @@
         <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Official Video)</v>
       </c>
       <c r="B20" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=OYtHvS7n7ic</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G20" t="str">
         <v>4:34</v>
@@ -1161,7 +1161,7 @@
         <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Official Music Video)</v>
       </c>
       <c r="B21" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=XKvzT2CTnLE</v>
@@ -1173,7 +1173,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G21" t="str">
         <v>5:14</v>
@@ -1199,7 +1199,7 @@
         <v>Michael Bolton | Cupid (Official Visualizer)</v>
       </c>
       <c r="B22" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=1XDIbfJ_OGw</v>
@@ -1211,7 +1211,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G22" t="str">
         <v>3:11</v>
@@ -1959,7 +1959,7 @@
         <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered)</v>
       </c>
       <c r="B42" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C42" t="str">
         <v>https://www.youtube.com/watch?v=I7a-pDZFE7U</v>
@@ -1971,7 +1971,7 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G42" t="str">
         <v>4:38</v>
@@ -3099,7 +3099,7 @@
         <v>Beck - Love (Audio)</v>
       </c>
       <c r="B72" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C72" t="str">
         <v>https://www.youtube.com/watch?v=ByABj3Xof1I</v>
@@ -3111,7 +3111,7 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G72" t="str">
         <v>3:14</v>
@@ -3213,7 +3213,7 @@
         <v>Jason Derulo - Sexy For Me [Official Music Video]</v>
       </c>
       <c r="B75" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C75" t="str">
         <v>https://www.youtube.com/watch?v=9ST-eBNL0NU</v>
@@ -3225,7 +3225,7 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G75" t="str">
         <v>2:10</v>
@@ -3251,7 +3251,7 @@
         <v>Lights - COME GET YOUR GIRL</v>
       </c>
       <c r="B76" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C76" t="str">
         <v>https://www.youtube.com/watch?v=EhzX2y5MpSM</v>
@@ -3263,7 +3263,7 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G76" t="str">
         <v>3:52</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Cliff Richard - Golden (75th Birthday Concert, Royal Albert Hall, 14 Oct 2015)</v>
       </c>
       <c r="B2" t="str">
-        <v>6 hours ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=JZM2tHMmqck</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>6 hours ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>4:37</v>
@@ -477,7 +477,7 @@
         <v>Bryan Adams - Hey Baby</v>
       </c>
       <c r="B3" t="str">
-        <v>7 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=aYcAl98fDYk</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>7 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>3:54</v>
@@ -515,7 +515,7 @@
         <v>Anna Graves - Ashes &amp; Smoke (Official Audio)</v>
       </c>
       <c r="B4" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=n90qajAa6oQ</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>3:06</v>
@@ -553,7 +553,7 @@
         <v>George Birge - Ride, Ride, Ride (Feat. Luke Bryan) [Official Music Video]</v>
       </c>
       <c r="B5" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=rWGpexrWhJE</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>3:21</v>
@@ -591,7 +591,7 @@
         <v>Morrissey - Notre-Dame (Official Lyric Video)</v>
       </c>
       <c r="B6" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=Q44JiUwa2Xg</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v>4:09</v>
@@ -629,7 +629,7 @@
         <v>Nick Jonas - Sweet To Me (Official Lyric Video)</v>
       </c>
       <c r="B7" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=Jy2dqfKWY-c</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G7" t="str">
         <v>4:18</v>
@@ -667,7 +667,7 @@
         <v>Charlie Puth - Cry (with Kenny G) [Official Audio]</v>
       </c>
       <c r="B8" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=Bam3O09kLAQ</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G8" t="str">
         <v>3:08</v>
@@ -705,7 +705,7 @@
         <v>Olivia Newton-John - Serenity (Visualizer) (Official)</v>
       </c>
       <c r="B9" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=F-usO6XVXcs</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G9" t="str">
         <v>4:03</v>
@@ -743,7 +743,7 @@
         <v>The Warning, Carín León - Love To Be Loved (Official Video)</v>
       </c>
       <c r="B10" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=8DUQ5vPcz9o</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G10" t="str">
         <v>3:01</v>
@@ -781,7 +781,7 @@
         <v>Iman Fandi - Tip Toes (Official Dance Visualiser)</v>
       </c>
       <c r="B11" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=WRvCKHSm12Y</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G11" t="str">
         <v>3:05</v>
@@ -819,7 +819,7 @@
         <v>Megan Moroney - Cloud 9 (Official Lyric Video)</v>
       </c>
       <c r="B12" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=BiNIdrm9miE</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G12" t="str">
         <v>3:34</v>
@@ -857,7 +857,7 @@
         <v>Dylan Davidson - Escape Artist</v>
       </c>
       <c r="B13" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=iKW4wCw_LoY</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G13" t="str">
         <v>3:15</v>
@@ -895,7 +895,7 @@
         <v>LADY GAGA - ABRACADABRA (LIVE AT THE 2026 GRAMMYS)</v>
       </c>
       <c r="B14" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=Rn89mUndYbo</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G14" t="str">
         <v>4:16</v>
@@ -933,7 +933,7 @@
         <v>Carlos Vives - Te Dedico (Official Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=H8KW0SgW99I</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="G15" t="str">
         <v>3:53</v>
@@ -971,7 +971,7 @@
         <v>Monsieur Periné, Jossman - MUCHO CON DEMASIAO' (Video Oficial)</v>
       </c>
       <c r="B16" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=mpmrrvhLzZ0</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="G16" t="str">
         <v>2:25</v>
@@ -1009,7 +1009,7 @@
         <v>The Happy Fits - Tenderly (Official Audio)</v>
       </c>
       <c r="B17" t="str">
-        <v>19 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=10hExzTW4Hc</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>19 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="G17" t="str">
         <v>4:09</v>
@@ -1047,7 +1047,7 @@
         <v>chase (lyric vid) - Michael Aldag</v>
       </c>
       <c r="B18" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=QASMKs97wec</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G18" t="str">
         <v>2:45</v>
@@ -1085,7 +1085,7 @@
         <v>Dermot Kennedy - Funeral (Live Acoustic Session)</v>
       </c>
       <c r="B19" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=RyR1xAw9edU</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G19" t="str">
         <v>4:07</v>
@@ -1123,7 +1123,7 @@
         <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Official Video)</v>
       </c>
       <c r="B20" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=OYtHvS7n7ic</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G20" t="str">
         <v>4:34</v>
@@ -1161,7 +1161,7 @@
         <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Official Music Video)</v>
       </c>
       <c r="B21" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=XKvzT2CTnLE</v>
@@ -1173,7 +1173,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G21" t="str">
         <v>5:14</v>
@@ -1199,7 +1199,7 @@
         <v>Michael Bolton | Cupid (Official Visualizer)</v>
       </c>
       <c r="B22" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=1XDIbfJ_OGw</v>
@@ -1211,7 +1211,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G22" t="str">
         <v>3:11</v>
@@ -1769,7 +1769,7 @@
         <v>Take That - Once You've Tasted Love (Live on Pebble Mill, 1992)</v>
       </c>
       <c r="B37" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C37" t="str">
         <v>https://www.youtube.com/watch?v=dOeoDOueESk</v>
@@ -1781,7 +1781,7 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G37" t="str">
         <v>3:36</v>
@@ -3061,7 +3061,7 @@
         <v>Teddy Swims - Need You More (Live - Green Room Sessions)</v>
       </c>
       <c r="B71" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C71" t="str">
         <v>https://www.youtube.com/watch?v=1ugf5aaY4pY</v>
@@ -3073,7 +3073,7 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G71" t="str">
         <v>3:16</v>
@@ -3175,7 +3175,7 @@
         <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show</v>
       </c>
       <c r="B74" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C74" t="str">
         <v>https://www.youtube.com/watch?v=ylifHFJWJ_c</v>
@@ -3187,7 +3187,7 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G74" t="str">
         <v>4:10</v>
@@ -3631,7 +3631,7 @@
         <v>Neal Francis - Back It Up (Live At The Salt Shed)</v>
       </c>
       <c r="B86" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C86" t="str">
         <v>https://www.youtube.com/watch?v=46iZEdsxjC0</v>
@@ -3643,7 +3643,7 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G86" t="str">
         <v>5:01</v>
@@ -3669,7 +3669,7 @@
         <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
       </c>
       <c r="B87" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
         <v>https://www.youtube.com/watch?v=K2nG1Uukz7E</v>
@@ -3681,7 +3681,7 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G87" t="str">
         <v>4:12</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L197"/>
+  <dimension ref="A1:L196"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -439,7 +439,7 @@
         <v>Cliff Richard - Golden (75th Birthday Concert, Royal Albert Hall, 14 Oct 2015)</v>
       </c>
       <c r="B2" t="str">
-        <v>7 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=JZM2tHMmqck</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>7 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>4:37</v>
@@ -477,7 +477,7 @@
         <v>Bryan Adams - Hey Baby</v>
       </c>
       <c r="B3" t="str">
-        <v>8 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=aYcAl98fDYk</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>8 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>3:54</v>
@@ -515,7 +515,7 @@
         <v>Anna Graves - Ashes &amp; Smoke (Official Audio)</v>
       </c>
       <c r="B4" t="str">
-        <v>11 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=n90qajAa6oQ</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>11 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>3:06</v>
@@ -553,7 +553,7 @@
         <v>George Birge - Ride, Ride, Ride (Feat. Luke Bryan) [Official Music Video]</v>
       </c>
       <c r="B5" t="str">
-        <v>11 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=rWGpexrWhJE</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>11 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>3:21</v>
@@ -591,7 +591,7 @@
         <v>Morrissey - Notre-Dame (Official Lyric Video)</v>
       </c>
       <c r="B6" t="str">
-        <v>11 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=Q44JiUwa2Xg</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>11 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v>4:09</v>
@@ -629,7 +629,7 @@
         <v>Nick Jonas - Sweet To Me (Official Lyric Video)</v>
       </c>
       <c r="B7" t="str">
-        <v>11 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=Jy2dqfKWY-c</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>11 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G7" t="str">
         <v>4:18</v>
@@ -667,7 +667,7 @@
         <v>Charlie Puth - Cry (with Kenny G) [Official Audio]</v>
       </c>
       <c r="B8" t="str">
-        <v>11 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=Bam3O09kLAQ</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>11 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G8" t="str">
         <v>3:08</v>
@@ -705,7 +705,7 @@
         <v>Olivia Newton-John - Serenity (Visualizer) (Official)</v>
       </c>
       <c r="B9" t="str">
-        <v>11 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=F-usO6XVXcs</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>11 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G9" t="str">
         <v>4:03</v>
@@ -743,7 +743,7 @@
         <v>The Warning, Carín León - Love To Be Loved (Official Video)</v>
       </c>
       <c r="B10" t="str">
-        <v>11 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=8DUQ5vPcz9o</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>11 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G10" t="str">
         <v>3:01</v>
@@ -781,7 +781,7 @@
         <v>Iman Fandi - Tip Toes (Official Dance Visualiser)</v>
       </c>
       <c r="B11" t="str">
-        <v>11 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=WRvCKHSm12Y</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>11 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G11" t="str">
         <v>3:05</v>
@@ -819,7 +819,7 @@
         <v>Megan Moroney - Cloud 9 (Official Lyric Video)</v>
       </c>
       <c r="B12" t="str">
-        <v>11 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=BiNIdrm9miE</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>11 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G12" t="str">
         <v>3:34</v>
@@ -857,7 +857,7 @@
         <v>Dylan Davidson - Escape Artist</v>
       </c>
       <c r="B13" t="str">
-        <v>11 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=iKW4wCw_LoY</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>11 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G13" t="str">
         <v>3:15</v>
@@ -895,7 +895,7 @@
         <v>LADY GAGA - ABRACADABRA (LIVE AT THE 2026 GRAMMYS)</v>
       </c>
       <c r="B14" t="str">
-        <v>17 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=Rn89mUndYbo</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>17 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="G14" t="str">
         <v>4:16</v>
@@ -933,7 +933,7 @@
         <v>Carlos Vives - Te Dedico (Official Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>16 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=H8KW0SgW99I</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>16 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G15" t="str">
         <v>3:53</v>
@@ -971,7 +971,7 @@
         <v>Monsieur Periné, Jossman - MUCHO CON DEMASIAO' (Video Oficial)</v>
       </c>
       <c r="B16" t="str">
-        <v>16 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=mpmrrvhLzZ0</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>16 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G16" t="str">
         <v>2:25</v>
@@ -1009,7 +1009,7 @@
         <v>The Happy Fits - Tenderly (Official Audio)</v>
       </c>
       <c r="B17" t="str">
-        <v>20 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=10hExzTW4Hc</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>20 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G17" t="str">
         <v>4:09</v>
@@ -1047,7 +1047,7 @@
         <v>chase (lyric vid) - Michael Aldag</v>
       </c>
       <c r="B18" t="str">
-        <v>22 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=QASMKs97wec</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>22 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G18" t="str">
         <v>2:45</v>
@@ -1085,7 +1085,7 @@
         <v>Dermot Kennedy - Funeral (Live Acoustic Session)</v>
       </c>
       <c r="B19" t="str">
-        <v>22 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=RyR1xAw9edU</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>22 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G19" t="str">
         <v>4:07</v>
@@ -1123,7 +1123,7 @@
         <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Official Video)</v>
       </c>
       <c r="B20" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=OYtHvS7n7ic</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G20" t="str">
         <v>4:34</v>
@@ -1161,7 +1161,7 @@
         <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Official Music Video)</v>
       </c>
       <c r="B21" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=XKvzT2CTnLE</v>
@@ -1173,7 +1173,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G21" t="str">
         <v>5:14</v>
@@ -1313,7 +1313,7 @@
         <v>Freya Skye - why'd you have to call</v>
       </c>
       <c r="B25" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=75o0FuwCdaA</v>
@@ -1325,7 +1325,7 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G25" t="str">
         <v>4:19</v>
@@ -1351,7 +1351,7 @@
         <v>Jessie J - FEEL IT ON ME (Lyric Visualiser) (Official Lyric Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=DGmbe49F8aI</v>
@@ -1363,7 +1363,7 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G26" t="str">
         <v>2:30</v>
@@ -1427,7 +1427,7 @@
         <v>Clara Mae - Never Been Yours ft. Bob John Holt</v>
       </c>
       <c r="B28" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=HtVuKBlBuPg</v>
@@ -1439,7 +1439,7 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G28" t="str">
         <v>2:33</v>
@@ -1465,7 +1465,7 @@
         <v>Metric - Victim of Luck (Official Music Video)</v>
       </c>
       <c r="B29" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=shmhTOUd8mA</v>
@@ -1477,7 +1477,7 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G29" t="str">
         <v>3:25</v>
@@ -1617,7 +1617,7 @@
         <v>Bob Moses - Need You Tonight (INXS Cover) - Brooklyn Mirage 2023</v>
       </c>
       <c r="B33" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C33" t="str">
         <v>https://www.youtube.com/watch?v=CoCqPwDIBOA</v>
@@ -1629,7 +1629,7 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G33" t="str">
         <v>3:08</v>
@@ -1655,7 +1655,7 @@
         <v>Marc Anthony - Un Mal Sueño (Visualizer)</v>
       </c>
       <c r="B34" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=18yZq5xtke4</v>
@@ -1667,7 +1667,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G34" t="str">
         <v>3:28</v>
@@ -1693,7 +1693,7 @@
         <v>Marc Anthony - Contra La Corriente (Visualizer)</v>
       </c>
       <c r="B35" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=IGLmJ71oHhQ</v>
@@ -1705,7 +1705,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G35" t="str">
         <v>5:05</v>
@@ -1731,7 +1731,7 @@
         <v>Loreen - Feels Like Heaven</v>
       </c>
       <c r="B36" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=BQc97moyQBg</v>
@@ -1743,7 +1743,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G36" t="str">
         <v>3:14</v>
@@ -1807,7 +1807,7 @@
         <v>Paul McCartney, Wings - Nineteen Hundred And Eighty Five (Visualiser)</v>
       </c>
       <c r="B38" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=a4AIjUHuWpU</v>
@@ -1819,7 +1819,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G38" t="str">
         <v>5:31</v>
@@ -1883,7 +1883,7 @@
         <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music</v>
       </c>
       <c r="B40" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=KdsHxyl4bE8</v>
@@ -1895,7 +1895,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G40" t="str">
         <v>4:58</v>
@@ -1921,7 +1921,7 @@
         <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield, CA (2026)</v>
       </c>
       <c r="B41" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=Mwkl_Cz_SG8</v>
@@ -1933,7 +1933,7 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G41" t="str">
         <v>5:08</v>
@@ -3023,7 +3023,7 @@
         <v>Demi Lovato - Ghost (Live)</v>
       </c>
       <c r="B70" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C70" t="str">
         <v>https://www.youtube.com/watch?v=E-ECwdRndVA</v>
@@ -3035,7 +3035,7 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G70" t="str">
         <v>4:05</v>
@@ -3137,7 +3137,7 @@
         <v>The Offspring - Looking Out For #1 | Live in Spokane, WA (2026)</v>
       </c>
       <c r="B73" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C73" t="str">
         <v>https://www.youtube.com/watch?v=2HSbo51EFNg</v>
@@ -3149,7 +3149,7 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G73" t="str">
         <v>2:57</v>
@@ -3517,7 +3517,7 @@
         <v>SIENNA SPIRO - Die On This Hill (Official Music Video)</v>
       </c>
       <c r="B83" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C83" t="str">
         <v>https://www.youtube.com/watch?v=5RNy_1odv20</v>
@@ -3529,7 +3529,7 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G83" t="str">
         <v>4:01</v>
@@ -3555,7 +3555,7 @@
         <v>Amazon Music presents: Sienna Spiro - You Stole The Show</v>
       </c>
       <c r="B84" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C84" t="str">
         <v>https://www.youtube.com/watch?v=stYIRyCLN4Y</v>
@@ -3567,7 +3567,7 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G84" t="str">
         <v>3:24</v>
@@ -3593,7 +3593,7 @@
         <v>Harry Styles - Aperture (Official Video)</v>
       </c>
       <c r="B85" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C85" t="str">
         <v>https://www.youtube.com/watch?v=7sxVHYZ_PnA</v>
@@ -3605,7 +3605,7 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G85" t="str">
         <v>5:52</v>
@@ -5604,13 +5604,13 @@
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>What It Feels Like (feat. Daya)</v>
+        <v>What It Feels Like</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/what-it-feels-like-feat-daya/1870886919</v>
+        <v>https://music.apple.com/us/song/what-it-feels-like/1870886919</v>
       </c>
       <c r="D138" t="str">
         <v>2026-02-06</v>
@@ -5619,7 +5619,7 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>What It Feels Like (feat. Daya) - Single</v>
+        <v>What It Feels Like - Single</v>
       </c>
       <c r="G138" t="str">
         <v>2:18</v>
@@ -5634,10 +5634,10 @@
         <v>https://music.apple.com/us/artist/dillon-francis/366828522</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/what-it-feels-like-feat-daya/1870886918</v>
+        <v>https://music.apple.com/us/album/what-it-feels-like/1870886918</v>
       </c>
       <c r="L138" t="str">
-        <v>What It Feels Like (feat. Daya) - Dillon Francis</v>
+        <v>What It Feels Like - Dillon Francis</v>
       </c>
     </row>
     <row r="139">
@@ -7200,13 +7200,13 @@
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Thecuntiest</v>
+        <v>Big Deal</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/thecuntiest/1873623673</v>
+        <v>https://music.apple.com/us/song/big-deal/1871607668</v>
       </c>
       <c r="D180" t="str">
         <v>2026-02-06</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Thecuntiest - Single</v>
+        <v>Big Deal - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>2:23</v>
+        <v>3:47</v>
       </c>
       <c r="H180" t="str">
-        <v>Spilata</v>
+        <v>In Color</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/spilata/1734141692</v>
+        <v>https://music.apple.com/us/artist/in-color/1788977129</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/thecuntiest/1873623672</v>
+        <v>https://music.apple.com/us/album/big-deal/1871607667</v>
       </c>
       <c r="L180" t="str">
-        <v>Thecuntiest - Spilata</v>
+        <v>Big Deal - In Color</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Big Deal</v>
+        <v>Buy What U Want</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/big-deal/1871607668</v>
+        <v>https://music.apple.com/us/song/buy-what-u-want/1872511530</v>
       </c>
       <c r="D181" t="str">
         <v>2026-02-06</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Big Deal - Single</v>
+        <v>Road To Osshland III - EP</v>
       </c>
       <c r="G181" t="str">
         <v>3:47</v>
       </c>
       <c r="H181" t="str">
-        <v>In Color</v>
+        <v>Black Fortune</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/in-color/1788977129</v>
+        <v>https://music.apple.com/us/artist/black-fortune/557044567</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/big-deal/1871607667</v>
+        <v>https://music.apple.com/us/album/buy-what-u-want/1872511292</v>
       </c>
       <c r="L181" t="str">
-        <v>Big Deal - In Color</v>
+        <v>Buy What U Want - Black Fortune</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Buy What U Want</v>
+        <v>Common Ground</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/buy-what-u-want/1872511530</v>
+        <v>https://music.apple.com/us/song/common-ground/1852654933</v>
       </c>
       <c r="D182" t="str">
         <v>2026-02-06</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Road To Osshland III - EP</v>
+        <v>Common Ground - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>3:47</v>
+        <v>1:42</v>
       </c>
       <c r="H182" t="str">
-        <v>Black Fortune</v>
+        <v>ELIO</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/black-fortune/557044567</v>
+        <v>https://music.apple.com/us/artist/elio/1501417625</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/buy-what-u-want/1872511292</v>
+        <v>https://music.apple.com/us/album/common-ground/1852654920</v>
       </c>
       <c r="L182" t="str">
-        <v>Buy What U Want - Black Fortune</v>
+        <v>Common Ground - ELIO</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Common Ground</v>
+        <v>Cellophane</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/common-ground/1852654933</v>
+        <v>https://music.apple.com/us/song/cellophane/1868833598</v>
       </c>
       <c r="D183" t="str">
         <v>2026-02-06</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Common Ground - Single</v>
+        <v>Cellophane - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>1:42</v>
+        <v>4:21</v>
       </c>
       <c r="H183" t="str">
-        <v>ELIO</v>
+        <v>Maddie Zahm</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/elio/1501417625</v>
+        <v>https://music.apple.com/us/artist/maddie-zahm/1397016641</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/common-ground/1852654920</v>
+        <v>https://music.apple.com/us/album/cellophane/1868833594</v>
       </c>
       <c r="L183" t="str">
-        <v>Common Ground - ELIO</v>
+        <v>Cellophane - Maddie Zahm</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Cellophane</v>
+        <v>96 Camry</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/cellophane/1868833598</v>
+        <v>https://music.apple.com/us/song/96-camry/1867251408</v>
       </c>
       <c r="D184" t="str">
         <v>2026-02-06</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>Cellophane - Single</v>
+        <v>PRAY FOR ME</v>
       </c>
       <c r="G184" t="str">
-        <v>4:21</v>
+        <v>3:15</v>
       </c>
       <c r="H184" t="str">
-        <v>Maddie Zahm</v>
+        <v>RAAHiiM</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/maddie-zahm/1397016641</v>
+        <v>https://music.apple.com/us/artist/raahiim/1539090681</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/cellophane/1868833594</v>
+        <v>https://music.apple.com/us/album/96-camry/1867251391</v>
       </c>
       <c r="L184" t="str">
-        <v>Cellophane - Maddie Zahm</v>
+        <v>96 Camry - RAAHiiM</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>96 Camry</v>
+        <v>La Allstar</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/96-camry/1867251408</v>
+        <v>https://music.apple.com/us/song/la-allstar/1867796343</v>
       </c>
       <c r="D185" t="str">
         <v>2026-02-06</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>PRAY FOR ME</v>
+        <v>La Allstar - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>3:15</v>
+        <v>2:49</v>
       </c>
       <c r="H185" t="str">
-        <v>RAAHiiM</v>
+        <v>ELIKAI</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/raahiim/1539090681</v>
+        <v>https://music.apple.com/us/artist/elikai/1764453112</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/96-camry/1867251391</v>
+        <v>https://music.apple.com/us/album/la-allstar/1867796342</v>
       </c>
       <c r="L185" t="str">
-        <v>96 Camry - RAAHiiM</v>
+        <v>La Allstar - ELIKAI</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>La Allstar</v>
+        <v>Luka</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/la-allstar/1867796343</v>
+        <v>https://music.apple.com/us/song/luka/1869396162</v>
       </c>
       <c r="D186" t="str">
         <v>2026-02-06</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>La Allstar - Single</v>
+        <v>Luka - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>2:49</v>
+        <v>2:07</v>
       </c>
       <c r="H186" t="str">
-        <v>ELIKAI</v>
+        <v>Fonta</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/elikai/1764453112</v>
+        <v>https://music.apple.com/us/artist/fonta/1757885481</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/la-allstar/1867796342</v>
+        <v>https://music.apple.com/us/album/luka/1869396161</v>
       </c>
       <c r="L186" t="str">
-        <v>La Allstar - ELIKAI</v>
+        <v>Luka - Fonta</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Luka</v>
+        <v>Ganas De Tenerla</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/luka/1869396162</v>
+        <v>https://music.apple.com/us/song/ganas-de-tenerla/1870909222</v>
       </c>
       <c r="D187" t="str">
         <v>2026-02-06</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Luka - Single</v>
+        <v>Ganas De Tenerla - Single</v>
       </c>
       <c r="G187" t="str">
-        <v>2:07</v>
+        <v>3:06</v>
       </c>
       <c r="H187" t="str">
-        <v>Fonta</v>
+        <v>Silvestre Dangond</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/fonta/1757885481</v>
+        <v>https://music.apple.com/us/artist/silvestre-dangond/311205761</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/luka/1869396161</v>
+        <v>https://music.apple.com/us/album/ganas-de-tenerla/1870909219</v>
       </c>
       <c r="L187" t="str">
-        <v>Luka - Fonta</v>
+        <v>Ganas De Tenerla - Silvestre Dangond</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Ganas De Tenerla</v>
+        <v>In My Blue</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/ganas-de-tenerla/1870909222</v>
+        <v>https://music.apple.com/us/song/in-my-blue/1838571293</v>
       </c>
       <c r="D188" t="str">
         <v>2026-02-06</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Ganas De Tenerla - Single</v>
+        <v>Doomsday...Don't Leave Me Here</v>
       </c>
       <c r="G188" t="str">
-        <v>3:06</v>
+        <v>3:26</v>
       </c>
       <c r="H188" t="str">
-        <v>Silvestre Dangond</v>
+        <v>Rosie Carney</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/silvestre-dangond/311205761</v>
+        <v>https://music.apple.com/us/artist/rosie-carney/1057803106</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/ganas-de-tenerla/1870909219</v>
+        <v>https://music.apple.com/us/album/in-my-blue/1838571277</v>
       </c>
       <c r="L188" t="str">
-        <v>Ganas De Tenerla - Silvestre Dangond</v>
+        <v>In My Blue - Rosie Carney</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>In My Blue</v>
+        <v>Living With It (feat. Feist)</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/in-my-blue/1838571293</v>
+        <v>https://music.apple.com/us/song/living-with-it-feat-feist/1860115264</v>
       </c>
       <c r="D189" t="str">
         <v>2026-02-06</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Doomsday...Don't Leave Me Here</v>
+        <v>Hurts Like Hell</v>
       </c>
       <c r="G189" t="str">
-        <v>3:26</v>
+        <v>3:20</v>
       </c>
       <c r="H189" t="str">
-        <v>Rosie Carney</v>
+        <v>Charlotte Cornfield</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/rosie-carney/1057803106</v>
+        <v>https://music.apple.com/us/artist/charlotte-cornfield/281901047</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/in-my-blue/1838571277</v>
+        <v>https://music.apple.com/us/album/living-with-it-feat-feist/1860115035</v>
       </c>
       <c r="L189" t="str">
-        <v>In My Blue - Rosie Carney</v>
+        <v>Living With It (feat. Feist) - Charlotte Cornfield</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Living With It (feat. Feist)</v>
+        <v>Silently</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/living-with-it-feat-feist/1860115264</v>
+        <v>https://music.apple.com/us/song/silently/1841629898</v>
       </c>
       <c r="D190" t="str">
         <v>2026-02-06</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Hurts Like Hell</v>
+        <v>Croak Dream</v>
       </c>
       <c r="G190" t="str">
-        <v>3:20</v>
+        <v>3:29</v>
       </c>
       <c r="H190" t="str">
-        <v>Charlotte Cornfield</v>
+        <v>Puma Blue</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/charlotte-cornfield/281901047</v>
+        <v>https://music.apple.com/us/artist/puma-blue/1231178386</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/living-with-it-feat-feist/1860115035</v>
+        <v>https://music.apple.com/us/album/silently/1841629444</v>
       </c>
       <c r="L190" t="str">
-        <v>Living With It (feat. Feist) - Charlotte Cornfield</v>
+        <v>Silently - Puma Blue</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Silently</v>
+        <v>Ashes &amp; Smoke</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/silently/1841629898</v>
+        <v>https://music.apple.com/us/song/ashes-smoke/1871026508</v>
       </c>
       <c r="D191" t="str">
         <v>2026-02-06</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Croak Dream</v>
+        <v>Ashes &amp; Smoke - Single</v>
       </c>
       <c r="G191" t="str">
-        <v>3:29</v>
+        <v>3:05</v>
       </c>
       <c r="H191" t="str">
-        <v>Puma Blue</v>
+        <v>Anna Graves</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/u